--- a/bodegas/LJ-05.xlsx
+++ b/bodegas/LJ-05.xlsx
@@ -9954,10 +9954,10 @@
         <v>78</v>
       </c>
       <c r="N219" t="n">
-        <v>4242.3899305556</v>
+        <v>4193.85</v>
       </c>
       <c r="O219" t="n">
-        <v>330906.4145833368</v>
+        <v>327120.3</v>
       </c>
       <c r="P219" t="n">
         <v>7500</v>
@@ -15991,10 +15991,10 @@
         <v>20</v>
       </c>
       <c r="N354" t="n">
-        <v>4254.3242335766</v>
+        <v>4163.1601459854</v>
       </c>
       <c r="O354" t="n">
-        <v>85086.484671532</v>
+        <v>83263.202919708</v>
       </c>
       <c r="P354" t="n">
         <v>6700</v>
@@ -16129,10 +16129,10 @@
         <v>105</v>
       </c>
       <c r="N357" t="n">
-        <v>5234.4433367983</v>
+        <v>5218.1704573805</v>
       </c>
       <c r="O357" t="n">
-        <v>549616.5503638216</v>
+        <v>547907.8980249525</v>
       </c>
       <c r="P357" t="n">
         <v>8500</v>
@@ -25758,10 +25758,10 @@
         <v>156</v>
       </c>
       <c r="N566" t="n">
-        <v>2861.1357880311</v>
+        <v>2857.22</v>
       </c>
       <c r="O566" t="n">
-        <v>446337.1829328517</v>
+        <v>445726.3199999999</v>
       </c>
       <c r="P566" t="n">
         <v>4900</v>

--- a/bodegas/LJ-05.xlsx
+++ b/bodegas/LJ-05.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-04</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-05</t>
         </is>
       </c>
     </row>
@@ -738,10 +738,10 @@
         <v>3</v>
       </c>
       <c r="N8" t="n">
-        <v>74676.655510204</v>
+        <v>74676.654222222</v>
       </c>
       <c r="O8" t="n">
-        <v>224029.966530612</v>
+        <v>224029.962666666</v>
       </c>
       <c r="P8" t="n">
         <v>144900</v>
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -984,19 +984,19 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="N14" t="n">
-        <v>3376.7465222073</v>
+        <v>3376.746520334</v>
       </c>
       <c r="O14" t="n">
-        <v>459237.5270201928</v>
+        <v>452484.033724756</v>
       </c>
       <c r="P14" t="n">
         <v>4500</v>
       </c>
       <c r="Q14" t="n">
-        <v>612000</v>
+        <v>603000</v>
       </c>
     </row>
     <row r="15">
@@ -3100,10 +3100,10 @@
         <v>41</v>
       </c>
       <c r="N64" t="n">
-        <v>15711.966415094</v>
+        <v>15711.966317829</v>
       </c>
       <c r="O64" t="n">
-        <v>644190.6230188541</v>
+        <v>644190.619030989</v>
       </c>
       <c r="P64" t="n">
         <v>28500</v>
@@ -3822,10 +3822,10 @@
         <v>1</v>
       </c>
       <c r="N81" t="n">
-        <v>56906.799135802</v>
+        <v>56906.800422535</v>
       </c>
       <c r="O81" t="n">
-        <v>56906.799135802</v>
+        <v>56906.800422535</v>
       </c>
       <c r="P81" t="n">
         <v>95900</v>
@@ -3904,7 +3904,7 @@
         </is>
       </c>
       <c r="J83" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K83" t="n">
         <v>0</v>
@@ -3913,19 +3913,19 @@
         <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N83" t="n">
-        <v>141416.8844164</v>
+        <v>141416.8844586</v>
       </c>
       <c r="O83" t="n">
-        <v>141416.8844164</v>
+        <v>848501.3067516</v>
       </c>
       <c r="P83" t="n">
         <v>251900</v>
       </c>
       <c r="Q83" t="n">
-        <v>251900</v>
+        <v>1511400</v>
       </c>
     </row>
     <row r="84">
@@ -3958,10 +3958,10 @@
         <v>6</v>
       </c>
       <c r="N84" t="n">
-        <v>200072.19889655</v>
+        <v>200072.19902098</v>
       </c>
       <c r="O84" t="n">
-        <v>1200433.1933793</v>
+        <v>1200433.19412588</v>
       </c>
       <c r="P84" t="n">
         <v>312000</v>
@@ -4096,10 +4096,10 @@
         <v>1</v>
       </c>
       <c r="N87" t="n">
-        <v>263530.18</v>
+        <v>263530.179</v>
       </c>
       <c r="O87" t="n">
-        <v>263530.18</v>
+        <v>263530.179</v>
       </c>
       <c r="P87" t="n">
         <v>402900</v>
@@ -4377,10 +4377,10 @@
         <v>8</v>
       </c>
       <c r="N94" t="n">
-        <v>61666.873832487</v>
+        <v>61666.873842239</v>
       </c>
       <c r="O94" t="n">
-        <v>493334.990659896</v>
+        <v>493334.990737912</v>
       </c>
       <c r="P94" t="n">
         <v>98900</v>
@@ -5846,7 +5846,7 @@
         </is>
       </c>
       <c r="J128" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="K128" t="n">
         <v>0</v>
@@ -5855,19 +5855,19 @@
         <v>0</v>
       </c>
       <c r="M128" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="N128" t="n">
-        <v>3340.6800775194</v>
+        <v>3340.6800784314</v>
       </c>
       <c r="O128" t="n">
-        <v>30066.1206976746</v>
+        <v>10022.0402352942</v>
       </c>
       <c r="P128" t="n">
         <v>7100</v>
       </c>
       <c r="Q128" t="n">
-        <v>63900</v>
+        <v>21300</v>
       </c>
     </row>
     <row r="129">
@@ -6513,7 +6513,7 @@
         </is>
       </c>
       <c r="J143" t="n">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="K143" t="n">
         <v>0</v>
@@ -6522,19 +6522,19 @@
         <v>0</v>
       </c>
       <c r="M143" t="n">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="N143" t="n">
         <v>2833</v>
       </c>
       <c r="O143" t="n">
-        <v>2096420</v>
+        <v>2087921</v>
       </c>
       <c r="P143" t="n">
         <v>3500</v>
       </c>
       <c r="Q143" t="n">
-        <v>2590000</v>
+        <v>2579500</v>
       </c>
     </row>
     <row r="144">
@@ -6554,7 +6554,7 @@
         </is>
       </c>
       <c r="J144" t="n">
-        <v>1435</v>
+        <v>1426</v>
       </c>
       <c r="K144" t="n">
         <v>0</v>
@@ -6563,19 +6563,19 @@
         <v>0</v>
       </c>
       <c r="M144" t="n">
-        <v>1435</v>
+        <v>1426</v>
       </c>
       <c r="N144" t="n">
         <v>1726.32</v>
       </c>
       <c r="O144" t="n">
-        <v>2477269.2</v>
+        <v>2461732.32</v>
       </c>
       <c r="P144" t="n">
         <v>1500</v>
       </c>
       <c r="Q144" t="n">
-        <v>2152500</v>
+        <v>2139000</v>
       </c>
     </row>
     <row r="145">
@@ -7591,10 +7591,10 @@
         <v>736</v>
       </c>
       <c r="N167" t="n">
-        <v>3158.8608123465</v>
+        <v>3158.860813208</v>
       </c>
       <c r="O167" t="n">
-        <v>2324921.557887024</v>
+        <v>2324921.558521088</v>
       </c>
       <c r="P167" t="n">
         <v>5600</v>
@@ -7671,7 +7671,7 @@
         </is>
       </c>
       <c r="J169" t="n">
-        <v>101</v>
+        <v>52</v>
       </c>
       <c r="K169" t="n">
         <v>0</v>
@@ -7680,19 +7680,19 @@
         <v>0</v>
       </c>
       <c r="M169" t="n">
-        <v>101</v>
+        <v>52</v>
       </c>
       <c r="N169" t="n">
         <v>519</v>
       </c>
       <c r="O169" t="n">
-        <v>52419</v>
+        <v>26988</v>
       </c>
       <c r="P169" t="n">
         <v>850</v>
       </c>
       <c r="Q169" t="n">
-        <v>85850</v>
+        <v>44200</v>
       </c>
     </row>
     <row r="170">
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="J172" t="n">
-        <v>123</v>
+        <v>99</v>
       </c>
       <c r="K172" t="n">
         <v>0</v>
@@ -7818,19 +7818,19 @@
         <v>0</v>
       </c>
       <c r="M172" t="n">
-        <v>123</v>
+        <v>99</v>
       </c>
       <c r="N172" t="n">
         <v>1026.13</v>
       </c>
       <c r="O172" t="n">
-        <v>126213.99</v>
+        <v>101586.87</v>
       </c>
       <c r="P172" t="n">
         <v>1900</v>
       </c>
       <c r="Q172" t="n">
-        <v>233700</v>
+        <v>188100</v>
       </c>
     </row>
     <row r="173">
@@ -7855,7 +7855,7 @@
         </is>
       </c>
       <c r="J173" t="n">
-        <v>1875</v>
+        <v>1815</v>
       </c>
       <c r="K173" t="n">
         <v>0</v>
@@ -7864,19 +7864,19 @@
         <v>0</v>
       </c>
       <c r="M173" t="n">
-        <v>1875</v>
+        <v>1815</v>
       </c>
       <c r="N173" t="n">
         <v>156.25</v>
       </c>
       <c r="O173" t="n">
-        <v>292968.75</v>
+        <v>283593.75</v>
       </c>
       <c r="P173" t="n">
         <v>250</v>
       </c>
       <c r="Q173" t="n">
-        <v>468750</v>
+        <v>453750</v>
       </c>
     </row>
     <row r="174">
@@ -8097,10 +8097,10 @@
         <v>14</v>
       </c>
       <c r="N178" t="n">
-        <v>3795.7100070286</v>
+        <v>3795.7100070299</v>
       </c>
       <c r="O178" t="n">
-        <v>53139.9400984004</v>
+        <v>53139.94009841861</v>
       </c>
       <c r="P178" t="n">
         <v>6200</v>
@@ -8405,7 +8405,7 @@
         </is>
       </c>
       <c r="J185" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K185" t="n">
         <v>0</v>
@@ -8414,19 +8414,19 @@
         <v>0</v>
       </c>
       <c r="M185" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N185" t="n">
-        <v>4967.81144</v>
+        <v>4967.8119354839</v>
       </c>
       <c r="O185" t="n">
-        <v>501748.95544</v>
+        <v>496781.19354839</v>
       </c>
       <c r="P185" t="n">
         <v>7500</v>
       </c>
       <c r="Q185" t="n">
-        <v>757500</v>
+        <v>750000</v>
       </c>
     </row>
     <row r="186">
@@ -8446,7 +8446,7 @@
         </is>
       </c>
       <c r="J186" t="n">
-        <v>184</v>
+        <v>164</v>
       </c>
       <c r="K186" t="n">
         <v>0</v>
@@ -8455,19 +8455,19 @@
         <v>0</v>
       </c>
       <c r="M186" t="n">
-        <v>184</v>
+        <v>164</v>
       </c>
       <c r="N186" t="n">
         <v>180</v>
       </c>
       <c r="O186" t="n">
-        <v>33120</v>
+        <v>29520</v>
       </c>
       <c r="P186" t="n">
         <v>220</v>
       </c>
       <c r="Q186" t="n">
-        <v>40480</v>
+        <v>36080</v>
       </c>
     </row>
     <row r="187">
@@ -9047,10 +9047,10 @@
         <v>14</v>
       </c>
       <c r="N199" t="n">
-        <v>3594.2542686567</v>
+        <v>3594.2542583732</v>
       </c>
       <c r="O199" t="n">
-        <v>50319.5597611938</v>
+        <v>50319.5596172248</v>
       </c>
       <c r="P199" t="n">
         <v>6500</v>
@@ -9130,7 +9130,7 @@
         </is>
       </c>
       <c r="J201" t="n">
-        <v>2088</v>
+        <v>2060</v>
       </c>
       <c r="K201" t="n">
         <v>0</v>
@@ -9139,19 +9139,19 @@
         <v>0</v>
       </c>
       <c r="M201" t="n">
-        <v>2088</v>
+        <v>2060</v>
       </c>
       <c r="N201" t="n">
         <v>489.88</v>
       </c>
       <c r="O201" t="n">
-        <v>1022869.44</v>
+        <v>1009152.8</v>
       </c>
       <c r="P201" t="n">
         <v>700</v>
       </c>
       <c r="Q201" t="n">
-        <v>1461600</v>
+        <v>1442000</v>
       </c>
     </row>
     <row r="202">
@@ -9587,7 +9587,7 @@
         </is>
       </c>
       <c r="J211" t="n">
-        <v>2472</v>
+        <v>2471</v>
       </c>
       <c r="K211" t="n">
         <v>0</v>
@@ -9596,19 +9596,19 @@
         <v>0</v>
       </c>
       <c r="M211" t="n">
-        <v>2472</v>
+        <v>2471</v>
       </c>
       <c r="N211" t="n">
-        <v>19098.750004659</v>
+        <v>19098.75000466</v>
       </c>
       <c r="O211" t="n">
-        <v>47212110.01151705</v>
+        <v>47193011.26151486</v>
       </c>
       <c r="P211" t="n">
         <v>15000</v>
       </c>
       <c r="Q211" t="n">
-        <v>37080000</v>
+        <v>37065000</v>
       </c>
     </row>
     <row r="212">
@@ -9942,7 +9942,7 @@
         </is>
       </c>
       <c r="J219" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="K219" t="n">
         <v>0</v>
@@ -9951,19 +9951,19 @@
         <v>0</v>
       </c>
       <c r="M219" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="N219" t="n">
         <v>4193.85</v>
       </c>
       <c r="O219" t="n">
-        <v>327120.3</v>
+        <v>301957.2</v>
       </c>
       <c r="P219" t="n">
         <v>7500</v>
       </c>
       <c r="Q219" t="n">
-        <v>585000</v>
+        <v>540000</v>
       </c>
     </row>
     <row r="220">
@@ -9991,7 +9991,7 @@
         </is>
       </c>
       <c r="J220" t="n">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="K220" t="n">
         <v>0</v>
@@ -10000,19 +10000,19 @@
         <v>0</v>
       </c>
       <c r="M220" t="n">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="N220" t="n">
-        <v>3041.6600119617</v>
+        <v>3041.6600120048</v>
       </c>
       <c r="O220" t="n">
-        <v>444082.3617464082</v>
+        <v>425832.401680672</v>
       </c>
       <c r="P220" t="n">
         <v>5500</v>
       </c>
       <c r="Q220" t="n">
-        <v>803000</v>
+        <v>770000</v>
       </c>
     </row>
     <row r="221">
@@ -10083,7 +10083,7 @@
         </is>
       </c>
       <c r="J222" t="n">
-        <v>558</v>
+        <v>549</v>
       </c>
       <c r="K222" t="n">
         <v>0</v>
@@ -10092,19 +10092,19 @@
         <v>0</v>
       </c>
       <c r="M222" t="n">
-        <v>558</v>
+        <v>549</v>
       </c>
       <c r="N222" t="n">
-        <v>1592.5679397781</v>
+        <v>1592.567877551</v>
       </c>
       <c r="O222" t="n">
-        <v>888652.9103961798</v>
+        <v>874319.764775499</v>
       </c>
       <c r="P222" t="n">
         <v>3900</v>
       </c>
       <c r="Q222" t="n">
-        <v>2176200</v>
+        <v>2141100</v>
       </c>
     </row>
     <row r="223">
@@ -10442,7 +10442,7 @@
         </is>
       </c>
       <c r="J230" t="n">
-        <v>292</v>
+        <v>252</v>
       </c>
       <c r="K230" t="n">
         <v>0</v>
@@ -10451,19 +10451,19 @@
         <v>0</v>
       </c>
       <c r="M230" t="n">
-        <v>292</v>
+        <v>252</v>
       </c>
       <c r="N230" t="n">
         <v>1770.37</v>
       </c>
       <c r="O230" t="n">
-        <v>516948.04</v>
+        <v>446133.24</v>
       </c>
       <c r="P230" t="n">
         <v>3900</v>
       </c>
       <c r="Q230" t="n">
-        <v>1138800</v>
+        <v>982800</v>
       </c>
     </row>
     <row r="231">
@@ -10620,7 +10620,7 @@
         </is>
       </c>
       <c r="J234" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K234" t="n">
         <v>0</v>
@@ -10629,19 +10629,19 @@
         <v>0</v>
       </c>
       <c r="M234" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="N234" t="n">
         <v>1530.63</v>
       </c>
       <c r="O234" t="n">
-        <v>139287.33</v>
+        <v>137756.7</v>
       </c>
       <c r="P234" t="n">
         <v>2900</v>
       </c>
       <c r="Q234" t="n">
-        <v>263900</v>
+        <v>261000</v>
       </c>
     </row>
     <row r="235">
@@ -10708,7 +10708,7 @@
         </is>
       </c>
       <c r="J236" t="n">
-        <v>2342</v>
+        <v>2338</v>
       </c>
       <c r="K236" t="n">
         <v>0</v>
@@ -10717,19 +10717,19 @@
         <v>0</v>
       </c>
       <c r="M236" t="n">
-        <v>2342</v>
+        <v>2338</v>
       </c>
       <c r="N236" t="n">
         <v>1387.55</v>
       </c>
       <c r="O236" t="n">
-        <v>3249642.1</v>
+        <v>3244091.9</v>
       </c>
       <c r="P236" t="n">
         <v>2300</v>
       </c>
       <c r="Q236" t="n">
-        <v>5386600</v>
+        <v>5377400</v>
       </c>
     </row>
     <row r="237">
@@ -11398,7 +11398,7 @@
         </is>
       </c>
       <c r="J251" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K251" t="n">
         <v>0</v>
@@ -11407,19 +11407,19 @@
         <v>0</v>
       </c>
       <c r="M251" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="N251" t="n">
-        <v>1630.9228476208</v>
+        <v>1630.9229073724</v>
       </c>
       <c r="O251" t="n">
-        <v>195710.741714496</v>
+        <v>192448.9030699432</v>
       </c>
       <c r="P251" t="n">
         <v>2500</v>
       </c>
       <c r="Q251" t="n">
-        <v>300000</v>
+        <v>295000</v>
       </c>
     </row>
     <row r="252">
@@ -11444,7 +11444,7 @@
         </is>
       </c>
       <c r="J252" t="n">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="K252" t="n">
         <v>0</v>
@@ -11453,19 +11453,19 @@
         <v>0</v>
       </c>
       <c r="M252" t="n">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="N252" t="n">
-        <v>1550.1927793589</v>
+        <v>1550.1928456407</v>
       </c>
       <c r="O252" t="n">
-        <v>410801.0865301085</v>
+        <v>404600.3327122227</v>
       </c>
       <c r="P252" t="n">
         <v>2500</v>
       </c>
       <c r="Q252" t="n">
-        <v>662500</v>
+        <v>652500</v>
       </c>
     </row>
     <row r="253">
@@ -11490,7 +11490,7 @@
         </is>
       </c>
       <c r="J253" t="n">
-        <v>694</v>
+        <v>687</v>
       </c>
       <c r="K253" t="n">
         <v>0</v>
@@ -11499,19 +11499,19 @@
         <v>0</v>
       </c>
       <c r="M253" t="n">
-        <v>694</v>
+        <v>687</v>
       </c>
       <c r="N253" t="n">
-        <v>2403.5096714419</v>
+        <v>2403.5097473321</v>
       </c>
       <c r="O253" t="n">
-        <v>1668035.711980679</v>
+        <v>1651211.196417153</v>
       </c>
       <c r="P253" t="n">
         <v>3500</v>
       </c>
       <c r="Q253" t="n">
-        <v>2429000</v>
+        <v>2404500</v>
       </c>
     </row>
     <row r="254">
@@ -11577,7 +11577,7 @@
         </is>
       </c>
       <c r="J255" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K255" t="n">
         <v>0</v>
@@ -11586,19 +11586,19 @@
         <v>0</v>
       </c>
       <c r="M255" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N255" t="n">
         <v>11507.72</v>
       </c>
       <c r="O255" t="n">
-        <v>552370.5599999999</v>
+        <v>540862.84</v>
       </c>
       <c r="P255" t="n">
         <v>25800</v>
       </c>
       <c r="Q255" t="n">
-        <v>1238400</v>
+        <v>1212600</v>
       </c>
     </row>
     <row r="256">
@@ -12589,7 +12589,7 @@
         </is>
       </c>
       <c r="J278" t="n">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="K278" t="n">
         <v>0</v>
@@ -12598,19 +12598,19 @@
         <v>0</v>
       </c>
       <c r="M278" t="n">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="N278" t="n">
         <v>2517.22</v>
       </c>
       <c r="O278" t="n">
-        <v>641891.1</v>
+        <v>631822.22</v>
       </c>
       <c r="P278" t="n">
         <v>4200</v>
       </c>
       <c r="Q278" t="n">
-        <v>1071000</v>
+        <v>1054200</v>
       </c>
     </row>
     <row r="279">
@@ -12683,10 +12683,10 @@
         <v>20</v>
       </c>
       <c r="N280" t="n">
-        <v>22485.695964126</v>
+        <v>22485.695955056</v>
       </c>
       <c r="O280" t="n">
-        <v>449713.91928252</v>
+        <v>449713.91910112</v>
       </c>
       <c r="P280" t="n">
         <v>36500</v>
@@ -12937,10 +12937,10 @@
         <v>64</v>
       </c>
       <c r="N286" t="n">
-        <v>2680.739700672</v>
+        <v>2680.739700489</v>
       </c>
       <c r="O286" t="n">
-        <v>171567.340843008</v>
+        <v>171567.340831296</v>
       </c>
       <c r="P286" t="n">
         <v>4900</v>
@@ -13191,7 +13191,7 @@
         </is>
       </c>
       <c r="J292" t="n">
-        <v>593</v>
+        <v>581</v>
       </c>
       <c r="K292" t="n">
         <v>0</v>
@@ -13200,19 +13200,19 @@
         <v>0</v>
       </c>
       <c r="M292" t="n">
-        <v>593</v>
+        <v>581</v>
       </c>
       <c r="N292" t="n">
         <v>1651</v>
       </c>
       <c r="O292" t="n">
-        <v>979043</v>
+        <v>959231</v>
       </c>
       <c r="P292" t="n">
         <v>2500</v>
       </c>
       <c r="Q292" t="n">
-        <v>1482500</v>
+        <v>1452500</v>
       </c>
     </row>
     <row r="293">
@@ -13237,7 +13237,7 @@
         </is>
       </c>
       <c r="J293" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="K293" t="n">
         <v>0</v>
@@ -13246,19 +13246,19 @@
         <v>0</v>
       </c>
       <c r="M293" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="N293" t="n">
-        <v>998.76125748503</v>
+        <v>998.76125816993</v>
       </c>
       <c r="O293" t="n">
-        <v>57928.15293413174</v>
+        <v>55930.63045751608</v>
       </c>
       <c r="P293" t="n">
         <v>1600</v>
       </c>
       <c r="Q293" t="n">
-        <v>92800</v>
+        <v>89600</v>
       </c>
     </row>
     <row r="294">
@@ -13344,10 +13344,10 @@
         <v>126</v>
       </c>
       <c r="N295" t="n">
-        <v>4285.1951469098</v>
+        <v>4285.1951678535</v>
       </c>
       <c r="O295" t="n">
-        <v>539934.5885106348</v>
+        <v>539934.591149541</v>
       </c>
       <c r="P295" t="n">
         <v>6900</v>
@@ -14046,7 +14046,7 @@
         </is>
       </c>
       <c r="J311" t="n">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="K311" t="n">
         <v>0</v>
@@ -14055,19 +14055,19 @@
         <v>0</v>
       </c>
       <c r="M311" t="n">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="N311" t="n">
         <v>4793.53</v>
       </c>
       <c r="O311" t="n">
-        <v>364308.28</v>
+        <v>306785.92</v>
       </c>
       <c r="P311" t="n">
         <v>7900</v>
       </c>
       <c r="Q311" t="n">
-        <v>600400</v>
+        <v>505600</v>
       </c>
     </row>
     <row r="312">
@@ -14329,10 +14329,10 @@
         <v>28</v>
       </c>
       <c r="N317" t="n">
-        <v>27123.765285451</v>
+        <v>27123.765268022</v>
       </c>
       <c r="O317" t="n">
-        <v>759465.4279926281</v>
+        <v>759465.4275046161</v>
       </c>
       <c r="P317" t="n">
         <v>44500</v>
@@ -14665,7 +14665,7 @@
         </is>
       </c>
       <c r="J325" t="n">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="K325" t="n">
         <v>0</v>
@@ -14674,19 +14674,19 @@
         <v>0</v>
       </c>
       <c r="M325" t="n">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="N325" t="n">
-        <v>1560.9980701754</v>
+        <v>1560.9982458387</v>
       </c>
       <c r="O325" t="n">
-        <v>280979.652631572</v>
+        <v>234149.736875805</v>
       </c>
       <c r="P325" t="n">
         <v>2900</v>
       </c>
       <c r="Q325" t="n">
-        <v>522000</v>
+        <v>435000</v>
       </c>
     </row>
     <row r="326">
@@ -15749,7 +15749,7 @@
         </is>
       </c>
       <c r="J349" t="n">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="K349" t="n">
         <v>0</v>
@@ -15758,19 +15758,19 @@
         <v>0</v>
       </c>
       <c r="M349" t="n">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="N349" t="n">
         <v>2634.61</v>
       </c>
       <c r="O349" t="n">
-        <v>479499.02</v>
+        <v>468960.58</v>
       </c>
       <c r="P349" t="n">
         <v>4200</v>
       </c>
       <c r="Q349" t="n">
-        <v>764400</v>
+        <v>747600</v>
       </c>
     </row>
     <row r="350">
@@ -15795,7 +15795,7 @@
         </is>
       </c>
       <c r="J350" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="K350" t="n">
         <v>0</v>
@@ -15804,19 +15804,19 @@
         <v>0</v>
       </c>
       <c r="M350" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="N350" t="n">
-        <v>3113.890023175</v>
+        <v>3113.8900237812</v>
       </c>
       <c r="O350" t="n">
-        <v>323844.5624102</v>
+        <v>317616.7824256824</v>
       </c>
       <c r="P350" t="n">
         <v>5000</v>
       </c>
       <c r="Q350" t="n">
-        <v>520000</v>
+        <v>510000</v>
       </c>
     </row>
     <row r="351">
@@ -15841,7 +15841,7 @@
         </is>
       </c>
       <c r="J351" t="n">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="K351" t="n">
         <v>0</v>
@@ -15850,19 +15850,19 @@
         <v>0</v>
       </c>
       <c r="M351" t="n">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="N351" t="n">
         <v>5569.98</v>
       </c>
       <c r="O351" t="n">
-        <v>462308.34</v>
+        <v>367618.68</v>
       </c>
       <c r="P351" t="n">
         <v>8900</v>
       </c>
       <c r="Q351" t="n">
-        <v>738700</v>
+        <v>587400</v>
       </c>
     </row>
     <row r="352">
@@ -15933,7 +15933,7 @@
         </is>
       </c>
       <c r="J353" t="n">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="K353" t="n">
         <v>0</v>
@@ -15942,19 +15942,19 @@
         <v>0</v>
       </c>
       <c r="M353" t="n">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="N353" t="n">
         <v>5410.72</v>
       </c>
       <c r="O353" t="n">
-        <v>703393.6</v>
+        <v>681750.7200000001</v>
       </c>
       <c r="P353" t="n">
         <v>8700</v>
       </c>
       <c r="Q353" t="n">
-        <v>1131000</v>
+        <v>1096200</v>
       </c>
     </row>
     <row r="354">
@@ -15979,7 +15979,7 @@
         </is>
       </c>
       <c r="J354" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K354" t="n">
         <v>0</v>
@@ -15988,19 +15988,19 @@
         <v>0</v>
       </c>
       <c r="M354" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="N354" t="n">
-        <v>4163.1601459854</v>
+        <v>4163.1601515152</v>
       </c>
       <c r="O354" t="n">
-        <v>83263.202919708</v>
+        <v>70773.72257575839</v>
       </c>
       <c r="P354" t="n">
         <v>6700</v>
       </c>
       <c r="Q354" t="n">
-        <v>134000</v>
+        <v>113900</v>
       </c>
     </row>
     <row r="355">
@@ -16025,7 +16025,7 @@
         </is>
       </c>
       <c r="J355" t="n">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="K355" t="n">
         <v>0</v>
@@ -16034,19 +16034,19 @@
         <v>0</v>
       </c>
       <c r="M355" t="n">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="N355" t="n">
         <v>2495.98</v>
       </c>
       <c r="O355" t="n">
-        <v>569083.4400000001</v>
+        <v>534139.72</v>
       </c>
       <c r="P355" t="n">
         <v>4100</v>
       </c>
       <c r="Q355" t="n">
-        <v>934800</v>
+        <v>877400</v>
       </c>
     </row>
     <row r="356">
@@ -16071,7 +16071,7 @@
         </is>
       </c>
       <c r="J356" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="K356" t="n">
         <v>0</v>
@@ -16080,19 +16080,19 @@
         <v>0</v>
       </c>
       <c r="M356" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="N356" t="n">
         <v>3254.49</v>
       </c>
       <c r="O356" t="n">
-        <v>520718.4</v>
+        <v>517463.91</v>
       </c>
       <c r="P356" t="n">
         <v>5200</v>
       </c>
       <c r="Q356" t="n">
-        <v>832000</v>
+        <v>826800</v>
       </c>
     </row>
     <row r="357">
@@ -16117,7 +16117,7 @@
         </is>
       </c>
       <c r="J357" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K357" t="n">
         <v>0</v>
@@ -16126,19 +16126,19 @@
         <v>0</v>
       </c>
       <c r="M357" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="N357" t="n">
-        <v>5218.1704573805</v>
+        <v>5218.1704631579</v>
       </c>
       <c r="O357" t="n">
-        <v>547907.8980249525</v>
+        <v>542689.7281684215</v>
       </c>
       <c r="P357" t="n">
         <v>8500</v>
       </c>
       <c r="Q357" t="n">
-        <v>892500</v>
+        <v>884000</v>
       </c>
     </row>
     <row r="358">
@@ -16163,7 +16163,7 @@
         </is>
       </c>
       <c r="J358" t="n">
-        <v>207</v>
+        <v>147</v>
       </c>
       <c r="K358" t="n">
         <v>0</v>
@@ -16172,19 +16172,19 @@
         <v>0</v>
       </c>
       <c r="M358" t="n">
-        <v>207</v>
+        <v>147</v>
       </c>
       <c r="N358" t="n">
-        <v>1595.0095696489</v>
+        <v>1595.009520202</v>
       </c>
       <c r="O358" t="n">
-        <v>330166.9809173223</v>
+        <v>234466.399469694</v>
       </c>
       <c r="P358" t="n">
         <v>2600</v>
       </c>
       <c r="Q358" t="n">
-        <v>538200</v>
+        <v>382200</v>
       </c>
     </row>
     <row r="359">
@@ -16209,7 +16209,7 @@
         </is>
       </c>
       <c r="J359" t="n">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="K359" t="n">
         <v>0</v>
@@ -16218,19 +16218,19 @@
         <v>0</v>
       </c>
       <c r="M359" t="n">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="N359" t="n">
-        <v>3610.6500224972</v>
+        <v>3610.6500229095</v>
       </c>
       <c r="O359" t="n">
-        <v>191364.4511923516</v>
+        <v>148036.6509392895</v>
       </c>
       <c r="P359" t="n">
         <v>5800</v>
       </c>
       <c r="Q359" t="n">
-        <v>307400</v>
+        <v>237800</v>
       </c>
     </row>
     <row r="360">
@@ -16255,7 +16255,7 @@
         </is>
       </c>
       <c r="J360" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K360" t="n">
         <v>0</v>
@@ -16264,19 +16264,19 @@
         <v>0</v>
       </c>
       <c r="M360" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N360" t="n">
         <v>5194</v>
       </c>
       <c r="O360" t="n">
-        <v>41552</v>
+        <v>36358</v>
       </c>
       <c r="P360" t="n">
         <v>9000</v>
       </c>
       <c r="Q360" t="n">
-        <v>72000</v>
+        <v>63000</v>
       </c>
     </row>
     <row r="361">
@@ -16301,7 +16301,7 @@
         </is>
       </c>
       <c r="J361" t="n">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="K361" t="n">
         <v>0</v>
@@ -16310,19 +16310,19 @@
         <v>0</v>
       </c>
       <c r="M361" t="n">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="N361" t="n">
         <v>4227.77</v>
       </c>
       <c r="O361" t="n">
-        <v>325538.29</v>
+        <v>262121.74</v>
       </c>
       <c r="P361" t="n">
         <v>6900</v>
       </c>
       <c r="Q361" t="n">
-        <v>531300</v>
+        <v>427800</v>
       </c>
     </row>
     <row r="362">
@@ -16347,7 +16347,7 @@
         </is>
       </c>
       <c r="J362" t="n">
-        <v>187</v>
+        <v>163</v>
       </c>
       <c r="K362" t="n">
         <v>0</v>
@@ -16356,19 +16356,19 @@
         <v>0</v>
       </c>
       <c r="M362" t="n">
-        <v>187</v>
+        <v>163</v>
       </c>
       <c r="N362" t="n">
         <v>3965.02</v>
       </c>
       <c r="O362" t="n">
-        <v>741458.74</v>
+        <v>646298.26</v>
       </c>
       <c r="P362" t="n">
         <v>6500</v>
       </c>
       <c r="Q362" t="n">
-        <v>1215500</v>
+        <v>1059500</v>
       </c>
     </row>
     <row r="363">
@@ -16439,7 +16439,7 @@
         </is>
       </c>
       <c r="J364" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="K364" t="n">
         <v>0</v>
@@ -16448,19 +16448,19 @@
         <v>0</v>
       </c>
       <c r="M364" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="N364" t="n">
-        <v>1664.362204192</v>
+        <v>1664.3618458274</v>
       </c>
       <c r="O364" t="n">
-        <v>118169.716497632</v>
+        <v>111512.2436704358</v>
       </c>
       <c r="P364" t="n">
         <v>2900</v>
       </c>
       <c r="Q364" t="n">
-        <v>205900</v>
+        <v>194300</v>
       </c>
     </row>
     <row r="365">
@@ -17052,10 +17052,10 @@
         <v>147</v>
       </c>
       <c r="N377" t="n">
-        <v>1778.4724989266</v>
+        <v>1778.4725014327</v>
       </c>
       <c r="O377" t="n">
-        <v>261435.4573422102</v>
+        <v>261435.4577106069</v>
       </c>
       <c r="P377" t="n">
         <v>4900</v>
@@ -19124,7 +19124,7 @@
         </is>
       </c>
       <c r="J422" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K422" t="n">
         <v>0</v>
@@ -19133,19 +19133,19 @@
         <v>0</v>
       </c>
       <c r="M422" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N422" t="n">
         <v>28116</v>
       </c>
       <c r="O422" t="n">
-        <v>477972</v>
+        <v>449856</v>
       </c>
       <c r="P422" t="n">
         <v>45900</v>
       </c>
       <c r="Q422" t="n">
-        <v>780300</v>
+        <v>734400</v>
       </c>
     </row>
     <row r="423">
@@ -19311,7 +19311,7 @@
         </is>
       </c>
       <c r="J426" t="n">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="K426" t="n">
         <v>0</v>
@@ -19320,19 +19320,19 @@
         <v>0</v>
       </c>
       <c r="M426" t="n">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="N426" t="n">
         <v>10411</v>
       </c>
       <c r="O426" t="n">
-        <v>93699</v>
+        <v>406029</v>
       </c>
       <c r="P426" t="n">
         <v>16900</v>
       </c>
       <c r="Q426" t="n">
-        <v>152100</v>
+        <v>659100</v>
       </c>
     </row>
     <row r="427">
@@ -20234,7 +20234,7 @@
         </is>
       </c>
       <c r="J446" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="K446" t="n">
         <v>0</v>
@@ -20243,19 +20243,19 @@
         <v>0</v>
       </c>
       <c r="M446" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="N446" t="n">
-        <v>4907.821884273</v>
+        <v>4907.8218926975</v>
       </c>
       <c r="O446" t="n">
-        <v>279745.847403561</v>
+        <v>269930.2040983625</v>
       </c>
       <c r="P446" t="n">
         <v>8200</v>
       </c>
       <c r="Q446" t="n">
-        <v>467400</v>
+        <v>451000</v>
       </c>
     </row>
     <row r="447">
@@ -21248,10 +21248,10 @@
         <v>205</v>
       </c>
       <c r="N468" t="n">
-        <v>5869.1728258706</v>
+        <v>5869.1727972028</v>
       </c>
       <c r="O468" t="n">
-        <v>1203180.429303473</v>
+        <v>1203180.423426574</v>
       </c>
       <c r="P468" t="n">
         <v>9500</v>
@@ -21696,7 +21696,7 @@
         </is>
       </c>
       <c r="J478" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="K478" t="n">
         <v>0</v>
@@ -21705,19 +21705,19 @@
         <v>0</v>
       </c>
       <c r="M478" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="N478" t="n">
         <v>3898</v>
       </c>
       <c r="O478" t="n">
-        <v>101348</v>
+        <v>93552</v>
       </c>
       <c r="P478" t="n">
         <v>6900</v>
       </c>
       <c r="Q478" t="n">
-        <v>179400</v>
+        <v>165600</v>
       </c>
     </row>
     <row r="479">
@@ -21880,7 +21880,7 @@
         </is>
       </c>
       <c r="J482" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K482" t="n">
         <v>0</v>
@@ -21889,19 +21889,19 @@
         <v>0</v>
       </c>
       <c r="M482" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N482" t="n">
         <v>5682</v>
       </c>
       <c r="O482" t="n">
-        <v>539790</v>
+        <v>534108</v>
       </c>
       <c r="P482" t="n">
         <v>9900</v>
       </c>
       <c r="Q482" t="n">
-        <v>940500</v>
+        <v>930600</v>
       </c>
     </row>
     <row r="483">
@@ -22343,7 +22343,7 @@
         </is>
       </c>
       <c r="J492" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="K492" t="n">
         <v>0</v>
@@ -22352,19 +22352,19 @@
         <v>0</v>
       </c>
       <c r="M492" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="N492" t="n">
         <v>11348</v>
       </c>
       <c r="O492" t="n">
-        <v>45392</v>
+        <v>306396</v>
       </c>
       <c r="P492" t="n">
         <v>19900</v>
       </c>
       <c r="Q492" t="n">
-        <v>79600</v>
+        <v>537300</v>
       </c>
     </row>
     <row r="493">
@@ -23031,7 +23031,7 @@
         </is>
       </c>
       <c r="J507" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K507" t="n">
         <v>0</v>
@@ -23040,19 +23040,19 @@
         <v>0</v>
       </c>
       <c r="M507" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N507" t="n">
         <v>29835</v>
       </c>
       <c r="O507" t="n">
-        <v>686205</v>
+        <v>656370</v>
       </c>
       <c r="P507" t="n">
         <v>47900</v>
       </c>
       <c r="Q507" t="n">
-        <v>1101700</v>
+        <v>1053800</v>
       </c>
     </row>
     <row r="508">
@@ -23399,7 +23399,7 @@
         </is>
       </c>
       <c r="J515" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K515" t="n">
         <v>0</v>
@@ -23408,19 +23408,19 @@
         <v>0</v>
       </c>
       <c r="M515" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N515" t="n">
         <v>3639.35</v>
       </c>
       <c r="O515" t="n">
-        <v>47311.55</v>
+        <v>43672.2</v>
       </c>
       <c r="P515" t="n">
         <v>7500</v>
       </c>
       <c r="Q515" t="n">
-        <v>97500</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="516">
@@ -23445,7 +23445,7 @@
         </is>
       </c>
       <c r="J516" t="n">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="K516" t="n">
         <v>0</v>
@@ -23454,19 +23454,19 @@
         <v>0</v>
       </c>
       <c r="M516" t="n">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="N516" t="n">
         <v>1326</v>
       </c>
       <c r="O516" t="n">
-        <v>140556</v>
+        <v>119340</v>
       </c>
       <c r="P516" t="n">
         <v>2500</v>
       </c>
       <c r="Q516" t="n">
-        <v>265000</v>
+        <v>225000</v>
       </c>
     </row>
     <row r="517">
@@ -24184,7 +24184,7 @@
         </is>
       </c>
       <c r="J532" t="n">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="K532" t="n">
         <v>0</v>
@@ -24193,19 +24193,19 @@
         <v>0</v>
       </c>
       <c r="M532" t="n">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="N532" t="n">
-        <v>1516.0388192979</v>
+        <v>1516.038818618</v>
       </c>
       <c r="O532" t="n">
-        <v>401750.2871139435</v>
+        <v>394170.09284068</v>
       </c>
       <c r="P532" t="n">
         <v>2300</v>
       </c>
       <c r="Q532" t="n">
-        <v>609500</v>
+        <v>598000</v>
       </c>
     </row>
     <row r="533">
@@ -24288,10 +24288,10 @@
         <v>455</v>
       </c>
       <c r="N534" t="n">
-        <v>2458.5136620146</v>
+        <v>2458.5136155257</v>
       </c>
       <c r="O534" t="n">
-        <v>1118623.716216643</v>
+        <v>1118623.695064194</v>
       </c>
       <c r="P534" t="n">
         <v>3500</v>
@@ -24322,7 +24322,7 @@
         </is>
       </c>
       <c r="J535" t="n">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="K535" t="n">
         <v>0</v>
@@ -24331,19 +24331,19 @@
         <v>0</v>
       </c>
       <c r="M535" t="n">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="N535" t="n">
-        <v>1907.3946349467</v>
+        <v>1907.3946039604</v>
       </c>
       <c r="O535" t="n">
-        <v>221257.7776538172</v>
+        <v>209813.406435644</v>
       </c>
       <c r="P535" t="n">
         <v>2500</v>
       </c>
       <c r="Q535" t="n">
-        <v>290000</v>
+        <v>275000</v>
       </c>
     </row>
     <row r="536">
@@ -24368,7 +24368,7 @@
         </is>
       </c>
       <c r="J536" t="n">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="K536" t="n">
         <v>0</v>
@@ -24377,19 +24377,19 @@
         <v>0</v>
       </c>
       <c r="M536" t="n">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="N536" t="n">
-        <v>1771.0915140845</v>
+        <v>1771.0914991182</v>
       </c>
       <c r="O536" t="n">
-        <v>350676.119788731</v>
+        <v>345362.842328049</v>
       </c>
       <c r="P536" t="n">
         <v>2500</v>
       </c>
       <c r="Q536" t="n">
-        <v>495000</v>
+        <v>487500</v>
       </c>
     </row>
     <row r="537">
@@ -24426,10 +24426,10 @@
         <v>471</v>
       </c>
       <c r="N537" t="n">
-        <v>2079.3843256997</v>
+        <v>2079.3842820513</v>
       </c>
       <c r="O537" t="n">
-        <v>979390.0174045588</v>
+        <v>979389.9968461624</v>
       </c>
       <c r="P537" t="n">
         <v>2900</v>
@@ -24460,7 +24460,7 @@
         </is>
       </c>
       <c r="J538" t="n">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="K538" t="n">
         <v>0</v>
@@ -24469,19 +24469,19 @@
         <v>0</v>
       </c>
       <c r="M538" t="n">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="N538" t="n">
-        <v>1803.0147949081</v>
+        <v>1803.0148044218</v>
       </c>
       <c r="O538" t="n">
-        <v>627449.1486280188</v>
+        <v>616631.0631122555</v>
       </c>
       <c r="P538" t="n">
         <v>2500</v>
       </c>
       <c r="Q538" t="n">
-        <v>870000</v>
+        <v>855000</v>
       </c>
     </row>
     <row r="539">
@@ -24506,7 +24506,7 @@
         </is>
       </c>
       <c r="J539" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="K539" t="n">
         <v>0</v>
@@ -24515,19 +24515,19 @@
         <v>0</v>
       </c>
       <c r="M539" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="N539" t="n">
-        <v>3306.5955223881</v>
+        <v>3306.595494368</v>
       </c>
       <c r="O539" t="n">
-        <v>367032.1029850791</v>
+        <v>357112.313391744</v>
       </c>
       <c r="P539" t="n">
         <v>4900</v>
       </c>
       <c r="Q539" t="n">
-        <v>543900</v>
+        <v>529200</v>
       </c>
     </row>
     <row r="540">
@@ -24598,7 +24598,7 @@
         </is>
       </c>
       <c r="J541" t="n">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="K541" t="n">
         <v>0</v>
@@ -24607,19 +24607,19 @@
         <v>0</v>
       </c>
       <c r="M541" t="n">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="N541" t="n">
-        <v>2108.7893319081</v>
+        <v>2108.7893820527</v>
       </c>
       <c r="O541" t="n">
-        <v>672703.7968786838</v>
+        <v>660051.0765824951</v>
       </c>
       <c r="P541" t="n">
         <v>2900</v>
       </c>
       <c r="Q541" t="n">
-        <v>925100</v>
+        <v>907700</v>
       </c>
     </row>
     <row r="542">
@@ -24690,7 +24690,7 @@
         </is>
       </c>
       <c r="J543" t="n">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="K543" t="n">
         <v>0</v>
@@ -24699,19 +24699,19 @@
         <v>0</v>
       </c>
       <c r="M543" t="n">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="N543" t="n">
-        <v>3224.5675847458</v>
+        <v>3224.5676430401</v>
       </c>
       <c r="O543" t="n">
-        <v>1193090.006355946</v>
+        <v>1180191.757352676</v>
       </c>
       <c r="P543" t="n">
         <v>4500</v>
       </c>
       <c r="Q543" t="n">
-        <v>1665000</v>
+        <v>1647000</v>
       </c>
     </row>
     <row r="544">
@@ -24736,7 +24736,7 @@
         </is>
       </c>
       <c r="J544" t="n">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="K544" t="n">
         <v>0</v>
@@ -24745,19 +24745,19 @@
         <v>0</v>
       </c>
       <c r="M544" t="n">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="N544" t="n">
-        <v>1655.9315412844</v>
+        <v>1655.9314708603</v>
       </c>
       <c r="O544" t="n">
-        <v>506715.0516330264</v>
+        <v>501747.2356706709</v>
       </c>
       <c r="P544" t="n">
         <v>2500</v>
       </c>
       <c r="Q544" t="n">
-        <v>765000</v>
+        <v>757500</v>
       </c>
     </row>
     <row r="545">
@@ -24920,7 +24920,7 @@
         </is>
       </c>
       <c r="J548" t="n">
-        <v>307</v>
+        <v>289</v>
       </c>
       <c r="K548" t="n">
         <v>0</v>
@@ -24929,19 +24929,19 @@
         <v>0</v>
       </c>
       <c r="M548" t="n">
-        <v>307</v>
+        <v>289</v>
       </c>
       <c r="N548" t="n">
-        <v>1592.274090065</v>
+        <v>1592.2743101761</v>
       </c>
       <c r="O548" t="n">
-        <v>488828.145649955</v>
+        <v>460167.2756408929</v>
       </c>
       <c r="P548" t="n">
         <v>2500</v>
       </c>
       <c r="Q548" t="n">
-        <v>767500</v>
+        <v>722500</v>
       </c>
     </row>
     <row r="549">
@@ -25022,10 +25022,10 @@
         <v>54</v>
       </c>
       <c r="N550" t="n">
-        <v>1906.1877678571</v>
+        <v>1906.1875409836</v>
       </c>
       <c r="O550" t="n">
-        <v>102934.1394642834</v>
+        <v>102934.1272131144</v>
       </c>
       <c r="P550" t="n">
         <v>2900</v>
@@ -25056,7 +25056,7 @@
         </is>
       </c>
       <c r="J551" t="n">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="K551" t="n">
         <v>0</v>
@@ -25065,19 +25065,19 @@
         <v>0</v>
       </c>
       <c r="M551" t="n">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="N551" t="n">
-        <v>1668.6125935484</v>
+        <v>1668.6130481283</v>
       </c>
       <c r="O551" t="n">
-        <v>251960.5016258084</v>
+        <v>228599.9875935771</v>
       </c>
       <c r="P551" t="n">
         <v>2500</v>
       </c>
       <c r="Q551" t="n">
-        <v>377500</v>
+        <v>342500</v>
       </c>
     </row>
     <row r="552">
@@ -25102,7 +25102,7 @@
         </is>
       </c>
       <c r="J552" t="n">
-        <v>128</v>
+        <v>56</v>
       </c>
       <c r="K552" t="n">
         <v>0</v>
@@ -25111,19 +25111,19 @@
         <v>0</v>
       </c>
       <c r="M552" t="n">
-        <v>128</v>
+        <v>56</v>
       </c>
       <c r="N552" t="n">
-        <v>2546.986027972</v>
+        <v>2546.985477707</v>
       </c>
       <c r="O552" t="n">
-        <v>326014.211580416</v>
+        <v>142631.186751592</v>
       </c>
       <c r="P552" t="n">
         <v>3900</v>
       </c>
       <c r="Q552" t="n">
-        <v>499200</v>
+        <v>218400</v>
       </c>
     </row>
     <row r="553">
@@ -25148,7 +25148,7 @@
         </is>
       </c>
       <c r="J553" t="n">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="K553" t="n">
         <v>0</v>
@@ -25157,19 +25157,19 @@
         <v>0</v>
       </c>
       <c r="M553" t="n">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="N553" t="n">
-        <v>1259.2742318172</v>
+        <v>1259.2742532126</v>
       </c>
       <c r="O553" t="n">
-        <v>1260533.506049017</v>
+        <v>1259274.2532126</v>
       </c>
       <c r="P553" t="n">
         <v>1900</v>
       </c>
       <c r="Q553" t="n">
-        <v>1901900</v>
+        <v>1900000</v>
       </c>
     </row>
     <row r="554">
@@ -25240,7 +25240,7 @@
         </is>
       </c>
       <c r="J555" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K555" t="n">
         <v>0</v>
@@ -25249,19 +25249,19 @@
         <v>0</v>
       </c>
       <c r="M555" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N555" t="n">
         <v>2944</v>
       </c>
       <c r="O555" t="n">
-        <v>52992</v>
+        <v>50048</v>
       </c>
       <c r="P555" t="n">
         <v>4900</v>
       </c>
       <c r="Q555" t="n">
-        <v>88200</v>
+        <v>83300</v>
       </c>
     </row>
     <row r="556">
@@ -25373,7 +25373,7 @@
         </is>
       </c>
       <c r="J558" t="n">
-        <v>120</v>
+        <v>264</v>
       </c>
       <c r="K558" t="n">
         <v>0</v>
@@ -25382,19 +25382,19 @@
         <v>0</v>
       </c>
       <c r="M558" t="n">
-        <v>120</v>
+        <v>264</v>
       </c>
       <c r="N558" t="n">
         <v>1801</v>
       </c>
       <c r="O558" t="n">
-        <v>216120</v>
+        <v>475464</v>
       </c>
       <c r="P558" t="n">
         <v>2900</v>
       </c>
       <c r="Q558" t="n">
-        <v>348000</v>
+        <v>765600</v>
       </c>
     </row>
     <row r="559">
@@ -25417,7 +25417,7 @@
         </is>
       </c>
       <c r="J559" t="n">
-        <v>378</v>
+        <v>342</v>
       </c>
       <c r="K559" t="n">
         <v>0</v>
@@ -25426,19 +25426,19 @@
         <v>0</v>
       </c>
       <c r="M559" t="n">
-        <v>378</v>
+        <v>342</v>
       </c>
       <c r="N559" t="n">
-        <v>692.151995671</v>
+        <v>692.15200959024</v>
       </c>
       <c r="O559" t="n">
-        <v>261633.454363638</v>
+        <v>236715.9872798621</v>
       </c>
       <c r="P559" t="n">
         <v>1200</v>
       </c>
       <c r="Q559" t="n">
-        <v>453600</v>
+        <v>410400</v>
       </c>
     </row>
     <row r="560">
@@ -25509,7 +25509,7 @@
         </is>
       </c>
       <c r="J561" t="n">
-        <v>2491</v>
+        <v>2490</v>
       </c>
       <c r="K561" t="n">
         <v>0</v>
@@ -25518,19 +25518,19 @@
         <v>0</v>
       </c>
       <c r="M561" t="n">
-        <v>2491</v>
+        <v>2490</v>
       </c>
       <c r="N561" t="n">
-        <v>1955.2371193049</v>
+        <v>1955.2371191444</v>
       </c>
       <c r="O561" t="n">
-        <v>4870495.664188506</v>
+        <v>4868540.426669556</v>
       </c>
       <c r="P561" t="n">
         <v>3000</v>
       </c>
       <c r="Q561" t="n">
-        <v>7473000</v>
+        <v>7470000</v>
       </c>
     </row>
     <row r="562">
@@ -26420,10 +26420,10 @@
         <v>21</v>
       </c>
       <c r="N580" t="n">
-        <v>10732.241818182</v>
+        <v>10732.241860465</v>
       </c>
       <c r="O580" t="n">
-        <v>225377.078181822</v>
+        <v>225377.079069765</v>
       </c>
       <c r="P580" t="n">
         <v>25900</v>
@@ -26503,7 +26503,7 @@
         </is>
       </c>
       <c r="J582" t="n">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="K582" t="n">
         <v>0</v>
@@ -26512,19 +26512,19 @@
         <v>0</v>
       </c>
       <c r="M582" t="n">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="N582" t="n">
         <v>7103.81</v>
       </c>
       <c r="O582" t="n">
-        <v>689069.5700000001</v>
+        <v>603823.85</v>
       </c>
       <c r="P582" t="n">
         <v>8900</v>
       </c>
       <c r="Q582" t="n">
-        <v>863300</v>
+        <v>756500</v>
       </c>
     </row>
     <row r="583">
@@ -26593,7 +26593,7 @@
         </is>
       </c>
       <c r="J584" t="n">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="K584" t="n">
         <v>0</v>
@@ -26602,19 +26602,19 @@
         <v>0</v>
       </c>
       <c r="M584" t="n">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="N584" t="n">
-        <v>1690.8700087336</v>
+        <v>1690.8700087796</v>
       </c>
       <c r="O584" t="n">
-        <v>355082.701834056</v>
+        <v>334792.2617383608</v>
       </c>
       <c r="P584" t="n">
         <v>3000</v>
       </c>
       <c r="Q584" t="n">
-        <v>630000</v>
+        <v>594000</v>
       </c>
     </row>
     <row r="585">
@@ -26835,10 +26835,10 @@
         <v>30</v>
       </c>
       <c r="N589" t="n">
-        <v>3907.5003162055</v>
+        <v>3907.5003174603</v>
       </c>
       <c r="O589" t="n">
-        <v>117225.009486165</v>
+        <v>117225.009523809</v>
       </c>
       <c r="P589" t="n">
         <v>3900</v>
@@ -26916,7 +26916,7 @@
         </is>
       </c>
       <c r="J591" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K591" t="n">
         <v>0</v>
@@ -26925,19 +26925,19 @@
         <v>0</v>
       </c>
       <c r="M591" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N591" t="n">
-        <v>711.33665018328</v>
+        <v>711.33665006743</v>
       </c>
       <c r="O591" t="n">
-        <v>71845.00166851128</v>
+        <v>71133.665006743</v>
       </c>
       <c r="P591" t="n">
         <v>900</v>
       </c>
       <c r="Q591" t="n">
-        <v>90900</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="592">
@@ -27237,7 +27237,7 @@
         </is>
       </c>
       <c r="J598" t="n">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="K598" t="n">
         <v>0</v>
@@ -27246,19 +27246,19 @@
         <v>0</v>
       </c>
       <c r="M598" t="n">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="N598" t="n">
         <v>177.65</v>
       </c>
       <c r="O598" t="n">
-        <v>19541.5</v>
+        <v>10659</v>
       </c>
       <c r="P598" t="n">
         <v>300</v>
       </c>
       <c r="Q598" t="n">
-        <v>33000</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="599">
@@ -27420,7 +27420,7 @@
         </is>
       </c>
       <c r="J602" t="n">
-        <v>2915</v>
+        <v>2834</v>
       </c>
       <c r="K602" t="n">
         <v>0</v>
@@ -27429,19 +27429,19 @@
         <v>0</v>
       </c>
       <c r="M602" t="n">
-        <v>2915</v>
+        <v>2834</v>
       </c>
       <c r="N602" t="n">
-        <v>517.28716412902</v>
+        <v>517.28728171896</v>
       </c>
       <c r="O602" t="n">
-        <v>1507892.083436093</v>
+        <v>1465992.156391533</v>
       </c>
       <c r="P602" t="n">
         <v>900</v>
       </c>
       <c r="Q602" t="n">
-        <v>2623500</v>
+        <v>2550600</v>
       </c>
     </row>
     <row r="603">
@@ -27602,7 +27602,7 @@
         </is>
       </c>
       <c r="J606" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="K606" t="n">
         <v>0</v>
@@ -27611,19 +27611,19 @@
         <v>0</v>
       </c>
       <c r="M606" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="N606" t="n">
         <v>2703.52</v>
       </c>
       <c r="O606" t="n">
-        <v>24331.68</v>
+        <v>8110.559999999999</v>
       </c>
       <c r="P606" t="n">
         <v>5800</v>
       </c>
       <c r="Q606" t="n">
-        <v>52200</v>
+        <v>17400</v>
       </c>
     </row>
     <row r="607">
@@ -27651,7 +27651,7 @@
         </is>
       </c>
       <c r="J607" t="n">
-        <v>250</v>
+        <v>179</v>
       </c>
       <c r="K607" t="n">
         <v>0</v>
@@ -27660,19 +27660,19 @@
         <v>0</v>
       </c>
       <c r="M607" t="n">
-        <v>250</v>
+        <v>179</v>
       </c>
       <c r="N607" t="n">
-        <v>3110.8436976288</v>
+        <v>3110.8435374771</v>
       </c>
       <c r="O607" t="n">
-        <v>777710.9244072</v>
+        <v>556840.9932084009</v>
       </c>
       <c r="P607" t="n">
         <v>4500</v>
       </c>
       <c r="Q607" t="n">
-        <v>1125000</v>
+        <v>805500</v>
       </c>
     </row>
     <row r="608">
@@ -27695,7 +27695,7 @@
         </is>
       </c>
       <c r="J608" t="n">
-        <v>676</v>
+        <v>556</v>
       </c>
       <c r="K608" t="n">
         <v>0</v>
@@ -27704,19 +27704,19 @@
         <v>0</v>
       </c>
       <c r="M608" t="n">
-        <v>676</v>
+        <v>556</v>
       </c>
       <c r="N608" t="n">
-        <v>703.79553051727</v>
+        <v>703.79547499887</v>
       </c>
       <c r="O608" t="n">
-        <v>475765.7786296745</v>
+        <v>391310.2840993717</v>
       </c>
       <c r="P608" t="n">
         <v>900</v>
       </c>
       <c r="Q608" t="n">
-        <v>608400</v>
+        <v>500400</v>
       </c>
     </row>
     <row r="609">
@@ -27753,10 +27753,10 @@
         <v>11</v>
       </c>
       <c r="N609" t="n">
-        <v>2501.3856275304</v>
+        <v>2501.3856097561</v>
       </c>
       <c r="O609" t="n">
-        <v>27515.2419028344</v>
+        <v>27515.2417073171</v>
       </c>
       <c r="P609" t="n">
         <v>4100</v>
@@ -28029,7 +28029,7 @@
         </is>
       </c>
       <c r="J615" t="n">
-        <v>594</v>
+        <v>542</v>
       </c>
       <c r="K615" t="n">
         <v>0</v>
@@ -28038,19 +28038,19 @@
         <v>0</v>
       </c>
       <c r="M615" t="n">
-        <v>594</v>
+        <v>542</v>
       </c>
       <c r="N615" t="n">
-        <v>1595.5195815035</v>
+        <v>1595.5194396439</v>
       </c>
       <c r="O615" t="n">
-        <v>947738.631413079</v>
+        <v>864771.5362869938</v>
       </c>
       <c r="P615" t="n">
         <v>2500</v>
       </c>
       <c r="Q615" t="n">
-        <v>1485000</v>
+        <v>1355000</v>
       </c>
     </row>
     <row r="616">
@@ -28665,7 +28665,7 @@
         </is>
       </c>
       <c r="J628" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K628" t="n">
         <v>0</v>
@@ -28674,19 +28674,19 @@
         <v>0</v>
       </c>
       <c r="M628" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N628" t="n">
-        <v>24491.526666667</v>
+        <v>24491.5275</v>
       </c>
       <c r="O628" t="n">
-        <v>122457.633333335</v>
+        <v>97966.11</v>
       </c>
       <c r="P628" t="n">
         <v>46500</v>
       </c>
       <c r="Q628" t="n">
-        <v>232500</v>
+        <v>186000</v>
       </c>
     </row>
     <row r="629">
@@ -31077,10 +31077,10 @@
         <v>33</v>
       </c>
       <c r="N678" t="n">
-        <v>4159.0002836879</v>
+        <v>4159.0002846975</v>
       </c>
       <c r="O678" t="n">
-        <v>137247.0093617007</v>
+        <v>137247.0093950175</v>
       </c>
       <c r="P678" t="n">
         <v>8900</v>
@@ -32344,7 +32344,7 @@
         </is>
       </c>
       <c r="J705" t="n">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K705" t="n">
         <v>0</v>
@@ -32353,19 +32353,19 @@
         <v>0</v>
       </c>
       <c r="M705" t="n">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="N705" t="n">
-        <v>7046.9398308668</v>
+        <v>7046.939830831</v>
       </c>
       <c r="O705" t="n">
-        <v>1000665.455983086</v>
+        <v>993618.516147171</v>
       </c>
       <c r="P705" t="n">
         <v>9900</v>
       </c>
       <c r="Q705" t="n">
-        <v>1405800</v>
+        <v>1395900</v>
       </c>
     </row>
     <row r="706">
@@ -32724,7 +32724,7 @@
         </is>
       </c>
       <c r="J713" t="n">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="K713" t="n">
         <v>0</v>
@@ -32733,19 +32733,19 @@
         <v>0</v>
       </c>
       <c r="M713" t="n">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="N713" t="n">
         <v>1338.14</v>
       </c>
       <c r="O713" t="n">
-        <v>303757.78</v>
+        <v>302419.64</v>
       </c>
       <c r="P713" t="n">
         <v>2500</v>
       </c>
       <c r="Q713" t="n">
-        <v>567500</v>
+        <v>565000</v>
       </c>
     </row>
     <row r="714">
@@ -32822,7 +32822,7 @@
         </is>
       </c>
       <c r="J715" t="n">
-        <v>25</v>
+        <v>145</v>
       </c>
       <c r="K715" t="n">
         <v>0</v>
@@ -32831,19 +32831,19 @@
         <v>0</v>
       </c>
       <c r="M715" t="n">
-        <v>25</v>
+        <v>145</v>
       </c>
       <c r="N715" t="n">
         <v>7811.9</v>
       </c>
       <c r="O715" t="n">
-        <v>195297.5</v>
+        <v>1132725.5</v>
       </c>
       <c r="P715" t="n">
         <v>13900</v>
       </c>
       <c r="Q715" t="n">
-        <v>347500</v>
+        <v>2015500</v>
       </c>
     </row>
     <row r="716">
@@ -33649,7 +33649,7 @@
         </is>
       </c>
       <c r="J733" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K733" t="n">
         <v>0</v>
@@ -33658,19 +33658,19 @@
         <v>0</v>
       </c>
       <c r="M733" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="N733" t="n">
         <v>5077</v>
       </c>
       <c r="O733" t="n">
-        <v>908783</v>
+        <v>903706</v>
       </c>
       <c r="P733" t="n">
         <v>8500</v>
       </c>
       <c r="Q733" t="n">
-        <v>1521500</v>
+        <v>1513000</v>
       </c>
     </row>
     <row r="734">
@@ -33782,7 +33782,7 @@
         </is>
       </c>
       <c r="J736" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="K736" t="n">
         <v>0</v>
@@ -33791,19 +33791,19 @@
         <v>0</v>
       </c>
       <c r="M736" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="N736" t="n">
-        <v>4985.4043478261</v>
+        <v>4985.4044444444</v>
       </c>
       <c r="O736" t="n">
-        <v>94722.6826086959</v>
+        <v>64810.25777777719</v>
       </c>
       <c r="P736" t="n">
         <v>7900</v>
       </c>
       <c r="Q736" t="n">
-        <v>150100</v>
+        <v>102700</v>
       </c>
     </row>
     <row r="737">
@@ -33920,7 +33920,7 @@
         </is>
       </c>
       <c r="J739" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K739" t="n">
         <v>0</v>
@@ -33929,19 +33929,19 @@
         <v>0</v>
       </c>
       <c r="M739" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N739" t="n">
         <v>10335.44</v>
       </c>
       <c r="O739" t="n">
-        <v>310063.2</v>
+        <v>299727.76</v>
       </c>
       <c r="P739" t="n">
         <v>10900</v>
       </c>
       <c r="Q739" t="n">
-        <v>327000</v>
+        <v>316100</v>
       </c>
     </row>
     <row r="740">
@@ -34058,7 +34058,7 @@
         </is>
       </c>
       <c r="J742" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="K742" t="n">
         <v>0</v>
@@ -34067,19 +34067,19 @@
         <v>0</v>
       </c>
       <c r="M742" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="N742" t="n">
         <v>2293.26</v>
       </c>
       <c r="O742" t="n">
-        <v>149061.9</v>
+        <v>146768.64</v>
       </c>
       <c r="P742" t="n">
         <v>4800</v>
       </c>
       <c r="Q742" t="n">
-        <v>312000</v>
+        <v>307200</v>
       </c>
     </row>
     <row r="743">
@@ -36378,7 +36378,7 @@
         </is>
       </c>
       <c r="J792" t="n">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="K792" t="n">
         <v>0</v>
@@ -36387,19 +36387,19 @@
         <v>0</v>
       </c>
       <c r="M792" t="n">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="N792" t="n">
         <v>4550</v>
       </c>
       <c r="O792" t="n">
-        <v>1474200</v>
+        <v>1460550</v>
       </c>
       <c r="P792" t="n">
         <v>6500</v>
       </c>
       <c r="Q792" t="n">
-        <v>2106000</v>
+        <v>2086500</v>
       </c>
     </row>
     <row r="793">

--- a/bodegas/LJ-05.xlsx
+++ b/bodegas/LJ-05.xlsx
@@ -948,10 +948,10 @@
         <v>10</v>
       </c>
       <c r="N13" t="n">
-        <v>27225.941422594</v>
+        <v>27000</v>
       </c>
       <c r="O13" t="n">
-        <v>272259.41422594</v>
+        <v>270000</v>
       </c>
       <c r="P13" t="n">
         <v>30000</v>
@@ -1065,10 +1065,10 @@
         <v>21</v>
       </c>
       <c r="N16" t="n">
-        <v>5784.4419026549</v>
+        <v>5758.9597787611</v>
       </c>
       <c r="O16" t="n">
-        <v>121473.2799557529</v>
+        <v>120938.1553539831</v>
       </c>
       <c r="P16" t="n">
         <v>16900</v>
@@ -1940,10 +1940,10 @@
         <v>2</v>
       </c>
       <c r="N38" t="n">
-        <v>21510.733070539</v>
+        <v>21333.69</v>
       </c>
       <c r="O38" t="n">
-        <v>43021.466141078</v>
+        <v>42667.38</v>
       </c>
       <c r="P38" t="n">
         <v>30000</v>
@@ -3100,10 +3100,10 @@
         <v>41</v>
       </c>
       <c r="N64" t="n">
-        <v>15834.716054688</v>
+        <v>15711.966289063</v>
       </c>
       <c r="O64" t="n">
-        <v>649223.358242208</v>
+        <v>644190.6178515831</v>
       </c>
       <c r="P64" t="n">
         <v>28500</v>
@@ -3147,10 +3147,10 @@
         <v>24</v>
       </c>
       <c r="N65" t="n">
-        <v>9642.5297333333</v>
+        <v>9392.0745333333</v>
       </c>
       <c r="O65" t="n">
-        <v>231420.7135999992</v>
+        <v>225409.7887999992</v>
       </c>
       <c r="P65" t="n">
         <v>18500</v>
@@ -4867,10 +4867,10 @@
         <v>5</v>
       </c>
       <c r="N105" t="n">
-        <v>27232.75862069</v>
+        <v>27000</v>
       </c>
       <c r="O105" t="n">
-        <v>136163.79310345</v>
+        <v>135000</v>
       </c>
       <c r="P105" t="n">
         <v>20000</v>
@@ -5200,10 +5200,10 @@
         <v>18</v>
       </c>
       <c r="N113" t="n">
-        <v>8104.9092</v>
+        <v>8046.39</v>
       </c>
       <c r="O113" t="n">
-        <v>145888.3656</v>
+        <v>144835.02</v>
       </c>
       <c r="P113" t="n">
         <v>20900</v>
@@ -5563,10 +5563,10 @@
         <v>23</v>
       </c>
       <c r="N121" t="n">
-        <v>7477.1013333333</v>
+        <v>7394.9354444444</v>
       </c>
       <c r="O121" t="n">
-        <v>171973.3306666659</v>
+        <v>170083.5152222212</v>
       </c>
       <c r="P121" t="n">
         <v>17900</v>
@@ -5902,10 +5902,10 @@
         <v>14</v>
       </c>
       <c r="N129" t="n">
-        <v>2576.9026455026</v>
+        <v>2563.34</v>
       </c>
       <c r="O129" t="n">
-        <v>36076.6370370364</v>
+        <v>35886.76</v>
       </c>
       <c r="P129" t="n">
         <v>4700</v>
@@ -7193,10 +7193,10 @@
         <v>24</v>
       </c>
       <c r="N158" t="n">
-        <v>13624.59908046</v>
+        <v>13593.35</v>
       </c>
       <c r="O158" t="n">
-        <v>326990.37793104</v>
+        <v>326240.4</v>
       </c>
       <c r="P158" t="n">
         <v>25500</v>
@@ -8647,10 +8647,10 @@
         <v>82</v>
       </c>
       <c r="N190" t="n">
-        <v>2289.4664730119</v>
+        <v>2267.0481788216</v>
       </c>
       <c r="O190" t="n">
-        <v>187736.2507869758</v>
+        <v>185897.9506633712</v>
       </c>
       <c r="P190" t="n">
         <v>3900</v>
@@ -9149,10 +9149,10 @@
         <v>37</v>
       </c>
       <c r="N201" t="n">
-        <v>4898.3218562874</v>
+        <v>4891</v>
       </c>
       <c r="O201" t="n">
-        <v>181237.9086826338</v>
+        <v>180967</v>
       </c>
       <c r="P201" t="n">
         <v>8200</v>
@@ -11550,10 +11550,10 @@
         <v>47</v>
       </c>
       <c r="N254" t="n">
-        <v>11658.147712418</v>
+        <v>11507.72</v>
       </c>
       <c r="O254" t="n">
-        <v>547932.942483646</v>
+        <v>540862.84</v>
       </c>
       <c r="P254" t="n">
         <v>25800</v>
@@ -13789,10 +13789,10 @@
         <v>44</v>
       </c>
       <c r="N305" t="n">
-        <v>13805.304244604</v>
+        <v>13513.64294964</v>
       </c>
       <c r="O305" t="n">
-        <v>607433.3867625759</v>
+        <v>594600.28978416</v>
       </c>
       <c r="P305" t="n">
         <v>21900</v>
@@ -14592,10 +14592,10 @@
         <v>52</v>
       </c>
       <c r="N323" t="n">
-        <v>5453.6557676349</v>
+        <v>5431.12</v>
       </c>
       <c r="O323" t="n">
-        <v>283590.0999170148</v>
+        <v>282418.24</v>
       </c>
       <c r="P323" t="n">
         <v>8900</v>
@@ -14730,10 +14730,10 @@
         <v>32</v>
       </c>
       <c r="N326" t="n">
-        <v>27226.972222222</v>
+        <v>26854</v>
       </c>
       <c r="O326" t="n">
-        <v>871263.111111104</v>
+        <v>859328</v>
       </c>
       <c r="P326" t="n">
         <v>43900</v>
@@ -15768,10 +15768,10 @@
         <v>102</v>
       </c>
       <c r="N349" t="n">
-        <v>3117.5970357143</v>
+        <v>3113.8900238095</v>
       </c>
       <c r="O349" t="n">
-        <v>317994.8976428586</v>
+        <v>317616.782428569</v>
       </c>
       <c r="P349" t="n">
         <v>5000</v>
@@ -15998,10 +15998,10 @@
         <v>214</v>
       </c>
       <c r="N354" t="n">
-        <v>2498.7228351648</v>
+        <v>2495.98</v>
       </c>
       <c r="O354" t="n">
-        <v>534726.6867252672</v>
+        <v>534139.72</v>
       </c>
       <c r="P354" t="n">
         <v>4100</v>
@@ -16320,10 +16320,10 @@
         <v>163</v>
       </c>
       <c r="N361" t="n">
-        <v>3969.9272029703</v>
+        <v>3965.02</v>
       </c>
       <c r="O361" t="n">
-        <v>647098.1340841589</v>
+        <v>646298.26</v>
       </c>
       <c r="P361" t="n">
         <v>6500</v>
@@ -16366,10 +16366,10 @@
         <v>1</v>
       </c>
       <c r="N362" t="n">
-        <v>5844.4237327189</v>
+        <v>5791.05</v>
       </c>
       <c r="O362" t="n">
-        <v>5844.4237327189</v>
+        <v>5791.05</v>
       </c>
       <c r="P362" t="n">
         <v>9300</v>
@@ -16829,10 +16829,10 @@
         <v>12</v>
       </c>
       <c r="N372" t="n">
-        <v>44124.685714286</v>
+        <v>42899</v>
       </c>
       <c r="O372" t="n">
-        <v>529496.2285714321</v>
+        <v>514788</v>
       </c>
       <c r="P372" t="n">
         <v>70900</v>
@@ -17059,10 +17059,10 @@
         <v>23</v>
       </c>
       <c r="N377" t="n">
-        <v>22795.894912427</v>
+        <v>22739</v>
       </c>
       <c r="O377" t="n">
-        <v>524305.5829858209</v>
+        <v>522997</v>
       </c>
       <c r="P377" t="n">
         <v>36900</v>
@@ -17151,10 +17151,10 @@
         <v>69</v>
       </c>
       <c r="N379" t="n">
-        <v>16092.045229682</v>
+        <v>16058</v>
       </c>
       <c r="O379" t="n">
-        <v>1110351.120848058</v>
+        <v>1108002</v>
       </c>
       <c r="P379" t="n">
         <v>25900</v>
@@ -19701,10 +19701,10 @@
         <v>37</v>
       </c>
       <c r="N434" t="n">
-        <v>21748.414253898</v>
+        <v>21676</v>
       </c>
       <c r="O434" t="n">
-        <v>804691.3273942261</v>
+        <v>802012</v>
       </c>
       <c r="P434" t="n">
         <v>34900</v>
@@ -21531,10 +21531,10 @@
         <v>15</v>
       </c>
       <c r="N474" t="n">
-        <v>27422.4</v>
+        <v>27186</v>
       </c>
       <c r="O474" t="n">
-        <v>411336</v>
+        <v>407790</v>
       </c>
       <c r="P474" t="n">
         <v>43900</v>
@@ -21669,10 +21669,10 @@
         <v>24</v>
       </c>
       <c r="N477" t="n">
-        <v>3903.9739463602</v>
+        <v>3898</v>
       </c>
       <c r="O477" t="n">
-        <v>93695.3747126448</v>
+        <v>93552</v>
       </c>
       <c r="P477" t="n">
         <v>6900</v>
@@ -21715,10 +21715,10 @@
         <v>25</v>
       </c>
       <c r="N478" t="n">
-        <v>13585.460030166</v>
+        <v>13565</v>
       </c>
       <c r="O478" t="n">
-        <v>339636.50075415</v>
+        <v>339125</v>
       </c>
       <c r="P478" t="n">
         <v>22500</v>
@@ -21899,10 +21899,10 @@
         <v>35</v>
       </c>
       <c r="N482" t="n">
-        <v>8836.1575342466</v>
+        <v>8806</v>
       </c>
       <c r="O482" t="n">
-        <v>309265.513698631</v>
+        <v>308210</v>
       </c>
       <c r="P482" t="n">
         <v>14900</v>
@@ -23372,10 +23372,10 @@
         <v>12</v>
       </c>
       <c r="N514" t="n">
-        <v>3647.235915493</v>
+        <v>3639.35</v>
       </c>
       <c r="O514" t="n">
-        <v>43766.830985916</v>
+        <v>43672.2</v>
       </c>
       <c r="P514" t="n">
         <v>7500</v>
@@ -23510,10 +23510,10 @@
         <v>5</v>
       </c>
       <c r="N517" t="n">
-        <v>10816.221634615</v>
+        <v>10713.21</v>
       </c>
       <c r="O517" t="n">
-        <v>54081.108173075</v>
+        <v>53566.05</v>
       </c>
       <c r="P517" t="n">
         <v>20900</v>
@@ -23602,10 +23602,10 @@
         <v>17</v>
       </c>
       <c r="N519" t="n">
-        <v>12664.079439252</v>
+        <v>12489</v>
       </c>
       <c r="O519" t="n">
-        <v>215289.350467284</v>
+        <v>212313</v>
       </c>
       <c r="P519" t="n">
         <v>20900</v>
@@ -23648,10 +23648,10 @@
         <v>12</v>
       </c>
       <c r="N520" t="n">
-        <v>21937.5</v>
+        <v>21762</v>
       </c>
       <c r="O520" t="n">
-        <v>263250</v>
+        <v>261144</v>
       </c>
       <c r="P520" t="n">
         <v>35900</v>
@@ -28007,10 +28007,10 @@
         <v>3</v>
       </c>
       <c r="N614" t="n">
-        <v>8330.0435897436</v>
+        <v>7923.7</v>
       </c>
       <c r="O614" t="n">
-        <v>24990.1307692308</v>
+        <v>23771.1</v>
       </c>
       <c r="P614" t="n">
         <v>16600</v>
@@ -28877,10 +28877,10 @@
         <v>5</v>
       </c>
       <c r="N632" t="n">
-        <v>29585.206779661</v>
+        <v>28615.2</v>
       </c>
       <c r="O632" t="n">
-        <v>147926.033898305</v>
+        <v>143076</v>
       </c>
       <c r="P632" t="n">
         <v>36500</v>
@@ -29297,10 +29297,10 @@
         <v>8</v>
       </c>
       <c r="N641" t="n">
-        <v>10459.349677419</v>
+        <v>10348.08</v>
       </c>
       <c r="O641" t="n">
-        <v>83674.79741935201</v>
+        <v>82784.64</v>
       </c>
       <c r="P641" t="n">
         <v>16900</v>
@@ -29346,10 +29346,10 @@
         <v>30</v>
       </c>
       <c r="N642" t="n">
-        <v>10806.564102564</v>
+        <v>10536.4</v>
       </c>
       <c r="O642" t="n">
-        <v>324196.92307692</v>
+        <v>316092</v>
       </c>
       <c r="P642" t="n">
         <v>16900</v>
@@ -29738,10 +29738,10 @@
         <v>15</v>
       </c>
       <c r="N650" t="n">
-        <v>10020.157196262</v>
+        <v>9746.8801869159</v>
       </c>
       <c r="O650" t="n">
-        <v>150302.35794393</v>
+        <v>146203.2028037385</v>
       </c>
       <c r="P650" t="n">
         <v>18500</v>
@@ -30268,10 +30268,10 @@
         <v>20</v>
       </c>
       <c r="N661" t="n">
-        <v>4388.3371764706</v>
+        <v>4337.31</v>
       </c>
       <c r="O661" t="n">
-        <v>87766.74352941199</v>
+        <v>86746.20000000001</v>
       </c>
       <c r="P661" t="n">
         <v>12900</v>
@@ -31456,10 +31456,10 @@
         <v>6</v>
       </c>
       <c r="N686" t="n">
-        <v>10018.344827586</v>
+        <v>9372</v>
       </c>
       <c r="O686" t="n">
-        <v>60110.06896551599</v>
+        <v>56232</v>
       </c>
       <c r="P686" t="n">
         <v>17900</v>
@@ -32319,10 +32319,10 @@
         <v>6</v>
       </c>
       <c r="N704" t="n">
-        <v>16236.522</v>
+        <v>15033.8164</v>
       </c>
       <c r="O704" t="n">
-        <v>97419.13200000001</v>
+        <v>90202.89840000001</v>
       </c>
       <c r="P704" t="n">
         <v>19900</v>
@@ -34996,10 +34996,10 @@
         <v>40</v>
       </c>
       <c r="N762" t="n">
-        <v>449.18534246575</v>
+        <v>415.07</v>
       </c>
       <c r="O762" t="n">
-        <v>17967.41369863</v>
+        <v>16602.8</v>
       </c>
       <c r="P762" t="n">
         <v>2900</v>
@@ -35277,10 +35277,10 @@
         <v>26</v>
       </c>
       <c r="N768" t="n">
-        <v>1039.9621428571</v>
+        <v>970.63142857143</v>
       </c>
       <c r="O768" t="n">
-        <v>27039.0157142846</v>
+        <v>25236.41714285718</v>
       </c>
       <c r="P768" t="n">
         <v>7200</v>

--- a/bodegas/LJ-05.xlsx
+++ b/bodegas/LJ-05.xlsx
@@ -5075,10 +5075,10 @@
         <v>9</v>
       </c>
       <c r="N110" t="n">
-        <v>3872.3234767642</v>
+        <v>3865.67</v>
       </c>
       <c r="O110" t="n">
-        <v>34850.9112908778</v>
+        <v>34791.03</v>
       </c>
       <c r="P110" t="n">
         <v>5500</v>
@@ -5337,10 +5337,10 @@
         <v>40</v>
       </c>
       <c r="N116" t="n">
-        <v>2589.9594489247</v>
+        <v>2572.67</v>
       </c>
       <c r="O116" t="n">
-        <v>103598.377956988</v>
+        <v>102906.8</v>
       </c>
       <c r="P116" t="n">
         <v>4700</v>
@@ -5429,10 +5429,10 @@
         <v>29</v>
       </c>
       <c r="N118" t="n">
-        <v>2597.4440764331</v>
+        <v>2570.16</v>
       </c>
       <c r="O118" t="n">
-        <v>75325.8782165599</v>
+        <v>74534.64</v>
       </c>
       <c r="P118" t="n">
         <v>4700</v>
@@ -5855,10 +5855,10 @@
         <v>14</v>
       </c>
       <c r="N128" t="n">
-        <v>2597.7011260054</v>
+        <v>2563.34</v>
       </c>
       <c r="O128" t="n">
-        <v>36367.8157640756</v>
+        <v>35886.76</v>
       </c>
       <c r="P128" t="n">
         <v>4700</v>
@@ -6439,10 +6439,10 @@
         <v>735</v>
       </c>
       <c r="N141" t="n">
-        <v>2837.5718128026</v>
+        <v>2833</v>
       </c>
       <c r="O141" t="n">
-        <v>2085615.282409911</v>
+        <v>2082255</v>
       </c>
       <c r="P141" t="n">
         <v>3500</v>
@@ -6567,10 +6567,10 @@
         <v>36</v>
       </c>
       <c r="N144" t="n">
-        <v>3489.6196317829</v>
+        <v>3456.13</v>
       </c>
       <c r="O144" t="n">
-        <v>125626.3067441844</v>
+        <v>124420.68</v>
       </c>
       <c r="P144" t="n">
         <v>5700</v>
@@ -7827,10 +7827,10 @@
         <v>111</v>
       </c>
       <c r="N172" t="n">
-        <v>7538.62740638</v>
+        <v>7507.39</v>
       </c>
       <c r="O172" t="n">
-        <v>836787.64210818</v>
+        <v>833320.29</v>
       </c>
       <c r="P172" t="n">
         <v>13500</v>
@@ -8011,10 +8011,10 @@
         <v>14</v>
       </c>
       <c r="N176" t="n">
-        <v>3801.7317574476</v>
+        <v>3795.7100070509</v>
       </c>
       <c r="O176" t="n">
-        <v>53224.2446042664</v>
+        <v>53139.9400987126</v>
       </c>
       <c r="P176" t="n">
         <v>6200</v>
@@ -8057,10 +8057,10 @@
         <v>59</v>
       </c>
       <c r="N177" t="n">
-        <v>3695.2967632027</v>
+        <v>3684</v>
       </c>
       <c r="O177" t="n">
-        <v>218022.5090289593</v>
+        <v>217356</v>
       </c>
       <c r="P177" t="n">
         <v>6200</v>
@@ -8421,10 +8421,10 @@
         <v>195</v>
       </c>
       <c r="N185" t="n">
-        <v>1213.150338295</v>
+        <v>1203.38</v>
       </c>
       <c r="O185" t="n">
-        <v>236564.315967525</v>
+        <v>234659.1</v>
       </c>
       <c r="P185" t="n">
         <v>1900</v>
@@ -8600,10 +8600,10 @@
         <v>82</v>
       </c>
       <c r="N189" t="n">
-        <v>2286.8353823774</v>
+        <v>2267.048162926</v>
       </c>
       <c r="O189" t="n">
-        <v>187520.5013549468</v>
+        <v>185897.949359932</v>
       </c>
       <c r="P189" t="n">
         <v>3900</v>
@@ -8784,10 +8784,10 @@
         <v>88</v>
       </c>
       <c r="N193" t="n">
-        <v>8687.96003996</v>
+        <v>8662</v>
       </c>
       <c r="O193" t="n">
-        <v>764540.4835164801</v>
+        <v>762256</v>
       </c>
       <c r="P193" t="n">
         <v>14200</v>
@@ -9148,10 +9148,10 @@
         <v>36</v>
       </c>
       <c r="N201" t="n">
-        <v>8209.849315068501</v>
+        <v>8154</v>
       </c>
       <c r="O201" t="n">
-        <v>295554.575342466</v>
+        <v>293544</v>
       </c>
       <c r="P201" t="n">
         <v>13500</v>
@@ -9238,10 +9238,10 @@
         <v>166</v>
       </c>
       <c r="N203" t="n">
-        <v>616.28176305926</v>
+        <v>616.01871898278</v>
       </c>
       <c r="O203" t="n">
-        <v>102302.7726678372</v>
+        <v>102259.1073511415</v>
       </c>
       <c r="P203" t="n">
         <v>800</v>
@@ -11731,10 +11731,10 @@
         <v>95</v>
       </c>
       <c r="N258" t="n">
-        <v>2678.0253782895</v>
+        <v>2651.8557072368</v>
       </c>
       <c r="O258" t="n">
-        <v>254412.4109375025</v>
+        <v>251926.292187496</v>
       </c>
       <c r="P258" t="n">
         <v>3800</v>
@@ -11777,10 +11777,10 @@
         <v>251</v>
       </c>
       <c r="N259" t="n">
-        <v>2030.7740585774</v>
+        <v>1965</v>
       </c>
       <c r="O259" t="n">
-        <v>509724.2887029274</v>
+        <v>493215</v>
       </c>
       <c r="P259" t="n">
         <v>3700</v>
@@ -12387,10 +12387,10 @@
         <v>46</v>
       </c>
       <c r="N273" t="n">
-        <v>8818.9498942682</v>
+        <v>8794.48</v>
       </c>
       <c r="O273" t="n">
-        <v>405671.6951363372</v>
+        <v>404546.08</v>
       </c>
       <c r="P273" t="n">
         <v>14500</v>
@@ -12515,10 +12515,10 @@
         <v>248</v>
       </c>
       <c r="N276" t="n">
-        <v>2558.6841592313</v>
+        <v>2517.22</v>
       </c>
       <c r="O276" t="n">
-        <v>634553.6714893624</v>
+        <v>624270.5599999999</v>
       </c>
       <c r="P276" t="n">
         <v>4200</v>
@@ -12556,10 +12556,10 @@
         <v>82</v>
       </c>
       <c r="N277" t="n">
-        <v>2035.7801454898</v>
+        <v>2029.8736372454</v>
       </c>
       <c r="O277" t="n">
-        <v>166933.9719301636</v>
+        <v>166449.6382541228</v>
       </c>
       <c r="P277" t="n">
         <v>3600</v>
@@ -12597,10 +12597,10 @@
         <v>20</v>
       </c>
       <c r="N278" t="n">
-        <v>22561.918644068</v>
+        <v>22485.695932203</v>
       </c>
       <c r="O278" t="n">
-        <v>451238.37288136</v>
+        <v>449713.91864406</v>
       </c>
       <c r="P278" t="n">
         <v>36500</v>
@@ -12761,10 +12761,10 @@
         <v>25</v>
       </c>
       <c r="N282" t="n">
-        <v>7136.7702060222</v>
+        <v>7103</v>
       </c>
       <c r="O282" t="n">
-        <v>178419.255150555</v>
+        <v>177575</v>
       </c>
       <c r="P282" t="n">
         <v>10700</v>
@@ -12984,10 +12984,10 @@
         <v>10</v>
       </c>
       <c r="N287" t="n">
-        <v>15639.519117647</v>
+        <v>14371.45</v>
       </c>
       <c r="O287" t="n">
-        <v>156395.19117647</v>
+        <v>143714.5</v>
       </c>
       <c r="P287" t="n">
         <v>23300</v>
@@ -13696,10 +13696,10 @@
         <v>37</v>
       </c>
       <c r="N303" t="n">
-        <v>11652.839895288</v>
+        <v>11562.038534031</v>
       </c>
       <c r="O303" t="n">
-        <v>431155.076125656</v>
+        <v>427795.425759147</v>
       </c>
       <c r="P303" t="n">
         <v>18500</v>
@@ -14018,10 +14018,10 @@
         <v>16</v>
       </c>
       <c r="N310" t="n">
-        <v>22817.681329923</v>
+        <v>22730.48</v>
       </c>
       <c r="O310" t="n">
-        <v>365082.901278768</v>
+        <v>363687.68</v>
       </c>
       <c r="P310" t="n">
         <v>36900</v>
@@ -15859,10 +15859,10 @@
         <v>17</v>
       </c>
       <c r="N351" t="n">
-        <v>4265.5329508197</v>
+        <v>4163.1601639344</v>
       </c>
       <c r="O351" t="n">
-        <v>72514.0601639349</v>
+        <v>70773.7227868848</v>
       </c>
       <c r="P351" t="n">
         <v>6700</v>
@@ -16135,10 +16135,10 @@
         <v>87</v>
       </c>
       <c r="N357" t="n">
-        <v>5220.5451448041</v>
+        <v>5194</v>
       </c>
       <c r="O357" t="n">
-        <v>454187.4275979567</v>
+        <v>451878</v>
       </c>
       <c r="P357" t="n">
         <v>9000</v>
@@ -17291,10 +17291,10 @@
         <v>63</v>
       </c>
       <c r="N382" t="n">
-        <v>11682.094594595</v>
+        <v>11450</v>
       </c>
       <c r="O382" t="n">
-        <v>735971.959459485</v>
+        <v>721350</v>
       </c>
       <c r="P382" t="n">
         <v>18300</v>
@@ -17383,10 +17383,10 @@
         <v>135</v>
       </c>
       <c r="N384" t="n">
-        <v>6365.625</v>
+        <v>6300</v>
       </c>
       <c r="O384" t="n">
-        <v>859359.375</v>
+        <v>850500</v>
       </c>
       <c r="P384" t="n">
         <v>10200</v>
@@ -17521,10 +17521,10 @@
         <v>72</v>
       </c>
       <c r="N387" t="n">
-        <v>7371.3029315961</v>
+        <v>7230</v>
       </c>
       <c r="O387" t="n">
-        <v>530733.8110749192</v>
+        <v>520560</v>
       </c>
       <c r="P387" t="n">
         <v>11600</v>
@@ -17567,10 +17567,10 @@
         <v>3</v>
       </c>
       <c r="N388" t="n">
-        <v>5291.8727915194</v>
+        <v>5200</v>
       </c>
       <c r="O388" t="n">
-        <v>15875.6183745582</v>
+        <v>15600</v>
       </c>
       <c r="P388" t="n">
         <v>8500</v>
@@ -17613,10 +17613,10 @@
         <v>125</v>
       </c>
       <c r="N389" t="n">
-        <v>1420.3389830508</v>
+        <v>1400</v>
       </c>
       <c r="O389" t="n">
-        <v>177542.37288135</v>
+        <v>175000</v>
       </c>
       <c r="P389" t="n">
         <v>2300</v>
@@ -17659,10 +17659,10 @@
         <v>125</v>
       </c>
       <c r="N390" t="n">
-        <v>6085.1063829787</v>
+        <v>6000</v>
       </c>
       <c r="O390" t="n">
-        <v>760638.2978723375</v>
+        <v>750000</v>
       </c>
       <c r="P390" t="n">
         <v>10000</v>
@@ -17751,10 +17751,10 @@
         <v>148</v>
       </c>
       <c r="N392" t="n">
-        <v>1243.273381295</v>
+        <v>1230</v>
       </c>
       <c r="O392" t="n">
-        <v>184004.46043166</v>
+        <v>182040</v>
       </c>
       <c r="P392" t="n">
         <v>2000</v>
@@ -17894,10 +17894,10 @@
         <v>116</v>
       </c>
       <c r="N395" t="n">
-        <v>1441.9626168224</v>
+        <v>1390</v>
       </c>
       <c r="O395" t="n">
-        <v>167267.6635513984</v>
+        <v>161240</v>
       </c>
       <c r="P395" t="n">
         <v>2300</v>
@@ -17940,10 +17940,10 @@
         <v>73</v>
       </c>
       <c r="N396" t="n">
-        <v>1944.3046357616</v>
+        <v>1870</v>
       </c>
       <c r="O396" t="n">
-        <v>141934.2384105968</v>
+        <v>136510</v>
       </c>
       <c r="P396" t="n">
         <v>3000</v>
@@ -17986,10 +17986,10 @@
         <v>54</v>
       </c>
       <c r="N397" t="n">
-        <v>2110.9815037594</v>
+        <v>2019.86</v>
       </c>
       <c r="O397" t="n">
-        <v>113993.0012030076</v>
+        <v>109072.44</v>
       </c>
       <c r="P397" t="n">
         <v>3300</v>
@@ -18032,10 +18032,10 @@
         <v>230</v>
       </c>
       <c r="N398" t="n">
-        <v>539.28902627512</v>
+        <v>520</v>
       </c>
       <c r="O398" t="n">
-        <v>124036.4760432776</v>
+        <v>119600</v>
       </c>
       <c r="P398" t="n">
         <v>850</v>
@@ -18124,10 +18124,10 @@
         <v>77</v>
       </c>
       <c r="N400" t="n">
-        <v>1872.4705882353</v>
+        <v>1840</v>
       </c>
       <c r="O400" t="n">
-        <v>144180.2352941181</v>
+        <v>141680</v>
       </c>
       <c r="P400" t="n">
         <v>3000</v>
@@ -18216,10 +18216,10 @@
         <v>94</v>
       </c>
       <c r="N402" t="n">
-        <v>2878.4650112867</v>
+        <v>2840</v>
       </c>
       <c r="O402" t="n">
-        <v>270575.7110609498</v>
+        <v>266960</v>
       </c>
       <c r="P402" t="n">
         <v>4600</v>
@@ -18682,10 +18682,10 @@
         <v>36</v>
       </c>
       <c r="N412" t="n">
-        <v>13863.987068966</v>
+        <v>13687</v>
       </c>
       <c r="O412" t="n">
-        <v>499103.534482776</v>
+        <v>492732</v>
       </c>
       <c r="P412" t="n">
         <v>21900</v>
@@ -19884,10 +19884,10 @@
         <v>31</v>
       </c>
       <c r="N438" t="n">
-        <v>9045.4669811321</v>
+        <v>9003</v>
       </c>
       <c r="O438" t="n">
-        <v>280409.4764150951</v>
+        <v>279093</v>
       </c>
       <c r="P438" t="n">
         <v>14900</v>
@@ -20840,10 +20840,10 @@
         <v>38</v>
       </c>
       <c r="N459" t="n">
-        <v>4223.6597938144</v>
+        <v>4202</v>
       </c>
       <c r="O459" t="n">
-        <v>160499.0721649472</v>
+        <v>159676</v>
       </c>
       <c r="P459" t="n">
         <v>7900</v>
@@ -21024,10 +21024,10 @@
         <v>14</v>
       </c>
       <c r="N463" t="n">
-        <v>10095.669565217</v>
+        <v>9839</v>
       </c>
       <c r="O463" t="n">
-        <v>141339.373913038</v>
+        <v>137746</v>
       </c>
       <c r="P463" t="n">
         <v>16900</v>
@@ -24202,10 +24202,10 @@
         <v>108</v>
       </c>
       <c r="N532" t="n">
-        <v>1946.0906677937</v>
+        <v>1907.3944716822</v>
       </c>
       <c r="O532" t="n">
-        <v>210177.7921217196</v>
+        <v>205998.6029416776</v>
       </c>
       <c r="P532" t="n">
         <v>2500</v>
@@ -24248,10 +24248,10 @@
         <v>189</v>
       </c>
       <c r="N533" t="n">
-        <v>1796.7129837251</v>
+        <v>1771.091283906</v>
       </c>
       <c r="O533" t="n">
-        <v>339578.7539240439</v>
+        <v>334736.252658234</v>
       </c>
       <c r="P533" t="n">
         <v>2500</v>
@@ -24294,10 +24294,10 @@
         <v>465</v>
       </c>
       <c r="N534" t="n">
-        <v>2095.5452849741</v>
+        <v>2079.3842227979</v>
       </c>
       <c r="O534" t="n">
-        <v>974428.5575129566</v>
+        <v>966913.6636010234</v>
       </c>
       <c r="P534" t="n">
         <v>2900</v>
@@ -24340,10 +24340,10 @@
         <v>340</v>
       </c>
       <c r="N535" t="n">
-        <v>1828.4692441176</v>
+        <v>1803.0149852941</v>
       </c>
       <c r="O535" t="n">
-        <v>621679.542999984</v>
+        <v>613025.0949999939</v>
       </c>
       <c r="P535" t="n">
         <v>2500</v>
@@ -24432,10 +24432,10 @@
         <v>565</v>
       </c>
       <c r="N537" t="n">
-        <v>2137.4820360902</v>
+        <v>2122.1641172932</v>
       </c>
       <c r="O537" t="n">
-        <v>1207677.350390963</v>
+        <v>1199022.726270658</v>
       </c>
       <c r="P537" t="n">
         <v>2900</v>
@@ -24570,10 +24570,10 @@
         <v>366</v>
       </c>
       <c r="N540" t="n">
-        <v>3276.0008772707</v>
+        <v>3224.5679308817</v>
       </c>
       <c r="O540" t="n">
-        <v>1199016.321081076</v>
+        <v>1180191.862702702</v>
       </c>
       <c r="P540" t="n">
         <v>4500</v>
@@ -24844,10 +24844,10 @@
         <v>14</v>
       </c>
       <c r="N546" t="n">
-        <v>5414.576625</v>
+        <v>5347.73</v>
       </c>
       <c r="O546" t="n">
-        <v>75804.07274999999</v>
+        <v>74868.22</v>
       </c>
       <c r="P546" t="n">
         <v>9500</v>
@@ -25074,10 +25074,10 @@
         <v>39</v>
       </c>
       <c r="N551" t="n">
-        <v>3051.52</v>
+        <v>2980</v>
       </c>
       <c r="O551" t="n">
-        <v>119009.28</v>
+        <v>116220</v>
       </c>
       <c r="P551" t="n">
         <v>4800</v>
@@ -25819,10 +25819,10 @@
         <v>7</v>
       </c>
       <c r="N567" t="n">
-        <v>2769.7168108108</v>
+        <v>2682.71</v>
       </c>
       <c r="O567" t="n">
-        <v>19388.0176756756</v>
+        <v>18778.97</v>
       </c>
       <c r="P567" t="n">
         <v>10900</v>
@@ -27531,10 +27531,10 @@
         <v>495</v>
       </c>
       <c r="N604" t="n">
-        <v>704.1779547101401</v>
+        <v>703.79545471015</v>
       </c>
       <c r="O604" t="n">
-        <v>348568.0875815193</v>
+        <v>348378.7500815243</v>
       </c>
       <c r="P604" t="n">
         <v>900</v>
@@ -31847,10 +31847,10 @@
         <v>114</v>
       </c>
       <c r="N694" t="n">
-        <v>713.93197013211</v>
+        <v>711.48</v>
       </c>
       <c r="O694" t="n">
-        <v>81388.24459506053</v>
+        <v>81108.72</v>
       </c>
       <c r="P694" t="n">
         <v>2500</v>
@@ -32751,10 +32751,10 @@
         <v>70</v>
       </c>
       <c r="N713" t="n">
-        <v>714.37850499616</v>
+        <v>704.8968946963899</v>
       </c>
       <c r="O713" t="n">
-        <v>50006.4953497312</v>
+        <v>49342.7826287473</v>
       </c>
       <c r="P713" t="n">
         <v>900</v>
@@ -33305,10 +33305,10 @@
         <v>181</v>
       </c>
       <c r="N725" t="n">
-        <v>3192.6751439214</v>
+        <v>3181.9</v>
       </c>
       <c r="O725" t="n">
-        <v>577874.2010497734</v>
+        <v>575923.9</v>
       </c>
       <c r="P725" t="n">
         <v>5100</v>
@@ -33528,10 +33528,10 @@
         <v>337</v>
       </c>
       <c r="N730" t="n">
-        <v>707.12182981928</v>
+        <v>705.52801204819</v>
       </c>
       <c r="O730" t="n">
-        <v>238300.0566490974</v>
+        <v>237762.94006024</v>
       </c>
       <c r="P730" t="n">
         <v>1500</v>
@@ -33983,10 +33983,10 @@
         <v>7</v>
       </c>
       <c r="N740" t="n">
-        <v>1338.6403076923</v>
+        <v>1160.1556923077</v>
       </c>
       <c r="O740" t="n">
-        <v>9370.4821538461</v>
+        <v>8121.0898461539</v>
       </c>
       <c r="P740" t="n">
         <v>1600</v>

--- a/bodegas/LJ-05.xlsx
+++ b/bodegas/LJ-05.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-07</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-08</t>
         </is>
       </c>
     </row>

--- a/bodegas/LJ-05.xlsx
+++ b/bodegas/LJ-05.xlsx
@@ -738,10 +738,10 @@
         <v>3</v>
       </c>
       <c r="N8" t="n">
-        <v>74676.654222222</v>
+        <v>74676.65386363601</v>
       </c>
       <c r="O8" t="n">
-        <v>224029.962666666</v>
+        <v>224029.961590908</v>
       </c>
       <c r="P8" t="n">
         <v>144900</v>
@@ -1583,10 +1583,10 @@
         <v>27</v>
       </c>
       <c r="N29" t="n">
-        <v>3926.8371326165</v>
+        <v>3926.8371296771</v>
       </c>
       <c r="O29" t="n">
-        <v>106024.6025806455</v>
+        <v>106024.6025012817</v>
       </c>
       <c r="P29" t="n">
         <v>4800</v>
@@ -1784,10 +1784,10 @@
         <v>29</v>
       </c>
       <c r="N34" t="n">
-        <v>3716.330188383</v>
+        <v>3716.3301889764</v>
       </c>
       <c r="O34" t="n">
-        <v>107773.575463107</v>
+        <v>107773.5754803156</v>
       </c>
       <c r="P34" t="n">
         <v>9500</v>
@@ -3100,10 +3100,10 @@
         <v>41</v>
       </c>
       <c r="N64" t="n">
-        <v>15711.966215139</v>
+        <v>15711.9662</v>
       </c>
       <c r="O64" t="n">
-        <v>644190.614820699</v>
+        <v>644190.6142000001</v>
       </c>
       <c r="P64" t="n">
         <v>28500</v>
@@ -3565,10 +3565,10 @@
         <v>4</v>
       </c>
       <c r="N75" t="n">
-        <v>22267.552</v>
+        <v>22267.552083333</v>
       </c>
       <c r="O75" t="n">
-        <v>89070.208</v>
+        <v>89070.208333332</v>
       </c>
       <c r="P75" t="n">
         <v>46300</v>
@@ -3822,10 +3822,10 @@
         <v>1</v>
       </c>
       <c r="N81" t="n">
-        <v>56906.800422535</v>
+        <v>56906.800571429</v>
       </c>
       <c r="O81" t="n">
-        <v>56906.800422535</v>
+        <v>56906.800571429</v>
       </c>
       <c r="P81" t="n">
         <v>95900</v>
@@ -3916,10 +3916,10 @@
         <v>6</v>
       </c>
       <c r="N83" t="n">
-        <v>141416.88447284</v>
+        <v>141416.88453074</v>
       </c>
       <c r="O83" t="n">
-        <v>848501.30683704</v>
+        <v>848501.3071844401</v>
       </c>
       <c r="P83" t="n">
         <v>251900</v>
@@ -4330,10 +4330,10 @@
         <v>8</v>
       </c>
       <c r="N93" t="n">
-        <v>61666.873842239</v>
+        <v>61666.873852041</v>
       </c>
       <c r="O93" t="n">
-        <v>493334.990737912</v>
+        <v>493334.990816328</v>
       </c>
       <c r="P93" t="n">
         <v>98900</v>
@@ -5108,22 +5108,22 @@
         <v>0</v>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M111" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N111" t="n">
         <v>16010.3</v>
       </c>
       <c r="O111" t="n">
-        <v>240154.5</v>
+        <v>208133.9</v>
       </c>
       <c r="P111" t="n">
         <v>30500</v>
       </c>
       <c r="Q111" t="n">
-        <v>457500</v>
+        <v>396500</v>
       </c>
     </row>
     <row r="112">
@@ -6216,10 +6216,10 @@
         <v>64</v>
       </c>
       <c r="N136" t="n">
-        <v>732.63410958904</v>
+        <v>732.63413793103</v>
       </c>
       <c r="O136" t="n">
-        <v>46888.58301369856</v>
+        <v>46888.58482758592</v>
       </c>
       <c r="P136" t="n">
         <v>6200</v>
@@ -6526,10 +6526,10 @@
         <v>1</v>
       </c>
       <c r="N143" t="n">
-        <v>4937.3101595359</v>
+        <v>4937.3101601164</v>
       </c>
       <c r="O143" t="n">
-        <v>4937.3101595359</v>
+        <v>4937.3101601164</v>
       </c>
       <c r="P143" t="n">
         <v>7500</v>
@@ -7358,22 +7358,22 @@
         <v>0</v>
       </c>
       <c r="L162" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M162" t="n">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="N162" t="n">
         <v>1194.83</v>
       </c>
       <c r="O162" t="n">
-        <v>461204.3799999999</v>
+        <v>451645.74</v>
       </c>
       <c r="P162" t="n">
         <v>2500</v>
       </c>
       <c r="Q162" t="n">
-        <v>965000</v>
+        <v>945000</v>
       </c>
     </row>
     <row r="163">
@@ -7407,22 +7407,22 @@
         <v>0</v>
       </c>
       <c r="L163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N163" t="n">
         <v>1566.77</v>
       </c>
       <c r="O163" t="n">
-        <v>1566.77</v>
+        <v>0</v>
       </c>
       <c r="P163" t="n">
         <v>2900</v>
       </c>
       <c r="Q163" t="n">
-        <v>2900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164">
@@ -7775,22 +7775,22 @@
         <v>0</v>
       </c>
       <c r="L171" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M171" t="n">
-        <v>1795</v>
+        <v>1745</v>
       </c>
       <c r="N171" t="n">
         <v>156.25</v>
       </c>
       <c r="O171" t="n">
-        <v>280468.75</v>
+        <v>272656.25</v>
       </c>
       <c r="P171" t="n">
         <v>250</v>
       </c>
       <c r="Q171" t="n">
-        <v>448750</v>
+        <v>436250</v>
       </c>
     </row>
     <row r="172">
@@ -8236,10 +8236,10 @@
         <v>56</v>
       </c>
       <c r="N181" t="n">
-        <v>4890.930045977</v>
+        <v>4890.9300460299</v>
       </c>
       <c r="O181" t="n">
-        <v>273892.082574712</v>
+        <v>273892.0825776744</v>
       </c>
       <c r="P181" t="n">
         <v>8200</v>
@@ -8415,22 +8415,22 @@
         <v>0</v>
       </c>
       <c r="L185" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M185" t="n">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="N185" t="n">
         <v>1203.38</v>
       </c>
       <c r="O185" t="n">
-        <v>234659.1</v>
+        <v>225032.06</v>
       </c>
       <c r="P185" t="n">
         <v>1900</v>
       </c>
       <c r="Q185" t="n">
-        <v>370500</v>
+        <v>355300</v>
       </c>
     </row>
     <row r="186">
@@ -8461,22 +8461,22 @@
         <v>0</v>
       </c>
       <c r="L186" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="M186" t="n">
-        <v>141</v>
+        <v>118</v>
       </c>
       <c r="N186" t="n">
         <v>3472</v>
       </c>
       <c r="O186" t="n">
-        <v>489552</v>
+        <v>409696</v>
       </c>
       <c r="P186" t="n">
         <v>4800</v>
       </c>
       <c r="Q186" t="n">
-        <v>676800</v>
+        <v>566400</v>
       </c>
     </row>
     <row r="187">
@@ -8600,10 +8600,10 @@
         <v>82</v>
       </c>
       <c r="N189" t="n">
-        <v>2267.048162926</v>
+        <v>2267.0481598668</v>
       </c>
       <c r="O189" t="n">
-        <v>185897.949359932</v>
+        <v>185897.9491090776</v>
       </c>
       <c r="P189" t="n">
         <v>3900</v>
@@ -8729,25 +8729,25 @@
         <v>12</v>
       </c>
       <c r="K192" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="L192" t="n">
         <v>0</v>
       </c>
       <c r="M192" t="n">
-        <v>12</v>
+        <v>76</v>
       </c>
       <c r="N192" t="n">
         <v>8012</v>
       </c>
       <c r="O192" t="n">
-        <v>96144</v>
+        <v>608912</v>
       </c>
       <c r="P192" t="n">
         <v>13200</v>
       </c>
       <c r="Q192" t="n">
-        <v>158400</v>
+        <v>1003200</v>
       </c>
     </row>
     <row r="193">
@@ -8961,10 +8961,10 @@
         <v>12</v>
       </c>
       <c r="N197" t="n">
-        <v>3594.2542480527</v>
+        <v>3594.2542307692</v>
       </c>
       <c r="O197" t="n">
-        <v>43131.0509766324</v>
+        <v>43131.0507692304</v>
       </c>
       <c r="P197" t="n">
         <v>6500</v>
@@ -9050,22 +9050,22 @@
         <v>0</v>
       </c>
       <c r="L199" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M199" t="n">
-        <v>2052</v>
+        <v>2047</v>
       </c>
       <c r="N199" t="n">
         <v>489.88</v>
       </c>
       <c r="O199" t="n">
-        <v>1005233.76</v>
+        <v>1002784.36</v>
       </c>
       <c r="P199" t="n">
         <v>700</v>
       </c>
       <c r="Q199" t="n">
-        <v>1436400</v>
+        <v>1432900</v>
       </c>
     </row>
     <row r="200">
@@ -9777,22 +9777,22 @@
         <v>0</v>
       </c>
       <c r="L215" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M215" t="n">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="N215" t="n">
         <v>1441.01</v>
       </c>
       <c r="O215" t="n">
-        <v>776704.39</v>
+        <v>773822.37</v>
       </c>
       <c r="P215" t="n">
         <v>2100</v>
       </c>
       <c r="Q215" t="n">
-        <v>1131900</v>
+        <v>1127700</v>
       </c>
     </row>
     <row r="216">
@@ -9862,22 +9862,22 @@
         <v>0</v>
       </c>
       <c r="L217" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M217" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="N217" t="n">
         <v>4193.85</v>
       </c>
       <c r="O217" t="n">
-        <v>301957.2</v>
+        <v>289375.65</v>
       </c>
       <c r="P217" t="n">
         <v>7500</v>
       </c>
       <c r="Q217" t="n">
-        <v>540000</v>
+        <v>517500</v>
       </c>
     </row>
     <row r="218">
@@ -9911,22 +9911,22 @@
         <v>0</v>
       </c>
       <c r="L218" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M218" t="n">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="N218" t="n">
-        <v>3041.6600123457</v>
+        <v>3041.6600124378</v>
       </c>
       <c r="O218" t="n">
-        <v>425832.401728398</v>
+        <v>416707.4217039786</v>
       </c>
       <c r="P218" t="n">
         <v>5500</v>
       </c>
       <c r="Q218" t="n">
-        <v>770000</v>
+        <v>753500</v>
       </c>
     </row>
     <row r="219">
@@ -9963,10 +9963,10 @@
         <v>71</v>
       </c>
       <c r="N219" t="n">
-        <v>4372.2107862617</v>
+        <v>4372.2107863175</v>
       </c>
       <c r="O219" t="n">
-        <v>310426.9658245808</v>
+        <v>310426.9658285425</v>
       </c>
       <c r="P219" t="n">
         <v>7500</v>
@@ -10003,22 +10003,22 @@
         <v>0</v>
       </c>
       <c r="L220" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="M220" t="n">
-        <v>529</v>
+        <v>508</v>
       </c>
       <c r="N220" t="n">
-        <v>1592.5677691978</v>
+        <v>1592.5677332171</v>
       </c>
       <c r="O220" t="n">
-        <v>842468.3499056363</v>
+        <v>809024.4084742869</v>
       </c>
       <c r="P220" t="n">
         <v>3900</v>
       </c>
       <c r="Q220" t="n">
-        <v>2063100</v>
+        <v>1981200</v>
       </c>
     </row>
     <row r="221">
@@ -10313,22 +10313,22 @@
         <v>0</v>
       </c>
       <c r="L227" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M227" t="n">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="N227" t="n">
         <v>4648.6</v>
       </c>
       <c r="O227" t="n">
-        <v>1668847.4</v>
+        <v>1659550.2</v>
       </c>
       <c r="P227" t="n">
         <v>8900</v>
       </c>
       <c r="Q227" t="n">
-        <v>3195100</v>
+        <v>3177300</v>
       </c>
     </row>
     <row r="228">
@@ -10628,22 +10628,22 @@
         <v>0</v>
       </c>
       <c r="L234" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M234" t="n">
-        <v>2327</v>
+        <v>2324</v>
       </c>
       <c r="N234" t="n">
         <v>1387.55</v>
       </c>
       <c r="O234" t="n">
-        <v>3228828.85</v>
+        <v>3224666.2</v>
       </c>
       <c r="P234" t="n">
         <v>2300</v>
       </c>
       <c r="Q234" t="n">
-        <v>5352100</v>
+        <v>5345200</v>
       </c>
     </row>
     <row r="235">
@@ -10822,10 +10822,10 @@
         <v>130</v>
       </c>
       <c r="N238" t="n">
-        <v>2021.7211191336</v>
+        <v>2021.7211218335</v>
       </c>
       <c r="O238" t="n">
-        <v>262823.745487368</v>
+        <v>262823.745838355</v>
       </c>
       <c r="P238" t="n">
         <v>2400</v>
@@ -11318,22 +11318,22 @@
         <v>0</v>
       </c>
       <c r="L249" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M249" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="N249" t="n">
-        <v>1630.9229788882</v>
+        <v>1630.9230192383</v>
       </c>
       <c r="O249" t="n">
-        <v>189187.0655510312</v>
+        <v>185925.2241931662</v>
       </c>
       <c r="P249" t="n">
         <v>2500</v>
       </c>
       <c r="Q249" t="n">
-        <v>290000</v>
+        <v>285000</v>
       </c>
     </row>
     <row r="250">
@@ -11370,10 +11370,10 @@
         <v>254</v>
       </c>
       <c r="N250" t="n">
-        <v>1550.1929105882</v>
+        <v>1550.19293615</v>
       </c>
       <c r="O250" t="n">
-        <v>393748.9992894028</v>
+        <v>393749.0057821</v>
       </c>
       <c r="P250" t="n">
         <v>2500</v>
@@ -11416,10 +11416,10 @@
         <v>681</v>
       </c>
       <c r="N251" t="n">
-        <v>2403.5099727039</v>
+        <v>2403.5100306848</v>
       </c>
       <c r="O251" t="n">
-        <v>1636790.291411356</v>
+        <v>1636790.330896349</v>
       </c>
       <c r="P251" t="n">
         <v>3500</v>
@@ -11456,22 +11456,22 @@
         <v>0</v>
       </c>
       <c r="L252" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M252" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="N252" t="n">
         <v>14778</v>
       </c>
       <c r="O252" t="n">
-        <v>443340</v>
+        <v>413784</v>
       </c>
       <c r="P252" t="n">
         <v>24900</v>
       </c>
       <c r="Q252" t="n">
-        <v>747000</v>
+        <v>697200</v>
       </c>
     </row>
     <row r="253">
@@ -12547,25 +12547,25 @@
         <v>82</v>
       </c>
       <c r="K277" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="L277" t="n">
         <v>0</v>
       </c>
       <c r="M277" t="n">
-        <v>82</v>
+        <v>226</v>
       </c>
       <c r="N277" t="n">
         <v>2029.8736372454</v>
       </c>
       <c r="O277" t="n">
-        <v>166449.6382541228</v>
+        <v>458751.4420174604</v>
       </c>
       <c r="P277" t="n">
         <v>3600</v>
       </c>
       <c r="Q277" t="n">
-        <v>295200</v>
+        <v>813600</v>
       </c>
     </row>
     <row r="278">
@@ -12597,10 +12597,10 @@
         <v>20</v>
       </c>
       <c r="N278" t="n">
-        <v>22485.695932203</v>
+        <v>22485.695927602</v>
       </c>
       <c r="O278" t="n">
-        <v>449713.91864406</v>
+        <v>449713.91855204</v>
       </c>
       <c r="P278" t="n">
         <v>36500</v>
@@ -12851,10 +12851,10 @@
         <v>64</v>
       </c>
       <c r="N284" t="n">
-        <v>2680.739700489</v>
+        <v>2680.7396999388</v>
       </c>
       <c r="O284" t="n">
-        <v>171567.340831296</v>
+        <v>171567.3407960832</v>
       </c>
       <c r="P284" t="n">
         <v>4900</v>
@@ -12929,25 +12929,25 @@
         <v>5</v>
       </c>
       <c r="K286" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L286" t="n">
         <v>0</v>
       </c>
       <c r="M286" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="N286" t="n">
         <v>14060.64</v>
       </c>
       <c r="O286" t="n">
-        <v>70303.2</v>
+        <v>407758.56</v>
       </c>
       <c r="P286" t="n">
         <v>22900</v>
       </c>
       <c r="Q286" t="n">
-        <v>114500</v>
+        <v>664100</v>
       </c>
     </row>
     <row r="287">
@@ -13203,22 +13203,22 @@
         <v>0</v>
       </c>
       <c r="L292" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M292" t="n">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="N292" t="n">
         <v>3877.89</v>
       </c>
       <c r="O292" t="n">
-        <v>476980.47</v>
+        <v>442079.46</v>
       </c>
       <c r="P292" t="n">
         <v>6500</v>
       </c>
       <c r="Q292" t="n">
-        <v>799500</v>
+        <v>741000</v>
       </c>
     </row>
     <row r="293">
@@ -13252,22 +13252,22 @@
         <v>0</v>
       </c>
       <c r="L293" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M293" t="n">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="N293" t="n">
-        <v>4285.1952263374</v>
+        <v>4285.1952479339</v>
       </c>
       <c r="O293" t="n">
-        <v>505653.0367078132</v>
+        <v>488512.2582644646</v>
       </c>
       <c r="P293" t="n">
         <v>6900</v>
       </c>
       <c r="Q293" t="n">
-        <v>814200</v>
+        <v>786600</v>
       </c>
     </row>
     <row r="294">
@@ -13517,10 +13517,10 @@
         <v>61</v>
       </c>
       <c r="N299" t="n">
-        <v>30244.600034662</v>
+        <v>30244.600034682</v>
       </c>
       <c r="O299" t="n">
-        <v>1844920.602114382</v>
+        <v>1844920.602115602</v>
       </c>
       <c r="P299" t="n">
         <v>48900</v>
@@ -13742,10 +13742,10 @@
         <v>44</v>
       </c>
       <c r="N304" t="n">
-        <v>13513.64294964</v>
+        <v>13513.642971014</v>
       </c>
       <c r="O304" t="n">
-        <v>594600.28978416</v>
+        <v>594600.290724616</v>
       </c>
       <c r="P304" t="n">
         <v>21900</v>
@@ -13966,22 +13966,22 @@
         <v>0</v>
       </c>
       <c r="L309" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M309" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N309" t="n">
         <v>4793.53</v>
       </c>
       <c r="O309" t="n">
-        <v>306785.92</v>
+        <v>301992.39</v>
       </c>
       <c r="P309" t="n">
         <v>7900</v>
       </c>
       <c r="Q309" t="n">
-        <v>505600</v>
+        <v>497700</v>
       </c>
     </row>
     <row r="310">
@@ -14243,10 +14243,10 @@
         <v>28</v>
       </c>
       <c r="N315" t="n">
-        <v>27123.765259259</v>
+        <v>27123.765250464</v>
       </c>
       <c r="O315" t="n">
-        <v>759465.4272592519</v>
+        <v>759465.427012992</v>
       </c>
       <c r="P315" t="n">
         <v>44500</v>
@@ -14591,10 +14591,10 @@
         <v>140</v>
       </c>
       <c r="N323" t="n">
-        <v>1560.9985110132</v>
+        <v>1560.9988178914</v>
       </c>
       <c r="O323" t="n">
-        <v>218539.791541848</v>
+        <v>218539.834504796</v>
       </c>
       <c r="P323" t="n">
         <v>2900</v>
@@ -14901,10 +14901,10 @@
         <v>156</v>
       </c>
       <c r="N330" t="n">
-        <v>7969.9501643017</v>
+        <v>7969.950164794</v>
       </c>
       <c r="O330" t="n">
-        <v>1243312.225631065</v>
+        <v>1243312.225707864</v>
       </c>
       <c r="P330" t="n">
         <v>12900</v>
@@ -15110,22 +15110,22 @@
         <v>0</v>
       </c>
       <c r="L335" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M335" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N335" t="n">
         <v>53742</v>
       </c>
       <c r="O335" t="n">
-        <v>161226</v>
+        <v>107484</v>
       </c>
       <c r="P335" t="n">
         <v>86900</v>
       </c>
       <c r="Q335" t="n">
-        <v>260700</v>
+        <v>173800</v>
       </c>
     </row>
     <row r="336">
@@ -15165,10 +15165,10 @@
         <v>22</v>
       </c>
       <c r="N336" t="n">
-        <v>548.14728797763</v>
+        <v>548.14728291317</v>
       </c>
       <c r="O336" t="n">
-        <v>12059.24033550786</v>
+        <v>12059.24022408974</v>
       </c>
       <c r="P336" t="n">
         <v>2000</v>
@@ -15623,22 +15623,22 @@
         <v>0</v>
       </c>
       <c r="L346" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M346" t="n">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="N346" t="n">
         <v>2634.61</v>
       </c>
       <c r="O346" t="n">
-        <v>463691.36</v>
+        <v>437345.26</v>
       </c>
       <c r="P346" t="n">
         <v>4200</v>
       </c>
       <c r="Q346" t="n">
-        <v>739200</v>
+        <v>697200</v>
       </c>
     </row>
     <row r="347">
@@ -15669,22 +15669,22 @@
         <v>0</v>
       </c>
       <c r="L347" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M347" t="n">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="N347" t="n">
-        <v>3113.8900239521</v>
+        <v>3113.8900249066</v>
       </c>
       <c r="O347" t="n">
-        <v>317616.7824431142</v>
+        <v>255338.9820423412</v>
       </c>
       <c r="P347" t="n">
         <v>5000</v>
       </c>
       <c r="Q347" t="n">
-        <v>510000</v>
+        <v>410000</v>
       </c>
     </row>
     <row r="348">
@@ -15715,22 +15715,22 @@
         <v>0</v>
       </c>
       <c r="L348" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M348" t="n">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="N348" t="n">
         <v>5569.98</v>
       </c>
       <c r="O348" t="n">
-        <v>350908.74</v>
+        <v>295208.94</v>
       </c>
       <c r="P348" t="n">
         <v>8900</v>
       </c>
       <c r="Q348" t="n">
-        <v>560700</v>
+        <v>471700</v>
       </c>
     </row>
     <row r="349">
@@ -15761,22 +15761,22 @@
         <v>0</v>
       </c>
       <c r="L349" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M349" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="N349" t="n">
         <v>4690.64</v>
       </c>
       <c r="O349" t="n">
-        <v>211078.8</v>
+        <v>117266</v>
       </c>
       <c r="P349" t="n">
         <v>7500</v>
       </c>
       <c r="Q349" t="n">
-        <v>337500</v>
+        <v>187500</v>
       </c>
     </row>
     <row r="350">
@@ -15807,22 +15807,22 @@
         <v>0</v>
       </c>
       <c r="L350" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M350" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="N350" t="n">
         <v>5410.72</v>
       </c>
       <c r="O350" t="n">
-        <v>670929.28</v>
+        <v>665518.5600000001</v>
       </c>
       <c r="P350" t="n">
         <v>8700</v>
       </c>
       <c r="Q350" t="n">
-        <v>1078800</v>
+        <v>1070100</v>
       </c>
     </row>
     <row r="351">
@@ -15859,10 +15859,10 @@
         <v>17</v>
       </c>
       <c r="N351" t="n">
-        <v>4163.1601639344</v>
+        <v>4163.1601724138</v>
       </c>
       <c r="O351" t="n">
-        <v>70773.7227868848</v>
+        <v>70773.7229310346</v>
       </c>
       <c r="P351" t="n">
         <v>6700</v>
@@ -15945,22 +15945,22 @@
         <v>0</v>
       </c>
       <c r="L353" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M353" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="N353" t="n">
         <v>3254.49</v>
       </c>
       <c r="O353" t="n">
-        <v>514209.42</v>
+        <v>510954.93</v>
       </c>
       <c r="P353" t="n">
         <v>5200</v>
       </c>
       <c r="Q353" t="n">
-        <v>821600</v>
+        <v>816400</v>
       </c>
     </row>
     <row r="354">
@@ -15991,22 +15991,22 @@
         <v>0</v>
       </c>
       <c r="L354" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M354" t="n">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="N354" t="n">
-        <v>5218.1704756757</v>
+        <v>5218.1704867257</v>
       </c>
       <c r="O354" t="n">
-        <v>532253.3885189213</v>
+        <v>516598.8781858443</v>
       </c>
       <c r="P354" t="n">
         <v>8500</v>
       </c>
       <c r="Q354" t="n">
-        <v>867000</v>
+        <v>841500</v>
       </c>
     </row>
     <row r="355">
@@ -16043,10 +16043,10 @@
         <v>145</v>
       </c>
       <c r="N355" t="n">
-        <v>1595.0095090439</v>
+        <v>1595.0094973545</v>
       </c>
       <c r="O355" t="n">
-        <v>231276.3788113655</v>
+        <v>231276.3771164025</v>
       </c>
       <c r="P355" t="n">
         <v>2600</v>
@@ -16083,22 +16083,22 @@
         <v>0</v>
       </c>
       <c r="L356" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M356" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N356" t="n">
-        <v>3610.6500232019</v>
+        <v>3610.6500236967</v>
       </c>
       <c r="O356" t="n">
-        <v>140815.3509048741</v>
+        <v>137204.7009004746</v>
       </c>
       <c r="P356" t="n">
         <v>5800</v>
       </c>
       <c r="Q356" t="n">
-        <v>226200</v>
+        <v>220400</v>
       </c>
     </row>
     <row r="357">
@@ -16175,22 +16175,22 @@
         <v>0</v>
       </c>
       <c r="L358" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M358" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N358" t="n">
         <v>4227.77</v>
       </c>
       <c r="O358" t="n">
-        <v>245210.66</v>
+        <v>240982.89</v>
       </c>
       <c r="P358" t="n">
         <v>6900</v>
       </c>
       <c r="Q358" t="n">
-        <v>400200</v>
+        <v>393300</v>
       </c>
     </row>
     <row r="359">
@@ -16221,22 +16221,22 @@
         <v>0</v>
       </c>
       <c r="L359" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M359" t="n">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="N359" t="n">
         <v>3965.02</v>
       </c>
       <c r="O359" t="n">
-        <v>646298.26</v>
+        <v>642333.24</v>
       </c>
       <c r="P359" t="n">
         <v>6500</v>
       </c>
       <c r="Q359" t="n">
-        <v>1059500</v>
+        <v>1053000</v>
       </c>
     </row>
     <row r="360">
@@ -16313,22 +16313,22 @@
         <v>0</v>
       </c>
       <c r="L361" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M361" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="N361" t="n">
-        <v>1664.3613046757</v>
+        <v>1664.3609992194</v>
       </c>
       <c r="O361" t="n">
-        <v>93204.2330618392</v>
+        <v>88211.13295862819</v>
       </c>
       <c r="P361" t="n">
         <v>2900</v>
       </c>
       <c r="Q361" t="n">
-        <v>162400</v>
+        <v>153700</v>
       </c>
     </row>
     <row r="362">
@@ -16920,10 +16920,10 @@
         <v>147</v>
       </c>
       <c r="N374" t="n">
-        <v>1778.4725093418</v>
+        <v>1778.4725198441</v>
       </c>
       <c r="O374" t="n">
-        <v>261435.4588732446</v>
+        <v>261435.4604170827</v>
       </c>
       <c r="P374" t="n">
         <v>4900</v>
@@ -19562,10 +19562,10 @@
         <v>271</v>
       </c>
       <c r="N431" t="n">
-        <v>2328.1187536917</v>
+        <v>2328.1187525865</v>
       </c>
       <c r="O431" t="n">
-        <v>630920.1822504507</v>
+        <v>630920.1819509414</v>
       </c>
       <c r="P431" t="n">
         <v>4500</v>
@@ -19602,22 +19602,22 @@
         <v>0</v>
       </c>
       <c r="L432" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M432" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="N432" t="n">
         <v>21676</v>
       </c>
       <c r="O432" t="n">
-        <v>802012</v>
+        <v>780336</v>
       </c>
       <c r="P432" t="n">
         <v>34900</v>
       </c>
       <c r="Q432" t="n">
-        <v>1291300</v>
+        <v>1256400</v>
       </c>
     </row>
     <row r="433">
@@ -19924,22 +19924,22 @@
         <v>0</v>
       </c>
       <c r="L439" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M439" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N439" t="n">
         <v>4544</v>
       </c>
       <c r="O439" t="n">
-        <v>458944</v>
+        <v>454400</v>
       </c>
       <c r="P439" t="n">
         <v>7900</v>
       </c>
       <c r="Q439" t="n">
-        <v>797900</v>
+        <v>790000</v>
       </c>
     </row>
     <row r="440">
@@ -20108,22 +20108,22 @@
         <v>0</v>
       </c>
       <c r="L443" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M443" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="N443" t="n">
-        <v>4907.821904048</v>
+        <v>4907.8219155354</v>
       </c>
       <c r="O443" t="n">
-        <v>269930.20472264</v>
+        <v>250298.9176923054</v>
       </c>
       <c r="P443" t="n">
         <v>8200</v>
       </c>
       <c r="Q443" t="n">
-        <v>451000</v>
+        <v>418200</v>
       </c>
     </row>
     <row r="444">
@@ -20482,10 +20482,10 @@
         <v>99</v>
       </c>
       <c r="N451" t="n">
-        <v>3903.7358605664</v>
+        <v>3903.7358951965</v>
       </c>
       <c r="O451" t="n">
-        <v>386469.8501960736</v>
+        <v>386469.8536244535</v>
       </c>
       <c r="P451" t="n">
         <v>7500</v>
@@ -21116,10 +21116,10 @@
         <v>205</v>
       </c>
       <c r="N465" t="n">
-        <v>5869.1727610442</v>
+        <v>5869.1727464789</v>
       </c>
       <c r="O465" t="n">
-        <v>1203180.416014061</v>
+        <v>1203180.413028175</v>
       </c>
       <c r="P465" t="n">
         <v>9500</v>
@@ -21570,22 +21570,22 @@
         <v>0</v>
       </c>
       <c r="L475" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M475" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="N475" t="n">
         <v>3898</v>
       </c>
       <c r="O475" t="n">
-        <v>93552</v>
+        <v>85756</v>
       </c>
       <c r="P475" t="n">
         <v>6900</v>
       </c>
       <c r="Q475" t="n">
-        <v>165600</v>
+        <v>151800</v>
       </c>
     </row>
     <row r="476">
@@ -23089,22 +23089,22 @@
         <v>0</v>
       </c>
       <c r="L508" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M508" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="N508" t="n">
         <v>4303</v>
       </c>
       <c r="O508" t="n">
-        <v>240968</v>
+        <v>228059</v>
       </c>
       <c r="P508" t="n">
         <v>7900</v>
       </c>
       <c r="Q508" t="n">
-        <v>442400</v>
+        <v>418700</v>
       </c>
     </row>
     <row r="509">
@@ -23224,25 +23224,25 @@
         <v>6</v>
       </c>
       <c r="K511" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="L511" t="n">
         <v>0</v>
       </c>
       <c r="M511" t="n">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="N511" t="n">
         <v>8700</v>
       </c>
       <c r="O511" t="n">
-        <v>52200</v>
+        <v>365400</v>
       </c>
       <c r="P511" t="n">
         <v>14900</v>
       </c>
       <c r="Q511" t="n">
-        <v>89400</v>
+        <v>625800</v>
       </c>
     </row>
     <row r="512">
@@ -24064,10 +24064,10 @@
         <v>253</v>
       </c>
       <c r="N529" t="n">
-        <v>1516.0388166875</v>
+        <v>1516.0388137227</v>
       </c>
       <c r="O529" t="n">
-        <v>383557.8206219375</v>
+        <v>383557.8198718431</v>
       </c>
       <c r="P529" t="n">
         <v>2300</v>
@@ -24156,10 +24156,10 @@
         <v>453</v>
       </c>
       <c r="N531" t="n">
-        <v>2458.5134637046</v>
+        <v>2458.5134514107</v>
       </c>
       <c r="O531" t="n">
-        <v>1113706.599058184</v>
+        <v>1113706.593489047</v>
       </c>
       <c r="P531" t="n">
         <v>3500</v>
@@ -24334,22 +24334,22 @@
         <v>0</v>
       </c>
       <c r="L535" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M535" t="n">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="N535" t="n">
-        <v>1803.0149852941</v>
+        <v>1803.0149867608</v>
       </c>
       <c r="O535" t="n">
-        <v>613025.0949999939</v>
+        <v>611222.0805119112</v>
       </c>
       <c r="P535" t="n">
         <v>2500</v>
       </c>
       <c r="Q535" t="n">
-        <v>850000</v>
+        <v>847500</v>
       </c>
     </row>
     <row r="536">
@@ -24478,10 +24478,10 @@
         <v>313</v>
       </c>
       <c r="N538" t="n">
-        <v>2108.7897270195</v>
+        <v>2108.7897651007</v>
       </c>
       <c r="O538" t="n">
-        <v>660051.1845571034</v>
+        <v>660051.1964765191</v>
       </c>
       <c r="P538" t="n">
         <v>2900</v>
@@ -24524,10 +24524,10 @@
         <v>409</v>
       </c>
       <c r="N539" t="n">
-        <v>2056.0839525344</v>
+        <v>2056.0838952972</v>
       </c>
       <c r="O539" t="n">
-        <v>840938.3365865696</v>
+        <v>840938.3131765547</v>
       </c>
       <c r="P539" t="n">
         <v>2900</v>
@@ -24570,10 +24570,10 @@
         <v>366</v>
       </c>
       <c r="N540" t="n">
-        <v>3224.5679308817</v>
+        <v>3224.5679626335</v>
       </c>
       <c r="O540" t="n">
-        <v>1180191.862702702</v>
+        <v>1180191.874323861</v>
       </c>
       <c r="P540" t="n">
         <v>4500</v>
@@ -24610,22 +24610,22 @@
         <v>0</v>
       </c>
       <c r="L541" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M541" t="n">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="N541" t="n">
-        <v>1655.9314259144</v>
+        <v>1655.93135625</v>
       </c>
       <c r="O541" t="n">
-        <v>501747.2220520632</v>
+        <v>496779.406875</v>
       </c>
       <c r="P541" t="n">
         <v>2500</v>
       </c>
       <c r="Q541" t="n">
-        <v>757500</v>
+        <v>750000</v>
       </c>
     </row>
     <row r="542">
@@ -24656,22 +24656,22 @@
         <v>0</v>
       </c>
       <c r="L542" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M542" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="N542" t="n">
         <v>3684</v>
       </c>
       <c r="O542" t="n">
-        <v>257880</v>
+        <v>250512</v>
       </c>
       <c r="P542" t="n">
         <v>6500</v>
       </c>
       <c r="Q542" t="n">
-        <v>455000</v>
+        <v>442000</v>
       </c>
     </row>
     <row r="543">
@@ -24748,22 +24748,22 @@
         <v>0</v>
       </c>
       <c r="L544" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M544" t="n">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="N544" t="n">
         <v>2454</v>
       </c>
       <c r="O544" t="n">
-        <v>201228</v>
+        <v>161964</v>
       </c>
       <c r="P544" t="n">
         <v>4200</v>
       </c>
       <c r="Q544" t="n">
-        <v>344400</v>
+        <v>277200</v>
       </c>
     </row>
     <row r="545">
@@ -24794,22 +24794,22 @@
         <v>0</v>
       </c>
       <c r="L545" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M545" t="n">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="N545" t="n">
-        <v>1592.2745718734</v>
+        <v>1592.2746762208</v>
       </c>
       <c r="O545" t="n">
-        <v>442652.3309808052</v>
+        <v>436283.2612844992</v>
       </c>
       <c r="P545" t="n">
         <v>2500</v>
       </c>
       <c r="Q545" t="n">
-        <v>695000</v>
+        <v>685000</v>
       </c>
     </row>
     <row r="546">
@@ -24884,22 +24884,22 @@
         <v>0</v>
       </c>
       <c r="L547" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M547" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="N547" t="n">
-        <v>1906.1870703125</v>
+        <v>1906.1869325153</v>
       </c>
       <c r="O547" t="n">
-        <v>22874.24484375</v>
+        <v>15249.4954601224</v>
       </c>
       <c r="P547" t="n">
         <v>2900</v>
       </c>
       <c r="Q547" t="n">
-        <v>34800</v>
+        <v>23200</v>
       </c>
     </row>
     <row r="548">
@@ -24930,22 +24930,22 @@
         <v>0</v>
       </c>
       <c r="L548" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M548" t="n">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="N548" t="n">
-        <v>1668.6141040462</v>
+        <v>1668.6155910543</v>
       </c>
       <c r="O548" t="n">
-        <v>208576.763005775</v>
+        <v>201902.4865175703</v>
       </c>
       <c r="P548" t="n">
         <v>2500</v>
       </c>
       <c r="Q548" t="n">
-        <v>312500</v>
+        <v>302500</v>
       </c>
     </row>
     <row r="549">
@@ -24982,10 +24982,10 @@
         <v>54</v>
       </c>
       <c r="N549" t="n">
-        <v>2546.9853442623</v>
+        <v>2546.9852428811</v>
       </c>
       <c r="O549" t="n">
-        <v>137537.2085901642</v>
+        <v>137537.2031155794</v>
       </c>
       <c r="P549" t="n">
         <v>3900</v>
@@ -25028,10 +25028,10 @@
         <v>996</v>
       </c>
       <c r="N550" t="n">
-        <v>1259.274396777</v>
+        <v>1259.2744102228</v>
       </c>
       <c r="O550" t="n">
-        <v>1254237.299189892</v>
+        <v>1254237.312581909</v>
       </c>
       <c r="P550" t="n">
         <v>1900</v>
@@ -25114,22 +25114,22 @@
         <v>0</v>
       </c>
       <c r="L552" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M552" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="N552" t="n">
         <v>2944</v>
       </c>
       <c r="O552" t="n">
-        <v>23552</v>
+        <v>8832</v>
       </c>
       <c r="P552" t="n">
         <v>4900</v>
       </c>
       <c r="Q552" t="n">
-        <v>39200</v>
+        <v>14700</v>
       </c>
     </row>
     <row r="553">
@@ -25161,10 +25161,10 @@
         <v>228</v>
       </c>
       <c r="N553" t="n">
-        <v>2842.2738221529</v>
+        <v>2842.2737931034</v>
       </c>
       <c r="O553" t="n">
-        <v>648038.4314508612</v>
+        <v>648038.4248275752</v>
       </c>
       <c r="P553" t="n">
         <v>4900</v>
@@ -25244,25 +25244,25 @@
         <v>194</v>
       </c>
       <c r="K555" t="n">
-        <v>0</v>
+        <v>432</v>
       </c>
       <c r="L555" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M555" t="n">
-        <v>194</v>
+        <v>611</v>
       </c>
       <c r="N555" t="n">
         <v>1801</v>
       </c>
       <c r="O555" t="n">
-        <v>349394</v>
+        <v>1100411</v>
       </c>
       <c r="P555" t="n">
         <v>2900</v>
       </c>
       <c r="Q555" t="n">
-        <v>562600</v>
+        <v>1771900</v>
       </c>
     </row>
     <row r="556">
@@ -25297,10 +25297,10 @@
         <v>342</v>
       </c>
       <c r="N556" t="n">
-        <v>692.1520380194499</v>
+        <v>692.15204525288</v>
       </c>
       <c r="O556" t="n">
-        <v>236715.9970026519</v>
+        <v>236715.999476485</v>
       </c>
       <c r="P556" t="n">
         <v>1200</v>
@@ -25666,25 +25666,25 @@
         <v>51</v>
       </c>
       <c r="K564" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L564" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M564" t="n">
-        <v>51</v>
+        <v>143</v>
       </c>
       <c r="N564" t="n">
         <v>8945.379999999999</v>
       </c>
       <c r="O564" t="n">
-        <v>456214.3799999999</v>
+        <v>1279189.34</v>
       </c>
       <c r="P564" t="n">
         <v>14900</v>
       </c>
       <c r="Q564" t="n">
-        <v>759900</v>
+        <v>2130700</v>
       </c>
     </row>
     <row r="565">
@@ -25721,10 +25721,10 @@
         <v>68</v>
       </c>
       <c r="N565" t="n">
-        <v>3026.5146116505</v>
+        <v>3026.514679803</v>
       </c>
       <c r="O565" t="n">
-        <v>205802.993592234</v>
+        <v>205802.998226604</v>
       </c>
       <c r="P565" t="n">
         <v>7000</v>
@@ -26421,22 +26421,22 @@
         <v>0</v>
       </c>
       <c r="L580" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M580" t="n">
-        <v>1341</v>
+        <v>1339</v>
       </c>
       <c r="N580" t="n">
         <v>1828.64</v>
       </c>
       <c r="O580" t="n">
-        <v>2452206.24</v>
+        <v>2448548.96</v>
       </c>
       <c r="P580" t="n">
         <v>2000</v>
       </c>
       <c r="Q580" t="n">
-        <v>2682000</v>
+        <v>2678000</v>
       </c>
     </row>
     <row r="581">
@@ -26517,10 +26517,10 @@
         <v>354</v>
       </c>
       <c r="N582" t="n">
-        <v>481.48791484103</v>
+        <v>481.48791460674</v>
       </c>
       <c r="O582" t="n">
-        <v>170446.7218537246</v>
+        <v>170446.721770786</v>
       </c>
       <c r="P582" t="n">
         <v>650</v>
@@ -26697,22 +26697,22 @@
         <v>0</v>
       </c>
       <c r="L586" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M586" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="N586" t="n">
-        <v>3907.5003187251</v>
+        <v>3907.5003212851</v>
       </c>
       <c r="O586" t="n">
-        <v>113317.5092430279</v>
+        <v>105502.5086746977</v>
       </c>
       <c r="P586" t="n">
         <v>3900</v>
       </c>
       <c r="Q586" t="n">
-        <v>113100</v>
+        <v>105300</v>
       </c>
     </row>
     <row r="587">
@@ -26975,22 +26975,22 @@
         <v>0</v>
       </c>
       <c r="L592" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M592" t="n">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="N592" t="n">
-        <v>1283.6542902208</v>
+        <v>1283.6540655738</v>
       </c>
       <c r="O592" t="n">
-        <v>189980.8349526784</v>
+        <v>174576.9529180368</v>
       </c>
       <c r="P592" t="n">
         <v>1900</v>
       </c>
       <c r="Q592" t="n">
-        <v>281200</v>
+        <v>258400</v>
       </c>
     </row>
     <row r="593">
@@ -27067,22 +27067,22 @@
         <v>0</v>
       </c>
       <c r="L594" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M594" t="n">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="N594" t="n">
         <v>1326</v>
       </c>
       <c r="O594" t="n">
-        <v>547638</v>
+        <v>539682</v>
       </c>
       <c r="P594" t="n">
         <v>2900</v>
       </c>
       <c r="Q594" t="n">
-        <v>1197700</v>
+        <v>1180300</v>
       </c>
     </row>
     <row r="595">
@@ -27250,22 +27250,22 @@
         <v>0</v>
       </c>
       <c r="L598" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M598" t="n">
-        <v>2772</v>
+        <v>2752</v>
       </c>
       <c r="N598" t="n">
-        <v>517.28747614462</v>
+        <v>517.28760395334</v>
       </c>
       <c r="O598" t="n">
-        <v>1433920.883872887</v>
+        <v>1423575.486079592</v>
       </c>
       <c r="P598" t="n">
         <v>900</v>
       </c>
       <c r="Q598" t="n">
-        <v>2494800</v>
+        <v>2476800</v>
       </c>
     </row>
     <row r="599">
@@ -27481,22 +27481,22 @@
         <v>0</v>
       </c>
       <c r="L603" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M603" t="n">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="N603" t="n">
-        <v>3110.8433414956</v>
+        <v>3110.843282022</v>
       </c>
       <c r="O603" t="n">
-        <v>1278556.613354692</v>
+        <v>1256780.685936888</v>
       </c>
       <c r="P603" t="n">
         <v>4500</v>
       </c>
       <c r="Q603" t="n">
-        <v>1849500</v>
+        <v>1818000</v>
       </c>
     </row>
     <row r="604">
@@ -27522,25 +27522,25 @@
         <v>495</v>
       </c>
       <c r="K604" t="n">
-        <v>0</v>
+        <v>576</v>
       </c>
       <c r="L604" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M604" t="n">
-        <v>495</v>
+        <v>1067</v>
       </c>
       <c r="N604" t="n">
-        <v>703.79545471015</v>
+        <v>703.79543678174</v>
       </c>
       <c r="O604" t="n">
-        <v>348378.7500815243</v>
+        <v>750949.7310461166</v>
       </c>
       <c r="P604" t="n">
         <v>900</v>
       </c>
       <c r="Q604" t="n">
-        <v>445500</v>
+        <v>960300</v>
       </c>
     </row>
     <row r="605">
@@ -27571,22 +27571,22 @@
         <v>0</v>
       </c>
       <c r="L605" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M605" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N605" t="n">
-        <v>2501.3854811715</v>
+        <v>2501.3854621849</v>
       </c>
       <c r="O605" t="n">
-        <v>27515.2402928865</v>
+        <v>25013.854621849</v>
       </c>
       <c r="P605" t="n">
         <v>4100</v>
       </c>
       <c r="Q605" t="n">
-        <v>45100</v>
+        <v>41000</v>
       </c>
     </row>
     <row r="606">
@@ -27859,22 +27859,22 @@
         <v>0</v>
       </c>
       <c r="L611" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="M611" t="n">
-        <v>464</v>
+        <v>438</v>
       </c>
       <c r="N611" t="n">
-        <v>1595.51921946</v>
+        <v>1595.5191410878</v>
       </c>
       <c r="O611" t="n">
-        <v>740320.91782944</v>
+        <v>698837.3837964565</v>
       </c>
       <c r="P611" t="n">
         <v>2500</v>
       </c>
       <c r="Q611" t="n">
-        <v>1160000</v>
+        <v>1095000</v>
       </c>
     </row>
     <row r="612">
@@ -28680,22 +28680,22 @@
         <v>0</v>
       </c>
       <c r="L628" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M628" t="n">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="N628" t="n">
         <v>1669.6</v>
       </c>
       <c r="O628" t="n">
-        <v>1013447.2</v>
+        <v>1010108</v>
       </c>
       <c r="P628" t="n">
         <v>2900</v>
       </c>
       <c r="Q628" t="n">
-        <v>1760300</v>
+        <v>1754500</v>
       </c>
     </row>
     <row r="629">
@@ -29982,10 +29982,10 @@
         <v>69</v>
       </c>
       <c r="N655" t="n">
-        <v>875.6901492537301</v>
+        <v>875.69015037594</v>
       </c>
       <c r="O655" t="n">
-        <v>60422.62029850738</v>
+        <v>60422.62037593986</v>
       </c>
       <c r="P655" t="n">
         <v>4500</v>
@@ -30555,22 +30555,22 @@
         <v>0</v>
       </c>
       <c r="L667" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M667" t="n">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="N667" t="n">
         <v>5347.88</v>
       </c>
       <c r="O667" t="n">
-        <v>716615.92</v>
+        <v>700572.28</v>
       </c>
       <c r="P667" t="n">
         <v>7900</v>
       </c>
       <c r="Q667" t="n">
-        <v>1058600</v>
+        <v>1034900</v>
       </c>
     </row>
     <row r="668">
@@ -30604,22 +30604,22 @@
         <v>0</v>
       </c>
       <c r="L668" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M668" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="N668" t="n">
         <v>4578.04</v>
       </c>
       <c r="O668" t="n">
-        <v>389133.4</v>
+        <v>379977.32</v>
       </c>
       <c r="P668" t="n">
         <v>7500</v>
       </c>
       <c r="Q668" t="n">
-        <v>637500</v>
+        <v>622500</v>
       </c>
     </row>
     <row r="669">
@@ -32131,10 +32131,10 @@
         <v>135</v>
       </c>
       <c r="N700" t="n">
-        <v>7046.9398305803</v>
+        <v>7046.9398302567</v>
       </c>
       <c r="O700" t="n">
-        <v>951336.8771283404</v>
+        <v>951336.8770846544</v>
       </c>
       <c r="P700" t="n">
         <v>9900</v>
@@ -32171,22 +32171,22 @@
         <v>0</v>
       </c>
       <c r="L701" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M701" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N701" t="n">
         <v>24338.47</v>
       </c>
       <c r="O701" t="n">
-        <v>705815.63</v>
+        <v>681477.16</v>
       </c>
       <c r="P701" t="n">
         <v>27900</v>
       </c>
       <c r="Q701" t="n">
-        <v>809100</v>
+        <v>781200</v>
       </c>
     </row>
     <row r="702">
@@ -32652,22 +32652,22 @@
         <v>0</v>
       </c>
       <c r="L711" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M711" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="N711" t="n">
         <v>4581.84</v>
       </c>
       <c r="O711" t="n">
-        <v>123709.68</v>
+        <v>87054.96000000001</v>
       </c>
       <c r="P711" t="n">
         <v>7900</v>
       </c>
       <c r="Q711" t="n">
-        <v>213300</v>
+        <v>150100</v>
       </c>
     </row>
     <row r="712">
@@ -32701,22 +32701,22 @@
         <v>0</v>
       </c>
       <c r="L712" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M712" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N712" t="n">
         <v>3155</v>
       </c>
       <c r="O712" t="n">
-        <v>268175</v>
+        <v>265020</v>
       </c>
       <c r="P712" t="n">
         <v>5900</v>
       </c>
       <c r="Q712" t="n">
-        <v>501500</v>
+        <v>495600</v>
       </c>
     </row>
     <row r="713">
@@ -33299,22 +33299,22 @@
         <v>0</v>
       </c>
       <c r="L725" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M725" t="n">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="N725" t="n">
         <v>3181.9</v>
       </c>
       <c r="O725" t="n">
-        <v>575923.9</v>
+        <v>544104.9</v>
       </c>
       <c r="P725" t="n">
         <v>5100</v>
       </c>
       <c r="Q725" t="n">
-        <v>923100</v>
+        <v>872100</v>
       </c>
     </row>
     <row r="726">
@@ -33346,10 +33346,10 @@
         <v>10</v>
       </c>
       <c r="N726" t="n">
-        <v>1213.6821153846</v>
+        <v>1213.6821194605</v>
       </c>
       <c r="O726" t="n">
-        <v>12136.821153846</v>
+        <v>12136.821194605</v>
       </c>
       <c r="P726" t="n">
         <v>1500</v>
@@ -33430,22 +33430,22 @@
         <v>0</v>
       </c>
       <c r="L728" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M728" t="n">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="N728" t="n">
         <v>5077</v>
       </c>
       <c r="O728" t="n">
-        <v>812320</v>
+        <v>792012</v>
       </c>
       <c r="P728" t="n">
         <v>8500</v>
       </c>
       <c r="Q728" t="n">
-        <v>1360000</v>
+        <v>1326000</v>
       </c>
     </row>
     <row r="729">
@@ -33569,10 +33569,10 @@
         <v>12</v>
       </c>
       <c r="N731" t="n">
-        <v>4985.4045627376</v>
+        <v>4985.4046332046</v>
       </c>
       <c r="O731" t="n">
-        <v>59824.8547528512</v>
+        <v>59824.8555984552</v>
       </c>
       <c r="P731" t="n">
         <v>7900</v>

--- a/bodegas/LJ-05.xlsx
+++ b/bodegas/LJ-05.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-09</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-10</t>
         </is>
       </c>
     </row>

--- a/bodegas/LJ-05.xlsx
+++ b/bodegas/LJ-05.xlsx
@@ -738,10 +738,10 @@
         <v>3</v>
       </c>
       <c r="N8" t="n">
-        <v>74676.65386363601</v>
+        <v>74676.651315789</v>
       </c>
       <c r="O8" t="n">
-        <v>224029.961590908</v>
+        <v>224029.953947367</v>
       </c>
       <c r="P8" t="n">
         <v>144900</v>
@@ -987,10 +987,10 @@
         <v>131</v>
       </c>
       <c r="N14" t="n">
-        <v>3376.7465175202</v>
+        <v>3376.746511879</v>
       </c>
       <c r="O14" t="n">
-        <v>442353.7937951462</v>
+        <v>442353.793056149</v>
       </c>
       <c r="P14" t="n">
         <v>4500</v>
@@ -1224,10 +1224,10 @@
         <v>8</v>
       </c>
       <c r="N20" t="n">
-        <v>27815.961111111</v>
+        <v>27815.961126761</v>
       </c>
       <c r="O20" t="n">
-        <v>222527.688888888</v>
+        <v>222527.689014088</v>
       </c>
       <c r="P20" t="n">
         <v>58600</v>
@@ -3058,10 +3058,10 @@
         <v>15</v>
       </c>
       <c r="N63" t="n">
-        <v>16486.410204082</v>
+        <v>16486.41</v>
       </c>
       <c r="O63" t="n">
-        <v>247296.15306123</v>
+        <v>247296.15</v>
       </c>
       <c r="P63" t="n">
         <v>30500</v>
@@ -3100,10 +3100,10 @@
         <v>41</v>
       </c>
       <c r="N64" t="n">
-        <v>15711.9662</v>
+        <v>15711.966184739</v>
       </c>
       <c r="O64" t="n">
-        <v>644190.6142000001</v>
+        <v>644190.613574299</v>
       </c>
       <c r="P64" t="n">
         <v>28500</v>
@@ -3147,10 +3147,10 @@
         <v>24</v>
       </c>
       <c r="N65" t="n">
-        <v>9392.0745333333</v>
+        <v>9392.0745945946</v>
       </c>
       <c r="O65" t="n">
-        <v>225409.7887999992</v>
+        <v>225409.7902702704</v>
       </c>
       <c r="P65" t="n">
         <v>18500</v>
@@ -3958,10 +3958,10 @@
         <v>5</v>
       </c>
       <c r="N84" t="n">
-        <v>200072.19914894</v>
+        <v>200072.19977273</v>
       </c>
       <c r="O84" t="n">
-        <v>1000360.9957447</v>
+        <v>1000360.99886365</v>
       </c>
       <c r="P84" t="n">
         <v>312000</v>
@@ -7640,10 +7640,10 @@
         <v>712</v>
       </c>
       <c r="N168" t="n">
-        <v>2694.8235120643</v>
+        <v>2694.8234975369</v>
       </c>
       <c r="O168" t="n">
-        <v>1918714.340589782</v>
+        <v>1918714.330246273</v>
       </c>
       <c r="P168" t="n">
         <v>4900</v>
@@ -8366,22 +8366,22 @@
         <v>0</v>
       </c>
       <c r="L184" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M184" t="n">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="N184" t="n">
         <v>1203.38</v>
       </c>
       <c r="O184" t="n">
-        <v>225032.06</v>
+        <v>220218.54</v>
       </c>
       <c r="P184" t="n">
         <v>1900</v>
       </c>
       <c r="Q184" t="n">
-        <v>355300</v>
+        <v>347700</v>
       </c>
     </row>
     <row r="185">
@@ -9145,10 +9145,10 @@
         <v>33</v>
       </c>
       <c r="N201" t="n">
-        <v>14822.378867925</v>
+        <v>14822.378867257</v>
       </c>
       <c r="O201" t="n">
-        <v>489138.502641525</v>
+        <v>489138.502619481</v>
       </c>
       <c r="P201" t="n">
         <v>24900</v>
@@ -9868,10 +9868,10 @@
         <v>137</v>
       </c>
       <c r="N217" t="n">
-        <v>3041.6600124378</v>
+        <v>3041.6600124456</v>
       </c>
       <c r="O217" t="n">
-        <v>416707.4217039786</v>
+        <v>416707.4217050472</v>
       </c>
       <c r="P217" t="n">
         <v>5500</v>
@@ -9960,10 +9960,10 @@
         <v>508</v>
       </c>
       <c r="N219" t="n">
-        <v>1592.5677332171</v>
+        <v>1592.567707231</v>
       </c>
       <c r="O219" t="n">
-        <v>809024.4084742869</v>
+        <v>809024.395273348</v>
       </c>
       <c r="P219" t="n">
         <v>3900</v>
@@ -11275,10 +11275,10 @@
         <v>114</v>
       </c>
       <c r="N248" t="n">
-        <v>1630.9230192383</v>
+        <v>1630.9230407276</v>
       </c>
       <c r="O248" t="n">
-        <v>185925.2241931662</v>
+        <v>185925.2266429464</v>
       </c>
       <c r="P248" t="n">
         <v>2500</v>
@@ -11321,10 +11321,10 @@
         <v>254</v>
       </c>
       <c r="N249" t="n">
-        <v>1550.19293615</v>
+        <v>1550.1929579149</v>
       </c>
       <c r="O249" t="n">
-        <v>393749.0057821</v>
+        <v>393749.0113103846</v>
       </c>
       <c r="P249" t="n">
         <v>2500</v>
@@ -11367,10 +11367,10 @@
         <v>681</v>
       </c>
       <c r="N250" t="n">
-        <v>2403.5100306848</v>
+        <v>2403.5100778841</v>
       </c>
       <c r="O250" t="n">
-        <v>1636790.330896349</v>
+        <v>1636790.363039072</v>
       </c>
       <c r="P250" t="n">
         <v>3500</v>
@@ -12507,10 +12507,10 @@
         <v>226</v>
       </c>
       <c r="N276" t="n">
-        <v>2029.8736372454</v>
+        <v>2029.8736443149</v>
       </c>
       <c r="O276" t="n">
-        <v>458751.4420174604</v>
+        <v>458751.4436151674</v>
       </c>
       <c r="P276" t="n">
         <v>3600</v>
@@ -13514,10 +13514,10 @@
         <v>72</v>
       </c>
       <c r="N299" t="n">
-        <v>4605.2146231618</v>
+        <v>4605.2146487985</v>
       </c>
       <c r="O299" t="n">
-        <v>331575.4528676496</v>
+        <v>331575.454713492</v>
       </c>
       <c r="P299" t="n">
         <v>7600</v>
@@ -13917,22 +13917,22 @@
         <v>0</v>
       </c>
       <c r="L308" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M308" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="N308" t="n">
         <v>4793.53</v>
       </c>
       <c r="O308" t="n">
-        <v>301992.39</v>
+        <v>287611.8</v>
       </c>
       <c r="P308" t="n">
         <v>7900</v>
       </c>
       <c r="Q308" t="n">
-        <v>497700</v>
+        <v>474000</v>
       </c>
     </row>
     <row r="309">
@@ -14542,10 +14542,10 @@
         <v>140</v>
       </c>
       <c r="N322" t="n">
-        <v>1560.9988178914</v>
+        <v>1560.9988868445</v>
       </c>
       <c r="O322" t="n">
-        <v>218539.834504796</v>
+        <v>218539.84415823</v>
       </c>
       <c r="P322" t="n">
         <v>2900</v>
@@ -15626,10 +15626,10 @@
         <v>82</v>
       </c>
       <c r="N346" t="n">
-        <v>3113.8900249066</v>
+        <v>3113.8900261438</v>
       </c>
       <c r="O346" t="n">
-        <v>255338.9820423412</v>
+        <v>255338.9821437916</v>
       </c>
       <c r="P346" t="n">
         <v>5000</v>
@@ -15948,10 +15948,10 @@
         <v>99</v>
       </c>
       <c r="N353" t="n">
-        <v>5218.1704867257</v>
+        <v>5218.170490524</v>
       </c>
       <c r="O353" t="n">
-        <v>516598.8781858443</v>
+        <v>516598.878561876</v>
       </c>
       <c r="P353" t="n">
         <v>8500</v>
@@ -15994,10 +15994,10 @@
         <v>145</v>
       </c>
       <c r="N354" t="n">
-        <v>1595.0094973545</v>
+        <v>1595.0094864865</v>
       </c>
       <c r="O354" t="n">
-        <v>231276.3771164025</v>
+        <v>231276.3755405425</v>
       </c>
       <c r="P354" t="n">
         <v>2600</v>
@@ -16040,10 +16040,10 @@
         <v>38</v>
       </c>
       <c r="N355" t="n">
-        <v>3610.6500236967</v>
+        <v>3610.6500238379</v>
       </c>
       <c r="O355" t="n">
-        <v>137204.7009004746</v>
+        <v>137204.7009058402</v>
       </c>
       <c r="P355" t="n">
         <v>5800</v>
@@ -16270,10 +16270,10 @@
         <v>53</v>
       </c>
       <c r="N360" t="n">
-        <v>1664.3609992194</v>
+        <v>1664.360841938</v>
       </c>
       <c r="O360" t="n">
-        <v>88211.13295862819</v>
+        <v>88211.12462271401</v>
       </c>
       <c r="P360" t="n">
         <v>2900</v>
@@ -16779,10 +16779,10 @@
         <v>7</v>
       </c>
       <c r="N371" t="n">
-        <v>23521.624852941</v>
+        <v>23521.624776119</v>
       </c>
       <c r="O371" t="n">
-        <v>164651.373970587</v>
+        <v>164651.373432833</v>
       </c>
       <c r="P371" t="n">
         <v>39000</v>
@@ -16871,10 +16871,10 @@
         <v>147</v>
       </c>
       <c r="N373" t="n">
-        <v>1778.4725198441</v>
+        <v>1778.4725231214</v>
       </c>
       <c r="O373" t="n">
-        <v>261435.4604170827</v>
+        <v>261435.4608988458</v>
       </c>
       <c r="P373" t="n">
         <v>4900</v>
@@ -19326,10 +19326,10 @@
         <v>59</v>
       </c>
       <c r="N426" t="n">
-        <v>2252.2963076923</v>
+        <v>2252.2963603819</v>
       </c>
       <c r="O426" t="n">
-        <v>132885.4821538457</v>
+        <v>132885.4852625321</v>
       </c>
       <c r="P426" t="n">
         <v>3900</v>
@@ -20065,10 +20065,10 @@
         <v>51</v>
       </c>
       <c r="N442" t="n">
-        <v>4907.8219155354</v>
+        <v>4907.8219300912</v>
       </c>
       <c r="O442" t="n">
-        <v>250298.9176923054</v>
+        <v>250298.9184346512</v>
       </c>
       <c r="P442" t="n">
         <v>8200</v>
@@ -20433,10 +20433,10 @@
         <v>99</v>
       </c>
       <c r="N450" t="n">
-        <v>3903.7358951965</v>
+        <v>3903.7359183673</v>
       </c>
       <c r="O450" t="n">
-        <v>386469.8536244535</v>
+        <v>386469.8559183627</v>
       </c>
       <c r="P450" t="n">
         <v>7500</v>
@@ -20785,22 +20785,22 @@
         <v>0</v>
       </c>
       <c r="L458" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M458" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="N458" t="n">
         <v>4202</v>
       </c>
       <c r="O458" t="n">
-        <v>159676</v>
+        <v>147070</v>
       </c>
       <c r="P458" t="n">
         <v>7900</v>
       </c>
       <c r="Q458" t="n">
-        <v>300200</v>
+        <v>276500</v>
       </c>
     </row>
     <row r="459">
@@ -22220,10 +22220,10 @@
         <v>147</v>
       </c>
       <c r="N489" t="n">
-        <v>17075.98952512</v>
+        <v>17075.989524793</v>
       </c>
       <c r="O489" t="n">
-        <v>2510170.46019264</v>
+        <v>2510170.460144571</v>
       </c>
       <c r="P489" t="n">
         <v>27500</v>
@@ -24015,10 +24015,10 @@
         <v>253</v>
       </c>
       <c r="N528" t="n">
-        <v>1516.0388137227</v>
+        <v>1516.0388131508</v>
       </c>
       <c r="O528" t="n">
-        <v>383557.8198718431</v>
+        <v>383557.8197271524</v>
       </c>
       <c r="P528" t="n">
         <v>2300</v>
@@ -24199,10 +24199,10 @@
         <v>189</v>
       </c>
       <c r="N532" t="n">
-        <v>1771.091283906</v>
+        <v>1771.0912628399</v>
       </c>
       <c r="O532" t="n">
-        <v>334736.252658234</v>
+        <v>334736.2486767411</v>
       </c>
       <c r="P532" t="n">
         <v>2500</v>
@@ -24245,10 +24245,10 @@
         <v>465</v>
       </c>
       <c r="N533" t="n">
-        <v>2079.3842227979</v>
+        <v>2079.3842209265</v>
       </c>
       <c r="O533" t="n">
-        <v>966913.6636010234</v>
+        <v>966913.6627308225</v>
       </c>
       <c r="P533" t="n">
         <v>2900</v>
@@ -24291,10 +24291,10 @@
         <v>339</v>
       </c>
       <c r="N534" t="n">
-        <v>1803.0149867608</v>
+        <v>1803.0149882284</v>
       </c>
       <c r="O534" t="n">
-        <v>611222.0805119112</v>
+        <v>611222.0810094276</v>
       </c>
       <c r="P534" t="n">
         <v>2500</v>
@@ -24337,10 +24337,10 @@
         <v>108</v>
       </c>
       <c r="N535" t="n">
-        <v>3306.5954602774</v>
+        <v>3306.5954545455</v>
       </c>
       <c r="O535" t="n">
-        <v>357112.3097099592</v>
+        <v>357112.309090914</v>
       </c>
       <c r="P535" t="n">
         <v>4900</v>
@@ -24383,10 +24383,10 @@
         <v>565</v>
       </c>
       <c r="N536" t="n">
-        <v>2122.1641172932</v>
+        <v>2122.1641155235</v>
       </c>
       <c r="O536" t="n">
-        <v>1199022.726270658</v>
+        <v>1199022.725270778</v>
       </c>
       <c r="P536" t="n">
         <v>2900</v>
@@ -24429,10 +24429,10 @@
         <v>313</v>
       </c>
       <c r="N537" t="n">
-        <v>2108.7897651007</v>
+        <v>2108.7897869955</v>
       </c>
       <c r="O537" t="n">
-        <v>660051.1964765191</v>
+        <v>660051.2033295915</v>
       </c>
       <c r="P537" t="n">
         <v>2900</v>
@@ -24475,10 +24475,10 @@
         <v>409</v>
       </c>
       <c r="N538" t="n">
-        <v>2056.0838952972</v>
+        <v>2056.0838880663</v>
       </c>
       <c r="O538" t="n">
-        <v>840938.3131765547</v>
+        <v>840938.3102191167</v>
       </c>
       <c r="P538" t="n">
         <v>2900</v>
@@ -24567,10 +24567,10 @@
         <v>300</v>
       </c>
       <c r="N540" t="n">
-        <v>1655.93135625</v>
+        <v>1655.931342723</v>
       </c>
       <c r="O540" t="n">
-        <v>496779.406875</v>
+        <v>496779.4028169</v>
       </c>
       <c r="P540" t="n">
         <v>2500</v>
@@ -24751,10 +24751,10 @@
         <v>274</v>
       </c>
       <c r="N544" t="n">
-        <v>1592.2746762208</v>
+        <v>1592.2747647377</v>
       </c>
       <c r="O544" t="n">
-        <v>436283.2612844992</v>
+        <v>436283.2855381298</v>
       </c>
       <c r="P544" t="n">
         <v>2500</v>
@@ -24841,10 +24841,10 @@
         <v>8</v>
       </c>
       <c r="N546" t="n">
-        <v>1906.1869325153</v>
+        <v>1906.1867602592</v>
       </c>
       <c r="O546" t="n">
-        <v>15249.4954601224</v>
+        <v>15249.4940820736</v>
       </c>
       <c r="P546" t="n">
         <v>2900</v>
@@ -24887,10 +24887,10 @@
         <v>121</v>
       </c>
       <c r="N547" t="n">
-        <v>1668.6155910543</v>
+        <v>1668.6157419355</v>
       </c>
       <c r="O547" t="n">
-        <v>201902.4865175703</v>
+        <v>201902.5047741955</v>
       </c>
       <c r="P547" t="n">
         <v>2500</v>
@@ -24933,10 +24933,10 @@
         <v>54</v>
       </c>
       <c r="N548" t="n">
-        <v>2546.9852428811</v>
+        <v>2546.9851864407</v>
       </c>
       <c r="O548" t="n">
-        <v>137537.2031155794</v>
+        <v>137537.2000677978</v>
       </c>
       <c r="P548" t="n">
         <v>3900</v>
@@ -24979,10 +24979,10 @@
         <v>996</v>
       </c>
       <c r="N549" t="n">
-        <v>1259.2744102228</v>
+        <v>1259.2744140796</v>
       </c>
       <c r="O549" t="n">
-        <v>1254237.312581909</v>
+        <v>1254237.316423282</v>
       </c>
       <c r="P549" t="n">
         <v>1900</v>
@@ -25242,22 +25242,22 @@
         <v>0</v>
       </c>
       <c r="L555" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M555" t="n">
-        <v>342</v>
+        <v>330</v>
       </c>
       <c r="N555" t="n">
-        <v>692.15204525288</v>
+        <v>692.15205253785</v>
       </c>
       <c r="O555" t="n">
-        <v>236715.999476485</v>
+        <v>228410.1773374905</v>
       </c>
       <c r="P555" t="n">
         <v>1200</v>
       </c>
       <c r="Q555" t="n">
-        <v>410400</v>
+        <v>396000</v>
       </c>
     </row>
     <row r="556">
@@ -25386,10 +25386,10 @@
         <v>3423</v>
       </c>
       <c r="N558" t="n">
-        <v>1185.3195720165</v>
+        <v>1185.3195716639</v>
       </c>
       <c r="O558" t="n">
-        <v>4057348.895012479</v>
+        <v>4057348.893805529</v>
       </c>
       <c r="P558" t="n">
         <v>1900</v>
@@ -25672,10 +25672,10 @@
         <v>68</v>
       </c>
       <c r="N564" t="n">
-        <v>3026.514679803</v>
+        <v>3026.5146568627</v>
       </c>
       <c r="O564" t="n">
-        <v>205802.998226604</v>
+        <v>205802.9966666636</v>
       </c>
       <c r="P564" t="n">
         <v>7000</v>
@@ -26418,22 +26418,22 @@
         <v>0</v>
       </c>
       <c r="L580" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M580" t="n">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="N580" t="n">
-        <v>1690.8700088067</v>
+        <v>1690.8700088574</v>
       </c>
       <c r="O580" t="n">
-        <v>333101.3917349199</v>
+        <v>322956.1716917634</v>
       </c>
       <c r="P580" t="n">
         <v>3000</v>
       </c>
       <c r="Q580" t="n">
-        <v>591000</v>
+        <v>573000</v>
       </c>
     </row>
     <row r="581">
@@ -27207,10 +27207,10 @@
         <v>2752</v>
       </c>
       <c r="N597" t="n">
-        <v>517.28760395334</v>
+        <v>517.28764753291</v>
       </c>
       <c r="O597" t="n">
-        <v>1423575.486079592</v>
+        <v>1423575.606010568</v>
       </c>
       <c r="P597" t="n">
         <v>900</v>
@@ -27438,10 +27438,10 @@
         <v>404</v>
       </c>
       <c r="N602" t="n">
-        <v>3110.843282022</v>
+        <v>3110.8431677619</v>
       </c>
       <c r="O602" t="n">
-        <v>1256780.685936888</v>
+        <v>1256780.639775808</v>
       </c>
       <c r="P602" t="n">
         <v>4500</v>
@@ -27482,10 +27482,10 @@
         <v>1067</v>
       </c>
       <c r="N603" t="n">
-        <v>703.79543678174</v>
+        <v>703.79542528945</v>
       </c>
       <c r="O603" t="n">
-        <v>750949.7310461166</v>
+        <v>750949.7187838432</v>
       </c>
       <c r="P603" t="n">
         <v>900</v>
@@ -27528,10 +27528,10 @@
         <v>10</v>
       </c>
       <c r="N604" t="n">
-        <v>2501.3854621849</v>
+        <v>2501.385443038</v>
       </c>
       <c r="O604" t="n">
-        <v>25013.854621849</v>
+        <v>25013.85443038</v>
       </c>
       <c r="P604" t="n">
         <v>4100</v>
@@ -27810,22 +27810,22 @@
         <v>0</v>
       </c>
       <c r="L610" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M610" t="n">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="N610" t="n">
-        <v>1595.5191410878</v>
+        <v>1595.5191323094</v>
       </c>
       <c r="O610" t="n">
-        <v>698837.3837964565</v>
+        <v>694050.822554589</v>
       </c>
       <c r="P610" t="n">
         <v>2500</v>
       </c>
       <c r="Q610" t="n">
-        <v>1095000</v>
+        <v>1087500</v>
       </c>
     </row>
     <row r="611">
@@ -29596,10 +29596,10 @@
         <v>15</v>
       </c>
       <c r="N647" t="n">
-        <v>9746.8801869159</v>
+        <v>9746.880188679201</v>
       </c>
       <c r="O647" t="n">
-        <v>146203.2028037385</v>
+        <v>146203.202830188</v>
       </c>
       <c r="P647" t="n">
         <v>18500</v>
@@ -29927,22 +29927,22 @@
         <v>0</v>
       </c>
       <c r="L654" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M654" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="N654" t="n">
-        <v>875.69015037594</v>
+        <v>875.69015686275</v>
       </c>
       <c r="O654" t="n">
-        <v>60422.62037593986</v>
+        <v>56044.170039216</v>
       </c>
       <c r="P654" t="n">
         <v>4500</v>
       </c>
       <c r="Q654" t="n">
-        <v>310500</v>
+        <v>288000</v>
       </c>
     </row>
     <row r="655">
@@ -31268,10 +31268,10 @@
         <v>29</v>
       </c>
       <c r="N682" t="n">
-        <v>14751.8203125</v>
+        <v>14751.82031746</v>
       </c>
       <c r="O682" t="n">
-        <v>427802.7890625</v>
+        <v>427802.78920634</v>
       </c>
       <c r="P682" t="n">
         <v>37100</v>
@@ -31792,22 +31792,22 @@
         <v>0</v>
       </c>
       <c r="L693" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M693" t="n">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="N693" t="n">
         <v>711.48</v>
       </c>
       <c r="O693" t="n">
-        <v>81108.72</v>
+        <v>78974.28</v>
       </c>
       <c r="P693" t="n">
         <v>2500</v>
       </c>
       <c r="Q693" t="n">
-        <v>285000</v>
+        <v>277500</v>
       </c>
     </row>
     <row r="694">
@@ -32505,22 +32505,22 @@
         <v>0</v>
       </c>
       <c r="L708" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M708" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="N708" t="n">
         <v>424.99</v>
       </c>
       <c r="O708" t="n">
-        <v>12749.7</v>
+        <v>11899.72</v>
       </c>
       <c r="P708" t="n">
         <v>2300</v>
       </c>
       <c r="Q708" t="n">
-        <v>69000</v>
+        <v>64400</v>
       </c>
     </row>
     <row r="709">
@@ -33790,22 +33790,22 @@
         <v>0</v>
       </c>
       <c r="L736" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M736" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N736" t="n">
         <v>2293.26</v>
       </c>
       <c r="O736" t="n">
-        <v>146768.64</v>
+        <v>142182.12</v>
       </c>
       <c r="P736" t="n">
         <v>4800</v>
       </c>
       <c r="Q736" t="n">
-        <v>307200</v>
+        <v>297600</v>
       </c>
     </row>
     <row r="737">

--- a/bodegas/LJ-05.xlsx
+++ b/bodegas/LJ-05.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-10</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-11</t>
         </is>
       </c>
     </row>
@@ -8360,13 +8360,13 @@
         </is>
       </c>
       <c r="J184" t="n">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="K184" t="n">
         <v>0</v>
       </c>
       <c r="L184" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M184" t="n">
         <v>183</v>
@@ -13911,13 +13911,13 @@
         </is>
       </c>
       <c r="J308" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="K308" t="n">
         <v>0</v>
       </c>
       <c r="L308" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M308" t="n">
         <v>60</v>
@@ -20779,13 +20779,13 @@
         </is>
       </c>
       <c r="J458" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="K458" t="n">
         <v>0</v>
       </c>
       <c r="L458" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M458" t="n">
         <v>35</v>
@@ -25236,13 +25236,13 @@
         </is>
       </c>
       <c r="J555" t="n">
-        <v>342</v>
+        <v>330</v>
       </c>
       <c r="K555" t="n">
         <v>0</v>
       </c>
       <c r="L555" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M555" t="n">
         <v>330</v>
@@ -26412,13 +26412,13 @@
         </is>
       </c>
       <c r="J580" t="n">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="K580" t="n">
         <v>0</v>
       </c>
       <c r="L580" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M580" t="n">
         <v>191</v>
@@ -27804,13 +27804,13 @@
         </is>
       </c>
       <c r="J610" t="n">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="K610" t="n">
         <v>0</v>
       </c>
       <c r="L610" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M610" t="n">
         <v>435</v>
@@ -29921,13 +29921,13 @@
         </is>
       </c>
       <c r="J654" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="K654" t="n">
         <v>0</v>
       </c>
       <c r="L654" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M654" t="n">
         <v>64</v>
@@ -31786,13 +31786,13 @@
         </is>
       </c>
       <c r="J693" t="n">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="K693" t="n">
         <v>0</v>
       </c>
       <c r="L693" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M693" t="n">
         <v>111</v>
@@ -32499,13 +32499,13 @@
         </is>
       </c>
       <c r="J708" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K708" t="n">
         <v>0</v>
       </c>
       <c r="L708" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M708" t="n">
         <v>28</v>
@@ -33784,13 +33784,13 @@
         </is>
       </c>
       <c r="J736" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="K736" t="n">
         <v>0</v>
       </c>
       <c r="L736" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M736" t="n">
         <v>62</v>

--- a/bodegas/LJ-05.xlsx
+++ b/bodegas/LJ-05.xlsx
@@ -556,10 +556,10 @@
         <v>2</v>
       </c>
       <c r="N4" t="n">
-        <v>27000</v>
+        <v>27043.062200957</v>
       </c>
       <c r="O4" t="n">
-        <v>54000</v>
+        <v>54086.124401914</v>
       </c>
       <c r="P4" t="n">
         <v>20000</v>
@@ -987,10 +987,10 @@
         <v>131</v>
       </c>
       <c r="N14" t="n">
-        <v>3376.746511879</v>
+        <v>3376.7465109371</v>
       </c>
       <c r="O14" t="n">
-        <v>442353.793056149</v>
+        <v>442353.7929327601</v>
       </c>
       <c r="P14" t="n">
         <v>4500</v>
@@ -1349,10 +1349,10 @@
         <v>6</v>
       </c>
       <c r="N23" t="n">
-        <v>27000</v>
+        <v>27064.133016627</v>
       </c>
       <c r="O23" t="n">
-        <v>162000</v>
+        <v>162384.798099762</v>
       </c>
       <c r="P23" t="n">
         <v>20000</v>
@@ -1583,10 +1583,10 @@
         <v>27</v>
       </c>
       <c r="N29" t="n">
-        <v>3926.8371296771</v>
+        <v>3926.8371267317</v>
       </c>
       <c r="O29" t="n">
-        <v>106024.6025012817</v>
+        <v>106024.6024217559</v>
       </c>
       <c r="P29" t="n">
         <v>4800</v>
@@ -1784,10 +1784,10 @@
         <v>29</v>
       </c>
       <c r="N34" t="n">
-        <v>3716.3301889764</v>
+        <v>3716.3301892744</v>
       </c>
       <c r="O34" t="n">
-        <v>107773.5754803156</v>
+        <v>107773.5754889576</v>
       </c>
       <c r="P34" t="n">
         <v>9500</v>
@@ -1940,10 +1940,10 @@
         <v>2</v>
       </c>
       <c r="N38" t="n">
-        <v>21333.69</v>
+        <v>21423.327352941</v>
       </c>
       <c r="O38" t="n">
-        <v>42667.38</v>
+        <v>42846.654705882</v>
       </c>
       <c r="P38" t="n">
         <v>30000</v>
@@ -3058,10 +3058,10 @@
         <v>15</v>
       </c>
       <c r="N63" t="n">
-        <v>16486.41</v>
+        <v>16486.409489051</v>
       </c>
       <c r="O63" t="n">
-        <v>247296.15</v>
+        <v>247296.142335765</v>
       </c>
       <c r="P63" t="n">
         <v>30500</v>
@@ -3100,10 +3100,10 @@
         <v>41</v>
       </c>
       <c r="N64" t="n">
-        <v>15711.966184739</v>
+        <v>15711.966106557</v>
       </c>
       <c r="O64" t="n">
-        <v>644190.613574299</v>
+        <v>644190.610368837</v>
       </c>
       <c r="P64" t="n">
         <v>28500</v>
@@ -3386,10 +3386,10 @@
         <v>16</v>
       </c>
       <c r="N71" t="n">
-        <v>14708.815789474</v>
+        <v>14708.815744681</v>
       </c>
       <c r="O71" t="n">
-        <v>235341.052631584</v>
+        <v>235341.051914896</v>
       </c>
       <c r="P71" t="n">
         <v>16900</v>
@@ -4330,10 +4330,10 @@
         <v>8</v>
       </c>
       <c r="N93" t="n">
-        <v>61666.873852041</v>
+        <v>61666.873861893</v>
       </c>
       <c r="O93" t="n">
-        <v>493334.990816328</v>
+        <v>493334.990895144</v>
       </c>
       <c r="P93" t="n">
         <v>98900</v>
@@ -4912,10 +4912,10 @@
         <v>41</v>
       </c>
       <c r="N106" t="n">
-        <v>580.36602666667</v>
+        <v>580.36600536193</v>
       </c>
       <c r="O106" t="n">
-        <v>23795.00709333347</v>
+        <v>23795.00621983913</v>
       </c>
       <c r="P106" t="n">
         <v>6800</v>
@@ -4958,10 +4958,10 @@
         <v>29</v>
       </c>
       <c r="N107" t="n">
-        <v>538.40029962547</v>
+        <v>538.40033834586</v>
       </c>
       <c r="O107" t="n">
-        <v>15613.60868913863</v>
+        <v>15613.60981202994</v>
       </c>
       <c r="P107" t="n">
         <v>6800</v>
@@ -6526,10 +6526,10 @@
         <v>1</v>
       </c>
       <c r="N143" t="n">
-        <v>4937.3101601164</v>
+        <v>4937.3101603499</v>
       </c>
       <c r="O143" t="n">
-        <v>4937.3101601164</v>
+        <v>4937.3101603499</v>
       </c>
       <c r="P143" t="n">
         <v>7500</v>
@@ -7323,10 +7323,10 @@
         <v>99</v>
       </c>
       <c r="N161" t="n">
-        <v>2804.33</v>
+        <v>2808.0329005282</v>
       </c>
       <c r="O161" t="n">
-        <v>277628.67</v>
+        <v>277995.2571522918</v>
       </c>
       <c r="P161" t="n">
         <v>4900</v>
@@ -7456,10 +7456,10 @@
         <v>735</v>
       </c>
       <c r="N164" t="n">
-        <v>3158.8608137572</v>
+        <v>3158.860813875</v>
       </c>
       <c r="O164" t="n">
-        <v>2321762.698111542</v>
+        <v>2321762.698198125</v>
       </c>
       <c r="P164" t="n">
         <v>5600</v>
@@ -7640,10 +7640,10 @@
         <v>712</v>
       </c>
       <c r="N168" t="n">
-        <v>2694.8234975369</v>
+        <v>2694.8234682861</v>
       </c>
       <c r="O168" t="n">
-        <v>1918714.330246273</v>
+        <v>1918714.309419703</v>
       </c>
       <c r="P168" t="n">
         <v>4900</v>
@@ -7916,10 +7916,10 @@
         <v>247</v>
       </c>
       <c r="N174" t="n">
-        <v>6507</v>
+        <v>6511.2612966601</v>
       </c>
       <c r="O174" t="n">
-        <v>1607229</v>
+        <v>1608281.540275045</v>
       </c>
       <c r="P174" t="n">
         <v>9900</v>
@@ -7962,10 +7962,10 @@
         <v>14</v>
       </c>
       <c r="N175" t="n">
-        <v>3795.7100070509</v>
+        <v>3795.7100070547</v>
       </c>
       <c r="O175" t="n">
-        <v>53139.9400987126</v>
+        <v>53139.9400987658</v>
       </c>
       <c r="P175" t="n">
         <v>6200</v>
@@ -8187,10 +8187,10 @@
         <v>56</v>
       </c>
       <c r="N180" t="n">
-        <v>4890.9300460299</v>
+        <v>4890.9300461095</v>
       </c>
       <c r="O180" t="n">
-        <v>273892.0825776744</v>
+        <v>273892.082582132</v>
       </c>
       <c r="P180" t="n">
         <v>8200</v>
@@ -8643,10 +8643,10 @@
         <v>18</v>
       </c>
       <c r="N190" t="n">
-        <v>5667.94</v>
+        <v>5672.995244381</v>
       </c>
       <c r="O190" t="n">
-        <v>102022.92</v>
+        <v>102113.914398858</v>
       </c>
       <c r="P190" t="n">
         <v>9500</v>
@@ -8735,10 +8735,10 @@
         <v>88</v>
       </c>
       <c r="N192" t="n">
-        <v>8662</v>
+        <v>8688.0641925777</v>
       </c>
       <c r="O192" t="n">
-        <v>762256</v>
+        <v>764549.6489468376</v>
       </c>
       <c r="P192" t="n">
         <v>14200</v>
@@ -8912,10 +8912,10 @@
         <v>12</v>
       </c>
       <c r="N196" t="n">
-        <v>3594.2542307692</v>
+        <v>3594.254188862</v>
       </c>
       <c r="O196" t="n">
-        <v>43131.0507692304</v>
+        <v>43131.050266344</v>
       </c>
       <c r="P196" t="n">
         <v>6500</v>
@@ -9369,10 +9369,10 @@
         <v>10</v>
       </c>
       <c r="N206" t="n">
-        <v>2665.4</v>
+        <v>2670.3450834879</v>
       </c>
       <c r="O206" t="n">
-        <v>26654</v>
+        <v>26703.450834879</v>
       </c>
       <c r="P206" t="n">
         <v>20900</v>
@@ -9510,10 +9510,10 @@
         <v>18</v>
       </c>
       <c r="N209" t="n">
-        <v>12267.651212121</v>
+        <v>12267.650842105</v>
       </c>
       <c r="O209" t="n">
-        <v>220817.721818178</v>
+        <v>220817.71515789</v>
       </c>
       <c r="P209" t="n">
         <v>19900</v>
@@ -9868,10 +9868,10 @@
         <v>137</v>
       </c>
       <c r="N217" t="n">
-        <v>3041.6600124456</v>
+        <v>3041.6600125549</v>
       </c>
       <c r="O217" t="n">
-        <v>416707.4217050472</v>
+        <v>416707.4217200213</v>
       </c>
       <c r="P217" t="n">
         <v>5500</v>
@@ -9914,10 +9914,10 @@
         <v>71</v>
       </c>
       <c r="N218" t="n">
-        <v>4372.2107863175</v>
+        <v>4372.2107866525</v>
       </c>
       <c r="O218" t="n">
-        <v>310426.9658285425</v>
+        <v>310426.9658523275</v>
       </c>
       <c r="P218" t="n">
         <v>7500</v>
@@ -9960,10 +9960,10 @@
         <v>508</v>
       </c>
       <c r="N219" t="n">
-        <v>1592.567707231</v>
+        <v>1592.5676712942</v>
       </c>
       <c r="O219" t="n">
-        <v>809024.395273348</v>
+        <v>809024.3770174535</v>
       </c>
       <c r="P219" t="n">
         <v>3900</v>
@@ -11275,10 +11275,10 @@
         <v>114</v>
       </c>
       <c r="N248" t="n">
-        <v>1630.9230407276</v>
+        <v>1630.9230521929</v>
       </c>
       <c r="O248" t="n">
-        <v>185925.2266429464</v>
+        <v>185925.2279499906</v>
       </c>
       <c r="P248" t="n">
         <v>2500</v>
@@ -11321,10 +11321,10 @@
         <v>254</v>
       </c>
       <c r="N249" t="n">
-        <v>1550.1929579149</v>
+        <v>1550.1930031561</v>
       </c>
       <c r="O249" t="n">
-        <v>393749.0113103846</v>
+        <v>393749.0228016494</v>
       </c>
       <c r="P249" t="n">
         <v>2500</v>
@@ -11367,10 +11367,10 @@
         <v>681</v>
       </c>
       <c r="N250" t="n">
-        <v>2403.5100778841</v>
+        <v>2403.5101337902</v>
       </c>
       <c r="O250" t="n">
-        <v>1636790.363039072</v>
+        <v>1636790.401111126</v>
       </c>
       <c r="P250" t="n">
         <v>3500</v>
@@ -12297,10 +12297,10 @@
         <v>1</v>
       </c>
       <c r="N271" t="n">
-        <v>7537.4721014493</v>
+        <v>7537.4721167883</v>
       </c>
       <c r="O271" t="n">
-        <v>7537.4721014493</v>
+        <v>7537.4721167883</v>
       </c>
       <c r="P271" t="n">
         <v>8900</v>
@@ -12507,10 +12507,10 @@
         <v>226</v>
       </c>
       <c r="N276" t="n">
-        <v>2029.8736443149</v>
+        <v>2029.8736460865</v>
       </c>
       <c r="O276" t="n">
-        <v>458751.4436151674</v>
+        <v>458751.444015549</v>
       </c>
       <c r="P276" t="n">
         <v>3600</v>
@@ -12548,10 +12548,10 @@
         <v>20</v>
       </c>
       <c r="N277" t="n">
-        <v>22485.695927602</v>
+        <v>22485.695904437</v>
       </c>
       <c r="O277" t="n">
-        <v>449713.91855204</v>
+        <v>449713.91808874</v>
       </c>
       <c r="P277" t="n">
         <v>36500</v>
@@ -13114,10 +13114,10 @@
         <v>56</v>
       </c>
       <c r="N290" t="n">
-        <v>998.76125816993</v>
+        <v>998.76125988546</v>
       </c>
       <c r="O290" t="n">
-        <v>55930.63045751608</v>
+        <v>55930.63055358576</v>
       </c>
       <c r="P290" t="n">
         <v>1600</v>
@@ -13468,10 +13468,10 @@
         <v>61</v>
       </c>
       <c r="N298" t="n">
-        <v>30244.600034682</v>
+        <v>30262.092573742</v>
       </c>
       <c r="O298" t="n">
-        <v>1844920.602115602</v>
+        <v>1845987.646998262</v>
       </c>
       <c r="P298" t="n">
         <v>48900</v>
@@ -13555,10 +13555,10 @@
         <v>58</v>
       </c>
       <c r="N300" t="n">
-        <v>3591.13</v>
+        <v>3592.9712903777</v>
       </c>
       <c r="O300" t="n">
-        <v>208285.54</v>
+        <v>208392.3348419066</v>
       </c>
       <c r="P300" t="n">
         <v>6300</v>
@@ -13647,10 +13647,10 @@
         <v>37</v>
       </c>
       <c r="N302" t="n">
-        <v>11562.038534031</v>
+        <v>11562.038530184</v>
       </c>
       <c r="O302" t="n">
-        <v>427795.425759147</v>
+        <v>427795.425616808</v>
       </c>
       <c r="P302" t="n">
         <v>18500</v>
@@ -13831,10 +13831,10 @@
         <v>38</v>
       </c>
       <c r="N306" t="n">
-        <v>21418.04</v>
+        <v>21897.548358209</v>
       </c>
       <c r="O306" t="n">
-        <v>813885.52</v>
+        <v>832106.837611942</v>
       </c>
       <c r="P306" t="n">
         <v>34900</v>
@@ -14363,10 +14363,10 @@
         <v>17</v>
       </c>
       <c r="N318" t="n">
-        <v>4100.45</v>
+        <v>4107.7418494369</v>
       </c>
       <c r="O318" t="n">
-        <v>69707.64999999999</v>
+        <v>69831.61144042731</v>
       </c>
       <c r="P318" t="n">
         <v>26900</v>
@@ -14542,10 +14542,10 @@
         <v>140</v>
       </c>
       <c r="N322" t="n">
-        <v>1560.9988868445</v>
+        <v>1560.9989986027</v>
       </c>
       <c r="O322" t="n">
-        <v>218539.84415823</v>
+        <v>218539.859804378</v>
       </c>
       <c r="P322" t="n">
         <v>2900</v>
@@ -15162,10 +15162,10 @@
         <v>33</v>
       </c>
       <c r="N336" t="n">
-        <v>12981.59</v>
+        <v>13028.454945848</v>
       </c>
       <c r="O336" t="n">
-        <v>428392.47</v>
+        <v>429939.013212984</v>
       </c>
       <c r="P336" t="n">
         <v>21900</v>
@@ -15948,10 +15948,10 @@
         <v>99</v>
       </c>
       <c r="N353" t="n">
-        <v>5218.170490524</v>
+        <v>5218.1704988662</v>
       </c>
       <c r="O353" t="n">
-        <v>516598.878561876</v>
+        <v>516598.8793877538</v>
       </c>
       <c r="P353" t="n">
         <v>8500</v>
@@ -15994,10 +15994,10 @@
         <v>145</v>
       </c>
       <c r="N354" t="n">
-        <v>1595.0094864865</v>
+        <v>1595.0094843962</v>
       </c>
       <c r="O354" t="n">
-        <v>231276.3755405425</v>
+        <v>231276.375237449</v>
       </c>
       <c r="P354" t="n">
         <v>2600</v>
@@ -16040,10 +16040,10 @@
         <v>38</v>
       </c>
       <c r="N355" t="n">
-        <v>3610.6500238379</v>
+        <v>3610.6500238663</v>
       </c>
       <c r="O355" t="n">
-        <v>137204.7009058402</v>
+        <v>137204.7009069194</v>
       </c>
       <c r="P355" t="n">
         <v>5800</v>
@@ -16270,10 +16270,10 @@
         <v>53</v>
       </c>
       <c r="N360" t="n">
-        <v>1664.360841938</v>
+        <v>1664.3605954323</v>
       </c>
       <c r="O360" t="n">
-        <v>88211.12462271401</v>
+        <v>88211.11155791189</v>
       </c>
       <c r="P360" t="n">
         <v>2900</v>
@@ -16871,10 +16871,10 @@
         <v>147</v>
       </c>
       <c r="N373" t="n">
-        <v>1778.4725231214</v>
+        <v>1778.4725400058</v>
       </c>
       <c r="O373" t="n">
-        <v>261435.4608988458</v>
+        <v>261435.4633808526</v>
       </c>
       <c r="P373" t="n">
         <v>4900</v>
@@ -17009,10 +17009,10 @@
         <v>69</v>
       </c>
       <c r="N376" t="n">
-        <v>16058</v>
+        <v>16069.364472753</v>
       </c>
       <c r="O376" t="n">
-        <v>1108002</v>
+        <v>1108786.148619957</v>
       </c>
       <c r="P376" t="n">
         <v>25900</v>
@@ -19927,10 +19927,10 @@
         <v>21</v>
       </c>
       <c r="N439" t="n">
-        <v>13922</v>
+        <v>13973.183823529</v>
       </c>
       <c r="O439" t="n">
-        <v>292362</v>
+        <v>293436.860294109</v>
       </c>
       <c r="P439" t="n">
         <v>22900</v>
@@ -20065,10 +20065,10 @@
         <v>51</v>
       </c>
       <c r="N442" t="n">
-        <v>4907.8219300912</v>
+        <v>4907.8219330289</v>
       </c>
       <c r="O442" t="n">
-        <v>250298.9184346512</v>
+        <v>250298.9185844739</v>
       </c>
       <c r="P442" t="n">
         <v>8200</v>
@@ -20295,10 +20295,10 @@
         <v>8</v>
       </c>
       <c r="N447" t="n">
-        <v>76839</v>
+        <v>77344.519736842</v>
       </c>
       <c r="O447" t="n">
-        <v>614712</v>
+        <v>618756.157894736</v>
       </c>
       <c r="P447" t="n">
         <v>122900</v>
@@ -20433,10 +20433,10 @@
         <v>99</v>
       </c>
       <c r="N450" t="n">
-        <v>3903.7359183673</v>
+        <v>3903.7359649123</v>
       </c>
       <c r="O450" t="n">
-        <v>386469.8559183627</v>
+        <v>386469.8605263177</v>
       </c>
       <c r="P450" t="n">
         <v>7500</v>
@@ -20607,10 +20607,10 @@
         <v>34</v>
       </c>
       <c r="N454" t="n">
-        <v>12113</v>
+        <v>12928.298076923</v>
       </c>
       <c r="O454" t="n">
-        <v>411842</v>
+        <v>439562.134615382</v>
       </c>
       <c r="P454" t="n">
         <v>19900</v>
@@ -21481,10 +21481,10 @@
         <v>27</v>
       </c>
       <c r="N473" t="n">
-        <v>7562</v>
+        <v>7649.2538461538</v>
       </c>
       <c r="O473" t="n">
-        <v>204174</v>
+        <v>206529.8538461526</v>
       </c>
       <c r="P473" t="n">
         <v>12900</v>
@@ -21990,10 +21990,10 @@
         <v>51</v>
       </c>
       <c r="N484" t="n">
-        <v>17992</v>
+        <v>18015.037131882</v>
       </c>
       <c r="O484" t="n">
-        <v>917592</v>
+        <v>918766.8937259819</v>
       </c>
       <c r="P484" t="n">
         <v>28900</v>
@@ -22220,10 +22220,10 @@
         <v>147</v>
       </c>
       <c r="N489" t="n">
-        <v>17075.989524793</v>
+        <v>17075.989524138</v>
       </c>
       <c r="O489" t="n">
-        <v>2510170.460144571</v>
+        <v>2510170.460048286</v>
       </c>
       <c r="P489" t="n">
         <v>27500</v>
@@ -23092,10 +23092,10 @@
         <v>8</v>
       </c>
       <c r="N508" t="n">
-        <v>16282</v>
+        <v>16694.202531646</v>
       </c>
       <c r="O508" t="n">
-        <v>130256</v>
+        <v>133553.620253168</v>
       </c>
       <c r="P508" t="n">
         <v>27900</v>
@@ -23184,10 +23184,10 @@
         <v>42</v>
       </c>
       <c r="N510" t="n">
-        <v>8700</v>
+        <v>8709.5604395604</v>
       </c>
       <c r="O510" t="n">
-        <v>365400</v>
+        <v>365801.5384615368</v>
       </c>
       <c r="P510" t="n">
         <v>14900</v>
@@ -24015,10 +24015,10 @@
         <v>253</v>
       </c>
       <c r="N528" t="n">
-        <v>1516.0388131508</v>
+        <v>1516.0388129219</v>
       </c>
       <c r="O528" t="n">
-        <v>383557.8197271524</v>
+        <v>383557.8196692407</v>
       </c>
       <c r="P528" t="n">
         <v>2300</v>
@@ -24107,10 +24107,10 @@
         <v>453</v>
       </c>
       <c r="N530" t="n">
-        <v>2458.5134514107</v>
+        <v>2458.5134452463</v>
       </c>
       <c r="O530" t="n">
-        <v>1113706.593489047</v>
+        <v>1113706.590696574</v>
       </c>
       <c r="P530" t="n">
         <v>3500</v>
@@ -24153,10 +24153,10 @@
         <v>108</v>
       </c>
       <c r="N531" t="n">
-        <v>1907.3944716822</v>
+        <v>1909.016377551</v>
       </c>
       <c r="O531" t="n">
-        <v>205998.6029416776</v>
+        <v>206173.768775508</v>
       </c>
       <c r="P531" t="n">
         <v>2500</v>
@@ -24245,10 +24245,10 @@
         <v>465</v>
       </c>
       <c r="N533" t="n">
-        <v>2079.3842209265</v>
+        <v>2079.3842077922</v>
       </c>
       <c r="O533" t="n">
-        <v>966913.6627308225</v>
+        <v>966913.6566233729</v>
       </c>
       <c r="P533" t="n">
         <v>2900</v>
@@ -24337,10 +24337,10 @@
         <v>108</v>
       </c>
       <c r="N535" t="n">
-        <v>3306.5954545455</v>
+        <v>3306.595443038</v>
       </c>
       <c r="O535" t="n">
-        <v>357112.309090914</v>
+        <v>357112.307848104</v>
       </c>
       <c r="P535" t="n">
         <v>4900</v>
@@ -24383,10 +24383,10 @@
         <v>565</v>
       </c>
       <c r="N536" t="n">
-        <v>2122.1641155235</v>
+        <v>2122.1641066586</v>
       </c>
       <c r="O536" t="n">
-        <v>1199022.725270778</v>
+        <v>1199022.720262109</v>
       </c>
       <c r="P536" t="n">
         <v>2900</v>
@@ -24429,10 +24429,10 @@
         <v>313</v>
       </c>
       <c r="N537" t="n">
-        <v>2108.7897869955</v>
+        <v>2108.7898867497</v>
       </c>
       <c r="O537" t="n">
-        <v>660051.2033295915</v>
+        <v>660051.2345526562</v>
       </c>
       <c r="P537" t="n">
         <v>2900</v>
@@ -24475,10 +24475,10 @@
         <v>409</v>
       </c>
       <c r="N538" t="n">
-        <v>2056.0838880663</v>
+        <v>2056.692917654</v>
       </c>
       <c r="O538" t="n">
-        <v>840938.3102191167</v>
+        <v>841187.4033204861</v>
       </c>
       <c r="P538" t="n">
         <v>2900</v>
@@ -24521,10 +24521,10 @@
         <v>366</v>
       </c>
       <c r="N539" t="n">
-        <v>3224.5679626335</v>
+        <v>3224.5679768271</v>
       </c>
       <c r="O539" t="n">
-        <v>1180191.874323861</v>
+        <v>1180191.879518719</v>
       </c>
       <c r="P539" t="n">
         <v>4500</v>
@@ -24567,10 +24567,10 @@
         <v>300</v>
       </c>
       <c r="N540" t="n">
-        <v>1655.931342723</v>
+        <v>1655.9313291536</v>
       </c>
       <c r="O540" t="n">
-        <v>496779.4028169</v>
+        <v>496779.39874608</v>
       </c>
       <c r="P540" t="n">
         <v>2500</v>
@@ -24751,10 +24751,10 @@
         <v>274</v>
       </c>
       <c r="N544" t="n">
-        <v>1592.2747647377</v>
+        <v>1592.2748727876</v>
       </c>
       <c r="O544" t="n">
-        <v>436283.2855381298</v>
+        <v>436283.3151438024</v>
       </c>
       <c r="P544" t="n">
         <v>2500</v>
@@ -24841,10 +24841,10 @@
         <v>8</v>
       </c>
       <c r="N546" t="n">
-        <v>1906.1867602592</v>
+        <v>1906.1867105263</v>
       </c>
       <c r="O546" t="n">
-        <v>15249.4940820736</v>
+        <v>15249.4936842104</v>
       </c>
       <c r="P546" t="n">
         <v>2900</v>
@@ -24887,10 +24887,10 @@
         <v>121</v>
       </c>
       <c r="N547" t="n">
-        <v>1668.6157419355</v>
+        <v>1668.6158441558</v>
       </c>
       <c r="O547" t="n">
-        <v>201902.5047741955</v>
+        <v>201902.5171428518</v>
       </c>
       <c r="P547" t="n">
         <v>2500</v>
@@ -24933,10 +24933,10 @@
         <v>54</v>
       </c>
       <c r="N548" t="n">
-        <v>2546.9851864407</v>
+        <v>2546.9851535836</v>
       </c>
       <c r="O548" t="n">
-        <v>137537.2000677978</v>
+        <v>137537.1982935144</v>
       </c>
       <c r="P548" t="n">
         <v>3900</v>
@@ -24979,10 +24979,10 @@
         <v>996</v>
       </c>
       <c r="N549" t="n">
-        <v>1259.2744140796</v>
+        <v>1259.2744160105</v>
       </c>
       <c r="O549" t="n">
-        <v>1254237.316423282</v>
+        <v>1254237.318346458</v>
       </c>
       <c r="P549" t="n">
         <v>1900</v>
@@ -25112,10 +25112,10 @@
         <v>228</v>
       </c>
       <c r="N552" t="n">
-        <v>2842.2737931034</v>
+        <v>2842.2737735849</v>
       </c>
       <c r="O552" t="n">
-        <v>648038.4248275752</v>
+        <v>648038.4203773572</v>
       </c>
       <c r="P552" t="n">
         <v>4900</v>
@@ -25868,10 +25868,10 @@
         <v>273</v>
       </c>
       <c r="N568" t="n">
-        <v>1530.4499204455</v>
+        <v>1530.4499204138</v>
       </c>
       <c r="O568" t="n">
-        <v>417812.8282816215</v>
+        <v>417812.8282729674</v>
       </c>
       <c r="P568" t="n">
         <v>2600</v>
@@ -26424,10 +26424,10 @@
         <v>191</v>
       </c>
       <c r="N580" t="n">
-        <v>1690.8700088574</v>
+        <v>1690.8700089286</v>
       </c>
       <c r="O580" t="n">
-        <v>322956.1716917634</v>
+        <v>322956.1717053626</v>
       </c>
       <c r="P580" t="n">
         <v>3000</v>
@@ -27207,10 +27207,10 @@
         <v>2752</v>
       </c>
       <c r="N597" t="n">
-        <v>517.28764753291</v>
+        <v>517.28774146762</v>
       </c>
       <c r="O597" t="n">
-        <v>1423575.606010568</v>
+        <v>1423575.86451889</v>
       </c>
       <c r="P597" t="n">
         <v>900</v>
@@ -27438,10 +27438,10 @@
         <v>404</v>
       </c>
       <c r="N602" t="n">
-        <v>3110.8431677619</v>
+        <v>3110.8430699863</v>
       </c>
       <c r="O602" t="n">
-        <v>1256780.639775808</v>
+        <v>1256780.600274465</v>
       </c>
       <c r="P602" t="n">
         <v>4500</v>
@@ -27482,10 +27482,10 @@
         <v>1067</v>
       </c>
       <c r="N603" t="n">
-        <v>703.79542528945</v>
+        <v>703.79541200942</v>
       </c>
       <c r="O603" t="n">
-        <v>750949.7187838432</v>
+        <v>750949.7046140512</v>
       </c>
       <c r="P603" t="n">
         <v>900</v>
@@ -30803,10 +30803,10 @@
         <v>33</v>
       </c>
       <c r="N672" t="n">
-        <v>4159.0002867384</v>
+        <v>4173.9607194245</v>
       </c>
       <c r="O672" t="n">
-        <v>137247.0094623672</v>
+        <v>137740.7037410085</v>
       </c>
       <c r="P672" t="n">
         <v>8900</v>
@@ -30980,10 +30980,10 @@
         <v>4</v>
       </c>
       <c r="N676" t="n">
-        <v>34880.155714286</v>
+        <v>34880.156666667</v>
       </c>
       <c r="O676" t="n">
-        <v>139520.622857144</v>
+        <v>139520.626666668</v>
       </c>
       <c r="P676" t="n">
         <v>65900</v>
@@ -33387,10 +33387,10 @@
         <v>156</v>
       </c>
       <c r="N727" t="n">
-        <v>5077</v>
+        <v>5174.6346153846</v>
       </c>
       <c r="O727" t="n">
-        <v>792012</v>
+        <v>807242.9999999976</v>
       </c>
       <c r="P727" t="n">
         <v>8500</v>
@@ -33520,10 +33520,10 @@
         <v>12</v>
       </c>
       <c r="N730" t="n">
-        <v>4985.4046332046</v>
+        <v>5004.7279069767</v>
       </c>
       <c r="O730" t="n">
-        <v>59824.8555984552</v>
+        <v>60056.7348837204</v>
       </c>
       <c r="P730" t="n">
         <v>7900</v>
@@ -36122,10 +36122,10 @@
         <v>1456000</v>
       </c>
       <c r="P786" t="n">
-        <v>6500</v>
+        <v>5500</v>
       </c>
       <c r="Q786" t="n">
-        <v>2080000</v>
+        <v>1760000</v>
       </c>
     </row>
     <row r="787">

--- a/bodegas/LJ-05.xlsx
+++ b/bodegas/LJ-05.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-11</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-12</t>
         </is>
       </c>
     </row>
@@ -556,10 +556,10 @@
         <v>2</v>
       </c>
       <c r="N4" t="n">
-        <v>27043.062200957</v>
+        <v>27000</v>
       </c>
       <c r="O4" t="n">
-        <v>54086.124401914</v>
+        <v>54000</v>
       </c>
       <c r="P4" t="n">
         <v>20000</v>
@@ -1349,10 +1349,10 @@
         <v>6</v>
       </c>
       <c r="N23" t="n">
-        <v>27064.133016627</v>
+        <v>27000</v>
       </c>
       <c r="O23" t="n">
-        <v>162384.798099762</v>
+        <v>162000</v>
       </c>
       <c r="P23" t="n">
         <v>20000</v>
@@ -1940,10 +1940,10 @@
         <v>2</v>
       </c>
       <c r="N38" t="n">
-        <v>21423.327352941</v>
+        <v>21333.69</v>
       </c>
       <c r="O38" t="n">
-        <v>42846.654705882</v>
+        <v>42667.38</v>
       </c>
       <c r="P38" t="n">
         <v>30000</v>
@@ -7323,10 +7323,10 @@
         <v>99</v>
       </c>
       <c r="N161" t="n">
-        <v>2808.0329005282</v>
+        <v>2804.33</v>
       </c>
       <c r="O161" t="n">
-        <v>277995.2571522918</v>
+        <v>277628.67</v>
       </c>
       <c r="P161" t="n">
         <v>4900</v>
@@ -7916,10 +7916,10 @@
         <v>247</v>
       </c>
       <c r="N174" t="n">
-        <v>6511.2612966601</v>
+        <v>6507</v>
       </c>
       <c r="O174" t="n">
-        <v>1608281.540275045</v>
+        <v>1607229</v>
       </c>
       <c r="P174" t="n">
         <v>9900</v>
@@ -8643,10 +8643,10 @@
         <v>18</v>
       </c>
       <c r="N190" t="n">
-        <v>5672.995244381</v>
+        <v>5667.94</v>
       </c>
       <c r="O190" t="n">
-        <v>102113.914398858</v>
+        <v>102022.92</v>
       </c>
       <c r="P190" t="n">
         <v>9500</v>
@@ -8735,10 +8735,10 @@
         <v>88</v>
       </c>
       <c r="N192" t="n">
-        <v>8688.0641925777</v>
+        <v>8662</v>
       </c>
       <c r="O192" t="n">
-        <v>764549.6489468376</v>
+        <v>762256</v>
       </c>
       <c r="P192" t="n">
         <v>14200</v>
@@ -9369,10 +9369,10 @@
         <v>10</v>
       </c>
       <c r="N206" t="n">
-        <v>2670.3450834879</v>
+        <v>2665.4</v>
       </c>
       <c r="O206" t="n">
-        <v>26703.450834879</v>
+        <v>26654</v>
       </c>
       <c r="P206" t="n">
         <v>20900</v>
@@ -13468,10 +13468,10 @@
         <v>61</v>
       </c>
       <c r="N298" t="n">
-        <v>30262.092573742</v>
+        <v>30244.600034702</v>
       </c>
       <c r="O298" t="n">
-        <v>1845987.646998262</v>
+        <v>1844920.602116822</v>
       </c>
       <c r="P298" t="n">
         <v>48900</v>
@@ -13555,10 +13555,10 @@
         <v>58</v>
       </c>
       <c r="N300" t="n">
-        <v>3592.9712903777</v>
+        <v>3591.13</v>
       </c>
       <c r="O300" t="n">
-        <v>208392.3348419066</v>
+        <v>208285.54</v>
       </c>
       <c r="P300" t="n">
         <v>6300</v>
@@ -13831,10 +13831,10 @@
         <v>38</v>
       </c>
       <c r="N306" t="n">
-        <v>21897.548358209</v>
+        <v>21418.04</v>
       </c>
       <c r="O306" t="n">
-        <v>832106.837611942</v>
+        <v>813885.52</v>
       </c>
       <c r="P306" t="n">
         <v>34900</v>
@@ -14363,10 +14363,10 @@
         <v>17</v>
       </c>
       <c r="N318" t="n">
-        <v>4107.7418494369</v>
+        <v>4100.45</v>
       </c>
       <c r="O318" t="n">
-        <v>69831.61144042731</v>
+        <v>69707.64999999999</v>
       </c>
       <c r="P318" t="n">
         <v>26900</v>
@@ -15162,10 +15162,10 @@
         <v>33</v>
       </c>
       <c r="N336" t="n">
-        <v>13028.454945848</v>
+        <v>12981.59</v>
       </c>
       <c r="O336" t="n">
-        <v>429939.013212984</v>
+        <v>428392.47</v>
       </c>
       <c r="P336" t="n">
         <v>21900</v>
@@ -17009,10 +17009,10 @@
         <v>69</v>
       </c>
       <c r="N376" t="n">
-        <v>16069.364472753</v>
+        <v>16058</v>
       </c>
       <c r="O376" t="n">
-        <v>1108786.148619957</v>
+        <v>1108002</v>
       </c>
       <c r="P376" t="n">
         <v>25900</v>
@@ -19927,10 +19927,10 @@
         <v>21</v>
       </c>
       <c r="N439" t="n">
-        <v>13973.183823529</v>
+        <v>13922</v>
       </c>
       <c r="O439" t="n">
-        <v>293436.860294109</v>
+        <v>292362</v>
       </c>
       <c r="P439" t="n">
         <v>22900</v>
@@ -20295,10 +20295,10 @@
         <v>8</v>
       </c>
       <c r="N447" t="n">
-        <v>77344.519736842</v>
+        <v>76839</v>
       </c>
       <c r="O447" t="n">
-        <v>618756.157894736</v>
+        <v>614712</v>
       </c>
       <c r="P447" t="n">
         <v>122900</v>
@@ -20607,10 +20607,10 @@
         <v>34</v>
       </c>
       <c r="N454" t="n">
-        <v>12928.298076923</v>
+        <v>12113</v>
       </c>
       <c r="O454" t="n">
-        <v>439562.134615382</v>
+        <v>411842</v>
       </c>
       <c r="P454" t="n">
         <v>19900</v>
@@ -21481,10 +21481,10 @@
         <v>27</v>
       </c>
       <c r="N473" t="n">
-        <v>7649.2538461538</v>
+        <v>7562</v>
       </c>
       <c r="O473" t="n">
-        <v>206529.8538461526</v>
+        <v>204174</v>
       </c>
       <c r="P473" t="n">
         <v>12900</v>
@@ -21990,10 +21990,10 @@
         <v>51</v>
       </c>
       <c r="N484" t="n">
-        <v>18015.037131882</v>
+        <v>17992</v>
       </c>
       <c r="O484" t="n">
-        <v>918766.8937259819</v>
+        <v>917592</v>
       </c>
       <c r="P484" t="n">
         <v>28900</v>
@@ -23092,10 +23092,10 @@
         <v>8</v>
       </c>
       <c r="N508" t="n">
-        <v>16694.202531646</v>
+        <v>16282</v>
       </c>
       <c r="O508" t="n">
-        <v>133553.620253168</v>
+        <v>130256</v>
       </c>
       <c r="P508" t="n">
         <v>27900</v>
@@ -23184,10 +23184,10 @@
         <v>42</v>
       </c>
       <c r="N510" t="n">
-        <v>8709.5604395604</v>
+        <v>8700</v>
       </c>
       <c r="O510" t="n">
-        <v>365801.5384615368</v>
+        <v>365400</v>
       </c>
       <c r="P510" t="n">
         <v>14900</v>
@@ -24153,10 +24153,10 @@
         <v>108</v>
       </c>
       <c r="N531" t="n">
-        <v>1909.016377551</v>
+        <v>1907.3944387755</v>
       </c>
       <c r="O531" t="n">
-        <v>206173.768775508</v>
+        <v>205998.599387754</v>
       </c>
       <c r="P531" t="n">
         <v>2500</v>
@@ -24475,10 +24475,10 @@
         <v>409</v>
       </c>
       <c r="N538" t="n">
-        <v>2056.692917654</v>
+        <v>2056.0838862559</v>
       </c>
       <c r="O538" t="n">
-        <v>841187.4033204861</v>
+        <v>840938.309478663</v>
       </c>
       <c r="P538" t="n">
         <v>2900</v>
@@ -30803,10 +30803,10 @@
         <v>33</v>
       </c>
       <c r="N672" t="n">
-        <v>4173.9607194245</v>
+        <v>4159.0002877698</v>
       </c>
       <c r="O672" t="n">
-        <v>137740.7037410085</v>
+        <v>137247.0094964034</v>
       </c>
       <c r="P672" t="n">
         <v>8900</v>
@@ -33387,10 +33387,10 @@
         <v>156</v>
       </c>
       <c r="N727" t="n">
-        <v>5174.6346153846</v>
+        <v>5077</v>
       </c>
       <c r="O727" t="n">
-        <v>807242.9999999976</v>
+        <v>792012</v>
       </c>
       <c r="P727" t="n">
         <v>8500</v>
@@ -33520,10 +33520,10 @@
         <v>12</v>
       </c>
       <c r="N730" t="n">
-        <v>5004.7279069767</v>
+        <v>4985.4046511628</v>
       </c>
       <c r="O730" t="n">
-        <v>60056.7348837204</v>
+        <v>59824.8558139536</v>
       </c>
       <c r="P730" t="n">
         <v>7900</v>

--- a/bodegas/LJ-05.xlsx
+++ b/bodegas/LJ-05.xlsx
@@ -738,10 +738,10 @@
         <v>3</v>
       </c>
       <c r="N8" t="n">
-        <v>74676.651315789</v>
+        <v>74676.651794872</v>
       </c>
       <c r="O8" t="n">
-        <v>224029.953947367</v>
+        <v>224029.955384616</v>
       </c>
       <c r="P8" t="n">
         <v>144900</v>
@@ -987,10 +987,10 @@
         <v>131</v>
       </c>
       <c r="N14" t="n">
-        <v>3376.7465109371</v>
+        <v>3376.7465014893</v>
       </c>
       <c r="O14" t="n">
-        <v>442353.7929327601</v>
+        <v>442353.7916950983</v>
       </c>
       <c r="P14" t="n">
         <v>4500</v>
@@ -1421,22 +1421,22 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M25" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="N25" t="n">
         <v>2812</v>
       </c>
       <c r="O25" t="n">
-        <v>134976</v>
+        <v>118104</v>
       </c>
       <c r="P25" t="n">
         <v>5000</v>
       </c>
       <c r="Q25" t="n">
-        <v>240000</v>
+        <v>210000</v>
       </c>
     </row>
     <row r="26">
@@ -1817,22 +1817,22 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M35" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="N35" t="n">
         <v>3465.29</v>
       </c>
       <c r="O35" t="n">
-        <v>69305.8</v>
+        <v>58909.93</v>
       </c>
       <c r="P35" t="n">
         <v>10100</v>
       </c>
       <c r="Q35" t="n">
-        <v>202000</v>
+        <v>171700</v>
       </c>
     </row>
     <row r="36">
@@ -1856,22 +1856,22 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M36" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="N36" t="n">
         <v>2681</v>
       </c>
       <c r="O36" t="n">
-        <v>34853</v>
+        <v>18767</v>
       </c>
       <c r="P36" t="n">
         <v>3500</v>
       </c>
       <c r="Q36" t="n">
-        <v>45500</v>
+        <v>24500</v>
       </c>
     </row>
     <row r="37">
@@ -2320,22 +2320,22 @@
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M47" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="N47" t="n">
-        <v>3910.628245614</v>
+        <v>3910.6282352941</v>
       </c>
       <c r="O47" t="n">
-        <v>54748.795438596</v>
+        <v>43016.9105882351</v>
       </c>
       <c r="P47" t="n">
         <v>9100</v>
       </c>
       <c r="Q47" t="n">
-        <v>127400</v>
+        <v>100100</v>
       </c>
     </row>
     <row r="48">
@@ -3100,10 +3100,10 @@
         <v>41</v>
       </c>
       <c r="N64" t="n">
-        <v>15711.966106557</v>
+        <v>15711.966058091</v>
       </c>
       <c r="O64" t="n">
-        <v>644190.610368837</v>
+        <v>644190.608381731</v>
       </c>
       <c r="P64" t="n">
         <v>28500</v>
@@ -3147,10 +3147,10 @@
         <v>24</v>
       </c>
       <c r="N65" t="n">
-        <v>9392.0745945946</v>
+        <v>9392.0746575342</v>
       </c>
       <c r="O65" t="n">
-        <v>225409.7902702704</v>
+        <v>225409.7917808208</v>
       </c>
       <c r="P65" t="n">
         <v>18500</v>
@@ -3822,10 +3822,10 @@
         <v>1</v>
       </c>
       <c r="N81" t="n">
-        <v>56906.800571429</v>
+        <v>56906.801935484</v>
       </c>
       <c r="O81" t="n">
-        <v>56906.800571429</v>
+        <v>56906.801935484</v>
       </c>
       <c r="P81" t="n">
         <v>95900</v>
@@ -3916,10 +3916,10 @@
         <v>6</v>
       </c>
       <c r="N83" t="n">
-        <v>141416.88453074</v>
+        <v>141416.88454545</v>
       </c>
       <c r="O83" t="n">
-        <v>848501.3071844401</v>
+        <v>848501.3072727001</v>
       </c>
       <c r="P83" t="n">
         <v>251900</v>
@@ -4246,22 +4246,22 @@
         <v>0</v>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M91" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N91" t="n">
         <v>26280.41</v>
       </c>
       <c r="O91" t="n">
-        <v>236523.69</v>
+        <v>210243.28</v>
       </c>
       <c r="P91" t="n">
         <v>46500</v>
       </c>
       <c r="Q91" t="n">
-        <v>418500</v>
+        <v>372000</v>
       </c>
     </row>
     <row r="92">
@@ -4324,22 +4324,22 @@
         <v>0</v>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M93" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N93" t="n">
-        <v>61666.873861893</v>
+        <v>61666.873932292</v>
       </c>
       <c r="O93" t="n">
-        <v>493334.990895144</v>
+        <v>431668.117526044</v>
       </c>
       <c r="P93" t="n">
         <v>98900</v>
       </c>
       <c r="Q93" t="n">
-        <v>791200</v>
+        <v>692300</v>
       </c>
     </row>
     <row r="94">
@@ -4866,10 +4866,10 @@
         <v>13</v>
       </c>
       <c r="N105" t="n">
-        <v>427.91890410959</v>
+        <v>430.87006896552</v>
       </c>
       <c r="O105" t="n">
-        <v>5562.94575342467</v>
+        <v>5601.310896551759</v>
       </c>
       <c r="P105" t="n">
         <v>6800</v>
@@ -4958,10 +4958,10 @@
         <v>29</v>
       </c>
       <c r="N107" t="n">
-        <v>538.40033834586</v>
+        <v>542.47912878788</v>
       </c>
       <c r="O107" t="n">
-        <v>15613.60981202994</v>
+        <v>15731.89473484852</v>
       </c>
       <c r="P107" t="n">
         <v>6800</v>
@@ -6474,22 +6474,22 @@
         <v>0</v>
       </c>
       <c r="L142" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M142" t="n">
-        <v>1370</v>
+        <v>1367</v>
       </c>
       <c r="N142" t="n">
         <v>1726.32</v>
       </c>
       <c r="O142" t="n">
-        <v>2365058.4</v>
+        <v>2359879.44</v>
       </c>
       <c r="P142" t="n">
         <v>1500</v>
       </c>
       <c r="Q142" t="n">
-        <v>2055000</v>
+        <v>2050500</v>
       </c>
     </row>
     <row r="143">
@@ -6526,10 +6526,10 @@
         <v>1</v>
       </c>
       <c r="N143" t="n">
-        <v>4937.3101603499</v>
+        <v>4937.3101608187</v>
       </c>
       <c r="O143" t="n">
-        <v>4937.3101603499</v>
+        <v>4937.3101608187</v>
       </c>
       <c r="P143" t="n">
         <v>7500</v>
@@ -7317,22 +7317,22 @@
         <v>0</v>
       </c>
       <c r="L161" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M161" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="N161" t="n">
         <v>2804.33</v>
       </c>
       <c r="O161" t="n">
-        <v>277628.67</v>
+        <v>272020.01</v>
       </c>
       <c r="P161" t="n">
         <v>4900</v>
       </c>
       <c r="Q161" t="n">
-        <v>485100</v>
+        <v>475300</v>
       </c>
     </row>
     <row r="162">
@@ -7456,10 +7456,10 @@
         <v>735</v>
       </c>
       <c r="N164" t="n">
-        <v>3158.860813875</v>
+        <v>3158.8608143857</v>
       </c>
       <c r="O164" t="n">
-        <v>2321762.698198125</v>
+        <v>2321762.69857349</v>
       </c>
       <c r="P164" t="n">
         <v>5600</v>
@@ -7640,10 +7640,10 @@
         <v>712</v>
       </c>
       <c r="N168" t="n">
-        <v>2694.8234682861</v>
+        <v>2694.8234624043</v>
       </c>
       <c r="O168" t="n">
-        <v>1918714.309419703</v>
+        <v>1918714.305231862</v>
       </c>
       <c r="P168" t="n">
         <v>4900</v>
@@ -7686,10 +7686,10 @@
         <v>84</v>
       </c>
       <c r="N169" t="n">
-        <v>1026.13</v>
+        <v>1037.4476102941</v>
       </c>
       <c r="O169" t="n">
-        <v>86194.92000000001</v>
+        <v>87145.5992647044</v>
       </c>
       <c r="P169" t="n">
         <v>1900</v>
@@ -7726,22 +7726,22 @@
         <v>0</v>
       </c>
       <c r="L170" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M170" t="n">
-        <v>1745</v>
+        <v>1725</v>
       </c>
       <c r="N170" t="n">
         <v>156.25</v>
       </c>
       <c r="O170" t="n">
-        <v>272656.25</v>
+        <v>269531.25</v>
       </c>
       <c r="P170" t="n">
         <v>250</v>
       </c>
       <c r="Q170" t="n">
-        <v>436250</v>
+        <v>431250</v>
       </c>
     </row>
     <row r="171">
@@ -8187,10 +8187,10 @@
         <v>56</v>
       </c>
       <c r="N180" t="n">
-        <v>4890.9300461095</v>
+        <v>4890.9300462963</v>
       </c>
       <c r="O180" t="n">
-        <v>273892.082582132</v>
+        <v>273892.0825925928</v>
       </c>
       <c r="P180" t="n">
         <v>8200</v>
@@ -8912,10 +8912,10 @@
         <v>12</v>
       </c>
       <c r="N196" t="n">
-        <v>3594.254188862</v>
+        <v>3594.2541747573</v>
       </c>
       <c r="O196" t="n">
-        <v>43131.050266344</v>
+        <v>43131.0500970876</v>
       </c>
       <c r="P196" t="n">
         <v>6500</v>
@@ -9001,22 +9001,22 @@
         <v>0</v>
       </c>
       <c r="L198" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M198" t="n">
-        <v>2047</v>
+        <v>2042</v>
       </c>
       <c r="N198" t="n">
         <v>489.88</v>
       </c>
       <c r="O198" t="n">
-        <v>1002784.36</v>
+        <v>1000334.96</v>
       </c>
       <c r="P198" t="n">
         <v>700</v>
       </c>
       <c r="Q198" t="n">
-        <v>1432900</v>
+        <v>1429400</v>
       </c>
     </row>
     <row r="199">
@@ -9145,10 +9145,10 @@
         <v>33</v>
       </c>
       <c r="N201" t="n">
-        <v>14822.378867257</v>
+        <v>14822.378864577</v>
       </c>
       <c r="O201" t="n">
-        <v>489138.502619481</v>
+        <v>489138.502531041</v>
       </c>
       <c r="P201" t="n">
         <v>24900</v>
@@ -9510,10 +9510,10 @@
         <v>18</v>
       </c>
       <c r="N209" t="n">
-        <v>12267.650842105</v>
+        <v>12267.650645161</v>
       </c>
       <c r="O209" t="n">
-        <v>220817.71515789</v>
+        <v>220817.711612898</v>
       </c>
       <c r="P209" t="n">
         <v>19900</v>
@@ -9690,10 +9690,10 @@
         <v>7</v>
       </c>
       <c r="N213" t="n">
-        <v>15851.61</v>
+        <v>15957.996644295</v>
       </c>
       <c r="O213" t="n">
-        <v>110961.27</v>
+        <v>111705.976510065</v>
       </c>
       <c r="P213" t="n">
         <v>23900</v>
@@ -9728,22 +9728,22 @@
         <v>0</v>
       </c>
       <c r="L214" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M214" t="n">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="N214" t="n">
         <v>1441.01</v>
       </c>
       <c r="O214" t="n">
-        <v>773822.37</v>
+        <v>768058.33</v>
       </c>
       <c r="P214" t="n">
         <v>2100</v>
       </c>
       <c r="Q214" t="n">
-        <v>1127700</v>
+        <v>1119300</v>
       </c>
     </row>
     <row r="215">
@@ -9813,22 +9813,22 @@
         <v>0</v>
       </c>
       <c r="L216" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M216" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="N216" t="n">
         <v>4193.85</v>
       </c>
       <c r="O216" t="n">
-        <v>289375.65</v>
+        <v>285181.8</v>
       </c>
       <c r="P216" t="n">
         <v>7500</v>
       </c>
       <c r="Q216" t="n">
-        <v>517500</v>
+        <v>510000</v>
       </c>
     </row>
     <row r="217">
@@ -9862,22 +9862,22 @@
         <v>0</v>
       </c>
       <c r="L217" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M217" t="n">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="N217" t="n">
-        <v>3041.6600125549</v>
+        <v>3041.6600125945</v>
       </c>
       <c r="O217" t="n">
-        <v>416707.4217200213</v>
+        <v>404540.7816750685</v>
       </c>
       <c r="P217" t="n">
         <v>5500</v>
       </c>
       <c r="Q217" t="n">
-        <v>753500</v>
+        <v>731500</v>
       </c>
     </row>
     <row r="218">
@@ -9914,10 +9914,10 @@
         <v>71</v>
       </c>
       <c r="N218" t="n">
-        <v>4372.2107866525</v>
+        <v>4372.2107869318</v>
       </c>
       <c r="O218" t="n">
-        <v>310426.9658523275</v>
+        <v>310426.9658721578</v>
       </c>
       <c r="P218" t="n">
         <v>7500</v>
@@ -9960,10 +9960,10 @@
         <v>508</v>
       </c>
       <c r="N219" t="n">
-        <v>1592.5676712942</v>
+        <v>1592.5675881262</v>
       </c>
       <c r="O219" t="n">
-        <v>809024.3770174535</v>
+        <v>809024.3347681096</v>
       </c>
       <c r="P219" t="n">
         <v>3900</v>
@@ -10313,22 +10313,22 @@
         <v>0</v>
       </c>
       <c r="L227" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M227" t="n">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="N227" t="n">
         <v>1770.37</v>
       </c>
       <c r="O227" t="n">
-        <v>393022.14</v>
+        <v>389481.4</v>
       </c>
       <c r="P227" t="n">
         <v>3900</v>
       </c>
       <c r="Q227" t="n">
-        <v>865800</v>
+        <v>858000</v>
       </c>
     </row>
     <row r="228">
@@ -10409,10 +10409,10 @@
         <v>65</v>
       </c>
       <c r="N229" t="n">
-        <v>17472.91</v>
+        <v>17476.031091396</v>
       </c>
       <c r="O229" t="n">
-        <v>1135739.15</v>
+        <v>1135942.02094074</v>
       </c>
       <c r="P229" t="n">
         <v>2900</v>
@@ -10910,10 +10910,10 @@
         <v>14</v>
       </c>
       <c r="N240" t="n">
-        <v>8341.030000000001</v>
+        <v>8367.5094603175</v>
       </c>
       <c r="O240" t="n">
-        <v>116774.42</v>
+        <v>117145.132444445</v>
       </c>
       <c r="P240" t="n">
         <v>13900</v>
@@ -11139,10 +11139,10 @@
         <v>15</v>
       </c>
       <c r="N245" t="n">
-        <v>1151.3923550423</v>
+        <v>1151.3923553227</v>
       </c>
       <c r="O245" t="n">
-        <v>17270.8853256345</v>
+        <v>17270.8853298405</v>
       </c>
       <c r="P245" t="n">
         <v>1500</v>
@@ -11174,22 +11174,22 @@
         <v>0</v>
       </c>
       <c r="L246" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M246" t="n">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="N246" t="n">
         <v>3751</v>
       </c>
       <c r="O246" t="n">
-        <v>2749483</v>
+        <v>2738230</v>
       </c>
       <c r="P246" t="n">
         <v>6400</v>
       </c>
       <c r="Q246" t="n">
-        <v>4691200</v>
+        <v>4672000</v>
       </c>
     </row>
     <row r="247">
@@ -11275,10 +11275,10 @@
         <v>114</v>
       </c>
       <c r="N248" t="n">
-        <v>1630.9230521929</v>
+        <v>1630.9231064431</v>
       </c>
       <c r="O248" t="n">
-        <v>185925.2279499906</v>
+        <v>185925.2341345134</v>
       </c>
       <c r="P248" t="n">
         <v>2500</v>
@@ -11321,10 +11321,10 @@
         <v>254</v>
       </c>
       <c r="N249" t="n">
-        <v>1550.1930031561</v>
+        <v>1550.1930735465</v>
       </c>
       <c r="O249" t="n">
-        <v>393749.0228016494</v>
+        <v>393749.040680811</v>
       </c>
       <c r="P249" t="n">
         <v>2500</v>
@@ -11361,22 +11361,22 @@
         <v>0</v>
       </c>
       <c r="L250" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M250" t="n">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="N250" t="n">
-        <v>2403.5101337902</v>
+        <v>2403.5102087442</v>
       </c>
       <c r="O250" t="n">
-        <v>1636790.401111126</v>
+        <v>1631983.431737312</v>
       </c>
       <c r="P250" t="n">
         <v>3500</v>
       </c>
       <c r="Q250" t="n">
-        <v>2383500</v>
+        <v>2376500</v>
       </c>
     </row>
     <row r="251">
@@ -12297,10 +12297,10 @@
         <v>1</v>
       </c>
       <c r="N271" t="n">
-        <v>7537.4721167883</v>
+        <v>7537.4721481481</v>
       </c>
       <c r="O271" t="n">
-        <v>7537.4721167883</v>
+        <v>7537.4721481481</v>
       </c>
       <c r="P271" t="n">
         <v>8900</v>
@@ -12460,22 +12460,22 @@
         <v>0</v>
       </c>
       <c r="L275" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M275" t="n">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="N275" t="n">
         <v>2517.22</v>
       </c>
       <c r="O275" t="n">
-        <v>624270.5599999999</v>
+        <v>594063.9199999999</v>
       </c>
       <c r="P275" t="n">
         <v>4200</v>
       </c>
       <c r="Q275" t="n">
-        <v>1041600</v>
+        <v>991200</v>
       </c>
     </row>
     <row r="276">
@@ -12507,10 +12507,10 @@
         <v>226</v>
       </c>
       <c r="N276" t="n">
-        <v>2029.8736460865</v>
+        <v>2029.8736549708</v>
       </c>
       <c r="O276" t="n">
-        <v>458751.444015549</v>
+        <v>458751.4460234008</v>
       </c>
       <c r="P276" t="n">
         <v>3600</v>
@@ -12583,22 +12583,22 @@
         <v>0</v>
       </c>
       <c r="L278" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M278" t="n">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="N278" t="n">
         <v>2673</v>
       </c>
       <c r="O278" t="n">
-        <v>489159</v>
+        <v>473121</v>
       </c>
       <c r="P278" t="n">
         <v>2500</v>
       </c>
       <c r="Q278" t="n">
-        <v>457500</v>
+        <v>442500</v>
       </c>
     </row>
     <row r="279">
@@ -13154,22 +13154,22 @@
         <v>0</v>
       </c>
       <c r="L291" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M291" t="n">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="N291" t="n">
         <v>3877.89</v>
       </c>
       <c r="O291" t="n">
-        <v>442079.46</v>
+        <v>418812.12</v>
       </c>
       <c r="P291" t="n">
         <v>6500</v>
       </c>
       <c r="Q291" t="n">
-        <v>741000</v>
+        <v>702000</v>
       </c>
     </row>
     <row r="292">
@@ -13203,22 +13203,22 @@
         <v>0</v>
       </c>
       <c r="L292" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M292" t="n">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="N292" t="n">
-        <v>4285.1952479339</v>
+        <v>4285.1952751817</v>
       </c>
       <c r="O292" t="n">
-        <v>488512.2582644646</v>
+        <v>467086.2849948053</v>
       </c>
       <c r="P292" t="n">
         <v>6900</v>
       </c>
       <c r="Q292" t="n">
-        <v>786600</v>
+        <v>752100</v>
       </c>
     </row>
     <row r="293">
@@ -13252,22 +13252,22 @@
         <v>0</v>
       </c>
       <c r="L293" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M293" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="N293" t="n">
         <v>9776.99</v>
       </c>
       <c r="O293" t="n">
-        <v>723497.26</v>
+        <v>694166.29</v>
       </c>
       <c r="P293" t="n">
         <v>15900</v>
       </c>
       <c r="Q293" t="n">
-        <v>1176600</v>
+        <v>1128900</v>
       </c>
     </row>
     <row r="294">
@@ -13514,10 +13514,10 @@
         <v>72</v>
       </c>
       <c r="N299" t="n">
-        <v>4605.2146487985</v>
+        <v>4605.2146574074</v>
       </c>
       <c r="O299" t="n">
-        <v>331575.454713492</v>
+        <v>331575.4553333328</v>
       </c>
       <c r="P299" t="n">
         <v>7600</v>
@@ -14194,10 +14194,10 @@
         <v>28</v>
       </c>
       <c r="N314" t="n">
-        <v>27123.765250464</v>
+        <v>27123.765241636</v>
       </c>
       <c r="O314" t="n">
-        <v>759465.427012992</v>
+        <v>759465.426765808</v>
       </c>
       <c r="P314" t="n">
         <v>44500</v>
@@ -14409,10 +14409,10 @@
         <v>14</v>
       </c>
       <c r="N319" t="n">
-        <v>8332.779624999999</v>
+        <v>8332.7796240601</v>
       </c>
       <c r="O319" t="n">
-        <v>116658.91475</v>
+        <v>116658.9147368414</v>
       </c>
       <c r="P319" t="n">
         <v>14900</v>
@@ -14536,22 +14536,22 @@
         <v>0</v>
       </c>
       <c r="L322" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M322" t="n">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="N322" t="n">
-        <v>1560.9989986027</v>
+        <v>1560.9991607397</v>
       </c>
       <c r="O322" t="n">
-        <v>218539.859804378</v>
+        <v>190441.8976102434</v>
       </c>
       <c r="P322" t="n">
         <v>2900</v>
       </c>
       <c r="Q322" t="n">
-        <v>406000</v>
+        <v>353800</v>
       </c>
     </row>
     <row r="323">
@@ -14852,10 +14852,10 @@
         <v>156</v>
       </c>
       <c r="N329" t="n">
-        <v>7969.950164794</v>
+        <v>7969.9501649175</v>
       </c>
       <c r="O329" t="n">
-        <v>1243312.225707864</v>
+        <v>1243312.22572713</v>
       </c>
       <c r="P329" t="n">
         <v>12900</v>
@@ -15850,22 +15850,22 @@
         <v>0</v>
       </c>
       <c r="L351" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M351" t="n">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="N351" t="n">
         <v>2495.98</v>
       </c>
       <c r="O351" t="n">
-        <v>534139.72</v>
+        <v>526651.78</v>
       </c>
       <c r="P351" t="n">
         <v>4100</v>
       </c>
       <c r="Q351" t="n">
-        <v>877400</v>
+        <v>865100</v>
       </c>
     </row>
     <row r="352">
@@ -15948,10 +15948,10 @@
         <v>99</v>
       </c>
       <c r="N353" t="n">
-        <v>5218.1704988662</v>
+        <v>5218.1705022831</v>
       </c>
       <c r="O353" t="n">
-        <v>516598.8793877538</v>
+        <v>516598.8797260269</v>
       </c>
       <c r="P353" t="n">
         <v>8500</v>
@@ -15994,10 +15994,10 @@
         <v>145</v>
       </c>
       <c r="N354" t="n">
-        <v>1595.0094843962</v>
+        <v>1595.0094808743</v>
       </c>
       <c r="O354" t="n">
-        <v>231276.375237449</v>
+        <v>231276.3747267735</v>
       </c>
       <c r="P354" t="n">
         <v>2600</v>
@@ -16270,10 +16270,10 @@
         <v>53</v>
       </c>
       <c r="N360" t="n">
-        <v>1664.3605954323</v>
+        <v>1664.360187234</v>
       </c>
       <c r="O360" t="n">
-        <v>88211.11155791189</v>
+        <v>88211.089923402</v>
       </c>
       <c r="P360" t="n">
         <v>2900</v>
@@ -16871,10 +16871,10 @@
         <v>147</v>
       </c>
       <c r="N373" t="n">
-        <v>1778.4725400058</v>
+        <v>1778.4725489051</v>
       </c>
       <c r="O373" t="n">
-        <v>261435.4633808526</v>
+        <v>261435.4646890497</v>
       </c>
       <c r="P373" t="n">
         <v>4900</v>
@@ -18771,10 +18771,10 @@
         <v>71</v>
       </c>
       <c r="N414" t="n">
-        <v>8293</v>
+        <v>8329.056521739099</v>
       </c>
       <c r="O414" t="n">
-        <v>588803</v>
+        <v>591363.013043476</v>
       </c>
       <c r="P414" t="n">
         <v>13500</v>
@@ -19044,22 +19044,22 @@
         <v>0</v>
       </c>
       <c r="L420" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M420" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="N420" t="n">
-        <v>2821.5820512821</v>
+        <v>2821.5822222222</v>
       </c>
       <c r="O420" t="n">
-        <v>107220.1179487198</v>
+        <v>98755.377777777</v>
       </c>
       <c r="P420" t="n">
         <v>4500</v>
       </c>
       <c r="Q420" t="n">
-        <v>171000</v>
+        <v>157500</v>
       </c>
     </row>
     <row r="421">
@@ -19234,10 +19234,10 @@
         <v>10</v>
       </c>
       <c r="N424" t="n">
-        <v>17644.653166667</v>
+        <v>17644.653275862</v>
       </c>
       <c r="O424" t="n">
-        <v>176446.53166667</v>
+        <v>176446.53275862</v>
       </c>
       <c r="P424" t="n">
         <v>28200</v>
@@ -19326,10 +19326,10 @@
         <v>59</v>
       </c>
       <c r="N426" t="n">
-        <v>2252.2963603819</v>
+        <v>2252.2964527845</v>
       </c>
       <c r="O426" t="n">
-        <v>132885.4852625321</v>
+        <v>132885.4907142855</v>
       </c>
       <c r="P426" t="n">
         <v>3900</v>
@@ -19513,10 +19513,10 @@
         <v>271</v>
       </c>
       <c r="N430" t="n">
-        <v>2328.1187525865</v>
+        <v>2328.1187507401</v>
       </c>
       <c r="O430" t="n">
-        <v>630920.1819509414</v>
+        <v>630920.1814505671</v>
       </c>
       <c r="P430" t="n">
         <v>4500</v>
@@ -20433,10 +20433,10 @@
         <v>99</v>
       </c>
       <c r="N450" t="n">
-        <v>3903.7359649123</v>
+        <v>3903.7361538462</v>
       </c>
       <c r="O450" t="n">
-        <v>386469.8605263177</v>
+        <v>386469.8792307738</v>
       </c>
       <c r="P450" t="n">
         <v>7500</v>
@@ -20791,10 +20791,10 @@
         <v>35</v>
       </c>
       <c r="N458" t="n">
-        <v>4202</v>
+        <v>4213.1164021164</v>
       </c>
       <c r="O458" t="n">
-        <v>147070</v>
+        <v>147459.074074074</v>
       </c>
       <c r="P458" t="n">
         <v>7900</v>
@@ -22220,10 +22220,10 @@
         <v>147</v>
       </c>
       <c r="N489" t="n">
-        <v>17075.989524138</v>
+        <v>17075.98952381</v>
       </c>
       <c r="O489" t="n">
-        <v>2510170.460048286</v>
+        <v>2510170.46000007</v>
       </c>
       <c r="P489" t="n">
         <v>27500</v>
@@ -24107,10 +24107,10 @@
         <v>453</v>
       </c>
       <c r="N530" t="n">
-        <v>2458.5134452463</v>
+        <v>2458.5134204724</v>
       </c>
       <c r="O530" t="n">
-        <v>1113706.590696574</v>
+        <v>1113706.579473997</v>
       </c>
       <c r="P530" t="n">
         <v>3500</v>
@@ -24153,10 +24153,10 @@
         <v>108</v>
       </c>
       <c r="N531" t="n">
-        <v>1907.3944387755</v>
+        <v>1907.3944245524</v>
       </c>
       <c r="O531" t="n">
-        <v>205998.599387754</v>
+        <v>205998.5978516592</v>
       </c>
       <c r="P531" t="n">
         <v>2500</v>
@@ -24245,10 +24245,10 @@
         <v>465</v>
       </c>
       <c r="N533" t="n">
-        <v>2079.3842077922</v>
+        <v>2079.384205911</v>
       </c>
       <c r="O533" t="n">
-        <v>966913.6566233729</v>
+        <v>966913.655748615</v>
       </c>
       <c r="P533" t="n">
         <v>2900</v>
@@ -24291,10 +24291,10 @@
         <v>339</v>
       </c>
       <c r="N534" t="n">
-        <v>1803.0149882284</v>
+        <v>1803.0150073855</v>
       </c>
       <c r="O534" t="n">
-        <v>611222.0810094276</v>
+        <v>611222.0875036845</v>
       </c>
       <c r="P534" t="n">
         <v>2500</v>
@@ -24337,10 +24337,10 @@
         <v>108</v>
       </c>
       <c r="N535" t="n">
-        <v>3306.595443038</v>
+        <v>3306.5954372624</v>
       </c>
       <c r="O535" t="n">
-        <v>357112.307848104</v>
+        <v>357112.3072243392</v>
       </c>
       <c r="P535" t="n">
         <v>4900</v>
@@ -24383,10 +24383,10 @@
         <v>565</v>
       </c>
       <c r="N536" t="n">
-        <v>2122.1641066586</v>
+        <v>2122.1640959855</v>
       </c>
       <c r="O536" t="n">
-        <v>1199022.720262109</v>
+        <v>1199022.714231808</v>
       </c>
       <c r="P536" t="n">
         <v>2900</v>
@@ -24429,10 +24429,10 @@
         <v>313</v>
       </c>
       <c r="N537" t="n">
-        <v>2108.7898867497</v>
+        <v>2108.7899091941</v>
       </c>
       <c r="O537" t="n">
-        <v>660051.2345526562</v>
+        <v>660051.2415777532</v>
       </c>
       <c r="P537" t="n">
         <v>2900</v>
@@ -24475,10 +24475,10 @@
         <v>409</v>
       </c>
       <c r="N538" t="n">
-        <v>2056.0838862559</v>
+        <v>2056.083871734</v>
       </c>
       <c r="O538" t="n">
-        <v>840938.309478663</v>
+        <v>840938.3035392059</v>
       </c>
       <c r="P538" t="n">
         <v>2900</v>
@@ -24521,10 +24521,10 @@
         <v>366</v>
       </c>
       <c r="N539" t="n">
-        <v>3224.5679768271</v>
+        <v>3224.5680666967</v>
       </c>
       <c r="O539" t="n">
-        <v>1180191.879518719</v>
+        <v>1180191.912410992</v>
       </c>
       <c r="P539" t="n">
         <v>4500</v>
@@ -24567,10 +24567,10 @@
         <v>300</v>
       </c>
       <c r="N540" t="n">
-        <v>1655.9313291536</v>
+        <v>1655.9312964128</v>
       </c>
       <c r="O540" t="n">
-        <v>496779.39874608</v>
+        <v>496779.38892384</v>
       </c>
       <c r="P540" t="n">
         <v>2500</v>
@@ -24699,22 +24699,22 @@
         <v>0</v>
       </c>
       <c r="L543" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M543" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="N543" t="n">
         <v>2454</v>
       </c>
       <c r="O543" t="n">
-        <v>161964</v>
+        <v>142332</v>
       </c>
       <c r="P543" t="n">
         <v>4200</v>
       </c>
       <c r="Q543" t="n">
-        <v>277200</v>
+        <v>243600</v>
       </c>
     </row>
     <row r="544">
@@ -24745,22 +24745,22 @@
         <v>0</v>
       </c>
       <c r="L544" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M544" t="n">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="N544" t="n">
-        <v>1592.2748727876</v>
+        <v>1592.2752659892</v>
       </c>
       <c r="O544" t="n">
-        <v>436283.3151438024</v>
+        <v>417176.1196891704</v>
       </c>
       <c r="P544" t="n">
         <v>2500</v>
       </c>
       <c r="Q544" t="n">
-        <v>685000</v>
+        <v>655000</v>
       </c>
     </row>
     <row r="545">
@@ -24795,10 +24795,10 @@
         <v>14</v>
       </c>
       <c r="N545" t="n">
-        <v>5347.73</v>
+        <v>5370.4862978723</v>
       </c>
       <c r="O545" t="n">
-        <v>74868.22</v>
+        <v>75186.8081702122</v>
       </c>
       <c r="P545" t="n">
         <v>9500</v>
@@ -24841,10 +24841,10 @@
         <v>8</v>
       </c>
       <c r="N546" t="n">
-        <v>1906.1867105263</v>
+        <v>1906.1864705882</v>
       </c>
       <c r="O546" t="n">
-        <v>15249.4936842104</v>
+        <v>15249.4917647056</v>
       </c>
       <c r="P546" t="n">
         <v>2900</v>
@@ -24887,10 +24887,10 @@
         <v>121</v>
       </c>
       <c r="N547" t="n">
-        <v>1668.6158441558</v>
+        <v>1668.6165143824</v>
       </c>
       <c r="O547" t="n">
-        <v>201902.5171428518</v>
+        <v>201902.5982402704</v>
       </c>
       <c r="P547" t="n">
         <v>2500</v>
@@ -24979,10 +24979,10 @@
         <v>996</v>
       </c>
       <c r="N549" t="n">
-        <v>1259.2744160105</v>
+        <v>1259.2744247206</v>
       </c>
       <c r="O549" t="n">
-        <v>1254237.318346458</v>
+        <v>1254237.327021718</v>
       </c>
       <c r="P549" t="n">
         <v>1900</v>
@@ -25198,22 +25198,22 @@
         <v>0</v>
       </c>
       <c r="L554" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M554" t="n">
-        <v>611</v>
+        <v>604</v>
       </c>
       <c r="N554" t="n">
         <v>1801</v>
       </c>
       <c r="O554" t="n">
-        <v>1100411</v>
+        <v>1087804</v>
       </c>
       <c r="P554" t="n">
         <v>2900</v>
       </c>
       <c r="Q554" t="n">
-        <v>1771900</v>
+        <v>1751600</v>
       </c>
     </row>
     <row r="555">
@@ -25242,22 +25242,22 @@
         <v>0</v>
       </c>
       <c r="L555" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M555" t="n">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="N555" t="n">
-        <v>692.15205253785</v>
+        <v>692.15206356312</v>
       </c>
       <c r="O555" t="n">
-        <v>228410.1773374905</v>
+        <v>220104.3562130722</v>
       </c>
       <c r="P555" t="n">
         <v>1200</v>
       </c>
       <c r="Q555" t="n">
-        <v>396000</v>
+        <v>381600</v>
       </c>
     </row>
     <row r="556">
@@ -25571,22 +25571,22 @@
         <v>0</v>
       </c>
       <c r="L562" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M562" t="n">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="N562" t="n">
         <v>2857.22</v>
       </c>
       <c r="O562" t="n">
-        <v>428582.9999999999</v>
+        <v>420011.34</v>
       </c>
       <c r="P562" t="n">
         <v>4900</v>
       </c>
       <c r="Q562" t="n">
-        <v>735000</v>
+        <v>720300</v>
       </c>
     </row>
     <row r="563">
@@ -25620,22 +25620,22 @@
         <v>0</v>
       </c>
       <c r="L563" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M563" t="n">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="N563" t="n">
         <v>8945.379999999999</v>
       </c>
       <c r="O563" t="n">
-        <v>1279189.34</v>
+        <v>1198680.92</v>
       </c>
       <c r="P563" t="n">
         <v>14900</v>
       </c>
       <c r="Q563" t="n">
-        <v>2130700</v>
+        <v>1996600</v>
       </c>
     </row>
     <row r="564">
@@ -25672,10 +25672,10 @@
         <v>68</v>
       </c>
       <c r="N564" t="n">
-        <v>3026.5146568627</v>
+        <v>3026.514679803</v>
       </c>
       <c r="O564" t="n">
-        <v>205802.9966666636</v>
+        <v>205802.998226604</v>
       </c>
       <c r="P564" t="n">
         <v>7000</v>
@@ -26372,22 +26372,22 @@
         <v>0</v>
       </c>
       <c r="L579" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M579" t="n">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="N579" t="n">
         <v>1828.64</v>
       </c>
       <c r="O579" t="n">
-        <v>2448548.96</v>
+        <v>2446720.32</v>
       </c>
       <c r="P579" t="n">
         <v>2000</v>
       </c>
       <c r="Q579" t="n">
-        <v>2678000</v>
+        <v>2676000</v>
       </c>
     </row>
     <row r="580">
@@ -26654,10 +26654,10 @@
         <v>27</v>
       </c>
       <c r="N585" t="n">
-        <v>3907.5003212851</v>
+        <v>3907.5003292181</v>
       </c>
       <c r="O585" t="n">
-        <v>105502.5086746977</v>
+        <v>105502.5088888887</v>
       </c>
       <c r="P585" t="n">
         <v>3900</v>
@@ -27201,22 +27201,22 @@
         <v>0</v>
       </c>
       <c r="L597" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M597" t="n">
-        <v>2752</v>
+        <v>2749</v>
       </c>
       <c r="N597" t="n">
-        <v>517.28774146762</v>
+        <v>517.2878865955601</v>
       </c>
       <c r="O597" t="n">
-        <v>1423575.86451889</v>
+        <v>1422024.400251195</v>
       </c>
       <c r="P597" t="n">
         <v>900</v>
       </c>
       <c r="Q597" t="n">
-        <v>2476800</v>
+        <v>2474100</v>
       </c>
     </row>
     <row r="598">
@@ -27438,10 +27438,10 @@
         <v>404</v>
       </c>
       <c r="N602" t="n">
-        <v>3110.8430699863</v>
+        <v>3110.8429819337</v>
       </c>
       <c r="O602" t="n">
-        <v>1256780.600274465</v>
+        <v>1256780.564701215</v>
       </c>
       <c r="P602" t="n">
         <v>4500</v>
@@ -27482,10 +27482,10 @@
         <v>1067</v>
       </c>
       <c r="N603" t="n">
-        <v>703.79541200942</v>
+        <v>703.79538564105</v>
       </c>
       <c r="O603" t="n">
-        <v>750949.7046140512</v>
+        <v>750949.6764790004</v>
       </c>
       <c r="P603" t="n">
         <v>900</v>
@@ -27528,10 +27528,10 @@
         <v>10</v>
       </c>
       <c r="N604" t="n">
-        <v>2501.385443038</v>
+        <v>2501.3854237288</v>
       </c>
       <c r="O604" t="n">
-        <v>25013.85443038</v>
+        <v>25013.854237288</v>
       </c>
       <c r="P604" t="n">
         <v>4100</v>
@@ -27721,10 +27721,10 @@
         <v>12</v>
       </c>
       <c r="N608" t="n">
-        <v>712.62863414634</v>
+        <v>712.6285492228</v>
       </c>
       <c r="O608" t="n">
-        <v>8551.54360975608</v>
+        <v>8551.5425906736</v>
       </c>
       <c r="P608" t="n">
         <v>700</v>
@@ -27810,22 +27810,22 @@
         <v>0</v>
       </c>
       <c r="L610" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M610" t="n">
-        <v>435</v>
+        <v>422</v>
       </c>
       <c r="N610" t="n">
-        <v>1595.5191323094</v>
+        <v>1595.5190941049</v>
       </c>
       <c r="O610" t="n">
-        <v>694050.822554589</v>
+        <v>673309.0577122677</v>
       </c>
       <c r="P610" t="n">
         <v>2500</v>
       </c>
       <c r="Q610" t="n">
-        <v>1087500</v>
+        <v>1055000</v>
       </c>
     </row>
     <row r="611">
@@ -27859,22 +27859,22 @@
         <v>0</v>
       </c>
       <c r="L611" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M611" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N611" t="n">
         <v>7923.7</v>
       </c>
       <c r="O611" t="n">
-        <v>23771.1</v>
+        <v>7923.7</v>
       </c>
       <c r="P611" t="n">
         <v>16600</v>
       </c>
       <c r="Q611" t="n">
-        <v>49800</v>
+        <v>16600</v>
       </c>
     </row>
     <row r="612">
@@ -28631,22 +28631,22 @@
         <v>0</v>
       </c>
       <c r="L627" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M627" t="n">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="N627" t="n">
         <v>1669.6</v>
       </c>
       <c r="O627" t="n">
-        <v>1010108</v>
+        <v>1005099.2</v>
       </c>
       <c r="P627" t="n">
         <v>2900</v>
       </c>
       <c r="Q627" t="n">
-        <v>1754500</v>
+        <v>1745800</v>
       </c>
     </row>
     <row r="628">
@@ -29927,22 +29927,22 @@
         <v>0</v>
       </c>
       <c r="L654" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M654" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="N654" t="n">
-        <v>875.69015686275</v>
+        <v>875.69016</v>
       </c>
       <c r="O654" t="n">
-        <v>56044.170039216</v>
+        <v>53417.09976</v>
       </c>
       <c r="P654" t="n">
         <v>4500</v>
       </c>
       <c r="Q654" t="n">
-        <v>288000</v>
+        <v>274500</v>
       </c>
     </row>
     <row r="655">
@@ -30313,22 +30313,22 @@
         <v>0</v>
       </c>
       <c r="L662" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M662" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="N662" t="n">
-        <v>3067.0905341246</v>
+        <v>3067.0905389222</v>
       </c>
       <c r="O662" t="n">
-        <v>147220.3456379808</v>
+        <v>138019.074251499</v>
       </c>
       <c r="P662" t="n">
         <v>7200</v>
       </c>
       <c r="Q662" t="n">
-        <v>345600</v>
+        <v>324000</v>
       </c>
     </row>
     <row r="663">
@@ -30463,10 +30463,10 @@
         <v>20</v>
       </c>
       <c r="N665" t="n">
-        <v>3499.72</v>
+        <v>3508.0033609467</v>
       </c>
       <c r="O665" t="n">
-        <v>69994.39999999999</v>
+        <v>70160.067218934</v>
       </c>
       <c r="P665" t="n">
         <v>6900</v>
@@ -30803,10 +30803,10 @@
         <v>33</v>
       </c>
       <c r="N672" t="n">
-        <v>4159.0002877698</v>
+        <v>4159.0002919708</v>
       </c>
       <c r="O672" t="n">
-        <v>137247.0094964034</v>
+        <v>137247.0096350364</v>
       </c>
       <c r="P672" t="n">
         <v>8900</v>
@@ -31029,10 +31029,10 @@
         <v>12</v>
       </c>
       <c r="N677" t="n">
-        <v>10737.526727273</v>
+        <v>10737.526666667</v>
       </c>
       <c r="O677" t="n">
-        <v>128850.320727276</v>
+        <v>128850.320000004</v>
       </c>
       <c r="P677" t="n">
         <v>18900</v>
@@ -31891,10 +31891,10 @@
         <v>55</v>
       </c>
       <c r="N695" t="n">
-        <v>1934.77</v>
+        <v>1942.8822431866</v>
       </c>
       <c r="O695" t="n">
-        <v>106412.35</v>
+        <v>106858.523375263</v>
       </c>
       <c r="P695" t="n">
         <v>8900</v>
@@ -32082,10 +32082,10 @@
         <v>135</v>
       </c>
       <c r="N699" t="n">
-        <v>7046.9398302567</v>
+        <v>7046.9398299681</v>
       </c>
       <c r="O699" t="n">
-        <v>951336.8770846544</v>
+        <v>951336.8770456935</v>
       </c>
       <c r="P699" t="n">
         <v>9900</v>
@@ -32410,22 +32410,22 @@
         <v>0</v>
       </c>
       <c r="L706" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M706" t="n">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="N706" t="n">
         <v>1080.18</v>
       </c>
       <c r="O706" t="n">
-        <v>373742.28</v>
+        <v>371581.92</v>
       </c>
       <c r="P706" t="n">
         <v>4900</v>
       </c>
       <c r="Q706" t="n">
-        <v>1695400</v>
+        <v>1685600</v>
       </c>
     </row>
     <row r="707">
@@ -32456,22 +32456,22 @@
         <v>0</v>
       </c>
       <c r="L707" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M707" t="n">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="N707" t="n">
         <v>1338.14</v>
       </c>
       <c r="O707" t="n">
-        <v>286361.96</v>
+        <v>283685.68</v>
       </c>
       <c r="P707" t="n">
         <v>2500</v>
       </c>
       <c r="Q707" t="n">
-        <v>535000</v>
+        <v>530000</v>
       </c>
     </row>
     <row r="708">
@@ -32554,22 +32554,22 @@
         <v>0</v>
       </c>
       <c r="L709" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M709" t="n">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="N709" t="n">
         <v>7811.9</v>
       </c>
       <c r="O709" t="n">
-        <v>1101477.9</v>
+        <v>1085854.1</v>
       </c>
       <c r="P709" t="n">
         <v>13900</v>
       </c>
       <c r="Q709" t="n">
-        <v>1959900</v>
+        <v>1932100</v>
       </c>
     </row>
     <row r="710">
@@ -32603,22 +32603,22 @@
         <v>0</v>
       </c>
       <c r="L710" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M710" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="N710" t="n">
         <v>4581.84</v>
       </c>
       <c r="O710" t="n">
-        <v>87054.96000000001</v>
+        <v>68727.60000000001</v>
       </c>
       <c r="P710" t="n">
         <v>7900</v>
       </c>
       <c r="Q710" t="n">
-        <v>150100</v>
+        <v>118500</v>
       </c>
     </row>
     <row r="711">
@@ -32652,22 +32652,22 @@
         <v>0</v>
       </c>
       <c r="L711" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M711" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="N711" t="n">
         <v>3155</v>
       </c>
       <c r="O711" t="n">
-        <v>265020</v>
+        <v>252400</v>
       </c>
       <c r="P711" t="n">
         <v>5900</v>
       </c>
       <c r="Q711" t="n">
-        <v>495600</v>
+        <v>472000</v>
       </c>
     </row>
     <row r="712">
@@ -32874,22 +32874,22 @@
         <v>0</v>
       </c>
       <c r="L716" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M716" t="n">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="N716" t="n">
         <v>6761.25</v>
       </c>
       <c r="O716" t="n">
-        <v>1189980</v>
+        <v>1176457.5</v>
       </c>
       <c r="P716" t="n">
         <v>5200</v>
       </c>
       <c r="Q716" t="n">
-        <v>915200</v>
+        <v>904800</v>
       </c>
     </row>
     <row r="717">
@@ -33297,10 +33297,10 @@
         <v>10</v>
       </c>
       <c r="N725" t="n">
-        <v>1213.6821194605</v>
+        <v>1213.6821442495</v>
       </c>
       <c r="O725" t="n">
-        <v>12136.821194605</v>
+        <v>12136.821442495</v>
       </c>
       <c r="P725" t="n">
         <v>1500</v>
@@ -33381,22 +33381,22 @@
         <v>0</v>
       </c>
       <c r="L727" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M727" t="n">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="N727" t="n">
         <v>5077</v>
       </c>
       <c r="O727" t="n">
-        <v>792012</v>
+        <v>781858</v>
       </c>
       <c r="P727" t="n">
         <v>8500</v>
       </c>
       <c r="Q727" t="n">
-        <v>1326000</v>
+        <v>1309000</v>
       </c>
     </row>
     <row r="728">
@@ -35129,22 +35129,22 @@
         <v>0</v>
       </c>
       <c r="L765" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M765" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="N765" t="n">
-        <v>970.63142857143</v>
+        <v>970.63153846154</v>
       </c>
       <c r="O765" t="n">
-        <v>25236.41714285718</v>
+        <v>23295.15692307696</v>
       </c>
       <c r="P765" t="n">
         <v>7200</v>
       </c>
       <c r="Q765" t="n">
-        <v>187200</v>
+        <v>172800</v>
       </c>
     </row>
     <row r="766">
@@ -35278,10 +35278,10 @@
         <v>51</v>
       </c>
       <c r="N768" t="n">
-        <v>1236.3</v>
+        <v>1242.6076530612</v>
       </c>
       <c r="O768" t="n">
-        <v>63051.3</v>
+        <v>63372.9903061212</v>
       </c>
       <c r="P768" t="n">
         <v>2300</v>
@@ -35318,22 +35318,22 @@
         <v>0</v>
       </c>
       <c r="L769" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M769" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N769" t="n">
         <v>11433.53</v>
       </c>
       <c r="O769" t="n">
-        <v>148635.89</v>
+        <v>125768.83</v>
       </c>
       <c r="P769" t="n">
         <v>15000</v>
       </c>
       <c r="Q769" t="n">
-        <v>195000</v>
+        <v>165000</v>
       </c>
     </row>
     <row r="770">
@@ -35415,22 +35415,22 @@
         <v>0</v>
       </c>
       <c r="L771" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M771" t="n">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="N771" t="n">
         <v>751.45</v>
       </c>
       <c r="O771" t="n">
-        <v>52601.5</v>
+        <v>45838.45</v>
       </c>
       <c r="P771" t="n">
         <v>2500</v>
       </c>
       <c r="Q771" t="n">
-        <v>175000</v>
+        <v>152500</v>
       </c>
     </row>
     <row r="772">
@@ -35461,22 +35461,22 @@
         <v>0</v>
       </c>
       <c r="L772" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M772" t="n">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="N772" t="n">
         <v>571.87</v>
       </c>
       <c r="O772" t="n">
-        <v>90927.33</v>
+        <v>88067.98</v>
       </c>
       <c r="P772" t="n">
         <v>2500</v>
       </c>
       <c r="Q772" t="n">
-        <v>397500</v>
+        <v>385000</v>
       </c>
     </row>
     <row r="773">
@@ -36110,22 +36110,22 @@
         <v>0</v>
       </c>
       <c r="L786" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M786" t="n">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="N786" t="n">
         <v>4550</v>
       </c>
       <c r="O786" t="n">
-        <v>1456000</v>
+        <v>1428700</v>
       </c>
       <c r="P786" t="n">
         <v>5500</v>
       </c>
       <c r="Q786" t="n">
-        <v>1760000</v>
+        <v>1727000</v>
       </c>
     </row>
     <row r="787">

--- a/bodegas/LJ-05.xlsx
+++ b/bodegas/LJ-05.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-12</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-13</t>
         </is>
       </c>
     </row>
@@ -1415,13 +1415,13 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
         <v>42</v>
@@ -1811,13 +1811,13 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
         <v>17</v>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="J36" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
         <v>7</v>
@@ -2314,13 +2314,13 @@
         </is>
       </c>
       <c r="J47" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
         <v>11</v>
@@ -4240,13 +4240,13 @@
         </is>
       </c>
       <c r="J91" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K91" t="n">
         <v>0</v>
       </c>
       <c r="L91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
         <v>8</v>
@@ -4318,13 +4318,13 @@
         </is>
       </c>
       <c r="J93" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
       </c>
       <c r="L93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
         <v>7</v>
@@ -4866,10 +4866,10 @@
         <v>13</v>
       </c>
       <c r="N105" t="n">
-        <v>430.87006896552</v>
+        <v>427.91889655172</v>
       </c>
       <c r="O105" t="n">
-        <v>5601.310896551759</v>
+        <v>5562.945655172361</v>
       </c>
       <c r="P105" t="n">
         <v>6800</v>
@@ -4958,10 +4958,10 @@
         <v>29</v>
       </c>
       <c r="N107" t="n">
-        <v>542.47912878788</v>
+        <v>538.40041666667</v>
       </c>
       <c r="O107" t="n">
-        <v>15731.89473484852</v>
+        <v>15613.61208333343</v>
       </c>
       <c r="P107" t="n">
         <v>6800</v>
@@ -6468,13 +6468,13 @@
         </is>
       </c>
       <c r="J142" t="n">
-        <v>1370</v>
+        <v>1367</v>
       </c>
       <c r="K142" t="n">
         <v>0</v>
       </c>
       <c r="L142" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M142" t="n">
         <v>1367</v>
@@ -7311,13 +7311,13 @@
         </is>
       </c>
       <c r="J161" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="K161" t="n">
         <v>0</v>
       </c>
       <c r="L161" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M161" t="n">
         <v>97</v>
@@ -7686,10 +7686,10 @@
         <v>84</v>
       </c>
       <c r="N169" t="n">
-        <v>1037.4476102941</v>
+        <v>1026.13</v>
       </c>
       <c r="O169" t="n">
-        <v>87145.5992647044</v>
+        <v>86194.92000000001</v>
       </c>
       <c r="P169" t="n">
         <v>1900</v>
@@ -7720,13 +7720,13 @@
         </is>
       </c>
       <c r="J170" t="n">
-        <v>1745</v>
+        <v>1725</v>
       </c>
       <c r="K170" t="n">
         <v>0</v>
       </c>
       <c r="L170" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M170" t="n">
         <v>1725</v>
@@ -8995,13 +8995,13 @@
         </is>
       </c>
       <c r="J198" t="n">
-        <v>2047</v>
+        <v>2042</v>
       </c>
       <c r="K198" t="n">
         <v>0</v>
       </c>
       <c r="L198" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M198" t="n">
         <v>2042</v>
@@ -9690,10 +9690,10 @@
         <v>7</v>
       </c>
       <c r="N213" t="n">
-        <v>15957.996644295</v>
+        <v>15851.61</v>
       </c>
       <c r="O213" t="n">
-        <v>111705.976510065</v>
+        <v>110961.27</v>
       </c>
       <c r="P213" t="n">
         <v>23900</v>
@@ -9722,13 +9722,13 @@
         </is>
       </c>
       <c r="J214" t="n">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="K214" t="n">
         <v>0</v>
       </c>
       <c r="L214" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M214" t="n">
         <v>533</v>
@@ -9807,13 +9807,13 @@
         </is>
       </c>
       <c r="J216" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K216" t="n">
         <v>0</v>
       </c>
       <c r="L216" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M216" t="n">
         <v>68</v>
@@ -9856,13 +9856,13 @@
         </is>
       </c>
       <c r="J217" t="n">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="K217" t="n">
         <v>0</v>
       </c>
       <c r="L217" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M217" t="n">
         <v>133</v>
@@ -10307,13 +10307,13 @@
         </is>
       </c>
       <c r="J227" t="n">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="K227" t="n">
         <v>0</v>
       </c>
       <c r="L227" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M227" t="n">
         <v>220</v>
@@ -10409,10 +10409,10 @@
         <v>65</v>
       </c>
       <c r="N229" t="n">
-        <v>17476.031091396</v>
+        <v>17472.91</v>
       </c>
       <c r="O229" t="n">
-        <v>1135942.02094074</v>
+        <v>1135739.15</v>
       </c>
       <c r="P229" t="n">
         <v>2900</v>
@@ -10910,10 +10910,10 @@
         <v>14</v>
       </c>
       <c r="N240" t="n">
-        <v>8367.5094603175</v>
+        <v>8341.030000000001</v>
       </c>
       <c r="O240" t="n">
-        <v>117145.132444445</v>
+        <v>116774.42</v>
       </c>
       <c r="P240" t="n">
         <v>13900</v>
@@ -11168,13 +11168,13 @@
         </is>
       </c>
       <c r="J246" t="n">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="K246" t="n">
         <v>0</v>
       </c>
       <c r="L246" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M246" t="n">
         <v>730</v>
@@ -11355,13 +11355,13 @@
         </is>
       </c>
       <c r="J250" t="n">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="K250" t="n">
         <v>0</v>
       </c>
       <c r="L250" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M250" t="n">
         <v>679</v>
@@ -12454,13 +12454,13 @@
         </is>
       </c>
       <c r="J275" t="n">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="K275" t="n">
         <v>0</v>
       </c>
       <c r="L275" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M275" t="n">
         <v>236</v>
@@ -12577,13 +12577,13 @@
         </is>
       </c>
       <c r="J278" t="n">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="K278" t="n">
         <v>0</v>
       </c>
       <c r="L278" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M278" t="n">
         <v>177</v>
@@ -13148,13 +13148,13 @@
         </is>
       </c>
       <c r="J291" t="n">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="K291" t="n">
         <v>0</v>
       </c>
       <c r="L291" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M291" t="n">
         <v>108</v>
@@ -13197,13 +13197,13 @@
         </is>
       </c>
       <c r="J292" t="n">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="K292" t="n">
         <v>0</v>
       </c>
       <c r="L292" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M292" t="n">
         <v>109</v>
@@ -13246,13 +13246,13 @@
         </is>
       </c>
       <c r="J293" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="K293" t="n">
         <v>0</v>
       </c>
       <c r="L293" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M293" t="n">
         <v>71</v>
@@ -14530,13 +14530,13 @@
         </is>
       </c>
       <c r="J322" t="n">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="K322" t="n">
         <v>0</v>
       </c>
       <c r="L322" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="M322" t="n">
         <v>122</v>
@@ -15844,13 +15844,13 @@
         </is>
       </c>
       <c r="J351" t="n">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="K351" t="n">
         <v>0</v>
       </c>
       <c r="L351" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M351" t="n">
         <v>211</v>
@@ -18771,10 +18771,10 @@
         <v>71</v>
       </c>
       <c r="N414" t="n">
-        <v>8329.056521739099</v>
+        <v>8293</v>
       </c>
       <c r="O414" t="n">
-        <v>591363.013043476</v>
+        <v>588803</v>
       </c>
       <c r="P414" t="n">
         <v>13500</v>
@@ -19038,13 +19038,13 @@
         </is>
       </c>
       <c r="J420" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="K420" t="n">
         <v>0</v>
       </c>
       <c r="L420" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M420" t="n">
         <v>35</v>
@@ -20791,10 +20791,10 @@
         <v>35</v>
       </c>
       <c r="N458" t="n">
-        <v>4213.1164021164</v>
+        <v>4202</v>
       </c>
       <c r="O458" t="n">
-        <v>147459.074074074</v>
+        <v>147070</v>
       </c>
       <c r="P458" t="n">
         <v>7900</v>
@@ -24693,13 +24693,13 @@
         </is>
       </c>
       <c r="J543" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="K543" t="n">
         <v>0</v>
       </c>
       <c r="L543" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M543" t="n">
         <v>58</v>
@@ -24739,13 +24739,13 @@
         </is>
       </c>
       <c r="J544" t="n">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="K544" t="n">
         <v>0</v>
       </c>
       <c r="L544" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M544" t="n">
         <v>262</v>
@@ -24795,10 +24795,10 @@
         <v>14</v>
       </c>
       <c r="N545" t="n">
-        <v>5370.4862978723</v>
+        <v>5347.73</v>
       </c>
       <c r="O545" t="n">
-        <v>75186.8081702122</v>
+        <v>74868.22</v>
       </c>
       <c r="P545" t="n">
         <v>9500</v>
@@ -25192,13 +25192,13 @@
         </is>
       </c>
       <c r="J554" t="n">
-        <v>611</v>
+        <v>604</v>
       </c>
       <c r="K554" t="n">
         <v>0</v>
       </c>
       <c r="L554" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M554" t="n">
         <v>604</v>
@@ -25236,13 +25236,13 @@
         </is>
       </c>
       <c r="J555" t="n">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="K555" t="n">
         <v>0</v>
       </c>
       <c r="L555" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M555" t="n">
         <v>318</v>
@@ -25565,13 +25565,13 @@
         </is>
       </c>
       <c r="J562" t="n">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="K562" t="n">
         <v>0</v>
       </c>
       <c r="L562" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M562" t="n">
         <v>147</v>
@@ -25614,13 +25614,13 @@
         </is>
       </c>
       <c r="J563" t="n">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="K563" t="n">
         <v>0</v>
       </c>
       <c r="L563" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M563" t="n">
         <v>134</v>
@@ -26366,13 +26366,13 @@
         </is>
       </c>
       <c r="J579" t="n">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="K579" t="n">
         <v>0</v>
       </c>
       <c r="L579" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M579" t="n">
         <v>1338</v>
@@ -27195,13 +27195,13 @@
         </is>
       </c>
       <c r="J597" t="n">
-        <v>2752</v>
+        <v>2749</v>
       </c>
       <c r="K597" t="n">
         <v>0</v>
       </c>
       <c r="L597" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M597" t="n">
         <v>2749</v>
@@ -27804,13 +27804,13 @@
         </is>
       </c>
       <c r="J610" t="n">
-        <v>435</v>
+        <v>422</v>
       </c>
       <c r="K610" t="n">
         <v>0</v>
       </c>
       <c r="L610" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="M610" t="n">
         <v>422</v>
@@ -27853,13 +27853,13 @@
         </is>
       </c>
       <c r="J611" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K611" t="n">
         <v>0</v>
       </c>
       <c r="L611" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M611" t="n">
         <v>1</v>
@@ -28625,13 +28625,13 @@
         </is>
       </c>
       <c r="J627" t="n">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="K627" t="n">
         <v>0</v>
       </c>
       <c r="L627" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M627" t="n">
         <v>602</v>
@@ -29921,13 +29921,13 @@
         </is>
       </c>
       <c r="J654" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="K654" t="n">
         <v>0</v>
       </c>
       <c r="L654" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M654" t="n">
         <v>61</v>
@@ -30307,13 +30307,13 @@
         </is>
       </c>
       <c r="J662" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="K662" t="n">
         <v>0</v>
       </c>
       <c r="L662" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M662" t="n">
         <v>45</v>
@@ -30463,10 +30463,10 @@
         <v>20</v>
       </c>
       <c r="N665" t="n">
-        <v>3508.0033609467</v>
+        <v>3499.72</v>
       </c>
       <c r="O665" t="n">
-        <v>70160.067218934</v>
+        <v>69994.39999999999</v>
       </c>
       <c r="P665" t="n">
         <v>6900</v>
@@ -31891,10 +31891,10 @@
         <v>55</v>
       </c>
       <c r="N695" t="n">
-        <v>1942.8822431866</v>
+        <v>1934.77</v>
       </c>
       <c r="O695" t="n">
-        <v>106858.523375263</v>
+        <v>106412.35</v>
       </c>
       <c r="P695" t="n">
         <v>8900</v>
@@ -32404,13 +32404,13 @@
         </is>
       </c>
       <c r="J706" t="n">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="K706" t="n">
         <v>0</v>
       </c>
       <c r="L706" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M706" t="n">
         <v>344</v>
@@ -32450,13 +32450,13 @@
         </is>
       </c>
       <c r="J707" t="n">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="K707" t="n">
         <v>0</v>
       </c>
       <c r="L707" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M707" t="n">
         <v>212</v>
@@ -32548,13 +32548,13 @@
         </is>
       </c>
       <c r="J709" t="n">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="K709" t="n">
         <v>0</v>
       </c>
       <c r="L709" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M709" t="n">
         <v>139</v>
@@ -32597,13 +32597,13 @@
         </is>
       </c>
       <c r="J710" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K710" t="n">
         <v>0</v>
       </c>
       <c r="L710" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M710" t="n">
         <v>15</v>
@@ -32646,13 +32646,13 @@
         </is>
       </c>
       <c r="J711" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K711" t="n">
         <v>0</v>
       </c>
       <c r="L711" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M711" t="n">
         <v>80</v>
@@ -32868,13 +32868,13 @@
         </is>
       </c>
       <c r="J716" t="n">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="K716" t="n">
         <v>0</v>
       </c>
       <c r="L716" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M716" t="n">
         <v>174</v>
@@ -33375,13 +33375,13 @@
         </is>
       </c>
       <c r="J727" t="n">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="K727" t="n">
         <v>0</v>
       </c>
       <c r="L727" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M727" t="n">
         <v>154</v>
@@ -35123,13 +35123,13 @@
         </is>
       </c>
       <c r="J765" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="K765" t="n">
         <v>0</v>
       </c>
       <c r="L765" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M765" t="n">
         <v>24</v>
@@ -35278,10 +35278,10 @@
         <v>51</v>
       </c>
       <c r="N768" t="n">
-        <v>1242.6076530612</v>
+        <v>1236.3</v>
       </c>
       <c r="O768" t="n">
-        <v>63372.9903061212</v>
+        <v>63051.3</v>
       </c>
       <c r="P768" t="n">
         <v>2300</v>
@@ -35312,13 +35312,13 @@
         </is>
       </c>
       <c r="J769" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K769" t="n">
         <v>0</v>
       </c>
       <c r="L769" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M769" t="n">
         <v>11</v>
@@ -35409,13 +35409,13 @@
         </is>
       </c>
       <c r="J771" t="n">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="K771" t="n">
         <v>0</v>
       </c>
       <c r="L771" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M771" t="n">
         <v>61</v>
@@ -35455,13 +35455,13 @@
         </is>
       </c>
       <c r="J772" t="n">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="K772" t="n">
         <v>0</v>
       </c>
       <c r="L772" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M772" t="n">
         <v>154</v>
@@ -36104,13 +36104,13 @@
         </is>
       </c>
       <c r="J786" t="n">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="K786" t="n">
         <v>0</v>
       </c>
       <c r="L786" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M786" t="n">
         <v>314</v>

--- a/bodegas/LJ-05.xlsx
+++ b/bodegas/LJ-05.xlsx
@@ -1137,22 +1137,22 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M18" t="n">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="N18" t="n">
         <v>4072</v>
       </c>
       <c r="O18" t="n">
-        <v>358336</v>
+        <v>333904</v>
       </c>
       <c r="P18" t="n">
         <v>7500</v>
       </c>
       <c r="Q18" t="n">
-        <v>660000</v>
+        <v>615000</v>
       </c>
     </row>
     <row r="19">
@@ -1583,10 +1583,10 @@
         <v>27</v>
       </c>
       <c r="N29" t="n">
-        <v>3926.8371267317</v>
+        <v>3926.8371237802</v>
       </c>
       <c r="O29" t="n">
-        <v>106024.6024217559</v>
+        <v>106024.6023420654</v>
       </c>
       <c r="P29" t="n">
         <v>4800</v>
@@ -1661,22 +1661,22 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M31" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="N31" t="n">
-        <v>11491.09631068</v>
+        <v>11955.383030303</v>
       </c>
       <c r="O31" t="n">
-        <v>390697.27456312</v>
+        <v>358661.49090909</v>
       </c>
       <c r="P31" t="n">
         <v>23000</v>
       </c>
       <c r="Q31" t="n">
-        <v>782000</v>
+        <v>690000</v>
       </c>
     </row>
     <row r="32">
@@ -2054,22 +2054,22 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M41" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N41" t="n">
-        <v>16335.98</v>
+        <v>17016.645833333</v>
       </c>
       <c r="O41" t="n">
-        <v>261375.68</v>
+        <v>255249.687499995</v>
       </c>
       <c r="P41" t="n">
         <v>44900</v>
       </c>
       <c r="Q41" t="n">
-        <v>718400</v>
+        <v>673500</v>
       </c>
     </row>
     <row r="42">
@@ -2320,22 +2320,22 @@
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M47" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="N47" t="n">
-        <v>3910.6282352941</v>
+        <v>3933.7680473373</v>
       </c>
       <c r="O47" t="n">
-        <v>43016.9105882351</v>
+        <v>31470.1443786984</v>
       </c>
       <c r="P47" t="n">
         <v>9100</v>
       </c>
       <c r="Q47" t="n">
-        <v>100100</v>
+        <v>72800</v>
       </c>
     </row>
     <row r="48">
@@ -3058,10 +3058,10 @@
         <v>15</v>
       </c>
       <c r="N63" t="n">
-        <v>16486.409489051</v>
+        <v>16486.409172932</v>
       </c>
       <c r="O63" t="n">
-        <v>247296.142335765</v>
+        <v>247296.13759398</v>
       </c>
       <c r="P63" t="n">
         <v>30500</v>
@@ -3468,22 +3468,22 @@
         <v>0</v>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M73" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N73" t="n">
-        <v>33582</v>
+        <v>36634.909090909</v>
       </c>
       <c r="O73" t="n">
-        <v>100746</v>
+        <v>73269.818181818</v>
       </c>
       <c r="P73" t="n">
         <v>53900</v>
       </c>
       <c r="Q73" t="n">
-        <v>161700</v>
+        <v>107800</v>
       </c>
     </row>
     <row r="74">
@@ -3559,22 +3559,22 @@
         <v>0</v>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M75" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N75" t="n">
-        <v>22267.552083333</v>
+        <v>23235.706521739</v>
       </c>
       <c r="O75" t="n">
-        <v>89070.208333332</v>
+        <v>69707.119565217</v>
       </c>
       <c r="P75" t="n">
         <v>46300</v>
       </c>
       <c r="Q75" t="n">
-        <v>185200</v>
+        <v>138900</v>
       </c>
     </row>
     <row r="76">
@@ -3952,22 +3952,22 @@
         <v>0</v>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M84" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N84" t="n">
-        <v>200072.19977273</v>
+        <v>200072.19992308</v>
       </c>
       <c r="O84" t="n">
-        <v>1000360.99886365</v>
+        <v>800288.7996923201</v>
       </c>
       <c r="P84" t="n">
         <v>312000</v>
       </c>
       <c r="Q84" t="n">
-        <v>1560000</v>
+        <v>1248000</v>
       </c>
     </row>
     <row r="85">
@@ -3996,22 +3996,22 @@
         <v>0</v>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>288344.10333333</v>
+        <v>288344.57</v>
       </c>
       <c r="O85" t="n">
-        <v>288344.10333333</v>
+        <v>0</v>
       </c>
       <c r="P85" t="n">
         <v>450000</v>
       </c>
       <c r="Q85" t="n">
-        <v>450000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -4043,22 +4043,22 @@
         <v>0</v>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>263530.179</v>
+        <v>263530.17666667</v>
       </c>
       <c r="O86" t="n">
-        <v>527060.358</v>
+        <v>0</v>
       </c>
       <c r="P86" t="n">
         <v>402900</v>
       </c>
       <c r="Q86" t="n">
-        <v>805800</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -4207,22 +4207,22 @@
         <v>0</v>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M90" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N90" t="n">
-        <v>20961.76</v>
+        <v>21291.002303665</v>
       </c>
       <c r="O90" t="n">
-        <v>125770.56</v>
+        <v>63873.00691099501</v>
       </c>
       <c r="P90" t="n">
         <v>38300</v>
       </c>
       <c r="Q90" t="n">
-        <v>229800</v>
+        <v>114900</v>
       </c>
     </row>
     <row r="91">
@@ -4324,22 +4324,22 @@
         <v>0</v>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M93" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N93" t="n">
-        <v>61666.873932292</v>
+        <v>61666.873994709</v>
       </c>
       <c r="O93" t="n">
-        <v>431668.117526044</v>
+        <v>246667.495978836</v>
       </c>
       <c r="P93" t="n">
         <v>98900</v>
       </c>
       <c r="Q93" t="n">
-        <v>692300</v>
+        <v>395600</v>
       </c>
     </row>
     <row r="94">
@@ -4866,10 +4866,10 @@
         <v>13</v>
       </c>
       <c r="N105" t="n">
-        <v>427.91889655172</v>
+        <v>427.91888111888</v>
       </c>
       <c r="O105" t="n">
-        <v>5562.945655172361</v>
+        <v>5562.94545454544</v>
       </c>
       <c r="P105" t="n">
         <v>6800</v>
@@ -6433,22 +6433,22 @@
         <v>0</v>
       </c>
       <c r="L141" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M141" t="n">
-        <v>735</v>
+        <v>729</v>
       </c>
       <c r="N141" t="n">
-        <v>2833</v>
+        <v>2837.5792025862</v>
       </c>
       <c r="O141" t="n">
-        <v>2082255</v>
+        <v>2068595.23868534</v>
       </c>
       <c r="P141" t="n">
         <v>3500</v>
       </c>
       <c r="Q141" t="n">
-        <v>2572500</v>
+        <v>2551500</v>
       </c>
     </row>
     <row r="142">
@@ -6697,22 +6697,22 @@
         <v>0</v>
       </c>
       <c r="L147" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M147" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N147" t="n">
-        <v>3775.99</v>
+        <v>3826.6744295302</v>
       </c>
       <c r="O147" t="n">
-        <v>173695.54</v>
+        <v>168373.6748993288</v>
       </c>
       <c r="P147" t="n">
         <v>7300</v>
       </c>
       <c r="Q147" t="n">
-        <v>335800</v>
+        <v>321200</v>
       </c>
     </row>
     <row r="148">
@@ -6915,22 +6915,22 @@
         <v>0</v>
       </c>
       <c r="L152" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M152" t="n">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="N152" t="n">
         <v>2613</v>
       </c>
       <c r="O152" t="n">
-        <v>452049</v>
+        <v>436371</v>
       </c>
       <c r="P152" t="n">
         <v>5100</v>
       </c>
       <c r="Q152" t="n">
-        <v>882300</v>
+        <v>851700</v>
       </c>
     </row>
     <row r="153">
@@ -7007,22 +7007,22 @@
         <v>0</v>
       </c>
       <c r="L154" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M154" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N154" t="n">
-        <v>7569</v>
+        <v>7632.3389121339</v>
       </c>
       <c r="O154" t="n">
-        <v>128673</v>
+        <v>114485.0836820085</v>
       </c>
       <c r="P154" t="n">
         <v>12900</v>
       </c>
       <c r="Q154" t="n">
-        <v>219300</v>
+        <v>193500</v>
       </c>
     </row>
     <row r="155">
@@ -7456,10 +7456,10 @@
         <v>735</v>
       </c>
       <c r="N164" t="n">
-        <v>3158.8608143857</v>
+        <v>3158.8608147003</v>
       </c>
       <c r="O164" t="n">
-        <v>2321762.69857349</v>
+        <v>2321762.698804721</v>
       </c>
       <c r="P164" t="n">
         <v>5600</v>
@@ -7640,10 +7640,10 @@
         <v>712</v>
       </c>
       <c r="N168" t="n">
-        <v>2694.8234624043</v>
+        <v>2694.8234565119</v>
       </c>
       <c r="O168" t="n">
-        <v>1918714.305231862</v>
+        <v>1918714.301036473</v>
       </c>
       <c r="P168" t="n">
         <v>4900</v>
@@ -7956,22 +7956,22 @@
         <v>0</v>
       </c>
       <c r="L175" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M175" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N175" t="n">
-        <v>3795.7100070547</v>
+        <v>3795.7100070621</v>
       </c>
       <c r="O175" t="n">
-        <v>53139.9400987658</v>
+        <v>45548.5200847452</v>
       </c>
       <c r="P175" t="n">
         <v>6200</v>
       </c>
       <c r="Q175" t="n">
-        <v>86800</v>
+        <v>74400</v>
       </c>
     </row>
     <row r="176">
@@ -8187,10 +8187,10 @@
         <v>56</v>
       </c>
       <c r="N180" t="n">
-        <v>4890.9300462963</v>
+        <v>4890.9300463499</v>
       </c>
       <c r="O180" t="n">
-        <v>273892.0825925928</v>
+        <v>273892.0825955944</v>
       </c>
       <c r="P180" t="n">
         <v>8200</v>
@@ -8366,22 +8366,22 @@
         <v>0</v>
       </c>
       <c r="L184" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M184" t="n">
-        <v>183</v>
+        <v>159</v>
       </c>
       <c r="N184" t="n">
         <v>1203.38</v>
       </c>
       <c r="O184" t="n">
-        <v>220218.54</v>
+        <v>191337.42</v>
       </c>
       <c r="P184" t="n">
         <v>1900</v>
       </c>
       <c r="Q184" t="n">
-        <v>347700</v>
+        <v>302100</v>
       </c>
     </row>
     <row r="185">
@@ -8412,22 +8412,22 @@
         <v>0</v>
       </c>
       <c r="L185" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M185" t="n">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="N185" t="n">
         <v>3472</v>
       </c>
       <c r="O185" t="n">
-        <v>409696</v>
+        <v>364560</v>
       </c>
       <c r="P185" t="n">
         <v>4800</v>
       </c>
       <c r="Q185" t="n">
-        <v>566400</v>
+        <v>504000</v>
       </c>
     </row>
     <row r="186">
@@ -8906,22 +8906,22 @@
         <v>0</v>
       </c>
       <c r="L196" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M196" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="N196" t="n">
-        <v>3594.2541747573</v>
+        <v>3594.25414277</v>
       </c>
       <c r="O196" t="n">
-        <v>43131.0500970876</v>
+        <v>21565.52485662</v>
       </c>
       <c r="P196" t="n">
         <v>6500</v>
       </c>
       <c r="Q196" t="n">
-        <v>78000</v>
+        <v>39000</v>
       </c>
     </row>
     <row r="197">
@@ -9001,22 +9001,22 @@
         <v>0</v>
       </c>
       <c r="L198" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M198" t="n">
-        <v>2042</v>
+        <v>1994</v>
       </c>
       <c r="N198" t="n">
         <v>489.88</v>
       </c>
       <c r="O198" t="n">
-        <v>1000334.96</v>
+        <v>976820.72</v>
       </c>
       <c r="P198" t="n">
         <v>700</v>
       </c>
       <c r="Q198" t="n">
-        <v>1429400</v>
+        <v>1395800</v>
       </c>
     </row>
     <row r="199">
@@ -9145,10 +9145,10 @@
         <v>33</v>
       </c>
       <c r="N201" t="n">
-        <v>14822.378864577</v>
+        <v>14822.378863905</v>
       </c>
       <c r="O201" t="n">
-        <v>489138.502531041</v>
+        <v>489138.502508865</v>
       </c>
       <c r="P201" t="n">
         <v>24900</v>
@@ -9908,22 +9908,22 @@
         <v>0</v>
       </c>
       <c r="L218" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M218" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="N218" t="n">
-        <v>4372.2107869318</v>
+        <v>4372.2107876031</v>
       </c>
       <c r="O218" t="n">
-        <v>310426.9658721578</v>
+        <v>301682.5443446139</v>
       </c>
       <c r="P218" t="n">
         <v>7500</v>
       </c>
       <c r="Q218" t="n">
-        <v>532500</v>
+        <v>517500</v>
       </c>
     </row>
     <row r="219">
@@ -9954,22 +9954,22 @@
         <v>0</v>
       </c>
       <c r="L219" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M219" t="n">
-        <v>508</v>
+        <v>494</v>
       </c>
       <c r="N219" t="n">
-        <v>1592.5675881262</v>
+        <v>1592.567520267</v>
       </c>
       <c r="O219" t="n">
-        <v>809024.3347681096</v>
+        <v>786728.355011898</v>
       </c>
       <c r="P219" t="n">
         <v>3900</v>
       </c>
       <c r="Q219" t="n">
-        <v>1981200</v>
+        <v>1926600</v>
       </c>
     </row>
     <row r="220">
@@ -10579,22 +10579,22 @@
         <v>0</v>
       </c>
       <c r="L233" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M233" t="n">
-        <v>2324</v>
+        <v>2322</v>
       </c>
       <c r="N233" t="n">
         <v>1387.55</v>
       </c>
       <c r="O233" t="n">
-        <v>3224666.2</v>
+        <v>3221891.1</v>
       </c>
       <c r="P233" t="n">
         <v>2300</v>
       </c>
       <c r="Q233" t="n">
-        <v>5345200</v>
+        <v>5340600</v>
       </c>
     </row>
     <row r="234">
@@ -10860,22 +10860,22 @@
         <v>0</v>
       </c>
       <c r="L239" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M239" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="N239" t="n">
-        <v>16897</v>
+        <v>17010.976391231</v>
       </c>
       <c r="O239" t="n">
-        <v>1622112</v>
+        <v>1565009.827993252</v>
       </c>
       <c r="P239" t="n">
         <v>27900</v>
       </c>
       <c r="Q239" t="n">
-        <v>2678400</v>
+        <v>2566800</v>
       </c>
     </row>
     <row r="240">
@@ -11269,22 +11269,22 @@
         <v>0</v>
       </c>
       <c r="L248" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M248" t="n">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="N248" t="n">
-        <v>1630.9231064431</v>
+        <v>1630.923147125</v>
       </c>
       <c r="O248" t="n">
-        <v>185925.2341345134</v>
+        <v>159830.46841825</v>
       </c>
       <c r="P248" t="n">
         <v>2500</v>
       </c>
       <c r="Q248" t="n">
-        <v>285000</v>
+        <v>245000</v>
       </c>
     </row>
     <row r="249">
@@ -11315,22 +11315,22 @@
         <v>0</v>
       </c>
       <c r="L249" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M249" t="n">
-        <v>254</v>
+        <v>238</v>
       </c>
       <c r="N249" t="n">
-        <v>1550.1930735465</v>
+        <v>1550.1931350849</v>
       </c>
       <c r="O249" t="n">
-        <v>393749.040680811</v>
+        <v>368945.9661502062</v>
       </c>
       <c r="P249" t="n">
         <v>2500</v>
       </c>
       <c r="Q249" t="n">
-        <v>635000</v>
+        <v>595000</v>
       </c>
     </row>
     <row r="250">
@@ -11361,22 +11361,22 @@
         <v>0</v>
       </c>
       <c r="L250" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M250" t="n">
-        <v>679</v>
+        <v>663</v>
       </c>
       <c r="N250" t="n">
-        <v>2403.5102087442</v>
+        <v>2403.5103430475</v>
       </c>
       <c r="O250" t="n">
-        <v>1631983.431737312</v>
+        <v>1593527.357440493</v>
       </c>
       <c r="P250" t="n">
         <v>3500</v>
       </c>
       <c r="Q250" t="n">
-        <v>2376500</v>
+        <v>2320500</v>
       </c>
     </row>
     <row r="251">
@@ -12297,10 +12297,10 @@
         <v>1</v>
       </c>
       <c r="N271" t="n">
-        <v>7537.4721481481</v>
+        <v>7537.4721641791</v>
       </c>
       <c r="O271" t="n">
-        <v>7537.4721481481</v>
+        <v>7537.4721641791</v>
       </c>
       <c r="P271" t="n">
         <v>8900</v>
@@ -12507,10 +12507,10 @@
         <v>226</v>
       </c>
       <c r="N276" t="n">
-        <v>2029.8736549708</v>
+        <v>2029.8736782737</v>
       </c>
       <c r="O276" t="n">
-        <v>458751.4460234008</v>
+        <v>458751.4512898562</v>
       </c>
       <c r="P276" t="n">
         <v>3600</v>
@@ -12542,22 +12542,22 @@
         <v>0</v>
       </c>
       <c r="L277" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M277" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N277" t="n">
-        <v>22485.695904437</v>
+        <v>22511.306036446</v>
       </c>
       <c r="O277" t="n">
-        <v>449713.91808874</v>
+        <v>427714.814692474</v>
       </c>
       <c r="P277" t="n">
         <v>36500</v>
       </c>
       <c r="Q277" t="n">
-        <v>730000</v>
+        <v>693500</v>
       </c>
     </row>
     <row r="278">
@@ -13647,10 +13647,10 @@
         <v>37</v>
       </c>
       <c r="N302" t="n">
-        <v>11562.038530184</v>
+        <v>11562.038526316</v>
       </c>
       <c r="O302" t="n">
-        <v>427795.425616808</v>
+        <v>427795.425473692</v>
       </c>
       <c r="P302" t="n">
         <v>18500</v>
@@ -13693,10 +13693,10 @@
         <v>44</v>
       </c>
       <c r="N303" t="n">
-        <v>13513.642971014</v>
+        <v>13513.642992701</v>
       </c>
       <c r="O303" t="n">
-        <v>594600.290724616</v>
+        <v>594600.291678844</v>
       </c>
       <c r="P303" t="n">
         <v>21900</v>
@@ -14194,10 +14194,10 @@
         <v>28</v>
       </c>
       <c r="N314" t="n">
-        <v>27123.765241636</v>
+        <v>27123.765232775</v>
       </c>
       <c r="O314" t="n">
-        <v>759465.426765808</v>
+        <v>759465.4265177</v>
       </c>
       <c r="P314" t="n">
         <v>44500</v>
@@ -14490,22 +14490,22 @@
         <v>0</v>
       </c>
       <c r="L321" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M321" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="N321" t="n">
-        <v>5431.12</v>
+        <v>5465.2779874214</v>
       </c>
       <c r="O321" t="n">
-        <v>282418.24</v>
+        <v>267798.6213836486</v>
       </c>
       <c r="P321" t="n">
         <v>8900</v>
       </c>
       <c r="Q321" t="n">
-        <v>462800</v>
+        <v>436100</v>
       </c>
     </row>
     <row r="322">
@@ -14536,22 +14536,22 @@
         <v>0</v>
       </c>
       <c r="L322" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M322" t="n">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="N322" t="n">
-        <v>1560.9991607397</v>
+        <v>1560.999261745</v>
       </c>
       <c r="O322" t="n">
-        <v>190441.8976102434</v>
+        <v>152977.92765101</v>
       </c>
       <c r="P322" t="n">
         <v>2900</v>
       </c>
       <c r="Q322" t="n">
-        <v>353800</v>
+        <v>284200</v>
       </c>
     </row>
     <row r="323">
@@ -14751,22 +14751,22 @@
         <v>0</v>
       </c>
       <c r="L327" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M327" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="N327" t="n">
-        <v>11662.4</v>
+        <v>12042.695652174</v>
       </c>
       <c r="O327" t="n">
-        <v>198260.8</v>
+        <v>168597.739130436</v>
       </c>
       <c r="P327" t="n">
         <v>19900</v>
       </c>
       <c r="Q327" t="n">
-        <v>338300</v>
+        <v>278600</v>
       </c>
     </row>
     <row r="328">
@@ -14846,22 +14846,22 @@
         <v>0</v>
       </c>
       <c r="L329" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M329" t="n">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="N329" t="n">
-        <v>7969.9501649175</v>
+        <v>7987.9139894816</v>
       </c>
       <c r="O329" t="n">
-        <v>1243312.22572713</v>
+        <v>1222150.840390685</v>
       </c>
       <c r="P329" t="n">
         <v>12900</v>
       </c>
       <c r="Q329" t="n">
-        <v>2012400</v>
+        <v>1973700</v>
       </c>
     </row>
     <row r="330">
@@ -15574,22 +15574,22 @@
         <v>0</v>
       </c>
       <c r="L345" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M345" t="n">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="N345" t="n">
         <v>2634.61</v>
       </c>
       <c r="O345" t="n">
-        <v>437345.26</v>
+        <v>403095.33</v>
       </c>
       <c r="P345" t="n">
         <v>4200</v>
       </c>
       <c r="Q345" t="n">
-        <v>697200</v>
+        <v>642600</v>
       </c>
     </row>
     <row r="346">
@@ -15626,10 +15626,10 @@
         <v>82</v>
       </c>
       <c r="N346" t="n">
-        <v>3113.8900261438</v>
+        <v>3113.8900262812</v>
       </c>
       <c r="O346" t="n">
-        <v>255338.9821437916</v>
+        <v>255338.9821550584</v>
       </c>
       <c r="P346" t="n">
         <v>5000</v>
@@ -15758,22 +15758,22 @@
         <v>0</v>
       </c>
       <c r="L349" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M349" t="n">
-        <v>123</v>
+        <v>103</v>
       </c>
       <c r="N349" t="n">
         <v>5410.72</v>
       </c>
       <c r="O349" t="n">
-        <v>665518.5600000001</v>
+        <v>557304.16</v>
       </c>
       <c r="P349" t="n">
         <v>8700</v>
       </c>
       <c r="Q349" t="n">
-        <v>1070100</v>
+        <v>896100</v>
       </c>
     </row>
     <row r="350">
@@ -15804,22 +15804,22 @@
         <v>0</v>
       </c>
       <c r="L350" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M350" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N350" t="n">
-        <v>4163.1601724138</v>
+        <v>4163.1601818182</v>
       </c>
       <c r="O350" t="n">
-        <v>70773.7229310346</v>
+        <v>66610.5629090912</v>
       </c>
       <c r="P350" t="n">
         <v>6700</v>
       </c>
       <c r="Q350" t="n">
-        <v>113900</v>
+        <v>107200</v>
       </c>
     </row>
     <row r="351">
@@ -15942,22 +15942,22 @@
         <v>0</v>
       </c>
       <c r="L353" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M353" t="n">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="N353" t="n">
-        <v>5218.1705022831</v>
+        <v>5218.1705134189</v>
       </c>
       <c r="O353" t="n">
-        <v>516598.8797260269</v>
+        <v>485289.8577479577</v>
       </c>
       <c r="P353" t="n">
         <v>8500</v>
       </c>
       <c r="Q353" t="n">
-        <v>841500</v>
+        <v>790500</v>
       </c>
     </row>
     <row r="354">
@@ -15988,22 +15988,22 @@
         <v>0</v>
       </c>
       <c r="L354" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M354" t="n">
-        <v>145</v>
+        <v>127</v>
       </c>
       <c r="N354" t="n">
-        <v>1595.0094808743</v>
+        <v>1595.0094571429</v>
       </c>
       <c r="O354" t="n">
-        <v>231276.3747267735</v>
+        <v>202566.2010571483</v>
       </c>
       <c r="P354" t="n">
         <v>2600</v>
       </c>
       <c r="Q354" t="n">
-        <v>377000</v>
+        <v>330200</v>
       </c>
     </row>
     <row r="355">
@@ -16034,22 +16034,22 @@
         <v>0</v>
       </c>
       <c r="L355" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M355" t="n">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="N355" t="n">
-        <v>3610.6500238663</v>
+        <v>3610.6500248756</v>
       </c>
       <c r="O355" t="n">
-        <v>137204.7009069194</v>
+        <v>28885.2001990048</v>
       </c>
       <c r="P355" t="n">
         <v>5800</v>
       </c>
       <c r="Q355" t="n">
-        <v>220400</v>
+        <v>46400</v>
       </c>
     </row>
     <row r="356">
@@ -16126,22 +16126,22 @@
         <v>0</v>
       </c>
       <c r="L357" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M357" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="N357" t="n">
         <v>4227.77</v>
       </c>
       <c r="O357" t="n">
-        <v>240982.89</v>
+        <v>224071.81</v>
       </c>
       <c r="P357" t="n">
         <v>6900</v>
       </c>
       <c r="Q357" t="n">
-        <v>393300</v>
+        <v>365700</v>
       </c>
     </row>
     <row r="358">
@@ -16172,22 +16172,22 @@
         <v>0</v>
       </c>
       <c r="L358" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M358" t="n">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="N358" t="n">
         <v>3965.02</v>
       </c>
       <c r="O358" t="n">
-        <v>642333.24</v>
+        <v>594753</v>
       </c>
       <c r="P358" t="n">
         <v>6500</v>
       </c>
       <c r="Q358" t="n">
-        <v>1053000</v>
+        <v>975000</v>
       </c>
     </row>
     <row r="359">
@@ -16264,22 +16264,22 @@
         <v>0</v>
       </c>
       <c r="L360" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M360" t="n">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="N360" t="n">
-        <v>1664.360187234</v>
+        <v>1664.359264432</v>
       </c>
       <c r="O360" t="n">
-        <v>88211.089923402</v>
+        <v>61581.292783984</v>
       </c>
       <c r="P360" t="n">
         <v>2900</v>
       </c>
       <c r="Q360" t="n">
-        <v>153700</v>
+        <v>107300</v>
       </c>
     </row>
     <row r="361">
@@ -16359,22 +16359,22 @@
         <v>0</v>
       </c>
       <c r="L362" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M362" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N362" t="n">
-        <v>10174</v>
+        <v>10716.613333333</v>
       </c>
       <c r="O362" t="n">
-        <v>40696</v>
+        <v>0</v>
       </c>
       <c r="P362" t="n">
         <v>16900</v>
       </c>
       <c r="Q362" t="n">
-        <v>67600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="363">
@@ -16543,22 +16543,22 @@
         <v>0</v>
       </c>
       <c r="L366" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M366" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N366" t="n">
-        <v>15824</v>
+        <v>15908.394666667</v>
       </c>
       <c r="O366" t="n">
-        <v>142416</v>
+        <v>111358.762666669</v>
       </c>
       <c r="P366" t="n">
         <v>26900</v>
       </c>
       <c r="Q366" t="n">
-        <v>242100</v>
+        <v>188300</v>
       </c>
     </row>
     <row r="367">
@@ -16773,22 +16773,22 @@
         <v>0</v>
       </c>
       <c r="L371" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M371" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N371" t="n">
-        <v>23521.624776119</v>
+        <v>23878.013030303</v>
       </c>
       <c r="O371" t="n">
-        <v>164651.373432833</v>
+        <v>143268.078181818</v>
       </c>
       <c r="P371" t="n">
         <v>39000</v>
       </c>
       <c r="Q371" t="n">
-        <v>273000</v>
+        <v>234000</v>
       </c>
     </row>
     <row r="372">
@@ -16825,10 +16825,10 @@
         <v>20</v>
       </c>
       <c r="N372" t="n">
-        <v>3486</v>
+        <v>3502.5901249256</v>
       </c>
       <c r="O372" t="n">
-        <v>69720</v>
+        <v>70051.802498512</v>
       </c>
       <c r="P372" t="n">
         <v>6900</v>
@@ -16865,22 +16865,22 @@
         <v>0</v>
       </c>
       <c r="L373" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="M373" t="n">
-        <v>147</v>
+        <v>115</v>
       </c>
       <c r="N373" t="n">
-        <v>1778.4725489051</v>
+        <v>1786.8332290289</v>
       </c>
       <c r="O373" t="n">
-        <v>261435.4646890497</v>
+        <v>205485.8213383235</v>
       </c>
       <c r="P373" t="n">
         <v>4900</v>
       </c>
       <c r="Q373" t="n">
-        <v>720300</v>
+        <v>563500</v>
       </c>
     </row>
     <row r="374">
@@ -18348,22 +18348,22 @@
         <v>0</v>
       </c>
       <c r="L405" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M405" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="N405" t="n">
-        <v>4917</v>
+        <v>5030.2949308756</v>
       </c>
       <c r="O405" t="n">
-        <v>93423</v>
+        <v>70424.1290322584</v>
       </c>
       <c r="P405" t="n">
         <v>8600</v>
       </c>
       <c r="Q405" t="n">
-        <v>163400</v>
+        <v>120400</v>
       </c>
     </row>
     <row r="406">
@@ -18581,22 +18581,22 @@
         <v>0</v>
       </c>
       <c r="L410" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M410" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N410" t="n">
         <v>89385</v>
       </c>
       <c r="O410" t="n">
-        <v>625695</v>
+        <v>536310</v>
       </c>
       <c r="P410" t="n">
         <v>150000</v>
       </c>
       <c r="Q410" t="n">
-        <v>1050000</v>
+        <v>900000</v>
       </c>
     </row>
     <row r="411">
@@ -18765,22 +18765,22 @@
         <v>0</v>
       </c>
       <c r="L414" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M414" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="N414" t="n">
-        <v>8293</v>
+        <v>8329.2139737991</v>
       </c>
       <c r="O414" t="n">
-        <v>588803</v>
+        <v>574715.7641921379</v>
       </c>
       <c r="P414" t="n">
         <v>13500</v>
       </c>
       <c r="Q414" t="n">
-        <v>958500</v>
+        <v>931500</v>
       </c>
     </row>
     <row r="415">
@@ -18811,22 +18811,22 @@
         <v>0</v>
       </c>
       <c r="L415" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M415" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="N415" t="n">
-        <v>7713</v>
+        <v>7735.3565217391</v>
       </c>
       <c r="O415" t="n">
-        <v>192825</v>
+        <v>177913.1999999993</v>
       </c>
       <c r="P415" t="n">
         <v>12500</v>
       </c>
       <c r="Q415" t="n">
-        <v>312500</v>
+        <v>287500</v>
       </c>
     </row>
     <row r="416">
@@ -19182,22 +19182,22 @@
         <v>0</v>
       </c>
       <c r="L423" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M423" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="N423" t="n">
-        <v>13019</v>
+        <v>13090.336986301</v>
       </c>
       <c r="O423" t="n">
-        <v>455665</v>
+        <v>431981.120547933</v>
       </c>
       <c r="P423" t="n">
         <v>20900</v>
       </c>
       <c r="Q423" t="n">
-        <v>731500</v>
+        <v>689700</v>
       </c>
     </row>
     <row r="424">
@@ -19234,10 +19234,10 @@
         <v>10</v>
       </c>
       <c r="N424" t="n">
-        <v>17644.653275862</v>
+        <v>17644.653166667</v>
       </c>
       <c r="O424" t="n">
-        <v>176446.53275862</v>
+        <v>176446.53166667</v>
       </c>
       <c r="P424" t="n">
         <v>28200</v>
@@ -19513,10 +19513,10 @@
         <v>271</v>
       </c>
       <c r="N430" t="n">
-        <v>2328.1187507401</v>
+        <v>2328.1187488882</v>
       </c>
       <c r="O430" t="n">
-        <v>630920.1814505671</v>
+        <v>630920.1809487023</v>
       </c>
       <c r="P430" t="n">
         <v>4500</v>
@@ -20065,10 +20065,10 @@
         <v>51</v>
       </c>
       <c r="N442" t="n">
-        <v>4907.8219330289</v>
+        <v>4907.821941896</v>
       </c>
       <c r="O442" t="n">
-        <v>250298.9185844739</v>
+        <v>250298.919036696</v>
       </c>
       <c r="P442" t="n">
         <v>8200</v>
@@ -20105,22 +20105,22 @@
         <v>0</v>
       </c>
       <c r="L443" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M443" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N443" t="n">
-        <v>6414</v>
+        <v>6426.7641791045</v>
       </c>
       <c r="O443" t="n">
-        <v>307872</v>
+        <v>295631.152238807</v>
       </c>
       <c r="P443" t="n">
         <v>10900</v>
       </c>
       <c r="Q443" t="n">
-        <v>523200</v>
+        <v>501400</v>
       </c>
     </row>
     <row r="444">
@@ -20433,10 +20433,10 @@
         <v>99</v>
       </c>
       <c r="N450" t="n">
-        <v>3903.7361538462</v>
+        <v>3903.7361658031</v>
       </c>
       <c r="O450" t="n">
-        <v>386469.8792307738</v>
+        <v>386469.8804145069</v>
       </c>
       <c r="P450" t="n">
         <v>7500</v>
@@ -20785,22 +20785,22 @@
         <v>0</v>
       </c>
       <c r="L458" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M458" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="N458" t="n">
-        <v>4202</v>
+        <v>4235.616</v>
       </c>
       <c r="O458" t="n">
-        <v>147070</v>
+        <v>135539.712</v>
       </c>
       <c r="P458" t="n">
         <v>7900</v>
       </c>
       <c r="Q458" t="n">
-        <v>276500</v>
+        <v>252800</v>
       </c>
     </row>
     <row r="459">
@@ -21015,22 +21015,22 @@
         <v>0</v>
       </c>
       <c r="L463" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M463" t="n">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="N463" t="n">
-        <v>2629</v>
+        <v>2655.7582697201</v>
       </c>
       <c r="O463" t="n">
-        <v>483736</v>
+        <v>456790.4223918572</v>
       </c>
       <c r="P463" t="n">
         <v>4500</v>
       </c>
       <c r="Q463" t="n">
-        <v>828000</v>
+        <v>774000</v>
       </c>
     </row>
     <row r="464">
@@ -21199,22 +21199,22 @@
         <v>0</v>
       </c>
       <c r="L467" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M467" t="n">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="N467" t="n">
-        <v>5772</v>
+        <v>5789.4673839946</v>
       </c>
       <c r="O467" t="n">
-        <v>1033188</v>
+        <v>984209.4552790819</v>
       </c>
       <c r="P467" t="n">
         <v>9900</v>
       </c>
       <c r="Q467" t="n">
-        <v>1772100</v>
+        <v>1683000</v>
       </c>
     </row>
     <row r="468">
@@ -21245,22 +21245,22 @@
         <v>0</v>
       </c>
       <c r="L468" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M468" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="N468" t="n">
-        <v>8637</v>
+        <v>9222.5593220339</v>
       </c>
       <c r="O468" t="n">
-        <v>164103</v>
+        <v>138338.3898305085</v>
       </c>
       <c r="P468" t="n">
         <v>14500</v>
       </c>
       <c r="Q468" t="n">
-        <v>275500</v>
+        <v>217500</v>
       </c>
     </row>
     <row r="469">
@@ -21291,22 +21291,22 @@
         <v>0</v>
       </c>
       <c r="L469" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M469" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="N469" t="n">
-        <v>6645</v>
+        <v>6663.0865541644</v>
       </c>
       <c r="O469" t="n">
-        <v>299025</v>
+        <v>233208.029395754</v>
       </c>
       <c r="P469" t="n">
         <v>10900</v>
       </c>
       <c r="Q469" t="n">
-        <v>490500</v>
+        <v>381500</v>
       </c>
     </row>
     <row r="470">
@@ -21337,22 +21337,22 @@
         <v>0</v>
       </c>
       <c r="L470" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M470" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="N470" t="n">
-        <v>13098</v>
+        <v>13167.485411141</v>
       </c>
       <c r="O470" t="n">
-        <v>497724</v>
+        <v>381857.076923089</v>
       </c>
       <c r="P470" t="n">
         <v>21200</v>
       </c>
       <c r="Q470" t="n">
-        <v>805600</v>
+        <v>614800</v>
       </c>
     </row>
     <row r="471">
@@ -21521,22 +21521,22 @@
         <v>0</v>
       </c>
       <c r="L474" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M474" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="N474" t="n">
-        <v>3898</v>
+        <v>3913.1437451437</v>
       </c>
       <c r="O474" t="n">
-        <v>85756</v>
+        <v>66523.4436674429</v>
       </c>
       <c r="P474" t="n">
         <v>6900</v>
       </c>
       <c r="Q474" t="n">
-        <v>151800</v>
+        <v>117300</v>
       </c>
     </row>
     <row r="475">
@@ -22122,22 +22122,22 @@
         <v>0</v>
       </c>
       <c r="L487" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M487" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N487" t="n">
         <v>3119</v>
       </c>
       <c r="O487" t="n">
-        <v>3119</v>
+        <v>0</v>
       </c>
       <c r="P487" t="n">
         <v>5900</v>
       </c>
       <c r="Q487" t="n">
-        <v>5900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="488">
@@ -22577,22 +22577,22 @@
         <v>0</v>
       </c>
       <c r="L497" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M497" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="N497" t="n">
-        <v>10219</v>
+        <v>10293.773170732</v>
       </c>
       <c r="O497" t="n">
-        <v>286132</v>
+        <v>257344.3292683</v>
       </c>
       <c r="P497" t="n">
         <v>16900</v>
       </c>
       <c r="Q497" t="n">
-        <v>473200</v>
+        <v>422500</v>
       </c>
     </row>
     <row r="498">
@@ -22764,22 +22764,22 @@
         <v>0</v>
       </c>
       <c r="L501" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M501" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N501" t="n">
-        <v>27254</v>
+        <v>27323.703324808</v>
       </c>
       <c r="O501" t="n">
-        <v>517826</v>
+        <v>464502.956521736</v>
       </c>
       <c r="P501" t="n">
         <v>43900</v>
       </c>
       <c r="Q501" t="n">
-        <v>834100</v>
+        <v>746300</v>
       </c>
     </row>
     <row r="502">
@@ -23224,22 +23224,22 @@
         <v>0</v>
       </c>
       <c r="L511" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M511" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="N511" t="n">
-        <v>3639.35</v>
+        <v>3659.324478595</v>
       </c>
       <c r="O511" t="n">
-        <v>43672.2</v>
+        <v>25615.271350165</v>
       </c>
       <c r="P511" t="n">
         <v>7500</v>
       </c>
       <c r="Q511" t="n">
-        <v>90000</v>
+        <v>52500</v>
       </c>
     </row>
     <row r="512">
@@ -23316,22 +23316,22 @@
         <v>0</v>
       </c>
       <c r="L513" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M513" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="N513" t="n">
-        <v>5640</v>
+        <v>5732.1568627451</v>
       </c>
       <c r="O513" t="n">
-        <v>163560</v>
+        <v>137571.7647058824</v>
       </c>
       <c r="P513" t="n">
         <v>9900</v>
       </c>
       <c r="Q513" t="n">
-        <v>287100</v>
+        <v>237600</v>
       </c>
     </row>
     <row r="514">
@@ -23546,22 +23546,22 @@
         <v>0</v>
       </c>
       <c r="L518" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M518" t="n">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="N518" t="n">
-        <v>3821</v>
+        <v>3828.7583756345</v>
       </c>
       <c r="O518" t="n">
-        <v>939966</v>
+        <v>895929.459898473</v>
       </c>
       <c r="P518" t="n">
         <v>5900</v>
       </c>
       <c r="Q518" t="n">
-        <v>1451400</v>
+        <v>1380600</v>
       </c>
     </row>
     <row r="519">
@@ -23822,22 +23822,22 @@
         <v>0</v>
       </c>
       <c r="L524" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M524" t="n">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="N524" t="n">
-        <v>5476</v>
+        <v>5504.4467532468</v>
       </c>
       <c r="O524" t="n">
-        <v>848780</v>
+        <v>809153.6727272796</v>
       </c>
       <c r="P524" t="n">
         <v>8900</v>
       </c>
       <c r="Q524" t="n">
-        <v>1379500</v>
+        <v>1308300</v>
       </c>
     </row>
     <row r="525">
@@ -24009,22 +24009,22 @@
         <v>0</v>
       </c>
       <c r="L528" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M528" t="n">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="N528" t="n">
-        <v>1516.0388129219</v>
+        <v>1517.7951815022</v>
       </c>
       <c r="O528" t="n">
-        <v>383557.8196692407</v>
+        <v>365788.6387420302</v>
       </c>
       <c r="P528" t="n">
         <v>2300</v>
       </c>
       <c r="Q528" t="n">
-        <v>581900</v>
+        <v>554300</v>
       </c>
     </row>
     <row r="529">
@@ -24101,22 +24101,22 @@
         <v>0</v>
       </c>
       <c r="L530" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M530" t="n">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="N530" t="n">
-        <v>2458.5134204724</v>
+        <v>2458.5134059343</v>
       </c>
       <c r="O530" t="n">
-        <v>1113706.579473997</v>
+        <v>1106331.032670435</v>
       </c>
       <c r="P530" t="n">
         <v>3500</v>
       </c>
       <c r="Q530" t="n">
-        <v>1585500</v>
+        <v>1575000</v>
       </c>
     </row>
     <row r="531">
@@ -24147,22 +24147,22 @@
         <v>0</v>
       </c>
       <c r="L531" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M531" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="N531" t="n">
-        <v>1907.3944245524</v>
+        <v>1907.3942832168</v>
       </c>
       <c r="O531" t="n">
-        <v>205998.5978516592</v>
+        <v>200276.399737764</v>
       </c>
       <c r="P531" t="n">
         <v>2500</v>
       </c>
       <c r="Q531" t="n">
-        <v>270000</v>
+        <v>262500</v>
       </c>
     </row>
     <row r="532">
@@ -24199,10 +24199,10 @@
         <v>189</v>
       </c>
       <c r="N532" t="n">
-        <v>1771.0912628399</v>
+        <v>1771.0911342735</v>
       </c>
       <c r="O532" t="n">
-        <v>334736.2486767411</v>
+        <v>334736.2243776915</v>
       </c>
       <c r="P532" t="n">
         <v>2500</v>
@@ -24245,10 +24245,10 @@
         <v>465</v>
       </c>
       <c r="N533" t="n">
-        <v>2079.384205911</v>
+        <v>2079.3842021449</v>
       </c>
       <c r="O533" t="n">
-        <v>966913.655748615</v>
+        <v>966913.6539973785</v>
       </c>
       <c r="P533" t="n">
         <v>2900</v>
@@ -24291,10 +24291,10 @@
         <v>339</v>
       </c>
       <c r="N534" t="n">
-        <v>1803.0150073855</v>
+        <v>1803.0151441578</v>
       </c>
       <c r="O534" t="n">
-        <v>611222.0875036845</v>
+        <v>611222.1338694942</v>
       </c>
       <c r="P534" t="n">
         <v>2500</v>
@@ -24331,22 +24331,22 @@
         <v>0</v>
       </c>
       <c r="L535" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M535" t="n">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="N535" t="n">
-        <v>3306.5954372624</v>
+        <v>3306.5953548387</v>
       </c>
       <c r="O535" t="n">
-        <v>357112.3072243392</v>
+        <v>317433.1540645152</v>
       </c>
       <c r="P535" t="n">
         <v>4900</v>
       </c>
       <c r="Q535" t="n">
-        <v>529200</v>
+        <v>470400</v>
       </c>
     </row>
     <row r="536">
@@ -24377,22 +24377,22 @@
         <v>0</v>
       </c>
       <c r="L536" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M536" t="n">
-        <v>565</v>
+        <v>559</v>
       </c>
       <c r="N536" t="n">
-        <v>2122.1640959855</v>
+        <v>2126.0638621746</v>
       </c>
       <c r="O536" t="n">
-        <v>1199022.714231808</v>
+        <v>1188469.698955602</v>
       </c>
       <c r="P536" t="n">
         <v>2900</v>
       </c>
       <c r="Q536" t="n">
-        <v>1638500</v>
+        <v>1621100</v>
       </c>
     </row>
     <row r="537">
@@ -24423,22 +24423,22 @@
         <v>0</v>
       </c>
       <c r="L537" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M537" t="n">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="N537" t="n">
-        <v>2108.7899091941</v>
+        <v>2108.7899828473</v>
       </c>
       <c r="O537" t="n">
-        <v>660051.2415777532</v>
+        <v>647398.5247341212</v>
       </c>
       <c r="P537" t="n">
         <v>2900</v>
       </c>
       <c r="Q537" t="n">
-        <v>907700</v>
+        <v>890300</v>
       </c>
     </row>
     <row r="538">
@@ -24469,22 +24469,22 @@
         <v>0</v>
       </c>
       <c r="L538" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M538" t="n">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="N538" t="n">
-        <v>2056.083871734</v>
+        <v>2059.7554464286</v>
       </c>
       <c r="O538" t="n">
-        <v>840938.3035392059</v>
+        <v>830081.4449107258</v>
       </c>
       <c r="P538" t="n">
         <v>2900</v>
       </c>
       <c r="Q538" t="n">
-        <v>1186100</v>
+        <v>1168700</v>
       </c>
     </row>
     <row r="539">
@@ -24515,22 +24515,22 @@
         <v>0</v>
       </c>
       <c r="L539" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M539" t="n">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="N539" t="n">
-        <v>3224.5680666967</v>
+        <v>3224.5682755432</v>
       </c>
       <c r="O539" t="n">
-        <v>1180191.912410992</v>
+        <v>1160844.579195552</v>
       </c>
       <c r="P539" t="n">
         <v>4500</v>
       </c>
       <c r="Q539" t="n">
-        <v>1647000</v>
+        <v>1620000</v>
       </c>
     </row>
     <row r="540">
@@ -24561,22 +24561,22 @@
         <v>0</v>
       </c>
       <c r="L540" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M540" t="n">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="N540" t="n">
-        <v>1655.9312964128</v>
+        <v>1657.5320592975</v>
       </c>
       <c r="O540" t="n">
-        <v>496779.38892384</v>
+        <v>492287.0216113575</v>
       </c>
       <c r="P540" t="n">
         <v>2500</v>
       </c>
       <c r="Q540" t="n">
-        <v>750000</v>
+        <v>742500</v>
       </c>
     </row>
     <row r="541">
@@ -24751,10 +24751,10 @@
         <v>262</v>
       </c>
       <c r="N544" t="n">
-        <v>1592.2752659892</v>
+        <v>1592.2754925187</v>
       </c>
       <c r="O544" t="n">
-        <v>417176.1196891704</v>
+        <v>417176.1790398994</v>
       </c>
       <c r="P544" t="n">
         <v>2500</v>
@@ -24789,22 +24789,22 @@
         <v>0</v>
       </c>
       <c r="L545" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M545" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N545" t="n">
-        <v>5347.73</v>
+        <v>5393.6332618026</v>
       </c>
       <c r="O545" t="n">
-        <v>74868.22</v>
+        <v>64723.5991416312</v>
       </c>
       <c r="P545" t="n">
         <v>9500</v>
       </c>
       <c r="Q545" t="n">
-        <v>133000</v>
+        <v>114000</v>
       </c>
     </row>
     <row r="546">
@@ -24835,22 +24835,22 @@
         <v>0</v>
       </c>
       <c r="L546" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M546" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N546" t="n">
-        <v>1906.1864705882</v>
+        <v>1906.1862686567</v>
       </c>
       <c r="O546" t="n">
-        <v>15249.4917647056</v>
+        <v>0</v>
       </c>
       <c r="P546" t="n">
         <v>2900</v>
       </c>
       <c r="Q546" t="n">
-        <v>23200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="547">
@@ -24887,10 +24887,10 @@
         <v>121</v>
       </c>
       <c r="N547" t="n">
-        <v>1668.6165143824</v>
+        <v>1668.6186615679</v>
       </c>
       <c r="O547" t="n">
-        <v>201902.5982402704</v>
+        <v>201902.8580497159</v>
       </c>
       <c r="P547" t="n">
         <v>2500</v>
@@ -24933,10 +24933,10 @@
         <v>54</v>
       </c>
       <c r="N548" t="n">
-        <v>2546.9851535836</v>
+        <v>2546.9851286449</v>
       </c>
       <c r="O548" t="n">
-        <v>137537.1982935144</v>
+        <v>137537.1969468246</v>
       </c>
       <c r="P548" t="n">
         <v>3900</v>
@@ -24979,10 +24979,10 @@
         <v>996</v>
       </c>
       <c r="N549" t="n">
-        <v>1259.2744247206</v>
+        <v>1259.2744276316</v>
       </c>
       <c r="O549" t="n">
-        <v>1254237.327021718</v>
+        <v>1254237.329921074</v>
       </c>
       <c r="P549" t="n">
         <v>1900</v>
@@ -25065,22 +25065,22 @@
         <v>0</v>
       </c>
       <c r="L551" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M551" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N551" t="n">
-        <v>2944</v>
+        <v>2991.7405405405</v>
       </c>
       <c r="O551" t="n">
-        <v>8832</v>
+        <v>0</v>
       </c>
       <c r="P551" t="n">
         <v>4900</v>
       </c>
       <c r="Q551" t="n">
-        <v>14700</v>
+        <v>0</v>
       </c>
     </row>
     <row r="552">
@@ -25106,22 +25106,22 @@
         <v>0</v>
       </c>
       <c r="L552" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M552" t="n">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="N552" t="n">
-        <v>2842.2737735849</v>
+        <v>2851.2399369085</v>
       </c>
       <c r="O552" t="n">
-        <v>648038.4203773572</v>
+        <v>644380.225741321</v>
       </c>
       <c r="P552" t="n">
         <v>4900</v>
       </c>
       <c r="Q552" t="n">
-        <v>1117200</v>
+        <v>1107400</v>
       </c>
     </row>
     <row r="553">
@@ -25198,22 +25198,22 @@
         <v>0</v>
       </c>
       <c r="L554" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M554" t="n">
-        <v>604</v>
+        <v>556</v>
       </c>
       <c r="N554" t="n">
-        <v>1801</v>
+        <v>1803.2544202785</v>
       </c>
       <c r="O554" t="n">
-        <v>1087804</v>
+        <v>1002609.457674846</v>
       </c>
       <c r="P554" t="n">
         <v>2900</v>
       </c>
       <c r="Q554" t="n">
-        <v>1751600</v>
+        <v>1612400</v>
       </c>
     </row>
     <row r="555">
@@ -25242,22 +25242,22 @@
         <v>0</v>
       </c>
       <c r="L555" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M555" t="n">
-        <v>318</v>
+        <v>270</v>
       </c>
       <c r="N555" t="n">
-        <v>692.15206356312</v>
+        <v>692.15208975521</v>
       </c>
       <c r="O555" t="n">
-        <v>220104.3562130722</v>
+        <v>186881.0642339067</v>
       </c>
       <c r="P555" t="n">
         <v>1200</v>
       </c>
       <c r="Q555" t="n">
-        <v>381600</v>
+        <v>324000</v>
       </c>
     </row>
     <row r="556">
@@ -25571,22 +25571,22 @@
         <v>0</v>
       </c>
       <c r="L562" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M562" t="n">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="N562" t="n">
-        <v>2857.22</v>
+        <v>2865.3179310345</v>
       </c>
       <c r="O562" t="n">
-        <v>420011.34</v>
+        <v>404009.8282758645</v>
       </c>
       <c r="P562" t="n">
         <v>4900</v>
       </c>
       <c r="Q562" t="n">
-        <v>720300</v>
+        <v>690900</v>
       </c>
     </row>
     <row r="563">
@@ -25620,22 +25620,22 @@
         <v>0</v>
       </c>
       <c r="L563" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M563" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="N563" t="n">
-        <v>8945.379999999999</v>
+        <v>8947.9898847557</v>
       </c>
       <c r="O563" t="n">
-        <v>1198680.92</v>
+        <v>1181134.664787752</v>
       </c>
       <c r="P563" t="n">
         <v>14900</v>
       </c>
       <c r="Q563" t="n">
-        <v>1996600</v>
+        <v>1966800</v>
       </c>
     </row>
     <row r="564">
@@ -25868,10 +25868,10 @@
         <v>273</v>
       </c>
       <c r="N568" t="n">
-        <v>1530.4499204138</v>
+        <v>1530.4499206034</v>
       </c>
       <c r="O568" t="n">
-        <v>417812.8282729674</v>
+        <v>417812.8283247282</v>
       </c>
       <c r="P568" t="n">
         <v>2600</v>
@@ -26279,22 +26279,22 @@
         <v>0</v>
       </c>
       <c r="L577" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M577" t="n">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="N577" t="n">
-        <v>6898.4</v>
+        <v>6979.7970501475</v>
       </c>
       <c r="O577" t="n">
-        <v>786417.6</v>
+        <v>767777.675516225</v>
       </c>
       <c r="P577" t="n">
         <v>12900</v>
       </c>
       <c r="Q577" t="n">
-        <v>1470600</v>
+        <v>1419000</v>
       </c>
     </row>
     <row r="578">
@@ -26424,10 +26424,10 @@
         <v>191</v>
       </c>
       <c r="N580" t="n">
-        <v>1690.8700089286</v>
+        <v>1690.8700089526</v>
       </c>
       <c r="O580" t="n">
-        <v>322956.1717053626</v>
+        <v>322956.1717099466</v>
       </c>
       <c r="P580" t="n">
         <v>3000</v>
@@ -27201,22 +27201,22 @@
         <v>0</v>
       </c>
       <c r="L597" t="n">
-        <v>0</v>
+        <v>243</v>
       </c>
       <c r="M597" t="n">
-        <v>2749</v>
+        <v>2506</v>
       </c>
       <c r="N597" t="n">
-        <v>517.2878865955601</v>
+        <v>523.15541944326</v>
       </c>
       <c r="O597" t="n">
-        <v>1422024.400251195</v>
+        <v>1311027.48112481</v>
       </c>
       <c r="P597" t="n">
         <v>900</v>
       </c>
       <c r="Q597" t="n">
-        <v>2474100</v>
+        <v>2255400</v>
       </c>
     </row>
     <row r="598">
@@ -27438,10 +27438,10 @@
         <v>404</v>
       </c>
       <c r="N602" t="n">
-        <v>3110.8429819337</v>
+        <v>3110.8429525518</v>
       </c>
       <c r="O602" t="n">
-        <v>1256780.564701215</v>
+        <v>1256780.552830927</v>
       </c>
       <c r="P602" t="n">
         <v>4500</v>
@@ -27476,22 +27476,22 @@
         <v>0</v>
       </c>
       <c r="L603" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M603" t="n">
-        <v>1067</v>
+        <v>947</v>
       </c>
       <c r="N603" t="n">
-        <v>703.79538564105</v>
+        <v>703.79534416571</v>
       </c>
       <c r="O603" t="n">
-        <v>750949.6764790004</v>
+        <v>666494.1909249274</v>
       </c>
       <c r="P603" t="n">
         <v>900</v>
       </c>
       <c r="Q603" t="n">
-        <v>960300</v>
+        <v>852300</v>
       </c>
     </row>
     <row r="604">
@@ -27810,22 +27810,22 @@
         <v>0</v>
       </c>
       <c r="L610" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M610" t="n">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="N610" t="n">
-        <v>1595.5190941049</v>
+        <v>1595.5190882035</v>
       </c>
       <c r="O610" t="n">
-        <v>673309.0577122677</v>
+        <v>670118.01704547</v>
       </c>
       <c r="P610" t="n">
         <v>2500</v>
       </c>
       <c r="Q610" t="n">
-        <v>1055000</v>
+        <v>1050000</v>
       </c>
     </row>
     <row r="611">
@@ -29688,22 +29688,22 @@
         <v>0</v>
       </c>
       <c r="L649" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M649" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N649" t="n">
-        <v>13623.91</v>
+        <v>14147.906538462</v>
       </c>
       <c r="O649" t="n">
-        <v>163486.92</v>
+        <v>155626.971923082</v>
       </c>
       <c r="P649" t="n">
         <v>26900</v>
       </c>
       <c r="Q649" t="n">
-        <v>322800</v>
+        <v>295900</v>
       </c>
     </row>
     <row r="650">
@@ -30457,22 +30457,22 @@
         <v>0</v>
       </c>
       <c r="L665" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M665" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="N665" t="n">
-        <v>3499.72</v>
+        <v>3516.3655172414</v>
       </c>
       <c r="O665" t="n">
-        <v>69994.39999999999</v>
+        <v>56261.8482758624</v>
       </c>
       <c r="P665" t="n">
         <v>6900</v>
       </c>
       <c r="Q665" t="n">
-        <v>138000</v>
+        <v>110400</v>
       </c>
     </row>
     <row r="666">
@@ -30506,22 +30506,22 @@
         <v>0</v>
       </c>
       <c r="L666" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M666" t="n">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="N666" t="n">
-        <v>5347.88</v>
+        <v>5377.3043741403</v>
       </c>
       <c r="O666" t="n">
-        <v>700572.28</v>
+        <v>682917.655515818</v>
       </c>
       <c r="P666" t="n">
         <v>7900</v>
       </c>
       <c r="Q666" t="n">
-        <v>1034900</v>
+        <v>1003300</v>
       </c>
     </row>
     <row r="667">
@@ -30555,22 +30555,22 @@
         <v>0</v>
       </c>
       <c r="L667" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M667" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="N667" t="n">
-        <v>4578.04</v>
+        <v>4597.9229098806</v>
       </c>
       <c r="O667" t="n">
-        <v>379977.32</v>
+        <v>363235.9098805674</v>
       </c>
       <c r="P667" t="n">
         <v>7500</v>
       </c>
       <c r="Q667" t="n">
-        <v>622500</v>
+        <v>592500</v>
       </c>
     </row>
     <row r="668">
@@ -31023,22 +31023,22 @@
         <v>0</v>
       </c>
       <c r="L677" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M677" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="N677" t="n">
-        <v>10737.526666667</v>
+        <v>11369.145882353</v>
       </c>
       <c r="O677" t="n">
-        <v>128850.320000004</v>
+        <v>102322.312941177</v>
       </c>
       <c r="P677" t="n">
         <v>18900</v>
       </c>
       <c r="Q677" t="n">
-        <v>226800</v>
+        <v>170100</v>
       </c>
     </row>
     <row r="678">
@@ -31550,22 +31550,22 @@
         <v>0</v>
       </c>
       <c r="L688" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M688" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N688" t="n">
-        <v>6669.55</v>
+        <v>9170.63125</v>
       </c>
       <c r="O688" t="n">
-        <v>46686.85</v>
+        <v>36682.525</v>
       </c>
       <c r="P688" t="n">
         <v>25500</v>
       </c>
       <c r="Q688" t="n">
-        <v>178500</v>
+        <v>102000</v>
       </c>
     </row>
     <row r="689">
@@ -32122,22 +32122,22 @@
         <v>0</v>
       </c>
       <c r="L700" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M700" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="N700" t="n">
         <v>24338.47</v>
       </c>
       <c r="O700" t="n">
-        <v>681477.16</v>
+        <v>608461.75</v>
       </c>
       <c r="P700" t="n">
         <v>27900</v>
       </c>
       <c r="Q700" t="n">
-        <v>781200</v>
+        <v>697500</v>
       </c>
     </row>
     <row r="701">
@@ -32740,22 +32740,22 @@
         <v>0</v>
       </c>
       <c r="L713" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M713" t="n">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="N713" t="n">
-        <v>2000</v>
+        <v>2075.1879699248</v>
       </c>
       <c r="O713" t="n">
-        <v>212000</v>
+        <v>188842.1052631568</v>
       </c>
       <c r="P713" t="n">
         <v>4100</v>
       </c>
       <c r="Q713" t="n">
-        <v>434600</v>
+        <v>373100</v>
       </c>
     </row>
     <row r="714">
@@ -33250,22 +33250,22 @@
         <v>0</v>
       </c>
       <c r="L724" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M724" t="n">
-        <v>171</v>
+        <v>121</v>
       </c>
       <c r="N724" t="n">
-        <v>3181.9</v>
+        <v>3209.0377398721</v>
       </c>
       <c r="O724" t="n">
-        <v>544104.9</v>
+        <v>388293.5665245241</v>
       </c>
       <c r="P724" t="n">
         <v>5100</v>
       </c>
       <c r="Q724" t="n">
-        <v>872100</v>
+        <v>617100</v>
       </c>
     </row>
     <row r="725">
@@ -33297,10 +33297,10 @@
         <v>10</v>
       </c>
       <c r="N725" t="n">
-        <v>1213.6821442495</v>
+        <v>1213.6821194605</v>
       </c>
       <c r="O725" t="n">
-        <v>12136.821442495</v>
+        <v>12136.821194605</v>
       </c>
       <c r="P725" t="n">
         <v>1500</v>
@@ -33381,22 +33381,22 @@
         <v>0</v>
       </c>
       <c r="L727" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M727" t="n">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="N727" t="n">
-        <v>5077</v>
+        <v>5337.8047945205</v>
       </c>
       <c r="O727" t="n">
-        <v>781858</v>
+        <v>741954.8664383495</v>
       </c>
       <c r="P727" t="n">
         <v>8500</v>
       </c>
       <c r="Q727" t="n">
-        <v>1309000</v>
+        <v>1181500</v>
       </c>
     </row>
     <row r="728">
@@ -35221,22 +35221,22 @@
         <v>0</v>
       </c>
       <c r="L767" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M767" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="N767" t="n">
-        <v>1129.14</v>
+        <v>1151.172</v>
       </c>
       <c r="O767" t="n">
-        <v>19195.38</v>
+        <v>14965.236</v>
       </c>
       <c r="P767" t="n">
         <v>6900</v>
       </c>
       <c r="Q767" t="n">
-        <v>117300</v>
+        <v>89700</v>
       </c>
     </row>
     <row r="768">

--- a/bodegas/LJ-05.xlsx
+++ b/bodegas/LJ-05.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-14</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-15</t>
         </is>
       </c>
     </row>
@@ -2314,13 +2314,13 @@
         </is>
       </c>
       <c r="J47" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
         <v>4</v>
@@ -3993,10 +3993,10 @@
         </is>
       </c>
       <c r="J85" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K85" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L85" t="n">
         <v>0</v>
@@ -4149,13 +4149,13 @@
         </is>
       </c>
       <c r="J89" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
       </c>
       <c r="L89" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
         <v>6</v>
@@ -6377,13 +6377,13 @@
         </is>
       </c>
       <c r="J140" t="n">
-        <v>1367</v>
+        <v>1365</v>
       </c>
       <c r="K140" t="n">
         <v>0</v>
       </c>
       <c r="L140" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M140" t="n">
         <v>1365</v>
@@ -6464,13 +6464,13 @@
         </is>
       </c>
       <c r="J142" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="K142" t="n">
         <v>0</v>
       </c>
       <c r="L142" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M142" t="n">
         <v>30</v>
@@ -7583,13 +7583,13 @@
         </is>
       </c>
       <c r="J167" t="n">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="K167" t="n">
         <v>0</v>
       </c>
       <c r="L167" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M167" t="n">
         <v>78</v>
@@ -8269,13 +8269,13 @@
         </is>
       </c>
       <c r="J182" t="n">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="K182" t="n">
         <v>0</v>
       </c>
       <c r="L182" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M182" t="n">
         <v>155</v>
@@ -11126,13 +11126,13 @@
         </is>
       </c>
       <c r="J245" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="K245" t="n">
         <v>0</v>
       </c>
       <c r="L245" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M245" t="n">
         <v>34</v>
@@ -11172,13 +11172,13 @@
         </is>
       </c>
       <c r="J246" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="K246" t="n">
         <v>0</v>
       </c>
       <c r="L246" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M246" t="n">
         <v>96</v>
@@ -12878,13 +12878,13 @@
         </is>
       </c>
       <c r="J285" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K285" t="n">
         <v>0</v>
       </c>
       <c r="L285" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M285" t="n">
         <v>7</v>
@@ -14654,13 +14654,13 @@
         </is>
       </c>
       <c r="J325" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K325" t="n">
         <v>0</v>
       </c>
       <c r="L325" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M325" t="n">
         <v>11</v>
@@ -16630,13 +16630,13 @@
         </is>
       </c>
       <c r="J368" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K368" t="n">
         <v>0</v>
       </c>
       <c r="L368" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M368" t="n">
         <v>4</v>
@@ -20008,13 +20008,13 @@
         </is>
       </c>
       <c r="J441" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K441" t="n">
         <v>0</v>
       </c>
       <c r="L441" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M441" t="n">
         <v>6</v>
@@ -20325,13 +20325,13 @@
         </is>
       </c>
       <c r="J448" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K448" t="n">
         <v>0</v>
       </c>
       <c r="L448" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M448" t="n">
         <v>22</v>
@@ -20734,13 +20734,13 @@
         </is>
       </c>
       <c r="J457" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K457" t="n">
         <v>0</v>
       </c>
       <c r="L457" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M457" t="n">
         <v>42</v>
@@ -21979,13 +21979,13 @@
         </is>
       </c>
       <c r="J484" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K484" t="n">
         <v>0</v>
       </c>
       <c r="L484" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M484" t="n">
         <v>25</v>
@@ -23495,13 +23495,13 @@
         </is>
       </c>
       <c r="J517" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K517" t="n">
         <v>0</v>
       </c>
       <c r="L517" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M517" t="n">
         <v>10</v>
@@ -23820,13 +23820,13 @@
         </is>
       </c>
       <c r="J524" t="n">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="K524" t="n">
         <v>0</v>
       </c>
       <c r="L524" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M524" t="n">
         <v>237</v>
@@ -24096,13 +24096,13 @@
         </is>
       </c>
       <c r="J530" t="n">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="K530" t="n">
         <v>0</v>
       </c>
       <c r="L530" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M530" t="n">
         <v>331</v>
@@ -24280,13 +24280,13 @@
         </is>
       </c>
       <c r="J534" t="n">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="K534" t="n">
         <v>0</v>
       </c>
       <c r="L534" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M534" t="n">
         <v>399</v>
@@ -24372,13 +24372,13 @@
         </is>
       </c>
       <c r="J536" t="n">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="K536" t="n">
         <v>0</v>
       </c>
       <c r="L536" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M536" t="n">
         <v>291</v>
@@ -24556,13 +24556,13 @@
         </is>
       </c>
       <c r="J540" t="n">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="K540" t="n">
         <v>0</v>
       </c>
       <c r="L540" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M540" t="n">
         <v>260</v>
@@ -24646,13 +24646,13 @@
         </is>
       </c>
       <c r="J542" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="K542" t="n">
         <v>0</v>
       </c>
       <c r="L542" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M542" t="n">
         <v>117</v>
@@ -24692,13 +24692,13 @@
         </is>
       </c>
       <c r="J543" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="K543" t="n">
         <v>0</v>
       </c>
       <c r="L543" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M543" t="n">
         <v>50</v>
@@ -24738,13 +24738,13 @@
         </is>
       </c>
       <c r="J544" t="n">
-        <v>996</v>
+        <v>990</v>
       </c>
       <c r="K544" t="n">
         <v>0</v>
       </c>
       <c r="L544" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M544" t="n">
         <v>990</v>
@@ -25339,13 +25339,13 @@
         </is>
       </c>
       <c r="J557" t="n">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="K557" t="n">
         <v>0</v>
       </c>
       <c r="L557" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="M557" t="n">
         <v>115</v>
@@ -26645,13 +26645,13 @@
         </is>
       </c>
       <c r="J585" t="n">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="K585" t="n">
         <v>0</v>
       </c>
       <c r="L585" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M585" t="n">
         <v>132</v>
@@ -26920,13 +26920,13 @@
         </is>
       </c>
       <c r="J591" t="n">
-        <v>2506</v>
+        <v>2456</v>
       </c>
       <c r="K591" t="n">
         <v>0</v>
       </c>
       <c r="L591" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M591" t="n">
         <v>2456</v>
@@ -27151,13 +27151,13 @@
         </is>
       </c>
       <c r="J596" t="n">
-        <v>404</v>
+        <v>384</v>
       </c>
       <c r="K596" t="n">
         <v>0</v>
       </c>
       <c r="L596" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M596" t="n">
         <v>384</v>
@@ -27483,13 +27483,13 @@
         </is>
       </c>
       <c r="J603" t="n">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="K603" t="n">
         <v>0</v>
       </c>
       <c r="L603" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M603" t="n">
         <v>416</v>
@@ -28451,13 +28451,13 @@
         </is>
       </c>
       <c r="J623" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K623" t="n">
         <v>0</v>
       </c>
       <c r="L623" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M623" t="n">
         <v>1</v>
@@ -29361,13 +29361,13 @@
         </is>
       </c>
       <c r="J642" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K642" t="n">
         <v>0</v>
       </c>
       <c r="L642" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M642" t="n">
         <v>10</v>
@@ -29888,13 +29888,13 @@
         </is>
       </c>
       <c r="J653" t="n">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="K653" t="n">
         <v>0</v>
       </c>
       <c r="L653" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M653" t="n">
         <v>266</v>
@@ -33146,10 +33146,10 @@
         </is>
       </c>
       <c r="J722" t="n">
-        <v>337</v>
+        <v>523</v>
       </c>
       <c r="K722" t="n">
-        <v>186</v>
+        <v>0</v>
       </c>
       <c r="L722" t="n">
         <v>0</v>
@@ -33325,13 +33325,13 @@
         </is>
       </c>
       <c r="J726" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K726" t="n">
         <v>0</v>
       </c>
       <c r="L726" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M726" t="n">
         <v>8</v>
@@ -33371,13 +33371,13 @@
         </is>
       </c>
       <c r="J727" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K727" t="n">
         <v>0</v>
       </c>
       <c r="L727" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M727" t="n">
         <v>20</v>
@@ -33417,13 +33417,13 @@
         </is>
       </c>
       <c r="J728" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K728" t="n">
         <v>0</v>
       </c>
       <c r="L728" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M728" t="n">
         <v>11</v>
@@ -33601,13 +33601,13 @@
         </is>
       </c>
       <c r="J732" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="K732" t="n">
         <v>0</v>
       </c>
       <c r="L732" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M732" t="n">
         <v>57</v>
@@ -33693,13 +33693,13 @@
         </is>
       </c>
       <c r="J734" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K734" t="n">
         <v>0</v>
       </c>
       <c r="L734" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M734" t="n">
         <v>20</v>
@@ -33739,13 +33739,13 @@
         </is>
       </c>
       <c r="J735" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K735" t="n">
         <v>0</v>
       </c>
       <c r="L735" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M735" t="n">
         <v>10</v>
@@ -33785,13 +33785,13 @@
         </is>
       </c>
       <c r="J736" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K736" t="n">
         <v>0</v>
       </c>
       <c r="L736" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M736" t="n">
         <v>10</v>
@@ -33831,13 +33831,13 @@
         </is>
       </c>
       <c r="J737" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="K737" t="n">
         <v>0</v>
       </c>
       <c r="L737" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M737" t="n">
         <v>9</v>
@@ -33877,13 +33877,13 @@
         </is>
       </c>
       <c r="J738" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K738" t="n">
         <v>0</v>
       </c>
       <c r="L738" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M738" t="n">
         <v>8</v>
@@ -34015,13 +34015,13 @@
         </is>
       </c>
       <c r="J741" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K741" t="n">
         <v>0</v>
       </c>
       <c r="L741" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M741" t="n">
         <v>10</v>
@@ -34199,13 +34199,13 @@
         </is>
       </c>
       <c r="J745" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K745" t="n">
         <v>0</v>
       </c>
       <c r="L745" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M745" t="n">
         <v>8</v>
@@ -34245,13 +34245,13 @@
         </is>
       </c>
       <c r="J746" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K746" t="n">
         <v>0</v>
       </c>
       <c r="L746" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M746" t="n">
         <v>2</v>
@@ -34291,13 +34291,13 @@
         </is>
       </c>
       <c r="J747" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K747" t="n">
         <v>0</v>
       </c>
       <c r="L747" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M747" t="n">
         <v>6</v>
@@ -34383,13 +34383,13 @@
         </is>
       </c>
       <c r="J749" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="K749" t="n">
         <v>0</v>
       </c>
       <c r="L749" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M749" t="n">
         <v>54</v>
@@ -34429,13 +34429,13 @@
         </is>
       </c>
       <c r="J750" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="K750" t="n">
         <v>0</v>
       </c>
       <c r="L750" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M750" t="n">
         <v>54</v>
@@ -34475,13 +34475,13 @@
         </is>
       </c>
       <c r="J751" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K751" t="n">
         <v>0</v>
       </c>
       <c r="L751" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M751" t="n">
         <v>3</v>
@@ -34567,13 +34567,13 @@
         </is>
       </c>
       <c r="J753" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="K753" t="n">
         <v>0</v>
       </c>
       <c r="L753" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M753" t="n">
         <v>21</v>
@@ -34613,13 +34613,13 @@
         </is>
       </c>
       <c r="J754" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K754" t="n">
         <v>0</v>
       </c>
       <c r="L754" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M754" t="n">
         <v>1</v>
@@ -34705,13 +34705,13 @@
         </is>
       </c>
       <c r="J756" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="K756" t="n">
         <v>0</v>
       </c>
       <c r="L756" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M756" t="n">
         <v>54</v>
@@ -34797,13 +34797,13 @@
         </is>
       </c>
       <c r="J758" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K758" t="n">
         <v>0</v>
       </c>
       <c r="L758" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M758" t="n">
         <v>4</v>
@@ -34843,13 +34843,13 @@
         </is>
       </c>
       <c r="J759" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K759" t="n">
         <v>0</v>
       </c>
       <c r="L759" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M759" t="n">
         <v>4</v>
@@ -34935,13 +34935,13 @@
         </is>
       </c>
       <c r="J761" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K761" t="n">
         <v>0</v>
       </c>
       <c r="L761" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M761" t="n">
         <v>1</v>
@@ -34981,13 +34981,13 @@
         </is>
       </c>
       <c r="J762" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K762" t="n">
         <v>0</v>
       </c>
       <c r="L762" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M762" t="n">
         <v>3</v>
@@ -35073,13 +35073,13 @@
         </is>
       </c>
       <c r="J764" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K764" t="n">
         <v>0</v>
       </c>
       <c r="L764" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M764" t="n">
         <v>22</v>

--- a/bodegas/LJ-05.xlsx
+++ b/bodegas/LJ-05.xlsx
@@ -987,10 +987,10 @@
         <v>128</v>
       </c>
       <c r="N14" t="n">
-        <v>3376.746498645</v>
+        <v>3376.7464976959</v>
       </c>
       <c r="O14" t="n">
-        <v>432223.55182656</v>
+        <v>432223.5517050752</v>
       </c>
       <c r="P14" t="n">
         <v>4500</v>
@@ -2326,10 +2326,10 @@
         <v>4</v>
       </c>
       <c r="N47" t="n">
-        <v>3910.6281963928</v>
+        <v>3910.6281927711</v>
       </c>
       <c r="O47" t="n">
-        <v>15642.5127855712</v>
+        <v>15642.5127710844</v>
       </c>
       <c r="P47" t="n">
         <v>9100</v>
@@ -2878,10 +2878,10 @@
         <v>6</v>
       </c>
       <c r="N59" t="n">
-        <v>28751.742258065</v>
+        <v>28751.742333333</v>
       </c>
       <c r="O59" t="n">
-        <v>172510.45354839</v>
+        <v>172510.453999998</v>
       </c>
       <c r="P59" t="n">
         <v>34800</v>
@@ -3380,22 +3380,22 @@
         <v>0</v>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M71" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N71" t="n">
-        <v>14708.815744681</v>
+        <v>14708.815698925</v>
       </c>
       <c r="O71" t="n">
-        <v>235341.051914896</v>
+        <v>220632.235483875</v>
       </c>
       <c r="P71" t="n">
         <v>16900</v>
       </c>
       <c r="Q71" t="n">
-        <v>270400</v>
+        <v>253500</v>
       </c>
     </row>
     <row r="72">
@@ -3952,22 +3952,22 @@
         <v>0</v>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N84" t="n">
-        <v>200072.2</v>
+        <v>200072.20007812</v>
       </c>
       <c r="O84" t="n">
-        <v>600216.6000000001</v>
+        <v>400144.40015624</v>
       </c>
       <c r="P84" t="n">
         <v>312000</v>
       </c>
       <c r="Q84" t="n">
-        <v>936000</v>
+        <v>624000</v>
       </c>
     </row>
     <row r="85">
@@ -4239,10 +4239,10 @@
         <v>4</v>
       </c>
       <c r="N91" t="n">
-        <v>61666.873994709</v>
+        <v>61666.874005305</v>
       </c>
       <c r="O91" t="n">
-        <v>246667.495978836</v>
+        <v>246667.49602122</v>
       </c>
       <c r="P91" t="n">
         <v>98900</v>
@@ -5017,22 +5017,22 @@
         <v>0</v>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M109" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N109" t="n">
         <v>16010.3</v>
       </c>
       <c r="O109" t="n">
-        <v>208133.9</v>
+        <v>192123.6</v>
       </c>
       <c r="P109" t="n">
         <v>30500</v>
       </c>
       <c r="Q109" t="n">
-        <v>396500</v>
+        <v>366000</v>
       </c>
     </row>
     <row r="110">
@@ -6125,10 +6125,10 @@
         <v>64</v>
       </c>
       <c r="N134" t="n">
-        <v>732.63413793103</v>
+        <v>732.63415224913</v>
       </c>
       <c r="O134" t="n">
-        <v>46888.58482758592</v>
+        <v>46888.58574394432</v>
       </c>
       <c r="P134" t="n">
         <v>6200</v>
@@ -6435,10 +6435,10 @@
         <v>1</v>
       </c>
       <c r="N141" t="n">
-        <v>4937.3101611722</v>
+        <v>4937.3101612903</v>
       </c>
       <c r="O141" t="n">
-        <v>4937.3101611722</v>
+        <v>4937.3101612903</v>
       </c>
       <c r="P141" t="n">
         <v>7500</v>
@@ -6652,22 +6652,22 @@
         <v>0</v>
       </c>
       <c r="L146" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M146" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="N146" t="n">
         <v>951</v>
       </c>
       <c r="O146" t="n">
-        <v>19971</v>
+        <v>15216</v>
       </c>
       <c r="P146" t="n">
         <v>1900</v>
       </c>
       <c r="Q146" t="n">
-        <v>39900</v>
+        <v>30400</v>
       </c>
     </row>
     <row r="147">
@@ -7365,10 +7365,10 @@
         <v>735</v>
       </c>
       <c r="N162" t="n">
-        <v>3158.860814779</v>
+        <v>3158.8608154486</v>
       </c>
       <c r="O162" t="n">
-        <v>2321762.698862565</v>
+        <v>2321762.699354721</v>
       </c>
       <c r="P162" t="n">
         <v>5600</v>
@@ -7543,22 +7543,22 @@
         <v>0</v>
       </c>
       <c r="L166" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M166" t="n">
-        <v>712</v>
+        <v>707</v>
       </c>
       <c r="N166" t="n">
-        <v>2694.8234565119</v>
+        <v>2694.8234059946</v>
       </c>
       <c r="O166" t="n">
-        <v>1918714.301036473</v>
+        <v>1905240.148038182</v>
       </c>
       <c r="P166" t="n">
         <v>4900</v>
       </c>
       <c r="Q166" t="n">
-        <v>3488800</v>
+        <v>3464300</v>
       </c>
     </row>
     <row r="167">
@@ -7589,22 +7589,22 @@
         <v>0</v>
       </c>
       <c r="L167" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M167" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="N167" t="n">
         <v>1026.13</v>
       </c>
       <c r="O167" t="n">
-        <v>80038.14000000001</v>
+        <v>77985.88</v>
       </c>
       <c r="P167" t="n">
         <v>1900</v>
       </c>
       <c r="Q167" t="n">
-        <v>148200</v>
+        <v>144400</v>
       </c>
     </row>
     <row r="168">
@@ -7871,10 +7871,10 @@
         <v>12</v>
       </c>
       <c r="N173" t="n">
-        <v>3795.7100070621</v>
+        <v>3795.7100070671</v>
       </c>
       <c r="O173" t="n">
-        <v>45548.5200847452</v>
+        <v>45548.5200848052</v>
       </c>
       <c r="P173" t="n">
         <v>6200</v>
@@ -8096,10 +8096,10 @@
         <v>56</v>
       </c>
       <c r="N178" t="n">
-        <v>4890.9300464306</v>
+        <v>4890.9300465929</v>
       </c>
       <c r="O178" t="n">
-        <v>273892.0826001136</v>
+        <v>273892.0826092024</v>
       </c>
       <c r="P178" t="n">
         <v>8200</v>
@@ -8275,22 +8275,22 @@
         <v>0</v>
       </c>
       <c r="L182" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M182" t="n">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="N182" t="n">
         <v>1203.38</v>
       </c>
       <c r="O182" t="n">
-        <v>186523.9</v>
+        <v>182913.76</v>
       </c>
       <c r="P182" t="n">
         <v>1900</v>
       </c>
       <c r="Q182" t="n">
-        <v>294500</v>
+        <v>288800</v>
       </c>
     </row>
     <row r="183">
@@ -8460,10 +8460,10 @@
         <v>82</v>
       </c>
       <c r="N186" t="n">
-        <v>2267.0481598668</v>
+        <v>2267.0481583333</v>
       </c>
       <c r="O186" t="n">
-        <v>185897.9491090776</v>
+        <v>185897.9489833306</v>
       </c>
       <c r="P186" t="n">
         <v>3900</v>
@@ -8821,10 +8821,10 @@
         <v>6</v>
       </c>
       <c r="N194" t="n">
-        <v>3594.2541391941</v>
+        <v>3594.254124847</v>
       </c>
       <c r="O194" t="n">
-        <v>21565.5248351646</v>
+        <v>21565.524749082</v>
       </c>
       <c r="P194" t="n">
         <v>6500</v>
@@ -9054,10 +9054,10 @@
         <v>33</v>
       </c>
       <c r="N199" t="n">
-        <v>14822.378862559</v>
+        <v>14822.378861885</v>
       </c>
       <c r="O199" t="n">
-        <v>489138.502464447</v>
+        <v>489138.502442205</v>
       </c>
       <c r="P199" t="n">
         <v>24900</v>
@@ -9637,22 +9637,22 @@
         <v>0</v>
       </c>
       <c r="L212" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M212" t="n">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="N212" t="n">
         <v>1441.01</v>
       </c>
       <c r="O212" t="n">
-        <v>768058.33</v>
+        <v>766617.3199999999</v>
       </c>
       <c r="P212" t="n">
         <v>2100</v>
       </c>
       <c r="Q212" t="n">
-        <v>1119300</v>
+        <v>1117200</v>
       </c>
     </row>
     <row r="213">
@@ -9771,22 +9771,22 @@
         <v>0</v>
       </c>
       <c r="L215" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M215" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="N215" t="n">
-        <v>3041.6600126502</v>
+        <v>3041.6600127551</v>
       </c>
       <c r="O215" t="n">
-        <v>404540.7816824766</v>
+        <v>401499.1216836732</v>
       </c>
       <c r="P215" t="n">
         <v>5500</v>
       </c>
       <c r="Q215" t="n">
-        <v>731500</v>
+        <v>726000</v>
       </c>
     </row>
     <row r="216">
@@ -9863,22 +9863,22 @@
         <v>0</v>
       </c>
       <c r="L217" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M217" t="n">
-        <v>482</v>
+        <v>464</v>
       </c>
       <c r="N217" t="n">
-        <v>1592.5674522293</v>
+        <v>1592.5674</v>
       </c>
       <c r="O217" t="n">
-        <v>767617.5119745226</v>
+        <v>738951.2736</v>
       </c>
       <c r="P217" t="n">
         <v>3900</v>
       </c>
       <c r="Q217" t="n">
-        <v>1879800</v>
+        <v>1809600</v>
       </c>
     </row>
     <row r="218">
@@ -10222,22 +10222,22 @@
         <v>0</v>
       </c>
       <c r="L225" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M225" t="n">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="N225" t="n">
         <v>1770.37</v>
       </c>
       <c r="O225" t="n">
-        <v>389481.4</v>
+        <v>384170.29</v>
       </c>
       <c r="P225" t="n">
         <v>3900</v>
       </c>
       <c r="Q225" t="n">
-        <v>858000</v>
+        <v>846300</v>
       </c>
     </row>
     <row r="226">
@@ -11083,22 +11083,22 @@
         <v>0</v>
       </c>
       <c r="L244" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M244" t="n">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="N244" t="n">
         <v>3751</v>
       </c>
       <c r="O244" t="n">
-        <v>2738230</v>
+        <v>2734479</v>
       </c>
       <c r="P244" t="n">
         <v>6400</v>
       </c>
       <c r="Q244" t="n">
-        <v>4672000</v>
+        <v>4665600</v>
       </c>
     </row>
     <row r="245">
@@ -11178,22 +11178,22 @@
         <v>0</v>
       </c>
       <c r="L246" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M246" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N246" t="n">
-        <v>1630.9231587595</v>
+        <v>1630.9231730968</v>
       </c>
       <c r="O246" t="n">
-        <v>156568.623240912</v>
+        <v>153306.7782710992</v>
       </c>
       <c r="P246" t="n">
         <v>2500</v>
       </c>
       <c r="Q246" t="n">
-        <v>240000</v>
+        <v>235000</v>
       </c>
     </row>
     <row r="247">
@@ -11230,10 +11230,10 @@
         <v>238</v>
       </c>
       <c r="N247" t="n">
-        <v>1550.1931558806</v>
+        <v>1550.193183768</v>
       </c>
       <c r="O247" t="n">
-        <v>368945.9710995828</v>
+        <v>368945.977736784</v>
       </c>
       <c r="P247" t="n">
         <v>2500</v>
@@ -11276,10 +11276,10 @@
         <v>663</v>
       </c>
       <c r="N248" t="n">
-        <v>2403.5103724115</v>
+        <v>2403.5104597508</v>
       </c>
       <c r="O248" t="n">
-        <v>1593527.376908825</v>
+        <v>1593527.43481478</v>
       </c>
       <c r="P248" t="n">
         <v>3500</v>
@@ -12416,10 +12416,10 @@
         <v>226</v>
       </c>
       <c r="N274" t="n">
-        <v>2029.8737073653</v>
+        <v>2029.8737091988</v>
       </c>
       <c r="O274" t="n">
-        <v>458751.4578645578</v>
+        <v>458751.4582789288</v>
       </c>
       <c r="P274" t="n">
         <v>3600</v>
@@ -12492,22 +12492,22 @@
         <v>0</v>
       </c>
       <c r="L276" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M276" t="n">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="N276" t="n">
         <v>2673</v>
       </c>
       <c r="O276" t="n">
-        <v>467775</v>
+        <v>462429</v>
       </c>
       <c r="P276" t="n">
         <v>2500</v>
       </c>
       <c r="Q276" t="n">
-        <v>437500</v>
+        <v>432500</v>
       </c>
     </row>
     <row r="277">
@@ -13023,10 +13023,10 @@
         <v>56</v>
       </c>
       <c r="N288" t="n">
-        <v>998.76125988546</v>
+        <v>998.76126091703</v>
       </c>
       <c r="O288" t="n">
-        <v>55930.63055358576</v>
+        <v>55930.63061135368</v>
       </c>
       <c r="P288" t="n">
         <v>1600</v>
@@ -13118,10 +13118,10 @@
         <v>109</v>
       </c>
       <c r="N290" t="n">
-        <v>4285.1952751817</v>
+        <v>4285.1952806653</v>
       </c>
       <c r="O290" t="n">
-        <v>467086.2849948053</v>
+        <v>467086.2855925177</v>
       </c>
       <c r="P290" t="n">
         <v>6900</v>
@@ -13458,22 +13458,22 @@
         <v>0</v>
       </c>
       <c r="L298" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M298" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="N298" t="n">
         <v>3591.13</v>
       </c>
       <c r="O298" t="n">
-        <v>208285.54</v>
+        <v>186738.76</v>
       </c>
       <c r="P298" t="n">
         <v>6300</v>
       </c>
       <c r="Q298" t="n">
-        <v>365400</v>
+        <v>327600</v>
       </c>
     </row>
     <row r="299">
@@ -13872,22 +13872,22 @@
         <v>0</v>
       </c>
       <c r="L307" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M307" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N307" t="n">
         <v>22730.48</v>
       </c>
       <c r="O307" t="n">
-        <v>363687.68</v>
+        <v>340957.2</v>
       </c>
       <c r="P307" t="n">
         <v>36900</v>
       </c>
       <c r="Q307" t="n">
-        <v>590400</v>
+        <v>553500</v>
       </c>
     </row>
     <row r="308">
@@ -14451,10 +14451,10 @@
         <v>94</v>
       </c>
       <c r="N320" t="n">
-        <v>1560.9993877551</v>
+        <v>1560.9994428152</v>
       </c>
       <c r="O320" t="n">
-        <v>146733.9424489794</v>
+        <v>146733.9476246288</v>
       </c>
       <c r="P320" t="n">
         <v>2900</v>
@@ -15025,10 +15025,10 @@
         <v>22</v>
       </c>
       <c r="N333" t="n">
-        <v>548.14725212465</v>
+        <v>548.14724692526</v>
       </c>
       <c r="O333" t="n">
-        <v>12059.2395467423</v>
+        <v>12059.23943235572</v>
       </c>
       <c r="P333" t="n">
         <v>2000</v>
@@ -15857,10 +15857,10 @@
         <v>93</v>
       </c>
       <c r="N351" t="n">
-        <v>5218.1705164319</v>
+        <v>5218.170521327</v>
       </c>
       <c r="O351" t="n">
-        <v>485289.8580281667</v>
+        <v>485289.858483411</v>
       </c>
       <c r="P351" t="n">
         <v>8500</v>
@@ -15903,10 +15903,10 @@
         <v>127</v>
       </c>
       <c r="N352" t="n">
-        <v>1595.0094492754</v>
+        <v>1595.0094476744</v>
       </c>
       <c r="O352" t="n">
-        <v>202566.2000579758</v>
+        <v>202566.1998546488</v>
       </c>
       <c r="P352" t="n">
         <v>2600</v>
@@ -15949,10 +15949,10 @@
         <v>8</v>
       </c>
       <c r="N353" t="n">
-        <v>3610.6500248756</v>
+        <v>3610.6500249688</v>
       </c>
       <c r="O353" t="n">
-        <v>28885.2001990048</v>
+        <v>28885.2001997504</v>
       </c>
       <c r="P353" t="n">
         <v>5800</v>
@@ -16179,10 +16179,10 @@
         <v>37</v>
       </c>
       <c r="N358" t="n">
-        <v>1664.3592041199</v>
+        <v>1664.3590294957</v>
       </c>
       <c r="O358" t="n">
-        <v>61581.29055243629</v>
+        <v>61581.2840913409</v>
       </c>
       <c r="P358" t="n">
         <v>2900</v>
@@ -19189,10 +19189,10 @@
         <v>59</v>
       </c>
       <c r="N423" t="n">
-        <v>2252.2965479115</v>
+        <v>2252.2965559656</v>
       </c>
       <c r="O423" t="n">
-        <v>132885.4963267785</v>
+        <v>132885.4968019704</v>
       </c>
       <c r="P423" t="n">
         <v>3900</v>
@@ -19922,22 +19922,22 @@
         <v>0</v>
       </c>
       <c r="L439" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M439" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N439" t="n">
-        <v>4907.8219448698</v>
+        <v>4907.8219751166</v>
       </c>
       <c r="O439" t="n">
-        <v>250298.9191883598</v>
+        <v>245391.09875583</v>
       </c>
       <c r="P439" t="n">
         <v>8200</v>
       </c>
       <c r="Q439" t="n">
-        <v>418200</v>
+        <v>410000</v>
       </c>
     </row>
     <row r="440">
@@ -21568,22 +21568,22 @@
         <v>0</v>
       </c>
       <c r="L475" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M475" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N475" t="n">
         <v>5682</v>
       </c>
       <c r="O475" t="n">
-        <v>522744</v>
+        <v>517062</v>
       </c>
       <c r="P475" t="n">
         <v>9900</v>
       </c>
       <c r="Q475" t="n">
-        <v>910800</v>
+        <v>900900</v>
       </c>
     </row>
     <row r="476">
@@ -23087,22 +23087,22 @@
         <v>0</v>
       </c>
       <c r="L508" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M508" t="n">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="N508" t="n">
         <v>1326</v>
       </c>
       <c r="O508" t="n">
-        <v>118014</v>
+        <v>112710</v>
       </c>
       <c r="P508" t="n">
         <v>2500</v>
       </c>
       <c r="Q508" t="n">
-        <v>222500</v>
+        <v>212500</v>
       </c>
     </row>
     <row r="509">
@@ -23832,10 +23832,10 @@
         <v>237</v>
       </c>
       <c r="N524" t="n">
-        <v>1516.0388110875</v>
+        <v>1516.0388102832</v>
       </c>
       <c r="O524" t="n">
-        <v>359301.1982277375</v>
+        <v>359301.1980371184</v>
       </c>
       <c r="P524" t="n">
         <v>2300</v>
@@ -23924,10 +23924,10 @@
         <v>450</v>
       </c>
       <c r="N526" t="n">
-        <v>2458.5133829585</v>
+        <v>2458.5133724619</v>
       </c>
       <c r="O526" t="n">
-        <v>1106331.022331325</v>
+        <v>1106331.017607855</v>
       </c>
       <c r="P526" t="n">
         <v>3500</v>
@@ -23970,10 +23970,10 @@
         <v>105</v>
       </c>
       <c r="N527" t="n">
-        <v>1907.3941918295</v>
+        <v>1907.3940437158</v>
       </c>
       <c r="O527" t="n">
-        <v>200276.3901420975</v>
+        <v>200276.374590159</v>
       </c>
       <c r="P527" t="n">
         <v>2500</v>
@@ -24016,10 +24016,10 @@
         <v>189</v>
       </c>
       <c r="N528" t="n">
-        <v>1771.0911342735</v>
+        <v>1771.0911179361</v>
       </c>
       <c r="O528" t="n">
-        <v>334736.2243776915</v>
+        <v>334736.2212899229</v>
       </c>
       <c r="P528" t="n">
         <v>2500</v>
@@ -24062,10 +24062,10 @@
         <v>465</v>
       </c>
       <c r="N529" t="n">
-        <v>2079.3841889251</v>
+        <v>2079.3841813438</v>
       </c>
       <c r="O529" t="n">
-        <v>966913.6478501714</v>
+        <v>966913.6443248669</v>
       </c>
       <c r="P529" t="n">
         <v>2900</v>
@@ -24108,10 +24108,10 @@
         <v>331</v>
       </c>
       <c r="N530" t="n">
-        <v>1803.0151566778</v>
+        <v>1803.0151724138</v>
       </c>
       <c r="O530" t="n">
-        <v>596798.0168603518</v>
+        <v>596798.0220689678</v>
       </c>
       <c r="P530" t="n">
         <v>2500</v>
@@ -24200,10 +24200,10 @@
         <v>559</v>
       </c>
       <c r="N532" t="n">
-        <v>2122.1640073529</v>
+        <v>2122.1640036787</v>
       </c>
       <c r="O532" t="n">
-        <v>1186289.680110271</v>
+        <v>1186289.678056393</v>
       </c>
       <c r="P532" t="n">
         <v>2900</v>
@@ -24240,22 +24240,22 @@
         <v>0</v>
       </c>
       <c r="L533" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M533" t="n">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="N533" t="n">
-        <v>2108.7899885584</v>
+        <v>2108.7900518135</v>
       </c>
       <c r="O533" t="n">
-        <v>647398.5264874288</v>
+        <v>643180.9658031176</v>
       </c>
       <c r="P533" t="n">
         <v>2900</v>
       </c>
       <c r="Q533" t="n">
-        <v>890300</v>
+        <v>884500</v>
       </c>
     </row>
     <row r="534">
@@ -24292,10 +24292,10 @@
         <v>399</v>
       </c>
       <c r="N534" t="n">
-        <v>2056.0838222089</v>
+        <v>2056.0837188071</v>
       </c>
       <c r="O534" t="n">
-        <v>820377.4450613512</v>
+        <v>820377.4038040329</v>
       </c>
       <c r="P534" t="n">
         <v>2900</v>
@@ -24338,10 +24338,10 @@
         <v>360</v>
       </c>
       <c r="N535" t="n">
-        <v>3224.568287037</v>
+        <v>3224.5683024119</v>
       </c>
       <c r="O535" t="n">
-        <v>1160844.58333332</v>
+        <v>1160844.588868284</v>
       </c>
       <c r="P535" t="n">
         <v>4500</v>
@@ -24384,10 +24384,10 @@
         <v>291</v>
       </c>
       <c r="N536" t="n">
-        <v>1655.931057226</v>
+        <v>1655.9310223953</v>
       </c>
       <c r="O536" t="n">
-        <v>481875.9376527659</v>
+        <v>481875.9275170323</v>
       </c>
       <c r="P536" t="n">
         <v>2500</v>
@@ -24516,22 +24516,22 @@
         <v>0</v>
       </c>
       <c r="L539" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M539" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="N539" t="n">
         <v>2454</v>
       </c>
       <c r="O539" t="n">
-        <v>142332</v>
+        <v>130062</v>
       </c>
       <c r="P539" t="n">
         <v>4200</v>
       </c>
       <c r="Q539" t="n">
-        <v>243600</v>
+        <v>222600</v>
       </c>
     </row>
     <row r="540">
@@ -24562,22 +24562,22 @@
         <v>0</v>
       </c>
       <c r="L540" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M540" t="n">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="N540" t="n">
-        <v>1592.2755269762</v>
+        <v>1592.2756948933</v>
       </c>
       <c r="O540" t="n">
-        <v>413991.637013812</v>
+        <v>410807.1292824714</v>
       </c>
       <c r="P540" t="n">
         <v>2500</v>
       </c>
       <c r="Q540" t="n">
-        <v>650000</v>
+        <v>645000</v>
       </c>
     </row>
     <row r="541">
@@ -24652,22 +24652,22 @@
         <v>0</v>
       </c>
       <c r="L542" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M542" t="n">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="N542" t="n">
-        <v>1668.6190998043</v>
+        <v>1668.6199591002</v>
       </c>
       <c r="O542" t="n">
-        <v>195228.4346771031</v>
+        <v>188554.0553783226</v>
       </c>
       <c r="P542" t="n">
         <v>2500</v>
       </c>
       <c r="Q542" t="n">
-        <v>292500</v>
+        <v>282500</v>
       </c>
     </row>
     <row r="543">
@@ -24698,22 +24698,22 @@
         <v>0</v>
       </c>
       <c r="L543" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M543" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="N543" t="n">
-        <v>2546.9850949914</v>
+        <v>2546.985</v>
       </c>
       <c r="O543" t="n">
-        <v>127349.25474957</v>
+        <v>119708.295</v>
       </c>
       <c r="P543" t="n">
         <v>3900</v>
       </c>
       <c r="Q543" t="n">
-        <v>195000</v>
+        <v>183300</v>
       </c>
     </row>
     <row r="544">
@@ -24750,10 +24750,10 @@
         <v>990</v>
       </c>
       <c r="N544" t="n">
-        <v>1259.2744422442</v>
+        <v>1259.2744638514</v>
       </c>
       <c r="O544" t="n">
-        <v>1246681.697821758</v>
+        <v>1246681.719212886</v>
       </c>
       <c r="P544" t="n">
         <v>1900</v>
@@ -24973,10 +24973,10 @@
         <v>270</v>
       </c>
       <c r="N549" t="n">
-        <v>692.15208975521</v>
+        <v>692.15209736124</v>
       </c>
       <c r="O549" t="n">
-        <v>186881.0642339067</v>
+        <v>186881.0662875348</v>
       </c>
       <c r="P549" t="n">
         <v>1200</v>
@@ -25345,22 +25345,22 @@
         <v>0</v>
       </c>
       <c r="L557" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M557" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="N557" t="n">
         <v>8945.379999999999</v>
       </c>
       <c r="O557" t="n">
-        <v>1028718.7</v>
+        <v>1019773.32</v>
       </c>
       <c r="P557" t="n">
         <v>14900</v>
       </c>
       <c r="Q557" t="n">
-        <v>1713500</v>
+        <v>1698600</v>
       </c>
     </row>
     <row r="558">
@@ -25725,22 +25725,22 @@
         <v>0</v>
       </c>
       <c r="L565" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M565" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N565" t="n">
         <v>1245.62</v>
       </c>
       <c r="O565" t="n">
-        <v>23666.78</v>
+        <v>22421.16</v>
       </c>
       <c r="P565" t="n">
         <v>4000</v>
       </c>
       <c r="Q565" t="n">
-        <v>76000</v>
+        <v>72000</v>
       </c>
     </row>
     <row r="566">
@@ -25964,10 +25964,10 @@
         <v>21</v>
       </c>
       <c r="N570" t="n">
-        <v>10732.241860465</v>
+        <v>10732.241904762</v>
       </c>
       <c r="O570" t="n">
-        <v>225377.079069765</v>
+        <v>225377.080000002</v>
       </c>
       <c r="P570" t="n">
         <v>25900</v>
@@ -26097,22 +26097,22 @@
         <v>0</v>
       </c>
       <c r="L573" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M573" t="n">
-        <v>1338</v>
+        <v>1331</v>
       </c>
       <c r="N573" t="n">
         <v>1828.64</v>
       </c>
       <c r="O573" t="n">
-        <v>2446720.32</v>
+        <v>2433919.84</v>
       </c>
       <c r="P573" t="n">
         <v>2000</v>
       </c>
       <c r="Q573" t="n">
-        <v>2676000</v>
+        <v>2662000</v>
       </c>
     </row>
     <row r="574">
@@ -26143,22 +26143,22 @@
         <v>0</v>
       </c>
       <c r="L574" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M574" t="n">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="N574" t="n">
-        <v>1690.8700089526</v>
+        <v>1690.8700089606</v>
       </c>
       <c r="O574" t="n">
-        <v>322956.1717099466</v>
+        <v>319574.4316935534</v>
       </c>
       <c r="P574" t="n">
         <v>3000</v>
       </c>
       <c r="Q574" t="n">
-        <v>573000</v>
+        <v>567000</v>
       </c>
     </row>
     <row r="575">
@@ -26834,10 +26834,10 @@
         <v>155</v>
       </c>
       <c r="N589" t="n">
-        <v>4032.3968542199</v>
+        <v>4032.3968461538</v>
       </c>
       <c r="O589" t="n">
-        <v>625021.5124040844</v>
+        <v>625021.5111538391</v>
       </c>
       <c r="P589" t="n">
         <v>4200</v>
@@ -26926,22 +26926,22 @@
         <v>0</v>
       </c>
       <c r="L591" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M591" t="n">
-        <v>2456</v>
+        <v>2443</v>
       </c>
       <c r="N591" t="n">
-        <v>517.28815469086</v>
+        <v>517.28824762181</v>
       </c>
       <c r="O591" t="n">
-        <v>1270459.707920752</v>
+        <v>1263735.188940082</v>
       </c>
       <c r="P591" t="n">
         <v>900</v>
       </c>
       <c r="Q591" t="n">
-        <v>2210400</v>
+        <v>2198700</v>
       </c>
     </row>
     <row r="592">
@@ -27157,22 +27157,22 @@
         <v>0</v>
       </c>
       <c r="L596" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M596" t="n">
-        <v>384</v>
+        <v>372</v>
       </c>
       <c r="N596" t="n">
-        <v>3110.8427709611</v>
+        <v>3110.8426932617</v>
       </c>
       <c r="O596" t="n">
-        <v>1194563.624049062</v>
+        <v>1157233.481893352</v>
       </c>
       <c r="P596" t="n">
         <v>4500</v>
       </c>
       <c r="Q596" t="n">
-        <v>1728000</v>
+        <v>1674000</v>
       </c>
     </row>
     <row r="597">
@@ -27201,22 +27201,22 @@
         <v>0</v>
       </c>
       <c r="L597" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M597" t="n">
-        <v>947</v>
+        <v>940</v>
       </c>
       <c r="N597" t="n">
-        <v>703.79533220158</v>
+        <v>703.7953201758</v>
       </c>
       <c r="O597" t="n">
-        <v>666494.1795948963</v>
+        <v>661567.600965252</v>
       </c>
       <c r="P597" t="n">
         <v>900</v>
       </c>
       <c r="Q597" t="n">
-        <v>852300</v>
+        <v>846000</v>
       </c>
     </row>
     <row r="598">
@@ -27489,22 +27489,22 @@
         <v>0</v>
       </c>
       <c r="L603" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M603" t="n">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="N603" t="n">
-        <v>1595.5155551576</v>
+        <v>1595.5155292429</v>
       </c>
       <c r="O603" t="n">
-        <v>663734.4709455615</v>
+        <v>655756.8825188319</v>
       </c>
       <c r="P603" t="n">
         <v>2500</v>
       </c>
       <c r="Q603" t="n">
-        <v>1040000</v>
+        <v>1027500</v>
       </c>
     </row>
     <row r="604">
@@ -28310,22 +28310,22 @@
         <v>0</v>
       </c>
       <c r="L620" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M620" t="n">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="N620" t="n">
         <v>1669.6</v>
       </c>
       <c r="O620" t="n">
-        <v>1005099.2</v>
+        <v>1000090.4</v>
       </c>
       <c r="P620" t="n">
         <v>2900</v>
       </c>
       <c r="Q620" t="n">
-        <v>1745800</v>
+        <v>1737100</v>
       </c>
     </row>
     <row r="621">
@@ -29894,22 +29894,22 @@
         <v>0</v>
       </c>
       <c r="L653" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M653" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="N653" t="n">
         <v>3000.33</v>
       </c>
       <c r="O653" t="n">
-        <v>798087.78</v>
+        <v>795087.45</v>
       </c>
       <c r="P653" t="n">
         <v>2900</v>
       </c>
       <c r="Q653" t="n">
-        <v>771400</v>
+        <v>768500</v>
       </c>
     </row>
     <row r="654">
@@ -29998,10 +29998,10 @@
         <v>45</v>
       </c>
       <c r="N655" t="n">
-        <v>3067.0905389222</v>
+        <v>3067.0905454545</v>
       </c>
       <c r="O655" t="n">
-        <v>138019.074251499</v>
+        <v>138019.0745454525</v>
       </c>
       <c r="P655" t="n">
         <v>7200</v>
@@ -30708,10 +30708,10 @@
         <v>9</v>
       </c>
       <c r="N670" t="n">
-        <v>10737.526470588</v>
+        <v>10737.5264</v>
       </c>
       <c r="O670" t="n">
-        <v>96637.738235292</v>
+        <v>96637.73760000001</v>
       </c>
       <c r="P670" t="n">
         <v>18900</v>
@@ -31761,10 +31761,10 @@
         <v>135</v>
       </c>
       <c r="N692" t="n">
-        <v>7046.939829932</v>
+        <v>7046.9398298958</v>
       </c>
       <c r="O692" t="n">
-        <v>951336.87704082</v>
+        <v>951336.8770359331</v>
       </c>
       <c r="P692" t="n">
         <v>9900</v>
@@ -32282,22 +32282,22 @@
         <v>0</v>
       </c>
       <c r="L703" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M703" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N703" t="n">
         <v>4581.84</v>
       </c>
       <c r="O703" t="n">
-        <v>68727.60000000001</v>
+        <v>59563.92</v>
       </c>
       <c r="P703" t="n">
         <v>7900</v>
       </c>
       <c r="Q703" t="n">
-        <v>118500</v>
+        <v>102700</v>
       </c>
     </row>
     <row r="704">
@@ -32929,22 +32929,22 @@
         <v>0</v>
       </c>
       <c r="L717" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M717" t="n">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="N717" t="n">
         <v>3181.9</v>
       </c>
       <c r="O717" t="n">
-        <v>385009.9</v>
+        <v>365918.5</v>
       </c>
       <c r="P717" t="n">
         <v>5100</v>
       </c>
       <c r="Q717" t="n">
-        <v>617100</v>
+        <v>586500</v>
       </c>
     </row>
     <row r="718">
@@ -33199,10 +33199,10 @@
         <v>12</v>
       </c>
       <c r="N723" t="n">
-        <v>4985.4046511628</v>
+        <v>4985.4047058824</v>
       </c>
       <c r="O723" t="n">
-        <v>59824.8558139536</v>
+        <v>59824.8564705888</v>
       </c>
       <c r="P723" t="n">
         <v>7900</v>
@@ -36608,10 +36608,10 @@
         <v>24</v>
       </c>
       <c r="N797" t="n">
-        <v>970.63153846154</v>
+        <v>970.63162162162</v>
       </c>
       <c r="O797" t="n">
-        <v>23295.15692307696</v>
+        <v>23295.15891891888</v>
       </c>
       <c r="P797" t="n">
         <v>7200</v>
@@ -36888,22 +36888,22 @@
         <v>0</v>
       </c>
       <c r="L803" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M803" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N803" t="n">
         <v>751.45</v>
       </c>
       <c r="O803" t="n">
-        <v>45838.45</v>
+        <v>45087</v>
       </c>
       <c r="P803" t="n">
         <v>2500</v>
       </c>
       <c r="Q803" t="n">
-        <v>152500</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="804">
@@ -37583,22 +37583,22 @@
         <v>0</v>
       </c>
       <c r="L818" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M818" t="n">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="N818" t="n">
         <v>4550</v>
       </c>
       <c r="O818" t="n">
-        <v>1428700</v>
+        <v>1424150</v>
       </c>
       <c r="P818" t="n">
         <v>5500</v>
       </c>
       <c r="Q818" t="n">
-        <v>1727000</v>
+        <v>1721500</v>
       </c>
     </row>
     <row r="819">
@@ -37635,10 +37635,10 @@
         <v>3</v>
       </c>
       <c r="N819" t="n">
-        <v>2402.6744966443</v>
+        <v>2402.6744594595</v>
       </c>
       <c r="O819" t="n">
-        <v>7208.023489932899</v>
+        <v>7208.023378378501</v>
       </c>
       <c r="P819" t="n">
         <v>3000</v>

--- a/bodegas/LJ-05.xlsx
+++ b/bodegas/LJ-05.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-15</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-16</t>
         </is>
       </c>
     </row>
@@ -3374,13 +3374,13 @@
         </is>
       </c>
       <c r="J71" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K71" t="n">
         <v>0</v>
       </c>
       <c r="L71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
         <v>15</v>
@@ -3946,13 +3946,13 @@
         </is>
       </c>
       <c r="J84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K84" t="n">
         <v>0</v>
       </c>
       <c r="L84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
         <v>2</v>
@@ -5011,13 +5011,13 @@
         </is>
       </c>
       <c r="J109" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K109" t="n">
         <v>0</v>
       </c>
       <c r="L109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M109" t="n">
         <v>12</v>
@@ -6646,13 +6646,13 @@
         </is>
       </c>
       <c r="J146" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="K146" t="n">
         <v>0</v>
       </c>
       <c r="L146" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M146" t="n">
         <v>16</v>
@@ -7537,13 +7537,13 @@
         </is>
       </c>
       <c r="J166" t="n">
-        <v>712</v>
+        <v>707</v>
       </c>
       <c r="K166" t="n">
         <v>0</v>
       </c>
       <c r="L166" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M166" t="n">
         <v>707</v>
@@ -7583,13 +7583,13 @@
         </is>
       </c>
       <c r="J167" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="K167" t="n">
         <v>0</v>
       </c>
       <c r="L167" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M167" t="n">
         <v>76</v>
@@ -8269,13 +8269,13 @@
         </is>
       </c>
       <c r="J182" t="n">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="K182" t="n">
         <v>0</v>
       </c>
       <c r="L182" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M182" t="n">
         <v>152</v>
@@ -9631,13 +9631,13 @@
         </is>
       </c>
       <c r="J212" t="n">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="K212" t="n">
         <v>0</v>
       </c>
       <c r="L212" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M212" t="n">
         <v>532</v>
@@ -9765,13 +9765,13 @@
         </is>
       </c>
       <c r="J215" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="K215" t="n">
         <v>0</v>
       </c>
       <c r="L215" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M215" t="n">
         <v>132</v>
@@ -9857,13 +9857,13 @@
         </is>
       </c>
       <c r="J217" t="n">
-        <v>482</v>
+        <v>464</v>
       </c>
       <c r="K217" t="n">
         <v>0</v>
       </c>
       <c r="L217" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="M217" t="n">
         <v>464</v>
@@ -10216,13 +10216,13 @@
         </is>
       </c>
       <c r="J225" t="n">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="K225" t="n">
         <v>0</v>
       </c>
       <c r="L225" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M225" t="n">
         <v>217</v>
@@ -11077,13 +11077,13 @@
         </is>
       </c>
       <c r="J244" t="n">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="K244" t="n">
         <v>0</v>
       </c>
       <c r="L244" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M244" t="n">
         <v>729</v>
@@ -11172,13 +11172,13 @@
         </is>
       </c>
       <c r="J246" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K246" t="n">
         <v>0</v>
       </c>
       <c r="L246" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M246" t="n">
         <v>94</v>
@@ -12486,13 +12486,13 @@
         </is>
       </c>
       <c r="J276" t="n">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="K276" t="n">
         <v>0</v>
       </c>
       <c r="L276" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M276" t="n">
         <v>173</v>
@@ -13452,13 +13452,13 @@
         </is>
       </c>
       <c r="J298" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="K298" t="n">
         <v>0</v>
       </c>
       <c r="L298" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M298" t="n">
         <v>52</v>
@@ -13866,13 +13866,13 @@
         </is>
       </c>
       <c r="J307" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K307" t="n">
         <v>0</v>
       </c>
       <c r="L307" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M307" t="n">
         <v>15</v>
@@ -19916,13 +19916,13 @@
         </is>
       </c>
       <c r="J439" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K439" t="n">
         <v>0</v>
       </c>
       <c r="L439" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M439" t="n">
         <v>50</v>
@@ -21562,13 +21562,13 @@
         </is>
       </c>
       <c r="J475" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K475" t="n">
         <v>0</v>
       </c>
       <c r="L475" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M475" t="n">
         <v>91</v>
@@ -23081,13 +23081,13 @@
         </is>
       </c>
       <c r="J508" t="n">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="K508" t="n">
         <v>0</v>
       </c>
       <c r="L508" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M508" t="n">
         <v>85</v>
@@ -24234,13 +24234,13 @@
         </is>
       </c>
       <c r="J533" t="n">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="K533" t="n">
         <v>0</v>
       </c>
       <c r="L533" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M533" t="n">
         <v>305</v>
@@ -24510,13 +24510,13 @@
         </is>
       </c>
       <c r="J539" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="K539" t="n">
         <v>0</v>
       </c>
       <c r="L539" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M539" t="n">
         <v>53</v>
@@ -24556,13 +24556,13 @@
         </is>
       </c>
       <c r="J540" t="n">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="K540" t="n">
         <v>0</v>
       </c>
       <c r="L540" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M540" t="n">
         <v>258</v>
@@ -24646,13 +24646,13 @@
         </is>
       </c>
       <c r="J542" t="n">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="K542" t="n">
         <v>0</v>
       </c>
       <c r="L542" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M542" t="n">
         <v>113</v>
@@ -24692,13 +24692,13 @@
         </is>
       </c>
       <c r="J543" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="K543" t="n">
         <v>0</v>
       </c>
       <c r="L543" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M543" t="n">
         <v>47</v>
@@ -25339,13 +25339,13 @@
         </is>
       </c>
       <c r="J557" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="K557" t="n">
         <v>0</v>
       </c>
       <c r="L557" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M557" t="n">
         <v>114</v>
@@ -25719,13 +25719,13 @@
         </is>
       </c>
       <c r="J565" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K565" t="n">
         <v>0</v>
       </c>
       <c r="L565" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M565" t="n">
         <v>18</v>
@@ -26091,13 +26091,13 @@
         </is>
       </c>
       <c r="J573" t="n">
-        <v>1338</v>
+        <v>1331</v>
       </c>
       <c r="K573" t="n">
         <v>0</v>
       </c>
       <c r="L573" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M573" t="n">
         <v>1331</v>
@@ -26137,13 +26137,13 @@
         </is>
       </c>
       <c r="J574" t="n">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="K574" t="n">
         <v>0</v>
       </c>
       <c r="L574" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M574" t="n">
         <v>189</v>
@@ -26920,13 +26920,13 @@
         </is>
       </c>
       <c r="J591" t="n">
-        <v>2456</v>
+        <v>2443</v>
       </c>
       <c r="K591" t="n">
         <v>0</v>
       </c>
       <c r="L591" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="M591" t="n">
         <v>2443</v>
@@ -27151,13 +27151,13 @@
         </is>
       </c>
       <c r="J596" t="n">
-        <v>384</v>
+        <v>372</v>
       </c>
       <c r="K596" t="n">
         <v>0</v>
       </c>
       <c r="L596" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M596" t="n">
         <v>372</v>
@@ -27195,13 +27195,13 @@
         </is>
       </c>
       <c r="J597" t="n">
-        <v>947</v>
+        <v>940</v>
       </c>
       <c r="K597" t="n">
         <v>0</v>
       </c>
       <c r="L597" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M597" t="n">
         <v>940</v>
@@ -27483,13 +27483,13 @@
         </is>
       </c>
       <c r="J603" t="n">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="K603" t="n">
         <v>0</v>
       </c>
       <c r="L603" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M603" t="n">
         <v>411</v>
@@ -28304,13 +28304,13 @@
         </is>
       </c>
       <c r="J620" t="n">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="K620" t="n">
         <v>0</v>
       </c>
       <c r="L620" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M620" t="n">
         <v>599</v>
@@ -29888,13 +29888,13 @@
         </is>
       </c>
       <c r="J653" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="K653" t="n">
         <v>0</v>
       </c>
       <c r="L653" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M653" t="n">
         <v>265</v>
@@ -32276,13 +32276,13 @@
         </is>
       </c>
       <c r="J703" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K703" t="n">
         <v>0</v>
       </c>
       <c r="L703" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M703" t="n">
         <v>13</v>
@@ -32923,13 +32923,13 @@
         </is>
       </c>
       <c r="J717" t="n">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="K717" t="n">
         <v>0</v>
       </c>
       <c r="L717" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M717" t="n">
         <v>115</v>
@@ -36882,13 +36882,13 @@
         </is>
       </c>
       <c r="J803" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K803" t="n">
         <v>0</v>
       </c>
       <c r="L803" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M803" t="n">
         <v>60</v>
@@ -37577,13 +37577,13 @@
         </is>
       </c>
       <c r="J818" t="n">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="K818" t="n">
         <v>0</v>
       </c>
       <c r="L818" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M818" t="n">
         <v>313</v>

--- a/bodegas/LJ-05.xlsx
+++ b/bodegas/LJ-05.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-16</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-17</t>
         </is>
       </c>
     </row>

--- a/bodegas/LJ-05.xlsx
+++ b/bodegas/LJ-05.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-17</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-18</t>
         </is>
       </c>
     </row>

--- a/bodegas/LJ-05.xlsx
+++ b/bodegas/LJ-05.xlsx
@@ -950,10 +950,10 @@
         <v>397</v>
       </c>
       <c r="N13" t="n">
-        <v>1811.3053012048</v>
+        <v>1811.3053333333</v>
       </c>
       <c r="O13" t="n">
-        <v>719088.2045783056</v>
+        <v>719088.2173333201</v>
       </c>
       <c r="P13" t="n">
         <v>2600</v>
@@ -1825,10 +1825,10 @@
         <v>19</v>
       </c>
       <c r="N35" t="n">
-        <v>3716.3301923077</v>
+        <v>3716.3301935484</v>
       </c>
       <c r="O35" t="n">
-        <v>70610.27365384631</v>
+        <v>70610.27367741959</v>
       </c>
       <c r="P35" t="n">
         <v>9500</v>
@@ -3951,22 +3951,22 @@
         <v>0</v>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M84" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N84" t="n">
-        <v>141416.88454545</v>
+        <v>141416.88456026</v>
       </c>
       <c r="O84" t="n">
-        <v>848501.3072727001</v>
+        <v>707084.4228013</v>
       </c>
       <c r="P84" t="n">
         <v>251900</v>
       </c>
       <c r="Q84" t="n">
-        <v>1511400</v>
+        <v>1259500</v>
       </c>
     </row>
     <row r="85">
@@ -4909,10 +4909,10 @@
         <v>41</v>
       </c>
       <c r="N106" t="n">
-        <v>580.36600536193</v>
+        <v>580.36599462366</v>
       </c>
       <c r="O106" t="n">
-        <v>23795.00621983913</v>
+        <v>23795.00577957006</v>
       </c>
       <c r="P106" t="n">
         <v>6800</v>
@@ -6425,22 +6425,22 @@
         <v>0</v>
       </c>
       <c r="L141" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M141" t="n">
-        <v>1325</v>
+        <v>1321</v>
       </c>
       <c r="N141" t="n">
         <v>1726.32</v>
       </c>
       <c r="O141" t="n">
-        <v>2287374</v>
+        <v>2280468.72</v>
       </c>
       <c r="P141" t="n">
         <v>1500</v>
       </c>
       <c r="Q141" t="n">
-        <v>1987500</v>
+        <v>1981500</v>
       </c>
     </row>
     <row r="142">
@@ -7407,10 +7407,10 @@
         <v>735</v>
       </c>
       <c r="N163" t="n">
-        <v>3158.8608230874</v>
+        <v>3158.86082365</v>
       </c>
       <c r="O163" t="n">
-        <v>2321762.704969239</v>
+        <v>2321762.70538275</v>
       </c>
       <c r="P163" t="n">
         <v>5600</v>
@@ -7591,10 +7591,10 @@
         <v>683</v>
       </c>
       <c r="N167" t="n">
-        <v>2694.8233333333</v>
+        <v>2694.8232839963</v>
       </c>
       <c r="O167" t="n">
-        <v>1840564.336666644</v>
+        <v>1840564.302969473</v>
       </c>
       <c r="P167" t="n">
         <v>4900</v>
@@ -7913,10 +7913,10 @@
         <v>12</v>
       </c>
       <c r="N174" t="n">
-        <v>3795.7100070822</v>
+        <v>3795.7100070872</v>
       </c>
       <c r="O174" t="n">
-        <v>45548.5200849864</v>
+        <v>45548.5200850464</v>
       </c>
       <c r="P174" t="n">
         <v>6200</v>
@@ -8138,10 +8138,10 @@
         <v>56</v>
       </c>
       <c r="N179" t="n">
-        <v>4890.9300467563</v>
+        <v>4890.9300468384</v>
       </c>
       <c r="O179" t="n">
-        <v>273892.0826183528</v>
+        <v>273892.0826229504</v>
       </c>
       <c r="P179" t="n">
         <v>8200</v>
@@ -8542,22 +8542,22 @@
         <v>0</v>
       </c>
       <c r="L188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M188" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N188" t="n">
         <v>7041</v>
       </c>
       <c r="O188" t="n">
-        <v>295722</v>
+        <v>288681</v>
       </c>
       <c r="P188" t="n">
         <v>11500</v>
       </c>
       <c r="Q188" t="n">
-        <v>483000</v>
+        <v>471500</v>
       </c>
     </row>
     <row r="189">
@@ -8952,22 +8952,22 @@
         <v>0</v>
       </c>
       <c r="L197" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M197" t="n">
-        <v>1875</v>
+        <v>1873</v>
       </c>
       <c r="N197" t="n">
         <v>489.88</v>
       </c>
       <c r="O197" t="n">
-        <v>918525</v>
+        <v>917545.24</v>
       </c>
       <c r="P197" t="n">
         <v>700</v>
       </c>
       <c r="Q197" t="n">
-        <v>1312500</v>
+        <v>1311100</v>
       </c>
     </row>
     <row r="198">
@@ -9096,10 +9096,10 @@
         <v>33</v>
       </c>
       <c r="N200" t="n">
-        <v>14822.378861885</v>
+        <v>14822.378858502</v>
       </c>
       <c r="O200" t="n">
-        <v>489138.502442205</v>
+        <v>489138.502330566</v>
       </c>
       <c r="P200" t="n">
         <v>24900</v>
@@ -9679,22 +9679,22 @@
         <v>0</v>
       </c>
       <c r="L213" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M213" t="n">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="N213" t="n">
         <v>1441.01</v>
       </c>
       <c r="O213" t="n">
-        <v>752207.22</v>
+        <v>747884.1899999999</v>
       </c>
       <c r="P213" t="n">
         <v>2100</v>
       </c>
       <c r="Q213" t="n">
-        <v>1096200</v>
+        <v>1089900</v>
       </c>
     </row>
     <row r="214">
@@ -9819,10 +9819,10 @@
         <v>122</v>
       </c>
       <c r="N216" t="n">
-        <v>3041.6600128617</v>
+        <v>3041.660012945</v>
       </c>
       <c r="O216" t="n">
-        <v>371082.5215691274</v>
+        <v>371082.52157929</v>
       </c>
       <c r="P216" t="n">
         <v>5500</v>
@@ -9905,22 +9905,22 @@
         <v>0</v>
       </c>
       <c r="L218" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M218" t="n">
-        <v>432</v>
+        <v>408</v>
       </c>
       <c r="N218" t="n">
-        <v>1592.5673455845</v>
+        <v>1592.5672645976</v>
       </c>
       <c r="O218" t="n">
-        <v>687989.093292504</v>
+        <v>649767.4439558208</v>
       </c>
       <c r="P218" t="n">
         <v>3900</v>
       </c>
       <c r="Q218" t="n">
-        <v>1684800</v>
+        <v>1591200</v>
       </c>
     </row>
     <row r="219">
@@ -10724,10 +10724,10 @@
         <v>130</v>
       </c>
       <c r="N236" t="n">
-        <v>2021.7211225106</v>
+        <v>2021.7211231884</v>
       </c>
       <c r="O236" t="n">
-        <v>262823.745926378</v>
+        <v>262823.746014492</v>
       </c>
       <c r="P236" t="n">
         <v>2400</v>
@@ -11125,22 +11125,22 @@
         <v>0</v>
       </c>
       <c r="L245" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M245" t="n">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N245" t="n">
         <v>3751</v>
       </c>
       <c r="O245" t="n">
-        <v>2704471</v>
+        <v>2700720</v>
       </c>
       <c r="P245" t="n">
         <v>6400</v>
       </c>
       <c r="Q245" t="n">
-        <v>4614400</v>
+        <v>4608000</v>
       </c>
     </row>
     <row r="246">
@@ -11226,10 +11226,10 @@
         <v>78</v>
       </c>
       <c r="N247" t="n">
-        <v>1630.9233118002</v>
+        <v>1630.9233376736</v>
       </c>
       <c r="O247" t="n">
-        <v>127212.0183204156</v>
+        <v>127212.0203385408</v>
       </c>
       <c r="P247" t="n">
         <v>2500</v>
@@ -11266,22 +11266,22 @@
         <v>0</v>
       </c>
       <c r="L248" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M248" t="n">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c r="N248" t="n">
-        <v>1550.1933219945</v>
+        <v>1550.1933547279</v>
       </c>
       <c r="O248" t="n">
-        <v>266633.251383054</v>
+        <v>241830.1633375524</v>
       </c>
       <c r="P248" t="n">
         <v>2500</v>
       </c>
       <c r="Q248" t="n">
-        <v>430000</v>
+        <v>390000</v>
       </c>
     </row>
     <row r="249">
@@ -11312,22 +11312,22 @@
         <v>0</v>
       </c>
       <c r="L249" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="M249" t="n">
-        <v>636</v>
+        <v>604</v>
       </c>
       <c r="N249" t="n">
-        <v>2403.5107961064</v>
+        <v>2403.5109560769</v>
       </c>
       <c r="O249" t="n">
-        <v>1528632.86632367</v>
+        <v>1451720.617470448</v>
       </c>
       <c r="P249" t="n">
         <v>3500</v>
       </c>
       <c r="Q249" t="n">
-        <v>2226000</v>
+        <v>2114000</v>
       </c>
     </row>
     <row r="250">
@@ -12411,22 +12411,22 @@
         <v>0</v>
       </c>
       <c r="L274" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M274" t="n">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="N274" t="n">
         <v>2517.22</v>
       </c>
       <c r="O274" t="n">
-        <v>594063.9199999999</v>
+        <v>563857.2799999999</v>
       </c>
       <c r="P274" t="n">
         <v>4200</v>
       </c>
       <c r="Q274" t="n">
-        <v>991200</v>
+        <v>940800</v>
       </c>
     </row>
     <row r="275">
@@ -12458,10 +12458,10 @@
         <v>226</v>
       </c>
       <c r="N275" t="n">
-        <v>2029.8737091988</v>
+        <v>2029.8737110341</v>
       </c>
       <c r="O275" t="n">
-        <v>458751.4582789288</v>
+        <v>458751.4586937066</v>
       </c>
       <c r="P275" t="n">
         <v>3600</v>
@@ -13546,22 +13546,22 @@
         <v>0</v>
       </c>
       <c r="L300" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M300" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N300" t="n">
         <v>11980</v>
       </c>
       <c r="O300" t="n">
-        <v>35940</v>
+        <v>23960</v>
       </c>
       <c r="P300" t="n">
         <v>19500</v>
       </c>
       <c r="Q300" t="n">
-        <v>58500</v>
+        <v>39000</v>
       </c>
     </row>
     <row r="301">
@@ -13592,22 +13592,22 @@
         <v>0</v>
       </c>
       <c r="L301" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M301" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="N301" t="n">
-        <v>11562.038526316</v>
+        <v>11562.038522427</v>
       </c>
       <c r="O301" t="n">
-        <v>427795.425473692</v>
+        <v>416233.386807372</v>
       </c>
       <c r="P301" t="n">
         <v>18500</v>
       </c>
       <c r="Q301" t="n">
-        <v>684500</v>
+        <v>666000</v>
       </c>
     </row>
     <row r="302">
@@ -14227,10 +14227,10 @@
         <v>137</v>
       </c>
       <c r="N315" t="n">
-        <v>1466.8807100592</v>
+        <v>1466.8807185629</v>
       </c>
       <c r="O315" t="n">
-        <v>200962.6572781104</v>
+        <v>200962.6584431173</v>
       </c>
       <c r="P315" t="n">
         <v>3400</v>
@@ -14493,10 +14493,10 @@
         <v>94</v>
       </c>
       <c r="N321" t="n">
-        <v>1560.9995548961</v>
+        <v>1560.9996939288</v>
       </c>
       <c r="O321" t="n">
-        <v>146733.9581602334</v>
+        <v>146733.9712293072</v>
       </c>
       <c r="P321" t="n">
         <v>2900</v>
@@ -15433,22 +15433,22 @@
         <v>0</v>
       </c>
       <c r="L342" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M342" t="n">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="N342" t="n">
         <v>7700</v>
       </c>
       <c r="O342" t="n">
-        <v>2025100</v>
+        <v>2002000</v>
       </c>
       <c r="P342" t="n">
         <v>13900</v>
       </c>
       <c r="Q342" t="n">
-        <v>3655700</v>
+        <v>3614000</v>
       </c>
     </row>
     <row r="343">
@@ -15525,22 +15525,22 @@
         <v>0</v>
       </c>
       <c r="L344" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M344" t="n">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="N344" t="n">
         <v>2634.61</v>
       </c>
       <c r="O344" t="n">
-        <v>403095.33</v>
+        <v>376749.23</v>
       </c>
       <c r="P344" t="n">
         <v>4200</v>
       </c>
       <c r="Q344" t="n">
-        <v>642600</v>
+        <v>600600</v>
       </c>
     </row>
     <row r="345">
@@ -15571,22 +15571,22 @@
         <v>0</v>
       </c>
       <c r="L345" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M345" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="N345" t="n">
-        <v>3113.8900265957</v>
+        <v>3113.890027137</v>
       </c>
       <c r="O345" t="n">
-        <v>255338.9821808474</v>
+        <v>224200.081953864</v>
       </c>
       <c r="P345" t="n">
         <v>5000</v>
       </c>
       <c r="Q345" t="n">
-        <v>410000</v>
+        <v>360000</v>
       </c>
     </row>
     <row r="346">
@@ -15663,22 +15663,22 @@
         <v>0</v>
       </c>
       <c r="L347" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M347" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="N347" t="n">
         <v>4690.64</v>
       </c>
       <c r="O347" t="n">
-        <v>117266</v>
+        <v>60978.32000000001</v>
       </c>
       <c r="P347" t="n">
         <v>7500</v>
       </c>
       <c r="Q347" t="n">
-        <v>187500</v>
+        <v>97500</v>
       </c>
     </row>
     <row r="348">
@@ -15755,22 +15755,22 @@
         <v>0</v>
       </c>
       <c r="L349" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M349" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="N349" t="n">
-        <v>4163.1601818182</v>
+        <v>4163.1601960784</v>
       </c>
       <c r="O349" t="n">
-        <v>66610.5629090912</v>
+        <v>33305.2815686272</v>
       </c>
       <c r="P349" t="n">
         <v>6700</v>
       </c>
       <c r="Q349" t="n">
-        <v>107200</v>
+        <v>53600</v>
       </c>
     </row>
     <row r="350">
@@ -15899,10 +15899,10 @@
         <v>93</v>
       </c>
       <c r="N352" t="n">
-        <v>5218.1705238095</v>
+        <v>5218.1705269461</v>
       </c>
       <c r="O352" t="n">
-        <v>485289.8587142835</v>
+        <v>485289.8590059873</v>
       </c>
       <c r="P352" t="n">
         <v>8500</v>
@@ -15945,10 +15945,10 @@
         <v>121</v>
       </c>
       <c r="N353" t="n">
-        <v>1595.0094378698</v>
+        <v>1595.0094189602</v>
       </c>
       <c r="O353" t="n">
-        <v>192996.1419822458</v>
+        <v>192996.1396941842</v>
       </c>
       <c r="P353" t="n">
         <v>2600</v>
@@ -15991,10 +15991,10 @@
         <v>6</v>
       </c>
       <c r="N354" t="n">
-        <v>3610.6500252207</v>
+        <v>3610.6500253807</v>
       </c>
       <c r="O354" t="n">
-        <v>21663.9001513242</v>
+        <v>21663.9001522842</v>
       </c>
       <c r="P354" t="n">
         <v>5800</v>
@@ -16077,22 +16077,22 @@
         <v>0</v>
       </c>
       <c r="L356" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M356" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="N356" t="n">
         <v>4227.77</v>
       </c>
       <c r="O356" t="n">
-        <v>224071.81</v>
+        <v>202932.96</v>
       </c>
       <c r="P356" t="n">
         <v>6900</v>
       </c>
       <c r="Q356" t="n">
-        <v>365700</v>
+        <v>331200</v>
       </c>
     </row>
     <row r="357">
@@ -16123,22 +16123,22 @@
         <v>0</v>
       </c>
       <c r="L357" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M357" t="n">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="N357" t="n">
         <v>3965.02</v>
       </c>
       <c r="O357" t="n">
-        <v>547172.76</v>
+        <v>539242.72</v>
       </c>
       <c r="P357" t="n">
         <v>6500</v>
       </c>
       <c r="Q357" t="n">
-        <v>897000</v>
+        <v>884000</v>
       </c>
     </row>
     <row r="358">
@@ -16221,10 +16221,10 @@
         <v>20</v>
       </c>
       <c r="N359" t="n">
-        <v>1664.3585273632</v>
+        <v>1664.3584236948</v>
       </c>
       <c r="O359" t="n">
-        <v>33287.170547264</v>
+        <v>33287.168473896</v>
       </c>
       <c r="P359" t="n">
         <v>2900</v>
@@ -16356,22 +16356,22 @@
         <v>0</v>
       </c>
       <c r="L362" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M362" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N362" t="n">
         <v>18536</v>
       </c>
       <c r="O362" t="n">
-        <v>278040</v>
+        <v>240968</v>
       </c>
       <c r="P362" t="n">
         <v>30900</v>
       </c>
       <c r="Q362" t="n">
-        <v>463500</v>
+        <v>401700</v>
       </c>
     </row>
     <row r="363">
@@ -16684,10 +16684,10 @@
         <v>4</v>
       </c>
       <c r="N369" t="n">
-        <v>23521.62453125</v>
+        <v>23521.624354839</v>
       </c>
       <c r="O369" t="n">
-        <v>94086.498125</v>
+        <v>94086.497419356</v>
       </c>
       <c r="P369" t="n">
         <v>39000</v>
@@ -16776,10 +16776,10 @@
         <v>115</v>
       </c>
       <c r="N371" t="n">
-        <v>1778.4725740823</v>
+        <v>1778.4725809313</v>
       </c>
       <c r="O371" t="n">
-        <v>204524.3460194645</v>
+        <v>204524.3468070995</v>
       </c>
       <c r="P371" t="n">
         <v>4900</v>
@@ -17003,22 +17003,22 @@
         <v>0</v>
       </c>
       <c r="L376" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M376" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N376" t="n">
         <v>26956</v>
       </c>
       <c r="O376" t="n">
-        <v>296516</v>
+        <v>269560</v>
       </c>
       <c r="P376" t="n">
         <v>44900</v>
       </c>
       <c r="Q376" t="n">
-        <v>493900</v>
+        <v>449000</v>
       </c>
     </row>
     <row r="377">
@@ -19418,10 +19418,10 @@
         <v>271</v>
       </c>
       <c r="N428" t="n">
-        <v>2328.1187488882</v>
+        <v>2328.118739546</v>
       </c>
       <c r="O428" t="n">
-        <v>630920.1809487023</v>
+        <v>630920.178416966</v>
       </c>
       <c r="P428" t="n">
         <v>4500</v>
@@ -20338,10 +20338,10 @@
         <v>98</v>
       </c>
       <c r="N448" t="n">
-        <v>3903.7362017804</v>
+        <v>3903.736812933</v>
       </c>
       <c r="O448" t="n">
-        <v>382566.1477744792</v>
+        <v>382566.207667434</v>
       </c>
       <c r="P448" t="n">
         <v>7500</v>
@@ -20972,10 +20972,10 @@
         <v>205</v>
       </c>
       <c r="N462" t="n">
-        <v>5869.1727464789</v>
+        <v>5869.1727391742</v>
       </c>
       <c r="O462" t="n">
-        <v>1203180.413028175</v>
+        <v>1203180.411530711</v>
       </c>
       <c r="P462" t="n">
         <v>9500</v>
@@ -21150,22 +21150,22 @@
         <v>0</v>
       </c>
       <c r="L466" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M466" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N466" t="n">
         <v>8637</v>
       </c>
       <c r="O466" t="n">
-        <v>129555</v>
+        <v>112281</v>
       </c>
       <c r="P466" t="n">
         <v>14500</v>
       </c>
       <c r="Q466" t="n">
-        <v>217500</v>
+        <v>188500</v>
       </c>
     </row>
     <row r="467">
@@ -21380,22 +21380,22 @@
         <v>0</v>
       </c>
       <c r="L471" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M471" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="N471" t="n">
         <v>7562</v>
       </c>
       <c r="O471" t="n">
-        <v>204174</v>
+        <v>189050</v>
       </c>
       <c r="P471" t="n">
         <v>12900</v>
       </c>
       <c r="Q471" t="n">
-        <v>348300</v>
+        <v>322500</v>
       </c>
     </row>
     <row r="472">
@@ -24104,10 +24104,10 @@
         <v>465</v>
       </c>
       <c r="N530" t="n">
-        <v>2079.3841354372</v>
+        <v>2079.384121911</v>
       </c>
       <c r="O530" t="n">
-        <v>966913.6229782979</v>
+        <v>966913.6166886149</v>
       </c>
       <c r="P530" t="n">
         <v>2900</v>
@@ -24150,10 +24150,10 @@
         <v>331</v>
       </c>
       <c r="N531" t="n">
-        <v>1803.0152234206</v>
+        <v>1803.0152282542</v>
       </c>
       <c r="O531" t="n">
-        <v>596798.0389522186</v>
+        <v>596798.0405521402</v>
       </c>
       <c r="P531" t="n">
         <v>2500</v>
@@ -24196,10 +24196,10 @@
         <v>96</v>
       </c>
       <c r="N532" t="n">
-        <v>3306.5953246753</v>
+        <v>3306.5952380952</v>
       </c>
       <c r="O532" t="n">
-        <v>317433.1511688288</v>
+        <v>317433.1428571392</v>
       </c>
       <c r="P532" t="n">
         <v>4900</v>
@@ -24242,10 +24242,10 @@
         <v>559</v>
       </c>
       <c r="N533" t="n">
-        <v>2122.164</v>
+        <v>2122.1639833897</v>
       </c>
       <c r="O533" t="n">
-        <v>1186289.676</v>
+        <v>1186289.666714842</v>
       </c>
       <c r="P533" t="n">
         <v>2900</v>
@@ -24282,22 +24282,22 @@
         <v>0</v>
       </c>
       <c r="L534" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M534" t="n">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="N534" t="n">
-        <v>2108.7900692042</v>
+        <v>2108.7902645503</v>
       </c>
       <c r="O534" t="n">
-        <v>643180.9711072809</v>
+        <v>630528.2891005396</v>
       </c>
       <c r="P534" t="n">
         <v>2900</v>
       </c>
       <c r="Q534" t="n">
-        <v>884500</v>
+        <v>867100</v>
       </c>
     </row>
     <row r="535">
@@ -24328,22 +24328,22 @@
         <v>0</v>
       </c>
       <c r="L535" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M535" t="n">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="N535" t="n">
-        <v>2056.0837111517</v>
+        <v>2056.0836725935</v>
       </c>
       <c r="O535" t="n">
-        <v>820377.4007495282</v>
+        <v>799816.5486388715</v>
       </c>
       <c r="P535" t="n">
         <v>2900</v>
       </c>
       <c r="Q535" t="n">
-        <v>1157100</v>
+        <v>1128100</v>
       </c>
     </row>
     <row r="536">
@@ -24604,22 +24604,22 @@
         <v>0</v>
       </c>
       <c r="L541" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M541" t="n">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="N541" t="n">
-        <v>1592.27610957</v>
+        <v>1592.2763108883</v>
       </c>
       <c r="O541" t="n">
-        <v>332785.70690013</v>
+        <v>307309.3280014419</v>
       </c>
       <c r="P541" t="n">
         <v>2500</v>
       </c>
       <c r="Q541" t="n">
-        <v>522500</v>
+        <v>482500</v>
       </c>
     </row>
     <row r="542">
@@ -24700,10 +24700,10 @@
         <v>41</v>
       </c>
       <c r="N543" t="n">
-        <v>1668.6236893204</v>
+        <v>1668.6240987654</v>
       </c>
       <c r="O543" t="n">
-        <v>68413.57126213639</v>
+        <v>68413.5880493814</v>
       </c>
       <c r="P543" t="n">
         <v>2500</v>
@@ -24746,10 +24746,10 @@
         <v>35</v>
       </c>
       <c r="N544" t="n">
-        <v>2546.9846915888</v>
+        <v>2546.9846816479</v>
       </c>
       <c r="O544" t="n">
-        <v>89144.464205608</v>
+        <v>89144.4638576765</v>
       </c>
       <c r="P544" t="n">
         <v>3900</v>
@@ -24786,22 +24786,22 @@
         <v>0</v>
       </c>
       <c r="L545" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M545" t="n">
-        <v>990</v>
+        <v>966</v>
       </c>
       <c r="N545" t="n">
-        <v>1259.2744638514</v>
+        <v>1259.2745016722</v>
       </c>
       <c r="O545" t="n">
-        <v>1246681.719212886</v>
+        <v>1216459.168615345</v>
       </c>
       <c r="P545" t="n">
         <v>1900</v>
       </c>
       <c r="Q545" t="n">
-        <v>1881000</v>
+        <v>1835400</v>
       </c>
     </row>
     <row r="546">
@@ -24965,22 +24965,22 @@
         <v>0</v>
       </c>
       <c r="L549" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M549" t="n">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="N549" t="n">
         <v>1801</v>
       </c>
       <c r="O549" t="n">
-        <v>986948</v>
+        <v>979744</v>
       </c>
       <c r="P549" t="n">
         <v>2900</v>
       </c>
       <c r="Q549" t="n">
-        <v>1589200</v>
+        <v>1577600</v>
       </c>
     </row>
     <row r="550">
@@ -25015,10 +25015,10 @@
         <v>234</v>
       </c>
       <c r="N550" t="n">
-        <v>692.15211662075</v>
+        <v>692.1521205151799</v>
       </c>
       <c r="O550" t="n">
-        <v>161963.5952892555</v>
+        <v>161963.5962005521</v>
       </c>
       <c r="P550" t="n">
         <v>1200</v>
@@ -25387,22 +25387,22 @@
         <v>0</v>
       </c>
       <c r="L558" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M558" t="n">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="N558" t="n">
         <v>8945.379999999999</v>
       </c>
       <c r="O558" t="n">
-        <v>1037664.08</v>
+        <v>1010827.94</v>
       </c>
       <c r="P558" t="n">
         <v>14900</v>
       </c>
       <c r="Q558" t="n">
-        <v>1728400</v>
+        <v>1683700</v>
       </c>
     </row>
     <row r="559">
@@ -25580,22 +25580,22 @@
         <v>0</v>
       </c>
       <c r="L562" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M562" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="N562" t="n">
         <v>2761.66</v>
       </c>
       <c r="O562" t="n">
-        <v>30378.26</v>
+        <v>0</v>
       </c>
       <c r="P562" t="n">
         <v>2900</v>
       </c>
       <c r="Q562" t="n">
-        <v>31900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="563">
@@ -26006,10 +26006,10 @@
         <v>21</v>
       </c>
       <c r="N571" t="n">
-        <v>10732.241904762</v>
+        <v>10732.24195122</v>
       </c>
       <c r="O571" t="n">
-        <v>225377.080000002</v>
+        <v>225377.08097562</v>
       </c>
       <c r="P571" t="n">
         <v>25900</v>
@@ -26139,22 +26139,22 @@
         <v>0</v>
       </c>
       <c r="L574" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M574" t="n">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="N574" t="n">
         <v>1828.64</v>
       </c>
       <c r="O574" t="n">
-        <v>2415633.44</v>
+        <v>2413804.8</v>
       </c>
       <c r="P574" t="n">
         <v>2000</v>
       </c>
       <c r="Q574" t="n">
-        <v>2642000</v>
+        <v>2640000</v>
       </c>
     </row>
     <row r="575">
@@ -26191,10 +26191,10 @@
         <v>183</v>
       </c>
       <c r="N575" t="n">
-        <v>1690.8700089847</v>
+        <v>1690.870009009</v>
       </c>
       <c r="O575" t="n">
-        <v>309429.2116442001</v>
+        <v>309429.211648647</v>
       </c>
       <c r="P575" t="n">
         <v>3000</v>
@@ -26699,10 +26699,10 @@
         <v>132</v>
       </c>
       <c r="N586" t="n">
-        <v>1283.653986711</v>
+        <v>1283.6539464883</v>
       </c>
       <c r="O586" t="n">
-        <v>169442.326245852</v>
+        <v>169442.3209364556</v>
       </c>
       <c r="P586" t="n">
         <v>1900</v>
@@ -26974,10 +26974,10 @@
         <v>2299</v>
       </c>
       <c r="N592" t="n">
-        <v>517.28836312001</v>
+        <v>517.2884408203601</v>
       </c>
       <c r="O592" t="n">
-        <v>1189245.946812903</v>
+        <v>1189246.125446008</v>
       </c>
       <c r="P592" t="n">
         <v>900</v>
@@ -27205,10 +27205,10 @@
         <v>344</v>
       </c>
       <c r="N597" t="n">
-        <v>3110.8426185007</v>
+        <v>3110.8425641565</v>
       </c>
       <c r="O597" t="n">
-        <v>1070129.860764241</v>
+        <v>1070129.842069836</v>
       </c>
       <c r="P597" t="n">
         <v>4500</v>
@@ -27249,10 +27249,10 @@
         <v>868</v>
       </c>
       <c r="N598" t="n">
-        <v>703.79529676406</v>
+        <v>703.79526826968</v>
       </c>
       <c r="O598" t="n">
-        <v>610894.3175912041</v>
+        <v>610894.2928580822</v>
       </c>
       <c r="P598" t="n">
         <v>900</v>
@@ -27531,22 +27531,22 @@
         <v>0</v>
       </c>
       <c r="L604" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="M604" t="n">
-        <v>371</v>
+        <v>345</v>
       </c>
       <c r="N604" t="n">
-        <v>1595.5153131828</v>
+        <v>1595.5151400147</v>
       </c>
       <c r="O604" t="n">
-        <v>591936.1811908188</v>
+        <v>550452.7233050715</v>
       </c>
       <c r="P604" t="n">
         <v>2500</v>
       </c>
       <c r="Q604" t="n">
-        <v>927500</v>
+        <v>862500</v>
       </c>
     </row>
     <row r="605">
@@ -28352,22 +28352,22 @@
         <v>0</v>
       </c>
       <c r="L621" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M621" t="n">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="N621" t="n">
         <v>1669.6</v>
       </c>
       <c r="O621" t="n">
-        <v>983394.3999999999</v>
+        <v>980055.2</v>
       </c>
       <c r="P621" t="n">
         <v>2900</v>
       </c>
       <c r="Q621" t="n">
-        <v>1708100</v>
+        <v>1702300</v>
       </c>
     </row>
     <row r="622">
@@ -29936,22 +29936,22 @@
         <v>0</v>
       </c>
       <c r="L654" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M654" t="n">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="N654" t="n">
         <v>3000.33</v>
       </c>
       <c r="O654" t="n">
-        <v>795087.45</v>
+        <v>786086.46</v>
       </c>
       <c r="P654" t="n">
         <v>2900</v>
       </c>
       <c r="Q654" t="n">
-        <v>768500</v>
+        <v>759800</v>
       </c>
     </row>
     <row r="655">
@@ -30750,10 +30750,10 @@
         <v>9</v>
       </c>
       <c r="N671" t="n">
-        <v>10737.5264</v>
+        <v>10737.526326531</v>
       </c>
       <c r="O671" t="n">
-        <v>96637.73760000001</v>
+        <v>96637.73693877901</v>
       </c>
       <c r="P671" t="n">
         <v>18900</v>
@@ -31606,22 +31606,22 @@
         <v>0</v>
       </c>
       <c r="L689" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M689" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="N689" t="n">
         <v>1934.77</v>
       </c>
       <c r="O689" t="n">
-        <v>106412.35</v>
+        <v>102542.81</v>
       </c>
       <c r="P689" t="n">
         <v>8900</v>
       </c>
       <c r="Q689" t="n">
-        <v>489500</v>
+        <v>471700</v>
       </c>
     </row>
     <row r="690">
@@ -32177,22 +32177,22 @@
         <v>0</v>
       </c>
       <c r="L701" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M701" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="N701" t="n">
         <v>1338.14</v>
       </c>
       <c r="O701" t="n">
-        <v>230160.08</v>
+        <v>227483.8</v>
       </c>
       <c r="P701" t="n">
         <v>2500</v>
       </c>
       <c r="Q701" t="n">
-        <v>430000</v>
+        <v>425000</v>
       </c>
     </row>
     <row r="702">
@@ -32324,22 +32324,22 @@
         <v>0</v>
       </c>
       <c r="L704" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M704" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="N704" t="n">
         <v>4581.84</v>
       </c>
       <c r="O704" t="n">
-        <v>45818.4</v>
+        <v>18327.36</v>
       </c>
       <c r="P704" t="n">
         <v>7900</v>
       </c>
       <c r="Q704" t="n">
-        <v>79000</v>
+        <v>31600</v>
       </c>
     </row>
     <row r="705">
@@ -33241,10 +33241,10 @@
         <v>12</v>
       </c>
       <c r="N724" t="n">
-        <v>4985.4047808765</v>
+        <v>4985.4050632911</v>
       </c>
       <c r="O724" t="n">
-        <v>59824.857370518</v>
+        <v>59824.8607594932</v>
       </c>
       <c r="P724" t="n">
         <v>7900</v>
@@ -35483,7 +35483,7 @@
         </is>
       </c>
       <c r="J773" t="n">
-        <v>7465</v>
+        <v>273</v>
       </c>
       <c r="K773" t="n">
         <v>0</v>
@@ -35492,19 +35492,19 @@
         <v>0</v>
       </c>
       <c r="M773" t="n">
-        <v>7465</v>
+        <v>273</v>
       </c>
       <c r="N773" t="n">
-        <v>288</v>
+        <v>7480</v>
       </c>
       <c r="O773" t="n">
-        <v>2149920</v>
+        <v>2042040</v>
       </c>
       <c r="P773" t="n">
         <v>9500</v>
       </c>
       <c r="Q773" t="n">
-        <v>70917500</v>
+        <v>2593500</v>
       </c>
     </row>
     <row r="774">
@@ -35575,19 +35575,19 @@
         </is>
       </c>
       <c r="J775" t="n">
+        <v>330</v>
+      </c>
+      <c r="K775" t="n">
+        <v>0</v>
+      </c>
+      <c r="L775" t="n">
+        <v>0</v>
+      </c>
+      <c r="M775" t="n">
+        <v>330</v>
+      </c>
+      <c r="N775" t="n">
         <v>7216</v>
-      </c>
-      <c r="K775" t="n">
-        <v>0</v>
-      </c>
-      <c r="L775" t="n">
-        <v>0</v>
-      </c>
-      <c r="M775" t="n">
-        <v>7216</v>
-      </c>
-      <c r="N775" t="n">
-        <v>330</v>
       </c>
       <c r="O775" t="n">
         <v>2381280</v>
@@ -35596,7 +35596,7 @@
         <v>9000</v>
       </c>
       <c r="Q775" t="n">
-        <v>64944000</v>
+        <v>2970000</v>
       </c>
     </row>
     <row r="776">

--- a/bodegas/LJ-05.xlsx
+++ b/bodegas/LJ-05.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q823"/>
+  <dimension ref="A1:Q819"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-20</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-21</t>
         </is>
       </c>
     </row>
@@ -1094,10 +1094,10 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="K17" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -7301,13 +7301,13 @@
         </is>
       </c>
       <c r="J161" t="n">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="K161" t="n">
         <v>0</v>
       </c>
       <c r="L161" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M161" t="n">
         <v>85</v>
@@ -7434,13 +7434,13 @@
         </is>
       </c>
       <c r="J164" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="K164" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L164" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M164" t="n">
         <v>35</v>
@@ -7710,13 +7710,13 @@
         </is>
       </c>
       <c r="J170" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="K170" t="n">
         <v>0</v>
       </c>
       <c r="L170" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="M170" t="n">
         <v>9</v>
@@ -7802,13 +7802,13 @@
         </is>
       </c>
       <c r="J172" t="n">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="K172" t="n">
         <v>0</v>
       </c>
       <c r="L172" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M172" t="n">
         <v>105</v>
@@ -8073,13 +8073,13 @@
         </is>
       </c>
       <c r="J178" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="K178" t="n">
         <v>0</v>
       </c>
       <c r="L178" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M178" t="n">
         <v>22</v>
@@ -8211,13 +8211,13 @@
         </is>
       </c>
       <c r="J181" t="n">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="K181" t="n">
         <v>0</v>
       </c>
       <c r="L181" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M181" t="n">
         <v>36</v>
@@ -8442,13 +8442,13 @@
         </is>
       </c>
       <c r="J186" t="n">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="K186" t="n">
         <v>0</v>
       </c>
       <c r="L186" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="M186" t="n">
         <v>84</v>
@@ -9077,13 +9077,13 @@
         </is>
       </c>
       <c r="J200" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="K200" t="n">
         <v>0</v>
       </c>
       <c r="L200" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M200" t="n">
         <v>27</v>
@@ -9123,13 +9123,13 @@
         </is>
       </c>
       <c r="J201" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="K201" t="n">
         <v>0</v>
       </c>
       <c r="L201" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M201" t="n">
         <v>30</v>
@@ -9488,13 +9488,13 @@
         </is>
       </c>
       <c r="J209" t="n">
-        <v>2471</v>
+        <v>2470</v>
       </c>
       <c r="K209" t="n">
         <v>0</v>
       </c>
       <c r="L209" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M209" t="n">
         <v>2470</v>
@@ -9583,13 +9583,13 @@
         </is>
       </c>
       <c r="J211" t="n">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="K211" t="n">
         <v>0</v>
       </c>
       <c r="L211" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M211" t="n">
         <v>63</v>
@@ -9938,13 +9938,13 @@
         </is>
       </c>
       <c r="J219" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="K219" t="n">
         <v>0</v>
       </c>
       <c r="L219" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M219" t="n">
         <v>58</v>
@@ -9984,13 +9984,13 @@
         </is>
       </c>
       <c r="J220" t="n">
-        <v>408</v>
+        <v>365</v>
       </c>
       <c r="K220" t="n">
         <v>0</v>
       </c>
       <c r="L220" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="M220" t="n">
         <v>365</v>
@@ -10294,13 +10294,13 @@
         </is>
       </c>
       <c r="J227" t="n">
-        <v>355</v>
+        <v>331</v>
       </c>
       <c r="K227" t="n">
         <v>0</v>
       </c>
       <c r="L227" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="M227" t="n">
         <v>331</v>
@@ -10477,13 +10477,13 @@
         </is>
       </c>
       <c r="J231" t="n">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="K231" t="n">
         <v>0</v>
       </c>
       <c r="L231" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M231" t="n">
         <v>204</v>
@@ -10609,13 +10609,13 @@
         </is>
       </c>
       <c r="J234" t="n">
-        <v>2270</v>
+        <v>2260</v>
       </c>
       <c r="K234" t="n">
         <v>0</v>
       </c>
       <c r="L234" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M234" t="n">
         <v>2260</v>
@@ -10707,13 +10707,13 @@
         </is>
       </c>
       <c r="J236" t="n">
-        <v>518</v>
+        <v>488</v>
       </c>
       <c r="K236" t="n">
         <v>0</v>
       </c>
       <c r="L236" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="M236" t="n">
         <v>488</v>
@@ -11204,13 +11204,13 @@
         </is>
       </c>
       <c r="J247" t="n">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="K247" t="n">
         <v>0</v>
       </c>
       <c r="L247" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M247" t="n">
         <v>719</v>
@@ -11299,13 +11299,13 @@
         </is>
       </c>
       <c r="J249" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="K249" t="n">
         <v>0</v>
       </c>
       <c r="L249" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M249" t="n">
         <v>76</v>
@@ -11345,13 +11345,13 @@
         </is>
       </c>
       <c r="J250" t="n">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="K250" t="n">
         <v>0</v>
       </c>
       <c r="L250" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M250" t="n">
         <v>146</v>
@@ -11391,13 +11391,13 @@
         </is>
       </c>
       <c r="J251" t="n">
-        <v>604</v>
+        <v>589</v>
       </c>
       <c r="K251" t="n">
         <v>0</v>
       </c>
       <c r="L251" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M251" t="n">
         <v>589</v>
@@ -11570,13 +11570,13 @@
         </is>
       </c>
       <c r="J255" t="n">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="K255" t="n">
         <v>0</v>
       </c>
       <c r="L255" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M255" t="n">
         <v>212</v>
@@ -12374,10 +12374,10 @@
         <v>46</v>
       </c>
       <c r="N273" t="n">
-        <v>8799.395863611</v>
+        <v>8794.48</v>
       </c>
       <c r="O273" t="n">
-        <v>404772.209726106</v>
+        <v>404546.08</v>
       </c>
       <c r="P273" t="n">
         <v>14500</v>
@@ -12408,13 +12408,13 @@
         </is>
       </c>
       <c r="J274" t="n">
-        <v>81</v>
+        <v>57</v>
       </c>
       <c r="K274" t="n">
         <v>0</v>
       </c>
       <c r="L274" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="M274" t="n">
         <v>57</v>
@@ -12490,13 +12490,13 @@
         </is>
       </c>
       <c r="J276" t="n">
-        <v>224</v>
+        <v>202</v>
       </c>
       <c r="K276" t="n">
         <v>0</v>
       </c>
       <c r="L276" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="M276" t="n">
         <v>202</v>
@@ -12613,13 +12613,13 @@
         </is>
       </c>
       <c r="J279" t="n">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K279" t="n">
         <v>0</v>
       </c>
       <c r="L279" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M279" t="n">
         <v>171</v>
@@ -13184,13 +13184,13 @@
         </is>
       </c>
       <c r="J292" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="K292" t="n">
         <v>0</v>
       </c>
       <c r="L292" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M292" t="n">
         <v>106</v>
@@ -13233,13 +13233,13 @@
         </is>
       </c>
       <c r="J293" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="K293" t="n">
         <v>0</v>
       </c>
       <c r="L293" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M293" t="n">
         <v>93</v>
@@ -13947,13 +13947,13 @@
         </is>
       </c>
       <c r="J309" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="K309" t="n">
         <v>0</v>
       </c>
       <c r="L309" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="M309" t="n">
         <v>35</v>
@@ -14612,13 +14612,13 @@
         </is>
       </c>
       <c r="J324" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="K324" t="n">
         <v>0</v>
       </c>
       <c r="L324" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M324" t="n">
         <v>55</v>
@@ -15696,13 +15696,13 @@
         </is>
       </c>
       <c r="J348" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="K348" t="n">
         <v>0</v>
       </c>
       <c r="L348" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M348" t="n">
         <v>51</v>
@@ -15742,13 +15742,13 @@
         </is>
       </c>
       <c r="J349" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K349" t="n">
         <v>0</v>
       </c>
       <c r="L349" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M349" t="n">
         <v>11</v>
@@ -15788,13 +15788,13 @@
         </is>
       </c>
       <c r="J350" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="K350" t="n">
         <v>0</v>
       </c>
       <c r="L350" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M350" t="n">
         <v>101</v>
@@ -15926,13 +15926,13 @@
         </is>
       </c>
       <c r="J353" t="n">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="K353" t="n">
         <v>0</v>
       </c>
       <c r="L353" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M353" t="n">
         <v>151</v>
@@ -15972,13 +15972,13 @@
         </is>
       </c>
       <c r="J354" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="K354" t="n">
         <v>0</v>
       </c>
       <c r="L354" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M354" t="n">
         <v>91</v>
@@ -16064,13 +16064,13 @@
         </is>
       </c>
       <c r="J356" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K356" t="n">
         <v>0</v>
       </c>
       <c r="L356" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M356" t="n">
         <v>2</v>
@@ -16294,13 +16294,13 @@
         </is>
       </c>
       <c r="J361" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="K361" t="n">
         <v>0</v>
       </c>
       <c r="L361" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M361" t="n">
         <v>8</v>
@@ -16803,13 +16803,13 @@
         </is>
       </c>
       <c r="J372" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="K372" t="n">
         <v>0</v>
       </c>
       <c r="L372" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M372" t="n">
         <v>4</v>
@@ -16849,13 +16849,13 @@
         </is>
       </c>
       <c r="J373" t="n">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="K373" t="n">
         <v>0</v>
       </c>
       <c r="L373" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M373" t="n">
         <v>99</v>
@@ -18381,13 +18381,13 @@
         </is>
       </c>
       <c r="J406" t="n">
-        <v>750</v>
+        <v>720</v>
       </c>
       <c r="K406" t="n">
         <v>0</v>
       </c>
       <c r="L406" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="M406" t="n">
         <v>720</v>
@@ -19120,13 +19120,13 @@
         </is>
       </c>
       <c r="J422" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="K422" t="n">
         <v>0</v>
       </c>
       <c r="L422" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M422" t="n">
         <v>35</v>
@@ -19491,13 +19491,13 @@
         </is>
       </c>
       <c r="J430" t="n">
-        <v>271</v>
+        <v>247</v>
       </c>
       <c r="K430" t="n">
         <v>0</v>
       </c>
       <c r="L430" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="M430" t="n">
         <v>247</v>
@@ -19963,10 +19963,10 @@
         <v>67</v>
       </c>
       <c r="N440" t="n">
-        <v>3418.6270305677</v>
+        <v>3396.38</v>
       </c>
       <c r="O440" t="n">
-        <v>229048.0110480359</v>
+        <v>227557.46</v>
       </c>
       <c r="P440" t="n">
         <v>6500</v>
@@ -20043,13 +20043,13 @@
         </is>
       </c>
       <c r="J442" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="K442" t="n">
         <v>0</v>
       </c>
       <c r="L442" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M442" t="n">
         <v>44</v>
@@ -20953,13 +20953,13 @@
         </is>
       </c>
       <c r="J462" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K462" t="n">
         <v>0</v>
       </c>
       <c r="L462" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M462" t="n">
         <v>10</v>
@@ -21011,10 +21011,10 @@
         <v>172</v>
       </c>
       <c r="N463" t="n">
-        <v>2637.9574105622</v>
+        <v>2629</v>
       </c>
       <c r="O463" t="n">
-        <v>453728.6746166984</v>
+        <v>452188</v>
       </c>
       <c r="P463" t="n">
         <v>4500</v>
@@ -21195,10 +21195,10 @@
         <v>170</v>
       </c>
       <c r="N467" t="n">
-        <v>5775.9026369168</v>
+        <v>5772</v>
       </c>
       <c r="O467" t="n">
-        <v>981903.448275856</v>
+        <v>981240</v>
       </c>
       <c r="P467" t="n">
         <v>9900</v>
@@ -21517,10 +21517,10 @@
         <v>17</v>
       </c>
       <c r="N474" t="n">
-        <v>3904.1097178683</v>
+        <v>3898</v>
       </c>
       <c r="O474" t="n">
-        <v>66369.8652037611</v>
+        <v>66266</v>
       </c>
       <c r="P474" t="n">
         <v>6900</v>
@@ -23254,13 +23254,13 @@
         </is>
       </c>
       <c r="J512" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K512" t="n">
         <v>0</v>
       </c>
       <c r="L512" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M512" t="n">
         <v>23</v>
@@ -23714,13 +23714,13 @@
         </is>
       </c>
       <c r="J522" t="n">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="K522" t="n">
         <v>0</v>
       </c>
       <c r="L522" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M522" t="n">
         <v>82</v>
@@ -23947,13 +23947,13 @@
         </is>
       </c>
       <c r="J527" t="n">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="K527" t="n">
         <v>0</v>
       </c>
       <c r="L527" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M527" t="n">
         <v>189</v>
@@ -24039,13 +24039,13 @@
         </is>
       </c>
       <c r="J529" t="n">
-        <v>450</v>
+        <v>435</v>
       </c>
       <c r="K529" t="n">
         <v>0</v>
       </c>
       <c r="L529" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M529" t="n">
         <v>435</v>
@@ -24143,10 +24143,10 @@
         <v>183</v>
       </c>
       <c r="N531" t="n">
-        <v>1775.6031464968</v>
+        <v>1771.0907898089</v>
       </c>
       <c r="O531" t="n">
-        <v>324935.3758089144</v>
+        <v>324109.6145350287</v>
       </c>
       <c r="P531" t="n">
         <v>2500</v>
@@ -24177,13 +24177,13 @@
         </is>
       </c>
       <c r="J532" t="n">
-        <v>465</v>
+        <v>441</v>
       </c>
       <c r="K532" t="n">
         <v>0</v>
       </c>
       <c r="L532" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="M532" t="n">
         <v>441</v>
@@ -24407,13 +24407,13 @@
         </is>
       </c>
       <c r="J537" t="n">
-        <v>389</v>
+        <v>341</v>
       </c>
       <c r="K537" t="n">
         <v>0</v>
       </c>
       <c r="L537" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="M537" t="n">
         <v>341</v>
@@ -24453,13 +24453,13 @@
         </is>
       </c>
       <c r="J538" t="n">
-        <v>360</v>
+        <v>336</v>
       </c>
       <c r="K538" t="n">
         <v>0</v>
       </c>
       <c r="L538" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="M538" t="n">
         <v>336</v>
@@ -24637,13 +24637,13 @@
         </is>
       </c>
       <c r="J542" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="K542" t="n">
         <v>0</v>
       </c>
       <c r="L542" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M542" t="n">
         <v>50</v>
@@ -24683,13 +24683,13 @@
         </is>
       </c>
       <c r="J543" t="n">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="K543" t="n">
         <v>0</v>
       </c>
       <c r="L543" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M543" t="n">
         <v>189</v>
@@ -26088,10 +26088,10 @@
         <v>110</v>
       </c>
       <c r="N573" t="n">
-        <v>6939.3400593472</v>
+        <v>6898.4</v>
       </c>
       <c r="O573" t="n">
-        <v>763327.406528192</v>
+        <v>758824</v>
       </c>
       <c r="P573" t="n">
         <v>12900</v>
@@ -26998,13 +26998,13 @@
         </is>
       </c>
       <c r="J593" t="n">
-        <v>2299</v>
+        <v>2049</v>
       </c>
       <c r="K593" t="n">
         <v>0</v>
       </c>
       <c r="L593" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="M593" t="n">
         <v>2049</v>
@@ -27229,13 +27229,13 @@
         </is>
       </c>
       <c r="J598" t="n">
-        <v>344</v>
+        <v>324</v>
       </c>
       <c r="K598" t="n">
         <v>0</v>
       </c>
       <c r="L598" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M598" t="n">
         <v>324</v>
@@ -28949,13 +28949,13 @@
         </is>
       </c>
       <c r="J634" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K634" t="n">
         <v>0</v>
       </c>
       <c r="L634" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M634" t="n">
         <v>28</v>
@@ -30064,13 +30064,13 @@
         </is>
       </c>
       <c r="J657" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="K657" t="n">
         <v>0</v>
       </c>
       <c r="L657" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M657" t="n">
         <v>25</v>
@@ -30306,13 +30306,13 @@
         </is>
       </c>
       <c r="J662" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K662" t="n">
         <v>0</v>
       </c>
       <c r="L662" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M662" t="n">
         <v>76</v>
@@ -31494,13 +31494,13 @@
         </is>
       </c>
       <c r="J687" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="K687" t="n">
         <v>0</v>
       </c>
       <c r="L687" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M687" t="n">
         <v>13</v>
@@ -31827,13 +31827,13 @@
         </is>
       </c>
       <c r="J694" t="n">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="K694" t="n">
         <v>0</v>
       </c>
       <c r="L694" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M694" t="n">
         <v>126</v>
@@ -32207,13 +32207,13 @@
         </is>
       </c>
       <c r="J702" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="K702" t="n">
         <v>0</v>
       </c>
       <c r="L702" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M702" t="n">
         <v>160</v>
@@ -32268,10 +32268,10 @@
         <v>28</v>
       </c>
       <c r="N703" t="n">
-        <v>432.57910714286</v>
+        <v>424.99</v>
       </c>
       <c r="O703" t="n">
-        <v>12112.21500000008</v>
+        <v>11899.72</v>
       </c>
       <c r="P703" t="n">
         <v>2300</v>
@@ -32403,13 +32403,13 @@
         </is>
       </c>
       <c r="J706" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K706" t="n">
         <v>0</v>
       </c>
       <c r="L706" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M706" t="n">
         <v>78</v>
@@ -33001,13 +33001,13 @@
         </is>
       </c>
       <c r="J719" t="n">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="K719" t="n">
         <v>0</v>
       </c>
       <c r="L719" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M719" t="n">
         <v>83</v>
@@ -33069,12 +33069,20 @@
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>C94</t>
-        </is>
+          <t>C97</t>
+        </is>
+      </c>
+      <c r="B721" t="n">
+        <v>6914919320040</v>
       </c>
       <c r="C721" t="inlineStr">
         <is>
-          <t>PITO ESPANTA SUEGRA PUNTOS</t>
+          <t>CARRO BOLSA OJITOS 95</t>
+        </is>
+      </c>
+      <c r="E721" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I721" t="inlineStr">
@@ -33083,42 +33091,39 @@
         </is>
       </c>
       <c r="J721" t="n">
-        <v>1</v>
+        <v>137</v>
       </c>
       <c r="K721" t="n">
         <v>0</v>
       </c>
       <c r="L721" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M721" t="n">
-        <v>0</v>
+        <v>137</v>
       </c>
       <c r="N721" t="n">
-        <v>7308.87</v>
+        <v>5077</v>
       </c>
       <c r="O721" t="n">
-        <v>0</v>
+        <v>695549</v>
       </c>
       <c r="P721" t="n">
-        <v>6000</v>
+        <v>8500</v>
       </c>
       <c r="Q721" t="n">
-        <v>0</v>
+        <v>1164500</v>
       </c>
     </row>
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>C97</t>
-        </is>
-      </c>
-      <c r="B722" t="n">
-        <v>6914919320040</v>
+          <t>C98</t>
+        </is>
       </c>
       <c r="C722" t="inlineStr">
         <is>
-          <t>CARRO BOLSA OJITOS 95</t>
+          <t>LANZADORA AGUA PQÑ</t>
         </is>
       </c>
       <c r="E722" t="inlineStr">
@@ -33128,11 +33133,11 @@
       </c>
       <c r="I722" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J722" t="n">
-        <v>137</v>
+        <v>72</v>
       </c>
       <c r="K722" t="n">
         <v>0</v>
@@ -33141,44 +33146,44 @@
         <v>0</v>
       </c>
       <c r="M722" t="n">
-        <v>137</v>
+        <v>72</v>
       </c>
       <c r="N722" t="n">
-        <v>5077</v>
+        <v>1600</v>
       </c>
       <c r="O722" t="n">
-        <v>695549</v>
+        <v>115200</v>
       </c>
       <c r="P722" t="n">
-        <v>8500</v>
+        <v>3500</v>
       </c>
       <c r="Q722" t="n">
-        <v>1164500</v>
+        <v>252000</v>
       </c>
     </row>
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>C98</t>
+          <t>C984</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>CG2016531</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
         <is>
-          <t>LANZADORA AGUA PQÑ</t>
-        </is>
-      </c>
-      <c r="E723" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>TANGRAM</t>
         </is>
       </c>
       <c r="I723" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J723" t="n">
-        <v>72</v>
+        <v>523</v>
       </c>
       <c r="K723" t="n">
         <v>0</v>
@@ -33187,44 +33192,44 @@
         <v>0</v>
       </c>
       <c r="M723" t="n">
-        <v>72</v>
+        <v>523</v>
       </c>
       <c r="N723" t="n">
-        <v>1600</v>
+        <v>705.52801204819</v>
       </c>
       <c r="O723" t="n">
-        <v>115200</v>
+        <v>368991.1503012034</v>
       </c>
       <c r="P723" t="n">
-        <v>3500</v>
+        <v>1500</v>
       </c>
       <c r="Q723" t="n">
-        <v>252000</v>
+        <v>784500</v>
       </c>
     </row>
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>C984</t>
-        </is>
-      </c>
-      <c r="B724" t="inlineStr">
-        <is>
-          <t>CG2016531</t>
+          <t>CH-448-04</t>
         </is>
       </c>
       <c r="C724" t="inlineStr">
         <is>
-          <t>TANGRAM</t>
+          <t>TAJA LAPUZ HUELLITA CH-448-04</t>
+        </is>
+      </c>
+      <c r="E724" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I724" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J724" t="n">
-        <v>523</v>
+        <v>12</v>
       </c>
       <c r="K724" t="n">
         <v>0</v>
@@ -33233,76 +33238,81 @@
         <v>0</v>
       </c>
       <c r="M724" t="n">
-        <v>523</v>
+        <v>12</v>
       </c>
       <c r="N724" t="n">
-        <v>705.52801204819</v>
+        <v>2367.6159854015</v>
       </c>
       <c r="O724" t="n">
-        <v>368991.1503012034</v>
+        <v>28411.391824818</v>
       </c>
       <c r="P724" t="n">
-        <v>1500</v>
+        <v>2900</v>
       </c>
       <c r="Q724" t="n">
-        <v>784500</v>
+        <v>34800</v>
       </c>
     </row>
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>C99</t>
+          <t>CM-MORRAL01</t>
         </is>
       </c>
       <c r="C725" t="inlineStr">
         <is>
-          <t>PELOTA EXPANDIBLE CON LUZ 29cm C99</t>
+          <t>MORRAL GRANDE PARA NIÑAS PRINCESS</t>
+        </is>
+      </c>
+      <c r="E725" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I725" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J725" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K725" t="n">
         <v>0</v>
       </c>
       <c r="L725" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M725" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N725" t="n">
-        <v>4985.4051948052</v>
+        <v>31846.46</v>
       </c>
       <c r="O725" t="n">
-        <v>0</v>
+        <v>286618.14</v>
       </c>
       <c r="P725" t="n">
-        <v>7900</v>
+        <v>55900</v>
       </c>
       <c r="Q725" t="n">
-        <v>0</v>
+        <v>503100</v>
       </c>
     </row>
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>CH-448-04</t>
+          <t>DPC029</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
         <is>
-          <t>TAJA LAPUZ HUELLITA CH-448-04</t>
+          <t>PELUCHE OSO CUMPLEAÑOS 30cm DP2512-016/DPC029</t>
         </is>
       </c>
       <c r="E726" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PELUCHES</t>
         </is>
       </c>
       <c r="I726" t="inlineStr">
@@ -33311,7 +33321,7 @@
         </is>
       </c>
       <c r="J726" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K726" t="n">
         <v>0</v>
@@ -33320,35 +33330,35 @@
         <v>0</v>
       </c>
       <c r="M726" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="N726" t="n">
-        <v>2367.6159854015</v>
+        <v>19800</v>
       </c>
       <c r="O726" t="n">
-        <v>28411.391824818</v>
+        <v>158400</v>
       </c>
       <c r="P726" t="n">
-        <v>2900</v>
+        <v>24900</v>
       </c>
       <c r="Q726" t="n">
-        <v>34800</v>
+        <v>199200</v>
       </c>
     </row>
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>CM-MORRAL01</t>
+          <t>DPC030</t>
         </is>
       </c>
       <c r="C727" t="inlineStr">
         <is>
-          <t>MORRAL GRANDE PARA NIÑAS PRINCESS</t>
+          <t>PELUCHE PANDA HIJO 35cm DP2512.032/DPC030</t>
         </is>
       </c>
       <c r="E727" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PELUCHES</t>
         </is>
       </c>
       <c r="I727" t="inlineStr">
@@ -33357,7 +33367,7 @@
         </is>
       </c>
       <c r="J727" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="K727" t="n">
         <v>0</v>
@@ -33366,35 +33376,35 @@
         <v>0</v>
       </c>
       <c r="M727" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="N727" t="n">
-        <v>31846.46</v>
+        <v>20700</v>
       </c>
       <c r="O727" t="n">
-        <v>286618.14</v>
+        <v>393300</v>
       </c>
       <c r="P727" t="n">
-        <v>55900</v>
+        <v>25900</v>
       </c>
       <c r="Q727" t="n">
-        <v>503100</v>
+        <v>492100</v>
       </c>
     </row>
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>DPC029</t>
+          <t>DPC031</t>
         </is>
       </c>
       <c r="C728" t="inlineStr">
         <is>
-          <t>PELUCHE OSO CUMPLEAÑOS 30cm DP2512-016/DPC029</t>
+          <t>PELUCHE ERIZO 28cm DP2512-064/DPC031</t>
         </is>
       </c>
       <c r="E728" t="inlineStr">
         <is>
-          <t>PELUCHES</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I728" t="inlineStr">
@@ -33403,7 +33413,7 @@
         </is>
       </c>
       <c r="J728" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K728" t="n">
         <v>0</v>
@@ -33412,30 +33422,30 @@
         <v>0</v>
       </c>
       <c r="M728" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="N728" t="n">
-        <v>19800</v>
+        <v>15300</v>
       </c>
       <c r="O728" t="n">
-        <v>158400</v>
+        <v>168300</v>
       </c>
       <c r="P728" t="n">
-        <v>24900</v>
+        <v>19500</v>
       </c>
       <c r="Q728" t="n">
-        <v>199200</v>
+        <v>214500</v>
       </c>
     </row>
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>DPC030</t>
+          <t>DPC033</t>
         </is>
       </c>
       <c r="C729" t="inlineStr">
         <is>
-          <t>PELUCHE PANDA HIJO 35cm DP2512.032/DPC030</t>
+          <t>PELUCHE ECO STD 20cm DP2503-003/033/AZ-025/DP2512-026</t>
         </is>
       </c>
       <c r="E729" t="inlineStr">
@@ -33449,7 +33459,7 @@
         </is>
       </c>
       <c r="J729" t="n">
-        <v>19</v>
+        <v>402</v>
       </c>
       <c r="K729" t="n">
         <v>0</v>
@@ -33458,35 +33468,35 @@
         <v>0</v>
       </c>
       <c r="M729" t="n">
-        <v>19</v>
+        <v>402</v>
       </c>
       <c r="N729" t="n">
-        <v>20700</v>
+        <v>5218.9108910891</v>
       </c>
       <c r="O729" t="n">
-        <v>393300</v>
+        <v>2098002.178217818</v>
       </c>
       <c r="P729" t="n">
-        <v>25900</v>
+        <v>6500</v>
       </c>
       <c r="Q729" t="n">
-        <v>492100</v>
+        <v>2613000</v>
       </c>
     </row>
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>DPC031</t>
+          <t>DPC034</t>
         </is>
       </c>
       <c r="C730" t="inlineStr">
         <is>
-          <t>PELUCHE ERIZO 28cm DP2512-064/DPC031</t>
+          <t>PELUCHE OSO MOÑO  20CM  DP2503-22/DPC034</t>
         </is>
       </c>
       <c r="E730" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PELUCHES</t>
         </is>
       </c>
       <c r="I730" t="inlineStr">
@@ -33495,7 +33505,7 @@
         </is>
       </c>
       <c r="J730" t="n">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="K730" t="n">
         <v>0</v>
@@ -33504,30 +33514,30 @@
         <v>0</v>
       </c>
       <c r="M730" t="n">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="N730" t="n">
-        <v>15300</v>
+        <v>5850</v>
       </c>
       <c r="O730" t="n">
-        <v>168300</v>
+        <v>298350</v>
       </c>
       <c r="P730" t="n">
-        <v>19500</v>
+        <v>7900</v>
       </c>
       <c r="Q730" t="n">
-        <v>214500</v>
+        <v>402900</v>
       </c>
     </row>
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>DPC033</t>
+          <t>DPC035</t>
         </is>
       </c>
       <c r="C731" t="inlineStr">
         <is>
-          <t>PELUCHE ECO STD 20cm DP2503-003/033/AZ-025/DP2512-026</t>
+          <t>PELUCHE COJIN CORAZON  25 X25 CM  DP2503-005/DPC035</t>
         </is>
       </c>
       <c r="E731" t="inlineStr">
@@ -33541,7 +33551,7 @@
         </is>
       </c>
       <c r="J731" t="n">
-        <v>402</v>
+        <v>36</v>
       </c>
       <c r="K731" t="n">
         <v>0</v>
@@ -33550,30 +33560,30 @@
         <v>0</v>
       </c>
       <c r="M731" t="n">
-        <v>402</v>
+        <v>36</v>
       </c>
       <c r="N731" t="n">
-        <v>5218.9108910891</v>
+        <v>5220</v>
       </c>
       <c r="O731" t="n">
-        <v>2098002.178217818</v>
+        <v>187920</v>
       </c>
       <c r="P731" t="n">
-        <v>6500</v>
+        <v>6900</v>
       </c>
       <c r="Q731" t="n">
-        <v>2613000</v>
+        <v>248400</v>
       </c>
     </row>
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>DPC034</t>
+          <t>DPC036</t>
         </is>
       </c>
       <c r="C732" t="inlineStr">
         <is>
-          <t>PELUCHE OSO MOÑO  20CM  DP2503-22/DPC034</t>
+          <t>PELUCHE TORTUGA 25CM DP2512-003/DPC036</t>
         </is>
       </c>
       <c r="E732" t="inlineStr">
@@ -33587,39 +33597,39 @@
         </is>
       </c>
       <c r="J732" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="K732" t="n">
         <v>0</v>
       </c>
       <c r="L732" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M732" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="N732" t="n">
-        <v>5850</v>
+        <v>5220</v>
       </c>
       <c r="O732" t="n">
-        <v>298350</v>
+        <v>292320</v>
       </c>
       <c r="P732" t="n">
-        <v>7900</v>
+        <v>7500</v>
       </c>
       <c r="Q732" t="n">
-        <v>402900</v>
+        <v>420000</v>
       </c>
     </row>
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>DPC035</t>
+          <t>DPC037</t>
         </is>
       </c>
       <c r="C733" t="inlineStr">
         <is>
-          <t>PELUCHE COJIN CORAZON  25 X25 CM  DP2503-005/DPC035</t>
+          <t>PELUCHE OSO CORBATA SATIN 28cm DP2512-061/DPC037</t>
         </is>
       </c>
       <c r="E733" t="inlineStr">
@@ -33633,7 +33643,7 @@
         </is>
       </c>
       <c r="J733" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="K733" t="n">
         <v>0</v>
@@ -33642,35 +33652,35 @@
         <v>0</v>
       </c>
       <c r="M733" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="N733" t="n">
-        <v>5220</v>
+        <v>7650</v>
       </c>
       <c r="O733" t="n">
-        <v>187920</v>
+        <v>344250</v>
       </c>
       <c r="P733" t="n">
-        <v>6900</v>
+        <v>9900</v>
       </c>
       <c r="Q733" t="n">
-        <v>248400</v>
+        <v>445500</v>
       </c>
     </row>
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>DPC036</t>
+          <t>DPC038</t>
         </is>
       </c>
       <c r="C734" t="inlineStr">
         <is>
-          <t>PELUCHE TORTUGA 25CM DP2512-003/DPC036</t>
+          <t>PELUCHE GATA CONEJO OSO 28cm DP2512-008/DPC038</t>
         </is>
       </c>
       <c r="E734" t="inlineStr">
         <is>
-          <t>PELUCHES</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I734" t="inlineStr">
@@ -33679,7 +33689,7 @@
         </is>
       </c>
       <c r="J734" t="n">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="K734" t="n">
         <v>0</v>
@@ -33688,30 +33698,30 @@
         <v>0</v>
       </c>
       <c r="M734" t="n">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="N734" t="n">
-        <v>5220</v>
+        <v>13500</v>
       </c>
       <c r="O734" t="n">
-        <v>292320</v>
+        <v>189000</v>
       </c>
       <c r="P734" t="n">
-        <v>7500</v>
+        <v>16900</v>
       </c>
       <c r="Q734" t="n">
-        <v>420000</v>
+        <v>236600</v>
       </c>
     </row>
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>DPC037</t>
+          <t>DPC039</t>
         </is>
       </c>
       <c r="C735" t="inlineStr">
         <is>
-          <t>PELUCHE OSO CORBATA SATIN 28cm DP2512-061/DPC037</t>
+          <t>PELUCHE OSO PAVA CORAZON 30cm DP2503-058/DPC039</t>
         </is>
       </c>
       <c r="E735" t="inlineStr">
@@ -33725,39 +33735,39 @@
         </is>
       </c>
       <c r="J735" t="n">
-        <v>57</v>
+        <v>9</v>
       </c>
       <c r="K735" t="n">
         <v>0</v>
       </c>
       <c r="L735" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M735" t="n">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="N735" t="n">
-        <v>7650</v>
+        <v>19800</v>
       </c>
       <c r="O735" t="n">
-        <v>344250</v>
+        <v>178200</v>
       </c>
       <c r="P735" t="n">
-        <v>9900</v>
+        <v>24900</v>
       </c>
       <c r="Q735" t="n">
-        <v>445500</v>
+        <v>224100</v>
       </c>
     </row>
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>DPC038</t>
+          <t>DPC041</t>
         </is>
       </c>
       <c r="C736" t="inlineStr">
         <is>
-          <t>PELUCHE GATA CONEJO OSO 28cm DP2512-008/DPC038</t>
+          <t>PELUCHE PERRO SOMBRERO 40cm DP2503-065/DPC041</t>
         </is>
       </c>
       <c r="E736" t="inlineStr">
@@ -33771,44 +33781,44 @@
         </is>
       </c>
       <c r="J736" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="K736" t="n">
         <v>0</v>
       </c>
       <c r="L736" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M736" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="N736" t="n">
-        <v>13500</v>
+        <v>31500</v>
       </c>
       <c r="O736" t="n">
-        <v>189000</v>
+        <v>315000</v>
       </c>
       <c r="P736" t="n">
-        <v>16900</v>
+        <v>39900</v>
       </c>
       <c r="Q736" t="n">
-        <v>236600</v>
+        <v>399000</v>
       </c>
     </row>
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>DPC039</t>
+          <t>DPC042</t>
         </is>
       </c>
       <c r="C737" t="inlineStr">
         <is>
-          <t>PELUCHE OSO PAVA CORAZON 30cm DP2503-058/DPC039</t>
+          <t>PELUCHE KOALA HIJO 35cm DP2503-048/DPC042</t>
         </is>
       </c>
       <c r="E737" t="inlineStr">
         <is>
-          <t>PELUCHES</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I737" t="inlineStr">
@@ -33835,26 +33845,26 @@
         <v>178200</v>
       </c>
       <c r="P737" t="n">
-        <v>24900</v>
+        <v>25900</v>
       </c>
       <c r="Q737" t="n">
-        <v>224100</v>
+        <v>233100</v>
       </c>
     </row>
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>DPC041</t>
+          <t>DPC043</t>
         </is>
       </c>
       <c r="C738" t="inlineStr">
         <is>
-          <t>PELUCHE PERRO SOMBRERO 40cm DP2503-065/DPC041</t>
+          <t>PELUCHE OSO BORDADO 30cm AB-46BORDADC/DPC043</t>
         </is>
       </c>
       <c r="E738" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PELUCHES</t>
         </is>
       </c>
       <c r="I738" t="inlineStr">
@@ -33863,7 +33873,7 @@
         </is>
       </c>
       <c r="J738" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K738" t="n">
         <v>0</v>
@@ -33872,30 +33882,30 @@
         <v>0</v>
       </c>
       <c r="M738" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N738" t="n">
-        <v>31500</v>
+        <v>18000</v>
       </c>
       <c r="O738" t="n">
-        <v>315000</v>
+        <v>144000</v>
       </c>
       <c r="P738" t="n">
-        <v>39900</v>
+        <v>23900</v>
       </c>
       <c r="Q738" t="n">
-        <v>399000</v>
+        <v>191200</v>
       </c>
     </row>
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>DPC042</t>
+          <t>DPC044</t>
         </is>
       </c>
       <c r="C739" t="inlineStr">
         <is>
-          <t>PELUCHE KOALA HIJO 35cm DP2503-048/DPC042</t>
+          <t>PELUCHE ABRAZADOS 20cm WZ-44/DPC044</t>
         </is>
       </c>
       <c r="E739" t="inlineStr">
@@ -33909,7 +33919,7 @@
         </is>
       </c>
       <c r="J739" t="n">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="K739" t="n">
         <v>0</v>
@@ -33918,30 +33928,30 @@
         <v>0</v>
       </c>
       <c r="M739" t="n">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="N739" t="n">
-        <v>19800</v>
+        <v>9000</v>
       </c>
       <c r="O739" t="n">
-        <v>178200</v>
+        <v>414000</v>
       </c>
       <c r="P739" t="n">
-        <v>25900</v>
+        <v>11500</v>
       </c>
       <c r="Q739" t="n">
-        <v>233100</v>
+        <v>529000</v>
       </c>
     </row>
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>DPC043</t>
+          <t>DPC047</t>
         </is>
       </c>
       <c r="C740" t="inlineStr">
         <is>
-          <t>PELUCHE OSO BORDADO 30cm AB-46BORDADC/DPC043</t>
+          <t>PELUCHE OSO CORAZON ROJO MOÑO 30cm DP2512-005/DPC047</t>
         </is>
       </c>
       <c r="E740" t="inlineStr">
@@ -33955,7 +33965,7 @@
         </is>
       </c>
       <c r="J740" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K740" t="n">
         <v>0</v>
@@ -33964,35 +33974,35 @@
         <v>0</v>
       </c>
       <c r="M740" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="N740" t="n">
-        <v>18000</v>
+        <v>18900</v>
       </c>
       <c r="O740" t="n">
-        <v>144000</v>
+        <v>226800</v>
       </c>
       <c r="P740" t="n">
-        <v>23900</v>
+        <v>24900</v>
       </c>
       <c r="Q740" t="n">
-        <v>191200</v>
+        <v>298800</v>
       </c>
     </row>
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>DPC044</t>
+          <t>DPC048</t>
         </is>
       </c>
       <c r="C741" t="inlineStr">
         <is>
-          <t>PELUCHE ABRAZADOS 20cm WZ-44/DPC044</t>
+          <t>PELUCHE ELEFANTE CORONA 28cm DP2512-056/DPC048</t>
         </is>
       </c>
       <c r="E741" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PELUCHES</t>
         </is>
       </c>
       <c r="I741" t="inlineStr">
@@ -34001,39 +34011,39 @@
         </is>
       </c>
       <c r="J741" t="n">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="K741" t="n">
         <v>0</v>
       </c>
       <c r="L741" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M741" t="n">
-        <v>46</v>
+        <v>6</v>
       </c>
       <c r="N741" t="n">
-        <v>9000</v>
+        <v>13500</v>
       </c>
       <c r="O741" t="n">
-        <v>414000</v>
+        <v>81000</v>
       </c>
       <c r="P741" t="n">
-        <v>11500</v>
+        <v>16900</v>
       </c>
       <c r="Q741" t="n">
-        <v>529000</v>
+        <v>101400</v>
       </c>
     </row>
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>DPC047</t>
+          <t>DPC050</t>
         </is>
       </c>
       <c r="C742" t="inlineStr">
         <is>
-          <t>PELUCHE OSO CORAZON ROJO MOÑO 30cm DP2512-005/DPC047</t>
+          <t>PELUCHE PERRO OJO PARCHE 30cm DP2512-029/DPC050</t>
         </is>
       </c>
       <c r="E742" t="inlineStr">
@@ -34047,7 +34057,7 @@
         </is>
       </c>
       <c r="J742" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="K742" t="n">
         <v>0</v>
@@ -34056,30 +34066,30 @@
         <v>0</v>
       </c>
       <c r="M742" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="N742" t="n">
-        <v>18900</v>
+        <v>18000</v>
       </c>
       <c r="O742" t="n">
-        <v>226800</v>
+        <v>432000</v>
       </c>
       <c r="P742" t="n">
-        <v>24900</v>
+        <v>22500</v>
       </c>
       <c r="Q742" t="n">
-        <v>298800</v>
+        <v>540000</v>
       </c>
     </row>
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>DPC048</t>
+          <t>DPC051</t>
         </is>
       </c>
       <c r="C743" t="inlineStr">
         <is>
-          <t>PELUCHE ELEFANTE CORONA 28cm DP2512-056/DPC048</t>
+          <t>PELUCHE MINNIE 45cm DP2512-147/DPC051</t>
         </is>
       </c>
       <c r="E743" t="inlineStr">
@@ -34093,44 +34103,44 @@
         </is>
       </c>
       <c r="J743" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="K743" t="n">
         <v>0</v>
       </c>
       <c r="L743" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M743" t="n">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="N743" t="n">
-        <v>13500</v>
+        <v>31500</v>
       </c>
       <c r="O743" t="n">
-        <v>81000</v>
+        <v>1890000</v>
       </c>
       <c r="P743" t="n">
-        <v>16900</v>
+        <v>39500</v>
       </c>
       <c r="Q743" t="n">
-        <v>101400</v>
+        <v>2370000</v>
       </c>
     </row>
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>DPC050</t>
+          <t>DPC052</t>
         </is>
       </c>
       <c r="C744" t="inlineStr">
         <is>
-          <t>PELUCHE PERRO OJO PARCHE 30cm DP2512-029/DPC050</t>
+          <t>PELUCHE COCODRILLO 60CM DPC052</t>
         </is>
       </c>
       <c r="E744" t="inlineStr">
         <is>
-          <t>PELUCHES</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I744" t="inlineStr">
@@ -34139,7 +34149,7 @@
         </is>
       </c>
       <c r="J744" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="K744" t="n">
         <v>0</v>
@@ -34148,30 +34158,30 @@
         <v>0</v>
       </c>
       <c r="M744" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="N744" t="n">
-        <v>18000</v>
+        <v>27900</v>
       </c>
       <c r="O744" t="n">
-        <v>432000</v>
+        <v>167400</v>
       </c>
       <c r="P744" t="n">
-        <v>22500</v>
+        <v>34900</v>
       </c>
       <c r="Q744" t="n">
-        <v>540000</v>
+        <v>209400</v>
       </c>
     </row>
     <row r="745">
       <c r="A745" t="inlineStr">
         <is>
-          <t>DPC051</t>
+          <t>DPC057</t>
         </is>
       </c>
       <c r="C745" t="inlineStr">
         <is>
-          <t>PELUCHE MINNIE 45cm DP2512-147/DPC051</t>
+          <t>PELUCHE OSO CORAZON LOVE 40cm DP2512-060/DPC057</t>
         </is>
       </c>
       <c r="E745" t="inlineStr">
@@ -34185,7 +34195,7 @@
         </is>
       </c>
       <c r="J745" t="n">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="K745" t="n">
         <v>0</v>
@@ -34194,35 +34204,35 @@
         <v>0</v>
       </c>
       <c r="M745" t="n">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="N745" t="n">
-        <v>31500</v>
+        <v>25200</v>
       </c>
       <c r="O745" t="n">
-        <v>1890000</v>
+        <v>201600</v>
       </c>
       <c r="P745" t="n">
-        <v>39500</v>
+        <v>31900</v>
       </c>
       <c r="Q745" t="n">
-        <v>2370000</v>
+        <v>255200</v>
       </c>
     </row>
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>DPC052</t>
+          <t>DPC059</t>
         </is>
       </c>
       <c r="C746" t="inlineStr">
         <is>
-          <t>PELUCHE COCODRILLO 60CM DPC052</t>
+          <t>PELUCHE TORO 40cm DP2512-028/DPC059</t>
         </is>
       </c>
       <c r="E746" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PELUCHES</t>
         </is>
       </c>
       <c r="I746" t="inlineStr">
@@ -34231,7 +34241,7 @@
         </is>
       </c>
       <c r="J746" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K746" t="n">
         <v>0</v>
@@ -34240,30 +34250,30 @@
         <v>0</v>
       </c>
       <c r="M746" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N746" t="n">
-        <v>27900</v>
+        <v>22500</v>
       </c>
       <c r="O746" t="n">
-        <v>167400</v>
+        <v>45000</v>
       </c>
       <c r="P746" t="n">
-        <v>34900</v>
+        <v>28900</v>
       </c>
       <c r="Q746" t="n">
-        <v>209400</v>
+        <v>57800</v>
       </c>
     </row>
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>DPC057</t>
+          <t>DPC060</t>
         </is>
       </c>
       <c r="C747" t="inlineStr">
         <is>
-          <t>PELUCHE OSO CORAZON LOVE 40cm DP2512-060/DPC057</t>
+          <t>PELUCHE MUÑECA 30cm DP2512-017/DPC060</t>
         </is>
       </c>
       <c r="E747" t="inlineStr">
@@ -34277,7 +34287,7 @@
         </is>
       </c>
       <c r="J747" t="n">
-        <v>8</v>
+        <v>120</v>
       </c>
       <c r="K747" t="n">
         <v>0</v>
@@ -34286,35 +34296,35 @@
         <v>0</v>
       </c>
       <c r="M747" t="n">
-        <v>8</v>
+        <v>120</v>
       </c>
       <c r="N747" t="n">
-        <v>25200</v>
+        <v>7200</v>
       </c>
       <c r="O747" t="n">
-        <v>201600</v>
+        <v>864000</v>
       </c>
       <c r="P747" t="n">
-        <v>31900</v>
+        <v>8900</v>
       </c>
       <c r="Q747" t="n">
-        <v>255200</v>
+        <v>1068000</v>
       </c>
     </row>
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>DPC059</t>
+          <t>DPC062</t>
         </is>
       </c>
       <c r="C748" t="inlineStr">
         <is>
-          <t>PELUCHE TORO 40cm DP2512-028/DPC059</t>
+          <t>PELUCHE MUÑECA 50cm DP2512-019/DPC062</t>
         </is>
       </c>
       <c r="E748" t="inlineStr">
         <is>
-          <t>PELUCHES</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I748" t="inlineStr">
@@ -34323,7 +34333,7 @@
         </is>
       </c>
       <c r="J748" t="n">
-        <v>2</v>
+        <v>54</v>
       </c>
       <c r="K748" t="n">
         <v>0</v>
@@ -34332,30 +34342,30 @@
         <v>0</v>
       </c>
       <c r="M748" t="n">
-        <v>2</v>
+        <v>54</v>
       </c>
       <c r="N748" t="n">
-        <v>22500</v>
+        <v>13500</v>
       </c>
       <c r="O748" t="n">
-        <v>45000</v>
+        <v>729000</v>
       </c>
       <c r="P748" t="n">
-        <v>28900</v>
+        <v>16900</v>
       </c>
       <c r="Q748" t="n">
-        <v>57800</v>
+        <v>912600</v>
       </c>
     </row>
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
-          <t>DPC06</t>
+          <t>DPC066</t>
         </is>
       </c>
       <c r="C749" t="inlineStr">
         <is>
-          <t>PELUCHE OSO 3 COLORES 30CM AB-46 DPC06</t>
+          <t>PELUCHE MUÑECA TRAPO 40cm DP2512-0187DPC066</t>
         </is>
       </c>
       <c r="E749" t="inlineStr">
@@ -34369,39 +34379,39 @@
         </is>
       </c>
       <c r="J749" t="n">
-        <v>6</v>
+        <v>54</v>
       </c>
       <c r="K749" t="n">
         <v>0</v>
       </c>
       <c r="L749" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M749" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="N749" t="n">
-        <v>12601.09</v>
+        <v>10800</v>
       </c>
       <c r="O749" t="n">
-        <v>0</v>
+        <v>583200</v>
       </c>
       <c r="P749" t="n">
-        <v>15900</v>
+        <v>13500</v>
       </c>
       <c r="Q749" t="n">
-        <v>0</v>
+        <v>729000</v>
       </c>
     </row>
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
-          <t>DPC060</t>
+          <t>DPC075</t>
         </is>
       </c>
       <c r="C750" t="inlineStr">
         <is>
-          <t>PELUCHE MUÑECA 30cm DP2512-017/DPC060</t>
+          <t>PELUCHE OSO CON HIJO 40cm DP2512-048/DPC075</t>
         </is>
       </c>
       <c r="E750" t="inlineStr">
@@ -34415,7 +34425,7 @@
         </is>
       </c>
       <c r="J750" t="n">
-        <v>120</v>
+        <v>12</v>
       </c>
       <c r="K750" t="n">
         <v>0</v>
@@ -34424,35 +34434,35 @@
         <v>0</v>
       </c>
       <c r="M750" t="n">
-        <v>120</v>
+        <v>12</v>
       </c>
       <c r="N750" t="n">
-        <v>7200</v>
+        <v>29700</v>
       </c>
       <c r="O750" t="n">
-        <v>864000</v>
+        <v>356400</v>
       </c>
       <c r="P750" t="n">
-        <v>8900</v>
+        <v>39900</v>
       </c>
       <c r="Q750" t="n">
-        <v>1068000</v>
+        <v>478800</v>
       </c>
     </row>
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
-          <t>DPC062</t>
+          <t>DPC078</t>
         </is>
       </c>
       <c r="C751" t="inlineStr">
         <is>
-          <t>PELUCHE MUÑECA 50cm DP2512-019/DPC062</t>
+          <t>PELUCHE OSO GRD 40cm DP2512-067/DPC078</t>
         </is>
       </c>
       <c r="E751" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PELUCHES</t>
         </is>
       </c>
       <c r="I751" t="inlineStr">
@@ -34461,7 +34471,7 @@
         </is>
       </c>
       <c r="J751" t="n">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="K751" t="n">
         <v>0</v>
@@ -34470,35 +34480,35 @@
         <v>0</v>
       </c>
       <c r="M751" t="n">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="N751" t="n">
-        <v>13500</v>
+        <v>31500</v>
       </c>
       <c r="O751" t="n">
-        <v>729000</v>
+        <v>661500</v>
       </c>
       <c r="P751" t="n">
-        <v>16900</v>
+        <v>39900</v>
       </c>
       <c r="Q751" t="n">
-        <v>912600</v>
+        <v>837900</v>
       </c>
     </row>
     <row r="752">
       <c r="A752" t="inlineStr">
         <is>
-          <t>DPC066</t>
+          <t>DPC080</t>
         </is>
       </c>
       <c r="C752" t="inlineStr">
         <is>
-          <t>PELUCHE MUÑECA TRAPO 40cm DP2512-0187DPC066</t>
+          <t>PELUCHE PERRO CON HIJO 45cm DP2512-047/DPC080</t>
         </is>
       </c>
       <c r="E752" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PELUCHES</t>
         </is>
       </c>
       <c r="I752" t="inlineStr">
@@ -34507,7 +34517,7 @@
         </is>
       </c>
       <c r="J752" t="n">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="K752" t="n">
         <v>0</v>
@@ -34516,35 +34526,35 @@
         <v>0</v>
       </c>
       <c r="M752" t="n">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="N752" t="n">
-        <v>10800</v>
+        <v>31500</v>
       </c>
       <c r="O752" t="n">
-        <v>583200</v>
+        <v>31500</v>
       </c>
       <c r="P752" t="n">
-        <v>13500</v>
+        <v>39900</v>
       </c>
       <c r="Q752" t="n">
-        <v>729000</v>
+        <v>39900</v>
       </c>
     </row>
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>DPC068</t>
+          <t>DPC082</t>
         </is>
       </c>
       <c r="C753" t="inlineStr">
         <is>
-          <t>PELUCHE GATO 30cm DP2512-055/DPC068</t>
+          <t>PELUCHE VACA PARADA 28cm 064a-3/DPC082</t>
         </is>
       </c>
       <c r="E753" t="inlineStr">
         <is>
-          <t>PELUCHES</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I753" t="inlineStr">
@@ -34553,44 +34563,44 @@
         </is>
       </c>
       <c r="J753" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="K753" t="n">
         <v>0</v>
       </c>
       <c r="L753" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M753" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="N753" t="n">
-        <v>0</v>
+        <v>9450</v>
       </c>
       <c r="O753" t="n">
-        <v>0</v>
+        <v>189000</v>
       </c>
       <c r="P753" t="n">
-        <v>16900</v>
+        <v>11900</v>
       </c>
       <c r="Q753" t="n">
-        <v>0</v>
+        <v>238000</v>
       </c>
     </row>
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>DPC075</t>
+          <t>DPC084</t>
         </is>
       </c>
       <c r="C754" t="inlineStr">
         <is>
-          <t>PELUCHE OSO CON HIJO 40cm DP2512-048/DPC075</t>
+          <t>PELUCHE MINNIE MICKEY 70cm DP2512-148/DPC084</t>
         </is>
       </c>
       <c r="E754" t="inlineStr">
         <is>
-          <t>PELUCHES</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I754" t="inlineStr">
@@ -34599,7 +34609,7 @@
         </is>
       </c>
       <c r="J754" t="n">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="K754" t="n">
         <v>0</v>
@@ -34608,35 +34618,35 @@
         <v>0</v>
       </c>
       <c r="M754" t="n">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="N754" t="n">
-        <v>29700</v>
+        <v>36000</v>
       </c>
       <c r="O754" t="n">
-        <v>356400</v>
+        <v>1944000</v>
       </c>
       <c r="P754" t="n">
-        <v>39900</v>
+        <v>45000</v>
       </c>
       <c r="Q754" t="n">
-        <v>478800</v>
+        <v>2430000</v>
       </c>
     </row>
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>DPC078</t>
+          <t>DPC085</t>
         </is>
       </c>
       <c r="C755" t="inlineStr">
         <is>
-          <t>PELUCHE OSO GRD 40cm DP2512-067/DPC078</t>
+          <t>PELUCHE OSO CORAZON 50m DP2512-013/DPC085</t>
         </is>
       </c>
       <c r="E755" t="inlineStr">
         <is>
-          <t>PELUCHES</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I755" t="inlineStr">
@@ -34645,7 +34655,7 @@
         </is>
       </c>
       <c r="J755" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="K755" t="n">
         <v>0</v>
@@ -34654,35 +34664,35 @@
         <v>0</v>
       </c>
       <c r="M755" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="N755" t="n">
-        <v>31500</v>
+        <v>36000</v>
       </c>
       <c r="O755" t="n">
-        <v>661500</v>
+        <v>72000</v>
       </c>
       <c r="P755" t="n">
-        <v>39900</v>
+        <v>45000</v>
       </c>
       <c r="Q755" t="n">
-        <v>837900</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>DPC080</t>
+          <t>DPC086</t>
         </is>
       </c>
       <c r="C756" t="inlineStr">
         <is>
-          <t>PELUCHE PERRO CON HIJO 45cm DP2512-047/DPC080</t>
+          <t>PELUCHE OS CORAZON TE AMO 50cm DP2512-012/DPC086</t>
         </is>
       </c>
       <c r="E756" t="inlineStr">
         <is>
-          <t>PELUCHES</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I756" t="inlineStr">
@@ -34691,7 +34701,7 @@
         </is>
       </c>
       <c r="J756" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K756" t="n">
         <v>0</v>
@@ -34700,30 +34710,30 @@
         <v>0</v>
       </c>
       <c r="M756" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N756" t="n">
-        <v>31500</v>
+        <v>36000</v>
       </c>
       <c r="O756" t="n">
-        <v>31500</v>
+        <v>144000</v>
       </c>
       <c r="P756" t="n">
-        <v>39900</v>
+        <v>45000</v>
       </c>
       <c r="Q756" t="n">
-        <v>39900</v>
+        <v>180000</v>
       </c>
     </row>
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>DPC082</t>
+          <t>DPC087</t>
         </is>
       </c>
       <c r="C757" t="inlineStr">
         <is>
-          <t>PELUCHE VACA PARADA 28cm 064a-3/DPC082</t>
+          <t>PELUCHE OSO CORAZON AMOR 55cm DP2512-037/DPC087</t>
         </is>
       </c>
       <c r="E757" t="inlineStr">
@@ -34737,39 +34747,39 @@
         </is>
       </c>
       <c r="J757" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="K757" t="n">
         <v>0</v>
       </c>
       <c r="L757" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M757" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="N757" t="n">
-        <v>9450</v>
+        <v>40500</v>
       </c>
       <c r="O757" t="n">
-        <v>189000</v>
+        <v>81000</v>
       </c>
       <c r="P757" t="n">
-        <v>11900</v>
+        <v>50900</v>
       </c>
       <c r="Q757" t="n">
-        <v>238000</v>
+        <v>101800</v>
       </c>
     </row>
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>DPC084</t>
+          <t>DPC088</t>
         </is>
       </c>
       <c r="C758" t="inlineStr">
         <is>
-          <t>PELUCHE MINNIE MICKEY 70cm DP2512-148/DPC084</t>
+          <t>PELUCHE OSO MIEL 70cm DP2512-070/DPC088</t>
         </is>
       </c>
       <c r="E758" t="inlineStr">
@@ -34783,7 +34793,7 @@
         </is>
       </c>
       <c r="J758" t="n">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="K758" t="n">
         <v>0</v>
@@ -34792,30 +34802,30 @@
         <v>0</v>
       </c>
       <c r="M758" t="n">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="N758" t="n">
-        <v>36000</v>
+        <v>54000</v>
       </c>
       <c r="O758" t="n">
-        <v>1944000</v>
+        <v>108000</v>
       </c>
       <c r="P758" t="n">
-        <v>45000</v>
+        <v>69900</v>
       </c>
       <c r="Q758" t="n">
-        <v>2430000</v>
+        <v>139800</v>
       </c>
     </row>
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
-          <t>DPC085</t>
+          <t>DPC089</t>
         </is>
       </c>
       <c r="C759" t="inlineStr">
         <is>
-          <t>PELUCHE OSO CORAZON 50m DP2512-013/DPC085</t>
+          <t>PELUCHE OSO LOVE PECHO 70cm DP2512-034/DPC089</t>
         </is>
       </c>
       <c r="E759" t="inlineStr">
@@ -34829,7 +34839,7 @@
         </is>
       </c>
       <c r="J759" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K759" t="n">
         <v>0</v>
@@ -34838,30 +34848,30 @@
         <v>0</v>
       </c>
       <c r="M759" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N759" t="n">
-        <v>36000</v>
+        <v>54000</v>
       </c>
       <c r="O759" t="n">
-        <v>72000</v>
+        <v>54000</v>
       </c>
       <c r="P759" t="n">
-        <v>45000</v>
+        <v>69900</v>
       </c>
       <c r="Q759" t="n">
-        <v>90000</v>
+        <v>69900</v>
       </c>
     </row>
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>DPC086</t>
+          <t>DPC090</t>
         </is>
       </c>
       <c r="C760" t="inlineStr">
         <is>
-          <t>PELUCHE OS CORAZON TE AMO 50cm DP2512-012/DPC086</t>
+          <t>PELUCHE OSO CORAZON BORDADO PATA BOLSILLO 70cm DP2512-034/DPC090</t>
         </is>
       </c>
       <c r="E760" t="inlineStr">
@@ -34875,7 +34885,7 @@
         </is>
       </c>
       <c r="J760" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K760" t="n">
         <v>0</v>
@@ -34884,30 +34894,30 @@
         <v>0</v>
       </c>
       <c r="M760" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N760" t="n">
-        <v>36000</v>
+        <v>54000</v>
       </c>
       <c r="O760" t="n">
-        <v>144000</v>
+        <v>162000</v>
       </c>
       <c r="P760" t="n">
-        <v>45000</v>
+        <v>69900</v>
       </c>
       <c r="Q760" t="n">
-        <v>180000</v>
+        <v>209700</v>
       </c>
     </row>
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>DPC087</t>
+          <t>DPC091</t>
         </is>
       </c>
       <c r="C761" t="inlineStr">
         <is>
-          <t>PELUCHE OSO CORAZON AMOR 55cm DP2512-037/DPC087</t>
+          <t>PELUCHE OSO CORBATA GARRA 70cm DP2512-036/DPC091</t>
         </is>
       </c>
       <c r="E761" t="inlineStr">
@@ -34921,44 +34931,44 @@
         </is>
       </c>
       <c r="J761" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K761" t="n">
         <v>0</v>
       </c>
       <c r="L761" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M761" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N761" t="n">
-        <v>40500</v>
+        <v>58500</v>
       </c>
       <c r="O761" t="n">
-        <v>81000</v>
+        <v>175500</v>
       </c>
       <c r="P761" t="n">
-        <v>50900</v>
+        <v>73900</v>
       </c>
       <c r="Q761" t="n">
-        <v>101800</v>
+        <v>221700</v>
       </c>
     </row>
     <row r="762">
       <c r="A762" t="inlineStr">
         <is>
-          <t>DPC088</t>
+          <t>DPC16</t>
         </is>
       </c>
       <c r="C762" t="inlineStr">
         <is>
-          <t>PELUCHE OSO MIEL 70cm DP2512-070/DPC088</t>
+          <t>PELUCHE  UNICORNIO PARADO 45cm DP2503-047/DPC16</t>
         </is>
       </c>
       <c r="E762" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PELUCHES</t>
         </is>
       </c>
       <c r="I762" t="inlineStr">
@@ -34967,7 +34977,7 @@
         </is>
       </c>
       <c r="J762" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="K762" t="n">
         <v>0</v>
@@ -34976,35 +34986,35 @@
         <v>0</v>
       </c>
       <c r="M762" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="N762" t="n">
-        <v>54000</v>
+        <v>28800</v>
       </c>
       <c r="O762" t="n">
-        <v>108000</v>
+        <v>633600</v>
       </c>
       <c r="P762" t="n">
-        <v>69900</v>
+        <v>36000</v>
       </c>
       <c r="Q762" t="n">
-        <v>139800</v>
+        <v>792000</v>
       </c>
     </row>
     <row r="763">
       <c r="A763" t="inlineStr">
         <is>
-          <t>DPC089</t>
+          <t>FG033</t>
         </is>
       </c>
       <c r="C763" t="inlineStr">
         <is>
-          <t>PELUCHE OSO LOVE PECHO 70cm DP2512-034/DPC089</t>
+          <t>CHILLON X 6 TRANSPORTE 192</t>
         </is>
       </c>
       <c r="E763" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I763" t="inlineStr">
@@ -35013,7 +35023,7 @@
         </is>
       </c>
       <c r="J763" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="K763" t="n">
         <v>0</v>
@@ -35022,35 +35032,35 @@
         <v>0</v>
       </c>
       <c r="M763" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="N763" t="n">
-        <v>54000</v>
+        <v>10335.44</v>
       </c>
       <c r="O763" t="n">
-        <v>54000</v>
+        <v>217044.24</v>
       </c>
       <c r="P763" t="n">
-        <v>69900</v>
+        <v>10900</v>
       </c>
       <c r="Q763" t="n">
-        <v>69900</v>
+        <v>228900</v>
       </c>
     </row>
     <row r="764">
       <c r="A764" t="inlineStr">
         <is>
-          <t>DPC090</t>
+          <t>FG039</t>
         </is>
       </c>
       <c r="C764" t="inlineStr">
         <is>
-          <t>PELUCHE OSO CORAZON BORDADO PATA BOLSILLO 70cm DP2512-034/DPC090</t>
+          <t>GAFA DE NATACION BLISTER 2404-2</t>
         </is>
       </c>
       <c r="E764" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I764" t="inlineStr">
@@ -35059,7 +35069,7 @@
         </is>
       </c>
       <c r="J764" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="K764" t="n">
         <v>0</v>
@@ -35068,35 +35078,35 @@
         <v>0</v>
       </c>
       <c r="M764" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="N764" t="n">
-        <v>54000</v>
+        <v>2644.9</v>
       </c>
       <c r="O764" t="n">
-        <v>162000</v>
+        <v>66122.5</v>
       </c>
       <c r="P764" t="n">
-        <v>69900</v>
+        <v>3900</v>
       </c>
       <c r="Q764" t="n">
-        <v>209700</v>
+        <v>97500</v>
       </c>
     </row>
     <row r="765">
       <c r="A765" t="inlineStr">
         <is>
-          <t>DPC091</t>
+          <t>FG050</t>
         </is>
       </c>
       <c r="C765" t="inlineStr">
         <is>
-          <t>PELUCHE OSO CORBATA GARRA 70cm DP2512-036/DPC091</t>
+          <t>CARRO DINOSAURIO X3 757-46 KZ958-1103E</t>
         </is>
       </c>
       <c r="E765" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I765" t="inlineStr">
@@ -35105,44 +35115,44 @@
         </is>
       </c>
       <c r="J765" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K765" t="n">
         <v>0</v>
       </c>
       <c r="L765" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M765" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N765" t="n">
-        <v>58500</v>
+        <v>9708.190000000001</v>
       </c>
       <c r="O765" t="n">
-        <v>175500</v>
+        <v>19416.38</v>
       </c>
       <c r="P765" t="n">
-        <v>73900</v>
+        <v>10200</v>
       </c>
       <c r="Q765" t="n">
-        <v>221700</v>
+        <v>20400</v>
       </c>
     </row>
     <row r="766">
       <c r="A766" t="inlineStr">
         <is>
-          <t>DPC16</t>
+          <t>FG057</t>
         </is>
       </c>
       <c r="C766" t="inlineStr">
         <is>
-          <t>PELUCHE  UNICORNIO PARADO 45cm DP2503-047/DPC16</t>
+          <t>ABACO BOLSA 8022</t>
         </is>
       </c>
       <c r="E766" t="inlineStr">
         <is>
-          <t>PELUCHES</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I766" t="inlineStr">
@@ -35151,7 +35161,7 @@
         </is>
       </c>
       <c r="J766" t="n">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="K766" t="n">
         <v>0</v>
@@ -35160,30 +35170,30 @@
         <v>0</v>
       </c>
       <c r="M766" t="n">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="N766" t="n">
-        <v>28800</v>
+        <v>2293.26</v>
       </c>
       <c r="O766" t="n">
-        <v>633600</v>
+        <v>142182.12</v>
       </c>
       <c r="P766" t="n">
-        <v>36000</v>
+        <v>4800</v>
       </c>
       <c r="Q766" t="n">
-        <v>792000</v>
+        <v>297600</v>
       </c>
     </row>
     <row r="767">
       <c r="A767" t="inlineStr">
         <is>
-          <t>FG033</t>
+          <t>FG093</t>
         </is>
       </c>
       <c r="C767" t="inlineStr">
         <is>
-          <t>CHILLON X 6 TRANSPORTE 192</t>
+          <t>VAJILLA BLISTER SJ277-1</t>
         </is>
       </c>
       <c r="E767" t="inlineStr">
@@ -35197,7 +35207,7 @@
         </is>
       </c>
       <c r="J767" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="K767" t="n">
         <v>0</v>
@@ -35206,35 +35216,35 @@
         <v>0</v>
       </c>
       <c r="M767" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="N767" t="n">
-        <v>10335.44</v>
+        <v>4031.65</v>
       </c>
       <c r="O767" t="n">
-        <v>217044.24</v>
+        <v>36284.85</v>
       </c>
       <c r="P767" t="n">
-        <v>10900</v>
+        <v>5500</v>
       </c>
       <c r="Q767" t="n">
-        <v>228900</v>
+        <v>49500</v>
       </c>
     </row>
     <row r="768">
       <c r="A768" t="inlineStr">
         <is>
-          <t>FG039</t>
+          <t>G-208</t>
         </is>
       </c>
       <c r="C768" t="inlineStr">
         <is>
-          <t>GAFA DE NATACION BLISTER 2404-2</t>
+          <t>SET MARCADORES BORRABLES X12 G-208</t>
         </is>
       </c>
       <c r="E768" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I768" t="inlineStr">
@@ -35243,7 +35253,7 @@
         </is>
       </c>
       <c r="J768" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="K768" t="n">
         <v>0</v>
@@ -35252,35 +35262,35 @@
         <v>0</v>
       </c>
       <c r="M768" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="N768" t="n">
-        <v>2644.9</v>
+        <v>13900</v>
       </c>
       <c r="O768" t="n">
-        <v>66122.5</v>
+        <v>111200</v>
       </c>
       <c r="P768" t="n">
-        <v>3900</v>
+        <v>16700</v>
       </c>
       <c r="Q768" t="n">
-        <v>97500</v>
+        <v>133600</v>
       </c>
     </row>
     <row r="769">
       <c r="A769" t="inlineStr">
         <is>
-          <t>FG050</t>
+          <t>HY-110K</t>
         </is>
       </c>
       <c r="C769" t="inlineStr">
         <is>
-          <t>CARRO DINOSAURIO X3 757-46 KZ958-1103E</t>
+          <t>TIJERAS PUNTA ROMA HY-110K</t>
         </is>
       </c>
       <c r="E769" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I769" t="inlineStr">
@@ -35289,7 +35299,7 @@
         </is>
       </c>
       <c r="J769" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K769" t="n">
         <v>0</v>
@@ -35298,35 +35308,35 @@
         <v>0</v>
       </c>
       <c r="M769" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="N769" t="n">
-        <v>9708.190000000001</v>
+        <v>1160.1556923077</v>
       </c>
       <c r="O769" t="n">
-        <v>19416.38</v>
+        <v>8121.0898461539</v>
       </c>
       <c r="P769" t="n">
-        <v>10200</v>
+        <v>1600</v>
       </c>
       <c r="Q769" t="n">
-        <v>20400</v>
+        <v>11200</v>
       </c>
     </row>
     <row r="770">
       <c r="A770" t="inlineStr">
         <is>
-          <t>FG057</t>
+          <t>J-017</t>
         </is>
       </c>
       <c r="C770" t="inlineStr">
         <is>
-          <t>ABACO BOLSA 8022</t>
+          <t>CONEJO CAMINA ALUMBRA ZANAHORIA J-017</t>
         </is>
       </c>
       <c r="E770" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I770" t="inlineStr">
@@ -35335,7 +35345,7 @@
         </is>
       </c>
       <c r="J770" t="n">
-        <v>62</v>
+        <v>264</v>
       </c>
       <c r="K770" t="n">
         <v>0</v>
@@ -35344,35 +35354,35 @@
         <v>0</v>
       </c>
       <c r="M770" t="n">
-        <v>62</v>
+        <v>264</v>
       </c>
       <c r="N770" t="n">
-        <v>2293.26</v>
+        <v>7480</v>
       </c>
       <c r="O770" t="n">
-        <v>142182.12</v>
+        <v>1974720</v>
       </c>
       <c r="P770" t="n">
-        <v>4800</v>
+        <v>9500</v>
       </c>
       <c r="Q770" t="n">
-        <v>297600</v>
+        <v>2508000</v>
       </c>
     </row>
     <row r="771">
       <c r="A771" t="inlineStr">
         <is>
-          <t>FG093</t>
+          <t>J-556</t>
         </is>
       </c>
       <c r="C771" t="inlineStr">
         <is>
-          <t>VAJILLA BLISTER SJ277-1</t>
+          <t>VUVUCELA 25CM J-556</t>
         </is>
       </c>
       <c r="E771" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I771" t="inlineStr">
@@ -35381,7 +35391,7 @@
         </is>
       </c>
       <c r="J771" t="n">
-        <v>9</v>
+        <v>240</v>
       </c>
       <c r="K771" t="n">
         <v>0</v>
@@ -35390,30 +35400,30 @@
         <v>0</v>
       </c>
       <c r="M771" t="n">
-        <v>9</v>
+        <v>240</v>
       </c>
       <c r="N771" t="n">
-        <v>4031.65</v>
+        <v>1260</v>
       </c>
       <c r="O771" t="n">
-        <v>36284.85</v>
+        <v>302400</v>
       </c>
       <c r="P771" t="n">
-        <v>5500</v>
+        <v>1700</v>
       </c>
       <c r="Q771" t="n">
-        <v>49500</v>
+        <v>408000</v>
       </c>
     </row>
     <row r="772">
       <c r="A772" t="inlineStr">
         <is>
-          <t>G-208</t>
+          <t>J-704</t>
         </is>
       </c>
       <c r="C772" t="inlineStr">
         <is>
-          <t>SET MARCADORES BORRABLES X12 G-208</t>
+          <t>MONO SONIDO J-704-705-706-707-708-710</t>
         </is>
       </c>
       <c r="E772" t="inlineStr">
@@ -35427,7 +35437,7 @@
         </is>
       </c>
       <c r="J772" t="n">
-        <v>8</v>
+        <v>330</v>
       </c>
       <c r="K772" t="n">
         <v>0</v>
@@ -35436,30 +35446,30 @@
         <v>0</v>
       </c>
       <c r="M772" t="n">
-        <v>8</v>
+        <v>330</v>
       </c>
       <c r="N772" t="n">
-        <v>13900</v>
+        <v>7216</v>
       </c>
       <c r="O772" t="n">
-        <v>111200</v>
+        <v>2381280</v>
       </c>
       <c r="P772" t="n">
-        <v>16700</v>
+        <v>9000</v>
       </c>
       <c r="Q772" t="n">
-        <v>133600</v>
+        <v>2970000</v>
       </c>
     </row>
     <row r="773">
       <c r="A773" t="inlineStr">
         <is>
-          <t>HY-110K</t>
+          <t>JBL0536</t>
         </is>
       </c>
       <c r="C773" t="inlineStr">
         <is>
-          <t>TIJERAS PUNTA ROMA HY-110K</t>
+          <t>SET DE REGLAS X7PCS JBL0536</t>
         </is>
       </c>
       <c r="E773" t="inlineStr">
@@ -35473,7 +35483,7 @@
         </is>
       </c>
       <c r="J773" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="K773" t="n">
         <v>0</v>
@@ -35482,30 +35492,30 @@
         <v>0</v>
       </c>
       <c r="M773" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="N773" t="n">
-        <v>1160.1556923077</v>
+        <v>5900</v>
       </c>
       <c r="O773" t="n">
-        <v>8121.0898461539</v>
+        <v>82600</v>
       </c>
       <c r="P773" t="n">
-        <v>1600</v>
+        <v>7100</v>
       </c>
       <c r="Q773" t="n">
-        <v>11200</v>
+        <v>99400</v>
       </c>
     </row>
     <row r="774">
       <c r="A774" t="inlineStr">
         <is>
-          <t>J-017</t>
+          <t>JBL0539</t>
         </is>
       </c>
       <c r="C774" t="inlineStr">
         <is>
-          <t>CONEJO CAMINA ALUMBRA ZANAHORIA J-017</t>
+          <t>MARCADORES CAJA PLASTICA X24 JBL0539</t>
         </is>
       </c>
       <c r="E774" t="inlineStr">
@@ -35519,39 +35529,39 @@
         </is>
       </c>
       <c r="J774" t="n">
-        <v>273</v>
+        <v>1</v>
       </c>
       <c r="K774" t="n">
         <v>0</v>
       </c>
       <c r="L774" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M774" t="n">
-        <v>264</v>
+        <v>1</v>
       </c>
       <c r="N774" t="n">
-        <v>7480</v>
+        <v>17500</v>
       </c>
       <c r="O774" t="n">
-        <v>1974720</v>
+        <v>17500</v>
       </c>
       <c r="P774" t="n">
-        <v>9500</v>
+        <v>21000</v>
       </c>
       <c r="Q774" t="n">
-        <v>2508000</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="775">
       <c r="A775" t="inlineStr">
         <is>
-          <t>J-556</t>
+          <t>JBL0540</t>
         </is>
       </c>
       <c r="C775" t="inlineStr">
         <is>
-          <t>VUVUCELA 25CM J-556</t>
+          <t>MARCADORES CAJA PLASTICA X36 JBL0540</t>
         </is>
       </c>
       <c r="E775" t="inlineStr">
@@ -35565,7 +35575,7 @@
         </is>
       </c>
       <c r="J775" t="n">
-        <v>240</v>
+        <v>11</v>
       </c>
       <c r="K775" t="n">
         <v>0</v>
@@ -35574,30 +35584,30 @@
         <v>0</v>
       </c>
       <c r="M775" t="n">
-        <v>240</v>
+        <v>11</v>
       </c>
       <c r="N775" t="n">
-        <v>1260</v>
+        <v>25000</v>
       </c>
       <c r="O775" t="n">
-        <v>302400</v>
+        <v>275000</v>
       </c>
       <c r="P775" t="n">
-        <v>1700</v>
+        <v>30000</v>
       </c>
       <c r="Q775" t="n">
-        <v>408000</v>
+        <v>330000</v>
       </c>
     </row>
     <row r="776">
       <c r="A776" t="inlineStr">
         <is>
-          <t>J-704</t>
+          <t>JBL0554</t>
         </is>
       </c>
       <c r="C776" t="inlineStr">
         <is>
-          <t>MONO SONIDO J-704-705-706-707-708-710</t>
+          <t>CAJA DE COLORES X 12 PCS JBL0554</t>
         </is>
       </c>
       <c r="E776" t="inlineStr">
@@ -35611,7 +35621,7 @@
         </is>
       </c>
       <c r="J776" t="n">
-        <v>330</v>
+        <v>18</v>
       </c>
       <c r="K776" t="n">
         <v>0</v>
@@ -35620,30 +35630,30 @@
         <v>0</v>
       </c>
       <c r="M776" t="n">
-        <v>330</v>
+        <v>18</v>
       </c>
       <c r="N776" t="n">
-        <v>7216</v>
+        <v>9500</v>
       </c>
       <c r="O776" t="n">
-        <v>2381280</v>
+        <v>171000</v>
       </c>
       <c r="P776" t="n">
-        <v>9000</v>
+        <v>11400</v>
       </c>
       <c r="Q776" t="n">
-        <v>2970000</v>
+        <v>205200</v>
       </c>
     </row>
     <row r="777">
       <c r="A777" t="inlineStr">
         <is>
-          <t>JBL0536</t>
+          <t>JBL0557</t>
         </is>
       </c>
       <c r="C777" t="inlineStr">
         <is>
-          <t>SET DE REGLAS X7PCS JBL0536</t>
+          <t>CAJA COLORES MINI X 12 PCS  JBL0557</t>
         </is>
       </c>
       <c r="E777" t="inlineStr">
@@ -35657,7 +35667,7 @@
         </is>
       </c>
       <c r="J777" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K777" t="n">
         <v>0</v>
@@ -35666,30 +35676,30 @@
         <v>0</v>
       </c>
       <c r="M777" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="N777" t="n">
-        <v>5900</v>
+        <v>2900</v>
       </c>
       <c r="O777" t="n">
-        <v>82600</v>
+        <v>55100</v>
       </c>
       <c r="P777" t="n">
-        <v>7100</v>
+        <v>3500</v>
       </c>
       <c r="Q777" t="n">
-        <v>99400</v>
+        <v>66500</v>
       </c>
     </row>
     <row r="778">
       <c r="A778" t="inlineStr">
         <is>
-          <t>JBL0539</t>
+          <t>JBL0657</t>
         </is>
       </c>
       <c r="C778" t="inlineStr">
         <is>
-          <t>MARCADORES CAJA PLASTICA X24 JBL0539</t>
+          <t>TAJALAPIZ CON DEPOSITO JBL0657</t>
         </is>
       </c>
       <c r="E778" t="inlineStr">
@@ -35703,7 +35713,7 @@
         </is>
       </c>
       <c r="J778" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="K778" t="n">
         <v>0</v>
@@ -35712,30 +35722,30 @@
         <v>0</v>
       </c>
       <c r="M778" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="N778" t="n">
-        <v>17500</v>
+        <v>1000</v>
       </c>
       <c r="O778" t="n">
-        <v>17500</v>
+        <v>14000</v>
       </c>
       <c r="P778" t="n">
-        <v>21000</v>
+        <v>1200</v>
       </c>
       <c r="Q778" t="n">
-        <v>21000</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="779">
       <c r="A779" t="inlineStr">
         <is>
-          <t>JBL0540</t>
+          <t>JBL0707</t>
         </is>
       </c>
       <c r="C779" t="inlineStr">
         <is>
-          <t>MARCADORES CAJA PLASTICA X36 JBL0540</t>
+          <t>SET GEOMETRICO FLEXIBLE X 4 PCS JBL0707</t>
         </is>
       </c>
       <c r="E779" t="inlineStr">
@@ -35749,7 +35759,7 @@
         </is>
       </c>
       <c r="J779" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="K779" t="n">
         <v>0</v>
@@ -35758,30 +35768,30 @@
         <v>0</v>
       </c>
       <c r="M779" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="N779" t="n">
-        <v>25000</v>
+        <v>3600</v>
       </c>
       <c r="O779" t="n">
-        <v>275000</v>
+        <v>72000</v>
       </c>
       <c r="P779" t="n">
-        <v>30000</v>
+        <v>4400</v>
       </c>
       <c r="Q779" t="n">
-        <v>330000</v>
+        <v>88000</v>
       </c>
     </row>
     <row r="780">
       <c r="A780" t="inlineStr">
         <is>
-          <t>JBL0554</t>
+          <t>JBL0729</t>
         </is>
       </c>
       <c r="C780" t="inlineStr">
         <is>
-          <t>CAJA DE COLORES X 12 PCS JBL0554</t>
+          <t>LONCHERA INFANTIL MODELOS STD 22,5cm JBL0729</t>
         </is>
       </c>
       <c r="E780" t="inlineStr">
@@ -35795,7 +35805,7 @@
         </is>
       </c>
       <c r="J780" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K780" t="n">
         <v>0</v>
@@ -35804,30 +35814,30 @@
         <v>0</v>
       </c>
       <c r="M780" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N780" t="n">
-        <v>9500</v>
+        <v>9300</v>
       </c>
       <c r="O780" t="n">
-        <v>171000</v>
+        <v>158100</v>
       </c>
       <c r="P780" t="n">
-        <v>11400</v>
+        <v>11200</v>
       </c>
       <c r="Q780" t="n">
-        <v>205200</v>
+        <v>190400</v>
       </c>
     </row>
     <row r="781">
       <c r="A781" t="inlineStr">
         <is>
-          <t>JBL0557</t>
+          <t>JO-129</t>
         </is>
       </c>
       <c r="C781" t="inlineStr">
         <is>
-          <t>CAJA COLORES MINI X 12 PCS  JBL0557</t>
+          <t>LAPICES COLORES X12 DOBLE PUNTA JO-129</t>
         </is>
       </c>
       <c r="E781" t="inlineStr">
@@ -35841,7 +35851,7 @@
         </is>
       </c>
       <c r="J781" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="K781" t="n">
         <v>0</v>
@@ -35850,30 +35860,30 @@
         <v>0</v>
       </c>
       <c r="M781" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="N781" t="n">
-        <v>2900</v>
+        <v>4500</v>
       </c>
       <c r="O781" t="n">
-        <v>55100</v>
+        <v>72000</v>
       </c>
       <c r="P781" t="n">
-        <v>3500</v>
+        <v>5400</v>
       </c>
       <c r="Q781" t="n">
-        <v>66500</v>
+        <v>86400</v>
       </c>
     </row>
     <row r="782">
       <c r="A782" t="inlineStr">
         <is>
-          <t>JBL0657</t>
+          <t>JO-139</t>
         </is>
       </c>
       <c r="C782" t="inlineStr">
         <is>
-          <t>TAJALAPIZ CON DEPOSITO JBL0657</t>
+          <t>ESFERO GIRATORIO 10 MINAS MUÑECA JO-139</t>
         </is>
       </c>
       <c r="E782" t="inlineStr">
@@ -35887,7 +35897,7 @@
         </is>
       </c>
       <c r="J782" t="n">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="K782" t="n">
         <v>0</v>
@@ -35896,30 +35906,30 @@
         <v>0</v>
       </c>
       <c r="M782" t="n">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="N782" t="n">
-        <v>1000</v>
+        <v>2700</v>
       </c>
       <c r="O782" t="n">
-        <v>14000</v>
+        <v>137700</v>
       </c>
       <c r="P782" t="n">
-        <v>1200</v>
+        <v>3300</v>
       </c>
       <c r="Q782" t="n">
-        <v>16800</v>
+        <v>168300</v>
       </c>
     </row>
     <row r="783">
       <c r="A783" t="inlineStr">
         <is>
-          <t>JBL0707</t>
+          <t>JO-142</t>
         </is>
       </c>
       <c r="C783" t="inlineStr">
         <is>
-          <t>SET GEOMETRICO FLEXIBLE X 4 PCS JBL0707</t>
+          <t>ESFERO BORRABLE CON BORRADOR ASTRONAUTA JO-142</t>
         </is>
       </c>
       <c r="E783" t="inlineStr">
@@ -35933,7 +35943,7 @@
         </is>
       </c>
       <c r="J783" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="K783" t="n">
         <v>0</v>
@@ -35942,30 +35952,30 @@
         <v>0</v>
       </c>
       <c r="M783" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="N783" t="n">
-        <v>3600</v>
+        <v>1900</v>
       </c>
       <c r="O783" t="n">
-        <v>72000</v>
+        <v>68400</v>
       </c>
       <c r="P783" t="n">
-        <v>4400</v>
+        <v>2300</v>
       </c>
       <c r="Q783" t="n">
-        <v>88000</v>
+        <v>82800</v>
       </c>
     </row>
     <row r="784">
       <c r="A784" t="inlineStr">
         <is>
-          <t>JBL0729</t>
+          <t>JO-143</t>
         </is>
       </c>
       <c r="C784" t="inlineStr">
         <is>
-          <t>LONCHERA INFANTIL MODELOS STD 22,5cm JBL0729</t>
+          <t>ESFERO BORRABKLE CON BORRADOR ARCOIRIS JO-143</t>
         </is>
       </c>
       <c r="E784" t="inlineStr">
@@ -35979,7 +35989,7 @@
         </is>
       </c>
       <c r="J784" t="n">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="K784" t="n">
         <v>0</v>
@@ -35988,30 +35998,30 @@
         <v>0</v>
       </c>
       <c r="M784" t="n">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="N784" t="n">
-        <v>9300</v>
+        <v>1400</v>
       </c>
       <c r="O784" t="n">
-        <v>158100</v>
+        <v>61600</v>
       </c>
       <c r="P784" t="n">
-        <v>11200</v>
+        <v>1700</v>
       </c>
       <c r="Q784" t="n">
-        <v>190400</v>
+        <v>74800</v>
       </c>
     </row>
     <row r="785">
       <c r="A785" t="inlineStr">
         <is>
-          <t>JO-129</t>
+          <t>JO-144</t>
         </is>
       </c>
       <c r="C785" t="inlineStr">
         <is>
-          <t>LAPICES COLORES X12 DOBLE PUNTA JO-129</t>
+          <t>ESFERO BORRABLE CON BORRADOR PANDA JO-144</t>
         </is>
       </c>
       <c r="E785" t="inlineStr">
@@ -36025,7 +36035,7 @@
         </is>
       </c>
       <c r="J785" t="n">
-        <v>16</v>
+        <v>72</v>
       </c>
       <c r="K785" t="n">
         <v>0</v>
@@ -36034,30 +36044,30 @@
         <v>0</v>
       </c>
       <c r="M785" t="n">
-        <v>16</v>
+        <v>72</v>
       </c>
       <c r="N785" t="n">
-        <v>4500</v>
+        <v>1900</v>
       </c>
       <c r="O785" t="n">
-        <v>72000</v>
+        <v>136800</v>
       </c>
       <c r="P785" t="n">
-        <v>5400</v>
+        <v>2300</v>
       </c>
       <c r="Q785" t="n">
-        <v>86400</v>
+        <v>165600</v>
       </c>
     </row>
     <row r="786">
       <c r="A786" t="inlineStr">
         <is>
-          <t>JO-139</t>
+          <t>JO-145</t>
         </is>
       </c>
       <c r="C786" t="inlineStr">
         <is>
-          <t>ESFERO GIRATORIO 10 MINAS MUÑECA JO-139</t>
+          <t>ESFERO BORRABLE CON BORRADOR OSITO JO-145</t>
         </is>
       </c>
       <c r="E786" t="inlineStr">
@@ -36071,7 +36081,7 @@
         </is>
       </c>
       <c r="J786" t="n">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="K786" t="n">
         <v>0</v>
@@ -36080,30 +36090,30 @@
         <v>0</v>
       </c>
       <c r="M786" t="n">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="N786" t="n">
-        <v>2700</v>
+        <v>1900</v>
       </c>
       <c r="O786" t="n">
-        <v>137700</v>
+        <v>119700</v>
       </c>
       <c r="P786" t="n">
-        <v>3300</v>
+        <v>2300</v>
       </c>
       <c r="Q786" t="n">
-        <v>168300</v>
+        <v>144900</v>
       </c>
     </row>
     <row r="787">
       <c r="A787" t="inlineStr">
         <is>
-          <t>JO-142</t>
+          <t>JOE-1813</t>
         </is>
       </c>
       <c r="C787" t="inlineStr">
         <is>
-          <t>ESFERO BORRABLE CON BORRADOR ASTRONAUTA JO-142</t>
+          <t>SET MARCADORES ACUARELA LAVAVBLE TUBO X 18 PCS JOE-1813</t>
         </is>
       </c>
       <c r="E787" t="inlineStr">
@@ -36117,7 +36127,7 @@
         </is>
       </c>
       <c r="J787" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="K787" t="n">
         <v>0</v>
@@ -36126,30 +36136,30 @@
         <v>0</v>
       </c>
       <c r="M787" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="N787" t="n">
-        <v>1900</v>
+        <v>6000</v>
       </c>
       <c r="O787" t="n">
-        <v>68400</v>
+        <v>60000</v>
       </c>
       <c r="P787" t="n">
-        <v>2300</v>
+        <v>7200</v>
       </c>
       <c r="Q787" t="n">
-        <v>82800</v>
+        <v>72000</v>
       </c>
     </row>
     <row r="788">
       <c r="A788" t="inlineStr">
         <is>
-          <t>JO-143</t>
+          <t>JOE-9812</t>
         </is>
       </c>
       <c r="C788" t="inlineStr">
         <is>
-          <t>ESFERO BORRABKLE CON BORRADOR ARCOIRIS JO-143</t>
+          <t>SET MARCADORES JUMBO ACUARELA X12/14cm</t>
         </is>
       </c>
       <c r="E788" t="inlineStr">
@@ -36163,7 +36173,7 @@
         </is>
       </c>
       <c r="J788" t="n">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="K788" t="n">
         <v>0</v>
@@ -36172,30 +36182,30 @@
         <v>0</v>
       </c>
       <c r="M788" t="n">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="N788" t="n">
-        <v>1400</v>
+        <v>5000</v>
       </c>
       <c r="O788" t="n">
-        <v>61600</v>
+        <v>30000</v>
       </c>
       <c r="P788" t="n">
-        <v>1700</v>
+        <v>6000</v>
       </c>
       <c r="Q788" t="n">
-        <v>74800</v>
+        <v>36000</v>
       </c>
     </row>
     <row r="789">
       <c r="A789" t="inlineStr">
         <is>
-          <t>JO-144</t>
+          <t>JT-13</t>
         </is>
       </c>
       <c r="C789" t="inlineStr">
         <is>
-          <t>ESFERO BORRABLE CON BORRADOR PANDA JO-144</t>
+          <t>CORRECTOR EN CINTA JT-13</t>
         </is>
       </c>
       <c r="E789" t="inlineStr">
@@ -36209,7 +36219,7 @@
         </is>
       </c>
       <c r="J789" t="n">
-        <v>72</v>
+        <v>7</v>
       </c>
       <c r="K789" t="n">
         <v>0</v>
@@ -36218,30 +36228,30 @@
         <v>0</v>
       </c>
       <c r="M789" t="n">
-        <v>72</v>
+        <v>7</v>
       </c>
       <c r="N789" t="n">
-        <v>1900</v>
+        <v>2400</v>
       </c>
       <c r="O789" t="n">
-        <v>136800</v>
+        <v>16800</v>
       </c>
       <c r="P789" t="n">
-        <v>2300</v>
+        <v>2900</v>
       </c>
       <c r="Q789" t="n">
-        <v>165600</v>
+        <v>20300</v>
       </c>
     </row>
     <row r="790">
       <c r="A790" t="inlineStr">
         <is>
-          <t>JO-145</t>
+          <t>K061A</t>
         </is>
       </c>
       <c r="C790" t="inlineStr">
         <is>
-          <t>ESFERO BORRABLE CON BORRADOR OSITO JO-145</t>
+          <t>ESFERO RETRACTIL CAPIBARA TINTA NEGRA K061A</t>
         </is>
       </c>
       <c r="E790" t="inlineStr">
@@ -36255,7 +36265,7 @@
         </is>
       </c>
       <c r="J790" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="K790" t="n">
         <v>0</v>
@@ -36264,30 +36274,30 @@
         <v>0</v>
       </c>
       <c r="M790" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="N790" t="n">
-        <v>1900</v>
+        <v>1800</v>
       </c>
       <c r="O790" t="n">
-        <v>119700</v>
+        <v>108000</v>
       </c>
       <c r="P790" t="n">
-        <v>2300</v>
+        <v>2200</v>
       </c>
       <c r="Q790" t="n">
-        <v>144900</v>
+        <v>132000</v>
       </c>
     </row>
     <row r="791">
       <c r="A791" t="inlineStr">
         <is>
-          <t>JOE-1813</t>
+          <t>LY6807</t>
         </is>
       </c>
       <c r="C791" t="inlineStr">
         <is>
-          <t>SET MARCADORES ACUARELA LAVAVBLE TUBO X 18 PCS JOE-1813</t>
+          <t>JUGUETE PATINETA DE CUATRO RUEDAS LY6807</t>
         </is>
       </c>
       <c r="E791" t="inlineStr">
@@ -36301,7 +36311,7 @@
         </is>
       </c>
       <c r="J791" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="K791" t="n">
         <v>0</v>
@@ -36310,30 +36320,30 @@
         <v>0</v>
       </c>
       <c r="M791" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="N791" t="n">
-        <v>6214.2857142857</v>
+        <v>415.07</v>
       </c>
       <c r="O791" t="n">
-        <v>62142.857142857</v>
+        <v>16602.8</v>
       </c>
       <c r="P791" t="n">
-        <v>7200</v>
+        <v>2900</v>
       </c>
       <c r="Q791" t="n">
-        <v>72000</v>
+        <v>116000</v>
       </c>
     </row>
     <row r="792">
       <c r="A792" t="inlineStr">
         <is>
-          <t>JOE-9812</t>
+          <t>MC121011-E</t>
         </is>
       </c>
       <c r="C792" t="inlineStr">
         <is>
-          <t>SET MARCADORES JUMBO ACUARELA X12/14cm</t>
+          <t>SET LAPIZ CON BORRADOR OSITOS MC121011-E</t>
         </is>
       </c>
       <c r="E792" t="inlineStr">
@@ -36359,27 +36369,27 @@
         <v>6</v>
       </c>
       <c r="N792" t="n">
-        <v>5000</v>
+        <v>6500</v>
       </c>
       <c r="O792" t="n">
-        <v>30000</v>
+        <v>39000</v>
       </c>
       <c r="P792" t="n">
-        <v>6000</v>
+        <v>7800</v>
       </c>
       <c r="Q792" t="n">
-        <v>36000</v>
+        <v>46800</v>
       </c>
     </row>
     <row r="793">
       <c r="A793" t="inlineStr">
         <is>
-          <t>JT-13</t>
+          <t>MC121212</t>
         </is>
       </c>
       <c r="C793" t="inlineStr">
         <is>
-          <t>CORRECTOR EN CINTA JT-13</t>
+          <t>SET LAPIZ CON BORRADOR Y TAJALAPIZ ROBOT MC121212</t>
         </is>
       </c>
       <c r="E793" t="inlineStr">
@@ -36393,7 +36403,7 @@
         </is>
       </c>
       <c r="J793" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K793" t="n">
         <v>0</v>
@@ -36402,35 +36412,40 @@
         <v>0</v>
       </c>
       <c r="M793" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N793" t="n">
-        <v>2400</v>
+        <v>6500</v>
       </c>
       <c r="O793" t="n">
-        <v>16800</v>
+        <v>39000</v>
       </c>
       <c r="P793" t="n">
-        <v>2900</v>
+        <v>7800</v>
       </c>
       <c r="Q793" t="n">
-        <v>20300</v>
+        <v>46800</v>
       </c>
     </row>
     <row r="794">
       <c r="A794" t="inlineStr">
         <is>
-          <t>K061A</t>
+          <t>MG16332</t>
+        </is>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>MG16332</t>
         </is>
       </c>
       <c r="C794" t="inlineStr">
         <is>
-          <t>ESFERO RETRACTIL CAPIBARA TINTA NEGRA K061A</t>
+          <t>LANZADOR  ARCO Y FLECA CON LASER MG16332</t>
         </is>
       </c>
       <c r="E794" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I794" t="inlineStr">
@@ -36439,7 +36454,7 @@
         </is>
       </c>
       <c r="J794" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="K794" t="n">
         <v>0</v>
@@ -36448,35 +36463,35 @@
         <v>0</v>
       </c>
       <c r="M794" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="N794" t="n">
-        <v>1800</v>
+        <v>8439.969999999999</v>
       </c>
       <c r="O794" t="n">
-        <v>108000</v>
+        <v>84399.7</v>
       </c>
       <c r="P794" t="n">
-        <v>2200</v>
+        <v>29500</v>
       </c>
       <c r="Q794" t="n">
-        <v>132000</v>
+        <v>295000</v>
       </c>
     </row>
     <row r="795">
       <c r="A795" t="inlineStr">
         <is>
-          <t>LY6807</t>
+          <t>MG20129</t>
         </is>
       </c>
       <c r="C795" t="inlineStr">
         <is>
-          <t>JUGUETE PATINETA DE CUATRO RUEDAS LY6807</t>
+          <t>SET MOLDE PARA HELADOS Y FRUTAS EN PLASTILINA MG20129</t>
         </is>
       </c>
       <c r="E795" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I795" t="inlineStr">
@@ -36485,7 +36500,7 @@
         </is>
       </c>
       <c r="J795" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="K795" t="n">
         <v>0</v>
@@ -36494,35 +36509,35 @@
         <v>0</v>
       </c>
       <c r="M795" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="N795" t="n">
-        <v>415.07</v>
+        <v>7860.59</v>
       </c>
       <c r="O795" t="n">
-        <v>16602.8</v>
+        <v>78605.89999999999</v>
       </c>
       <c r="P795" t="n">
-        <v>2900</v>
+        <v>21500</v>
       </c>
       <c r="Q795" t="n">
-        <v>116000</v>
+        <v>215000</v>
       </c>
     </row>
     <row r="796">
       <c r="A796" t="inlineStr">
         <is>
-          <t>MC121011-E</t>
+          <t>MG20430</t>
         </is>
       </c>
       <c r="C796" t="inlineStr">
         <is>
-          <t>SET LAPIZ CON BORRADOR OSITOS MC121011-E</t>
+          <t>SET PLASTILINA CON MOLDES BARBERIA MALETA MG20430</t>
         </is>
       </c>
       <c r="E796" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I796" t="inlineStr">
@@ -36531,7 +36546,7 @@
         </is>
       </c>
       <c r="J796" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K796" t="n">
         <v>0</v>
@@ -36540,35 +36555,35 @@
         <v>0</v>
       </c>
       <c r="M796" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N796" t="n">
-        <v>6500</v>
+        <v>12189.832</v>
       </c>
       <c r="O796" t="n">
-        <v>39000</v>
+        <v>24379.664</v>
       </c>
       <c r="P796" t="n">
-        <v>7800</v>
+        <v>30900</v>
       </c>
       <c r="Q796" t="n">
-        <v>46800</v>
+        <v>61800</v>
       </c>
     </row>
     <row r="797">
       <c r="A797" t="inlineStr">
         <is>
-          <t>MC121212</t>
+          <t>MG20669</t>
         </is>
       </c>
       <c r="C797" t="inlineStr">
         <is>
-          <t>SET LAPIZ CON BORRADOR Y TAJALAPIZ ROBOT MC121212</t>
+          <t>SET DE PLASTILINA PARA MOLDEAR EN BLISTER MG20669</t>
         </is>
       </c>
       <c r="E797" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I797" t="inlineStr">
@@ -36577,7 +36592,7 @@
         </is>
       </c>
       <c r="J797" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="K797" t="n">
         <v>0</v>
@@ -36586,40 +36601,35 @@
         <v>0</v>
       </c>
       <c r="M797" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="N797" t="n">
-        <v>6500</v>
+        <v>970.63171428571</v>
       </c>
       <c r="O797" t="n">
-        <v>39000</v>
+        <v>23295.16114285704</v>
       </c>
       <c r="P797" t="n">
-        <v>7800</v>
+        <v>7200</v>
       </c>
       <c r="Q797" t="n">
-        <v>46800</v>
+        <v>172800</v>
       </c>
     </row>
     <row r="798">
       <c r="A798" t="inlineStr">
         <is>
-          <t>MG16332</t>
-        </is>
-      </c>
-      <c r="B798" t="inlineStr">
-        <is>
-          <t>MG16332</t>
+          <t>MG20906</t>
         </is>
       </c>
       <c r="C798" t="inlineStr">
         <is>
-          <t>LANZADOR  ARCO Y FLECA CON LASER MG16332</t>
+          <t>DINOSAURIO DIDACTICO EN BOLSA MG20906</t>
         </is>
       </c>
       <c r="E798" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I798" t="inlineStr">
@@ -36628,7 +36638,7 @@
         </is>
       </c>
       <c r="J798" t="n">
-        <v>10</v>
+        <v>63</v>
       </c>
       <c r="K798" t="n">
         <v>0</v>
@@ -36637,35 +36647,35 @@
         <v>0</v>
       </c>
       <c r="M798" t="n">
-        <v>10</v>
+        <v>63</v>
       </c>
       <c r="N798" t="n">
-        <v>8439.969999999999</v>
+        <v>1482.84</v>
       </c>
       <c r="O798" t="n">
-        <v>84399.7</v>
+        <v>93418.92</v>
       </c>
       <c r="P798" t="n">
-        <v>29500</v>
+        <v>6500</v>
       </c>
       <c r="Q798" t="n">
-        <v>295000</v>
+        <v>409500</v>
       </c>
     </row>
     <row r="799">
       <c r="A799" t="inlineStr">
         <is>
-          <t>MG20129</t>
+          <t>MG22320</t>
         </is>
       </c>
       <c r="C799" t="inlineStr">
         <is>
-          <t>SET MOLDE PARA HELADOS Y FRUTAS EN PLASTILINA MG20129</t>
+          <t>CABALLO DIDACTICO DESARMABLE PQÑ MG22320</t>
         </is>
       </c>
       <c r="E799" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>DIDACTICOS</t>
         </is>
       </c>
       <c r="I799" t="inlineStr">
@@ -36674,7 +36684,7 @@
         </is>
       </c>
       <c r="J799" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K799" t="n">
         <v>0</v>
@@ -36683,30 +36693,35 @@
         <v>0</v>
       </c>
       <c r="M799" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="N799" t="n">
-        <v>7860.59</v>
+        <v>1129.14</v>
       </c>
       <c r="O799" t="n">
-        <v>78605.89999999999</v>
+        <v>14678.82</v>
       </c>
       <c r="P799" t="n">
-        <v>21500</v>
+        <v>6900</v>
       </c>
       <c r="Q799" t="n">
-        <v>215000</v>
+        <v>89700</v>
       </c>
     </row>
     <row r="800">
       <c r="A800" t="inlineStr">
         <is>
-          <t>MG20430</t>
+          <t>MG22435</t>
+        </is>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>MG22435</t>
         </is>
       </c>
       <c r="C800" t="inlineStr">
         <is>
-          <t>SET PLASTILINA CON MOLDES BARBERIA MALETA MG20430</t>
+          <t>SONAJERO PERRITO BOLSA PQÑ MG22435</t>
         </is>
       </c>
       <c r="E800" t="inlineStr">
@@ -36720,7 +36735,7 @@
         </is>
       </c>
       <c r="J800" t="n">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="K800" t="n">
         <v>0</v>
@@ -36729,35 +36744,35 @@
         <v>0</v>
       </c>
       <c r="M800" t="n">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="N800" t="n">
-        <v>12189.832</v>
+        <v>1236.3</v>
       </c>
       <c r="O800" t="n">
-        <v>24379.664</v>
+        <v>63051.3</v>
       </c>
       <c r="P800" t="n">
-        <v>30900</v>
+        <v>2300</v>
       </c>
       <c r="Q800" t="n">
-        <v>61800</v>
+        <v>117300</v>
       </c>
     </row>
     <row r="801">
       <c r="A801" t="inlineStr">
         <is>
-          <t>MG20669</t>
+          <t>MG26010</t>
         </is>
       </c>
       <c r="C801" t="inlineStr">
         <is>
-          <t>SET DE PLASTILINA PARA MOLDEAR EN BLISTER MG20669</t>
+          <t>SET BELLEZA CON ACCESORIOS EMPAQUE BOLSO MG26010</t>
         </is>
       </c>
       <c r="E801" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I801" t="inlineStr">
@@ -36766,7 +36781,7 @@
         </is>
       </c>
       <c r="J801" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="K801" t="n">
         <v>0</v>
@@ -36775,35 +36790,35 @@
         <v>0</v>
       </c>
       <c r="M801" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="N801" t="n">
-        <v>970.63171428571</v>
+        <v>11433.53</v>
       </c>
       <c r="O801" t="n">
-        <v>23295.16114285704</v>
+        <v>125768.83</v>
       </c>
       <c r="P801" t="n">
-        <v>7200</v>
+        <v>15000</v>
       </c>
       <c r="Q801" t="n">
-        <v>172800</v>
+        <v>165000</v>
       </c>
     </row>
     <row r="802">
       <c r="A802" t="inlineStr">
         <is>
-          <t>MG20906</t>
+          <t>MG27230</t>
         </is>
       </c>
       <c r="C802" t="inlineStr">
         <is>
-          <t>DINOSAURIO DIDACTICO EN BOLSA MG20906</t>
+          <t>SET PLASTILINA ODONTOLOGICO CAJA MG27230</t>
         </is>
       </c>
       <c r="E802" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I802" t="inlineStr">
@@ -36812,7 +36827,7 @@
         </is>
       </c>
       <c r="J802" t="n">
-        <v>63</v>
+        <v>9</v>
       </c>
       <c r="K802" t="n">
         <v>0</v>
@@ -36821,35 +36836,40 @@
         <v>0</v>
       </c>
       <c r="M802" t="n">
-        <v>63</v>
+        <v>9</v>
       </c>
       <c r="N802" t="n">
-        <v>1482.84</v>
+        <v>12115.88</v>
       </c>
       <c r="O802" t="n">
-        <v>93418.92</v>
+        <v>109042.92</v>
       </c>
       <c r="P802" t="n">
-        <v>6500</v>
+        <v>31500</v>
       </c>
       <c r="Q802" t="n">
-        <v>409500</v>
+        <v>283500</v>
       </c>
     </row>
     <row r="803">
       <c r="A803" t="inlineStr">
         <is>
-          <t>MG22320</t>
+          <t>MG33219</t>
+        </is>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>MG33219</t>
         </is>
       </c>
       <c r="C803" t="inlineStr">
         <is>
-          <t>CABALLO DIDACTICO DESARMABLE PQÑ MG22320</t>
+          <t>BINOCULARES CAMUFLADOS MG33219</t>
         </is>
       </c>
       <c r="E803" t="inlineStr">
         <is>
-          <t>DIDACTICOS</t>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I803" t="inlineStr">
@@ -36858,7 +36878,7 @@
         </is>
       </c>
       <c r="J803" t="n">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="K803" t="n">
         <v>0</v>
@@ -36867,40 +36887,35 @@
         <v>0</v>
       </c>
       <c r="M803" t="n">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="N803" t="n">
-        <v>1129.14</v>
+        <v>751.45</v>
       </c>
       <c r="O803" t="n">
-        <v>14678.82</v>
+        <v>45087</v>
       </c>
       <c r="P803" t="n">
-        <v>6900</v>
+        <v>2500</v>
       </c>
       <c r="Q803" t="n">
-        <v>89700</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="804">
       <c r="A804" t="inlineStr">
         <is>
-          <t>MG22435</t>
-        </is>
-      </c>
-      <c r="B804" t="inlineStr">
-        <is>
-          <t>MG22435</t>
+          <t>MG40210</t>
         </is>
       </c>
       <c r="C804" t="inlineStr">
         <is>
-          <t>SONAJERO PERRITO BOLSA PQÑ MG22435</t>
+          <t>SONAJERO OSO MG40210</t>
         </is>
       </c>
       <c r="E804" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I804" t="inlineStr">
@@ -36909,7 +36924,7 @@
         </is>
       </c>
       <c r="J804" t="n">
-        <v>51</v>
+        <v>154</v>
       </c>
       <c r="K804" t="n">
         <v>0</v>
@@ -36918,30 +36933,35 @@
         <v>0</v>
       </c>
       <c r="M804" t="n">
-        <v>51</v>
+        <v>154</v>
       </c>
       <c r="N804" t="n">
-        <v>1236.3</v>
+        <v>571.87</v>
       </c>
       <c r="O804" t="n">
-        <v>63051.3</v>
+        <v>88067.98</v>
       </c>
       <c r="P804" t="n">
-        <v>2300</v>
+        <v>2500</v>
       </c>
       <c r="Q804" t="n">
-        <v>117300</v>
+        <v>385000</v>
       </c>
     </row>
     <row r="805">
       <c r="A805" t="inlineStr">
         <is>
-          <t>MG26010</t>
+          <t>MG40720</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>MG40720</t>
         </is>
       </c>
       <c r="C805" t="inlineStr">
         <is>
-          <t>SET BELLEZA CON ACCESORIOS EMPAQUE BOLSO MG26010</t>
+          <t>MAQUINA DE COSER MINI MG40720</t>
         </is>
       </c>
       <c r="E805" t="inlineStr">
@@ -36955,7 +36975,7 @@
         </is>
       </c>
       <c r="J805" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K805" t="n">
         <v>0</v>
@@ -36964,30 +36984,30 @@
         <v>0</v>
       </c>
       <c r="M805" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="N805" t="n">
-        <v>11433.53</v>
+        <v>9917.040000000001</v>
       </c>
       <c r="O805" t="n">
-        <v>125768.83</v>
+        <v>89253.36000000002</v>
       </c>
       <c r="P805" t="n">
-        <v>15000</v>
+        <v>15900</v>
       </c>
       <c r="Q805" t="n">
-        <v>165000</v>
+        <v>143100</v>
       </c>
     </row>
     <row r="806">
       <c r="A806" t="inlineStr">
         <is>
-          <t>MG27230</t>
+          <t>MG40721</t>
         </is>
       </c>
       <c r="C806" t="inlineStr">
         <is>
-          <t>SET PLASTILINA ODONTOLOGICO CAJA MG27230</t>
+          <t>MAQUINA DE COSER CON PLANCHA MG40721</t>
         </is>
       </c>
       <c r="E806" t="inlineStr">
@@ -37001,7 +37021,7 @@
         </is>
       </c>
       <c r="J806" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K806" t="n">
         <v>0</v>
@@ -37010,40 +37030,35 @@
         <v>0</v>
       </c>
       <c r="M806" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N806" t="n">
-        <v>12115.88</v>
+        <v>12391.068181818</v>
       </c>
       <c r="O806" t="n">
-        <v>109042.92</v>
+        <v>136301.749999998</v>
       </c>
       <c r="P806" t="n">
-        <v>31500</v>
+        <v>34900</v>
       </c>
       <c r="Q806" t="n">
-        <v>283500</v>
+        <v>383900</v>
       </c>
     </row>
     <row r="807">
       <c r="A807" t="inlineStr">
         <is>
-          <t>MG33219</t>
-        </is>
-      </c>
-      <c r="B807" t="inlineStr">
-        <is>
-          <t>MG33219</t>
+          <t>MG40942</t>
         </is>
       </c>
       <c r="C807" t="inlineStr">
         <is>
-          <t>BINOCULARES CAMUFLADOS MG33219</t>
+          <t>SONAJERO CARRO LEON MG40942</t>
         </is>
       </c>
       <c r="E807" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I807" t="inlineStr">
@@ -37052,7 +37067,7 @@
         </is>
       </c>
       <c r="J807" t="n">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="K807" t="n">
         <v>0</v>
@@ -37061,35 +37076,35 @@
         <v>0</v>
       </c>
       <c r="M807" t="n">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="N807" t="n">
-        <v>751.45</v>
+        <v>1864.5</v>
       </c>
       <c r="O807" t="n">
-        <v>45087</v>
+        <v>7458</v>
       </c>
       <c r="P807" t="n">
-        <v>2500</v>
+        <v>17900</v>
       </c>
       <c r="Q807" t="n">
-        <v>150000</v>
+        <v>71600</v>
       </c>
     </row>
     <row r="808">
       <c r="A808" t="inlineStr">
         <is>
-          <t>MG40210</t>
+          <t>MJC-558</t>
         </is>
       </c>
       <c r="C808" t="inlineStr">
         <is>
-          <t>SONAJERO OSO MG40210</t>
+          <t>MOORAL ESCOLAR TONOS PASTELES 20cm MJC-558</t>
         </is>
       </c>
       <c r="E808" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I808" t="inlineStr">
@@ -37098,7 +37113,7 @@
         </is>
       </c>
       <c r="J808" t="n">
-        <v>154</v>
+        <v>22</v>
       </c>
       <c r="K808" t="n">
         <v>0</v>
@@ -37107,40 +37122,35 @@
         <v>0</v>
       </c>
       <c r="M808" t="n">
-        <v>154</v>
+        <v>22</v>
       </c>
       <c r="N808" t="n">
-        <v>571.87</v>
+        <v>40500</v>
       </c>
       <c r="O808" t="n">
-        <v>88067.98</v>
+        <v>891000</v>
       </c>
       <c r="P808" t="n">
-        <v>2500</v>
+        <v>48600</v>
       </c>
       <c r="Q808" t="n">
-        <v>385000</v>
+        <v>1069200</v>
       </c>
     </row>
     <row r="809">
       <c r="A809" t="inlineStr">
         <is>
-          <t>MG40720</t>
-        </is>
-      </c>
-      <c r="B809" t="inlineStr">
-        <is>
-          <t>MG40720</t>
+          <t>MJC-558-1</t>
         </is>
       </c>
       <c r="C809" t="inlineStr">
         <is>
-          <t>MAQUINA DE COSER MINI MG40720</t>
+          <t>MORRAL ESCOLAR 20cm MOTIVO ESPACIAL DEPORTE MJ-558-1</t>
         </is>
       </c>
       <c r="E809" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I809" t="inlineStr">
@@ -37149,7 +37159,7 @@
         </is>
       </c>
       <c r="J809" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="K809" t="n">
         <v>0</v>
@@ -37158,35 +37168,35 @@
         <v>0</v>
       </c>
       <c r="M809" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="N809" t="n">
-        <v>9917.040000000001</v>
+        <v>40500</v>
       </c>
       <c r="O809" t="n">
-        <v>89253.36000000002</v>
+        <v>607500</v>
       </c>
       <c r="P809" t="n">
-        <v>15900</v>
+        <v>48600</v>
       </c>
       <c r="Q809" t="n">
-        <v>143100</v>
+        <v>729000</v>
       </c>
     </row>
     <row r="810">
       <c r="A810" t="inlineStr">
         <is>
-          <t>MG40721</t>
+          <t>PT14019</t>
         </is>
       </c>
       <c r="C810" t="inlineStr">
         <is>
-          <t>MAQUINA DE COSER CON PLANCHA MG40721</t>
+          <t>CUATRIMOTO CON DESTORNILLADOR DIDACTICA PT14019</t>
         </is>
       </c>
       <c r="E810" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>DIDACTICOS</t>
         </is>
       </c>
       <c r="I810" t="inlineStr">
@@ -37195,7 +37205,7 @@
         </is>
       </c>
       <c r="J810" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K810" t="n">
         <v>0</v>
@@ -37204,35 +37214,35 @@
         <v>0</v>
       </c>
       <c r="M810" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="N810" t="n">
-        <v>12391.068181818</v>
+        <v>1950.7</v>
       </c>
       <c r="O810" t="n">
-        <v>136301.749999998</v>
+        <v>17556.3</v>
       </c>
       <c r="P810" t="n">
-        <v>34900</v>
+        <v>7500</v>
       </c>
       <c r="Q810" t="n">
-        <v>383900</v>
+        <v>67500</v>
       </c>
     </row>
     <row r="811">
       <c r="A811" t="inlineStr">
         <is>
-          <t>MG40942</t>
+          <t>QQ-1502</t>
         </is>
       </c>
       <c r="C811" t="inlineStr">
         <is>
-          <t>SONAJERO CARRO LEON MG40942</t>
+          <t>LAPIZ INFINITO REYRACTIL DEPORTES QQ-1502</t>
         </is>
       </c>
       <c r="E811" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I811" t="inlineStr">
@@ -37241,7 +37251,7 @@
         </is>
       </c>
       <c r="J811" t="n">
-        <v>4</v>
+        <v>72</v>
       </c>
       <c r="K811" t="n">
         <v>0</v>
@@ -37250,30 +37260,30 @@
         <v>0</v>
       </c>
       <c r="M811" t="n">
-        <v>4</v>
+        <v>72</v>
       </c>
       <c r="N811" t="n">
-        <v>1864.5</v>
+        <v>2200</v>
       </c>
       <c r="O811" t="n">
-        <v>7458</v>
+        <v>158400</v>
       </c>
       <c r="P811" t="n">
-        <v>17900</v>
+        <v>2700</v>
       </c>
       <c r="Q811" t="n">
-        <v>71600</v>
+        <v>194400</v>
       </c>
     </row>
     <row r="812">
       <c r="A812" t="inlineStr">
         <is>
-          <t>MJC-558</t>
+          <t>QQ-1503</t>
         </is>
       </c>
       <c r="C812" t="inlineStr">
         <is>
-          <t>MOORAL ESCOLAR TONOS PASTELES 20cm MJC-558</t>
+          <t>LAPIZ INFINITO RETRACTIL CARRITO QQ-1503</t>
         </is>
       </c>
       <c r="E812" t="inlineStr">
@@ -37287,7 +37297,7 @@
         </is>
       </c>
       <c r="J812" t="n">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="K812" t="n">
         <v>0</v>
@@ -37296,30 +37306,30 @@
         <v>0</v>
       </c>
       <c r="M812" t="n">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="N812" t="n">
-        <v>40500</v>
+        <v>2200</v>
       </c>
       <c r="O812" t="n">
-        <v>891000</v>
+        <v>145200</v>
       </c>
       <c r="P812" t="n">
-        <v>48600</v>
+        <v>2700</v>
       </c>
       <c r="Q812" t="n">
-        <v>1069200</v>
+        <v>178200</v>
       </c>
     </row>
     <row r="813">
       <c r="A813" t="inlineStr">
         <is>
-          <t>MJC-558-1</t>
+          <t>QQ-1525</t>
         </is>
       </c>
       <c r="C813" t="inlineStr">
         <is>
-          <t>MORRAL ESCOLAR 20cm MOTIVO ESPACIAL DEPORTE MJ-558-1</t>
+          <t>LAPIZ INFINITO RETRACTIL CAPOBARA QQ-1525</t>
         </is>
       </c>
       <c r="E813" t="inlineStr">
@@ -37333,7 +37343,7 @@
         </is>
       </c>
       <c r="J813" t="n">
-        <v>15</v>
+        <v>67</v>
       </c>
       <c r="K813" t="n">
         <v>0</v>
@@ -37342,35 +37352,35 @@
         <v>0</v>
       </c>
       <c r="M813" t="n">
-        <v>15</v>
+        <v>67</v>
       </c>
       <c r="N813" t="n">
-        <v>40500</v>
+        <v>2200</v>
       </c>
       <c r="O813" t="n">
-        <v>607500</v>
+        <v>147400</v>
       </c>
       <c r="P813" t="n">
-        <v>48600</v>
+        <v>2700</v>
       </c>
       <c r="Q813" t="n">
-        <v>729000</v>
+        <v>180900</v>
       </c>
     </row>
     <row r="814">
       <c r="A814" t="inlineStr">
         <is>
-          <t>PT14019</t>
+          <t>QQ-827</t>
         </is>
       </c>
       <c r="C814" t="inlineStr">
         <is>
-          <t>CUATRIMOTO CON DESTORNILLADOR DIDACTICA PT14019</t>
+          <t>ESFERO CON LUZ BALONES QQ-827</t>
         </is>
       </c>
       <c r="E814" t="inlineStr">
         <is>
-          <t>DIDACTICOS</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I814" t="inlineStr">
@@ -37379,7 +37389,7 @@
         </is>
       </c>
       <c r="J814" t="n">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="K814" t="n">
         <v>0</v>
@@ -37388,30 +37398,30 @@
         <v>0</v>
       </c>
       <c r="M814" t="n">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="N814" t="n">
-        <v>1950.7</v>
+        <v>2100</v>
       </c>
       <c r="O814" t="n">
-        <v>17556.3</v>
+        <v>71400</v>
       </c>
       <c r="P814" t="n">
-        <v>7500</v>
+        <v>2600</v>
       </c>
       <c r="Q814" t="n">
-        <v>67500</v>
+        <v>88400</v>
       </c>
     </row>
     <row r="815">
       <c r="A815" t="inlineStr">
         <is>
-          <t>QQ-1502</t>
+          <t>QT511252-E</t>
         </is>
       </c>
       <c r="C815" t="inlineStr">
         <is>
-          <t>LAPIZ INFINITO REYRACTIL DEPORTES QQ-1502</t>
+          <t>COLORES DE ALTA GAMA CARRITOS X12PCS QT511252-E</t>
         </is>
       </c>
       <c r="E815" t="inlineStr">
@@ -37425,7 +37435,7 @@
         </is>
       </c>
       <c r="J815" t="n">
-        <v>72</v>
+        <v>21</v>
       </c>
       <c r="K815" t="n">
         <v>0</v>
@@ -37434,30 +37444,30 @@
         <v>0</v>
       </c>
       <c r="M815" t="n">
-        <v>72</v>
+        <v>21</v>
       </c>
       <c r="N815" t="n">
-        <v>2200</v>
+        <v>5026.6659322034</v>
       </c>
       <c r="O815" t="n">
-        <v>158400</v>
+        <v>105559.9845762714</v>
       </c>
       <c r="P815" t="n">
-        <v>2700</v>
+        <v>6300</v>
       </c>
       <c r="Q815" t="n">
-        <v>194400</v>
+        <v>132300</v>
       </c>
     </row>
     <row r="816">
       <c r="A816" t="inlineStr">
         <is>
-          <t>QQ-1503</t>
+          <t>QT511253-E</t>
         </is>
       </c>
       <c r="C816" t="inlineStr">
         <is>
-          <t>LAPIZ INFINITO RETRACTIL CARRITO QQ-1503</t>
+          <t>COLORES DE ALTA GAMA PRINCESAS X12 PCS QT511253-E</t>
         </is>
       </c>
       <c r="E816" t="inlineStr">
@@ -37471,7 +37481,7 @@
         </is>
       </c>
       <c r="J816" t="n">
-        <v>66</v>
+        <v>21</v>
       </c>
       <c r="K816" t="n">
         <v>0</v>
@@ -37480,30 +37490,30 @@
         <v>0</v>
       </c>
       <c r="M816" t="n">
-        <v>66</v>
+        <v>21</v>
       </c>
       <c r="N816" t="n">
-        <v>2200</v>
+        <v>5200</v>
       </c>
       <c r="O816" t="n">
-        <v>145200</v>
+        <v>109200</v>
       </c>
       <c r="P816" t="n">
-        <v>2700</v>
+        <v>6300</v>
       </c>
       <c r="Q816" t="n">
-        <v>178200</v>
+        <v>132300</v>
       </c>
     </row>
     <row r="817">
       <c r="A817" t="inlineStr">
         <is>
-          <t>QQ-1525</t>
+          <t>QT512453-E</t>
         </is>
       </c>
       <c r="C817" t="inlineStr">
         <is>
-          <t>LAPIZ INFINITO RETRACTIL CAPOBARA QQ-1525</t>
+          <t>COLORES DE ALTA GAMA PRINCESA X24 PCS QT512453-E</t>
         </is>
       </c>
       <c r="E817" t="inlineStr">
@@ -37517,7 +37527,7 @@
         </is>
       </c>
       <c r="J817" t="n">
-        <v>67</v>
+        <v>22</v>
       </c>
       <c r="K817" t="n">
         <v>0</v>
@@ -37526,30 +37536,30 @@
         <v>0</v>
       </c>
       <c r="M817" t="n">
-        <v>67</v>
+        <v>22</v>
       </c>
       <c r="N817" t="n">
-        <v>2200</v>
+        <v>8800</v>
       </c>
       <c r="O817" t="n">
-        <v>147400</v>
+        <v>193600</v>
       </c>
       <c r="P817" t="n">
-        <v>2700</v>
+        <v>10600</v>
       </c>
       <c r="Q817" t="n">
-        <v>180900</v>
+        <v>233200</v>
       </c>
     </row>
     <row r="818">
       <c r="A818" t="inlineStr">
         <is>
-          <t>QQ-827</t>
+          <t>SLT1934</t>
         </is>
       </c>
       <c r="C818" t="inlineStr">
         <is>
-          <t>ESFERO CON LUZ BALONES QQ-827</t>
+          <t>BROMA DE FIESTA CARTON X 40 PCS</t>
         </is>
       </c>
       <c r="E818" t="inlineStr">
@@ -37563,7 +37573,7 @@
         </is>
       </c>
       <c r="J818" t="n">
-        <v>34</v>
+        <v>298</v>
       </c>
       <c r="K818" t="n">
         <v>0</v>
@@ -37572,30 +37582,30 @@
         <v>0</v>
       </c>
       <c r="M818" t="n">
-        <v>34</v>
+        <v>298</v>
       </c>
       <c r="N818" t="n">
-        <v>2100</v>
+        <v>4550</v>
       </c>
       <c r="O818" t="n">
-        <v>71400</v>
+        <v>1355900</v>
       </c>
       <c r="P818" t="n">
-        <v>2600</v>
+        <v>5500</v>
       </c>
       <c r="Q818" t="n">
-        <v>88400</v>
+        <v>1639000</v>
       </c>
     </row>
     <row r="819">
       <c r="A819" t="inlineStr">
         <is>
-          <t>QT511252-E</t>
+          <t>XP-2986</t>
         </is>
       </c>
       <c r="C819" t="inlineStr">
         <is>
-          <t>COLORES DE ALTA GAMA CARRITOS X12PCS QT511252-E</t>
+          <t>BORRADOR RETRACTIL COHETE XP-2986</t>
         </is>
       </c>
       <c r="E819" t="inlineStr">
@@ -37609,7 +37619,7 @@
         </is>
       </c>
       <c r="J819" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="K819" t="n">
         <v>0</v>
@@ -37618,202 +37628,18 @@
         <v>0</v>
       </c>
       <c r="M819" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="N819" t="n">
-        <v>5026.6659322034</v>
+        <v>2402.6741428571</v>
       </c>
       <c r="O819" t="n">
-        <v>105559.9845762714</v>
+        <v>7208.022428571299</v>
       </c>
       <c r="P819" t="n">
-        <v>6300</v>
+        <v>3000</v>
       </c>
       <c r="Q819" t="n">
-        <v>132300</v>
-      </c>
-    </row>
-    <row r="820">
-      <c r="A820" t="inlineStr">
-        <is>
-          <t>QT511253-E</t>
-        </is>
-      </c>
-      <c r="C820" t="inlineStr">
-        <is>
-          <t>COLORES DE ALTA GAMA PRINCESAS X12 PCS QT511253-E</t>
-        </is>
-      </c>
-      <c r="E820" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
-        </is>
-      </c>
-      <c r="I820" t="inlineStr">
-        <is>
-          <t>Und</t>
-        </is>
-      </c>
-      <c r="J820" t="n">
-        <v>21</v>
-      </c>
-      <c r="K820" t="n">
-        <v>0</v>
-      </c>
-      <c r="L820" t="n">
-        <v>0</v>
-      </c>
-      <c r="M820" t="n">
-        <v>21</v>
-      </c>
-      <c r="N820" t="n">
-        <v>5200</v>
-      </c>
-      <c r="O820" t="n">
-        <v>109200</v>
-      </c>
-      <c r="P820" t="n">
-        <v>6300</v>
-      </c>
-      <c r="Q820" t="n">
-        <v>132300</v>
-      </c>
-    </row>
-    <row r="821">
-      <c r="A821" t="inlineStr">
-        <is>
-          <t>QT512453-E</t>
-        </is>
-      </c>
-      <c r="C821" t="inlineStr">
-        <is>
-          <t>COLORES DE ALTA GAMA PRINCESA X24 PCS QT512453-E</t>
-        </is>
-      </c>
-      <c r="E821" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
-        </is>
-      </c>
-      <c r="I821" t="inlineStr">
-        <is>
-          <t>Und</t>
-        </is>
-      </c>
-      <c r="J821" t="n">
-        <v>22</v>
-      </c>
-      <c r="K821" t="n">
-        <v>0</v>
-      </c>
-      <c r="L821" t="n">
-        <v>0</v>
-      </c>
-      <c r="M821" t="n">
-        <v>22</v>
-      </c>
-      <c r="N821" t="n">
-        <v>8800</v>
-      </c>
-      <c r="O821" t="n">
-        <v>193600</v>
-      </c>
-      <c r="P821" t="n">
-        <v>10600</v>
-      </c>
-      <c r="Q821" t="n">
-        <v>233200</v>
-      </c>
-    </row>
-    <row r="822">
-      <c r="A822" t="inlineStr">
-        <is>
-          <t>SLT1934</t>
-        </is>
-      </c>
-      <c r="C822" t="inlineStr">
-        <is>
-          <t>BROMA DE FIESTA CARTON X 40 PCS</t>
-        </is>
-      </c>
-      <c r="E822" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
-        </is>
-      </c>
-      <c r="I822" t="inlineStr">
-        <is>
-          <t>Und</t>
-        </is>
-      </c>
-      <c r="J822" t="n">
-        <v>300</v>
-      </c>
-      <c r="K822" t="n">
-        <v>0</v>
-      </c>
-      <c r="L822" t="n">
-        <v>2</v>
-      </c>
-      <c r="M822" t="n">
-        <v>298</v>
-      </c>
-      <c r="N822" t="n">
-        <v>4550</v>
-      </c>
-      <c r="O822" t="n">
-        <v>1355900</v>
-      </c>
-      <c r="P822" t="n">
-        <v>5500</v>
-      </c>
-      <c r="Q822" t="n">
-        <v>1639000</v>
-      </c>
-    </row>
-    <row r="823">
-      <c r="A823" t="inlineStr">
-        <is>
-          <t>XP-2986</t>
-        </is>
-      </c>
-      <c r="C823" t="inlineStr">
-        <is>
-          <t>BORRADOR RETRACTIL COHETE XP-2986</t>
-        </is>
-      </c>
-      <c r="E823" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
-        </is>
-      </c>
-      <c r="I823" t="inlineStr">
-        <is>
-          <t>Und</t>
-        </is>
-      </c>
-      <c r="J823" t="n">
-        <v>3</v>
-      </c>
-      <c r="K823" t="n">
-        <v>0</v>
-      </c>
-      <c r="L823" t="n">
-        <v>0</v>
-      </c>
-      <c r="M823" t="n">
-        <v>3</v>
-      </c>
-      <c r="N823" t="n">
-        <v>2402.6741428571</v>
-      </c>
-      <c r="O823" t="n">
-        <v>7208.022428571299</v>
-      </c>
-      <c r="P823" t="n">
-        <v>3000</v>
-      </c>
-      <c r="Q823" t="n">
         <v>9000</v>
       </c>
     </row>

--- a/bodegas/LJ-05.xlsx
+++ b/bodegas/LJ-05.xlsx
@@ -944,22 +944,22 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M13" t="n">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="N13" t="n">
-        <v>1811.3058666667</v>
+        <v>1811.3059701493</v>
       </c>
       <c r="O13" t="n">
-        <v>715465.8173333465</v>
+        <v>704598.0223880777</v>
       </c>
       <c r="P13" t="n">
         <v>2600</v>
       </c>
       <c r="Q13" t="n">
-        <v>1027000</v>
+        <v>1011400</v>
       </c>
     </row>
     <row r="14">
@@ -1022,22 +1022,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M15" t="n">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="N15" t="n">
-        <v>3376.7464891304</v>
+        <v>3376.7464843537</v>
       </c>
       <c r="O15" t="n">
-        <v>422093.3111413</v>
+        <v>405209.578122444</v>
       </c>
       <c r="P15" t="n">
         <v>4500</v>
       </c>
       <c r="Q15" t="n">
-        <v>562500</v>
+        <v>540000</v>
       </c>
     </row>
     <row r="16">
@@ -1145,10 +1145,10 @@
         <v>21</v>
       </c>
       <c r="N18" t="n">
-        <v>5758.9597787611</v>
+        <v>5758.9597782705</v>
       </c>
       <c r="O18" t="n">
-        <v>120938.1553539831</v>
+        <v>120938.1553436805</v>
       </c>
       <c r="P18" t="n">
         <v>16900</v>
@@ -1217,22 +1217,22 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M20" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="N20" t="n">
         <v>4072</v>
       </c>
       <c r="O20" t="n">
-        <v>321688</v>
+        <v>280968</v>
       </c>
       <c r="P20" t="n">
         <v>7500</v>
       </c>
       <c r="Q20" t="n">
-        <v>592500</v>
+        <v>517500</v>
       </c>
     </row>
     <row r="21">
@@ -2406,10 +2406,10 @@
         <v>1</v>
       </c>
       <c r="N49" t="n">
-        <v>3910.6281818182</v>
+        <v>3910.6281707317</v>
       </c>
       <c r="O49" t="n">
-        <v>3910.6281818182</v>
+        <v>3910.6281707317</v>
       </c>
       <c r="P49" t="n">
         <v>9100</v>
@@ -3180,10 +3180,10 @@
         <v>41</v>
       </c>
       <c r="N66" t="n">
-        <v>15711.966041667</v>
+        <v>15711.966008403</v>
       </c>
       <c r="O66" t="n">
-        <v>644190.607708347</v>
+        <v>644190.606344523</v>
       </c>
       <c r="P66" t="n">
         <v>28500</v>
@@ -3902,10 +3902,10 @@
         <v>1</v>
       </c>
       <c r="N83" t="n">
-        <v>56906.802542373</v>
+        <v>56906.802982456</v>
       </c>
       <c r="O83" t="n">
-        <v>56906.802542373</v>
+        <v>56906.802982456</v>
       </c>
       <c r="P83" t="n">
         <v>95900</v>
@@ -3949,10 +3949,10 @@
         <v>4</v>
       </c>
       <c r="N84" t="n">
-        <v>62349.658857143</v>
+        <v>62349.657575758</v>
       </c>
       <c r="O84" t="n">
-        <v>249398.635428572</v>
+        <v>249398.630303032</v>
       </c>
       <c r="P84" t="n">
         <v>109900</v>
@@ -4038,10 +4038,10 @@
         <v>2</v>
       </c>
       <c r="N86" t="n">
-        <v>200072.2004878</v>
+        <v>200072.20057377</v>
       </c>
       <c r="O86" t="n">
-        <v>400144.4009756</v>
+        <v>400144.40114754</v>
       </c>
       <c r="P86" t="n">
         <v>312000</v>
@@ -6464,22 +6464,22 @@
         <v>0</v>
       </c>
       <c r="L142" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="M142" t="n">
-        <v>1309</v>
+        <v>1286</v>
       </c>
       <c r="N142" t="n">
         <v>1726.32</v>
       </c>
       <c r="O142" t="n">
-        <v>2259752.88</v>
+        <v>2220047.52</v>
       </c>
       <c r="P142" t="n">
         <v>1500</v>
       </c>
       <c r="Q142" t="n">
-        <v>1963500</v>
+        <v>1929000</v>
       </c>
     </row>
     <row r="143">
@@ -6516,10 +6516,10 @@
         <v>1</v>
       </c>
       <c r="N143" t="n">
-        <v>4937.3101616458</v>
+        <v>4937.3101623616</v>
       </c>
       <c r="O143" t="n">
-        <v>4937.3101616458</v>
+        <v>4937.3101623616</v>
       </c>
       <c r="P143" t="n">
         <v>7500</v>
@@ -6733,22 +6733,22 @@
         <v>0</v>
       </c>
       <c r="L148" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M148" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="N148" t="n">
         <v>951</v>
       </c>
       <c r="O148" t="n">
-        <v>15216</v>
+        <v>0</v>
       </c>
       <c r="P148" t="n">
         <v>1900</v>
       </c>
       <c r="Q148" t="n">
-        <v>30400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149">
@@ -7400,10 +7400,10 @@
         <v>31</v>
       </c>
       <c r="N163" t="n">
-        <v>2582.2558919365</v>
+        <v>2582.2558569052</v>
       </c>
       <c r="O163" t="n">
-        <v>80049.93265003151</v>
+        <v>80049.93156406119</v>
       </c>
       <c r="P163" t="n">
         <v>4500</v>
@@ -7440,22 +7440,22 @@
         <v>0</v>
       </c>
       <c r="L164" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M164" t="n">
-        <v>303</v>
+        <v>283</v>
       </c>
       <c r="N164" t="n">
         <v>10600</v>
       </c>
       <c r="O164" t="n">
-        <v>3211800</v>
+        <v>2999800</v>
       </c>
       <c r="P164" t="n">
         <v>17200</v>
       </c>
       <c r="Q164" t="n">
-        <v>5211600</v>
+        <v>4867600</v>
       </c>
     </row>
     <row r="165">
@@ -7492,10 +7492,10 @@
         <v>27</v>
       </c>
       <c r="N165" t="n">
-        <v>5216.8961798703</v>
+        <v>5216.8961652752</v>
       </c>
       <c r="O165" t="n">
-        <v>140856.1968564981</v>
+        <v>140856.1964624304</v>
       </c>
       <c r="P165" t="n">
         <v>8500</v>
@@ -7538,10 +7538,10 @@
         <v>735</v>
       </c>
       <c r="N166" t="n">
-        <v>3158.8608246566</v>
+        <v>3158.8608249792</v>
       </c>
       <c r="O166" t="n">
-        <v>2321762.706122601</v>
+        <v>2321762.706359712</v>
       </c>
       <c r="P166" t="n">
         <v>5600</v>
@@ -7722,10 +7722,10 @@
         <v>683</v>
       </c>
       <c r="N170" t="n">
-        <v>2694.8232527881</v>
+        <v>2694.823243369</v>
       </c>
       <c r="O170" t="n">
-        <v>1840564.281654272</v>
+        <v>1840564.275221027</v>
       </c>
       <c r="P170" t="n">
         <v>4900</v>
@@ -7808,22 +7808,22 @@
         <v>0</v>
       </c>
       <c r="L172" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M172" t="n">
-        <v>1725</v>
+        <v>1715</v>
       </c>
       <c r="N172" t="n">
         <v>156.25</v>
       </c>
       <c r="O172" t="n">
-        <v>269531.25</v>
+        <v>267968.75</v>
       </c>
       <c r="P172" t="n">
         <v>250</v>
       </c>
       <c r="Q172" t="n">
-        <v>431250</v>
+        <v>428750</v>
       </c>
     </row>
     <row r="173">
@@ -7992,22 +7992,22 @@
         <v>0</v>
       </c>
       <c r="L176" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M176" t="n">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="N176" t="n">
         <v>6507</v>
       </c>
       <c r="O176" t="n">
-        <v>1600722</v>
+        <v>1594215</v>
       </c>
       <c r="P176" t="n">
         <v>9900</v>
       </c>
       <c r="Q176" t="n">
-        <v>2435400</v>
+        <v>2425500</v>
       </c>
     </row>
     <row r="177">
@@ -8263,22 +8263,22 @@
         <v>0</v>
       </c>
       <c r="L182" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M182" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="N182" t="n">
-        <v>4890.9300476474</v>
+        <v>4890.9300481348</v>
       </c>
       <c r="O182" t="n">
-        <v>166291.6216200116</v>
+        <v>117382.3211552352</v>
       </c>
       <c r="P182" t="n">
         <v>8200</v>
       </c>
       <c r="Q182" t="n">
-        <v>278800</v>
+        <v>196800</v>
       </c>
     </row>
     <row r="183">
@@ -8358,22 +8358,22 @@
         <v>0</v>
       </c>
       <c r="L184" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M184" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="N184" t="n">
-        <v>4967.8238461538</v>
+        <v>4967.8308421053</v>
       </c>
       <c r="O184" t="n">
-        <v>397425.907692304</v>
+        <v>367619.4823157922</v>
       </c>
       <c r="P184" t="n">
         <v>7500</v>
       </c>
       <c r="Q184" t="n">
-        <v>600000</v>
+        <v>555000</v>
       </c>
     </row>
     <row r="185">
@@ -8448,22 +8448,22 @@
         <v>0</v>
       </c>
       <c r="L186" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M186" t="n">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="N186" t="n">
         <v>1203.38</v>
       </c>
       <c r="O186" t="n">
-        <v>87846.74000000001</v>
+        <v>58965.62</v>
       </c>
       <c r="P186" t="n">
         <v>1900</v>
       </c>
       <c r="Q186" t="n">
-        <v>138700</v>
+        <v>93100</v>
       </c>
     </row>
     <row r="187">
@@ -8994,10 +8994,10 @@
         <v>5</v>
       </c>
       <c r="N198" t="n">
-        <v>3594.25408867</v>
+        <v>3594.2540740741</v>
       </c>
       <c r="O198" t="n">
-        <v>17971.27044335</v>
+        <v>17971.2703703705</v>
       </c>
       <c r="P198" t="n">
         <v>6500</v>
@@ -9083,22 +9083,22 @@
         <v>0</v>
       </c>
       <c r="L200" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="M200" t="n">
-        <v>1825</v>
+        <v>1786</v>
       </c>
       <c r="N200" t="n">
         <v>489.88</v>
       </c>
       <c r="O200" t="n">
-        <v>894031</v>
+        <v>874925.6799999999</v>
       </c>
       <c r="P200" t="n">
         <v>700</v>
       </c>
       <c r="Q200" t="n">
-        <v>1277500</v>
+        <v>1250200</v>
       </c>
     </row>
     <row r="201">
@@ -9227,10 +9227,10 @@
         <v>31</v>
       </c>
       <c r="N203" t="n">
-        <v>14822.378855098</v>
+        <v>14822.378854415</v>
       </c>
       <c r="O203" t="n">
-        <v>459493.744508038</v>
+        <v>459493.744486865</v>
       </c>
       <c r="P203" t="n">
         <v>24900</v>
@@ -9810,22 +9810,22 @@
         <v>0</v>
       </c>
       <c r="L216" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M216" t="n">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="N216" t="n">
         <v>1441.01</v>
       </c>
       <c r="O216" t="n">
-        <v>742120.15</v>
+        <v>737797.12</v>
       </c>
       <c r="P216" t="n">
         <v>2100</v>
       </c>
       <c r="Q216" t="n">
-        <v>1081500</v>
+        <v>1075200</v>
       </c>
     </row>
     <row r="217">
@@ -9950,10 +9950,10 @@
         <v>122</v>
       </c>
       <c r="N219" t="n">
-        <v>3041.6600129618</v>
+        <v>3041.6600129786</v>
       </c>
       <c r="O219" t="n">
-        <v>371082.5215813396</v>
+        <v>371082.5215833892</v>
       </c>
       <c r="P219" t="n">
         <v>5500</v>
@@ -9996,10 +9996,10 @@
         <v>58</v>
       </c>
       <c r="N220" t="n">
-        <v>4372.210788556</v>
+        <v>4372.2107886682</v>
       </c>
       <c r="O220" t="n">
-        <v>253588.225736248</v>
+        <v>253588.2257427556</v>
       </c>
       <c r="P220" t="n">
         <v>7500</v>
@@ -10042,10 +10042,10 @@
         <v>348</v>
       </c>
       <c r="N221" t="n">
-        <v>1592.5670028818</v>
+        <v>1592.5669608416</v>
       </c>
       <c r="O221" t="n">
-        <v>554213.3170028664</v>
+        <v>554213.3023728768</v>
       </c>
       <c r="P221" t="n">
         <v>3900</v>
@@ -10297,22 +10297,22 @@
         <v>0</v>
       </c>
       <c r="L227" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M227" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="N227" t="n">
         <v>6242.93</v>
       </c>
       <c r="O227" t="n">
-        <v>480705.61</v>
+        <v>468219.75</v>
       </c>
       <c r="P227" t="n">
         <v>10400</v>
       </c>
       <c r="Q227" t="n">
-        <v>800800</v>
+        <v>780000</v>
       </c>
     </row>
     <row r="228">
@@ -10395,22 +10395,22 @@
         <v>0</v>
       </c>
       <c r="L229" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M229" t="n">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="N229" t="n">
         <v>1770.37</v>
       </c>
       <c r="O229" t="n">
-        <v>377088.81</v>
+        <v>364696.22</v>
       </c>
       <c r="P229" t="n">
         <v>3900</v>
       </c>
       <c r="Q229" t="n">
-        <v>830700</v>
+        <v>803400</v>
       </c>
     </row>
     <row r="230">
@@ -10661,22 +10661,22 @@
         <v>0</v>
       </c>
       <c r="L235" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M235" t="n">
-        <v>2260</v>
+        <v>2256</v>
       </c>
       <c r="N235" t="n">
         <v>1387.55</v>
       </c>
       <c r="O235" t="n">
-        <v>3135863</v>
+        <v>3130312.8</v>
       </c>
       <c r="P235" t="n">
         <v>2300</v>
       </c>
       <c r="Q235" t="n">
-        <v>5198000</v>
+        <v>5188800</v>
       </c>
     </row>
     <row r="236">
@@ -10986,22 +10986,22 @@
         <v>0</v>
       </c>
       <c r="L242" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M242" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N242" t="n">
         <v>8341.030000000001</v>
       </c>
       <c r="O242" t="n">
-        <v>108433.39</v>
+        <v>100092.36</v>
       </c>
       <c r="P242" t="n">
         <v>13900</v>
       </c>
       <c r="Q242" t="n">
-        <v>180700</v>
+        <v>166800</v>
       </c>
     </row>
     <row r="243">
@@ -11351,22 +11351,22 @@
         <v>0</v>
       </c>
       <c r="L250" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M250" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="N250" t="n">
-        <v>1630.9234162594</v>
+        <v>1630.9234624043</v>
       </c>
       <c r="O250" t="n">
-        <v>97855.404975564</v>
+        <v>94593.5608194494</v>
       </c>
       <c r="P250" t="n">
         <v>2500</v>
       </c>
       <c r="Q250" t="n">
-        <v>150000</v>
+        <v>145000</v>
       </c>
     </row>
     <row r="251">
@@ -11397,22 +11397,22 @@
         <v>0</v>
       </c>
       <c r="L251" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M251" t="n">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="N251" t="n">
-        <v>1550.1934418475</v>
+        <v>1550.1935205388</v>
       </c>
       <c r="O251" t="n">
-        <v>195324.373672785</v>
+        <v>190673.8030262724</v>
       </c>
       <c r="P251" t="n">
         <v>2500</v>
       </c>
       <c r="Q251" t="n">
-        <v>315000</v>
+        <v>307500</v>
       </c>
     </row>
     <row r="252">
@@ -11443,22 +11443,22 @@
         <v>0</v>
       </c>
       <c r="L252" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M252" t="n">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="N252" t="n">
-        <v>2403.5113112366</v>
+        <v>2403.5114869613</v>
       </c>
       <c r="O252" t="n">
-        <v>1329141.75511384</v>
+        <v>1319527.806341754</v>
       </c>
       <c r="P252" t="n">
         <v>3500</v>
       </c>
       <c r="Q252" t="n">
-        <v>1935500</v>
+        <v>1921500</v>
       </c>
     </row>
     <row r="253">
@@ -12589,10 +12589,10 @@
         <v>226</v>
       </c>
       <c r="N278" t="n">
-        <v>2029.8737332006</v>
+        <v>2029.8737350598</v>
       </c>
       <c r="O278" t="n">
-        <v>458751.4637033356</v>
+        <v>458751.4641235148</v>
       </c>
       <c r="P278" t="n">
         <v>3600</v>
@@ -12630,10 +12630,10 @@
         <v>19</v>
       </c>
       <c r="N279" t="n">
-        <v>22485.695890411</v>
+        <v>22485.695885714</v>
       </c>
       <c r="O279" t="n">
-        <v>427228.221917809</v>
+        <v>427228.221828566</v>
       </c>
       <c r="P279" t="n">
         <v>36500</v>
@@ -12665,22 +12665,22 @@
         <v>0</v>
       </c>
       <c r="L280" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M280" t="n">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="N280" t="n">
         <v>2673</v>
       </c>
       <c r="O280" t="n">
-        <v>446391</v>
+        <v>425007</v>
       </c>
       <c r="P280" t="n">
         <v>2500</v>
       </c>
       <c r="Q280" t="n">
-        <v>417500</v>
+        <v>397500</v>
       </c>
     </row>
     <row r="281">
@@ -12884,10 +12884,10 @@
         <v>64</v>
       </c>
       <c r="N285" t="n">
-        <v>2680.7396999388</v>
+        <v>2680.7396995708</v>
       </c>
       <c r="O285" t="n">
-        <v>171567.3407960832</v>
+        <v>171567.3407725312</v>
       </c>
       <c r="P285" t="n">
         <v>4900</v>
@@ -13291,10 +13291,10 @@
         <v>93</v>
       </c>
       <c r="N294" t="n">
-        <v>4285.1953927813</v>
+        <v>4285.1954215582</v>
       </c>
       <c r="O294" t="n">
-        <v>398523.1715286609</v>
+        <v>398523.1742049126</v>
       </c>
       <c r="P294" t="n">
         <v>6900</v>
@@ -13596,10 +13596,10 @@
         <v>72</v>
       </c>
       <c r="N301" t="n">
-        <v>4605.2146617238</v>
+        <v>4605.2146660482</v>
       </c>
       <c r="O301" t="n">
-        <v>331575.4556441137</v>
+        <v>331575.4559554704</v>
       </c>
       <c r="P301" t="n">
         <v>7600</v>
@@ -13631,22 +13631,22 @@
         <v>0</v>
       </c>
       <c r="L302" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M302" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="N302" t="n">
         <v>3591.13</v>
       </c>
       <c r="O302" t="n">
-        <v>186738.76</v>
+        <v>183147.63</v>
       </c>
       <c r="P302" t="n">
         <v>6300</v>
       </c>
       <c r="Q302" t="n">
-        <v>327600</v>
+        <v>321300</v>
       </c>
     </row>
     <row r="303">
@@ -13729,10 +13729,10 @@
         <v>36</v>
       </c>
       <c r="N304" t="n">
-        <v>11562.038522427</v>
+        <v>11562.038518519</v>
       </c>
       <c r="O304" t="n">
-        <v>416233.386807372</v>
+        <v>416233.386666684</v>
       </c>
       <c r="P304" t="n">
         <v>18500</v>
@@ -14618,22 +14618,22 @@
         <v>0</v>
       </c>
       <c r="L324" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M324" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="N324" t="n">
-        <v>1561</v>
+        <v>1561.0000887728</v>
       </c>
       <c r="O324" t="n">
-        <v>121758</v>
+        <v>113953.0064804144</v>
       </c>
       <c r="P324" t="n">
         <v>2900</v>
       </c>
       <c r="Q324" t="n">
-        <v>226200</v>
+        <v>211700</v>
       </c>
     </row>
     <row r="325">
@@ -14928,22 +14928,22 @@
         <v>0</v>
       </c>
       <c r="L331" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M331" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="N331" t="n">
-        <v>7969.9501660377</v>
+        <v>7969.9501665405</v>
       </c>
       <c r="O331" t="n">
-        <v>1219402.375403768</v>
+        <v>1211432.425314156</v>
       </c>
       <c r="P331" t="n">
         <v>12900</v>
       </c>
       <c r="Q331" t="n">
-        <v>1973700</v>
+        <v>1960800</v>
       </c>
     </row>
     <row r="332">
@@ -15656,22 +15656,22 @@
         <v>0</v>
       </c>
       <c r="L347" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M347" t="n">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="N347" t="n">
         <v>2634.61</v>
       </c>
       <c r="O347" t="n">
-        <v>368845.4</v>
+        <v>360941.57</v>
       </c>
       <c r="P347" t="n">
         <v>4200</v>
       </c>
       <c r="Q347" t="n">
-        <v>588000</v>
+        <v>575400</v>
       </c>
     </row>
     <row r="348">
@@ -15702,22 +15702,22 @@
         <v>0</v>
       </c>
       <c r="L348" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M348" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="N348" t="n">
-        <v>3113.8900273598</v>
+        <v>3113.8900274725</v>
       </c>
       <c r="O348" t="n">
-        <v>211744.5218604664</v>
+        <v>202402.8517857125</v>
       </c>
       <c r="P348" t="n">
         <v>5000</v>
       </c>
       <c r="Q348" t="n">
-        <v>340000</v>
+        <v>325000</v>
       </c>
     </row>
     <row r="349">
@@ -15748,22 +15748,22 @@
         <v>0</v>
       </c>
       <c r="L349" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M349" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N349" t="n">
         <v>5569.98</v>
       </c>
       <c r="O349" t="n">
-        <v>261789.06</v>
+        <v>256219.08</v>
       </c>
       <c r="P349" t="n">
         <v>8900</v>
       </c>
       <c r="Q349" t="n">
-        <v>418300</v>
+        <v>409400</v>
       </c>
     </row>
     <row r="350">
@@ -15886,22 +15886,22 @@
         <v>0</v>
       </c>
       <c r="L352" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M352" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N352" t="n">
-        <v>4163.1602</v>
+        <v>4163.1602061856</v>
       </c>
       <c r="O352" t="n">
-        <v>29142.1214</v>
+        <v>16652.6408247424</v>
       </c>
       <c r="P352" t="n">
         <v>6700</v>
       </c>
       <c r="Q352" t="n">
-        <v>46900</v>
+        <v>26800</v>
       </c>
     </row>
     <row r="353">
@@ -16030,10 +16030,10 @@
         <v>91</v>
       </c>
       <c r="N355" t="n">
-        <v>5218.1705346294</v>
+        <v>5218.1705412054</v>
       </c>
       <c r="O355" t="n">
-        <v>474853.5186512754</v>
+        <v>474853.5192496914</v>
       </c>
       <c r="P355" t="n">
         <v>8500</v>
@@ -16076,10 +16076,10 @@
         <v>115</v>
       </c>
       <c r="N356" t="n">
-        <v>1595.0094090202</v>
+        <v>1595.0093958665</v>
       </c>
       <c r="O356" t="n">
-        <v>183426.082037323</v>
+        <v>183426.0805246475</v>
       </c>
       <c r="P356" t="n">
         <v>2600</v>
@@ -16769,10 +16769,10 @@
         <v>99</v>
       </c>
       <c r="N371" t="n">
-        <v>1778.4725974412</v>
+        <v>1778.4725978277</v>
       </c>
       <c r="O371" t="n">
-        <v>176068.7871466788</v>
+        <v>176068.7871849423</v>
       </c>
       <c r="P371" t="n">
         <v>4900</v>
@@ -19963,10 +19963,10 @@
         <v>38</v>
       </c>
       <c r="N440" t="n">
-        <v>4907.8220483871</v>
+        <v>4907.8220583468</v>
       </c>
       <c r="O440" t="n">
-        <v>186497.2378387098</v>
+        <v>186497.2382171784</v>
       </c>
       <c r="P440" t="n">
         <v>8200</v>
@@ -20331,10 +20331,10 @@
         <v>98</v>
       </c>
       <c r="N448" t="n">
-        <v>3903.7363106796</v>
+        <v>3903.7364457831</v>
       </c>
       <c r="O448" t="n">
-        <v>382566.1584466008</v>
+        <v>382566.1716867438</v>
       </c>
       <c r="P448" t="n">
         <v>7500</v>
@@ -21097,22 +21097,22 @@
         <v>0</v>
       </c>
       <c r="L465" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M465" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="N465" t="n">
         <v>5772</v>
       </c>
       <c r="O465" t="n">
-        <v>981240</v>
+        <v>975468</v>
       </c>
       <c r="P465" t="n">
         <v>9900</v>
       </c>
       <c r="Q465" t="n">
-        <v>1683000</v>
+        <v>1673100</v>
       </c>
     </row>
     <row r="466">
@@ -21419,22 +21419,22 @@
         <v>0</v>
       </c>
       <c r="L472" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M472" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N472" t="n">
         <v>3898</v>
       </c>
       <c r="O472" t="n">
-        <v>62368</v>
+        <v>54572</v>
       </c>
       <c r="P472" t="n">
         <v>6900</v>
       </c>
       <c r="Q472" t="n">
-        <v>110400</v>
+        <v>96600</v>
       </c>
     </row>
     <row r="473">
@@ -22072,10 +22072,10 @@
         <v>147</v>
       </c>
       <c r="N486" t="n">
-        <v>17075.98952381</v>
+        <v>17075.989523481</v>
       </c>
       <c r="O486" t="n">
-        <v>2510170.46000007</v>
+        <v>2510170.459951707</v>
       </c>
       <c r="P486" t="n">
         <v>27500</v>
@@ -22245,22 +22245,22 @@
         <v>0</v>
       </c>
       <c r="L490" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M490" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="N490" t="n">
         <v>11015</v>
       </c>
       <c r="O490" t="n">
-        <v>176240</v>
+        <v>132180</v>
       </c>
       <c r="P490" t="n">
         <v>17900</v>
       </c>
       <c r="Q490" t="n">
-        <v>286400</v>
+        <v>214800</v>
       </c>
     </row>
     <row r="491">
@@ -23122,22 +23122,22 @@
         <v>0</v>
       </c>
       <c r="L509" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M509" t="n">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="N509" t="n">
         <v>1326</v>
       </c>
       <c r="O509" t="n">
-        <v>91494</v>
+        <v>78234</v>
       </c>
       <c r="P509" t="n">
         <v>2500</v>
       </c>
       <c r="Q509" t="n">
-        <v>172500</v>
+        <v>147500</v>
       </c>
     </row>
     <row r="510">
@@ -23867,10 +23867,10 @@
         <v>189</v>
       </c>
       <c r="N525" t="n">
-        <v>1516.0388031113</v>
+        <v>1516.0388018299</v>
       </c>
       <c r="O525" t="n">
-        <v>286531.3337880357</v>
+        <v>286531.3335458511</v>
       </c>
       <c r="P525" t="n">
         <v>2300</v>
@@ -23959,10 +23959,10 @@
         <v>435</v>
       </c>
       <c r="N527" t="n">
-        <v>2458.5132807977</v>
+        <v>2458.5132504039</v>
       </c>
       <c r="O527" t="n">
-        <v>1069453.277146999</v>
+        <v>1069453.263925696</v>
       </c>
       <c r="P527" t="n">
         <v>3500</v>
@@ -24005,10 +24005,10 @@
         <v>96</v>
       </c>
       <c r="N528" t="n">
-        <v>1907.3938243626</v>
+        <v>1907.3938009479</v>
       </c>
       <c r="O528" t="n">
-        <v>183109.8071388096</v>
+        <v>183109.8048909984</v>
       </c>
       <c r="P528" t="n">
         <v>2500</v>
@@ -24051,10 +24051,10 @@
         <v>183</v>
       </c>
       <c r="N529" t="n">
-        <v>1771.0906468305</v>
+        <v>1771.0905981795</v>
       </c>
       <c r="O529" t="n">
-        <v>324109.5883699815</v>
+        <v>324109.5794668485</v>
       </c>
       <c r="P529" t="n">
         <v>2500</v>
@@ -24097,10 +24097,10 @@
         <v>441</v>
       </c>
       <c r="N530" t="n">
-        <v>2079.3840533333</v>
+        <v>2079.3840473807</v>
       </c>
       <c r="O530" t="n">
-        <v>917008.3675199853</v>
+        <v>917008.3648948887</v>
       </c>
       <c r="P530" t="n">
         <v>2900</v>
@@ -24143,10 +24143,10 @@
         <v>307</v>
       </c>
       <c r="N531" t="n">
-        <v>1803.0155537353</v>
+        <v>1803.0155591997</v>
       </c>
       <c r="O531" t="n">
-        <v>553525.7749967371</v>
+        <v>553525.7766743079</v>
       </c>
       <c r="P531" t="n">
         <v>2500</v>
@@ -24189,10 +24189,10 @@
         <v>96</v>
       </c>
       <c r="N532" t="n">
-        <v>3306.5952380952</v>
+        <v>3306.5951935915</v>
       </c>
       <c r="O532" t="n">
-        <v>317433.1428571392</v>
+        <v>317433.138584784</v>
       </c>
       <c r="P532" t="n">
         <v>4900</v>
@@ -24235,10 +24235,10 @@
         <v>559</v>
       </c>
       <c r="N533" t="n">
-        <v>2122.1639235788</v>
+        <v>2122.1639198011</v>
       </c>
       <c r="O533" t="n">
-        <v>1186289.633280549</v>
+        <v>1186289.631168815</v>
       </c>
       <c r="P533" t="n">
         <v>2900</v>
@@ -24281,10 +24281,10 @@
         <v>299</v>
       </c>
       <c r="N534" t="n">
-        <v>2108.7910927573</v>
+        <v>2108.7914267016</v>
       </c>
       <c r="O534" t="n">
-        <v>630528.5367344327</v>
+        <v>630528.6365837784</v>
       </c>
       <c r="P534" t="n">
         <v>2900</v>
@@ -24327,10 +24327,10 @@
         <v>317</v>
       </c>
       <c r="N535" t="n">
-        <v>2056.0834704208</v>
+        <v>2056.0834183673</v>
       </c>
       <c r="O535" t="n">
-        <v>651778.4601233936</v>
+        <v>651778.4436224342</v>
       </c>
       <c r="P535" t="n">
         <v>2900</v>
@@ -24373,10 +24373,10 @@
         <v>333</v>
       </c>
       <c r="N536" t="n">
-        <v>3224.5685035629</v>
+        <v>3224.5685238095</v>
       </c>
       <c r="O536" t="n">
-        <v>1073781.311686446</v>
+        <v>1073781.318428564</v>
       </c>
       <c r="P536" t="n">
         <v>4500</v>
@@ -24419,10 +24419,10 @@
         <v>285</v>
       </c>
       <c r="N537" t="n">
-        <v>1655.9309755302</v>
+        <v>1655.9309666884</v>
       </c>
       <c r="O537" t="n">
-        <v>471940.328026107</v>
+        <v>471940.325506194</v>
       </c>
       <c r="P537" t="n">
         <v>2500</v>
@@ -24551,22 +24551,22 @@
         <v>0</v>
       </c>
       <c r="L540" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M540" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="N540" t="n">
         <v>2454</v>
       </c>
       <c r="O540" t="n">
-        <v>112884</v>
+        <v>100614</v>
       </c>
       <c r="P540" t="n">
         <v>4200</v>
       </c>
       <c r="Q540" t="n">
-        <v>193200</v>
+        <v>172200</v>
       </c>
     </row>
     <row r="541">
@@ -24597,22 +24597,22 @@
         <v>0</v>
       </c>
       <c r="L541" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M541" t="n">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="N541" t="n">
-        <v>1592.276898982</v>
+        <v>1592.2773416667</v>
       </c>
       <c r="O541" t="n">
-        <v>299348.057008616</v>
+        <v>297755.8628916729</v>
       </c>
       <c r="P541" t="n">
         <v>2500</v>
       </c>
       <c r="Q541" t="n">
-        <v>470000</v>
+        <v>467500</v>
       </c>
     </row>
     <row r="542">
@@ -24693,10 +24693,10 @@
         <v>41</v>
       </c>
       <c r="N543" t="n">
-        <v>1668.6274157303</v>
+        <v>1668.628045977</v>
       </c>
       <c r="O543" t="n">
-        <v>68413.7240449423</v>
+        <v>68413.749885057</v>
       </c>
       <c r="P543" t="n">
         <v>2500</v>
@@ -24739,10 +24739,10 @@
         <v>35</v>
       </c>
       <c r="N544" t="n">
-        <v>2546.9846516008</v>
+        <v>2546.9843873518</v>
       </c>
       <c r="O544" t="n">
-        <v>89144.46280602801</v>
+        <v>89144.453557313</v>
       </c>
       <c r="P544" t="n">
         <v>3900</v>
@@ -24785,10 +24785,10 @@
         <v>966</v>
       </c>
       <c r="N545" t="n">
-        <v>1259.2745137492</v>
+        <v>1259.2745258911</v>
       </c>
       <c r="O545" t="n">
-        <v>1216459.180281727</v>
+        <v>1216459.192010803</v>
       </c>
       <c r="P545" t="n">
         <v>1900</v>
@@ -24866,22 +24866,22 @@
         <v>0</v>
       </c>
       <c r="L547" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M547" t="n">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="N547" t="n">
-        <v>2842.2737539432</v>
+        <v>2842.2737341772</v>
       </c>
       <c r="O547" t="n">
-        <v>642353.8683911632</v>
+        <v>636669.3164556928</v>
       </c>
       <c r="P547" t="n">
         <v>4900</v>
       </c>
       <c r="Q547" t="n">
-        <v>1107400</v>
+        <v>1097600</v>
       </c>
     </row>
     <row r="548">
@@ -24958,22 +24958,22 @@
         <v>0</v>
       </c>
       <c r="L549" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="M549" t="n">
-        <v>538</v>
+        <v>489</v>
       </c>
       <c r="N549" t="n">
         <v>1801</v>
       </c>
       <c r="O549" t="n">
-        <v>968938</v>
+        <v>880689</v>
       </c>
       <c r="P549" t="n">
         <v>2900</v>
       </c>
       <c r="Q549" t="n">
-        <v>1560200</v>
+        <v>1418100</v>
       </c>
     </row>
     <row r="550">
@@ -26039,22 +26039,22 @@
         <v>0</v>
       </c>
       <c r="L572" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M572" t="n">
-        <v>1316</v>
+        <v>1313</v>
       </c>
       <c r="N572" t="n">
         <v>1828.64</v>
       </c>
       <c r="O572" t="n">
-        <v>2406490.24</v>
+        <v>2401004.32</v>
       </c>
       <c r="P572" t="n">
         <v>2000</v>
       </c>
       <c r="Q572" t="n">
-        <v>2632000</v>
+        <v>2626000</v>
       </c>
     </row>
     <row r="573">
@@ -26091,10 +26091,10 @@
         <v>180</v>
       </c>
       <c r="N573" t="n">
-        <v>1690.870009058</v>
+        <v>1690.8700090909</v>
       </c>
       <c r="O573" t="n">
-        <v>304356.60163044</v>
+        <v>304356.601636362</v>
       </c>
       <c r="P573" t="n">
         <v>3000</v>
@@ -26593,22 +26593,22 @@
         <v>0</v>
       </c>
       <c r="L584" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M584" t="n">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="N584" t="n">
-        <v>1283.6539261745</v>
+        <v>1283.6538013699</v>
       </c>
       <c r="O584" t="n">
-        <v>169442.318255034</v>
+        <v>161740.3789726074</v>
       </c>
       <c r="P584" t="n">
         <v>1900</v>
       </c>
       <c r="Q584" t="n">
-        <v>250800</v>
+        <v>239400</v>
       </c>
     </row>
     <row r="585">
@@ -26868,22 +26868,22 @@
         <v>0</v>
       </c>
       <c r="L590" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="M590" t="n">
-        <v>1998</v>
+        <v>1962</v>
       </c>
       <c r="N590" t="n">
-        <v>517.28896164542</v>
+        <v>517.28908220781</v>
       </c>
       <c r="O590" t="n">
-        <v>1033543.345367549</v>
+        <v>1014921.179291723</v>
       </c>
       <c r="P590" t="n">
         <v>900</v>
       </c>
       <c r="Q590" t="n">
-        <v>1798200</v>
+        <v>1765800</v>
       </c>
     </row>
     <row r="591">
@@ -27105,10 +27105,10 @@
         <v>312</v>
       </c>
       <c r="N595" t="n">
-        <v>3110.8423302235</v>
+        <v>3110.842321894</v>
       </c>
       <c r="O595" t="n">
-        <v>970582.807029732</v>
+        <v>970582.8044309281</v>
       </c>
       <c r="P595" t="n">
         <v>4500</v>
@@ -27143,22 +27143,22 @@
         <v>0</v>
       </c>
       <c r="L596" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M596" t="n">
-        <v>1681</v>
+        <v>1633</v>
       </c>
       <c r="N596" t="n">
-        <v>703.79522697548</v>
+        <v>703.79521051815</v>
       </c>
       <c r="O596" t="n">
-        <v>1183079.776545782</v>
+        <v>1149297.578776139</v>
       </c>
       <c r="P596" t="n">
         <v>900</v>
       </c>
       <c r="Q596" t="n">
-        <v>1512900</v>
+        <v>1469700</v>
       </c>
     </row>
     <row r="597">
@@ -27431,22 +27431,22 @@
         <v>0</v>
       </c>
       <c r="L602" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M602" t="n">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="N602" t="n">
-        <v>1595.5132863655</v>
+        <v>1595.513125523</v>
       </c>
       <c r="O602" t="n">
-        <v>550452.0837960975</v>
+        <v>540878.949552297</v>
       </c>
       <c r="P602" t="n">
         <v>2500</v>
       </c>
       <c r="Q602" t="n">
-        <v>862500</v>
+        <v>847500</v>
       </c>
     </row>
     <row r="603">
@@ -28252,22 +28252,22 @@
         <v>0</v>
       </c>
       <c r="L619" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M619" t="n">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="N619" t="n">
         <v>1669.6</v>
       </c>
       <c r="O619" t="n">
-        <v>966698.3999999999</v>
+        <v>958350.3999999999</v>
       </c>
       <c r="P619" t="n">
         <v>2900</v>
       </c>
       <c r="Q619" t="n">
-        <v>1679100</v>
+        <v>1664600</v>
       </c>
     </row>
     <row r="620">
@@ -28770,22 +28770,22 @@
         <v>0</v>
       </c>
       <c r="L630" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M630" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N630" t="n">
         <v>10348.08</v>
       </c>
       <c r="O630" t="n">
-        <v>82784.64</v>
+        <v>72436.56</v>
       </c>
       <c r="P630" t="n">
         <v>16900</v>
       </c>
       <c r="Q630" t="n">
-        <v>135200</v>
+        <v>118300</v>
       </c>
     </row>
     <row r="631">
@@ -28819,22 +28819,22 @@
         <v>0</v>
       </c>
       <c r="L631" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M631" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="N631" t="n">
         <v>10536.4</v>
       </c>
       <c r="O631" t="n">
-        <v>295019.2</v>
+        <v>284482.8</v>
       </c>
       <c r="P631" t="n">
         <v>16900</v>
       </c>
       <c r="Q631" t="n">
-        <v>473200</v>
+        <v>456300</v>
       </c>
     </row>
     <row r="632">
@@ -29836,22 +29836,22 @@
         <v>0</v>
       </c>
       <c r="L652" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M652" t="n">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="N652" t="n">
         <v>3000.33</v>
       </c>
       <c r="O652" t="n">
-        <v>777085.47</v>
+        <v>774085.14</v>
       </c>
       <c r="P652" t="n">
         <v>2900</v>
       </c>
       <c r="Q652" t="n">
-        <v>751100</v>
+        <v>748200</v>
       </c>
     </row>
     <row r="653">
@@ -30424,10 +30424,10 @@
         <v>33</v>
       </c>
       <c r="N664" t="n">
-        <v>4159.0002941176</v>
+        <v>4159.000295203</v>
       </c>
       <c r="O664" t="n">
-        <v>137247.0097058808</v>
+        <v>137247.009741699</v>
       </c>
       <c r="P664" t="n">
         <v>8900</v>
@@ -30929,22 +30929,22 @@
         <v>0</v>
       </c>
       <c r="L675" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M675" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N675" t="n">
         <v>9372</v>
       </c>
       <c r="O675" t="n">
-        <v>56232</v>
+        <v>46860</v>
       </c>
       <c r="P675" t="n">
         <v>17900</v>
       </c>
       <c r="Q675" t="n">
-        <v>107400</v>
+        <v>89500</v>
       </c>
     </row>
     <row r="676">
@@ -31743,22 +31743,22 @@
         <v>0</v>
       </c>
       <c r="L692" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M692" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N692" t="n">
         <v>24338.47</v>
       </c>
       <c r="O692" t="n">
-        <v>608461.75</v>
+        <v>584123.28</v>
       </c>
       <c r="P692" t="n">
         <v>27900</v>
       </c>
       <c r="Q692" t="n">
-        <v>697500</v>
+        <v>669600</v>
       </c>
     </row>
     <row r="693">
@@ -32077,22 +32077,22 @@
         <v>0</v>
       </c>
       <c r="L699" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M699" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="N699" t="n">
         <v>1338.14</v>
       </c>
       <c r="O699" t="n">
-        <v>210087.98</v>
+        <v>207411.7</v>
       </c>
       <c r="P699" t="n">
         <v>2500</v>
       </c>
       <c r="Q699" t="n">
-        <v>392500</v>
+        <v>387500</v>
       </c>
     </row>
     <row r="700">
@@ -32126,22 +32126,22 @@
         <v>0</v>
       </c>
       <c r="L700" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M700" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="N700" t="n">
         <v>424.99</v>
       </c>
       <c r="O700" t="n">
-        <v>11899.72</v>
+        <v>7649.82</v>
       </c>
       <c r="P700" t="n">
         <v>2300</v>
       </c>
       <c r="Q700" t="n">
-        <v>64400</v>
+        <v>41400</v>
       </c>
     </row>
     <row r="701">
@@ -33053,22 +33053,22 @@
         <v>0</v>
       </c>
       <c r="L720" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M720" t="n">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="N720" t="n">
-        <v>705.52801204819</v>
+        <v>705.52800453515</v>
       </c>
       <c r="O720" t="n">
-        <v>368991.1503012034</v>
+        <v>365463.5063492077</v>
       </c>
       <c r="P720" t="n">
         <v>1500</v>
       </c>
       <c r="Q720" t="n">
-        <v>784500</v>
+        <v>777000</v>
       </c>
     </row>
     <row r="721">
@@ -33375,22 +33375,22 @@
         <v>0</v>
       </c>
       <c r="L727" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M727" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="N727" t="n">
         <v>5850</v>
       </c>
       <c r="O727" t="n">
-        <v>245700</v>
+        <v>210600</v>
       </c>
       <c r="P727" t="n">
         <v>7900</v>
       </c>
       <c r="Q727" t="n">
-        <v>331800</v>
+        <v>284400</v>
       </c>
     </row>
     <row r="728">
@@ -33743,22 +33743,22 @@
         <v>0</v>
       </c>
       <c r="L735" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M735" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N735" t="n">
         <v>18000</v>
       </c>
       <c r="O735" t="n">
-        <v>144000</v>
+        <v>108000</v>
       </c>
       <c r="P735" t="n">
         <v>23900</v>
       </c>
       <c r="Q735" t="n">
-        <v>191200</v>
+        <v>143400</v>
       </c>
     </row>
     <row r="736">
@@ -33881,22 +33881,22 @@
         <v>0</v>
       </c>
       <c r="L738" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M738" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="N738" t="n">
         <v>18000</v>
       </c>
       <c r="O738" t="n">
-        <v>378000</v>
+        <v>324000</v>
       </c>
       <c r="P738" t="n">
         <v>22500</v>
       </c>
       <c r="Q738" t="n">
-        <v>472500</v>
+        <v>405000</v>
       </c>
     </row>
     <row r="739">
@@ -34341,22 +34341,22 @@
         <v>0</v>
       </c>
       <c r="L748" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M748" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N748" t="n">
-        <v>31500</v>
+        <v>0</v>
       </c>
       <c r="O748" t="n">
-        <v>31500</v>
+        <v>0</v>
       </c>
       <c r="P748" t="n">
         <v>39900</v>
       </c>
       <c r="Q748" t="n">
-        <v>39900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="749">
@@ -34663,22 +34663,22 @@
         <v>0</v>
       </c>
       <c r="L755" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M755" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N755" t="n">
         <v>58500</v>
       </c>
       <c r="O755" t="n">
-        <v>175500</v>
+        <v>58500</v>
       </c>
       <c r="P755" t="n">
         <v>73900</v>
       </c>
       <c r="Q755" t="n">
-        <v>221700</v>
+        <v>73900</v>
       </c>
     </row>
     <row r="756">
@@ -35169,22 +35169,22 @@
         <v>0</v>
       </c>
       <c r="L766" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M766" t="n">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="N766" t="n">
         <v>7216</v>
       </c>
       <c r="O766" t="n">
-        <v>2381280</v>
+        <v>2359632</v>
       </c>
       <c r="P766" t="n">
         <v>9000</v>
       </c>
       <c r="Q766" t="n">
-        <v>2970000</v>
+        <v>2943000</v>
       </c>
     </row>
     <row r="767">
@@ -36330,10 +36330,10 @@
         <v>24</v>
       </c>
       <c r="N791" t="n">
-        <v>970.63171428571</v>
+        <v>970.631875</v>
       </c>
       <c r="O791" t="n">
-        <v>23295.16114285704</v>
+        <v>23295.165</v>
       </c>
       <c r="P791" t="n">
         <v>7200</v>
@@ -36610,22 +36610,22 @@
         <v>0</v>
       </c>
       <c r="L797" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M797" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="N797" t="n">
         <v>751.45</v>
       </c>
       <c r="O797" t="n">
-        <v>45087</v>
+        <v>41329.75</v>
       </c>
       <c r="P797" t="n">
         <v>2500</v>
       </c>
       <c r="Q797" t="n">
-        <v>150000</v>
+        <v>137500</v>
       </c>
     </row>
     <row r="798">
@@ -37305,22 +37305,22 @@
         <v>0</v>
       </c>
       <c r="L812" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M812" t="n">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="N812" t="n">
         <v>4550</v>
       </c>
       <c r="O812" t="n">
-        <v>1355900</v>
+        <v>1346800</v>
       </c>
       <c r="P812" t="n">
         <v>5500</v>
       </c>
       <c r="Q812" t="n">
-        <v>1639000</v>
+        <v>1628000</v>
       </c>
     </row>
     <row r="813">

--- a/bodegas/LJ-05.xlsx
+++ b/bodegas/LJ-05.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q811"/>
+  <dimension ref="A1:Q834"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35006,12 +35006,12 @@
     <row r="763">
       <c r="A763" t="inlineStr">
         <is>
-          <t>J-556</t>
+          <t>J-1307</t>
         </is>
       </c>
       <c r="C763" t="inlineStr">
         <is>
-          <t>VUVUCELA 25CM J-556</t>
+          <t>CAMION CONTENEDOR J-1307</t>
         </is>
       </c>
       <c r="E763" t="inlineStr">
@@ -35025,39 +35025,39 @@
         </is>
       </c>
       <c r="J763" t="n">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="K763" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="L763" t="n">
         <v>0</v>
       </c>
       <c r="M763" t="n">
-        <v>240</v>
+        <v>108</v>
       </c>
       <c r="N763" t="n">
-        <v>1260</v>
+        <v>15224</v>
       </c>
       <c r="O763" t="n">
-        <v>302400</v>
+        <v>1644192</v>
       </c>
       <c r="P763" t="n">
-        <v>1700</v>
+        <v>19000</v>
       </c>
       <c r="Q763" t="n">
-        <v>408000</v>
+        <v>2052000</v>
       </c>
     </row>
     <row r="764">
       <c r="A764" t="inlineStr">
         <is>
-          <t>J-704</t>
+          <t>J-1308</t>
         </is>
       </c>
       <c r="C764" t="inlineStr">
         <is>
-          <t>MONO SONIDO J-704-705-706-707-708-710</t>
+          <t>CAMION CONTENEDR J-1308</t>
         </is>
       </c>
       <c r="E764" t="inlineStr">
@@ -35071,39 +35071,39 @@
         </is>
       </c>
       <c r="J764" t="n">
-        <v>327</v>
+        <v>0</v>
       </c>
       <c r="K764" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="L764" t="n">
         <v>0</v>
       </c>
       <c r="M764" t="n">
-        <v>327</v>
+        <v>108</v>
       </c>
       <c r="N764" t="n">
-        <v>7216</v>
+        <v>15224</v>
       </c>
       <c r="O764" t="n">
-        <v>2359632</v>
+        <v>1644192</v>
       </c>
       <c r="P764" t="n">
-        <v>9000</v>
+        <v>19000</v>
       </c>
       <c r="Q764" t="n">
-        <v>2943000</v>
+        <v>2052000</v>
       </c>
     </row>
     <row r="765">
       <c r="A765" t="inlineStr">
         <is>
-          <t>JBL0536</t>
+          <t>J-1313</t>
         </is>
       </c>
       <c r="C765" t="inlineStr">
         <is>
-          <t>SET DE REGLAS X7PCS JBL0536</t>
+          <t>CONEJO CAMINA ZANAHORIA LUZ J-1313</t>
         </is>
       </c>
       <c r="E765" t="inlineStr">
@@ -35117,39 +35117,39 @@
         </is>
       </c>
       <c r="J765" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K765" t="n">
-        <v>0</v>
+        <v>432</v>
       </c>
       <c r="L765" t="n">
         <v>0</v>
       </c>
       <c r="M765" t="n">
-        <v>14</v>
+        <v>432</v>
       </c>
       <c r="N765" t="n">
-        <v>5900</v>
+        <v>7480</v>
       </c>
       <c r="O765" t="n">
-        <v>82600</v>
+        <v>3231360</v>
       </c>
       <c r="P765" t="n">
-        <v>7100</v>
+        <v>9500</v>
       </c>
       <c r="Q765" t="n">
-        <v>99400</v>
+        <v>4104000</v>
       </c>
     </row>
     <row r="766">
       <c r="A766" t="inlineStr">
         <is>
-          <t>JBL0539</t>
+          <t>J-1314</t>
         </is>
       </c>
       <c r="C766" t="inlineStr">
         <is>
-          <t>MARCADORES CAJA PLASTICA X24 JBL0539</t>
+          <t>PERRO CON GAFAS CAMINA J-1314</t>
         </is>
       </c>
       <c r="E766" t="inlineStr">
@@ -35163,39 +35163,39 @@
         </is>
       </c>
       <c r="J766" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K766" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="L766" t="n">
         <v>0</v>
       </c>
       <c r="M766" t="n">
-        <v>1</v>
+        <v>144</v>
       </c>
       <c r="N766" t="n">
-        <v>17500</v>
+        <v>6336</v>
       </c>
       <c r="O766" t="n">
-        <v>17500</v>
+        <v>912384</v>
       </c>
       <c r="P766" t="n">
-        <v>21000</v>
+        <v>7500</v>
       </c>
       <c r="Q766" t="n">
-        <v>21000</v>
+        <v>1080000</v>
       </c>
     </row>
     <row r="767">
       <c r="A767" t="inlineStr">
         <is>
-          <t>JBL0540</t>
+          <t>J-1316</t>
         </is>
       </c>
       <c r="C767" t="inlineStr">
         <is>
-          <t>MARCADORES CAJA PLASTICA X36 JBL0540</t>
+          <t>SET DE GAFAS CELULAR Y BILLETERA J-1316</t>
         </is>
       </c>
       <c r="E767" t="inlineStr">
@@ -35209,39 +35209,39 @@
         </is>
       </c>
       <c r="J767" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K767" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="L767" t="n">
         <v>0</v>
       </c>
       <c r="M767" t="n">
-        <v>11</v>
+        <v>168</v>
       </c>
       <c r="N767" t="n">
-        <v>25000</v>
+        <v>5280</v>
       </c>
       <c r="O767" t="n">
-        <v>275000</v>
+        <v>887040</v>
       </c>
       <c r="P767" t="n">
-        <v>30000</v>
+        <v>6900</v>
       </c>
       <c r="Q767" t="n">
-        <v>330000</v>
+        <v>1159200</v>
       </c>
     </row>
     <row r="768">
       <c r="A768" t="inlineStr">
         <is>
-          <t>JBL0554</t>
+          <t>J-1319</t>
         </is>
       </c>
       <c r="C768" t="inlineStr">
         <is>
-          <t>CAJA DE COLORES X 12 PCS JBL0554</t>
+          <t>CARRO PQÑ TODO TERRENO</t>
         </is>
       </c>
       <c r="E768" t="inlineStr">
@@ -35255,39 +35255,39 @@
         </is>
       </c>
       <c r="J768" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K768" t="n">
-        <v>0</v>
+        <v>720</v>
       </c>
       <c r="L768" t="n">
         <v>0</v>
       </c>
       <c r="M768" t="n">
-        <v>18</v>
+        <v>720</v>
       </c>
       <c r="N768" t="n">
-        <v>9500</v>
+        <v>2376</v>
       </c>
       <c r="O768" t="n">
-        <v>171000</v>
+        <v>1710720</v>
       </c>
       <c r="P768" t="n">
-        <v>11400</v>
+        <v>3000</v>
       </c>
       <c r="Q768" t="n">
-        <v>205200</v>
+        <v>2160000</v>
       </c>
     </row>
     <row r="769">
       <c r="A769" t="inlineStr">
         <is>
-          <t>JBL0557</t>
+          <t>J-1320</t>
         </is>
       </c>
       <c r="C769" t="inlineStr">
         <is>
-          <t>CAJA COLORES MINI X 12 PCS  JBL0557</t>
+          <t>CARRO TODO TERRENO J-1320</t>
         </is>
       </c>
       <c r="E769" t="inlineStr">
@@ -35301,39 +35301,39 @@
         </is>
       </c>
       <c r="J769" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K769" t="n">
-        <v>0</v>
+        <v>288</v>
       </c>
       <c r="L769" t="n">
         <v>0</v>
       </c>
       <c r="M769" t="n">
-        <v>19</v>
+        <v>288</v>
       </c>
       <c r="N769" t="n">
-        <v>2900</v>
+        <v>1584</v>
       </c>
       <c r="O769" t="n">
-        <v>55100</v>
+        <v>456192</v>
       </c>
       <c r="P769" t="n">
-        <v>3500</v>
+        <v>2000</v>
       </c>
       <c r="Q769" t="n">
-        <v>66500</v>
+        <v>576000</v>
       </c>
     </row>
     <row r="770">
       <c r="A770" t="inlineStr">
         <is>
-          <t>JBL0657</t>
+          <t>J-1321</t>
         </is>
       </c>
       <c r="C770" t="inlineStr">
         <is>
-          <t>TAJALAPIZ CON DEPOSITO JBL0657</t>
+          <t>CARRO TODO TERRENO J-1321</t>
         </is>
       </c>
       <c r="E770" t="inlineStr">
@@ -35347,39 +35347,39 @@
         </is>
       </c>
       <c r="J770" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K770" t="n">
-        <v>0</v>
+        <v>720</v>
       </c>
       <c r="L770" t="n">
         <v>0</v>
       </c>
       <c r="M770" t="n">
-        <v>14</v>
+        <v>720</v>
       </c>
       <c r="N770" t="n">
-        <v>1000</v>
+        <v>1584</v>
       </c>
       <c r="O770" t="n">
-        <v>14000</v>
+        <v>1140480</v>
       </c>
       <c r="P770" t="n">
-        <v>1200</v>
+        <v>2000</v>
       </c>
       <c r="Q770" t="n">
-        <v>16800</v>
+        <v>1440000</v>
       </c>
     </row>
     <row r="771">
       <c r="A771" t="inlineStr">
         <is>
-          <t>JBL0707</t>
+          <t>J-1322</t>
         </is>
       </c>
       <c r="C771" t="inlineStr">
         <is>
-          <t>SET GEOMETRICO FLEXIBLE X 4 PCS JBL0707</t>
+          <t>CARRO TODO TERRENO J-1322</t>
         </is>
       </c>
       <c r="E771" t="inlineStr">
@@ -35393,39 +35393,39 @@
         </is>
       </c>
       <c r="J771" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K771" t="n">
-        <v>0</v>
+        <v>288</v>
       </c>
       <c r="L771" t="n">
         <v>0</v>
       </c>
       <c r="M771" t="n">
-        <v>20</v>
+        <v>288</v>
       </c>
       <c r="N771" t="n">
-        <v>3600</v>
+        <v>3872</v>
       </c>
       <c r="O771" t="n">
-        <v>72000</v>
+        <v>1115136</v>
       </c>
       <c r="P771" t="n">
-        <v>4400</v>
+        <v>4900</v>
       </c>
       <c r="Q771" t="n">
-        <v>88000</v>
+        <v>1411200</v>
       </c>
     </row>
     <row r="772">
       <c r="A772" t="inlineStr">
         <is>
-          <t>JBL0729</t>
+          <t>J-1323</t>
         </is>
       </c>
       <c r="C772" t="inlineStr">
         <is>
-          <t>LONCHERA INFANTIL MODELOS STD 22,5cm JBL0729</t>
+          <t>CARRO FRICCION TODO TERRENO OJITOS J-1323</t>
         </is>
       </c>
       <c r="E772" t="inlineStr">
@@ -35439,39 +35439,39 @@
         </is>
       </c>
       <c r="J772" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K772" t="n">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="L772" t="n">
         <v>0</v>
       </c>
       <c r="M772" t="n">
-        <v>17</v>
+        <v>192</v>
       </c>
       <c r="N772" t="n">
-        <v>9300</v>
+        <v>3872</v>
       </c>
       <c r="O772" t="n">
-        <v>158100</v>
+        <v>743424</v>
       </c>
       <c r="P772" t="n">
-        <v>11200</v>
+        <v>4900</v>
       </c>
       <c r="Q772" t="n">
-        <v>190400</v>
+        <v>940800</v>
       </c>
     </row>
     <row r="773">
       <c r="A773" t="inlineStr">
         <is>
-          <t>JO-129</t>
+          <t>J-1324</t>
         </is>
       </c>
       <c r="C773" t="inlineStr">
         <is>
-          <t>LAPICES COLORES X12 DOBLE PUNTA JO-129</t>
+          <t>CARRO TODO TERRENO J-1324</t>
         </is>
       </c>
       <c r="E773" t="inlineStr">
@@ -35485,39 +35485,39 @@
         </is>
       </c>
       <c r="J773" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K773" t="n">
-        <v>0</v>
+        <v>288</v>
       </c>
       <c r="L773" t="n">
         <v>0</v>
       </c>
       <c r="M773" t="n">
-        <v>16</v>
+        <v>288</v>
       </c>
       <c r="N773" t="n">
-        <v>4500</v>
+        <v>3872</v>
       </c>
       <c r="O773" t="n">
-        <v>72000</v>
+        <v>1115136</v>
       </c>
       <c r="P773" t="n">
-        <v>5400</v>
+        <v>4900</v>
       </c>
       <c r="Q773" t="n">
-        <v>86400</v>
+        <v>1411200</v>
       </c>
     </row>
     <row r="774">
       <c r="A774" t="inlineStr">
         <is>
-          <t>JO-139</t>
+          <t>J-1325</t>
         </is>
       </c>
       <c r="C774" t="inlineStr">
         <is>
-          <t>ESFERO GIRATORIO 10 MINAS MUÑECA JO-139</t>
+          <t>CARRO FRICCION TODO TERRENO J-1325</t>
         </is>
       </c>
       <c r="E774" t="inlineStr">
@@ -35531,39 +35531,39 @@
         </is>
       </c>
       <c r="J774" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="K774" t="n">
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="L774" t="n">
         <v>0</v>
       </c>
       <c r="M774" t="n">
-        <v>51</v>
+        <v>216</v>
       </c>
       <c r="N774" t="n">
-        <v>2700</v>
+        <v>6160</v>
       </c>
       <c r="O774" t="n">
-        <v>137700</v>
+        <v>1330560</v>
       </c>
       <c r="P774" t="n">
-        <v>3300</v>
+        <v>7900</v>
       </c>
       <c r="Q774" t="n">
-        <v>168300</v>
+        <v>1706400</v>
       </c>
     </row>
     <row r="775">
       <c r="A775" t="inlineStr">
         <is>
-          <t>JO-142</t>
+          <t>J-1326</t>
         </is>
       </c>
       <c r="C775" t="inlineStr">
         <is>
-          <t>ESFERO BORRABLE CON BORRADOR ASTRONAUTA JO-142</t>
+          <t>CARRO TODO TERRENO J-1326</t>
         </is>
       </c>
       <c r="E775" t="inlineStr">
@@ -35577,39 +35577,39 @@
         </is>
       </c>
       <c r="J775" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K775" t="n">
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="L775" t="n">
         <v>0</v>
       </c>
       <c r="M775" t="n">
-        <v>36</v>
+        <v>216</v>
       </c>
       <c r="N775" t="n">
-        <v>1900</v>
+        <v>6160</v>
       </c>
       <c r="O775" t="n">
-        <v>68400</v>
+        <v>1330560</v>
       </c>
       <c r="P775" t="n">
-        <v>2300</v>
+        <v>7900</v>
       </c>
       <c r="Q775" t="n">
-        <v>82800</v>
+        <v>1706400</v>
       </c>
     </row>
     <row r="776">
       <c r="A776" t="inlineStr">
         <is>
-          <t>JO-143</t>
+          <t>J-1327</t>
         </is>
       </c>
       <c r="C776" t="inlineStr">
         <is>
-          <t>ESFERO BORRABKLE CON BORRADOR ARCOIRIS JO-143</t>
+          <t>CARRO TODO TERRENO J-1327</t>
         </is>
       </c>
       <c r="E776" t="inlineStr">
@@ -35623,39 +35623,39 @@
         </is>
       </c>
       <c r="J776" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="K776" t="n">
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="L776" t="n">
         <v>0</v>
       </c>
       <c r="M776" t="n">
-        <v>44</v>
+        <v>216</v>
       </c>
       <c r="N776" t="n">
-        <v>1400</v>
+        <v>6160</v>
       </c>
       <c r="O776" t="n">
-        <v>61600</v>
+        <v>1330560</v>
       </c>
       <c r="P776" t="n">
-        <v>1700</v>
+        <v>7900</v>
       </c>
       <c r="Q776" t="n">
-        <v>74800</v>
+        <v>1706400</v>
       </c>
     </row>
     <row r="777">
       <c r="A777" t="inlineStr">
         <is>
-          <t>JO-144</t>
+          <t>J-1328</t>
         </is>
       </c>
       <c r="C777" t="inlineStr">
         <is>
-          <t>ESFERO BORRABLE CON BORRADOR PANDA JO-144</t>
+          <t>CUATRIMOTO LUZ IMPULSO J-1328</t>
         </is>
       </c>
       <c r="E777" t="inlineStr">
@@ -35669,39 +35669,39 @@
         </is>
       </c>
       <c r="J777" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="K777" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L777" t="n">
         <v>0</v>
       </c>
       <c r="M777" t="n">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="N777" t="n">
-        <v>1900</v>
+        <v>6160</v>
       </c>
       <c r="O777" t="n">
-        <v>136800</v>
+        <v>591360</v>
       </c>
       <c r="P777" t="n">
-        <v>2300</v>
+        <v>7900</v>
       </c>
       <c r="Q777" t="n">
-        <v>165600</v>
+        <v>758400</v>
       </c>
     </row>
     <row r="778">
       <c r="A778" t="inlineStr">
         <is>
-          <t>JO-145</t>
+          <t>J-1329</t>
         </is>
       </c>
       <c r="C778" t="inlineStr">
         <is>
-          <t>ESFERO BORRABLE CON BORRADOR OSITO JO-145</t>
+          <t>CARRO TODO TERRENO J-1329</t>
         </is>
       </c>
       <c r="E778" t="inlineStr">
@@ -35715,39 +35715,39 @@
         </is>
       </c>
       <c r="J778" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="K778" t="n">
-        <v>0</v>
+        <v>384</v>
       </c>
       <c r="L778" t="n">
         <v>0</v>
       </c>
       <c r="M778" t="n">
-        <v>63</v>
+        <v>384</v>
       </c>
       <c r="N778" t="n">
-        <v>1900</v>
+        <v>3344</v>
       </c>
       <c r="O778" t="n">
-        <v>119700</v>
+        <v>1284096</v>
       </c>
       <c r="P778" t="n">
-        <v>2300</v>
+        <v>4500</v>
       </c>
       <c r="Q778" t="n">
-        <v>144900</v>
+        <v>1728000</v>
       </c>
     </row>
     <row r="779">
       <c r="A779" t="inlineStr">
         <is>
-          <t>JOE-1813</t>
+          <t>J-1330</t>
         </is>
       </c>
       <c r="C779" t="inlineStr">
         <is>
-          <t>SET MARCADORES ACUARELA LAVAVBLE TUBO X 18 PCS JOE-1813</t>
+          <t>CARRO TODO TERRENO J-1330</t>
         </is>
       </c>
       <c r="E779" t="inlineStr">
@@ -35761,39 +35761,39 @@
         </is>
       </c>
       <c r="J779" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K779" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="L779" t="n">
         <v>0</v>
       </c>
       <c r="M779" t="n">
-        <v>10</v>
+        <v>360</v>
       </c>
       <c r="N779" t="n">
-        <v>6000</v>
+        <v>3344</v>
       </c>
       <c r="O779" t="n">
-        <v>60000</v>
+        <v>1203840</v>
       </c>
       <c r="P779" t="n">
-        <v>7200</v>
+        <v>4500</v>
       </c>
       <c r="Q779" t="n">
-        <v>72000</v>
+        <v>1620000</v>
       </c>
     </row>
     <row r="780">
       <c r="A780" t="inlineStr">
         <is>
-          <t>JOE-9812</t>
+          <t>J-1331</t>
         </is>
       </c>
       <c r="C780" t="inlineStr">
         <is>
-          <t>SET MARCADORES JUMBO ACUARELA X12/14cm</t>
+          <t>CARRO TODO TERRENO DOBLE IMAGEN J-1331</t>
         </is>
       </c>
       <c r="E780" t="inlineStr">
@@ -35807,39 +35807,39 @@
         </is>
       </c>
       <c r="J780" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K780" t="n">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="L780" t="n">
         <v>0</v>
       </c>
       <c r="M780" t="n">
-        <v>6</v>
+        <v>192</v>
       </c>
       <c r="N780" t="n">
-        <v>5000</v>
+        <v>4400</v>
       </c>
       <c r="O780" t="n">
-        <v>30000</v>
+        <v>844800</v>
       </c>
       <c r="P780" t="n">
-        <v>6000</v>
+        <v>5900</v>
       </c>
       <c r="Q780" t="n">
-        <v>36000</v>
+        <v>1132800</v>
       </c>
     </row>
     <row r="781">
       <c r="A781" t="inlineStr">
         <is>
-          <t>JT-13</t>
+          <t>J-455</t>
         </is>
       </c>
       <c r="C781" t="inlineStr">
         <is>
-          <t>CORRECTOR EN CINTA JT-13</t>
+          <t>TABLETA MAGICA J-455</t>
         </is>
       </c>
       <c r="E781" t="inlineStr">
@@ -35853,39 +35853,39 @@
         </is>
       </c>
       <c r="J781" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K781" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="L781" t="n">
         <v>0</v>
       </c>
       <c r="M781" t="n">
-        <v>7</v>
+        <v>200</v>
       </c>
       <c r="N781" t="n">
-        <v>2400</v>
+        <v>3520</v>
       </c>
       <c r="O781" t="n">
-        <v>16800</v>
+        <v>704000</v>
       </c>
       <c r="P781" t="n">
-        <v>2900</v>
+        <v>4500</v>
       </c>
       <c r="Q781" t="n">
-        <v>20300</v>
+        <v>900000</v>
       </c>
     </row>
     <row r="782">
       <c r="A782" t="inlineStr">
         <is>
-          <t>K061A</t>
+          <t>J-556</t>
         </is>
       </c>
       <c r="C782" t="inlineStr">
         <is>
-          <t>ESFERO RETRACTIL CAPIBARA TINTA NEGRA K061A</t>
+          <t>VUVUCELA 25CM J-556</t>
         </is>
       </c>
       <c r="E782" t="inlineStr">
@@ -35899,7 +35899,7 @@
         </is>
       </c>
       <c r="J782" t="n">
-        <v>60</v>
+        <v>240</v>
       </c>
       <c r="K782" t="n">
         <v>0</v>
@@ -35908,30 +35908,30 @@
         <v>0</v>
       </c>
       <c r="M782" t="n">
-        <v>60</v>
+        <v>240</v>
       </c>
       <c r="N782" t="n">
-        <v>1800</v>
+        <v>1260</v>
       </c>
       <c r="O782" t="n">
-        <v>108000</v>
+        <v>302400</v>
       </c>
       <c r="P782" t="n">
-        <v>2200</v>
+        <v>1700</v>
       </c>
       <c r="Q782" t="n">
-        <v>132000</v>
+        <v>408000</v>
       </c>
     </row>
     <row r="783">
       <c r="A783" t="inlineStr">
         <is>
-          <t>LY6807</t>
+          <t>J-582</t>
         </is>
       </c>
       <c r="C783" t="inlineStr">
         <is>
-          <t>JUGUETE PATINETA DE CUATRO RUEDAS LY6807</t>
+          <t>BURBUJERO ALAS J-582</t>
         </is>
       </c>
       <c r="E783" t="inlineStr">
@@ -35945,39 +35945,39 @@
         </is>
       </c>
       <c r="J783" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K783" t="n">
-        <v>0</v>
+        <v>840</v>
       </c>
       <c r="L783" t="n">
         <v>0</v>
       </c>
       <c r="M783" t="n">
-        <v>40</v>
+        <v>840</v>
       </c>
       <c r="N783" t="n">
-        <v>415.07</v>
+        <v>9240</v>
       </c>
       <c r="O783" t="n">
-        <v>16602.8</v>
+        <v>7761600</v>
       </c>
       <c r="P783" t="n">
-        <v>2900</v>
+        <v>11500</v>
       </c>
       <c r="Q783" t="n">
-        <v>116000</v>
+        <v>9660000</v>
       </c>
     </row>
     <row r="784">
       <c r="A784" t="inlineStr">
         <is>
-          <t>MC121011-E</t>
+          <t>J-687</t>
         </is>
       </c>
       <c r="C784" t="inlineStr">
         <is>
-          <t>SET LAPIZ CON BORRADOR OSITOS MC121011-E</t>
+          <t>BOLITRON OJO 3 COLORES J-687</t>
         </is>
       </c>
       <c r="E784" t="inlineStr">
@@ -35991,39 +35991,39 @@
         </is>
       </c>
       <c r="J784" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K784" t="n">
-        <v>0</v>
+        <v>384</v>
       </c>
       <c r="L784" t="n">
         <v>0</v>
       </c>
       <c r="M784" t="n">
-        <v>6</v>
+        <v>384</v>
       </c>
       <c r="N784" t="n">
-        <v>6500</v>
+        <v>2288</v>
       </c>
       <c r="O784" t="n">
-        <v>39000</v>
+        <v>878592</v>
       </c>
       <c r="P784" t="n">
-        <v>7800</v>
+        <v>2900</v>
       </c>
       <c r="Q784" t="n">
-        <v>46800</v>
+        <v>1113600</v>
       </c>
     </row>
     <row r="785">
       <c r="A785" t="inlineStr">
         <is>
-          <t>MC121212</t>
+          <t>J-704</t>
         </is>
       </c>
       <c r="C785" t="inlineStr">
         <is>
-          <t>SET LAPIZ CON BORRADOR Y TAJALAPIZ ROBOT MC121212</t>
+          <t>MONO SONIDO J-704-705-706-707-708-710</t>
         </is>
       </c>
       <c r="E785" t="inlineStr">
@@ -36037,7 +36037,7 @@
         </is>
       </c>
       <c r="J785" t="n">
-        <v>6</v>
+        <v>327</v>
       </c>
       <c r="K785" t="n">
         <v>0</v>
@@ -36046,40 +36046,35 @@
         <v>0</v>
       </c>
       <c r="M785" t="n">
-        <v>6</v>
+        <v>327</v>
       </c>
       <c r="N785" t="n">
-        <v>6500</v>
+        <v>7216</v>
       </c>
       <c r="O785" t="n">
-        <v>39000</v>
+        <v>2359632</v>
       </c>
       <c r="P785" t="n">
-        <v>7800</v>
+        <v>9000</v>
       </c>
       <c r="Q785" t="n">
-        <v>46800</v>
+        <v>2943000</v>
       </c>
     </row>
     <row r="786">
       <c r="A786" t="inlineStr">
         <is>
-          <t>MG16332</t>
-        </is>
-      </c>
-      <c r="B786" t="inlineStr">
-        <is>
-          <t>MG16332</t>
+          <t>J-718</t>
         </is>
       </c>
       <c r="C786" t="inlineStr">
         <is>
-          <t>LANZADOR  ARCO Y FLECA CON LASER MG16332</t>
+          <t>MOTO DE IMPULSO BLISTER J-718</t>
         </is>
       </c>
       <c r="E786" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I786" t="inlineStr">
@@ -36088,44 +36083,44 @@
         </is>
       </c>
       <c r="J786" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K786" t="n">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="L786" t="n">
         <v>0</v>
       </c>
       <c r="M786" t="n">
-        <v>10</v>
+        <v>192</v>
       </c>
       <c r="N786" t="n">
-        <v>8439.969999999999</v>
+        <v>4576</v>
       </c>
       <c r="O786" t="n">
-        <v>84399.7</v>
+        <v>878592</v>
       </c>
       <c r="P786" t="n">
-        <v>29500</v>
+        <v>5900</v>
       </c>
       <c r="Q786" t="n">
-        <v>295000</v>
+        <v>1132800</v>
       </c>
     </row>
     <row r="787">
       <c r="A787" t="inlineStr">
         <is>
-          <t>MG20129</t>
+          <t>J-719</t>
         </is>
       </c>
       <c r="C787" t="inlineStr">
         <is>
-          <t>SET MOLDE PARA HELADOS Y FRUTAS EN PLASTILINA MG20129</t>
+          <t>MOTO ENCARTONADA J-719</t>
         </is>
       </c>
       <c r="E787" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I787" t="inlineStr">
@@ -36134,44 +36129,44 @@
         </is>
       </c>
       <c r="J787" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K787" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="L787" t="n">
         <v>0</v>
       </c>
       <c r="M787" t="n">
-        <v>10</v>
+        <v>300</v>
       </c>
       <c r="N787" t="n">
-        <v>7860.59</v>
+        <v>5280</v>
       </c>
       <c r="O787" t="n">
-        <v>78605.89999999999</v>
+        <v>1584000</v>
       </c>
       <c r="P787" t="n">
-        <v>21500</v>
+        <v>6900</v>
       </c>
       <c r="Q787" t="n">
-        <v>215000</v>
+        <v>2070000</v>
       </c>
     </row>
     <row r="788">
       <c r="A788" t="inlineStr">
         <is>
-          <t>MG20430</t>
+          <t>JBL0536</t>
         </is>
       </c>
       <c r="C788" t="inlineStr">
         <is>
-          <t>SET PLASTILINA CON MOLDES BARBERIA MALETA MG20430</t>
+          <t>SET DE REGLAS X7PCS JBL0536</t>
         </is>
       </c>
       <c r="E788" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I788" t="inlineStr">
@@ -36180,7 +36175,7 @@
         </is>
       </c>
       <c r="J788" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="K788" t="n">
         <v>0</v>
@@ -36189,35 +36184,35 @@
         <v>0</v>
       </c>
       <c r="M788" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="N788" t="n">
-        <v>12189.832</v>
+        <v>5900</v>
       </c>
       <c r="O788" t="n">
-        <v>24379.664</v>
+        <v>82600</v>
       </c>
       <c r="P788" t="n">
-        <v>30900</v>
+        <v>7100</v>
       </c>
       <c r="Q788" t="n">
-        <v>61800</v>
+        <v>99400</v>
       </c>
     </row>
     <row r="789">
       <c r="A789" t="inlineStr">
         <is>
-          <t>MG20669</t>
+          <t>JBL0539</t>
         </is>
       </c>
       <c r="C789" t="inlineStr">
         <is>
-          <t>SET DE PLASTILINA PARA MOLDEAR EN BLISTER MG20669</t>
+          <t>MARCADORES CAJA PLASTICA X24 JBL0539</t>
         </is>
       </c>
       <c r="E789" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I789" t="inlineStr">
@@ -36226,7 +36221,7 @@
         </is>
       </c>
       <c r="J789" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="K789" t="n">
         <v>0</v>
@@ -36235,35 +36230,35 @@
         <v>0</v>
       </c>
       <c r="M789" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="N789" t="n">
-        <v>970.631875</v>
+        <v>17500</v>
       </c>
       <c r="O789" t="n">
-        <v>23295.165</v>
+        <v>17500</v>
       </c>
       <c r="P789" t="n">
-        <v>7200</v>
+        <v>21000</v>
       </c>
       <c r="Q789" t="n">
-        <v>172800</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="790">
       <c r="A790" t="inlineStr">
         <is>
-          <t>MG20906</t>
+          <t>JBL0540</t>
         </is>
       </c>
       <c r="C790" t="inlineStr">
         <is>
-          <t>DINOSAURIO DIDACTICO EN BOLSA MG20906</t>
+          <t>MARCADORES CAJA PLASTICA X36 JBL0540</t>
         </is>
       </c>
       <c r="E790" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I790" t="inlineStr">
@@ -36272,7 +36267,7 @@
         </is>
       </c>
       <c r="J790" t="n">
-        <v>63</v>
+        <v>11</v>
       </c>
       <c r="K790" t="n">
         <v>0</v>
@@ -36281,35 +36276,35 @@
         <v>0</v>
       </c>
       <c r="M790" t="n">
-        <v>63</v>
+        <v>11</v>
       </c>
       <c r="N790" t="n">
-        <v>1482.84</v>
+        <v>25000</v>
       </c>
       <c r="O790" t="n">
-        <v>93418.92</v>
+        <v>275000</v>
       </c>
       <c r="P790" t="n">
-        <v>6500</v>
+        <v>30000</v>
       </c>
       <c r="Q790" t="n">
-        <v>409500</v>
+        <v>330000</v>
       </c>
     </row>
     <row r="791">
       <c r="A791" t="inlineStr">
         <is>
-          <t>MG22320</t>
+          <t>JBL0554</t>
         </is>
       </c>
       <c r="C791" t="inlineStr">
         <is>
-          <t>CABALLO DIDACTICO DESARMABLE PQÑ MG22320</t>
+          <t>CAJA DE COLORES X 12 PCS JBL0554</t>
         </is>
       </c>
       <c r="E791" t="inlineStr">
         <is>
-          <t>DIDACTICOS</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I791" t="inlineStr">
@@ -36318,7 +36313,7 @@
         </is>
       </c>
       <c r="J791" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K791" t="n">
         <v>0</v>
@@ -36327,40 +36322,35 @@
         <v>0</v>
       </c>
       <c r="M791" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="N791" t="n">
-        <v>1129.14</v>
+        <v>9500</v>
       </c>
       <c r="O791" t="n">
-        <v>14678.82</v>
+        <v>171000</v>
       </c>
       <c r="P791" t="n">
-        <v>6900</v>
+        <v>11400</v>
       </c>
       <c r="Q791" t="n">
-        <v>89700</v>
+        <v>205200</v>
       </c>
     </row>
     <row r="792">
       <c r="A792" t="inlineStr">
         <is>
-          <t>MG22435</t>
-        </is>
-      </c>
-      <c r="B792" t="inlineStr">
-        <is>
-          <t>MG22435</t>
+          <t>JBL0557</t>
         </is>
       </c>
       <c r="C792" t="inlineStr">
         <is>
-          <t>SONAJERO PERRITO BOLSA PQÑ MG22435</t>
+          <t>CAJA COLORES MINI X 12 PCS  JBL0557</t>
         </is>
       </c>
       <c r="E792" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I792" t="inlineStr">
@@ -36369,7 +36359,7 @@
         </is>
       </c>
       <c r="J792" t="n">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="K792" t="n">
         <v>0</v>
@@ -36378,35 +36368,35 @@
         <v>0</v>
       </c>
       <c r="M792" t="n">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="N792" t="n">
-        <v>1236.3</v>
+        <v>2900</v>
       </c>
       <c r="O792" t="n">
-        <v>63051.3</v>
+        <v>55100</v>
       </c>
       <c r="P792" t="n">
-        <v>2300</v>
+        <v>3500</v>
       </c>
       <c r="Q792" t="n">
-        <v>117300</v>
+        <v>66500</v>
       </c>
     </row>
     <row r="793">
       <c r="A793" t="inlineStr">
         <is>
-          <t>MG26010</t>
+          <t>JBL0657</t>
         </is>
       </c>
       <c r="C793" t="inlineStr">
         <is>
-          <t>SET BELLEZA CON ACCESORIOS EMPAQUE BOLSO MG26010</t>
+          <t>TAJALAPIZ CON DEPOSITO JBL0657</t>
         </is>
       </c>
       <c r="E793" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I793" t="inlineStr">
@@ -36415,7 +36405,7 @@
         </is>
       </c>
       <c r="J793" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K793" t="n">
         <v>0</v>
@@ -36424,35 +36414,35 @@
         <v>0</v>
       </c>
       <c r="M793" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="N793" t="n">
-        <v>11433.53</v>
+        <v>1000</v>
       </c>
       <c r="O793" t="n">
-        <v>125768.83</v>
+        <v>14000</v>
       </c>
       <c r="P793" t="n">
-        <v>15000</v>
+        <v>1200</v>
       </c>
       <c r="Q793" t="n">
-        <v>165000</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="794">
       <c r="A794" t="inlineStr">
         <is>
-          <t>MG27230</t>
+          <t>JBL0707</t>
         </is>
       </c>
       <c r="C794" t="inlineStr">
         <is>
-          <t>SET PLASTILINA ODONTOLOGICO CAJA MG27230</t>
+          <t>SET GEOMETRICO FLEXIBLE X 4 PCS JBL0707</t>
         </is>
       </c>
       <c r="E794" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I794" t="inlineStr">
@@ -36461,7 +36451,7 @@
         </is>
       </c>
       <c r="J794" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="K794" t="n">
         <v>0</v>
@@ -36470,40 +36460,35 @@
         <v>0</v>
       </c>
       <c r="M794" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="N794" t="n">
-        <v>12115.88</v>
+        <v>3600</v>
       </c>
       <c r="O794" t="n">
-        <v>109042.92</v>
+        <v>72000</v>
       </c>
       <c r="P794" t="n">
-        <v>31500</v>
+        <v>4400</v>
       </c>
       <c r="Q794" t="n">
-        <v>283500</v>
+        <v>88000</v>
       </c>
     </row>
     <row r="795">
       <c r="A795" t="inlineStr">
         <is>
-          <t>MG33219</t>
-        </is>
-      </c>
-      <c r="B795" t="inlineStr">
-        <is>
-          <t>MG33219</t>
+          <t>JBL0729</t>
         </is>
       </c>
       <c r="C795" t="inlineStr">
         <is>
-          <t>BINOCULARES CAMUFLADOS MG33219</t>
+          <t>LONCHERA INFANTIL MODELOS STD 22,5cm JBL0729</t>
         </is>
       </c>
       <c r="E795" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I795" t="inlineStr">
@@ -36512,7 +36497,7 @@
         </is>
       </c>
       <c r="J795" t="n">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="K795" t="n">
         <v>0</v>
@@ -36521,35 +36506,35 @@
         <v>0</v>
       </c>
       <c r="M795" t="n">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="N795" t="n">
-        <v>751.45</v>
+        <v>9300</v>
       </c>
       <c r="O795" t="n">
-        <v>41329.75</v>
+        <v>158100</v>
       </c>
       <c r="P795" t="n">
-        <v>2500</v>
+        <v>11200</v>
       </c>
       <c r="Q795" t="n">
-        <v>137500</v>
+        <v>190400</v>
       </c>
     </row>
     <row r="796">
       <c r="A796" t="inlineStr">
         <is>
-          <t>MG40210</t>
+          <t>JO-129</t>
         </is>
       </c>
       <c r="C796" t="inlineStr">
         <is>
-          <t>SONAJERO OSO MG40210</t>
+          <t>LAPICES COLORES X12 DOBLE PUNTA JO-129</t>
         </is>
       </c>
       <c r="E796" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I796" t="inlineStr">
@@ -36558,7 +36543,7 @@
         </is>
       </c>
       <c r="J796" t="n">
-        <v>154</v>
+        <v>16</v>
       </c>
       <c r="K796" t="n">
         <v>0</v>
@@ -36567,40 +36552,35 @@
         <v>0</v>
       </c>
       <c r="M796" t="n">
-        <v>154</v>
+        <v>16</v>
       </c>
       <c r="N796" t="n">
-        <v>571.87</v>
+        <v>4500</v>
       </c>
       <c r="O796" t="n">
-        <v>88067.98</v>
+        <v>72000</v>
       </c>
       <c r="P796" t="n">
-        <v>2500</v>
+        <v>5400</v>
       </c>
       <c r="Q796" t="n">
-        <v>385000</v>
+        <v>86400</v>
       </c>
     </row>
     <row r="797">
       <c r="A797" t="inlineStr">
         <is>
-          <t>MG40720</t>
-        </is>
-      </c>
-      <c r="B797" t="inlineStr">
-        <is>
-          <t>MG40720</t>
+          <t>JO-139</t>
         </is>
       </c>
       <c r="C797" t="inlineStr">
         <is>
-          <t>MAQUINA DE COSER MINI MG40720</t>
+          <t>ESFERO GIRATORIO 10 MINAS MUÑECA JO-139</t>
         </is>
       </c>
       <c r="E797" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I797" t="inlineStr">
@@ -36609,7 +36589,7 @@
         </is>
       </c>
       <c r="J797" t="n">
-        <v>9</v>
+        <v>51</v>
       </c>
       <c r="K797" t="n">
         <v>0</v>
@@ -36618,35 +36598,35 @@
         <v>0</v>
       </c>
       <c r="M797" t="n">
-        <v>9</v>
+        <v>51</v>
       </c>
       <c r="N797" t="n">
-        <v>9917.040000000001</v>
+        <v>2700</v>
       </c>
       <c r="O797" t="n">
-        <v>89253.36000000002</v>
+        <v>137700</v>
       </c>
       <c r="P797" t="n">
-        <v>15900</v>
+        <v>3300</v>
       </c>
       <c r="Q797" t="n">
-        <v>143100</v>
+        <v>168300</v>
       </c>
     </row>
     <row r="798">
       <c r="A798" t="inlineStr">
         <is>
-          <t>MG40721</t>
+          <t>JO-142</t>
         </is>
       </c>
       <c r="C798" t="inlineStr">
         <is>
-          <t>MAQUINA DE COSER CON PLANCHA MG40721</t>
+          <t>ESFERO BORRABLE CON BORRADOR ASTRONAUTA JO-142</t>
         </is>
       </c>
       <c r="E798" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I798" t="inlineStr">
@@ -36655,7 +36635,7 @@
         </is>
       </c>
       <c r="J798" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="K798" t="n">
         <v>0</v>
@@ -36664,35 +36644,35 @@
         <v>0</v>
       </c>
       <c r="M798" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="N798" t="n">
-        <v>12391.068181818</v>
+        <v>1900</v>
       </c>
       <c r="O798" t="n">
-        <v>136301.749999998</v>
+        <v>68400</v>
       </c>
       <c r="P798" t="n">
-        <v>34900</v>
+        <v>2300</v>
       </c>
       <c r="Q798" t="n">
-        <v>383900</v>
+        <v>82800</v>
       </c>
     </row>
     <row r="799">
       <c r="A799" t="inlineStr">
         <is>
-          <t>MG40942</t>
+          <t>JO-143</t>
         </is>
       </c>
       <c r="C799" t="inlineStr">
         <is>
-          <t>SONAJERO CARRO LEON MG40942</t>
+          <t>ESFERO BORRABKLE CON BORRADOR ARCOIRIS JO-143</t>
         </is>
       </c>
       <c r="E799" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I799" t="inlineStr">
@@ -36701,7 +36681,7 @@
         </is>
       </c>
       <c r="J799" t="n">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="K799" t="n">
         <v>0</v>
@@ -36710,30 +36690,30 @@
         <v>0</v>
       </c>
       <c r="M799" t="n">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="N799" t="n">
-        <v>1864.5</v>
+        <v>1400</v>
       </c>
       <c r="O799" t="n">
-        <v>7458</v>
+        <v>61600</v>
       </c>
       <c r="P799" t="n">
-        <v>17900</v>
+        <v>1700</v>
       </c>
       <c r="Q799" t="n">
-        <v>71600</v>
+        <v>74800</v>
       </c>
     </row>
     <row r="800">
       <c r="A800" t="inlineStr">
         <is>
-          <t>MJC-558</t>
+          <t>JO-144</t>
         </is>
       </c>
       <c r="C800" t="inlineStr">
         <is>
-          <t>MOORAL ESCOLAR TONOS PASTELES 20cm MJC-558</t>
+          <t>ESFERO BORRABLE CON BORRADOR PANDA JO-144</t>
         </is>
       </c>
       <c r="E800" t="inlineStr">
@@ -36747,7 +36727,7 @@
         </is>
       </c>
       <c r="J800" t="n">
-        <v>22</v>
+        <v>72</v>
       </c>
       <c r="K800" t="n">
         <v>0</v>
@@ -36756,30 +36736,30 @@
         <v>0</v>
       </c>
       <c r="M800" t="n">
-        <v>22</v>
+        <v>72</v>
       </c>
       <c r="N800" t="n">
-        <v>40500</v>
+        <v>1900</v>
       </c>
       <c r="O800" t="n">
-        <v>891000</v>
+        <v>136800</v>
       </c>
       <c r="P800" t="n">
-        <v>48600</v>
+        <v>2300</v>
       </c>
       <c r="Q800" t="n">
-        <v>1069200</v>
+        <v>165600</v>
       </c>
     </row>
     <row r="801">
       <c r="A801" t="inlineStr">
         <is>
-          <t>MJC-558-1</t>
+          <t>JO-145</t>
         </is>
       </c>
       <c r="C801" t="inlineStr">
         <is>
-          <t>MORRAL ESCOLAR 20cm MOTIVO ESPACIAL DEPORTE MJ-558-1</t>
+          <t>ESFERO BORRABLE CON BORRADOR OSITO JO-145</t>
         </is>
       </c>
       <c r="E801" t="inlineStr">
@@ -36793,7 +36773,7 @@
         </is>
       </c>
       <c r="J801" t="n">
-        <v>15</v>
+        <v>63</v>
       </c>
       <c r="K801" t="n">
         <v>0</v>
@@ -36802,35 +36782,35 @@
         <v>0</v>
       </c>
       <c r="M801" t="n">
-        <v>15</v>
+        <v>63</v>
       </c>
       <c r="N801" t="n">
-        <v>40500</v>
+        <v>1900</v>
       </c>
       <c r="O801" t="n">
-        <v>607500</v>
+        <v>119700</v>
       </c>
       <c r="P801" t="n">
-        <v>48600</v>
+        <v>2300</v>
       </c>
       <c r="Q801" t="n">
-        <v>729000</v>
+        <v>144900</v>
       </c>
     </row>
     <row r="802">
       <c r="A802" t="inlineStr">
         <is>
-          <t>PT14019</t>
+          <t>JOE-1813</t>
         </is>
       </c>
       <c r="C802" t="inlineStr">
         <is>
-          <t>CUATRIMOTO CON DESTORNILLADOR DIDACTICA PT14019</t>
+          <t>SET MARCADORES ACUARELA LAVAVBLE TUBO X 18 PCS JOE-1813</t>
         </is>
       </c>
       <c r="E802" t="inlineStr">
         <is>
-          <t>DIDACTICOS</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I802" t="inlineStr">
@@ -36839,7 +36819,7 @@
         </is>
       </c>
       <c r="J802" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K802" t="n">
         <v>0</v>
@@ -36848,30 +36828,30 @@
         <v>0</v>
       </c>
       <c r="M802" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N802" t="n">
-        <v>1950.7</v>
+        <v>6000</v>
       </c>
       <c r="O802" t="n">
-        <v>17556.3</v>
+        <v>60000</v>
       </c>
       <c r="P802" t="n">
-        <v>7500</v>
+        <v>7200</v>
       </c>
       <c r="Q802" t="n">
-        <v>67500</v>
+        <v>72000</v>
       </c>
     </row>
     <row r="803">
       <c r="A803" t="inlineStr">
         <is>
-          <t>QQ-1502</t>
+          <t>JOE-9812</t>
         </is>
       </c>
       <c r="C803" t="inlineStr">
         <is>
-          <t>LAPIZ INFINITO REYRACTIL DEPORTES QQ-1502</t>
+          <t>SET MARCADORES JUMBO ACUARELA X12/14cm</t>
         </is>
       </c>
       <c r="E803" t="inlineStr">
@@ -36885,7 +36865,7 @@
         </is>
       </c>
       <c r="J803" t="n">
-        <v>72</v>
+        <v>6</v>
       </c>
       <c r="K803" t="n">
         <v>0</v>
@@ -36894,30 +36874,30 @@
         <v>0</v>
       </c>
       <c r="M803" t="n">
-        <v>72</v>
+        <v>6</v>
       </c>
       <c r="N803" t="n">
-        <v>2200</v>
+        <v>5000</v>
       </c>
       <c r="O803" t="n">
-        <v>158400</v>
+        <v>30000</v>
       </c>
       <c r="P803" t="n">
-        <v>2700</v>
+        <v>6000</v>
       </c>
       <c r="Q803" t="n">
-        <v>194400</v>
+        <v>36000</v>
       </c>
     </row>
     <row r="804">
       <c r="A804" t="inlineStr">
         <is>
-          <t>QQ-1503</t>
+          <t>JT-13</t>
         </is>
       </c>
       <c r="C804" t="inlineStr">
         <is>
-          <t>LAPIZ INFINITO RETRACTIL CARRITO QQ-1503</t>
+          <t>CORRECTOR EN CINTA JT-13</t>
         </is>
       </c>
       <c r="E804" t="inlineStr">
@@ -36931,7 +36911,7 @@
         </is>
       </c>
       <c r="J804" t="n">
-        <v>66</v>
+        <v>7</v>
       </c>
       <c r="K804" t="n">
         <v>0</v>
@@ -36940,30 +36920,30 @@
         <v>0</v>
       </c>
       <c r="M804" t="n">
-        <v>66</v>
+        <v>7</v>
       </c>
       <c r="N804" t="n">
-        <v>2200</v>
+        <v>2400</v>
       </c>
       <c r="O804" t="n">
-        <v>145200</v>
+        <v>16800</v>
       </c>
       <c r="P804" t="n">
-        <v>2700</v>
+        <v>2900</v>
       </c>
       <c r="Q804" t="n">
-        <v>178200</v>
+        <v>20300</v>
       </c>
     </row>
     <row r="805">
       <c r="A805" t="inlineStr">
         <is>
-          <t>QQ-1525</t>
+          <t>K061A</t>
         </is>
       </c>
       <c r="C805" t="inlineStr">
         <is>
-          <t>LAPIZ INFINITO RETRACTIL CAPOBARA QQ-1525</t>
+          <t>ESFERO RETRACTIL CAPIBARA TINTA NEGRA K061A</t>
         </is>
       </c>
       <c r="E805" t="inlineStr">
@@ -36977,7 +36957,7 @@
         </is>
       </c>
       <c r="J805" t="n">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="K805" t="n">
         <v>0</v>
@@ -36986,30 +36966,30 @@
         <v>0</v>
       </c>
       <c r="M805" t="n">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="N805" t="n">
+        <v>1800</v>
+      </c>
+      <c r="O805" t="n">
+        <v>108000</v>
+      </c>
+      <c r="P805" t="n">
         <v>2200</v>
       </c>
-      <c r="O805" t="n">
-        <v>147400</v>
-      </c>
-      <c r="P805" t="n">
-        <v>2700</v>
-      </c>
       <c r="Q805" t="n">
-        <v>180900</v>
+        <v>132000</v>
       </c>
     </row>
     <row r="806">
       <c r="A806" t="inlineStr">
         <is>
-          <t>QQ-827</t>
+          <t>LY6807</t>
         </is>
       </c>
       <c r="C806" t="inlineStr">
         <is>
-          <t>ESFERO CON LUZ BALONES QQ-827</t>
+          <t>JUGUETE PATINETA DE CUATRO RUEDAS LY6807</t>
         </is>
       </c>
       <c r="E806" t="inlineStr">
@@ -37023,7 +37003,7 @@
         </is>
       </c>
       <c r="J806" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="K806" t="n">
         <v>0</v>
@@ -37032,30 +37012,30 @@
         <v>0</v>
       </c>
       <c r="M806" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="N806" t="n">
-        <v>2100</v>
+        <v>415.07</v>
       </c>
       <c r="O806" t="n">
-        <v>71400</v>
+        <v>16602.8</v>
       </c>
       <c r="P806" t="n">
-        <v>2600</v>
+        <v>2900</v>
       </c>
       <c r="Q806" t="n">
-        <v>88400</v>
+        <v>116000</v>
       </c>
     </row>
     <row r="807">
       <c r="A807" t="inlineStr">
         <is>
-          <t>QT511252-E</t>
+          <t>MC121011-E</t>
         </is>
       </c>
       <c r="C807" t="inlineStr">
         <is>
-          <t>COLORES DE ALTA GAMA CARRITOS X12PCS QT511252-E</t>
+          <t>SET LAPIZ CON BORRADOR OSITOS MC121011-E</t>
         </is>
       </c>
       <c r="E807" t="inlineStr">
@@ -37069,7 +37049,7 @@
         </is>
       </c>
       <c r="J807" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="K807" t="n">
         <v>0</v>
@@ -37078,30 +37058,30 @@
         <v>0</v>
       </c>
       <c r="M807" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="N807" t="n">
-        <v>5026.6659322034</v>
+        <v>6500</v>
       </c>
       <c r="O807" t="n">
-        <v>105559.9845762714</v>
+        <v>39000</v>
       </c>
       <c r="P807" t="n">
-        <v>6300</v>
+        <v>7800</v>
       </c>
       <c r="Q807" t="n">
-        <v>132300</v>
+        <v>46800</v>
       </c>
     </row>
     <row r="808">
       <c r="A808" t="inlineStr">
         <is>
-          <t>QT511253-E</t>
+          <t>MC121212</t>
         </is>
       </c>
       <c r="C808" t="inlineStr">
         <is>
-          <t>COLORES DE ALTA GAMA PRINCESAS X12 PCS QT511253-E</t>
+          <t>SET LAPIZ CON BORRADOR Y TAJALAPIZ ROBOT MC121212</t>
         </is>
       </c>
       <c r="E808" t="inlineStr">
@@ -37115,7 +37095,7 @@
         </is>
       </c>
       <c r="J808" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="K808" t="n">
         <v>0</v>
@@ -37124,35 +37104,40 @@
         <v>0</v>
       </c>
       <c r="M808" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="N808" t="n">
-        <v>5200</v>
+        <v>6500</v>
       </c>
       <c r="O808" t="n">
-        <v>109200</v>
+        <v>39000</v>
       </c>
       <c r="P808" t="n">
-        <v>6300</v>
+        <v>7800</v>
       </c>
       <c r="Q808" t="n">
-        <v>132300</v>
+        <v>46800</v>
       </c>
     </row>
     <row r="809">
       <c r="A809" t="inlineStr">
         <is>
-          <t>QT512453-E</t>
+          <t>MG16332</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>MG16332</t>
         </is>
       </c>
       <c r="C809" t="inlineStr">
         <is>
-          <t>COLORES DE ALTA GAMA PRINCESA X24 PCS QT512453-E</t>
+          <t>LANZADOR  ARCO Y FLECA CON LASER MG16332</t>
         </is>
       </c>
       <c r="E809" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I809" t="inlineStr">
@@ -37161,7 +37146,7 @@
         </is>
       </c>
       <c r="J809" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="K809" t="n">
         <v>0</v>
@@ -37170,35 +37155,35 @@
         <v>0</v>
       </c>
       <c r="M809" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="N809" t="n">
-        <v>8800</v>
+        <v>8439.969999999999</v>
       </c>
       <c r="O809" t="n">
-        <v>193600</v>
+        <v>84399.7</v>
       </c>
       <c r="P809" t="n">
-        <v>10600</v>
+        <v>29500</v>
       </c>
       <c r="Q809" t="n">
-        <v>233200</v>
+        <v>295000</v>
       </c>
     </row>
     <row r="810">
       <c r="A810" t="inlineStr">
         <is>
-          <t>SLT1934</t>
+          <t>MG20129</t>
         </is>
       </c>
       <c r="C810" t="inlineStr">
         <is>
-          <t>BROMA DE FIESTA CARTON X 40 PCS</t>
+          <t>SET MOLDE PARA HELADOS Y FRUTAS EN PLASTILINA MG20129</t>
         </is>
       </c>
       <c r="E810" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I810" t="inlineStr">
@@ -37207,7 +37192,7 @@
         </is>
       </c>
       <c r="J810" t="n">
-        <v>296</v>
+        <v>10</v>
       </c>
       <c r="K810" t="n">
         <v>0</v>
@@ -37216,64 +37201,1137 @@
         <v>0</v>
       </c>
       <c r="M810" t="n">
-        <v>296</v>
+        <v>10</v>
       </c>
       <c r="N810" t="n">
-        <v>4550</v>
+        <v>7860.59</v>
       </c>
       <c r="O810" t="n">
-        <v>1346800</v>
+        <v>78605.89999999999</v>
       </c>
       <c r="P810" t="n">
-        <v>5500</v>
+        <v>21500</v>
       </c>
       <c r="Q810" t="n">
-        <v>1628000</v>
+        <v>215000</v>
       </c>
     </row>
     <row r="811">
       <c r="A811" t="inlineStr">
         <is>
+          <t>MG20430</t>
+        </is>
+      </c>
+      <c r="C811" t="inlineStr">
+        <is>
+          <t>SET PLASTILINA CON MOLDES BARBERIA MALETA MG20430</t>
+        </is>
+      </c>
+      <c r="E811" t="inlineStr">
+        <is>
+          <t>PIÑATERIA</t>
+        </is>
+      </c>
+      <c r="I811" t="inlineStr">
+        <is>
+          <t>Und</t>
+        </is>
+      </c>
+      <c r="J811" t="n">
+        <v>2</v>
+      </c>
+      <c r="K811" t="n">
+        <v>0</v>
+      </c>
+      <c r="L811" t="n">
+        <v>0</v>
+      </c>
+      <c r="M811" t="n">
+        <v>2</v>
+      </c>
+      <c r="N811" t="n">
+        <v>12189.832</v>
+      </c>
+      <c r="O811" t="n">
+        <v>24379.664</v>
+      </c>
+      <c r="P811" t="n">
+        <v>30900</v>
+      </c>
+      <c r="Q811" t="n">
+        <v>61800</v>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>MG20669</t>
+        </is>
+      </c>
+      <c r="C812" t="inlineStr">
+        <is>
+          <t>SET DE PLASTILINA PARA MOLDEAR EN BLISTER MG20669</t>
+        </is>
+      </c>
+      <c r="E812" t="inlineStr">
+        <is>
+          <t>DIDACTICO</t>
+        </is>
+      </c>
+      <c r="I812" t="inlineStr">
+        <is>
+          <t>Und</t>
+        </is>
+      </c>
+      <c r="J812" t="n">
+        <v>24</v>
+      </c>
+      <c r="K812" t="n">
+        <v>0</v>
+      </c>
+      <c r="L812" t="n">
+        <v>0</v>
+      </c>
+      <c r="M812" t="n">
+        <v>24</v>
+      </c>
+      <c r="N812" t="n">
+        <v>970.631875</v>
+      </c>
+      <c r="O812" t="n">
+        <v>23295.165</v>
+      </c>
+      <c r="P812" t="n">
+        <v>7200</v>
+      </c>
+      <c r="Q812" t="n">
+        <v>172800</v>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>MG20906</t>
+        </is>
+      </c>
+      <c r="C813" t="inlineStr">
+        <is>
+          <t>DINOSAURIO DIDACTICO EN BOLSA MG20906</t>
+        </is>
+      </c>
+      <c r="E813" t="inlineStr">
+        <is>
+          <t>DIDACTICO</t>
+        </is>
+      </c>
+      <c r="I813" t="inlineStr">
+        <is>
+          <t>Und</t>
+        </is>
+      </c>
+      <c r="J813" t="n">
+        <v>63</v>
+      </c>
+      <c r="K813" t="n">
+        <v>0</v>
+      </c>
+      <c r="L813" t="n">
+        <v>0</v>
+      </c>
+      <c r="M813" t="n">
+        <v>63</v>
+      </c>
+      <c r="N813" t="n">
+        <v>1482.84</v>
+      </c>
+      <c r="O813" t="n">
+        <v>93418.92</v>
+      </c>
+      <c r="P813" t="n">
+        <v>6500</v>
+      </c>
+      <c r="Q813" t="n">
+        <v>409500</v>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>MG22320</t>
+        </is>
+      </c>
+      <c r="C814" t="inlineStr">
+        <is>
+          <t>CABALLO DIDACTICO DESARMABLE PQÑ MG22320</t>
+        </is>
+      </c>
+      <c r="E814" t="inlineStr">
+        <is>
+          <t>DIDACTICOS</t>
+        </is>
+      </c>
+      <c r="I814" t="inlineStr">
+        <is>
+          <t>Und</t>
+        </is>
+      </c>
+      <c r="J814" t="n">
+        <v>13</v>
+      </c>
+      <c r="K814" t="n">
+        <v>0</v>
+      </c>
+      <c r="L814" t="n">
+        <v>0</v>
+      </c>
+      <c r="M814" t="n">
+        <v>13</v>
+      </c>
+      <c r="N814" t="n">
+        <v>1129.14</v>
+      </c>
+      <c r="O814" t="n">
+        <v>14678.82</v>
+      </c>
+      <c r="P814" t="n">
+        <v>6900</v>
+      </c>
+      <c r="Q814" t="n">
+        <v>89700</v>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>MG22435</t>
+        </is>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>MG22435</t>
+        </is>
+      </c>
+      <c r="C815" t="inlineStr">
+        <is>
+          <t>SONAJERO PERRITO BOLSA PQÑ MG22435</t>
+        </is>
+      </c>
+      <c r="E815" t="inlineStr">
+        <is>
+          <t>PIÑATERIA</t>
+        </is>
+      </c>
+      <c r="I815" t="inlineStr">
+        <is>
+          <t>Und</t>
+        </is>
+      </c>
+      <c r="J815" t="n">
+        <v>51</v>
+      </c>
+      <c r="K815" t="n">
+        <v>0</v>
+      </c>
+      <c r="L815" t="n">
+        <v>0</v>
+      </c>
+      <c r="M815" t="n">
+        <v>51</v>
+      </c>
+      <c r="N815" t="n">
+        <v>1236.3</v>
+      </c>
+      <c r="O815" t="n">
+        <v>63051.3</v>
+      </c>
+      <c r="P815" t="n">
+        <v>2300</v>
+      </c>
+      <c r="Q815" t="n">
+        <v>117300</v>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>MG26010</t>
+        </is>
+      </c>
+      <c r="C816" t="inlineStr">
+        <is>
+          <t>SET BELLEZA CON ACCESORIOS EMPAQUE BOLSO MG26010</t>
+        </is>
+      </c>
+      <c r="E816" t="inlineStr">
+        <is>
+          <t>PIÑATERIA</t>
+        </is>
+      </c>
+      <c r="I816" t="inlineStr">
+        <is>
+          <t>Und</t>
+        </is>
+      </c>
+      <c r="J816" t="n">
+        <v>11</v>
+      </c>
+      <c r="K816" t="n">
+        <v>0</v>
+      </c>
+      <c r="L816" t="n">
+        <v>0</v>
+      </c>
+      <c r="M816" t="n">
+        <v>11</v>
+      </c>
+      <c r="N816" t="n">
+        <v>11433.53</v>
+      </c>
+      <c r="O816" t="n">
+        <v>125768.83</v>
+      </c>
+      <c r="P816" t="n">
+        <v>15000</v>
+      </c>
+      <c r="Q816" t="n">
+        <v>165000</v>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>MG27230</t>
+        </is>
+      </c>
+      <c r="C817" t="inlineStr">
+        <is>
+          <t>SET PLASTILINA ODONTOLOGICO CAJA MG27230</t>
+        </is>
+      </c>
+      <c r="E817" t="inlineStr">
+        <is>
+          <t>PIÑATERIA</t>
+        </is>
+      </c>
+      <c r="I817" t="inlineStr">
+        <is>
+          <t>Und</t>
+        </is>
+      </c>
+      <c r="J817" t="n">
+        <v>9</v>
+      </c>
+      <c r="K817" t="n">
+        <v>0</v>
+      </c>
+      <c r="L817" t="n">
+        <v>0</v>
+      </c>
+      <c r="M817" t="n">
+        <v>9</v>
+      </c>
+      <c r="N817" t="n">
+        <v>12115.88</v>
+      </c>
+      <c r="O817" t="n">
+        <v>109042.92</v>
+      </c>
+      <c r="P817" t="n">
+        <v>31500</v>
+      </c>
+      <c r="Q817" t="n">
+        <v>283500</v>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>MG33219</t>
+        </is>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>MG33219</t>
+        </is>
+      </c>
+      <c r="C818" t="inlineStr">
+        <is>
+          <t>BINOCULARES CAMUFLADOS MG33219</t>
+        </is>
+      </c>
+      <c r="E818" t="inlineStr">
+        <is>
+          <t>MICELANEOS</t>
+        </is>
+      </c>
+      <c r="I818" t="inlineStr">
+        <is>
+          <t>Und</t>
+        </is>
+      </c>
+      <c r="J818" t="n">
+        <v>55</v>
+      </c>
+      <c r="K818" t="n">
+        <v>0</v>
+      </c>
+      <c r="L818" t="n">
+        <v>0</v>
+      </c>
+      <c r="M818" t="n">
+        <v>55</v>
+      </c>
+      <c r="N818" t="n">
+        <v>751.45</v>
+      </c>
+      <c r="O818" t="n">
+        <v>41329.75</v>
+      </c>
+      <c r="P818" t="n">
+        <v>2500</v>
+      </c>
+      <c r="Q818" t="n">
+        <v>137500</v>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>MG40210</t>
+        </is>
+      </c>
+      <c r="C819" t="inlineStr">
+        <is>
+          <t>SONAJERO OSO MG40210</t>
+        </is>
+      </c>
+      <c r="E819" t="inlineStr">
+        <is>
+          <t>DIDACTICO</t>
+        </is>
+      </c>
+      <c r="I819" t="inlineStr">
+        <is>
+          <t>Und</t>
+        </is>
+      </c>
+      <c r="J819" t="n">
+        <v>154</v>
+      </c>
+      <c r="K819" t="n">
+        <v>0</v>
+      </c>
+      <c r="L819" t="n">
+        <v>0</v>
+      </c>
+      <c r="M819" t="n">
+        <v>154</v>
+      </c>
+      <c r="N819" t="n">
+        <v>571.87</v>
+      </c>
+      <c r="O819" t="n">
+        <v>88067.98</v>
+      </c>
+      <c r="P819" t="n">
+        <v>2500</v>
+      </c>
+      <c r="Q819" t="n">
+        <v>385000</v>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>MG40720</t>
+        </is>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>MG40720</t>
+        </is>
+      </c>
+      <c r="C820" t="inlineStr">
+        <is>
+          <t>MAQUINA DE COSER MINI MG40720</t>
+        </is>
+      </c>
+      <c r="E820" t="inlineStr">
+        <is>
+          <t>PIÑATERIA</t>
+        </is>
+      </c>
+      <c r="I820" t="inlineStr">
+        <is>
+          <t>Und</t>
+        </is>
+      </c>
+      <c r="J820" t="n">
+        <v>9</v>
+      </c>
+      <c r="K820" t="n">
+        <v>0</v>
+      </c>
+      <c r="L820" t="n">
+        <v>0</v>
+      </c>
+      <c r="M820" t="n">
+        <v>9</v>
+      </c>
+      <c r="N820" t="n">
+        <v>9917.040000000001</v>
+      </c>
+      <c r="O820" t="n">
+        <v>89253.36000000002</v>
+      </c>
+      <c r="P820" t="n">
+        <v>15900</v>
+      </c>
+      <c r="Q820" t="n">
+        <v>143100</v>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>MG40721</t>
+        </is>
+      </c>
+      <c r="C821" t="inlineStr">
+        <is>
+          <t>MAQUINA DE COSER CON PLANCHA MG40721</t>
+        </is>
+      </c>
+      <c r="E821" t="inlineStr">
+        <is>
+          <t>PIÑATERIA</t>
+        </is>
+      </c>
+      <c r="I821" t="inlineStr">
+        <is>
+          <t>Und</t>
+        </is>
+      </c>
+      <c r="J821" t="n">
+        <v>11</v>
+      </c>
+      <c r="K821" t="n">
+        <v>0</v>
+      </c>
+      <c r="L821" t="n">
+        <v>0</v>
+      </c>
+      <c r="M821" t="n">
+        <v>11</v>
+      </c>
+      <c r="N821" t="n">
+        <v>12391.068181818</v>
+      </c>
+      <c r="O821" t="n">
+        <v>136301.749999998</v>
+      </c>
+      <c r="P821" t="n">
+        <v>34900</v>
+      </c>
+      <c r="Q821" t="n">
+        <v>383900</v>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>MG40942</t>
+        </is>
+      </c>
+      <c r="C822" t="inlineStr">
+        <is>
+          <t>SONAJERO CARRO LEON MG40942</t>
+        </is>
+      </c>
+      <c r="E822" t="inlineStr">
+        <is>
+          <t>DIDACTICO</t>
+        </is>
+      </c>
+      <c r="I822" t="inlineStr">
+        <is>
+          <t>Und</t>
+        </is>
+      </c>
+      <c r="J822" t="n">
+        <v>4</v>
+      </c>
+      <c r="K822" t="n">
+        <v>0</v>
+      </c>
+      <c r="L822" t="n">
+        <v>0</v>
+      </c>
+      <c r="M822" t="n">
+        <v>4</v>
+      </c>
+      <c r="N822" t="n">
+        <v>1864.5</v>
+      </c>
+      <c r="O822" t="n">
+        <v>7458</v>
+      </c>
+      <c r="P822" t="n">
+        <v>17900</v>
+      </c>
+      <c r="Q822" t="n">
+        <v>71600</v>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>MJC-558</t>
+        </is>
+      </c>
+      <c r="C823" t="inlineStr">
+        <is>
+          <t>MOORAL ESCOLAR TONOS PASTELES 20cm MJC-558</t>
+        </is>
+      </c>
+      <c r="E823" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
+        </is>
+      </c>
+      <c r="I823" t="inlineStr">
+        <is>
+          <t>Und</t>
+        </is>
+      </c>
+      <c r="J823" t="n">
+        <v>22</v>
+      </c>
+      <c r="K823" t="n">
+        <v>0</v>
+      </c>
+      <c r="L823" t="n">
+        <v>0</v>
+      </c>
+      <c r="M823" t="n">
+        <v>22</v>
+      </c>
+      <c r="N823" t="n">
+        <v>40500</v>
+      </c>
+      <c r="O823" t="n">
+        <v>891000</v>
+      </c>
+      <c r="P823" t="n">
+        <v>48600</v>
+      </c>
+      <c r="Q823" t="n">
+        <v>1069200</v>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>MJC-558-1</t>
+        </is>
+      </c>
+      <c r="C824" t="inlineStr">
+        <is>
+          <t>MORRAL ESCOLAR 20cm MOTIVO ESPACIAL DEPORTE MJ-558-1</t>
+        </is>
+      </c>
+      <c r="E824" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
+        </is>
+      </c>
+      <c r="I824" t="inlineStr">
+        <is>
+          <t>Und</t>
+        </is>
+      </c>
+      <c r="J824" t="n">
+        <v>15</v>
+      </c>
+      <c r="K824" t="n">
+        <v>0</v>
+      </c>
+      <c r="L824" t="n">
+        <v>0</v>
+      </c>
+      <c r="M824" t="n">
+        <v>15</v>
+      </c>
+      <c r="N824" t="n">
+        <v>40500</v>
+      </c>
+      <c r="O824" t="n">
+        <v>607500</v>
+      </c>
+      <c r="P824" t="n">
+        <v>48600</v>
+      </c>
+      <c r="Q824" t="n">
+        <v>729000</v>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>PT14019</t>
+        </is>
+      </c>
+      <c r="C825" t="inlineStr">
+        <is>
+          <t>CUATRIMOTO CON DESTORNILLADOR DIDACTICA PT14019</t>
+        </is>
+      </c>
+      <c r="E825" t="inlineStr">
+        <is>
+          <t>DIDACTICOS</t>
+        </is>
+      </c>
+      <c r="I825" t="inlineStr">
+        <is>
+          <t>Und</t>
+        </is>
+      </c>
+      <c r="J825" t="n">
+        <v>9</v>
+      </c>
+      <c r="K825" t="n">
+        <v>0</v>
+      </c>
+      <c r="L825" t="n">
+        <v>0</v>
+      </c>
+      <c r="M825" t="n">
+        <v>9</v>
+      </c>
+      <c r="N825" t="n">
+        <v>1950.7</v>
+      </c>
+      <c r="O825" t="n">
+        <v>17556.3</v>
+      </c>
+      <c r="P825" t="n">
+        <v>7500</v>
+      </c>
+      <c r="Q825" t="n">
+        <v>67500</v>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>QQ-1502</t>
+        </is>
+      </c>
+      <c r="C826" t="inlineStr">
+        <is>
+          <t>LAPIZ INFINITO REYRACTIL DEPORTES QQ-1502</t>
+        </is>
+      </c>
+      <c r="E826" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
+        </is>
+      </c>
+      <c r="I826" t="inlineStr">
+        <is>
+          <t>Und</t>
+        </is>
+      </c>
+      <c r="J826" t="n">
+        <v>72</v>
+      </c>
+      <c r="K826" t="n">
+        <v>0</v>
+      </c>
+      <c r="L826" t="n">
+        <v>0</v>
+      </c>
+      <c r="M826" t="n">
+        <v>72</v>
+      </c>
+      <c r="N826" t="n">
+        <v>2200</v>
+      </c>
+      <c r="O826" t="n">
+        <v>158400</v>
+      </c>
+      <c r="P826" t="n">
+        <v>2700</v>
+      </c>
+      <c r="Q826" t="n">
+        <v>194400</v>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>QQ-1503</t>
+        </is>
+      </c>
+      <c r="C827" t="inlineStr">
+        <is>
+          <t>LAPIZ INFINITO RETRACTIL CARRITO QQ-1503</t>
+        </is>
+      </c>
+      <c r="E827" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
+        </is>
+      </c>
+      <c r="I827" t="inlineStr">
+        <is>
+          <t>Und</t>
+        </is>
+      </c>
+      <c r="J827" t="n">
+        <v>66</v>
+      </c>
+      <c r="K827" t="n">
+        <v>0</v>
+      </c>
+      <c r="L827" t="n">
+        <v>0</v>
+      </c>
+      <c r="M827" t="n">
+        <v>66</v>
+      </c>
+      <c r="N827" t="n">
+        <v>2200</v>
+      </c>
+      <c r="O827" t="n">
+        <v>145200</v>
+      </c>
+      <c r="P827" t="n">
+        <v>2700</v>
+      </c>
+      <c r="Q827" t="n">
+        <v>178200</v>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>QQ-1525</t>
+        </is>
+      </c>
+      <c r="C828" t="inlineStr">
+        <is>
+          <t>LAPIZ INFINITO RETRACTIL CAPOBARA QQ-1525</t>
+        </is>
+      </c>
+      <c r="E828" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
+        </is>
+      </c>
+      <c r="I828" t="inlineStr">
+        <is>
+          <t>Und</t>
+        </is>
+      </c>
+      <c r="J828" t="n">
+        <v>67</v>
+      </c>
+      <c r="K828" t="n">
+        <v>0</v>
+      </c>
+      <c r="L828" t="n">
+        <v>0</v>
+      </c>
+      <c r="M828" t="n">
+        <v>67</v>
+      </c>
+      <c r="N828" t="n">
+        <v>2200</v>
+      </c>
+      <c r="O828" t="n">
+        <v>147400</v>
+      </c>
+      <c r="P828" t="n">
+        <v>2700</v>
+      </c>
+      <c r="Q828" t="n">
+        <v>180900</v>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>QQ-827</t>
+        </is>
+      </c>
+      <c r="C829" t="inlineStr">
+        <is>
+          <t>ESFERO CON LUZ BALONES QQ-827</t>
+        </is>
+      </c>
+      <c r="E829" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
+        </is>
+      </c>
+      <c r="I829" t="inlineStr">
+        <is>
+          <t>Und</t>
+        </is>
+      </c>
+      <c r="J829" t="n">
+        <v>34</v>
+      </c>
+      <c r="K829" t="n">
+        <v>0</v>
+      </c>
+      <c r="L829" t="n">
+        <v>0</v>
+      </c>
+      <c r="M829" t="n">
+        <v>34</v>
+      </c>
+      <c r="N829" t="n">
+        <v>2100</v>
+      </c>
+      <c r="O829" t="n">
+        <v>71400</v>
+      </c>
+      <c r="P829" t="n">
+        <v>2600</v>
+      </c>
+      <c r="Q829" t="n">
+        <v>88400</v>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>QT511252-E</t>
+        </is>
+      </c>
+      <c r="C830" t="inlineStr">
+        <is>
+          <t>COLORES DE ALTA GAMA CARRITOS X12PCS QT511252-E</t>
+        </is>
+      </c>
+      <c r="E830" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
+        </is>
+      </c>
+      <c r="I830" t="inlineStr">
+        <is>
+          <t>Und</t>
+        </is>
+      </c>
+      <c r="J830" t="n">
+        <v>21</v>
+      </c>
+      <c r="K830" t="n">
+        <v>0</v>
+      </c>
+      <c r="L830" t="n">
+        <v>0</v>
+      </c>
+      <c r="M830" t="n">
+        <v>21</v>
+      </c>
+      <c r="N830" t="n">
+        <v>5026.6659322034</v>
+      </c>
+      <c r="O830" t="n">
+        <v>105559.9845762714</v>
+      </c>
+      <c r="P830" t="n">
+        <v>6300</v>
+      </c>
+      <c r="Q830" t="n">
+        <v>132300</v>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>QT511253-E</t>
+        </is>
+      </c>
+      <c r="C831" t="inlineStr">
+        <is>
+          <t>COLORES DE ALTA GAMA PRINCESAS X12 PCS QT511253-E</t>
+        </is>
+      </c>
+      <c r="E831" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
+        </is>
+      </c>
+      <c r="I831" t="inlineStr">
+        <is>
+          <t>Und</t>
+        </is>
+      </c>
+      <c r="J831" t="n">
+        <v>21</v>
+      </c>
+      <c r="K831" t="n">
+        <v>0</v>
+      </c>
+      <c r="L831" t="n">
+        <v>0</v>
+      </c>
+      <c r="M831" t="n">
+        <v>21</v>
+      </c>
+      <c r="N831" t="n">
+        <v>5200</v>
+      </c>
+      <c r="O831" t="n">
+        <v>109200</v>
+      </c>
+      <c r="P831" t="n">
+        <v>6300</v>
+      </c>
+      <c r="Q831" t="n">
+        <v>132300</v>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>QT512453-E</t>
+        </is>
+      </c>
+      <c r="C832" t="inlineStr">
+        <is>
+          <t>COLORES DE ALTA GAMA PRINCESA X24 PCS QT512453-E</t>
+        </is>
+      </c>
+      <c r="E832" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
+        </is>
+      </c>
+      <c r="I832" t="inlineStr">
+        <is>
+          <t>Und</t>
+        </is>
+      </c>
+      <c r="J832" t="n">
+        <v>22</v>
+      </c>
+      <c r="K832" t="n">
+        <v>0</v>
+      </c>
+      <c r="L832" t="n">
+        <v>0</v>
+      </c>
+      <c r="M832" t="n">
+        <v>22</v>
+      </c>
+      <c r="N832" t="n">
+        <v>8800</v>
+      </c>
+      <c r="O832" t="n">
+        <v>193600</v>
+      </c>
+      <c r="P832" t="n">
+        <v>10600</v>
+      </c>
+      <c r="Q832" t="n">
+        <v>233200</v>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>SLT1934</t>
+        </is>
+      </c>
+      <c r="C833" t="inlineStr">
+        <is>
+          <t>BROMA DE FIESTA CARTON X 40 PCS</t>
+        </is>
+      </c>
+      <c r="E833" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
+        </is>
+      </c>
+      <c r="I833" t="inlineStr">
+        <is>
+          <t>Und</t>
+        </is>
+      </c>
+      <c r="J833" t="n">
+        <v>296</v>
+      </c>
+      <c r="K833" t="n">
+        <v>0</v>
+      </c>
+      <c r="L833" t="n">
+        <v>0</v>
+      </c>
+      <c r="M833" t="n">
+        <v>296</v>
+      </c>
+      <c r="N833" t="n">
+        <v>4550</v>
+      </c>
+      <c r="O833" t="n">
+        <v>1346800</v>
+      </c>
+      <c r="P833" t="n">
+        <v>5500</v>
+      </c>
+      <c r="Q833" t="n">
+        <v>1628000</v>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
           <t>XP-2986</t>
         </is>
       </c>
-      <c r="C811" t="inlineStr">
+      <c r="C834" t="inlineStr">
         <is>
           <t>BORRADOR RETRACTIL COHETE XP-2986</t>
         </is>
       </c>
-      <c r="E811" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
-        </is>
-      </c>
-      <c r="I811" t="inlineStr">
-        <is>
-          <t>Und</t>
-        </is>
-      </c>
-      <c r="J811" t="n">
+      <c r="E834" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
+        </is>
+      </c>
+      <c r="I834" t="inlineStr">
+        <is>
+          <t>Und</t>
+        </is>
+      </c>
+      <c r="J834" t="n">
         <v>3</v>
       </c>
-      <c r="K811" t="n">
-        <v>0</v>
-      </c>
-      <c r="L811" t="n">
-        <v>0</v>
-      </c>
-      <c r="M811" t="n">
+      <c r="K834" t="n">
+        <v>0</v>
+      </c>
+      <c r="L834" t="n">
+        <v>0</v>
+      </c>
+      <c r="M834" t="n">
         <v>3</v>
       </c>
-      <c r="N811" t="n">
+      <c r="N834" t="n">
         <v>2402.6741428571</v>
       </c>
-      <c r="O811" t="n">
+      <c r="O834" t="n">
         <v>7208.022428571299</v>
       </c>
-      <c r="P811" t="n">
+      <c r="P834" t="n">
         <v>3000</v>
       </c>
-      <c r="Q811" t="n">
+      <c r="Q834" t="n">
         <v>9000</v>
       </c>
     </row>

--- a/bodegas/LJ-05.xlsx
+++ b/bodegas/LJ-05.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-23</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-24</t>
         </is>
       </c>
     </row>
@@ -35025,10 +35025,10 @@
         </is>
       </c>
       <c r="J763" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="K763" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="L763" t="n">
         <v>0</v>
@@ -35071,10 +35071,10 @@
         </is>
       </c>
       <c r="J764" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="K764" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="L764" t="n">
         <v>0</v>
@@ -35117,10 +35117,10 @@
         </is>
       </c>
       <c r="J765" t="n">
-        <v>0</v>
+        <v>432</v>
       </c>
       <c r="K765" t="n">
-        <v>432</v>
+        <v>0</v>
       </c>
       <c r="L765" t="n">
         <v>0</v>
@@ -35163,10 +35163,10 @@
         </is>
       </c>
       <c r="J766" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="K766" t="n">
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="L766" t="n">
         <v>0</v>
@@ -35209,10 +35209,10 @@
         </is>
       </c>
       <c r="J767" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="K767" t="n">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="L767" t="n">
         <v>0</v>
@@ -35255,10 +35255,10 @@
         </is>
       </c>
       <c r="J768" t="n">
-        <v>0</v>
+        <v>720</v>
       </c>
       <c r="K768" t="n">
-        <v>720</v>
+        <v>0</v>
       </c>
       <c r="L768" t="n">
         <v>0</v>
@@ -35301,10 +35301,10 @@
         </is>
       </c>
       <c r="J769" t="n">
-        <v>0</v>
+        <v>288</v>
       </c>
       <c r="K769" t="n">
-        <v>288</v>
+        <v>0</v>
       </c>
       <c r="L769" t="n">
         <v>0</v>
@@ -35347,10 +35347,10 @@
         </is>
       </c>
       <c r="J770" t="n">
-        <v>0</v>
+        <v>720</v>
       </c>
       <c r="K770" t="n">
-        <v>720</v>
+        <v>0</v>
       </c>
       <c r="L770" t="n">
         <v>0</v>
@@ -35393,10 +35393,10 @@
         </is>
       </c>
       <c r="J771" t="n">
-        <v>0</v>
+        <v>288</v>
       </c>
       <c r="K771" t="n">
-        <v>288</v>
+        <v>0</v>
       </c>
       <c r="L771" t="n">
         <v>0</v>
@@ -35439,10 +35439,10 @@
         </is>
       </c>
       <c r="J772" t="n">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="K772" t="n">
-        <v>192</v>
+        <v>0</v>
       </c>
       <c r="L772" t="n">
         <v>0</v>
@@ -35485,10 +35485,10 @@
         </is>
       </c>
       <c r="J773" t="n">
-        <v>0</v>
+        <v>288</v>
       </c>
       <c r="K773" t="n">
-        <v>288</v>
+        <v>0</v>
       </c>
       <c r="L773" t="n">
         <v>0</v>
@@ -35531,10 +35531,10 @@
         </is>
       </c>
       <c r="J774" t="n">
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="K774" t="n">
-        <v>216</v>
+        <v>0</v>
       </c>
       <c r="L774" t="n">
         <v>0</v>
@@ -35577,10 +35577,10 @@
         </is>
       </c>
       <c r="J775" t="n">
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="K775" t="n">
-        <v>216</v>
+        <v>0</v>
       </c>
       <c r="L775" t="n">
         <v>0</v>
@@ -35623,10 +35623,10 @@
         </is>
       </c>
       <c r="J776" t="n">
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="K776" t="n">
-        <v>216</v>
+        <v>0</v>
       </c>
       <c r="L776" t="n">
         <v>0</v>
@@ -35669,10 +35669,10 @@
         </is>
       </c>
       <c r="J777" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="K777" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="L777" t="n">
         <v>0</v>
@@ -35715,10 +35715,10 @@
         </is>
       </c>
       <c r="J778" t="n">
-        <v>0</v>
+        <v>384</v>
       </c>
       <c r="K778" t="n">
-        <v>384</v>
+        <v>0</v>
       </c>
       <c r="L778" t="n">
         <v>0</v>
@@ -35761,10 +35761,10 @@
         </is>
       </c>
       <c r="J779" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="K779" t="n">
-        <v>360</v>
+        <v>0</v>
       </c>
       <c r="L779" t="n">
         <v>0</v>
@@ -35807,10 +35807,10 @@
         </is>
       </c>
       <c r="J780" t="n">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="K780" t="n">
-        <v>192</v>
+        <v>0</v>
       </c>
       <c r="L780" t="n">
         <v>0</v>
@@ -35853,10 +35853,10 @@
         </is>
       </c>
       <c r="J781" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K781" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="L781" t="n">
         <v>0</v>
@@ -35945,10 +35945,10 @@
         </is>
       </c>
       <c r="J783" t="n">
-        <v>0</v>
+        <v>840</v>
       </c>
       <c r="K783" t="n">
-        <v>840</v>
+        <v>0</v>
       </c>
       <c r="L783" t="n">
         <v>0</v>
@@ -35991,10 +35991,10 @@
         </is>
       </c>
       <c r="J784" t="n">
-        <v>0</v>
+        <v>384</v>
       </c>
       <c r="K784" t="n">
-        <v>384</v>
+        <v>0</v>
       </c>
       <c r="L784" t="n">
         <v>0</v>
@@ -36083,10 +36083,10 @@
         </is>
       </c>
       <c r="J786" t="n">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="K786" t="n">
-        <v>192</v>
+        <v>0</v>
       </c>
       <c r="L786" t="n">
         <v>0</v>
@@ -36129,10 +36129,10 @@
         </is>
       </c>
       <c r="J787" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="K787" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="L787" t="n">
         <v>0</v>

--- a/bodegas/LJ-05.xlsx
+++ b/bodegas/LJ-05.xlsx
@@ -944,22 +944,22 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M13" t="n">
-        <v>389</v>
+        <v>365</v>
       </c>
       <c r="N13" t="n">
-        <v>1811.3059701493</v>
+        <v>1811.3062015504</v>
       </c>
       <c r="O13" t="n">
-        <v>704598.0223880777</v>
+        <v>661126.763565896</v>
       </c>
       <c r="P13" t="n">
         <v>2600</v>
       </c>
       <c r="Q13" t="n">
-        <v>1011400</v>
+        <v>949000</v>
       </c>
     </row>
     <row r="14">
@@ -1022,22 +1022,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M15" t="n">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="N15" t="n">
-        <v>3376.7464843537</v>
+        <v>3376.7464728365</v>
       </c>
       <c r="O15" t="n">
-        <v>405209.578122444</v>
+        <v>364688.619066342</v>
       </c>
       <c r="P15" t="n">
         <v>4500</v>
       </c>
       <c r="Q15" t="n">
-        <v>540000</v>
+        <v>486000</v>
       </c>
     </row>
     <row r="16">
@@ -1145,10 +1145,10 @@
         <v>21</v>
       </c>
       <c r="N18" t="n">
-        <v>5758.9597782705</v>
+        <v>5758.9597777778</v>
       </c>
       <c r="O18" t="n">
-        <v>120938.1553436805</v>
+        <v>120938.1553333338</v>
       </c>
       <c r="P18" t="n">
         <v>16900</v>
@@ -1585,10 +1585,10 @@
         <v>18</v>
       </c>
       <c r="N29" t="n">
-        <v>12357.960416667</v>
+        <v>12357.96041958</v>
       </c>
       <c r="O29" t="n">
-        <v>222443.287500006</v>
+        <v>222443.28755244</v>
       </c>
       <c r="P29" t="n">
         <v>15900</v>
@@ -1747,10 +1747,10 @@
         <v>30</v>
       </c>
       <c r="N33" t="n">
-        <v>11491.096565657</v>
+        <v>11491.096989247</v>
       </c>
       <c r="O33" t="n">
-        <v>344732.89696971</v>
+        <v>344732.90967741</v>
       </c>
       <c r="P33" t="n">
         <v>23000</v>
@@ -3132,22 +3132,22 @@
         <v>0</v>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M65" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N65" t="n">
-        <v>16486.408923077</v>
+        <v>16614.210542636</v>
       </c>
       <c r="O65" t="n">
-        <v>247296.133846155</v>
+        <v>232598.947596904</v>
       </c>
       <c r="P65" t="n">
         <v>30500</v>
       </c>
       <c r="Q65" t="n">
-        <v>457500</v>
+        <v>427000</v>
       </c>
     </row>
     <row r="66">
@@ -3180,10 +3180,10 @@
         <v>41</v>
       </c>
       <c r="N66" t="n">
-        <v>15711.966008403</v>
+        <v>15711.965957447</v>
       </c>
       <c r="O66" t="n">
-        <v>644190.606344523</v>
+        <v>644190.604255327</v>
       </c>
       <c r="P66" t="n">
         <v>28500</v>
@@ -3227,10 +3227,10 @@
         <v>24</v>
       </c>
       <c r="N67" t="n">
-        <v>9392.0747222222</v>
+        <v>9392.075000000001</v>
       </c>
       <c r="O67" t="n">
-        <v>225409.7933333328</v>
+        <v>225409.8</v>
       </c>
       <c r="P67" t="n">
         <v>18500</v>
@@ -3902,10 +3902,10 @@
         <v>1</v>
       </c>
       <c r="N83" t="n">
-        <v>56906.802982456</v>
+        <v>56906.803962264</v>
       </c>
       <c r="O83" t="n">
-        <v>56906.802982456</v>
+        <v>56906.803962264</v>
       </c>
       <c r="P83" t="n">
         <v>95900</v>
@@ -5144,22 +5144,22 @@
         <v>0</v>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M112" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N112" t="n">
-        <v>16010.3</v>
+        <v>16128.022794118</v>
       </c>
       <c r="O112" t="n">
-        <v>192123.6</v>
+        <v>177408.250735298</v>
       </c>
       <c r="P112" t="n">
         <v>30500</v>
       </c>
       <c r="Q112" t="n">
-        <v>366000</v>
+        <v>335500</v>
       </c>
     </row>
     <row r="113">
@@ -5183,22 +5183,22 @@
         <v>0</v>
       </c>
       <c r="L113" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M113" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N113" t="n">
-        <v>8046.39</v>
+        <v>8106.4376865672</v>
       </c>
       <c r="O113" t="n">
-        <v>144835.02</v>
+        <v>129703.0029850752</v>
       </c>
       <c r="P113" t="n">
         <v>20900</v>
       </c>
       <c r="Q113" t="n">
-        <v>376200</v>
+        <v>334400</v>
       </c>
     </row>
     <row r="114">
@@ -6423,22 +6423,22 @@
         <v>0</v>
       </c>
       <c r="L141" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M141" t="n">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="N141" t="n">
         <v>2833</v>
       </c>
       <c r="O141" t="n">
-        <v>2065257</v>
+        <v>2056758</v>
       </c>
       <c r="P141" t="n">
         <v>3500</v>
       </c>
       <c r="Q141" t="n">
-        <v>2551500</v>
+        <v>2541000</v>
       </c>
     </row>
     <row r="142">
@@ -6951,22 +6951,22 @@
         <v>0</v>
       </c>
       <c r="L153" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M153" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="N153" t="n">
-        <v>7569</v>
+        <v>7769.0616740088</v>
       </c>
       <c r="O153" t="n">
-        <v>113535</v>
+        <v>69921.55506607919</v>
       </c>
       <c r="P153" t="n">
         <v>12900</v>
       </c>
       <c r="Q153" t="n">
-        <v>193500</v>
+        <v>116100</v>
       </c>
     </row>
     <row r="154">
@@ -7348,22 +7348,22 @@
         <v>0</v>
       </c>
       <c r="L162" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M162" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="N162" t="n">
-        <v>2582.2558569052</v>
+        <v>2582.2558256496</v>
       </c>
       <c r="O162" t="n">
-        <v>80049.93156406119</v>
+        <v>49062.8606873424</v>
       </c>
       <c r="P162" t="n">
         <v>4500</v>
       </c>
       <c r="Q162" t="n">
-        <v>139500</v>
+        <v>85500</v>
       </c>
     </row>
     <row r="163">
@@ -7440,22 +7440,22 @@
         <v>0</v>
       </c>
       <c r="L164" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M164" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="N164" t="n">
-        <v>5216.8961652752</v>
+        <v>5216.8961603854</v>
       </c>
       <c r="O164" t="n">
-        <v>140856.1964624304</v>
+        <v>119988.6116888642</v>
       </c>
       <c r="P164" t="n">
         <v>8500</v>
       </c>
       <c r="Q164" t="n">
-        <v>229500</v>
+        <v>195500</v>
       </c>
     </row>
     <row r="165">
@@ -7486,22 +7486,22 @@
         <v>0</v>
       </c>
       <c r="L165" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M165" t="n">
-        <v>735</v>
+        <v>726</v>
       </c>
       <c r="N165" t="n">
-        <v>3158.8608249792</v>
+        <v>3158.860825504</v>
       </c>
       <c r="O165" t="n">
-        <v>2321762.706359712</v>
+        <v>2293332.959315904</v>
       </c>
       <c r="P165" t="n">
         <v>5600</v>
       </c>
       <c r="Q165" t="n">
-        <v>4116000</v>
+        <v>4065600</v>
       </c>
     </row>
     <row r="166">
@@ -7578,22 +7578,22 @@
         <v>0</v>
       </c>
       <c r="L167" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="M167" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="N167" t="n">
         <v>519</v>
       </c>
       <c r="O167" t="n">
-        <v>14013</v>
+        <v>0</v>
       </c>
       <c r="P167" t="n">
         <v>850</v>
       </c>
       <c r="Q167" t="n">
-        <v>22950</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168">
@@ -7676,10 +7676,10 @@
         <v>683</v>
       </c>
       <c r="N169" t="n">
-        <v>2694.823243369</v>
+        <v>2694.8232244517</v>
       </c>
       <c r="O169" t="n">
-        <v>1840564.275221027</v>
+        <v>1840564.262300511</v>
       </c>
       <c r="P169" t="n">
         <v>4900</v>
@@ -7716,22 +7716,22 @@
         <v>0</v>
       </c>
       <c r="L170" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M170" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N170" t="n">
-        <v>1026.13</v>
+        <v>1032.527319202</v>
       </c>
       <c r="O170" t="n">
-        <v>5130.650000000001</v>
+        <v>0</v>
       </c>
       <c r="P170" t="n">
         <v>1900</v>
       </c>
       <c r="Q170" t="n">
-        <v>9500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171">
@@ -7762,22 +7762,22 @@
         <v>0</v>
       </c>
       <c r="L171" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M171" t="n">
-        <v>1715</v>
+        <v>1705</v>
       </c>
       <c r="N171" t="n">
         <v>156.25</v>
       </c>
       <c r="O171" t="n">
-        <v>267968.75</v>
+        <v>266406.25</v>
       </c>
       <c r="P171" t="n">
         <v>250</v>
       </c>
       <c r="Q171" t="n">
-        <v>428750</v>
+        <v>426250</v>
       </c>
     </row>
     <row r="172">
@@ -7998,10 +7998,10 @@
         <v>12</v>
       </c>
       <c r="N176" t="n">
-        <v>3795.7100071073</v>
+        <v>3795.7100075415</v>
       </c>
       <c r="O176" t="n">
-        <v>45548.5200852876</v>
+        <v>45548.520090498</v>
       </c>
       <c r="P176" t="n">
         <v>6200</v>
@@ -8079,22 +8079,22 @@
         <v>0</v>
       </c>
       <c r="L178" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M178" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N178" t="n">
         <v>2612.77</v>
       </c>
       <c r="O178" t="n">
-        <v>57480.94</v>
+        <v>54868.17</v>
       </c>
       <c r="P178" t="n">
         <v>4900</v>
       </c>
       <c r="Q178" t="n">
-        <v>107800</v>
+        <v>102900</v>
       </c>
     </row>
     <row r="179">
@@ -8217,22 +8217,22 @@
         <v>0</v>
       </c>
       <c r="L181" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M181" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="N181" t="n">
-        <v>4890.9300481348</v>
+        <v>4914.5862998791</v>
       </c>
       <c r="O181" t="n">
-        <v>117382.3211552352</v>
+        <v>78633.3807980656</v>
       </c>
       <c r="P181" t="n">
         <v>8200</v>
       </c>
       <c r="Q181" t="n">
-        <v>196800</v>
+        <v>131200</v>
       </c>
     </row>
     <row r="182">
@@ -8448,22 +8448,22 @@
         <v>0</v>
       </c>
       <c r="L186" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M186" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="N186" t="n">
         <v>3472</v>
       </c>
       <c r="O186" t="n">
-        <v>249984</v>
+        <v>236096</v>
       </c>
       <c r="P186" t="n">
         <v>4800</v>
       </c>
       <c r="Q186" t="n">
-        <v>345600</v>
+        <v>326400</v>
       </c>
     </row>
     <row r="187">
@@ -8627,22 +8627,22 @@
         <v>0</v>
       </c>
       <c r="L190" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M190" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="N190" t="n">
-        <v>7041</v>
+        <v>7095.9541463415</v>
       </c>
       <c r="O190" t="n">
-        <v>288681</v>
+        <v>234166.4868292695</v>
       </c>
       <c r="P190" t="n">
         <v>11500</v>
       </c>
       <c r="Q190" t="n">
-        <v>471500</v>
+        <v>379500</v>
       </c>
     </row>
     <row r="191">
@@ -8673,22 +8673,22 @@
         <v>0</v>
       </c>
       <c r="L191" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M191" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="N191" t="n">
         <v>5667.94</v>
       </c>
       <c r="O191" t="n">
-        <v>102022.92</v>
+        <v>68015.28</v>
       </c>
       <c r="P191" t="n">
         <v>9500</v>
       </c>
       <c r="Q191" t="n">
-        <v>171000</v>
+        <v>114000</v>
       </c>
     </row>
     <row r="192">
@@ -8719,22 +8719,22 @@
         <v>0</v>
       </c>
       <c r="L192" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M192" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="N192" t="n">
-        <v>8012</v>
+        <v>8088.1838351823</v>
       </c>
       <c r="O192" t="n">
-        <v>592888</v>
+        <v>549996.5007923964</v>
       </c>
       <c r="P192" t="n">
         <v>13200</v>
       </c>
       <c r="Q192" t="n">
-        <v>976800</v>
+        <v>897600</v>
       </c>
     </row>
     <row r="193">
@@ -8852,22 +8852,22 @@
         <v>0</v>
       </c>
       <c r="L195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M195" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N195" t="n">
         <v>10716.34</v>
       </c>
       <c r="O195" t="n">
-        <v>96447.06</v>
+        <v>85730.72</v>
       </c>
       <c r="P195" t="n">
         <v>39000</v>
       </c>
       <c r="Q195" t="n">
-        <v>351000</v>
+        <v>312000</v>
       </c>
     </row>
     <row r="196">
@@ -8948,10 +8948,10 @@
         <v>5</v>
       </c>
       <c r="N197" t="n">
-        <v>3594.2540740741</v>
+        <v>3594.2540520446</v>
       </c>
       <c r="O197" t="n">
-        <v>17971.2703703705</v>
+        <v>17971.270260223</v>
       </c>
       <c r="P197" t="n">
         <v>6500</v>
@@ -9083,22 +9083,22 @@
         <v>0</v>
       </c>
       <c r="L200" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M200" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="N200" t="n">
-        <v>4891</v>
+        <v>4913.5912240185</v>
       </c>
       <c r="O200" t="n">
-        <v>132057</v>
+        <v>103185.4157043885</v>
       </c>
       <c r="P200" t="n">
         <v>8200</v>
       </c>
       <c r="Q200" t="n">
-        <v>221400</v>
+        <v>172200</v>
       </c>
     </row>
     <row r="201">
@@ -9494,22 +9494,22 @@
         <v>0</v>
       </c>
       <c r="L209" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M209" t="n">
-        <v>2470</v>
+        <v>2468</v>
       </c>
       <c r="N209" t="n">
-        <v>19098.750004663</v>
+        <v>19098.750004664</v>
       </c>
       <c r="O209" t="n">
-        <v>47173912.51151761</v>
+        <v>47135715.01151076</v>
       </c>
       <c r="P209" t="n">
         <v>15000</v>
       </c>
       <c r="Q209" t="n">
-        <v>37050000</v>
+        <v>37020000</v>
       </c>
     </row>
     <row r="210">
@@ -9546,10 +9546,10 @@
         <v>18</v>
       </c>
       <c r="N210" t="n">
-        <v>12267.650113636</v>
+        <v>12267.649642857</v>
       </c>
       <c r="O210" t="n">
-        <v>220817.702045448</v>
+        <v>220817.693571426</v>
       </c>
       <c r="P210" t="n">
         <v>19900</v>
@@ -9589,22 +9589,22 @@
         <v>0</v>
       </c>
       <c r="L211" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M211" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="N211" t="n">
         <v>1381.75</v>
       </c>
       <c r="O211" t="n">
-        <v>87050.25</v>
+        <v>85668.5</v>
       </c>
       <c r="P211" t="n">
         <v>2500</v>
       </c>
       <c r="Q211" t="n">
-        <v>157500</v>
+        <v>155000</v>
       </c>
     </row>
     <row r="212">
@@ -9944,22 +9944,22 @@
         <v>0</v>
       </c>
       <c r="L219" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M219" t="n">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="N219" t="n">
-        <v>4372.2107886682</v>
+        <v>4374.7024319704</v>
       </c>
       <c r="O219" t="n">
-        <v>253588.2257427556</v>
+        <v>205611.0143026088</v>
       </c>
       <c r="P219" t="n">
         <v>7500</v>
       </c>
       <c r="Q219" t="n">
-        <v>435000</v>
+        <v>352500</v>
       </c>
     </row>
     <row r="220">
@@ -9990,22 +9990,22 @@
         <v>0</v>
       </c>
       <c r="L220" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M220" t="n">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="N220" t="n">
-        <v>1592.5669608416</v>
+        <v>1592.5669555035</v>
       </c>
       <c r="O220" t="n">
-        <v>554213.3023728768</v>
+        <v>551028.166604211</v>
       </c>
       <c r="P220" t="n">
         <v>3900</v>
       </c>
       <c r="Q220" t="n">
-        <v>1357200</v>
+        <v>1349400</v>
       </c>
     </row>
     <row r="221">
@@ -10072,22 +10072,22 @@
         <v>0</v>
       </c>
       <c r="L222" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M222" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="N222" t="n">
         <v>2224.56</v>
       </c>
       <c r="O222" t="n">
-        <v>113452.56</v>
+        <v>104554.32</v>
       </c>
       <c r="P222" t="n">
         <v>3900</v>
       </c>
       <c r="Q222" t="n">
-        <v>198900</v>
+        <v>183300</v>
       </c>
     </row>
     <row r="223">
@@ -10349,22 +10349,22 @@
         <v>0</v>
       </c>
       <c r="L228" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M228" t="n">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="N228" t="n">
         <v>1770.37</v>
       </c>
       <c r="O228" t="n">
-        <v>364696.22</v>
+        <v>361155.48</v>
       </c>
       <c r="P228" t="n">
         <v>3900</v>
       </c>
       <c r="Q228" t="n">
-        <v>803400</v>
+        <v>795600</v>
       </c>
     </row>
     <row r="229">
@@ -11033,22 +11033,22 @@
         <v>0</v>
       </c>
       <c r="L243" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M243" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="N243" t="n">
-        <v>3761.6</v>
+        <v>3788.0590855803</v>
       </c>
       <c r="O243" t="n">
-        <v>109086.4</v>
+        <v>87125.35896834689</v>
       </c>
       <c r="P243" t="n">
         <v>6900</v>
       </c>
       <c r="Q243" t="n">
-        <v>200100</v>
+        <v>158700</v>
       </c>
     </row>
     <row r="244">
@@ -11210,22 +11210,22 @@
         <v>0</v>
       </c>
       <c r="L247" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M247" t="n">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="N247" t="n">
         <v>3751</v>
       </c>
       <c r="O247" t="n">
-        <v>2696969</v>
+        <v>2693218</v>
       </c>
       <c r="P247" t="n">
         <v>6400</v>
       </c>
       <c r="Q247" t="n">
-        <v>4601600</v>
+        <v>4595200</v>
       </c>
     </row>
     <row r="248">
@@ -11305,22 +11305,22 @@
         <v>0</v>
       </c>
       <c r="L249" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M249" t="n">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="N249" t="n">
-        <v>1630.9234624043</v>
+        <v>1630.9234875283</v>
       </c>
       <c r="O249" t="n">
-        <v>94593.5608194494</v>
+        <v>61975.0925260754</v>
       </c>
       <c r="P249" t="n">
         <v>2500</v>
       </c>
       <c r="Q249" t="n">
-        <v>145000</v>
+        <v>95000</v>
       </c>
     </row>
     <row r="250">
@@ -11351,22 +11351,22 @@
         <v>0</v>
       </c>
       <c r="L250" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M250" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="N250" t="n">
-        <v>1550.1935205388</v>
+        <v>1550.1935332762</v>
       </c>
       <c r="O250" t="n">
-        <v>190673.8030262724</v>
+        <v>187573.4175264202</v>
       </c>
       <c r="P250" t="n">
         <v>2500</v>
       </c>
       <c r="Q250" t="n">
-        <v>307500</v>
+        <v>302500</v>
       </c>
     </row>
     <row r="251">
@@ -11397,22 +11397,22 @@
         <v>0</v>
       </c>
       <c r="L251" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M251" t="n">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="N251" t="n">
-        <v>2403.5114869613</v>
+        <v>2403.5115510508</v>
       </c>
       <c r="O251" t="n">
-        <v>1319527.806341754</v>
+        <v>1305106.772220584</v>
       </c>
       <c r="P251" t="n">
         <v>3500</v>
       </c>
       <c r="Q251" t="n">
-        <v>1921500</v>
+        <v>1900500</v>
       </c>
     </row>
     <row r="252">
@@ -12286,22 +12286,22 @@
         <v>0</v>
       </c>
       <c r="L271" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M271" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N271" t="n">
-        <v>5162.2539766082</v>
+        <v>5162.2539411765</v>
       </c>
       <c r="O271" t="n">
-        <v>61947.0477192984</v>
+        <v>56784.7933529415</v>
       </c>
       <c r="P271" t="n">
         <v>8200</v>
       </c>
       <c r="Q271" t="n">
-        <v>98400</v>
+        <v>90200</v>
       </c>
     </row>
     <row r="272">
@@ -12496,22 +12496,22 @@
         <v>0</v>
       </c>
       <c r="L276" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M276" t="n">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="N276" t="n">
-        <v>2517.22</v>
+        <v>2528.6359637188</v>
       </c>
       <c r="O276" t="n">
-        <v>508478.4399999999</v>
+        <v>495612.6488888849</v>
       </c>
       <c r="P276" t="n">
         <v>4200</v>
       </c>
       <c r="Q276" t="n">
-        <v>848400</v>
+        <v>823200</v>
       </c>
     </row>
     <row r="277">
@@ -12537,22 +12537,22 @@
         <v>0</v>
       </c>
       <c r="L277" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M277" t="n">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="N277" t="n">
-        <v>2029.8737350598</v>
+        <v>2029.8737443834</v>
       </c>
       <c r="O277" t="n">
-        <v>458751.4641235148</v>
+        <v>456721.592486265</v>
       </c>
       <c r="P277" t="n">
         <v>3600</v>
       </c>
       <c r="Q277" t="n">
-        <v>813600</v>
+        <v>810000</v>
       </c>
     </row>
     <row r="278">
@@ -12584,10 +12584,10 @@
         <v>19</v>
       </c>
       <c r="N278" t="n">
-        <v>22485.695885714</v>
+        <v>22485.695881007</v>
       </c>
       <c r="O278" t="n">
-        <v>427228.221828566</v>
+        <v>427228.221739133</v>
       </c>
       <c r="P278" t="n">
         <v>36500</v>
@@ -13239,22 +13239,22 @@
         <v>0</v>
       </c>
       <c r="L293" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M293" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="N293" t="n">
-        <v>4285.1954215582</v>
+        <v>4285.1954682454</v>
       </c>
       <c r="O293" t="n">
-        <v>398523.1742049126</v>
+        <v>389952.7876103314</v>
       </c>
       <c r="P293" t="n">
         <v>6900</v>
       </c>
       <c r="Q293" t="n">
-        <v>641700</v>
+        <v>627900</v>
       </c>
     </row>
     <row r="294">
@@ -13544,22 +13544,22 @@
         <v>0</v>
       </c>
       <c r="L300" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M300" t="n">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="N300" t="n">
-        <v>4605.2146660482</v>
+        <v>4657.0557317073</v>
       </c>
       <c r="O300" t="n">
-        <v>331575.4559554704</v>
+        <v>279423.343902438</v>
       </c>
       <c r="P300" t="n">
         <v>7600</v>
       </c>
       <c r="Q300" t="n">
-        <v>547200</v>
+        <v>456000</v>
       </c>
     </row>
     <row r="301">
@@ -13585,22 +13585,22 @@
         <v>0</v>
       </c>
       <c r="L301" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M301" t="n">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="N301" t="n">
-        <v>3591.13</v>
+        <v>3598.612819934</v>
       </c>
       <c r="O301" t="n">
-        <v>183147.63</v>
+        <v>140345.899977426</v>
       </c>
       <c r="P301" t="n">
         <v>6300</v>
       </c>
       <c r="Q301" t="n">
-        <v>321300</v>
+        <v>245700</v>
       </c>
     </row>
     <row r="302">
@@ -13950,25 +13950,25 @@
         <v>35</v>
       </c>
       <c r="K309" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="L309" t="n">
         <v>0</v>
       </c>
       <c r="M309" t="n">
-        <v>35</v>
+        <v>155</v>
       </c>
       <c r="N309" t="n">
         <v>4793.53</v>
       </c>
       <c r="O309" t="n">
-        <v>167773.55</v>
+        <v>742997.1499999999</v>
       </c>
       <c r="P309" t="n">
         <v>7900</v>
       </c>
       <c r="Q309" t="n">
-        <v>276500</v>
+        <v>1224500</v>
       </c>
     </row>
     <row r="310">
@@ -14572,22 +14572,22 @@
         <v>0</v>
       </c>
       <c r="L323" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M323" t="n">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="N323" t="n">
-        <v>1561.0000887728</v>
+        <v>1561.000152391</v>
       </c>
       <c r="O323" t="n">
-        <v>113953.0064804144</v>
+        <v>95221.00929585101</v>
       </c>
       <c r="P323" t="n">
         <v>2900</v>
       </c>
       <c r="Q323" t="n">
-        <v>211700</v>
+        <v>176900</v>
       </c>
     </row>
     <row r="324">
@@ -15152,10 +15152,10 @@
         <v>22</v>
       </c>
       <c r="N336" t="n">
-        <v>548.14724170616</v>
+        <v>548.14722592946</v>
       </c>
       <c r="O336" t="n">
-        <v>12059.23931753552</v>
+        <v>12059.23897044812</v>
       </c>
       <c r="P336" t="n">
         <v>2000</v>
@@ -15794,22 +15794,22 @@
         <v>0</v>
       </c>
       <c r="L350" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M350" t="n">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="N350" t="n">
         <v>5410.72</v>
       </c>
       <c r="O350" t="n">
-        <v>514018.4</v>
+        <v>492375.52</v>
       </c>
       <c r="P350" t="n">
         <v>8700</v>
       </c>
       <c r="Q350" t="n">
-        <v>826500</v>
+        <v>791700</v>
       </c>
     </row>
     <row r="351">
@@ -15932,22 +15932,22 @@
         <v>0</v>
       </c>
       <c r="L353" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M353" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="N353" t="n">
         <v>3254.49</v>
       </c>
       <c r="O353" t="n">
-        <v>484919.01</v>
+        <v>478410.03</v>
       </c>
       <c r="P353" t="n">
         <v>5200</v>
       </c>
       <c r="Q353" t="n">
-        <v>774800</v>
+        <v>764400</v>
       </c>
     </row>
     <row r="354">
@@ -15978,22 +15978,22 @@
         <v>0</v>
       </c>
       <c r="L354" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M354" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="N354" t="n">
-        <v>5218.1705412054</v>
+        <v>5218.1705479452</v>
       </c>
       <c r="O354" t="n">
-        <v>474853.5192496914</v>
+        <v>464417.1787671229</v>
       </c>
       <c r="P354" t="n">
         <v>8500</v>
       </c>
       <c r="Q354" t="n">
-        <v>773500</v>
+        <v>756500</v>
       </c>
     </row>
     <row r="355">
@@ -16024,22 +16024,22 @@
         <v>0</v>
       </c>
       <c r="L355" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M355" t="n">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="N355" t="n">
-        <v>1595.0093958665</v>
+        <v>1595.0093800979</v>
       </c>
       <c r="O355" t="n">
-        <v>183426.0805246475</v>
+        <v>167475.9849102795</v>
       </c>
       <c r="P355" t="n">
         <v>2600</v>
       </c>
       <c r="Q355" t="n">
-        <v>299000</v>
+        <v>273000</v>
       </c>
     </row>
     <row r="356">
@@ -16723,10 +16723,10 @@
         <v>99</v>
       </c>
       <c r="N370" t="n">
-        <v>1778.4725978277</v>
+        <v>1778.4726172988</v>
       </c>
       <c r="O370" t="n">
-        <v>176068.7871849423</v>
+        <v>176068.7891125812</v>
       </c>
       <c r="P370" t="n">
         <v>4900</v>
@@ -18200,22 +18200,22 @@
         <v>0</v>
       </c>
       <c r="L402" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M402" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="N402" t="n">
         <v>4917</v>
       </c>
       <c r="O402" t="n">
-        <v>63921</v>
+        <v>34419</v>
       </c>
       <c r="P402" t="n">
         <v>8600</v>
       </c>
       <c r="Q402" t="n">
-        <v>111800</v>
+        <v>60200</v>
       </c>
     </row>
     <row r="403">
@@ -19178,10 +19178,10 @@
         <v>59</v>
       </c>
       <c r="N423" t="n">
-        <v>2252.2966541823</v>
+        <v>2252.2966708385</v>
       </c>
       <c r="O423" t="n">
-        <v>132885.5025967557</v>
+        <v>132885.5035794715</v>
       </c>
       <c r="P423" t="n">
         <v>3900</v>
@@ -19365,10 +19365,10 @@
         <v>247</v>
       </c>
       <c r="N427" t="n">
-        <v>2328.1187258454</v>
+        <v>2328.1187254606</v>
       </c>
       <c r="O427" t="n">
-        <v>575045.3252838139</v>
+        <v>575045.3251887682</v>
       </c>
       <c r="P427" t="n">
         <v>4500</v>
@@ -19589,22 +19589,22 @@
         <v>0</v>
       </c>
       <c r="L432" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M432" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="N432" t="n">
         <v>3519</v>
       </c>
       <c r="O432" t="n">
-        <v>380052</v>
+        <v>365976</v>
       </c>
       <c r="P432" t="n">
         <v>5900</v>
       </c>
       <c r="Q432" t="n">
-        <v>637200</v>
+        <v>613600</v>
       </c>
     </row>
     <row r="433">
@@ -20285,10 +20285,10 @@
         <v>98</v>
       </c>
       <c r="N447" t="n">
-        <v>3903.7364457831</v>
+        <v>3903.7364581763</v>
       </c>
       <c r="O447" t="n">
-        <v>382566.1716867438</v>
+        <v>382566.1729012774</v>
       </c>
       <c r="P447" t="n">
         <v>7500</v>
@@ -20913,22 +20913,22 @@
         <v>0</v>
       </c>
       <c r="L461" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M461" t="n">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="N461" t="n">
-        <v>5869.1726950355</v>
+        <v>5869.172680203</v>
       </c>
       <c r="O461" t="n">
-        <v>1203180.402482277</v>
+        <v>1191442.054081209</v>
       </c>
       <c r="P461" t="n">
         <v>9500</v>
       </c>
       <c r="Q461" t="n">
-        <v>1947500</v>
+        <v>1928500</v>
       </c>
     </row>
     <row r="462">
@@ -21051,22 +21051,22 @@
         <v>0</v>
       </c>
       <c r="L464" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M464" t="n">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="N464" t="n">
         <v>5772</v>
       </c>
       <c r="O464" t="n">
-        <v>975468</v>
+        <v>911976</v>
       </c>
       <c r="P464" t="n">
         <v>9900</v>
       </c>
       <c r="Q464" t="n">
-        <v>1673100</v>
+        <v>1564200</v>
       </c>
     </row>
     <row r="465">
@@ -21097,22 +21097,22 @@
         <v>0</v>
       </c>
       <c r="L465" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M465" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="N465" t="n">
-        <v>8637</v>
+        <v>9422.1818181818</v>
       </c>
       <c r="O465" t="n">
-        <v>112281</v>
+        <v>84799.63636363619</v>
       </c>
       <c r="P465" t="n">
         <v>14500</v>
       </c>
       <c r="Q465" t="n">
-        <v>188500</v>
+        <v>130500</v>
       </c>
     </row>
     <row r="466">
@@ -21143,22 +21143,22 @@
         <v>0</v>
       </c>
       <c r="L466" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M466" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="N466" t="n">
-        <v>6645</v>
+        <v>6666.7987971569</v>
       </c>
       <c r="O466" t="n">
-        <v>205995</v>
+        <v>126669.1771459811</v>
       </c>
       <c r="P466" t="n">
         <v>10900</v>
       </c>
       <c r="Q466" t="n">
-        <v>337900</v>
+        <v>207100</v>
       </c>
     </row>
     <row r="467">
@@ -21327,22 +21327,22 @@
         <v>0</v>
       </c>
       <c r="L470" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M470" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="N470" t="n">
-        <v>7562</v>
+        <v>7693.5130434783</v>
       </c>
       <c r="O470" t="n">
-        <v>189050</v>
+        <v>161563.7739130443</v>
       </c>
       <c r="P470" t="n">
         <v>12900</v>
       </c>
       <c r="Q470" t="n">
-        <v>322500</v>
+        <v>270900</v>
       </c>
     </row>
     <row r="471">
@@ -21373,22 +21373,22 @@
         <v>0</v>
       </c>
       <c r="L471" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M471" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="N471" t="n">
         <v>3898</v>
       </c>
       <c r="O471" t="n">
-        <v>54572</v>
+        <v>0</v>
       </c>
       <c r="P471" t="n">
         <v>6900</v>
       </c>
       <c r="Q471" t="n">
-        <v>96600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="472">
@@ -21557,22 +21557,22 @@
         <v>0</v>
       </c>
       <c r="L475" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M475" t="n">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="N475" t="n">
         <v>5682</v>
       </c>
       <c r="O475" t="n">
-        <v>517062</v>
+        <v>494334</v>
       </c>
       <c r="P475" t="n">
         <v>9900</v>
       </c>
       <c r="Q475" t="n">
-        <v>900900</v>
+        <v>861300</v>
       </c>
     </row>
     <row r="476">
@@ -22245,22 +22245,22 @@
         <v>0</v>
       </c>
       <c r="L490" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M490" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="N490" t="n">
         <v>59834</v>
       </c>
       <c r="O490" t="n">
-        <v>2154024</v>
+        <v>1974522</v>
       </c>
       <c r="P490" t="n">
         <v>7900</v>
       </c>
       <c r="Q490" t="n">
-        <v>284400</v>
+        <v>260700</v>
       </c>
     </row>
     <row r="491">
@@ -22800,22 +22800,22 @@
         <v>0</v>
       </c>
       <c r="L502" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M502" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N502" t="n">
         <v>40073</v>
       </c>
       <c r="O502" t="n">
-        <v>1683066</v>
+        <v>1642993</v>
       </c>
       <c r="P502" t="n">
         <v>64900</v>
       </c>
       <c r="Q502" t="n">
-        <v>2725800</v>
+        <v>2660900</v>
       </c>
     </row>
     <row r="503">
@@ -23076,22 +23076,22 @@
         <v>0</v>
       </c>
       <c r="L508" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="M508" t="n">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="N508" t="n">
         <v>1326</v>
       </c>
       <c r="O508" t="n">
-        <v>78234</v>
+        <v>33150</v>
       </c>
       <c r="P508" t="n">
         <v>2500</v>
       </c>
       <c r="Q508" t="n">
-        <v>147500</v>
+        <v>62500</v>
       </c>
     </row>
     <row r="509">
@@ -23907,22 +23907,22 @@
         <v>0</v>
       </c>
       <c r="L526" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M526" t="n">
-        <v>435</v>
+        <v>411</v>
       </c>
       <c r="N526" t="n">
-        <v>2458.5132504039</v>
+        <v>2477.7391560769</v>
       </c>
       <c r="O526" t="n">
-        <v>1069453.263925696</v>
+        <v>1018350.793147606</v>
       </c>
       <c r="P526" t="n">
         <v>3500</v>
       </c>
       <c r="Q526" t="n">
-        <v>1522500</v>
+        <v>1438500</v>
       </c>
     </row>
     <row r="527">
@@ -23953,22 +23953,22 @@
         <v>0</v>
       </c>
       <c r="L527" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M527" t="n">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="N527" t="n">
-        <v>1907.3938009479</v>
+        <v>1951.7948205626</v>
       </c>
       <c r="O527" t="n">
-        <v>183109.8048909984</v>
+        <v>140529.2270805072</v>
       </c>
       <c r="P527" t="n">
         <v>2500</v>
       </c>
       <c r="Q527" t="n">
-        <v>240000</v>
+        <v>180000</v>
       </c>
     </row>
     <row r="528">
@@ -23999,22 +23999,22 @@
         <v>0</v>
       </c>
       <c r="L528" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M528" t="n">
-        <v>183</v>
+        <v>159</v>
       </c>
       <c r="N528" t="n">
-        <v>1771.0905981795</v>
+        <v>1799.166010568</v>
       </c>
       <c r="O528" t="n">
-        <v>324109.5794668485</v>
+        <v>286067.395680312</v>
       </c>
       <c r="P528" t="n">
         <v>2500</v>
       </c>
       <c r="Q528" t="n">
-        <v>457500</v>
+        <v>397500</v>
       </c>
     </row>
     <row r="529">
@@ -24051,10 +24051,10 @@
         <v>441</v>
       </c>
       <c r="N529" t="n">
-        <v>2079.3840473807</v>
+        <v>2079.3840374332</v>
       </c>
       <c r="O529" t="n">
-        <v>917008.3648948887</v>
+        <v>917008.3605080411</v>
       </c>
       <c r="P529" t="n">
         <v>2900</v>
@@ -24091,22 +24091,22 @@
         <v>0</v>
       </c>
       <c r="L530" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M530" t="n">
-        <v>307</v>
+        <v>283</v>
       </c>
       <c r="N530" t="n">
-        <v>1803.0155591997</v>
+        <v>1817.3204760331</v>
       </c>
       <c r="O530" t="n">
-        <v>553525.7766743079</v>
+        <v>514301.6947173673</v>
       </c>
       <c r="P530" t="n">
         <v>2500</v>
       </c>
       <c r="Q530" t="n">
-        <v>767500</v>
+        <v>707500</v>
       </c>
     </row>
     <row r="531">
@@ -24143,10 +24143,10 @@
         <v>96</v>
       </c>
       <c r="N531" t="n">
-        <v>3306.5951935915</v>
+        <v>3306.5951807229</v>
       </c>
       <c r="O531" t="n">
-        <v>317433.138584784</v>
+        <v>317433.1373493984</v>
       </c>
       <c r="P531" t="n">
         <v>4900</v>
@@ -24183,22 +24183,22 @@
         <v>0</v>
       </c>
       <c r="L532" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M532" t="n">
-        <v>559</v>
+        <v>535</v>
       </c>
       <c r="N532" t="n">
-        <v>2122.1639198011</v>
+        <v>2138.1701634192</v>
       </c>
       <c r="O532" t="n">
-        <v>1186289.631168815</v>
+        <v>1143921.037429272</v>
       </c>
       <c r="P532" t="n">
         <v>2900</v>
       </c>
       <c r="Q532" t="n">
-        <v>1621100</v>
+        <v>1551500</v>
       </c>
     </row>
     <row r="533">
@@ -24229,22 +24229,22 @@
         <v>0</v>
       </c>
       <c r="L533" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M533" t="n">
-        <v>299</v>
+        <v>275</v>
       </c>
       <c r="N533" t="n">
-        <v>2108.7914267016</v>
+        <v>2142.8043145161</v>
       </c>
       <c r="O533" t="n">
-        <v>630528.6365837784</v>
+        <v>589271.1864919275</v>
       </c>
       <c r="P533" t="n">
         <v>2900</v>
       </c>
       <c r="Q533" t="n">
-        <v>867100</v>
+        <v>797500</v>
       </c>
     </row>
     <row r="534">
@@ -24275,22 +24275,22 @@
         <v>0</v>
       </c>
       <c r="L534" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M534" t="n">
-        <v>317</v>
+        <v>293</v>
       </c>
       <c r="N534" t="n">
-        <v>2056.0834183673</v>
+        <v>2056.0833654773</v>
       </c>
       <c r="O534" t="n">
-        <v>651778.4436224342</v>
+        <v>602432.4260848489</v>
       </c>
       <c r="P534" t="n">
         <v>2900</v>
       </c>
       <c r="Q534" t="n">
-        <v>919300</v>
+        <v>849700</v>
       </c>
     </row>
     <row r="535">
@@ -24321,22 +24321,22 @@
         <v>0</v>
       </c>
       <c r="L535" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M535" t="n">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="N535" t="n">
-        <v>3224.5685238095</v>
+        <v>3224.5685400763</v>
       </c>
       <c r="O535" t="n">
-        <v>1073781.318428564</v>
+        <v>1060883.049685103</v>
       </c>
       <c r="P535" t="n">
         <v>4500</v>
       </c>
       <c r="Q535" t="n">
-        <v>1498500</v>
+        <v>1480500</v>
       </c>
     </row>
     <row r="536">
@@ -24367,22 +24367,22 @@
         <v>0</v>
       </c>
       <c r="L536" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M536" t="n">
-        <v>285</v>
+        <v>261</v>
       </c>
       <c r="N536" t="n">
-        <v>1655.9309666884</v>
+        <v>1669.0127123107</v>
       </c>
       <c r="O536" t="n">
-        <v>471940.325506194</v>
+        <v>435612.3179130927</v>
       </c>
       <c r="P536" t="n">
         <v>2500</v>
       </c>
       <c r="Q536" t="n">
-        <v>712500</v>
+        <v>652500</v>
       </c>
     </row>
     <row r="537">
@@ -24551,22 +24551,22 @@
         <v>0</v>
       </c>
       <c r="L540" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M540" t="n">
-        <v>187</v>
+        <v>169</v>
       </c>
       <c r="N540" t="n">
-        <v>1592.2773416667</v>
+        <v>1592.2776475694</v>
       </c>
       <c r="O540" t="n">
-        <v>297755.8628916729</v>
+        <v>269094.9224392286</v>
       </c>
       <c r="P540" t="n">
         <v>2500</v>
       </c>
       <c r="Q540" t="n">
-        <v>467500</v>
+        <v>422500</v>
       </c>
     </row>
     <row r="541">
@@ -24647,10 +24647,10 @@
         <v>41</v>
       </c>
       <c r="N542" t="n">
-        <v>1668.628045977</v>
+        <v>1668.6281268012</v>
       </c>
       <c r="O542" t="n">
-        <v>68413.749885057</v>
+        <v>68413.7531988492</v>
       </c>
       <c r="P542" t="n">
         <v>2500</v>
@@ -24687,22 +24687,22 @@
         <v>0</v>
       </c>
       <c r="L543" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M543" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="N543" t="n">
-        <v>2546.9843873518</v>
+        <v>2609.1059349593</v>
       </c>
       <c r="O543" t="n">
-        <v>89144.453557313</v>
+        <v>54791.22463414531</v>
       </c>
       <c r="P543" t="n">
         <v>3900</v>
       </c>
       <c r="Q543" t="n">
-        <v>136500</v>
+        <v>81900</v>
       </c>
     </row>
     <row r="544">
@@ -24733,22 +24733,22 @@
         <v>0</v>
       </c>
       <c r="L544" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="M544" t="n">
-        <v>966</v>
+        <v>947</v>
       </c>
       <c r="N544" t="n">
-        <v>1259.2745258911</v>
+        <v>1264.6608869878</v>
       </c>
       <c r="O544" t="n">
-        <v>1216459.192010803</v>
+        <v>1197633.859977447</v>
       </c>
       <c r="P544" t="n">
         <v>1900</v>
       </c>
       <c r="Q544" t="n">
-        <v>1835400</v>
+        <v>1799300</v>
       </c>
     </row>
     <row r="545">
@@ -24912,22 +24912,22 @@
         <v>0</v>
       </c>
       <c r="L548" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M548" t="n">
-        <v>489</v>
+        <v>478</v>
       </c>
       <c r="N548" t="n">
         <v>1801</v>
       </c>
       <c r="O548" t="n">
-        <v>880689</v>
+        <v>860878</v>
       </c>
       <c r="P548" t="n">
         <v>2900</v>
       </c>
       <c r="Q548" t="n">
-        <v>1418100</v>
+        <v>1386200</v>
       </c>
     </row>
     <row r="549">
@@ -25290,22 +25290,22 @@
         <v>0</v>
       </c>
       <c r="L556" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M556" t="n">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="N556" t="n">
         <v>8945.379999999999</v>
       </c>
       <c r="O556" t="n">
-        <v>1010827.94</v>
+        <v>966101.0399999999</v>
       </c>
       <c r="P556" t="n">
         <v>14900</v>
       </c>
       <c r="Q556" t="n">
-        <v>1683700</v>
+        <v>1609200</v>
       </c>
     </row>
     <row r="557">
@@ -26039,22 +26039,22 @@
         <v>0</v>
       </c>
       <c r="L572" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M572" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="N572" t="n">
-        <v>1690.8700090909</v>
+        <v>1690.870009095</v>
       </c>
       <c r="O572" t="n">
-        <v>304356.601636362</v>
+        <v>302665.731628005</v>
       </c>
       <c r="P572" t="n">
         <v>3000</v>
       </c>
       <c r="Q572" t="n">
-        <v>540000</v>
+        <v>537000</v>
       </c>
     </row>
     <row r="573">
@@ -26269,22 +26269,22 @@
         <v>0</v>
       </c>
       <c r="L577" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M577" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N577" t="n">
-        <v>3907.5003292181</v>
+        <v>3907.5003305785</v>
       </c>
       <c r="O577" t="n">
-        <v>105502.5088888887</v>
+        <v>101595.008595041</v>
       </c>
       <c r="P577" t="n">
         <v>3900</v>
       </c>
       <c r="Q577" t="n">
-        <v>105300</v>
+        <v>101400</v>
       </c>
     </row>
     <row r="578">
@@ -26680,22 +26680,22 @@
         <v>0</v>
       </c>
       <c r="L586" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M586" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="N586" t="n">
         <v>4243.87</v>
       </c>
       <c r="O586" t="n">
-        <v>106096.75</v>
+        <v>97609.00999999999</v>
       </c>
       <c r="P586" t="n">
         <v>5900</v>
       </c>
       <c r="Q586" t="n">
-        <v>147500</v>
+        <v>135700</v>
       </c>
     </row>
     <row r="587">
@@ -26822,22 +26822,22 @@
         <v>0</v>
       </c>
       <c r="L589" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="M589" t="n">
-        <v>1962</v>
+        <v>1921</v>
       </c>
       <c r="N589" t="n">
-        <v>517.28908220781</v>
+        <v>517.28922545101</v>
       </c>
       <c r="O589" t="n">
-        <v>1014921.179291723</v>
+        <v>993712.6020913902</v>
       </c>
       <c r="P589" t="n">
         <v>900</v>
       </c>
       <c r="Q589" t="n">
-        <v>1765800</v>
+        <v>1728900</v>
       </c>
     </row>
     <row r="590">
@@ -27053,22 +27053,22 @@
         <v>0</v>
       </c>
       <c r="L594" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M594" t="n">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="N594" t="n">
-        <v>3110.842321894</v>
+        <v>3110.8421999117</v>
       </c>
       <c r="O594" t="n">
-        <v>970582.8044309281</v>
+        <v>967471.9241725387</v>
       </c>
       <c r="P594" t="n">
         <v>4500</v>
       </c>
       <c r="Q594" t="n">
-        <v>1404000</v>
+        <v>1399500</v>
       </c>
     </row>
     <row r="595">
@@ -27097,22 +27097,22 @@
         <v>0</v>
       </c>
       <c r="L595" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="M595" t="n">
-        <v>1633</v>
+        <v>1610</v>
       </c>
       <c r="N595" t="n">
-        <v>703.79521051815</v>
+        <v>703.79520622865</v>
       </c>
       <c r="O595" t="n">
-        <v>1149297.578776139</v>
+        <v>1133110.282028127</v>
       </c>
       <c r="P595" t="n">
         <v>900</v>
       </c>
       <c r="Q595" t="n">
-        <v>1469700</v>
+        <v>1449000</v>
       </c>
     </row>
     <row r="596">
@@ -27385,22 +27385,22 @@
         <v>0</v>
       </c>
       <c r="L601" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M601" t="n">
-        <v>339</v>
+        <v>323</v>
       </c>
       <c r="N601" t="n">
-        <v>1595.513125523</v>
+        <v>1595.5130117944</v>
       </c>
       <c r="O601" t="n">
-        <v>540878.949552297</v>
+        <v>515350.7028095912</v>
       </c>
       <c r="P601" t="n">
         <v>2500</v>
       </c>
       <c r="Q601" t="n">
-        <v>847500</v>
+        <v>807500</v>
       </c>
     </row>
     <row r="602">
@@ -29508,10 +29508,10 @@
         <v>61</v>
       </c>
       <c r="N645" t="n">
-        <v>875.69016</v>
+        <v>875.69016806723</v>
       </c>
       <c r="O645" t="n">
-        <v>53417.09976</v>
+        <v>53417.10025210103</v>
       </c>
       <c r="P645" t="n">
         <v>4500</v>
@@ -31367,22 +31367,22 @@
         <v>0</v>
       </c>
       <c r="L684" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M684" t="n">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="N684" t="n">
         <v>711.48</v>
       </c>
       <c r="O684" t="n">
-        <v>78974.28</v>
+        <v>70436.52</v>
       </c>
       <c r="P684" t="n">
         <v>2500</v>
       </c>
       <c r="Q684" t="n">
-        <v>277500</v>
+        <v>247500</v>
       </c>
     </row>
     <row r="685">
@@ -31752,10 +31752,10 @@
         <v>6</v>
       </c>
       <c r="N692" t="n">
-        <v>15033.816086957</v>
+        <v>15033.815909091</v>
       </c>
       <c r="O692" t="n">
-        <v>90202.896521742</v>
+        <v>90202.895454546</v>
       </c>
       <c r="P692" t="n">
         <v>19900</v>
@@ -31942,10 +31942,10 @@
         <v>13</v>
       </c>
       <c r="N696" t="n">
-        <v>44113.603820225</v>
+        <v>44113.603841808</v>
       </c>
       <c r="O696" t="n">
-        <v>573476.849662925</v>
+        <v>573476.849943504</v>
       </c>
       <c r="P696" t="n">
         <v>71900</v>
@@ -32031,22 +32031,22 @@
         <v>0</v>
       </c>
       <c r="L698" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M698" t="n">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="N698" t="n">
         <v>1338.14</v>
       </c>
       <c r="O698" t="n">
-        <v>207411.7</v>
+        <v>204735.42</v>
       </c>
       <c r="P698" t="n">
         <v>2500</v>
       </c>
       <c r="Q698" t="n">
-        <v>387500</v>
+        <v>382500</v>
       </c>
     </row>
     <row r="699">
@@ -32490,22 +32490,22 @@
         <v>0</v>
       </c>
       <c r="L708" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M708" t="n">
-        <v>588</v>
+        <v>576</v>
       </c>
       <c r="N708" t="n">
-        <v>1176.57</v>
+        <v>1179.3131202642</v>
       </c>
       <c r="O708" t="n">
-        <v>691823.1599999999</v>
+        <v>679284.3572721792</v>
       </c>
       <c r="P708" t="n">
         <v>1900</v>
       </c>
       <c r="Q708" t="n">
-        <v>1117200</v>
+        <v>1094400</v>
       </c>
     </row>
     <row r="709">
@@ -32915,22 +32915,22 @@
         <v>0</v>
       </c>
       <c r="L717" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M717" t="n">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="N717" t="n">
         <v>5077</v>
       </c>
       <c r="O717" t="n">
-        <v>695549</v>
+        <v>685395</v>
       </c>
       <c r="P717" t="n">
         <v>8500</v>
       </c>
       <c r="Q717" t="n">
-        <v>1164500</v>
+        <v>1147500</v>
       </c>
     </row>
     <row r="718">
@@ -33013,10 +33013,10 @@
         <v>518</v>
       </c>
       <c r="N719" t="n">
-        <v>705.52800453515</v>
+        <v>705.5279984837</v>
       </c>
       <c r="O719" t="n">
-        <v>365463.5063492077</v>
+        <v>365463.5032145566</v>
       </c>
       <c r="P719" t="n">
         <v>1500</v>
@@ -33191,22 +33191,22 @@
         <v>0</v>
       </c>
       <c r="L723" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M723" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N723" t="n">
         <v>20700</v>
       </c>
       <c r="O723" t="n">
-        <v>372600</v>
+        <v>351900</v>
       </c>
       <c r="P723" t="n">
         <v>25900</v>
       </c>
       <c r="Q723" t="n">
-        <v>466200</v>
+        <v>440300</v>
       </c>
     </row>
     <row r="724">
@@ -33329,22 +33329,22 @@
         <v>0</v>
       </c>
       <c r="L726" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M726" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="N726" t="n">
         <v>5850</v>
       </c>
       <c r="O726" t="n">
-        <v>210600</v>
+        <v>175500</v>
       </c>
       <c r="P726" t="n">
         <v>7900</v>
       </c>
       <c r="Q726" t="n">
-        <v>284400</v>
+        <v>237000</v>
       </c>
     </row>
     <row r="727">
@@ -33421,22 +33421,22 @@
         <v>0</v>
       </c>
       <c r="L728" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M728" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N728" t="n">
         <v>5220</v>
       </c>
       <c r="O728" t="n">
-        <v>292320</v>
+        <v>287100</v>
       </c>
       <c r="P728" t="n">
         <v>7500</v>
       </c>
       <c r="Q728" t="n">
-        <v>420000</v>
+        <v>412500</v>
       </c>
     </row>
     <row r="729">
@@ -33467,22 +33467,22 @@
         <v>0</v>
       </c>
       <c r="L729" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M729" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="N729" t="n">
         <v>7650</v>
       </c>
       <c r="O729" t="n">
-        <v>321300</v>
+        <v>298350</v>
       </c>
       <c r="P729" t="n">
         <v>9900</v>
       </c>
       <c r="Q729" t="n">
-        <v>415800</v>
+        <v>386100</v>
       </c>
     </row>
     <row r="730">
@@ -33743,22 +33743,22 @@
         <v>0</v>
       </c>
       <c r="L735" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M735" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="N735" t="n">
         <v>9000</v>
       </c>
       <c r="O735" t="n">
-        <v>387000</v>
+        <v>360000</v>
       </c>
       <c r="P735" t="n">
         <v>11500</v>
       </c>
       <c r="Q735" t="n">
-        <v>494500</v>
+        <v>460000</v>
       </c>
     </row>
     <row r="736">
@@ -33973,22 +33973,22 @@
         <v>0</v>
       </c>
       <c r="L740" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M740" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N740" t="n">
         <v>25200</v>
       </c>
       <c r="O740" t="n">
-        <v>176400</v>
+        <v>151200</v>
       </c>
       <c r="P740" t="n">
         <v>31900</v>
       </c>
       <c r="Q740" t="n">
-        <v>223300</v>
+        <v>191400</v>
       </c>
     </row>
     <row r="741">
@@ -34019,22 +34019,22 @@
         <v>0</v>
       </c>
       <c r="L741" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M741" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N741" t="n">
         <v>22500</v>
       </c>
       <c r="O741" t="n">
-        <v>45000</v>
+        <v>22500</v>
       </c>
       <c r="P741" t="n">
         <v>28900</v>
       </c>
       <c r="Q741" t="n">
-        <v>57800</v>
+        <v>28900</v>
       </c>
     </row>
     <row r="742">
@@ -34479,22 +34479,22 @@
         <v>0</v>
       </c>
       <c r="L751" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M751" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N751" t="n">
-        <v>40500</v>
+        <v>0</v>
       </c>
       <c r="O751" t="n">
-        <v>40500</v>
+        <v>0</v>
       </c>
       <c r="P751" t="n">
         <v>50900</v>
       </c>
       <c r="Q751" t="n">
-        <v>50900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="752">
@@ -34525,22 +34525,22 @@
         <v>0</v>
       </c>
       <c r="L752" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M752" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N752" t="n">
         <v>54000</v>
       </c>
       <c r="O752" t="n">
-        <v>162000</v>
+        <v>108000</v>
       </c>
       <c r="P752" t="n">
         <v>69900</v>
       </c>
       <c r="Q752" t="n">
-        <v>209700</v>
+        <v>139800</v>
       </c>
     </row>
     <row r="753">
@@ -34663,22 +34663,22 @@
         <v>0</v>
       </c>
       <c r="L755" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M755" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="N755" t="n">
-        <v>10335.44</v>
+        <v>12402.528</v>
       </c>
       <c r="O755" t="n">
-        <v>217044.24</v>
+        <v>210842.976</v>
       </c>
       <c r="P755" t="n">
         <v>10900</v>
       </c>
       <c r="Q755" t="n">
-        <v>228900</v>
+        <v>185300</v>
       </c>
     </row>
     <row r="756">
@@ -35031,22 +35031,22 @@
         <v>0</v>
       </c>
       <c r="L763" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M763" t="n">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="N763" t="n">
         <v>15224</v>
       </c>
       <c r="O763" t="n">
-        <v>1644192</v>
+        <v>1461504</v>
       </c>
       <c r="P763" t="n">
         <v>19000</v>
       </c>
       <c r="Q763" t="n">
-        <v>2052000</v>
+        <v>1824000</v>
       </c>
     </row>
     <row r="764">
@@ -35077,22 +35077,22 @@
         <v>0</v>
       </c>
       <c r="L764" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M764" t="n">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="N764" t="n">
         <v>15224</v>
       </c>
       <c r="O764" t="n">
-        <v>1644192</v>
+        <v>1446280</v>
       </c>
       <c r="P764" t="n">
         <v>19000</v>
       </c>
       <c r="Q764" t="n">
-        <v>2052000</v>
+        <v>1805000</v>
       </c>
     </row>
     <row r="765">
@@ -35169,22 +35169,22 @@
         <v>0</v>
       </c>
       <c r="L766" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M766" t="n">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="N766" t="n">
         <v>6336</v>
       </c>
       <c r="O766" t="n">
-        <v>912384</v>
+        <v>823680</v>
       </c>
       <c r="P766" t="n">
         <v>7500</v>
       </c>
       <c r="Q766" t="n">
-        <v>1080000</v>
+        <v>975000</v>
       </c>
     </row>
     <row r="767">
@@ -35215,22 +35215,22 @@
         <v>0</v>
       </c>
       <c r="L767" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M767" t="n">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="N767" t="n">
         <v>5280</v>
       </c>
       <c r="O767" t="n">
-        <v>887040</v>
+        <v>802560</v>
       </c>
       <c r="P767" t="n">
         <v>6900</v>
       </c>
       <c r="Q767" t="n">
-        <v>1159200</v>
+        <v>1048800</v>
       </c>
     </row>
     <row r="768">
@@ -35261,22 +35261,22 @@
         <v>0</v>
       </c>
       <c r="L768" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M768" t="n">
-        <v>720</v>
+        <v>696</v>
       </c>
       <c r="N768" t="n">
         <v>2376</v>
       </c>
       <c r="O768" t="n">
-        <v>1710720</v>
+        <v>1653696</v>
       </c>
       <c r="P768" t="n">
         <v>3000</v>
       </c>
       <c r="Q768" t="n">
-        <v>2160000</v>
+        <v>2088000</v>
       </c>
     </row>
     <row r="769">
@@ -35307,22 +35307,22 @@
         <v>0</v>
       </c>
       <c r="L769" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M769" t="n">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="N769" t="n">
         <v>1584</v>
       </c>
       <c r="O769" t="n">
-        <v>456192</v>
+        <v>437184</v>
       </c>
       <c r="P769" t="n">
         <v>2000</v>
       </c>
       <c r="Q769" t="n">
-        <v>576000</v>
+        <v>552000</v>
       </c>
     </row>
     <row r="770">
@@ -35353,22 +35353,22 @@
         <v>0</v>
       </c>
       <c r="L770" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M770" t="n">
-        <v>720</v>
+        <v>714</v>
       </c>
       <c r="N770" t="n">
         <v>1584</v>
       </c>
       <c r="O770" t="n">
-        <v>1140480</v>
+        <v>1130976</v>
       </c>
       <c r="P770" t="n">
         <v>2000</v>
       </c>
       <c r="Q770" t="n">
-        <v>1440000</v>
+        <v>1428000</v>
       </c>
     </row>
     <row r="771">
@@ -35445,22 +35445,22 @@
         <v>0</v>
       </c>
       <c r="L772" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M772" t="n">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="N772" t="n">
         <v>3872</v>
       </c>
       <c r="O772" t="n">
-        <v>743424</v>
+        <v>735680</v>
       </c>
       <c r="P772" t="n">
         <v>4900</v>
       </c>
       <c r="Q772" t="n">
-        <v>940800</v>
+        <v>931000</v>
       </c>
     </row>
     <row r="773">
@@ -35491,22 +35491,22 @@
         <v>0</v>
       </c>
       <c r="L773" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M773" t="n">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="N773" t="n">
         <v>3872</v>
       </c>
       <c r="O773" t="n">
-        <v>1115136</v>
+        <v>1068672</v>
       </c>
       <c r="P773" t="n">
         <v>4900</v>
       </c>
       <c r="Q773" t="n">
-        <v>1411200</v>
+        <v>1352400</v>
       </c>
     </row>
     <row r="774">
@@ -35537,22 +35537,22 @@
         <v>0</v>
       </c>
       <c r="L774" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M774" t="n">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="N774" t="n">
         <v>6160</v>
       </c>
       <c r="O774" t="n">
-        <v>1330560</v>
+        <v>1305920</v>
       </c>
       <c r="P774" t="n">
         <v>7900</v>
       </c>
       <c r="Q774" t="n">
-        <v>1706400</v>
+        <v>1674800</v>
       </c>
     </row>
     <row r="775">
@@ -35675,22 +35675,22 @@
         <v>0</v>
       </c>
       <c r="L777" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M777" t="n">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="N777" t="n">
         <v>6160</v>
       </c>
       <c r="O777" t="n">
-        <v>591360</v>
+        <v>517440</v>
       </c>
       <c r="P777" t="n">
         <v>7900</v>
       </c>
       <c r="Q777" t="n">
-        <v>758400</v>
+        <v>663600</v>
       </c>
     </row>
     <row r="778">
@@ -35721,22 +35721,22 @@
         <v>0</v>
       </c>
       <c r="L778" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M778" t="n">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="N778" t="n">
         <v>3344</v>
       </c>
       <c r="O778" t="n">
-        <v>1284096</v>
+        <v>1257344</v>
       </c>
       <c r="P778" t="n">
         <v>4500</v>
       </c>
       <c r="Q778" t="n">
-        <v>1728000</v>
+        <v>1692000</v>
       </c>
     </row>
     <row r="779">
@@ -35813,22 +35813,22 @@
         <v>0</v>
       </c>
       <c r="L780" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M780" t="n">
-        <v>192</v>
+        <v>168</v>
       </c>
       <c r="N780" t="n">
         <v>4400</v>
       </c>
       <c r="O780" t="n">
-        <v>844800</v>
+        <v>739200</v>
       </c>
       <c r="P780" t="n">
         <v>5900</v>
       </c>
       <c r="Q780" t="n">
-        <v>1132800</v>
+        <v>991200</v>
       </c>
     </row>
     <row r="781">
@@ -35859,22 +35859,22 @@
         <v>0</v>
       </c>
       <c r="L781" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M781" t="n">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="N781" t="n">
         <v>3520</v>
       </c>
       <c r="O781" t="n">
-        <v>704000</v>
+        <v>682880</v>
       </c>
       <c r="P781" t="n">
         <v>4500</v>
       </c>
       <c r="Q781" t="n">
-        <v>900000</v>
+        <v>873000</v>
       </c>
     </row>
     <row r="782">
@@ -35951,22 +35951,22 @@
         <v>0</v>
       </c>
       <c r="L783" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="M783" t="n">
-        <v>840</v>
+        <v>791</v>
       </c>
       <c r="N783" t="n">
         <v>9240</v>
       </c>
       <c r="O783" t="n">
-        <v>7761600</v>
+        <v>7308840</v>
       </c>
       <c r="P783" t="n">
         <v>11500</v>
       </c>
       <c r="Q783" t="n">
-        <v>9660000</v>
+        <v>9096500</v>
       </c>
     </row>
     <row r="784">
@@ -35997,22 +35997,22 @@
         <v>0</v>
       </c>
       <c r="L784" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="M784" t="n">
-        <v>384</v>
+        <v>356</v>
       </c>
       <c r="N784" t="n">
-        <v>2288</v>
+        <v>2346.9184549356</v>
       </c>
       <c r="O784" t="n">
-        <v>878592</v>
+        <v>835502.9699570736</v>
       </c>
       <c r="P784" t="n">
         <v>2900</v>
       </c>
       <c r="Q784" t="n">
-        <v>1113600</v>
+        <v>1032400</v>
       </c>
     </row>
     <row r="785">
@@ -36089,22 +36089,22 @@
         <v>0</v>
       </c>
       <c r="L786" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="M786" t="n">
-        <v>192</v>
+        <v>157</v>
       </c>
       <c r="N786" t="n">
         <v>4576</v>
       </c>
       <c r="O786" t="n">
-        <v>878592</v>
+        <v>718432</v>
       </c>
       <c r="P786" t="n">
         <v>5900</v>
       </c>
       <c r="Q786" t="n">
-        <v>1132800</v>
+        <v>926300</v>
       </c>
     </row>
     <row r="787">
@@ -36135,22 +36135,22 @@
         <v>0</v>
       </c>
       <c r="L787" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M787" t="n">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="N787" t="n">
         <v>5280</v>
       </c>
       <c r="O787" t="n">
-        <v>1584000</v>
+        <v>1547040</v>
       </c>
       <c r="P787" t="n">
         <v>6900</v>
       </c>
       <c r="Q787" t="n">
-        <v>2070000</v>
+        <v>2021700</v>
       </c>
     </row>
     <row r="788">
@@ -37382,22 +37382,22 @@
         <v>0</v>
       </c>
       <c r="L814" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M814" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="N814" t="n">
         <v>1129.14</v>
       </c>
       <c r="O814" t="n">
-        <v>14678.82</v>
+        <v>11291.4</v>
       </c>
       <c r="P814" t="n">
         <v>6900</v>
       </c>
       <c r="Q814" t="n">
-        <v>89700</v>
+        <v>69000</v>
       </c>
     </row>
     <row r="815">
@@ -37433,22 +37433,22 @@
         <v>0</v>
       </c>
       <c r="L815" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M815" t="n">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="N815" t="n">
         <v>1236.3</v>
       </c>
       <c r="O815" t="n">
-        <v>63051.3</v>
+        <v>45743.1</v>
       </c>
       <c r="P815" t="n">
         <v>2300</v>
       </c>
       <c r="Q815" t="n">
-        <v>117300</v>
+        <v>85100</v>
       </c>
     </row>
     <row r="816">
@@ -37622,22 +37622,22 @@
         <v>0</v>
       </c>
       <c r="L819" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M819" t="n">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="N819" t="n">
         <v>571.87</v>
       </c>
       <c r="O819" t="n">
-        <v>88067.98</v>
+        <v>80061.8</v>
       </c>
       <c r="P819" t="n">
         <v>2500</v>
       </c>
       <c r="Q819" t="n">
-        <v>385000</v>
+        <v>350000</v>
       </c>
     </row>
     <row r="820">

--- a/bodegas/LJ-05.xlsx
+++ b/bodegas/LJ-05.xlsx
@@ -938,28 +938,28 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>365</v>
+        <v>265</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M13" t="n">
-        <v>365</v>
+        <v>250</v>
       </c>
       <c r="N13" t="n">
-        <v>1811.3062015504</v>
+        <v>1811.3067953668</v>
       </c>
       <c r="O13" t="n">
-        <v>661126.763565896</v>
+        <v>452826.6988417</v>
       </c>
       <c r="P13" t="n">
         <v>2600</v>
       </c>
       <c r="Q13" t="n">
-        <v>949000</v>
+        <v>650000</v>
       </c>
     </row>
     <row r="14">
@@ -1217,22 +1217,22 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M20" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="N20" t="n">
         <v>4072</v>
       </c>
       <c r="O20" t="n">
-        <v>280968</v>
+        <v>268752</v>
       </c>
       <c r="P20" t="n">
         <v>7500</v>
       </c>
       <c r="Q20" t="n">
-        <v>517500</v>
+        <v>495000</v>
       </c>
     </row>
     <row r="21">
@@ -1864,10 +1864,10 @@
         <v>19</v>
       </c>
       <c r="N36" t="n">
-        <v>3716.3301935484</v>
+        <v>3716.3301938611</v>
       </c>
       <c r="O36" t="n">
-        <v>70610.27367741959</v>
+        <v>70610.27368336089</v>
       </c>
       <c r="P36" t="n">
         <v>9500</v>
@@ -2406,10 +2406,10 @@
         <v>1</v>
       </c>
       <c r="N49" t="n">
-        <v>3910.6281707317</v>
+        <v>3910.6281632653</v>
       </c>
       <c r="O49" t="n">
-        <v>3910.6281707317</v>
+        <v>3910.6281632653</v>
       </c>
       <c r="P49" t="n">
         <v>9100</v>
@@ -3338,22 +3338,22 @@
         <v>0</v>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M70" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="N70" t="n">
         <v>6321.94</v>
       </c>
       <c r="O70" t="n">
-        <v>442535.8</v>
+        <v>436213.86</v>
       </c>
       <c r="P70" t="n">
         <v>14100</v>
       </c>
       <c r="Q70" t="n">
-        <v>987000</v>
+        <v>972900</v>
       </c>
     </row>
     <row r="71">
@@ -4366,10 +4366,10 @@
         <v>13</v>
       </c>
       <c r="N94" t="n">
-        <v>61666.874026667</v>
+        <v>61666.874048257</v>
       </c>
       <c r="O94" t="n">
-        <v>801669.3623466709</v>
+        <v>801669.3626273409</v>
       </c>
       <c r="P94" t="n">
         <v>98900</v>
@@ -6464,22 +6464,22 @@
         <v>0</v>
       </c>
       <c r="L142" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M142" t="n">
-        <v>1286</v>
+        <v>1271</v>
       </c>
       <c r="N142" t="n">
         <v>1726.32</v>
       </c>
       <c r="O142" t="n">
-        <v>2220047.52</v>
+        <v>2194152.72</v>
       </c>
       <c r="P142" t="n">
         <v>1500</v>
       </c>
       <c r="Q142" t="n">
-        <v>1929000</v>
+        <v>1906500</v>
       </c>
     </row>
     <row r="143">
@@ -7348,22 +7348,22 @@
         <v>0</v>
       </c>
       <c r="L162" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M162" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="N162" t="n">
-        <v>2582.2558256496</v>
+        <v>2582.2557662062</v>
       </c>
       <c r="O162" t="n">
-        <v>49062.8606873424</v>
+        <v>30987.0691944744</v>
       </c>
       <c r="P162" t="n">
         <v>4500</v>
       </c>
       <c r="Q162" t="n">
-        <v>85500</v>
+        <v>54000</v>
       </c>
     </row>
     <row r="163">
@@ -7440,22 +7440,22 @@
         <v>0</v>
       </c>
       <c r="L164" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M164" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="N164" t="n">
-        <v>5216.8961603854</v>
+        <v>5216.8961467368</v>
       </c>
       <c r="O164" t="n">
-        <v>119988.6116888642</v>
+        <v>88687.2344945256</v>
       </c>
       <c r="P164" t="n">
         <v>8500</v>
       </c>
       <c r="Q164" t="n">
-        <v>195500</v>
+        <v>144500</v>
       </c>
     </row>
     <row r="165">
@@ -7670,22 +7670,22 @@
         <v>0</v>
       </c>
       <c r="L169" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M169" t="n">
-        <v>1705</v>
+        <v>1685</v>
       </c>
       <c r="N169" t="n">
         <v>156.25</v>
       </c>
       <c r="O169" t="n">
-        <v>266406.25</v>
+        <v>263281.25</v>
       </c>
       <c r="P169" t="n">
         <v>250</v>
       </c>
       <c r="Q169" t="n">
-        <v>426250</v>
+        <v>421250</v>
       </c>
     </row>
     <row r="170">
@@ -8131,10 +8131,10 @@
         <v>16</v>
       </c>
       <c r="N179" t="n">
-        <v>4890.9300483676</v>
+        <v>4890.9300485437</v>
       </c>
       <c r="O179" t="n">
-        <v>78254.8807738816</v>
+        <v>78254.8807766992</v>
       </c>
       <c r="P179" t="n">
         <v>8200</v>
@@ -8310,22 +8310,22 @@
         <v>0</v>
       </c>
       <c r="L183" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M183" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="N183" t="n">
         <v>1203.38</v>
       </c>
       <c r="O183" t="n">
-        <v>58965.62</v>
+        <v>50541.96000000001</v>
       </c>
       <c r="P183" t="n">
         <v>1900</v>
       </c>
       <c r="Q183" t="n">
-        <v>93100</v>
+        <v>79800</v>
       </c>
     </row>
     <row r="184">
@@ -8856,10 +8856,10 @@
         <v>5</v>
       </c>
       <c r="N195" t="n">
-        <v>3594.2540520446</v>
+        <v>3594.2540372671</v>
       </c>
       <c r="O195" t="n">
-        <v>17971.270260223</v>
+        <v>17971.2701863355</v>
       </c>
       <c r="P195" t="n">
         <v>6500</v>
@@ -8945,22 +8945,22 @@
         <v>0</v>
       </c>
       <c r="L197" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="M197" t="n">
-        <v>1786</v>
+        <v>1759</v>
       </c>
       <c r="N197" t="n">
         <v>489.88</v>
       </c>
       <c r="O197" t="n">
-        <v>874925.6799999999</v>
+        <v>861698.92</v>
       </c>
       <c r="P197" t="n">
         <v>700</v>
       </c>
       <c r="Q197" t="n">
-        <v>1250200</v>
+        <v>1231300</v>
       </c>
     </row>
     <row r="198">
@@ -9037,22 +9037,22 @@
         <v>0</v>
       </c>
       <c r="L199" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M199" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N199" t="n">
         <v>8154</v>
       </c>
       <c r="O199" t="n">
-        <v>244620</v>
+        <v>203850</v>
       </c>
       <c r="P199" t="n">
         <v>13500</v>
       </c>
       <c r="Q199" t="n">
-        <v>405000</v>
+        <v>337500</v>
       </c>
     </row>
     <row r="200">
@@ -9089,10 +9089,10 @@
         <v>31</v>
       </c>
       <c r="N200" t="n">
-        <v>14822.378854415</v>
+        <v>14822.378852361</v>
       </c>
       <c r="O200" t="n">
-        <v>459493.744486865</v>
+        <v>459493.744423191</v>
       </c>
       <c r="P200" t="n">
         <v>24900</v>
@@ -9454,10 +9454,10 @@
         <v>18</v>
       </c>
       <c r="N208" t="n">
-        <v>12267.649642857</v>
+        <v>12267.648987342</v>
       </c>
       <c r="O208" t="n">
-        <v>220817.693571426</v>
+        <v>220817.681772156</v>
       </c>
       <c r="P208" t="n">
         <v>19900</v>
@@ -9672,22 +9672,22 @@
         <v>0</v>
       </c>
       <c r="L213" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M213" t="n">
-        <v>512</v>
+        <v>504</v>
       </c>
       <c r="N213" t="n">
         <v>1441.01</v>
       </c>
       <c r="O213" t="n">
-        <v>737797.12</v>
+        <v>726269.04</v>
       </c>
       <c r="P213" t="n">
         <v>2100</v>
       </c>
       <c r="Q213" t="n">
-        <v>1075200</v>
+        <v>1058400</v>
       </c>
     </row>
     <row r="214">
@@ -9812,10 +9812,10 @@
         <v>122</v>
       </c>
       <c r="N216" t="n">
-        <v>3041.6600129786</v>
+        <v>3041.6600130804</v>
       </c>
       <c r="O216" t="n">
-        <v>371082.5215833892</v>
+        <v>371082.5215958088</v>
       </c>
       <c r="P216" t="n">
         <v>5500</v>
@@ -9852,22 +9852,22 @@
         <v>0</v>
       </c>
       <c r="L217" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M217" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="N217" t="n">
-        <v>4372.2107892862</v>
+        <v>4372.2107896237</v>
       </c>
       <c r="O217" t="n">
-        <v>205493.9070964514</v>
+        <v>188005.0639538191</v>
       </c>
       <c r="P217" t="n">
         <v>7500</v>
       </c>
       <c r="Q217" t="n">
-        <v>352500</v>
+        <v>322500</v>
       </c>
     </row>
     <row r="218">
@@ -9904,10 +9904,10 @@
         <v>346</v>
       </c>
       <c r="N218" t="n">
-        <v>1592.5669555035</v>
+        <v>1592.5668955224</v>
       </c>
       <c r="O218" t="n">
-        <v>551028.166604211</v>
+        <v>551028.1458507504</v>
       </c>
       <c r="P218" t="n">
         <v>3900</v>
@@ -10208,22 +10208,22 @@
         <v>0</v>
       </c>
       <c r="L225" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M225" t="n">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="N225" t="n">
         <v>4648.6</v>
       </c>
       <c r="O225" t="n">
-        <v>1538686.6</v>
+        <v>1482903.4</v>
       </c>
       <c r="P225" t="n">
         <v>8900</v>
       </c>
       <c r="Q225" t="n">
-        <v>2945900</v>
+        <v>2839100</v>
       </c>
     </row>
     <row r="226">
@@ -11207,28 +11207,28 @@
         </is>
       </c>
       <c r="J247" t="n">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="K247" t="n">
         <v>0</v>
       </c>
       <c r="L247" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M247" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="N247" t="n">
-        <v>1630.9234875283</v>
+        <v>1630.9235527836</v>
       </c>
       <c r="O247" t="n">
-        <v>61975.0925260754</v>
+        <v>1630.9235527836</v>
       </c>
       <c r="P247" t="n">
         <v>2500</v>
       </c>
       <c r="Q247" t="n">
-        <v>95000</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="248">
@@ -11253,28 +11253,28 @@
         </is>
       </c>
       <c r="J248" t="n">
-        <v>121</v>
+        <v>81</v>
       </c>
       <c r="K248" t="n">
         <v>0</v>
       </c>
       <c r="L248" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M248" t="n">
-        <v>121</v>
+        <v>61</v>
       </c>
       <c r="N248" t="n">
-        <v>1550.1935332762</v>
+        <v>1550.1935823921</v>
       </c>
       <c r="O248" t="n">
-        <v>187573.4175264202</v>
+        <v>94561.80852591811</v>
       </c>
       <c r="P248" t="n">
         <v>2500</v>
       </c>
       <c r="Q248" t="n">
-        <v>302500</v>
+        <v>152500</v>
       </c>
     </row>
     <row r="249">
@@ -11305,22 +11305,22 @@
         <v>0</v>
       </c>
       <c r="L249" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M249" t="n">
-        <v>543</v>
+        <v>536</v>
       </c>
       <c r="N249" t="n">
-        <v>2403.5115510508</v>
+        <v>2403.5116616598</v>
       </c>
       <c r="O249" t="n">
-        <v>1305106.772220584</v>
+        <v>1288282.250649653</v>
       </c>
       <c r="P249" t="n">
         <v>3500</v>
       </c>
       <c r="Q249" t="n">
-        <v>1900500</v>
+        <v>1876000</v>
       </c>
     </row>
     <row r="250">
@@ -11666,22 +11666,22 @@
         <v>0</v>
       </c>
       <c r="L257" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M257" t="n">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="N257" t="n">
         <v>1965</v>
       </c>
       <c r="O257" t="n">
-        <v>493215</v>
+        <v>481425</v>
       </c>
       <c r="P257" t="n">
         <v>3700</v>
       </c>
       <c r="Q257" t="n">
-        <v>928700</v>
+        <v>906500</v>
       </c>
     </row>
     <row r="258">
@@ -12492,10 +12492,10 @@
         <v>19</v>
       </c>
       <c r="N276" t="n">
-        <v>22485.695881007</v>
+        <v>22485.695577396</v>
       </c>
       <c r="O276" t="n">
-        <v>427228.221739133</v>
+        <v>427228.215970524</v>
       </c>
       <c r="P276" t="n">
         <v>36500</v>
@@ -13153,10 +13153,10 @@
         <v>91</v>
       </c>
       <c r="N291" t="n">
-        <v>4285.1954682454</v>
+        <v>4285.1954741379</v>
       </c>
       <c r="O291" t="n">
-        <v>389952.7876103314</v>
+        <v>389952.788146549</v>
       </c>
       <c r="P291" t="n">
         <v>6900</v>
@@ -13412,10 +13412,10 @@
         <v>61</v>
       </c>
       <c r="N297" t="n">
-        <v>30244.600034702</v>
+        <v>30244.600034722</v>
       </c>
       <c r="O297" t="n">
-        <v>1844920.602116822</v>
+        <v>1844920.602118042</v>
       </c>
       <c r="P297" t="n">
         <v>48900</v>
@@ -13458,10 +13458,10 @@
         <v>60</v>
       </c>
       <c r="N298" t="n">
-        <v>4605.2147185741</v>
+        <v>4605.2147274436</v>
       </c>
       <c r="O298" t="n">
-        <v>276312.883114446</v>
+        <v>276312.883646616</v>
       </c>
       <c r="P298" t="n">
         <v>7600</v>
@@ -13585,22 +13585,22 @@
         <v>0</v>
       </c>
       <c r="L301" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M301" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="N301" t="n">
-        <v>11562.038518519</v>
+        <v>11562.038494624</v>
       </c>
       <c r="O301" t="n">
-        <v>416233.386666684</v>
+        <v>346861.15483872</v>
       </c>
       <c r="P301" t="n">
         <v>18500</v>
       </c>
       <c r="Q301" t="n">
-        <v>666000</v>
+        <v>555000</v>
       </c>
     </row>
     <row r="302">
@@ -14353,10 +14353,10 @@
         <v>14</v>
       </c>
       <c r="N318" t="n">
-        <v>8332.7796240601</v>
+        <v>8332.779622166199</v>
       </c>
       <c r="O318" t="n">
-        <v>116658.9147368414</v>
+        <v>116658.9147103268</v>
       </c>
       <c r="P318" t="n">
         <v>14900</v>
@@ -14486,10 +14486,10 @@
         <v>61</v>
       </c>
       <c r="N321" t="n">
-        <v>1561.000152391</v>
+        <v>1561.0001684211</v>
       </c>
       <c r="O321" t="n">
-        <v>95221.00929585101</v>
+        <v>95221.01027368709</v>
       </c>
       <c r="P321" t="n">
         <v>2900</v>
@@ -15060,10 +15060,10 @@
         <v>22</v>
       </c>
       <c r="N334" t="n">
-        <v>548.14722592946</v>
+        <v>548.14720461095</v>
       </c>
       <c r="O334" t="n">
-        <v>12059.23897044812</v>
+        <v>12059.2385014409</v>
       </c>
       <c r="P334" t="n">
         <v>2000</v>
@@ -15892,10 +15892,10 @@
         <v>89</v>
       </c>
       <c r="N352" t="n">
-        <v>5218.1705479452</v>
+        <v>5218.1705520703</v>
       </c>
       <c r="O352" t="n">
-        <v>464417.1787671229</v>
+        <v>464417.1791342567</v>
       </c>
       <c r="P352" t="n">
         <v>8500</v>
@@ -15938,10 +15938,10 @@
         <v>105</v>
       </c>
       <c r="N353" t="n">
-        <v>1595.0093800979</v>
+        <v>1595.0093780687</v>
       </c>
       <c r="O353" t="n">
-        <v>167475.9849102795</v>
+        <v>167475.9846972135</v>
       </c>
       <c r="P353" t="n">
         <v>2600</v>
@@ -18804,22 +18804,22 @@
         <v>0</v>
       </c>
       <c r="L415" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M415" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="N415" t="n">
-        <v>2821.5822222222</v>
+        <v>2821.5826666667</v>
       </c>
       <c r="O415" t="n">
-        <v>98755.377777777</v>
+        <v>81825.8973333343</v>
       </c>
       <c r="P415" t="n">
         <v>4500</v>
       </c>
       <c r="Q415" t="n">
-        <v>157500</v>
+        <v>130500</v>
       </c>
     </row>
     <row r="416">
@@ -18896,22 +18896,22 @@
         <v>0</v>
       </c>
       <c r="L417" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M417" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="N417" t="n">
         <v>10411</v>
       </c>
       <c r="O417" t="n">
-        <v>364385</v>
+        <v>322741</v>
       </c>
       <c r="P417" t="n">
         <v>16900</v>
       </c>
       <c r="Q417" t="n">
-        <v>591500</v>
+        <v>523900</v>
       </c>
     </row>
     <row r="418">
@@ -19086,10 +19086,10 @@
         <v>59</v>
       </c>
       <c r="N421" t="n">
-        <v>2252.2966708385</v>
+        <v>2252.2968774194</v>
       </c>
       <c r="O421" t="n">
-        <v>132885.5035794715</v>
+        <v>132885.5157677446</v>
       </c>
       <c r="P421" t="n">
         <v>3900</v>
@@ -19267,22 +19267,22 @@
         <v>0</v>
       </c>
       <c r="L425" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M425" t="n">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="N425" t="n">
-        <v>2328.1187254606</v>
+        <v>2328.1187184938</v>
       </c>
       <c r="O425" t="n">
-        <v>575045.3251887682</v>
+        <v>547107.8988460429</v>
       </c>
       <c r="P425" t="n">
         <v>4500</v>
       </c>
       <c r="Q425" t="n">
-        <v>1111500</v>
+        <v>1057500</v>
       </c>
     </row>
     <row r="426">
@@ -19825,10 +19825,10 @@
         <v>38</v>
       </c>
       <c r="N437" t="n">
-        <v>4907.8220583468</v>
+        <v>4907.8220751634</v>
       </c>
       <c r="O437" t="n">
-        <v>186497.2382171784</v>
+        <v>186497.2388562092</v>
       </c>
       <c r="P437" t="n">
         <v>8200</v>
@@ -20827,10 +20827,10 @@
         <v>203</v>
       </c>
       <c r="N459" t="n">
-        <v>5869.172680203</v>
+        <v>5869.1726653103</v>
       </c>
       <c r="O459" t="n">
-        <v>1191442.054081209</v>
+        <v>1191442.051057991</v>
       </c>
       <c r="P459" t="n">
         <v>9500</v>
@@ -21465,22 +21465,22 @@
         <v>0</v>
       </c>
       <c r="L473" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M473" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="N473" t="n">
         <v>8806</v>
       </c>
       <c r="O473" t="n">
-        <v>308210</v>
+        <v>255374</v>
       </c>
       <c r="P473" t="n">
         <v>14900</v>
       </c>
       <c r="Q473" t="n">
-        <v>521500</v>
+        <v>432100</v>
       </c>
     </row>
     <row r="474">
@@ -22294,22 +22294,22 @@
         <v>0</v>
       </c>
       <c r="L491" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M491" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="N491" t="n">
         <v>10755</v>
       </c>
       <c r="O491" t="n">
-        <v>172080</v>
+        <v>107550</v>
       </c>
       <c r="P491" t="n">
         <v>17900</v>
       </c>
       <c r="Q491" t="n">
-        <v>286400</v>
+        <v>179000</v>
       </c>
     </row>
     <row r="492">
@@ -22938,22 +22938,22 @@
         <v>0</v>
       </c>
       <c r="L505" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M505" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="N505" t="n">
         <v>1326</v>
       </c>
       <c r="O505" t="n">
-        <v>33150</v>
+        <v>1326</v>
       </c>
       <c r="P505" t="n">
         <v>2500</v>
       </c>
       <c r="Q505" t="n">
-        <v>62500</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="506">
@@ -22984,22 +22984,22 @@
         <v>0</v>
       </c>
       <c r="L506" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M506" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="N506" t="n">
         <v>5640</v>
       </c>
       <c r="O506" t="n">
-        <v>124080</v>
+        <v>56400</v>
       </c>
       <c r="P506" t="n">
         <v>9900</v>
       </c>
       <c r="Q506" t="n">
-        <v>217800</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="507">
@@ -23076,22 +23076,22 @@
         <v>0</v>
       </c>
       <c r="L508" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M508" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="N508" t="n">
         <v>10817</v>
       </c>
       <c r="O508" t="n">
-        <v>227157</v>
+        <v>162255</v>
       </c>
       <c r="P508" t="n">
         <v>17900</v>
       </c>
       <c r="Q508" t="n">
-        <v>375900</v>
+        <v>268500</v>
       </c>
     </row>
     <row r="509">
@@ -23122,22 +23122,22 @@
         <v>0</v>
       </c>
       <c r="L509" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M509" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="N509" t="n">
         <v>12489</v>
       </c>
       <c r="O509" t="n">
-        <v>212313</v>
+        <v>137379</v>
       </c>
       <c r="P509" t="n">
         <v>20900</v>
       </c>
       <c r="Q509" t="n">
-        <v>355300</v>
+        <v>229900</v>
       </c>
     </row>
     <row r="510">
@@ -23677,22 +23677,22 @@
         <v>0</v>
       </c>
       <c r="L521" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M521" t="n">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="N521" t="n">
-        <v>1516.0388018299</v>
+        <v>1516.038799961</v>
       </c>
       <c r="O521" t="n">
-        <v>286531.3335458511</v>
+        <v>280467.177992785</v>
       </c>
       <c r="P521" t="n">
         <v>2300</v>
       </c>
       <c r="Q521" t="n">
-        <v>434700</v>
+        <v>425500</v>
       </c>
     </row>
     <row r="522">
@@ -23775,10 +23775,10 @@
         <v>411</v>
       </c>
       <c r="N523" t="n">
-        <v>2458.5131932225</v>
+        <v>2458.5131821149</v>
       </c>
       <c r="O523" t="n">
-        <v>1010448.922414447</v>
+        <v>1010448.917849224</v>
       </c>
       <c r="P523" t="n">
         <v>3500</v>
@@ -23959,10 +23959,10 @@
         <v>283</v>
       </c>
       <c r="N527" t="n">
-        <v>1803.0156033058</v>
+        <v>1803.0156051587</v>
       </c>
       <c r="O527" t="n">
-        <v>510253.4157355414</v>
+        <v>510253.4162599121</v>
       </c>
       <c r="P527" t="n">
         <v>2500</v>
@@ -24005,10 +24005,10 @@
         <v>96</v>
       </c>
       <c r="N528" t="n">
-        <v>3306.5951807229</v>
+        <v>3306.5951742627</v>
       </c>
       <c r="O528" t="n">
-        <v>317433.1373493984</v>
+        <v>317433.1367292192</v>
       </c>
       <c r="P528" t="n">
         <v>4900</v>
@@ -24097,10 +24097,10 @@
         <v>275</v>
       </c>
       <c r="N530" t="n">
-        <v>2108.791733871</v>
+        <v>2108.7917654987</v>
       </c>
       <c r="O530" t="n">
-        <v>579917.726814525</v>
+        <v>579917.7355121425</v>
       </c>
       <c r="P530" t="n">
         <v>2900</v>
@@ -24143,10 +24143,10 @@
         <v>293</v>
       </c>
       <c r="N531" t="n">
-        <v>2056.0833654773</v>
+        <v>2056.0833612094</v>
       </c>
       <c r="O531" t="n">
-        <v>602432.4260848489</v>
+        <v>602432.4248343543</v>
       </c>
       <c r="P531" t="n">
         <v>2900</v>
@@ -24189,10 +24189,10 @@
         <v>329</v>
       </c>
       <c r="N532" t="n">
-        <v>3224.5685400763</v>
+        <v>3224.5685727969</v>
       </c>
       <c r="O532" t="n">
-        <v>1060883.049685103</v>
+        <v>1060883.06045018</v>
       </c>
       <c r="P532" t="n">
         <v>4500</v>
@@ -24235,10 +24235,10 @@
         <v>261</v>
       </c>
       <c r="N533" t="n">
-        <v>1655.9308953259</v>
+        <v>1655.9308833223</v>
       </c>
       <c r="O533" t="n">
-        <v>432197.9636800599</v>
+        <v>432197.9605471203</v>
       </c>
       <c r="P533" t="n">
         <v>2500</v>
@@ -24413,22 +24413,22 @@
         <v>0</v>
       </c>
       <c r="L537" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M537" t="n">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="N537" t="n">
-        <v>1592.2776475694</v>
+        <v>1592.2780825688</v>
       </c>
       <c r="O537" t="n">
-        <v>269094.9224392286</v>
+        <v>249987.6589633016</v>
       </c>
       <c r="P537" t="n">
         <v>2500</v>
       </c>
       <c r="Q537" t="n">
-        <v>422500</v>
+        <v>392500</v>
       </c>
     </row>
     <row r="538">
@@ -24503,22 +24503,22 @@
         <v>0</v>
       </c>
       <c r="L539" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M539" t="n">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="N539" t="n">
-        <v>1668.6281268012</v>
+        <v>1668.6302167183</v>
       </c>
       <c r="O539" t="n">
-        <v>68413.7531988492</v>
+        <v>28366.7136842111</v>
       </c>
       <c r="P539" t="n">
         <v>2500</v>
       </c>
       <c r="Q539" t="n">
-        <v>102500</v>
+        <v>42500</v>
       </c>
     </row>
     <row r="540">
@@ -24555,10 +24555,10 @@
         <v>21</v>
       </c>
       <c r="N540" t="n">
-        <v>2546.9842276423</v>
+        <v>2546.9839957717</v>
       </c>
       <c r="O540" t="n">
-        <v>53486.6687804883</v>
+        <v>53486.6639112057</v>
       </c>
       <c r="P540" t="n">
         <v>3900</v>
@@ -24866,22 +24866,22 @@
         <v>0</v>
       </c>
       <c r="L547" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M547" t="n">
-        <v>2470</v>
+        <v>2458</v>
       </c>
       <c r="N547" t="n">
-        <v>1955.2371159315</v>
+        <v>1955.2371140003</v>
       </c>
       <c r="O547" t="n">
-        <v>4829435.676350805</v>
+        <v>4805972.826212737</v>
       </c>
       <c r="P547" t="n">
         <v>3000</v>
       </c>
       <c r="Q547" t="n">
-        <v>7410000</v>
+        <v>7374000</v>
       </c>
     </row>
     <row r="548">
@@ -25722,10 +25722,10 @@
         <v>21</v>
       </c>
       <c r="N565" t="n">
-        <v>10732.242051282</v>
+        <v>10732.242105263</v>
       </c>
       <c r="O565" t="n">
-        <v>225377.083076922</v>
+        <v>225377.084210523</v>
       </c>
       <c r="P565" t="n">
         <v>25900</v>
@@ -26230,10 +26230,10 @@
         <v>100</v>
       </c>
       <c r="N576" t="n">
-        <v>711.3366499515799</v>
+        <v>711.33664971986</v>
       </c>
       <c r="O576" t="n">
-        <v>71133.66499515799</v>
+        <v>71133.664971986</v>
       </c>
       <c r="P576" t="n">
         <v>900</v>
@@ -26684,22 +26684,22 @@
         <v>0</v>
       </c>
       <c r="L586" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M586" t="n">
-        <v>1921</v>
+        <v>1873</v>
       </c>
       <c r="N586" t="n">
-        <v>517.28922545101</v>
+        <v>517.2892916984</v>
       </c>
       <c r="O586" t="n">
-        <v>993712.6020913902</v>
+        <v>968882.8433511032</v>
       </c>
       <c r="P586" t="n">
         <v>900</v>
       </c>
       <c r="Q586" t="n">
-        <v>1728900</v>
+        <v>1685700</v>
       </c>
     </row>
     <row r="587">
@@ -26915,22 +26915,22 @@
         <v>0</v>
       </c>
       <c r="L591" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="M591" t="n">
-        <v>311</v>
+        <v>249</v>
       </c>
       <c r="N591" t="n">
-        <v>3110.8421999117</v>
+        <v>3110.8418772978</v>
       </c>
       <c r="O591" t="n">
-        <v>967471.9241725387</v>
+        <v>774599.6274471522</v>
       </c>
       <c r="P591" t="n">
         <v>4500</v>
       </c>
       <c r="Q591" t="n">
-        <v>1399500</v>
+        <v>1120500</v>
       </c>
     </row>
     <row r="592">
@@ -26959,22 +26959,22 @@
         <v>0</v>
       </c>
       <c r="L592" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="M592" t="n">
-        <v>1610</v>
+        <v>1532</v>
       </c>
       <c r="N592" t="n">
-        <v>703.79520622865</v>
+        <v>703.79518726322</v>
       </c>
       <c r="O592" t="n">
-        <v>1133110.282028127</v>
+        <v>1078214.226887253</v>
       </c>
       <c r="P592" t="n">
         <v>900</v>
       </c>
       <c r="Q592" t="n">
-        <v>1449000</v>
+        <v>1378800</v>
       </c>
     </row>
     <row r="593">
@@ -27247,22 +27247,22 @@
         <v>0</v>
       </c>
       <c r="L598" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M598" t="n">
-        <v>323</v>
+        <v>309</v>
       </c>
       <c r="N598" t="n">
-        <v>1595.5130117944</v>
+        <v>1595.5128965225</v>
       </c>
       <c r="O598" t="n">
-        <v>515350.7028095912</v>
+        <v>493013.4850254524</v>
       </c>
       <c r="P598" t="n">
         <v>2500</v>
       </c>
       <c r="Q598" t="n">
-        <v>807500</v>
+        <v>772500</v>
       </c>
     </row>
     <row r="599">
@@ -28068,22 +28068,22 @@
         <v>0</v>
       </c>
       <c r="L615" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M615" t="n">
-        <v>574</v>
+        <v>568</v>
       </c>
       <c r="N615" t="n">
         <v>1669.6</v>
       </c>
       <c r="O615" t="n">
-        <v>958350.3999999999</v>
+        <v>948332.7999999999</v>
       </c>
       <c r="P615" t="n">
         <v>2900</v>
       </c>
       <c r="Q615" t="n">
-        <v>1664600</v>
+        <v>1647200</v>
       </c>
     </row>
     <row r="616">
@@ -28359,10 +28359,10 @@
         <v>35</v>
       </c>
       <c r="N621" t="n">
-        <v>3505.3804</v>
+        <v>3505.3804081633</v>
       </c>
       <c r="O621" t="n">
-        <v>122688.314</v>
+        <v>122688.3142857155</v>
       </c>
       <c r="P621" t="n">
         <v>12900</v>
@@ -28635,22 +28635,22 @@
         <v>0</v>
       </c>
       <c r="L627" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M627" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="N627" t="n">
         <v>10536.4</v>
       </c>
       <c r="O627" t="n">
-        <v>284482.8</v>
+        <v>263410</v>
       </c>
       <c r="P627" t="n">
         <v>16900</v>
       </c>
       <c r="Q627" t="n">
-        <v>456300</v>
+        <v>422500</v>
       </c>
     </row>
     <row r="628">
@@ -32352,22 +32352,22 @@
         <v>0</v>
       </c>
       <c r="L705" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M705" t="n">
-        <v>576</v>
+        <v>561</v>
       </c>
       <c r="N705" t="n">
         <v>1176.57</v>
       </c>
       <c r="O705" t="n">
-        <v>677704.3199999999</v>
+        <v>660055.77</v>
       </c>
       <c r="P705" t="n">
         <v>1900</v>
       </c>
       <c r="Q705" t="n">
-        <v>1094400</v>
+        <v>1065900</v>
       </c>
     </row>
     <row r="706">
@@ -32777,22 +32777,22 @@
         <v>0</v>
       </c>
       <c r="L714" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M714" t="n">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="N714" t="n">
         <v>5077</v>
       </c>
       <c r="O714" t="n">
-        <v>685395</v>
+        <v>624471</v>
       </c>
       <c r="P714" t="n">
         <v>8500</v>
       </c>
       <c r="Q714" t="n">
-        <v>1147500</v>
+        <v>1045500</v>
       </c>
     </row>
     <row r="715">
@@ -33231,7 +33231,7 @@
         </is>
       </c>
       <c r="J724" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="K724" t="n">
         <v>0</v>
@@ -33240,19 +33240,19 @@
         <v>0</v>
       </c>
       <c r="M724" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="N724" t="n">
         <v>5220</v>
       </c>
       <c r="O724" t="n">
-        <v>156600</v>
+        <v>125280</v>
       </c>
       <c r="P724" t="n">
         <v>6900</v>
       </c>
       <c r="Q724" t="n">
-        <v>207000</v>
+        <v>165600</v>
       </c>
     </row>
     <row r="725">
@@ -33323,7 +33323,7 @@
         </is>
       </c>
       <c r="J726" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K726" t="n">
         <v>0</v>
@@ -33332,19 +33332,19 @@
         <v>0</v>
       </c>
       <c r="M726" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="N726" t="n">
         <v>7650</v>
       </c>
       <c r="O726" t="n">
-        <v>298350</v>
+        <v>275400</v>
       </c>
       <c r="P726" t="n">
         <v>9900</v>
       </c>
       <c r="Q726" t="n">
-        <v>386100</v>
+        <v>356400</v>
       </c>
     </row>
     <row r="727">
@@ -33599,7 +33599,7 @@
         </is>
       </c>
       <c r="J732" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="K732" t="n">
         <v>0</v>
@@ -33608,19 +33608,19 @@
         <v>0</v>
       </c>
       <c r="M732" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="N732" t="n">
         <v>9000</v>
       </c>
       <c r="O732" t="n">
-        <v>360000</v>
+        <v>324000</v>
       </c>
       <c r="P732" t="n">
         <v>11500</v>
       </c>
       <c r="Q732" t="n">
-        <v>460000</v>
+        <v>414000</v>
       </c>
     </row>
     <row r="733">
@@ -33829,7 +33829,7 @@
         </is>
       </c>
       <c r="J737" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K737" t="n">
         <v>0</v>
@@ -33838,19 +33838,19 @@
         <v>0</v>
       </c>
       <c r="M737" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N737" t="n">
         <v>25200</v>
       </c>
       <c r="O737" t="n">
-        <v>151200</v>
+        <v>126000</v>
       </c>
       <c r="P737" t="n">
         <v>31900</v>
       </c>
       <c r="Q737" t="n">
-        <v>191400</v>
+        <v>159500</v>
       </c>
     </row>
     <row r="738">
@@ -34289,7 +34289,7 @@
         </is>
       </c>
       <c r="J747" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K747" t="n">
         <v>0</v>
@@ -34298,19 +34298,19 @@
         <v>0</v>
       </c>
       <c r="M747" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N747" t="n">
         <v>36000</v>
       </c>
       <c r="O747" t="n">
-        <v>144000</v>
+        <v>108000</v>
       </c>
       <c r="P747" t="n">
         <v>45000</v>
       </c>
       <c r="Q747" t="n">
-        <v>180000</v>
+        <v>135000</v>
       </c>
     </row>
     <row r="748">
@@ -34335,7 +34335,7 @@
         </is>
       </c>
       <c r="J748" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K748" t="n">
         <v>0</v>
@@ -34344,19 +34344,19 @@
         <v>0</v>
       </c>
       <c r="M748" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N748" t="n">
         <v>54000</v>
       </c>
       <c r="O748" t="n">
-        <v>108000</v>
+        <v>54000</v>
       </c>
       <c r="P748" t="n">
         <v>69900</v>
       </c>
       <c r="Q748" t="n">
-        <v>139800</v>
+        <v>69900</v>
       </c>
     </row>
     <row r="749">
@@ -34985,22 +34985,22 @@
         <v>0</v>
       </c>
       <c r="L762" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M762" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="N762" t="n">
         <v>6336</v>
       </c>
       <c r="O762" t="n">
-        <v>823680</v>
+        <v>811008</v>
       </c>
       <c r="P762" t="n">
         <v>7500</v>
       </c>
       <c r="Q762" t="n">
-        <v>975000</v>
+        <v>960000</v>
       </c>
     </row>
     <row r="763">
@@ -35031,22 +35031,22 @@
         <v>0</v>
       </c>
       <c r="L763" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M763" t="n">
-        <v>152</v>
+        <v>128</v>
       </c>
       <c r="N763" t="n">
         <v>5280</v>
       </c>
       <c r="O763" t="n">
-        <v>802560</v>
+        <v>675840</v>
       </c>
       <c r="P763" t="n">
         <v>6900</v>
       </c>
       <c r="Q763" t="n">
-        <v>1048800</v>
+        <v>883200</v>
       </c>
     </row>
     <row r="764">
@@ -35123,22 +35123,22 @@
         <v>0</v>
       </c>
       <c r="L765" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M765" t="n">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="N765" t="n">
         <v>1584</v>
       </c>
       <c r="O765" t="n">
-        <v>437184</v>
+        <v>432432</v>
       </c>
       <c r="P765" t="n">
         <v>2000</v>
       </c>
       <c r="Q765" t="n">
-        <v>552000</v>
+        <v>546000</v>
       </c>
     </row>
     <row r="766">
@@ -35169,22 +35169,22 @@
         <v>0</v>
       </c>
       <c r="L766" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M766" t="n">
-        <v>714</v>
+        <v>708</v>
       </c>
       <c r="N766" t="n">
         <v>1584</v>
       </c>
       <c r="O766" t="n">
-        <v>1130976</v>
+        <v>1121472</v>
       </c>
       <c r="P766" t="n">
         <v>2000</v>
       </c>
       <c r="Q766" t="n">
-        <v>1428000</v>
+        <v>1416000</v>
       </c>
     </row>
     <row r="767">
@@ -35261,22 +35261,22 @@
         <v>0</v>
       </c>
       <c r="L768" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M768" t="n">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="N768" t="n">
         <v>3872</v>
       </c>
       <c r="O768" t="n">
-        <v>735680</v>
+        <v>727936</v>
       </c>
       <c r="P768" t="n">
         <v>4900</v>
       </c>
       <c r="Q768" t="n">
-        <v>931000</v>
+        <v>921200</v>
       </c>
     </row>
     <row r="769">
@@ -35399,22 +35399,22 @@
         <v>0</v>
       </c>
       <c r="L771" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M771" t="n">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="N771" t="n">
         <v>6160</v>
       </c>
       <c r="O771" t="n">
-        <v>1330560</v>
+        <v>1318240</v>
       </c>
       <c r="P771" t="n">
         <v>7900</v>
       </c>
       <c r="Q771" t="n">
-        <v>1706400</v>
+        <v>1690600</v>
       </c>
     </row>
     <row r="772">
@@ -35445,22 +35445,22 @@
         <v>0</v>
       </c>
       <c r="L772" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M772" t="n">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="N772" t="n">
         <v>6160</v>
       </c>
       <c r="O772" t="n">
-        <v>1330560</v>
+        <v>1256640</v>
       </c>
       <c r="P772" t="n">
         <v>7900</v>
       </c>
       <c r="Q772" t="n">
-        <v>1706400</v>
+        <v>1611600</v>
       </c>
     </row>
     <row r="773">
@@ -35491,22 +35491,22 @@
         <v>0</v>
       </c>
       <c r="L773" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M773" t="n">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="N773" t="n">
         <v>6160</v>
       </c>
       <c r="O773" t="n">
-        <v>517440</v>
+        <v>443520</v>
       </c>
       <c r="P773" t="n">
         <v>7900</v>
       </c>
       <c r="Q773" t="n">
-        <v>663600</v>
+        <v>568800</v>
       </c>
     </row>
     <row r="774">
@@ -35537,22 +35537,22 @@
         <v>0</v>
       </c>
       <c r="L774" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M774" t="n">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="N774" t="n">
         <v>3344</v>
       </c>
       <c r="O774" t="n">
-        <v>1257344</v>
+        <v>1250656</v>
       </c>
       <c r="P774" t="n">
         <v>4500</v>
       </c>
       <c r="Q774" t="n">
-        <v>1692000</v>
+        <v>1683000</v>
       </c>
     </row>
     <row r="775">
@@ -35583,22 +35583,22 @@
         <v>0</v>
       </c>
       <c r="L775" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M775" t="n">
-        <v>360</v>
+        <v>348</v>
       </c>
       <c r="N775" t="n">
         <v>3344</v>
       </c>
       <c r="O775" t="n">
-        <v>1203840</v>
+        <v>1163712</v>
       </c>
       <c r="P775" t="n">
         <v>4500</v>
       </c>
       <c r="Q775" t="n">
-        <v>1620000</v>
+        <v>1566000</v>
       </c>
     </row>
     <row r="776">
@@ -35721,22 +35721,22 @@
         <v>0</v>
       </c>
       <c r="L778" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M778" t="n">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="N778" t="n">
         <v>1260</v>
       </c>
       <c r="O778" t="n">
-        <v>302400</v>
+        <v>287280</v>
       </c>
       <c r="P778" t="n">
         <v>1700</v>
       </c>
       <c r="Q778" t="n">
-        <v>408000</v>
+        <v>387600</v>
       </c>
     </row>
     <row r="779">
@@ -35767,22 +35767,22 @@
         <v>0</v>
       </c>
       <c r="L779" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="M779" t="n">
-        <v>791</v>
+        <v>702</v>
       </c>
       <c r="N779" t="n">
         <v>9240</v>
       </c>
       <c r="O779" t="n">
-        <v>7308840</v>
+        <v>6486480</v>
       </c>
       <c r="P779" t="n">
         <v>11500</v>
       </c>
       <c r="Q779" t="n">
-        <v>9096500</v>
+        <v>8073000</v>
       </c>
     </row>
     <row r="780">
@@ -35813,22 +35813,22 @@
         <v>0</v>
       </c>
       <c r="L780" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="M780" t="n">
-        <v>356</v>
+        <v>323</v>
       </c>
       <c r="N780" t="n">
         <v>2288</v>
       </c>
       <c r="O780" t="n">
-        <v>814528</v>
+        <v>739024</v>
       </c>
       <c r="P780" t="n">
         <v>2900</v>
       </c>
       <c r="Q780" t="n">
-        <v>1032400</v>
+        <v>936700</v>
       </c>
     </row>
     <row r="781">
@@ -35859,22 +35859,22 @@
         <v>0</v>
       </c>
       <c r="L781" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M781" t="n">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="N781" t="n">
         <v>7216</v>
       </c>
       <c r="O781" t="n">
-        <v>2359632</v>
+        <v>2345200</v>
       </c>
       <c r="P781" t="n">
         <v>9000</v>
       </c>
       <c r="Q781" t="n">
-        <v>2943000</v>
+        <v>2925000</v>
       </c>
     </row>
     <row r="782">
@@ -35905,22 +35905,22 @@
         <v>0</v>
       </c>
       <c r="L782" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M782" t="n">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="N782" t="n">
         <v>4576</v>
       </c>
       <c r="O782" t="n">
-        <v>718432</v>
+        <v>663520</v>
       </c>
       <c r="P782" t="n">
         <v>5900</v>
       </c>
       <c r="Q782" t="n">
-        <v>926300</v>
+        <v>855500</v>
       </c>
     </row>
     <row r="783">
@@ -35951,22 +35951,22 @@
         <v>0</v>
       </c>
       <c r="L783" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M783" t="n">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="N783" t="n">
         <v>5280</v>
       </c>
       <c r="O783" t="n">
-        <v>1547040</v>
+        <v>1483680</v>
       </c>
       <c r="P783" t="n">
         <v>6900</v>
       </c>
       <c r="Q783" t="n">
-        <v>2021700</v>
+        <v>1938900</v>
       </c>
     </row>
     <row r="784">
@@ -37106,22 +37106,22 @@
         <v>0</v>
       </c>
       <c r="L808" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M808" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="N808" t="n">
-        <v>970.631875</v>
+        <v>970.63230769231</v>
       </c>
       <c r="O808" t="n">
-        <v>23295.165</v>
+        <v>17471.38153846158</v>
       </c>
       <c r="P808" t="n">
         <v>7200</v>
       </c>
       <c r="Q808" t="n">
-        <v>172800</v>
+        <v>129600</v>
       </c>
     </row>
     <row r="809">
@@ -37392,22 +37392,22 @@
         <v>0</v>
       </c>
       <c r="L814" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M814" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="N814" t="n">
         <v>751.45</v>
       </c>
       <c r="O814" t="n">
-        <v>41329.75</v>
+        <v>32312.35</v>
       </c>
       <c r="P814" t="n">
         <v>2500</v>
       </c>
       <c r="Q814" t="n">
-        <v>137500</v>
+        <v>107500</v>
       </c>
     </row>
     <row r="815">
@@ -38087,22 +38087,22 @@
         <v>0</v>
       </c>
       <c r="L829" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M829" t="n">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="N829" t="n">
         <v>4550</v>
       </c>
       <c r="O829" t="n">
-        <v>1346800</v>
+        <v>1342250</v>
       </c>
       <c r="P829" t="n">
         <v>5500</v>
       </c>
       <c r="Q829" t="n">
-        <v>1628000</v>
+        <v>1622500</v>
       </c>
     </row>
     <row r="830">

--- a/bodegas/LJ-05.xlsx
+++ b/bodegas/LJ-05.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-25</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-26</t>
         </is>
       </c>
     </row>
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>265</v>
+        <v>250</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>250</v>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
         <v>66</v>
@@ -3332,13 +3332,13 @@
         </is>
       </c>
       <c r="J70" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K70" t="n">
         <v>0</v>
       </c>
       <c r="L70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
         <v>69</v>
@@ -6458,13 +6458,13 @@
         </is>
       </c>
       <c r="J142" t="n">
-        <v>1286</v>
+        <v>1271</v>
       </c>
       <c r="K142" t="n">
         <v>0</v>
       </c>
       <c r="L142" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M142" t="n">
         <v>1271</v>
@@ -7342,13 +7342,13 @@
         </is>
       </c>
       <c r="J162" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="K162" t="n">
         <v>0</v>
       </c>
       <c r="L162" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M162" t="n">
         <v>12</v>
@@ -7434,13 +7434,13 @@
         </is>
       </c>
       <c r="J164" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="K164" t="n">
         <v>0</v>
       </c>
       <c r="L164" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M164" t="n">
         <v>17</v>
@@ -7664,13 +7664,13 @@
         </is>
       </c>
       <c r="J169" t="n">
-        <v>1705</v>
+        <v>1685</v>
       </c>
       <c r="K169" t="n">
         <v>0</v>
       </c>
       <c r="L169" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M169" t="n">
         <v>1685</v>
@@ -8304,13 +8304,13 @@
         </is>
       </c>
       <c r="J183" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="K183" t="n">
         <v>0</v>
       </c>
       <c r="L183" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M183" t="n">
         <v>42</v>
@@ -8939,13 +8939,13 @@
         </is>
       </c>
       <c r="J197" t="n">
-        <v>1786</v>
+        <v>1759</v>
       </c>
       <c r="K197" t="n">
         <v>0</v>
       </c>
       <c r="L197" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="M197" t="n">
         <v>1759</v>
@@ -9031,13 +9031,13 @@
         </is>
       </c>
       <c r="J199" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K199" t="n">
         <v>0</v>
       </c>
       <c r="L199" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M199" t="n">
         <v>25</v>
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="J213" t="n">
-        <v>512</v>
+        <v>504</v>
       </c>
       <c r="K213" t="n">
         <v>0</v>
       </c>
       <c r="L213" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M213" t="n">
         <v>504</v>
@@ -9846,13 +9846,13 @@
         </is>
       </c>
       <c r="J217" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K217" t="n">
         <v>0</v>
       </c>
       <c r="L217" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M217" t="n">
         <v>43</v>
@@ -10202,13 +10202,13 @@
         </is>
       </c>
       <c r="J225" t="n">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="K225" t="n">
         <v>0</v>
       </c>
       <c r="L225" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M225" t="n">
         <v>319</v>
@@ -11207,13 +11207,13 @@
         </is>
       </c>
       <c r="J247" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="K247" t="n">
         <v>0</v>
       </c>
       <c r="L247" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M247" t="n">
         <v>1</v>
@@ -11253,13 +11253,13 @@
         </is>
       </c>
       <c r="J248" t="n">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="K248" t="n">
         <v>0</v>
       </c>
       <c r="L248" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M248" t="n">
         <v>61</v>
@@ -11299,13 +11299,13 @@
         </is>
       </c>
       <c r="J249" t="n">
-        <v>543</v>
+        <v>536</v>
       </c>
       <c r="K249" t="n">
         <v>0</v>
       </c>
       <c r="L249" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M249" t="n">
         <v>536</v>
@@ -11660,13 +11660,13 @@
         </is>
       </c>
       <c r="J257" t="n">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="K257" t="n">
         <v>0</v>
       </c>
       <c r="L257" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M257" t="n">
         <v>245</v>
@@ -13579,13 +13579,13 @@
         </is>
       </c>
       <c r="J301" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="K301" t="n">
         <v>0</v>
       </c>
       <c r="L301" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M301" t="n">
         <v>30</v>
@@ -18798,13 +18798,13 @@
         </is>
       </c>
       <c r="J415" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="K415" t="n">
         <v>0</v>
       </c>
       <c r="L415" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M415" t="n">
         <v>29</v>
@@ -18890,13 +18890,13 @@
         </is>
       </c>
       <c r="J417" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="K417" t="n">
         <v>0</v>
       </c>
       <c r="L417" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M417" t="n">
         <v>31</v>
@@ -19261,13 +19261,13 @@
         </is>
       </c>
       <c r="J425" t="n">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="K425" t="n">
         <v>0</v>
       </c>
       <c r="L425" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M425" t="n">
         <v>235</v>
@@ -21459,13 +21459,13 @@
         </is>
       </c>
       <c r="J473" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="K473" t="n">
         <v>0</v>
       </c>
       <c r="L473" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M473" t="n">
         <v>29</v>
@@ -22288,13 +22288,13 @@
         </is>
       </c>
       <c r="J491" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="K491" t="n">
         <v>0</v>
       </c>
       <c r="L491" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M491" t="n">
         <v>10</v>
@@ -22932,13 +22932,13 @@
         </is>
       </c>
       <c r="J505" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="K505" t="n">
         <v>0</v>
       </c>
       <c r="L505" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="M505" t="n">
         <v>1</v>
@@ -22978,13 +22978,13 @@
         </is>
       </c>
       <c r="J506" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="K506" t="n">
         <v>0</v>
       </c>
       <c r="L506" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M506" t="n">
         <v>10</v>
@@ -23070,13 +23070,13 @@
         </is>
       </c>
       <c r="J508" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="K508" t="n">
         <v>0</v>
       </c>
       <c r="L508" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M508" t="n">
         <v>15</v>
@@ -23116,13 +23116,13 @@
         </is>
       </c>
       <c r="J509" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="K509" t="n">
         <v>0</v>
       </c>
       <c r="L509" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M509" t="n">
         <v>11</v>
@@ -23671,13 +23671,13 @@
         </is>
       </c>
       <c r="J521" t="n">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="K521" t="n">
         <v>0</v>
       </c>
       <c r="L521" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M521" t="n">
         <v>185</v>
@@ -24407,13 +24407,13 @@
         </is>
       </c>
       <c r="J537" t="n">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="K537" t="n">
         <v>0</v>
       </c>
       <c r="L537" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M537" t="n">
         <v>157</v>
@@ -24497,13 +24497,13 @@
         </is>
       </c>
       <c r="J539" t="n">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="K539" t="n">
         <v>0</v>
       </c>
       <c r="L539" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="M539" t="n">
         <v>17</v>
@@ -24860,13 +24860,13 @@
         </is>
       </c>
       <c r="J547" t="n">
-        <v>2470</v>
+        <v>2458</v>
       </c>
       <c r="K547" t="n">
         <v>0</v>
       </c>
       <c r="L547" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M547" t="n">
         <v>2458</v>
@@ -26678,13 +26678,13 @@
         </is>
       </c>
       <c r="J586" t="n">
-        <v>1921</v>
+        <v>1873</v>
       </c>
       <c r="K586" t="n">
         <v>0</v>
       </c>
       <c r="L586" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="M586" t="n">
         <v>1873</v>
@@ -26909,13 +26909,13 @@
         </is>
       </c>
       <c r="J591" t="n">
-        <v>311</v>
+        <v>249</v>
       </c>
       <c r="K591" t="n">
         <v>0</v>
       </c>
       <c r="L591" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="M591" t="n">
         <v>249</v>
@@ -26953,13 +26953,13 @@
         </is>
       </c>
       <c r="J592" t="n">
-        <v>1610</v>
+        <v>1532</v>
       </c>
       <c r="K592" t="n">
         <v>0</v>
       </c>
       <c r="L592" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="M592" t="n">
         <v>1532</v>
@@ -27241,13 +27241,13 @@
         </is>
       </c>
       <c r="J598" t="n">
-        <v>323</v>
+        <v>309</v>
       </c>
       <c r="K598" t="n">
         <v>0</v>
       </c>
       <c r="L598" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="M598" t="n">
         <v>309</v>
@@ -28062,13 +28062,13 @@
         </is>
       </c>
       <c r="J615" t="n">
-        <v>574</v>
+        <v>568</v>
       </c>
       <c r="K615" t="n">
         <v>0</v>
       </c>
       <c r="L615" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M615" t="n">
         <v>568</v>
@@ -28629,13 +28629,13 @@
         </is>
       </c>
       <c r="J627" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="K627" t="n">
         <v>0</v>
       </c>
       <c r="L627" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M627" t="n">
         <v>25</v>
@@ -32346,13 +32346,13 @@
         </is>
       </c>
       <c r="J705" t="n">
-        <v>576</v>
+        <v>561</v>
       </c>
       <c r="K705" t="n">
         <v>0</v>
       </c>
       <c r="L705" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M705" t="n">
         <v>561</v>
@@ -32771,13 +32771,13 @@
         </is>
       </c>
       <c r="J714" t="n">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="K714" t="n">
         <v>0</v>
       </c>
       <c r="L714" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M714" t="n">
         <v>123</v>
@@ -34979,13 +34979,13 @@
         </is>
       </c>
       <c r="J762" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="K762" t="n">
         <v>0</v>
       </c>
       <c r="L762" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M762" t="n">
         <v>128</v>
@@ -35025,13 +35025,13 @@
         </is>
       </c>
       <c r="J763" t="n">
-        <v>152</v>
+        <v>128</v>
       </c>
       <c r="K763" t="n">
         <v>0</v>
       </c>
       <c r="L763" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="M763" t="n">
         <v>128</v>
@@ -35117,13 +35117,13 @@
         </is>
       </c>
       <c r="J765" t="n">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="K765" t="n">
         <v>0</v>
       </c>
       <c r="L765" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M765" t="n">
         <v>273</v>
@@ -35163,13 +35163,13 @@
         </is>
       </c>
       <c r="J766" t="n">
-        <v>714</v>
+        <v>708</v>
       </c>
       <c r="K766" t="n">
         <v>0</v>
       </c>
       <c r="L766" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M766" t="n">
         <v>708</v>
@@ -35255,13 +35255,13 @@
         </is>
       </c>
       <c r="J768" t="n">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="K768" t="n">
         <v>0</v>
       </c>
       <c r="L768" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M768" t="n">
         <v>188</v>
@@ -35393,13 +35393,13 @@
         </is>
       </c>
       <c r="J771" t="n">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="K771" t="n">
         <v>0</v>
       </c>
       <c r="L771" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M771" t="n">
         <v>214</v>
@@ -35439,13 +35439,13 @@
         </is>
       </c>
       <c r="J772" t="n">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="K772" t="n">
         <v>0</v>
       </c>
       <c r="L772" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M772" t="n">
         <v>204</v>
@@ -35485,13 +35485,13 @@
         </is>
       </c>
       <c r="J773" t="n">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="K773" t="n">
         <v>0</v>
       </c>
       <c r="L773" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M773" t="n">
         <v>72</v>
@@ -35531,13 +35531,13 @@
         </is>
       </c>
       <c r="J774" t="n">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="K774" t="n">
         <v>0</v>
       </c>
       <c r="L774" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M774" t="n">
         <v>374</v>
@@ -35577,13 +35577,13 @@
         </is>
       </c>
       <c r="J775" t="n">
-        <v>360</v>
+        <v>348</v>
       </c>
       <c r="K775" t="n">
         <v>0</v>
       </c>
       <c r="L775" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M775" t="n">
         <v>348</v>
@@ -35715,13 +35715,13 @@
         </is>
       </c>
       <c r="J778" t="n">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="K778" t="n">
         <v>0</v>
       </c>
       <c r="L778" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M778" t="n">
         <v>228</v>
@@ -35761,13 +35761,13 @@
         </is>
       </c>
       <c r="J779" t="n">
-        <v>791</v>
+        <v>702</v>
       </c>
       <c r="K779" t="n">
         <v>0</v>
       </c>
       <c r="L779" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="M779" t="n">
         <v>702</v>
@@ -35807,13 +35807,13 @@
         </is>
       </c>
       <c r="J780" t="n">
-        <v>356</v>
+        <v>323</v>
       </c>
       <c r="K780" t="n">
         <v>0</v>
       </c>
       <c r="L780" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="M780" t="n">
         <v>323</v>
@@ -35853,13 +35853,13 @@
         </is>
       </c>
       <c r="J781" t="n">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="K781" t="n">
         <v>0</v>
       </c>
       <c r="L781" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M781" t="n">
         <v>325</v>
@@ -35899,13 +35899,13 @@
         </is>
       </c>
       <c r="J782" t="n">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="K782" t="n">
         <v>0</v>
       </c>
       <c r="L782" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M782" t="n">
         <v>145</v>
@@ -35945,13 +35945,13 @@
         </is>
       </c>
       <c r="J783" t="n">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="K783" t="n">
         <v>0</v>
       </c>
       <c r="L783" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M783" t="n">
         <v>281</v>
@@ -37100,13 +37100,13 @@
         </is>
       </c>
       <c r="J808" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="K808" t="n">
         <v>0</v>
       </c>
       <c r="L808" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M808" t="n">
         <v>18</v>
@@ -37386,13 +37386,13 @@
         </is>
       </c>
       <c r="J814" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="K814" t="n">
         <v>0</v>
       </c>
       <c r="L814" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M814" t="n">
         <v>43</v>
@@ -38081,13 +38081,13 @@
         </is>
       </c>
       <c r="J829" t="n">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="K829" t="n">
         <v>0</v>
       </c>
       <c r="L829" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M829" t="n">
         <v>295</v>

--- a/bodegas/LJ-05.xlsx
+++ b/bodegas/LJ-05.xlsx
@@ -691,10 +691,10 @@
         <v>1</v>
       </c>
       <c r="N7" t="n">
-        <v>66707.99230769199</v>
+        <v>108400.4875</v>
       </c>
       <c r="O7" t="n">
-        <v>66707.99230769199</v>
+        <v>108400.4875</v>
       </c>
       <c r="P7" t="n">
         <v>125900</v>
@@ -738,10 +738,10 @@
         <v>3</v>
       </c>
       <c r="N8" t="n">
-        <v>74676.64464285701</v>
+        <v>87122.75208333301</v>
       </c>
       <c r="O8" t="n">
-        <v>224029.933928571</v>
+        <v>261368.256249999</v>
       </c>
       <c r="P8" t="n">
         <v>144900</v>
@@ -859,22 +859,22 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M11" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N11" t="n">
         <v>27000</v>
       </c>
       <c r="O11" t="n">
-        <v>324000</v>
+        <v>270000</v>
       </c>
       <c r="P11" t="n">
         <v>20000</v>
       </c>
       <c r="Q11" t="n">
-        <v>240000</v>
+        <v>200000</v>
       </c>
     </row>
     <row r="12">
@@ -938,28 +938,28 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M13" t="n">
-        <v>246</v>
+        <v>224</v>
       </c>
       <c r="N13" t="n">
-        <v>1811.3069785884</v>
+        <v>1811.307219032</v>
       </c>
       <c r="O13" t="n">
-        <v>445581.5167327464</v>
+        <v>405732.817063168</v>
       </c>
       <c r="P13" t="n">
         <v>2600</v>
       </c>
       <c r="Q13" t="n">
-        <v>639600</v>
+        <v>582400</v>
       </c>
     </row>
     <row r="14">
@@ -1028,10 +1028,10 @@
         <v>108</v>
       </c>
       <c r="N15" t="n">
-        <v>3376.7464699454</v>
+        <v>3376.7464660832</v>
       </c>
       <c r="O15" t="n">
-        <v>364688.6187541032</v>
+        <v>364688.6183369856</v>
       </c>
       <c r="P15" t="n">
         <v>4500</v>
@@ -2265,7 +2265,7 @@
         </is>
       </c>
       <c r="J46" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -2274,19 +2274,19 @@
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N46" t="n">
         <v>1800</v>
       </c>
       <c r="O46" t="n">
-        <v>43200</v>
+        <v>41400</v>
       </c>
       <c r="P46" t="n">
         <v>2200</v>
       </c>
       <c r="Q46" t="n">
-        <v>52800</v>
+        <v>50600</v>
       </c>
     </row>
     <row r="47">
@@ -4280,10 +4280,10 @@
         <v>13</v>
       </c>
       <c r="N92" t="n">
-        <v>61666.874070081</v>
+        <v>61666.874081081</v>
       </c>
       <c r="O92" t="n">
-        <v>801669.362911053</v>
+        <v>801669.3630540529</v>
       </c>
       <c r="P92" t="n">
         <v>98900</v>
@@ -6337,22 +6337,22 @@
         <v>0</v>
       </c>
       <c r="L139" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M139" t="n">
-        <v>726</v>
+        <v>706</v>
       </c>
       <c r="N139" t="n">
         <v>2833</v>
       </c>
       <c r="O139" t="n">
-        <v>2056758</v>
+        <v>2000098</v>
       </c>
       <c r="P139" t="n">
         <v>3500</v>
       </c>
       <c r="Q139" t="n">
-        <v>2541000</v>
+        <v>2471000</v>
       </c>
     </row>
     <row r="140">
@@ -7227,10 +7227,10 @@
         <v>12</v>
       </c>
       <c r="N159" t="n">
-        <v>2582.2557508532</v>
+        <v>2582.2557353886</v>
       </c>
       <c r="O159" t="n">
-        <v>30987.0690102384</v>
+        <v>30987.0688246632</v>
       </c>
       <c r="P159" t="n">
         <v>4500</v>
@@ -7319,10 +7319,10 @@
         <v>93</v>
       </c>
       <c r="N161" t="n">
-        <v>5216.8961296772</v>
+        <v>5216.8961258041</v>
       </c>
       <c r="O161" t="n">
-        <v>485171.3400599796</v>
+        <v>485171.3396997813</v>
       </c>
       <c r="P161" t="n">
         <v>8500</v>
@@ -7543,22 +7543,22 @@
         <v>0</v>
       </c>
       <c r="L166" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="M166" t="n">
-        <v>1625</v>
+        <v>1475</v>
       </c>
       <c r="N166" t="n">
         <v>156.25</v>
       </c>
       <c r="O166" t="n">
-        <v>253906.25</v>
+        <v>230468.75</v>
       </c>
       <c r="P166" t="n">
         <v>250</v>
       </c>
       <c r="Q166" t="n">
-        <v>406250</v>
+        <v>368750</v>
       </c>
     </row>
     <row r="167">
@@ -7773,22 +7773,22 @@
         <v>0</v>
       </c>
       <c r="L171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M171" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N171" t="n">
-        <v>3795.7100075514</v>
+        <v>3795.7100075529</v>
       </c>
       <c r="O171" t="n">
-        <v>45548.5200906168</v>
+        <v>41752.8100830819</v>
       </c>
       <c r="P171" t="n">
         <v>6200</v>
       </c>
       <c r="Q171" t="n">
-        <v>74400</v>
+        <v>68200</v>
       </c>
     </row>
     <row r="172">
@@ -7819,22 +7819,22 @@
         <v>0</v>
       </c>
       <c r="L172" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M172" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="N172" t="n">
         <v>3684</v>
       </c>
       <c r="O172" t="n">
-        <v>217356</v>
+        <v>209988</v>
       </c>
       <c r="P172" t="n">
         <v>6200</v>
       </c>
       <c r="Q172" t="n">
-        <v>365800</v>
+        <v>353400</v>
       </c>
     </row>
     <row r="173">
@@ -8004,10 +8004,10 @@
         <v>66</v>
       </c>
       <c r="N176" t="n">
-        <v>4890.9300486322</v>
+        <v>4890.9300487805</v>
       </c>
       <c r="O176" t="n">
-        <v>322801.3832097252</v>
+        <v>322801.383219513</v>
       </c>
       <c r="P176" t="n">
         <v>8200</v>
@@ -8269,7 +8269,7 @@
         </is>
       </c>
       <c r="J182" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K182" t="n">
         <v>0</v>
@@ -8278,19 +8278,19 @@
         <v>0</v>
       </c>
       <c r="M182" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N182" t="n">
         <v>41064.84</v>
       </c>
       <c r="O182" t="n">
-        <v>657037.4399999999</v>
+        <v>574907.76</v>
       </c>
       <c r="P182" t="n">
         <v>68900</v>
       </c>
       <c r="Q182" t="n">
-        <v>1102400</v>
+        <v>964600</v>
       </c>
     </row>
     <row r="183">
@@ -8315,7 +8315,7 @@
         </is>
       </c>
       <c r="J183" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K183" t="n">
         <v>0</v>
@@ -8324,19 +8324,19 @@
         <v>0</v>
       </c>
       <c r="M183" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N183" t="n">
         <v>46958</v>
       </c>
       <c r="O183" t="n">
-        <v>328706</v>
+        <v>234790</v>
       </c>
       <c r="P183" t="n">
         <v>76900</v>
       </c>
       <c r="Q183" t="n">
-        <v>538300</v>
+        <v>384500</v>
       </c>
     </row>
     <row r="184">
@@ -8368,10 +8368,10 @@
         <v>82</v>
       </c>
       <c r="N184" t="n">
-        <v>2267.0481451951</v>
+        <v>2267.0481436371</v>
       </c>
       <c r="O184" t="n">
-        <v>185897.9479059982</v>
+        <v>185897.9477782422</v>
       </c>
       <c r="P184" t="n">
         <v>3900</v>
@@ -8956,22 +8956,22 @@
         <v>0</v>
       </c>
       <c r="L197" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M197" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="N197" t="n">
-        <v>14822.378850987</v>
+        <v>14822.378849611</v>
       </c>
       <c r="O197" t="n">
-        <v>459493.744380597</v>
+        <v>429848.986638719</v>
       </c>
       <c r="P197" t="n">
         <v>24900</v>
       </c>
       <c r="Q197" t="n">
-        <v>771900</v>
+        <v>722100</v>
       </c>
     </row>
     <row r="198">
@@ -9180,22 +9180,22 @@
         <v>0</v>
       </c>
       <c r="L202" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M202" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N202" t="n">
         <v>2665.4</v>
       </c>
       <c r="O202" t="n">
-        <v>21323.2</v>
+        <v>18657.8</v>
       </c>
       <c r="P202" t="n">
         <v>20900</v>
       </c>
       <c r="Q202" t="n">
-        <v>167200</v>
+        <v>146300</v>
       </c>
     </row>
     <row r="203">
@@ -9501,22 +9501,22 @@
         <v>0</v>
       </c>
       <c r="L209" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M209" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N209" t="n">
         <v>15851.61</v>
       </c>
       <c r="O209" t="n">
-        <v>110961.27</v>
+        <v>79258.05</v>
       </c>
       <c r="P209" t="n">
         <v>23900</v>
       </c>
       <c r="Q209" t="n">
-        <v>167300</v>
+        <v>119500</v>
       </c>
     </row>
     <row r="210">
@@ -9685,10 +9685,10 @@
         <v>122</v>
       </c>
       <c r="N213" t="n">
-        <v>3041.6600131579</v>
+        <v>3041.660013245</v>
       </c>
       <c r="O213" t="n">
-        <v>371082.5216052638</v>
+        <v>371082.52161589</v>
       </c>
       <c r="P213" t="n">
         <v>5500</v>
@@ -9731,10 +9731,10 @@
         <v>93</v>
       </c>
       <c r="N214" t="n">
-        <v>4372.2107896237</v>
+        <v>4372.2107901305</v>
       </c>
       <c r="O214" t="n">
-        <v>406615.6034350041</v>
+        <v>406615.6034821365</v>
       </c>
       <c r="P214" t="n">
         <v>7500</v>
@@ -9771,22 +9771,22 @@
         <v>0</v>
       </c>
       <c r="L215" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M215" t="n">
-        <v>343</v>
+        <v>319</v>
       </c>
       <c r="N215" t="n">
-        <v>1592.5668693558</v>
+        <v>1592.5667761934</v>
       </c>
       <c r="O215" t="n">
-        <v>546250.4361890394</v>
+        <v>508028.8016056946</v>
       </c>
       <c r="P215" t="n">
         <v>3900</v>
       </c>
       <c r="Q215" t="n">
-        <v>1337700</v>
+        <v>1244100</v>
       </c>
     </row>
     <row r="216">
@@ -9986,22 +9986,22 @@
         <v>0</v>
       </c>
       <c r="L220" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M220" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N220" t="n">
         <v>5633.97</v>
       </c>
       <c r="O220" t="n">
-        <v>33803.82</v>
+        <v>28169.85</v>
       </c>
       <c r="P220" t="n">
         <v>9600</v>
       </c>
       <c r="Q220" t="n">
-        <v>57600</v>
+        <v>48000</v>
       </c>
     </row>
     <row r="221">
@@ -10032,22 +10032,22 @@
         <v>0</v>
       </c>
       <c r="L221" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M221" t="n">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="N221" t="n">
         <v>6242.93</v>
       </c>
       <c r="O221" t="n">
-        <v>455733.89</v>
+        <v>424519.24</v>
       </c>
       <c r="P221" t="n">
         <v>10400</v>
       </c>
       <c r="Q221" t="n">
-        <v>759200</v>
+        <v>707200</v>
       </c>
     </row>
     <row r="222">
@@ -10264,22 +10264,22 @@
         <v>0</v>
       </c>
       <c r="L226" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M226" t="n">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="N226" t="n">
         <v>1343.77</v>
       </c>
       <c r="O226" t="n">
-        <v>274129.08</v>
+        <v>271441.54</v>
       </c>
       <c r="P226" t="n">
         <v>2500</v>
       </c>
       <c r="Q226" t="n">
-        <v>510000</v>
+        <v>505000</v>
       </c>
     </row>
     <row r="227">
@@ -10396,22 +10396,22 @@
         <v>0</v>
       </c>
       <c r="L229" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M229" t="n">
-        <v>2252</v>
+        <v>2249</v>
       </c>
       <c r="N229" t="n">
         <v>1387.55</v>
       </c>
       <c r="O229" t="n">
-        <v>3124762.6</v>
+        <v>3120599.95</v>
       </c>
       <c r="P229" t="n">
         <v>2300</v>
       </c>
       <c r="Q229" t="n">
-        <v>5179600</v>
+        <v>5172700</v>
       </c>
     </row>
     <row r="230">
@@ -10721,22 +10721,22 @@
         <v>0</v>
       </c>
       <c r="L236" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M236" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N236" t="n">
         <v>8341.030000000001</v>
       </c>
       <c r="O236" t="n">
-        <v>100092.36</v>
+        <v>83410.3</v>
       </c>
       <c r="P236" t="n">
         <v>13900</v>
       </c>
       <c r="Q236" t="n">
-        <v>166800</v>
+        <v>139000</v>
       </c>
     </row>
     <row r="237">
@@ -10808,28 +10808,28 @@
         </is>
       </c>
       <c r="J238" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="K238" t="n">
         <v>0</v>
       </c>
       <c r="L238" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M238" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="N238" t="n">
         <v>3761.6</v>
       </c>
       <c r="O238" t="n">
-        <v>86516.8</v>
+        <v>33854.4</v>
       </c>
       <c r="P238" t="n">
         <v>6900</v>
       </c>
       <c r="Q238" t="n">
-        <v>158700</v>
+        <v>62100</v>
       </c>
     </row>
     <row r="239">
@@ -10991,22 +10991,22 @@
         <v>0</v>
       </c>
       <c r="L242" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M242" t="n">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="N242" t="n">
         <v>3751</v>
       </c>
       <c r="O242" t="n">
-        <v>2689467</v>
+        <v>2685716</v>
       </c>
       <c r="P242" t="n">
         <v>6400</v>
       </c>
       <c r="Q242" t="n">
-        <v>4588800</v>
+        <v>4582400</v>
       </c>
     </row>
     <row r="243">
@@ -11040,22 +11040,22 @@
         <v>0</v>
       </c>
       <c r="L243" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M243" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="N243" t="n">
         <v>9903</v>
       </c>
       <c r="O243" t="n">
-        <v>326799</v>
+        <v>267381</v>
       </c>
       <c r="P243" t="n">
         <v>15900</v>
       </c>
       <c r="Q243" t="n">
-        <v>524700</v>
+        <v>429300</v>
       </c>
     </row>
     <row r="244">
@@ -11080,28 +11080,28 @@
         </is>
       </c>
       <c r="J244" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="K244" t="n">
         <v>0</v>
       </c>
       <c r="L244" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M244" t="n">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="N244" t="n">
-        <v>1550.1936350279</v>
+        <v>1550.1936746212</v>
       </c>
       <c r="O244" t="n">
-        <v>93011.618101674</v>
+        <v>68208.5216833328</v>
       </c>
       <c r="P244" t="n">
         <v>2500</v>
       </c>
       <c r="Q244" t="n">
-        <v>150000</v>
+        <v>110000</v>
       </c>
     </row>
     <row r="245">
@@ -11132,22 +11132,22 @@
         <v>0</v>
       </c>
       <c r="L245" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M245" t="n">
-        <v>527</v>
+        <v>511</v>
       </c>
       <c r="N245" t="n">
-        <v>2403.5118666412</v>
+        <v>2403.5119649393</v>
       </c>
       <c r="O245" t="n">
-        <v>1266650.753719912</v>
+        <v>1228194.614083982</v>
       </c>
       <c r="P245" t="n">
         <v>3500</v>
       </c>
       <c r="Q245" t="n">
-        <v>1844500</v>
+        <v>1788500</v>
       </c>
     </row>
     <row r="246">
@@ -12272,22 +12272,22 @@
         <v>0</v>
       </c>
       <c r="L271" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M271" t="n">
-        <v>225</v>
+        <v>201</v>
       </c>
       <c r="N271" t="n">
-        <v>2029.8737669513</v>
+        <v>2029.8738600103</v>
       </c>
       <c r="O271" t="n">
-        <v>456721.5975640425</v>
+        <v>408004.6458620703</v>
       </c>
       <c r="P271" t="n">
         <v>3600</v>
       </c>
       <c r="Q271" t="n">
-        <v>810000</v>
+        <v>723600</v>
       </c>
     </row>
     <row r="272">
@@ -12573,10 +12573,10 @@
         <v>64</v>
       </c>
       <c r="N278" t="n">
-        <v>2680.7396995708</v>
+        <v>2680.739699202</v>
       </c>
       <c r="O278" t="n">
-        <v>171567.3407725312</v>
+        <v>171567.340748928</v>
       </c>
       <c r="P278" t="n">
         <v>4900</v>
@@ -12980,10 +12980,10 @@
         <v>91</v>
       </c>
       <c r="N287" t="n">
-        <v>4285.1954859611</v>
+        <v>4285.1954978355</v>
       </c>
       <c r="O287" t="n">
-        <v>389952.7892224601</v>
+        <v>389952.7903030305</v>
       </c>
       <c r="P287" t="n">
         <v>6900</v>
@@ -13279,22 +13279,22 @@
         <v>0</v>
       </c>
       <c r="L294" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M294" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="N294" t="n">
-        <v>4605.2147274436</v>
+        <v>4605.2147318909</v>
       </c>
       <c r="O294" t="n">
-        <v>276312.883646616</v>
+        <v>271707.6691815631</v>
       </c>
       <c r="P294" t="n">
         <v>7600</v>
       </c>
       <c r="Q294" t="n">
-        <v>456000</v>
+        <v>448400</v>
       </c>
     </row>
     <row r="295">
@@ -13320,22 +13320,22 @@
         <v>0</v>
       </c>
       <c r="L295" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M295" t="n">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="N295" t="n">
         <v>3591.13</v>
       </c>
       <c r="O295" t="n">
-        <v>319610.57</v>
+        <v>305246.05</v>
       </c>
       <c r="P295" t="n">
         <v>6300</v>
       </c>
       <c r="Q295" t="n">
-        <v>560700</v>
+        <v>535500</v>
       </c>
     </row>
     <row r="296">
@@ -13418,10 +13418,10 @@
         <v>28</v>
       </c>
       <c r="N297" t="n">
-        <v>11562.038478261</v>
+        <v>11562.038474114</v>
       </c>
       <c r="O297" t="n">
-        <v>323737.077391308</v>
+        <v>323737.077275192</v>
       </c>
       <c r="P297" t="n">
         <v>18500</v>
@@ -13464,10 +13464,10 @@
         <v>44</v>
       </c>
       <c r="N298" t="n">
-        <v>13513.643014706</v>
+        <v>13513.643059701</v>
       </c>
       <c r="O298" t="n">
-        <v>594600.292647064</v>
+        <v>594600.294626844</v>
       </c>
       <c r="P298" t="n">
         <v>21900</v>
@@ -13959,22 +13959,22 @@
         <v>0</v>
       </c>
       <c r="L309" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M309" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="N309" t="n">
-        <v>27123.765223881</v>
+        <v>27123.765205993</v>
       </c>
       <c r="O309" t="n">
-        <v>759465.426268668</v>
+        <v>705217.895355818</v>
       </c>
       <c r="P309" t="n">
         <v>44500</v>
       </c>
       <c r="Q309" t="n">
-        <v>1246000</v>
+        <v>1157000</v>
       </c>
     </row>
     <row r="310">
@@ -14128,22 +14128,22 @@
         <v>0</v>
       </c>
       <c r="L313" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M313" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="N313" t="n">
         <v>4100.45</v>
       </c>
       <c r="O313" t="n">
-        <v>65607.2</v>
+        <v>53305.85</v>
       </c>
       <c r="P313" t="n">
         <v>26900</v>
       </c>
       <c r="Q313" t="n">
-        <v>430400</v>
+        <v>349700</v>
       </c>
     </row>
     <row r="314">
@@ -14313,10 +14313,10 @@
         <v>61</v>
       </c>
       <c r="N317" t="n">
-        <v>1561.0002330508</v>
+        <v>1561.0003094984</v>
       </c>
       <c r="O317" t="n">
-        <v>95221.0142160988</v>
+        <v>95221.0188794024</v>
       </c>
       <c r="P317" t="n">
         <v>2900</v>
@@ -14623,10 +14623,10 @@
         <v>152</v>
       </c>
       <c r="N324" t="n">
-        <v>7969.9501669196</v>
+        <v>7969.9501671733</v>
       </c>
       <c r="O324" t="n">
-        <v>1211432.425371779</v>
+        <v>1211432.425410341</v>
       </c>
       <c r="P324" t="n">
         <v>12900</v>
@@ -15529,22 +15529,22 @@
         <v>0</v>
       </c>
       <c r="L344" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M344" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="N344" t="n">
         <v>5410.72</v>
       </c>
       <c r="O344" t="n">
-        <v>476143.36</v>
+        <v>465321.92</v>
       </c>
       <c r="P344" t="n">
         <v>8700</v>
       </c>
       <c r="Q344" t="n">
-        <v>765600</v>
+        <v>748200</v>
       </c>
     </row>
     <row r="345">
@@ -15621,22 +15621,22 @@
         <v>0</v>
       </c>
       <c r="L346" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M346" t="n">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="N346" t="n">
         <v>2495.98</v>
       </c>
       <c r="O346" t="n">
-        <v>526651.78</v>
+        <v>521659.82</v>
       </c>
       <c r="P346" t="n">
         <v>4100</v>
       </c>
       <c r="Q346" t="n">
-        <v>865100</v>
+        <v>856900</v>
       </c>
     </row>
     <row r="347">
@@ -15719,10 +15719,10 @@
         <v>89</v>
       </c>
       <c r="N348" t="n">
-        <v>5218.1705520703</v>
+        <v>5218.1705541562</v>
       </c>
       <c r="O348" t="n">
-        <v>464417.1791342567</v>
+        <v>464417.1793199017</v>
       </c>
       <c r="P348" t="n">
         <v>8500</v>
@@ -15765,10 +15765,10 @@
         <v>105</v>
       </c>
       <c r="N349" t="n">
-        <v>1595.009375</v>
+        <v>1595.0093687708</v>
       </c>
       <c r="O349" t="n">
-        <v>167475.984375</v>
+        <v>167475.983720934</v>
       </c>
       <c r="P349" t="n">
         <v>2600</v>
@@ -16452,22 +16452,22 @@
         <v>0</v>
       </c>
       <c r="L364" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M364" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="N364" t="n">
-        <v>1778.4726251691</v>
+        <v>1778.4726394558</v>
       </c>
       <c r="O364" t="n">
-        <v>176068.7898917409</v>
+        <v>161841.0101904778</v>
       </c>
       <c r="P364" t="n">
         <v>4900</v>
       </c>
       <c r="Q364" t="n">
-        <v>485100</v>
+        <v>445900</v>
       </c>
     </row>
     <row r="365">
@@ -16590,22 +16590,22 @@
         <v>0</v>
       </c>
       <c r="L367" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M367" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="N367" t="n">
         <v>16058</v>
       </c>
       <c r="O367" t="n">
-        <v>1108002</v>
+        <v>1059828</v>
       </c>
       <c r="P367" t="n">
         <v>25900</v>
       </c>
       <c r="Q367" t="n">
-        <v>1787100</v>
+        <v>1709400</v>
       </c>
     </row>
     <row r="368">
@@ -18490,22 +18490,22 @@
         <v>0</v>
       </c>
       <c r="L408" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M408" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N408" t="n">
         <v>12709</v>
       </c>
       <c r="O408" t="n">
-        <v>25418</v>
+        <v>0</v>
       </c>
       <c r="P408" t="n">
         <v>20500</v>
       </c>
       <c r="Q408" t="n">
-        <v>41000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="409">
@@ -18723,22 +18723,22 @@
         <v>0</v>
       </c>
       <c r="L413" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M413" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N413" t="n">
         <v>10411</v>
       </c>
       <c r="O413" t="n">
-        <v>322741</v>
+        <v>312330</v>
       </c>
       <c r="P413" t="n">
         <v>16900</v>
       </c>
       <c r="Q413" t="n">
-        <v>523900</v>
+        <v>507000</v>
       </c>
     </row>
     <row r="414">
@@ -18907,22 +18907,22 @@
         <v>0</v>
       </c>
       <c r="L417" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M417" t="n">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="N417" t="n">
-        <v>2252.2968774194</v>
+        <v>2252.2969855832</v>
       </c>
       <c r="O417" t="n">
-        <v>132885.5157677446</v>
+        <v>105857.9583224104</v>
       </c>
       <c r="P417" t="n">
         <v>3900</v>
       </c>
       <c r="Q417" t="n">
-        <v>230100</v>
+        <v>183300</v>
       </c>
     </row>
     <row r="418">
@@ -19094,22 +19094,22 @@
         <v>0</v>
       </c>
       <c r="L421" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M421" t="n">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="N421" t="n">
-        <v>2328.1187161545</v>
+        <v>2328.1187114504</v>
       </c>
       <c r="O421" t="n">
-        <v>533139.1859993804</v>
+        <v>505201.7603847368</v>
       </c>
       <c r="P421" t="n">
         <v>4500</v>
       </c>
       <c r="Q421" t="n">
-        <v>1030500</v>
+        <v>976500</v>
       </c>
     </row>
     <row r="422">
@@ -20020,10 +20020,10 @@
         <v>98</v>
       </c>
       <c r="N441" t="n">
-        <v>3903.7365705615</v>
+        <v>3903.736684492</v>
       </c>
       <c r="O441" t="n">
-        <v>382566.183915027</v>
+        <v>382566.195080216</v>
       </c>
       <c r="P441" t="n">
         <v>7500</v>
@@ -20832,22 +20832,22 @@
         <v>0</v>
       </c>
       <c r="L459" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M459" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="N459" t="n">
         <v>8637</v>
       </c>
       <c r="O459" t="n">
-        <v>77733</v>
+        <v>25911</v>
       </c>
       <c r="P459" t="n">
         <v>14500</v>
       </c>
       <c r="Q459" t="n">
-        <v>130500</v>
+        <v>43500</v>
       </c>
     </row>
     <row r="460">
@@ -21246,22 +21246,22 @@
         <v>0</v>
       </c>
       <c r="L468" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M468" t="n">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="N468" t="n">
         <v>5682</v>
       </c>
       <c r="O468" t="n">
-        <v>494334</v>
+        <v>460242</v>
       </c>
       <c r="P468" t="n">
         <v>9900</v>
       </c>
       <c r="Q468" t="n">
-        <v>861300</v>
+        <v>801900</v>
       </c>
     </row>
     <row r="469">
@@ -21715,10 +21715,10 @@
         <v>147</v>
       </c>
       <c r="N478" t="n">
-        <v>17075.989523481</v>
+        <v>17075.989523151</v>
       </c>
       <c r="O478" t="n">
-        <v>2510170.459951707</v>
+        <v>2510170.459903197</v>
       </c>
       <c r="P478" t="n">
         <v>27500</v>
@@ -22121,22 +22121,22 @@
         <v>0</v>
       </c>
       <c r="L487" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M487" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N487" t="n">
         <v>10755</v>
       </c>
       <c r="O487" t="n">
-        <v>107550</v>
+        <v>96795</v>
       </c>
       <c r="P487" t="n">
         <v>17900</v>
       </c>
       <c r="Q487" t="n">
-        <v>179000</v>
+        <v>161100</v>
       </c>
     </row>
     <row r="488">
@@ -22213,22 +22213,22 @@
         <v>0</v>
       </c>
       <c r="L489" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M489" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="N489" t="n">
         <v>20014</v>
       </c>
       <c r="O489" t="n">
-        <v>220154</v>
+        <v>160112</v>
       </c>
       <c r="P489" t="n">
         <v>33900</v>
       </c>
       <c r="Q489" t="n">
-        <v>372900</v>
+        <v>271200</v>
       </c>
     </row>
     <row r="490">
@@ -23501,25 +23501,25 @@
         <v>184</v>
       </c>
       <c r="K517" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L517" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M517" t="n">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="N517" t="n">
-        <v>1516.0387986728</v>
+        <v>1516.0387953812</v>
       </c>
       <c r="O517" t="n">
-        <v>278951.1389557952</v>
+        <v>272886.983168616</v>
       </c>
       <c r="P517" t="n">
         <v>2300</v>
       </c>
       <c r="Q517" t="n">
-        <v>423200</v>
+        <v>414000</v>
       </c>
     </row>
     <row r="518">
@@ -23596,22 +23596,22 @@
         <v>0</v>
       </c>
       <c r="L519" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M519" t="n">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="N519" t="n">
-        <v>2458.5131821149</v>
+        <v>2458.5130781975</v>
       </c>
       <c r="O519" t="n">
-        <v>1010448.917849224</v>
+        <v>1000614.822826382</v>
       </c>
       <c r="P519" t="n">
         <v>3500</v>
       </c>
       <c r="Q519" t="n">
-        <v>1438500</v>
+        <v>1424500</v>
       </c>
     </row>
     <row r="520">
@@ -23688,22 +23688,22 @@
         <v>0</v>
       </c>
       <c r="L521" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M521" t="n">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="N521" t="n">
-        <v>1771.0904491413</v>
+        <v>1771.0904111406</v>
       </c>
       <c r="O521" t="n">
-        <v>281603.3814134667</v>
+        <v>270976.8329045118</v>
       </c>
       <c r="P521" t="n">
         <v>2500</v>
       </c>
       <c r="Q521" t="n">
-        <v>397500</v>
+        <v>382500</v>
       </c>
     </row>
     <row r="522">
@@ -23740,10 +23740,10 @@
         <v>441</v>
       </c>
       <c r="N522" t="n">
-        <v>2079.3840254521</v>
+        <v>2079.3839770425</v>
       </c>
       <c r="O522" t="n">
-        <v>917008.3552243762</v>
+        <v>917008.3338757426</v>
       </c>
       <c r="P522" t="n">
         <v>2900</v>
@@ -23832,10 +23832,10 @@
         <v>96</v>
       </c>
       <c r="N524" t="n">
-        <v>3306.5951351351</v>
+        <v>3306.5946902655</v>
       </c>
       <c r="O524" t="n">
-        <v>317433.1329729696</v>
+        <v>317433.090265488</v>
       </c>
       <c r="P524" t="n">
         <v>4900</v>
@@ -23918,22 +23918,22 @@
         <v>0</v>
       </c>
       <c r="L526" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M526" t="n">
-        <v>267</v>
+        <v>243</v>
       </c>
       <c r="N526" t="n">
-        <v>2108.7918292683</v>
+        <v>2108.7920330806</v>
       </c>
       <c r="O526" t="n">
-        <v>563047.418414636</v>
+        <v>512436.4640385858</v>
       </c>
       <c r="P526" t="n">
         <v>2900</v>
       </c>
       <c r="Q526" t="n">
-        <v>774300</v>
+        <v>704700</v>
       </c>
     </row>
     <row r="527">
@@ -23970,10 +23970,10 @@
         <v>293</v>
       </c>
       <c r="N527" t="n">
-        <v>2056.0833612094</v>
+        <v>2056.0831903662</v>
       </c>
       <c r="O527" t="n">
-        <v>602432.4248343543</v>
+        <v>602432.3747772967</v>
       </c>
       <c r="P527" t="n">
         <v>2900</v>
@@ -24062,10 +24062,10 @@
         <v>261</v>
       </c>
       <c r="N529" t="n">
-        <v>1655.9308652576</v>
+        <v>1655.9308592201</v>
       </c>
       <c r="O529" t="n">
-        <v>432197.9558322337</v>
+        <v>432197.9542564461</v>
       </c>
       <c r="P529" t="n">
         <v>2500</v>
@@ -24148,22 +24148,22 @@
         <v>0</v>
       </c>
       <c r="L531" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M531" t="n">
-        <v>304</v>
+        <v>292</v>
       </c>
       <c r="N531" t="n">
         <v>1871</v>
       </c>
       <c r="O531" t="n">
-        <v>568784</v>
+        <v>546332</v>
       </c>
       <c r="P531" t="n">
         <v>3900</v>
       </c>
       <c r="Q531" t="n">
-        <v>1185600</v>
+        <v>1138800</v>
       </c>
     </row>
     <row r="532">
@@ -24240,22 +24240,22 @@
         <v>0</v>
       </c>
       <c r="L533" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M533" t="n">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="N533" t="n">
-        <v>1592.278225957</v>
+        <v>1592.2785867446</v>
       </c>
       <c r="O533" t="n">
-        <v>238841.73389355</v>
+        <v>221326.7235574994</v>
       </c>
       <c r="P533" t="n">
         <v>2500</v>
       </c>
       <c r="Q533" t="n">
-        <v>375000</v>
+        <v>347500</v>
       </c>
     </row>
     <row r="534">
@@ -24330,22 +24330,22 @@
         <v>0</v>
       </c>
       <c r="L535" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M535" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="N535" t="n">
-        <v>1668.6302167183</v>
+        <v>1668.6318954248</v>
       </c>
       <c r="O535" t="n">
-        <v>28366.7136842111</v>
+        <v>0</v>
       </c>
       <c r="P535" t="n">
         <v>2500</v>
       </c>
       <c r="Q535" t="n">
-        <v>42500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="536">
@@ -24422,22 +24422,22 @@
         <v>0</v>
       </c>
       <c r="L537" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M537" t="n">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="N537" t="n">
-        <v>1259.2745452499</v>
+        <v>1259.2745472973</v>
       </c>
       <c r="O537" t="n">
-        <v>1192532.994351655</v>
+        <v>1190014.447195948</v>
       </c>
       <c r="P537" t="n">
         <v>1900</v>
       </c>
       <c r="Q537" t="n">
-        <v>1799300</v>
+        <v>1795500</v>
       </c>
     </row>
     <row r="538">
@@ -24601,22 +24601,22 @@
         <v>0</v>
       </c>
       <c r="L541" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M541" t="n">
-        <v>459</v>
+        <v>411</v>
       </c>
       <c r="N541" t="n">
         <v>1801</v>
       </c>
       <c r="O541" t="n">
-        <v>826659</v>
+        <v>740211</v>
       </c>
       <c r="P541" t="n">
         <v>2900</v>
       </c>
       <c r="Q541" t="n">
-        <v>1331100</v>
+        <v>1191900</v>
       </c>
     </row>
     <row r="542">
@@ -25537,7 +25537,7 @@
         </is>
       </c>
       <c r="J561" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K561" t="n">
         <v>0</v>
@@ -25546,19 +25546,19 @@
         <v>0</v>
       </c>
       <c r="M561" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N561" t="n">
-        <v>10732.242162162</v>
+        <v>10732.242222222</v>
       </c>
       <c r="O561" t="n">
-        <v>225377.085405402</v>
+        <v>214644.84444444</v>
       </c>
       <c r="P561" t="n">
         <v>25900</v>
       </c>
       <c r="Q561" t="n">
-        <v>543900</v>
+        <v>518000</v>
       </c>
     </row>
     <row r="562">
@@ -26511,22 +26511,22 @@
         <v>0</v>
       </c>
       <c r="L582" t="n">
-        <v>0</v>
+        <v>264</v>
       </c>
       <c r="M582" t="n">
-        <v>1805</v>
+        <v>1541</v>
       </c>
       <c r="N582" t="n">
-        <v>517.28943177426</v>
+        <v>517.28978235968</v>
       </c>
       <c r="O582" t="n">
-        <v>933707.4243525394</v>
+        <v>797143.5546162669</v>
       </c>
       <c r="P582" t="n">
         <v>900</v>
       </c>
       <c r="Q582" t="n">
-        <v>1624500</v>
+        <v>1386900</v>
       </c>
     </row>
     <row r="583">
@@ -26606,22 +26606,22 @@
         <v>0</v>
       </c>
       <c r="L584" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M584" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N584" t="n">
         <v>2166.81</v>
       </c>
       <c r="O584" t="n">
-        <v>75838.34999999999</v>
+        <v>73671.53999999999</v>
       </c>
       <c r="P584" t="n">
         <v>2900</v>
       </c>
       <c r="Q584" t="n">
-        <v>101500</v>
+        <v>98600</v>
       </c>
     </row>
     <row r="585">
@@ -26742,22 +26742,22 @@
         <v>0</v>
       </c>
       <c r="L587" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M587" t="n">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="N587" t="n">
-        <v>3110.8416960301</v>
+        <v>3110.8415531661</v>
       </c>
       <c r="O587" t="n">
-        <v>774599.582311495</v>
+        <v>749712.8143130301</v>
       </c>
       <c r="P587" t="n">
         <v>4500</v>
       </c>
       <c r="Q587" t="n">
-        <v>1120500</v>
+        <v>1084500</v>
       </c>
     </row>
     <row r="588">
@@ -26786,22 +26786,22 @@
         <v>0</v>
       </c>
       <c r="L588" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M588" t="n">
-        <v>1519</v>
+        <v>1495</v>
       </c>
       <c r="N588" t="n">
-        <v>703.79518287415</v>
+        <v>703.79517569581</v>
       </c>
       <c r="O588" t="n">
-        <v>1069064.882785834</v>
+        <v>1052173.787665236</v>
       </c>
       <c r="P588" t="n">
         <v>900</v>
       </c>
       <c r="Q588" t="n">
-        <v>1367100</v>
+        <v>1345500</v>
       </c>
     </row>
     <row r="589">
@@ -27074,22 +27074,22 @@
         <v>0</v>
       </c>
       <c r="L594" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M594" t="n">
-        <v>295</v>
+        <v>247</v>
       </c>
       <c r="N594" t="n">
-        <v>1595.5127943686</v>
+        <v>1595.5120596085</v>
       </c>
       <c r="O594" t="n">
-        <v>470676.274338737</v>
+        <v>394091.4787232995</v>
       </c>
       <c r="P594" t="n">
         <v>2500</v>
       </c>
       <c r="Q594" t="n">
-        <v>737500</v>
+        <v>617500</v>
       </c>
     </row>
     <row r="595">
@@ -28042,22 +28042,22 @@
         <v>0</v>
       </c>
       <c r="L614" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M614" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N614" t="n">
-        <v>14421.4</v>
+        <v>0</v>
       </c>
       <c r="O614" t="n">
-        <v>14421.4</v>
+        <v>0</v>
       </c>
       <c r="P614" t="n">
         <v>20500</v>
       </c>
       <c r="Q614" t="n">
-        <v>20500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="615">
@@ -29819,22 +29819,22 @@
         <v>0</v>
       </c>
       <c r="L651" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M651" t="n">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="N651" t="n">
         <v>4578.04</v>
       </c>
       <c r="O651" t="n">
-        <v>576833.04</v>
+        <v>549364.8</v>
       </c>
       <c r="P651" t="n">
         <v>7500</v>
       </c>
       <c r="Q651" t="n">
-        <v>945000</v>
+        <v>900000</v>
       </c>
     </row>
     <row r="652">
@@ -31198,22 +31198,22 @@
         <v>0</v>
       </c>
       <c r="L680" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M680" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="N680" t="n">
         <v>7465.9</v>
       </c>
       <c r="O680" t="n">
-        <v>164249.8</v>
+        <v>134386.2</v>
       </c>
       <c r="P680" t="n">
         <v>11900</v>
       </c>
       <c r="Q680" t="n">
-        <v>261800</v>
+        <v>214200</v>
       </c>
     </row>
     <row r="681">
@@ -32088,7 +32088,7 @@
         </is>
       </c>
       <c r="J699" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K699" t="n">
         <v>0</v>
@@ -32097,19 +32097,19 @@
         <v>0</v>
       </c>
       <c r="M699" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N699" t="n">
         <v>110520.77</v>
       </c>
       <c r="O699" t="n">
-        <v>1105207.7</v>
+        <v>994686.9300000001</v>
       </c>
       <c r="P699" t="n">
         <v>176900</v>
       </c>
       <c r="Q699" t="n">
-        <v>1769000</v>
+        <v>1592100</v>
       </c>
     </row>
     <row r="700">
@@ -32514,22 +32514,22 @@
         <v>0</v>
       </c>
       <c r="L708" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M708" t="n">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="N708" t="n">
         <v>3181.9</v>
       </c>
       <c r="O708" t="n">
-        <v>225914.9</v>
+        <v>206823.5</v>
       </c>
       <c r="P708" t="n">
         <v>5100</v>
       </c>
       <c r="Q708" t="n">
-        <v>362100</v>
+        <v>331500</v>
       </c>
     </row>
     <row r="709">
@@ -32555,22 +32555,22 @@
         <v>0</v>
       </c>
       <c r="L709" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M709" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="N709" t="n">
-        <v>1213.6821194605</v>
+        <v>1213.6821359223</v>
       </c>
       <c r="O709" t="n">
-        <v>12136.821194605</v>
+        <v>7282.0928155338</v>
       </c>
       <c r="P709" t="n">
         <v>1500</v>
       </c>
       <c r="Q709" t="n">
-        <v>15000</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="710">
@@ -32604,22 +32604,22 @@
         <v>0</v>
       </c>
       <c r="L710" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M710" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="N710" t="n">
         <v>5077</v>
       </c>
       <c r="O710" t="n">
-        <v>563547</v>
+        <v>548316</v>
       </c>
       <c r="P710" t="n">
         <v>8500</v>
       </c>
       <c r="Q710" t="n">
-        <v>943500</v>
+        <v>918000</v>
       </c>
     </row>
     <row r="711">
@@ -32834,22 +32834,22 @@
         <v>0</v>
       </c>
       <c r="L715" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M715" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N715" t="n">
         <v>19800</v>
       </c>
       <c r="O715" t="n">
-        <v>158400</v>
+        <v>138600</v>
       </c>
       <c r="P715" t="n">
         <v>24900</v>
       </c>
       <c r="Q715" t="n">
-        <v>199200</v>
+        <v>174300</v>
       </c>
     </row>
     <row r="716">
@@ -32880,22 +32880,22 @@
         <v>0</v>
       </c>
       <c r="L716" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M716" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N716" t="n">
         <v>20700</v>
       </c>
       <c r="O716" t="n">
-        <v>351900</v>
+        <v>310500</v>
       </c>
       <c r="P716" t="n">
         <v>25900</v>
       </c>
       <c r="Q716" t="n">
-        <v>440300</v>
+        <v>388500</v>
       </c>
     </row>
     <row r="717">
@@ -32920,28 +32920,28 @@
         </is>
       </c>
       <c r="J717" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K717" t="n">
         <v>0</v>
       </c>
       <c r="L717" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M717" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="N717" t="n">
         <v>15300</v>
       </c>
       <c r="O717" t="n">
-        <v>168300</v>
+        <v>107100</v>
       </c>
       <c r="P717" t="n">
         <v>19500</v>
       </c>
       <c r="Q717" t="n">
-        <v>214500</v>
+        <v>136500</v>
       </c>
     </row>
     <row r="718">
@@ -33064,22 +33064,22 @@
         <v>0</v>
       </c>
       <c r="L720" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M720" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="N720" t="n">
         <v>5220</v>
       </c>
       <c r="O720" t="n">
-        <v>125280</v>
+        <v>93960</v>
       </c>
       <c r="P720" t="n">
         <v>6900</v>
       </c>
       <c r="Q720" t="n">
-        <v>165600</v>
+        <v>124200</v>
       </c>
     </row>
     <row r="721">
@@ -33150,28 +33150,28 @@
         </is>
       </c>
       <c r="J722" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K722" t="n">
         <v>0</v>
       </c>
       <c r="L722" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M722" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="N722" t="n">
         <v>7650</v>
       </c>
       <c r="O722" t="n">
-        <v>275400</v>
+        <v>206550</v>
       </c>
       <c r="P722" t="n">
         <v>9900</v>
       </c>
       <c r="Q722" t="n">
-        <v>356400</v>
+        <v>267300</v>
       </c>
     </row>
     <row r="723">
@@ -33202,22 +33202,22 @@
         <v>0</v>
       </c>
       <c r="L723" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M723" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="N723" t="n">
         <v>13500</v>
       </c>
       <c r="O723" t="n">
-        <v>135000</v>
+        <v>81000</v>
       </c>
       <c r="P723" t="n">
         <v>16900</v>
       </c>
       <c r="Q723" t="n">
-        <v>169000</v>
+        <v>101400</v>
       </c>
     </row>
     <row r="724">
@@ -33334,28 +33334,28 @@
         </is>
       </c>
       <c r="J726" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K726" t="n">
         <v>0</v>
       </c>
       <c r="L726" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M726" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="N726" t="n">
         <v>19800</v>
       </c>
       <c r="O726" t="n">
-        <v>158400</v>
+        <v>79200</v>
       </c>
       <c r="P726" t="n">
         <v>25900</v>
       </c>
       <c r="Q726" t="n">
-        <v>207200</v>
+        <v>103600</v>
       </c>
     </row>
     <row r="727">
@@ -33432,22 +33432,22 @@
         <v>0</v>
       </c>
       <c r="L728" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="M728" t="n">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="N728" t="n">
         <v>9000</v>
       </c>
       <c r="O728" t="n">
-        <v>324000</v>
+        <v>117000</v>
       </c>
       <c r="P728" t="n">
         <v>11500</v>
       </c>
       <c r="Q728" t="n">
-        <v>414000</v>
+        <v>149500</v>
       </c>
     </row>
     <row r="729">
@@ -33564,7 +33564,7 @@
         </is>
       </c>
       <c r="J731" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="K731" t="n">
         <v>0</v>
@@ -33573,19 +33573,19 @@
         <v>0</v>
       </c>
       <c r="M731" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="N731" t="n">
         <v>31500</v>
       </c>
       <c r="O731" t="n">
-        <v>1795500</v>
+        <v>1732500</v>
       </c>
       <c r="P731" t="n">
         <v>39500</v>
       </c>
       <c r="Q731" t="n">
-        <v>2251500</v>
+        <v>2172500</v>
       </c>
     </row>
     <row r="732">
@@ -33616,22 +33616,22 @@
         <v>0</v>
       </c>
       <c r="L732" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M732" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N732" t="n">
         <v>27900</v>
       </c>
       <c r="O732" t="n">
-        <v>167400</v>
+        <v>139500</v>
       </c>
       <c r="P732" t="n">
         <v>34900</v>
       </c>
       <c r="Q732" t="n">
-        <v>209400</v>
+        <v>174500</v>
       </c>
     </row>
     <row r="733">
@@ -33708,22 +33708,22 @@
         <v>0</v>
       </c>
       <c r="L734" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M734" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N734" t="n">
-        <v>22500</v>
+        <v>0</v>
       </c>
       <c r="O734" t="n">
-        <v>22500</v>
+        <v>0</v>
       </c>
       <c r="P734" t="n">
         <v>28900</v>
       </c>
       <c r="Q734" t="n">
-        <v>28900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="735">
@@ -33984,22 +33984,22 @@
         <v>0</v>
       </c>
       <c r="L740" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M740" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="N740" t="n">
         <v>9450</v>
       </c>
       <c r="O740" t="n">
-        <v>170100</v>
+        <v>132300</v>
       </c>
       <c r="P740" t="n">
         <v>11900</v>
       </c>
       <c r="Q740" t="n">
-        <v>214200</v>
+        <v>166600</v>
       </c>
     </row>
     <row r="741">
@@ -34024,7 +34024,7 @@
         </is>
       </c>
       <c r="J741" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="K741" t="n">
         <v>0</v>
@@ -34033,19 +34033,19 @@
         <v>0</v>
       </c>
       <c r="M741" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="N741" t="n">
         <v>36000</v>
       </c>
       <c r="O741" t="n">
-        <v>1872000</v>
+        <v>1800000</v>
       </c>
       <c r="P741" t="n">
         <v>45000</v>
       </c>
       <c r="Q741" t="n">
-        <v>2340000</v>
+        <v>2250000</v>
       </c>
     </row>
     <row r="742">
@@ -34306,22 +34306,22 @@
         <v>0</v>
       </c>
       <c r="L747" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M747" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="N747" t="n">
         <v>10335.44</v>
       </c>
       <c r="O747" t="n">
-        <v>165367.04</v>
+        <v>103354.4</v>
       </c>
       <c r="P747" t="n">
         <v>10900</v>
       </c>
       <c r="Q747" t="n">
-        <v>174400</v>
+        <v>109000</v>
       </c>
     </row>
     <row r="748">
@@ -34628,22 +34628,22 @@
         <v>0</v>
       </c>
       <c r="L754" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M754" t="n">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="N754" t="n">
         <v>7480</v>
       </c>
       <c r="O754" t="n">
-        <v>1937320</v>
+        <v>1914880</v>
       </c>
       <c r="P754" t="n">
         <v>9500</v>
       </c>
       <c r="Q754" t="n">
-        <v>2460500</v>
+        <v>2432000</v>
       </c>
     </row>
     <row r="755">
@@ -34812,22 +34812,22 @@
         <v>0</v>
       </c>
       <c r="L758" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M758" t="n">
-        <v>124</v>
+        <v>107</v>
       </c>
       <c r="N758" t="n">
         <v>6336</v>
       </c>
       <c r="O758" t="n">
-        <v>785664</v>
+        <v>677952</v>
       </c>
       <c r="P758" t="n">
         <v>7500</v>
       </c>
       <c r="Q758" t="n">
-        <v>930000</v>
+        <v>802500</v>
       </c>
     </row>
     <row r="759">
@@ -34904,22 +34904,22 @@
         <v>0</v>
       </c>
       <c r="L760" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="M760" t="n">
-        <v>696</v>
+        <v>652</v>
       </c>
       <c r="N760" t="n">
         <v>2376</v>
       </c>
       <c r="O760" t="n">
-        <v>1653696</v>
+        <v>1549152</v>
       </c>
       <c r="P760" t="n">
         <v>3000</v>
       </c>
       <c r="Q760" t="n">
-        <v>2088000</v>
+        <v>1956000</v>
       </c>
     </row>
     <row r="761">
@@ -34950,22 +34950,22 @@
         <v>0</v>
       </c>
       <c r="L761" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="M761" t="n">
-        <v>273</v>
+        <v>201</v>
       </c>
       <c r="N761" t="n">
         <v>1584</v>
       </c>
       <c r="O761" t="n">
-        <v>432432</v>
+        <v>318384</v>
       </c>
       <c r="P761" t="n">
         <v>2000</v>
       </c>
       <c r="Q761" t="n">
-        <v>546000</v>
+        <v>402000</v>
       </c>
     </row>
     <row r="762">
@@ -34996,22 +34996,22 @@
         <v>0</v>
       </c>
       <c r="L762" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="M762" t="n">
-        <v>708</v>
+        <v>624</v>
       </c>
       <c r="N762" t="n">
         <v>1584</v>
       </c>
       <c r="O762" t="n">
-        <v>1121472</v>
+        <v>988416</v>
       </c>
       <c r="P762" t="n">
         <v>2000</v>
       </c>
       <c r="Q762" t="n">
-        <v>1416000</v>
+        <v>1248000</v>
       </c>
     </row>
     <row r="763">
@@ -35042,22 +35042,22 @@
         <v>0</v>
       </c>
       <c r="L763" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M763" t="n">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="N763" t="n">
         <v>3872</v>
       </c>
       <c r="O763" t="n">
-        <v>1115136</v>
+        <v>1068672</v>
       </c>
       <c r="P763" t="n">
         <v>4900</v>
       </c>
       <c r="Q763" t="n">
-        <v>1411200</v>
+        <v>1352400</v>
       </c>
     </row>
     <row r="764">
@@ -35364,22 +35364,22 @@
         <v>0</v>
       </c>
       <c r="L770" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M770" t="n">
-        <v>374</v>
+        <v>362</v>
       </c>
       <c r="N770" t="n">
         <v>3344</v>
       </c>
       <c r="O770" t="n">
-        <v>1250656</v>
+        <v>1210528</v>
       </c>
       <c r="P770" t="n">
         <v>4500</v>
       </c>
       <c r="Q770" t="n">
-        <v>1683000</v>
+        <v>1629000</v>
       </c>
     </row>
     <row r="771">
@@ -35410,22 +35410,22 @@
         <v>0</v>
       </c>
       <c r="L771" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M771" t="n">
-        <v>348</v>
+        <v>336</v>
       </c>
       <c r="N771" t="n">
         <v>3344</v>
       </c>
       <c r="O771" t="n">
-        <v>1163712</v>
+        <v>1123584</v>
       </c>
       <c r="P771" t="n">
         <v>4500</v>
       </c>
       <c r="Q771" t="n">
-        <v>1566000</v>
+        <v>1512000</v>
       </c>
     </row>
     <row r="772">
@@ -35456,22 +35456,22 @@
         <v>0</v>
       </c>
       <c r="L772" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M772" t="n">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="N772" t="n">
         <v>4400</v>
       </c>
       <c r="O772" t="n">
-        <v>739200</v>
+        <v>682000</v>
       </c>
       <c r="P772" t="n">
         <v>5900</v>
       </c>
       <c r="Q772" t="n">
-        <v>991200</v>
+        <v>914500</v>
       </c>
     </row>
     <row r="773">
@@ -35502,22 +35502,22 @@
         <v>0</v>
       </c>
       <c r="L773" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="M773" t="n">
-        <v>189</v>
+        <v>167</v>
       </c>
       <c r="N773" t="n">
         <v>3520</v>
       </c>
       <c r="O773" t="n">
-        <v>665280</v>
+        <v>587840</v>
       </c>
       <c r="P773" t="n">
         <v>4500</v>
       </c>
       <c r="Q773" t="n">
-        <v>850500</v>
+        <v>751500</v>
       </c>
     </row>
     <row r="774">
@@ -35594,22 +35594,22 @@
         <v>0</v>
       </c>
       <c r="L775" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M775" t="n">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="N775" t="n">
         <v>9240</v>
       </c>
       <c r="O775" t="n">
-        <v>6403320</v>
+        <v>6384840</v>
       </c>
       <c r="P775" t="n">
         <v>11500</v>
       </c>
       <c r="Q775" t="n">
-        <v>7969500</v>
+        <v>7946500</v>
       </c>
     </row>
     <row r="776">
@@ -35634,28 +35634,28 @@
         </is>
       </c>
       <c r="J776" t="n">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="K776" t="n">
         <v>0</v>
       </c>
       <c r="L776" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M776" t="n">
-        <v>317</v>
+        <v>291</v>
       </c>
       <c r="N776" t="n">
         <v>2288</v>
       </c>
       <c r="O776" t="n">
-        <v>725296</v>
+        <v>665808</v>
       </c>
       <c r="P776" t="n">
         <v>2900</v>
       </c>
       <c r="Q776" t="n">
-        <v>919300</v>
+        <v>843900</v>
       </c>
     </row>
     <row r="777">
@@ -35732,22 +35732,22 @@
         <v>0</v>
       </c>
       <c r="L778" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M778" t="n">
-        <v>141</v>
+        <v>117</v>
       </c>
       <c r="N778" t="n">
         <v>4576</v>
       </c>
       <c r="O778" t="n">
-        <v>645216</v>
+        <v>535392</v>
       </c>
       <c r="P778" t="n">
         <v>5900</v>
       </c>
       <c r="Q778" t="n">
-        <v>831900</v>
+        <v>690300</v>
       </c>
     </row>
     <row r="779">
@@ -35778,22 +35778,22 @@
         <v>0</v>
       </c>
       <c r="L779" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M779" t="n">
-        <v>280</v>
+        <v>266</v>
       </c>
       <c r="N779" t="n">
         <v>5280</v>
       </c>
       <c r="O779" t="n">
-        <v>1478400</v>
+        <v>1404480</v>
       </c>
       <c r="P779" t="n">
         <v>6900</v>
       </c>
       <c r="Q779" t="n">
-        <v>1932000</v>
+        <v>1835400</v>
       </c>
     </row>
     <row r="780">
@@ -37546,22 +37546,22 @@
         <v>0</v>
       </c>
       <c r="L817" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M817" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="N817" t="n">
         <v>1950.7</v>
       </c>
       <c r="O817" t="n">
-        <v>17556.3</v>
+        <v>5852.1</v>
       </c>
       <c r="P817" t="n">
         <v>7500</v>
       </c>
       <c r="Q817" t="n">
-        <v>67500</v>
+        <v>22500</v>
       </c>
     </row>
     <row r="818">
@@ -37914,22 +37914,22 @@
         <v>0</v>
       </c>
       <c r="L825" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M825" t="n">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="N825" t="n">
         <v>4550</v>
       </c>
       <c r="O825" t="n">
-        <v>1269450</v>
+        <v>1264900</v>
       </c>
       <c r="P825" t="n">
         <v>5500</v>
       </c>
       <c r="Q825" t="n">
-        <v>1534500</v>
+        <v>1529000</v>
       </c>
     </row>
     <row r="826">

--- a/bodegas/LJ-05.xlsx
+++ b/bodegas/LJ-05.xlsx
@@ -944,22 +944,22 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M13" t="n">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="N13" t="n">
-        <v>1811.307219032</v>
+        <v>1811.307345576</v>
       </c>
       <c r="O13" t="n">
-        <v>405732.817063168</v>
+        <v>387619.771953264</v>
       </c>
       <c r="P13" t="n">
         <v>2600</v>
       </c>
       <c r="Q13" t="n">
-        <v>582400</v>
+        <v>556400</v>
       </c>
     </row>
     <row r="14">
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>108</v>
+        <v>208</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1025,19 +1025,19 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>108</v>
+        <v>208</v>
       </c>
       <c r="N15" t="n">
-        <v>3376.7464660832</v>
+        <v>3376.7464651163</v>
       </c>
       <c r="O15" t="n">
-        <v>364688.6183369856</v>
+        <v>702363.2647441904</v>
       </c>
       <c r="P15" t="n">
         <v>4500</v>
       </c>
       <c r="Q15" t="n">
-        <v>486000</v>
+        <v>936000</v>
       </c>
     </row>
     <row r="16">
@@ -3904,22 +3904,22 @@
         <v>0</v>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M83" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N83" t="n">
-        <v>141416.88456026</v>
+        <v>141416.88457516</v>
       </c>
       <c r="O83" t="n">
-        <v>707084.4228013</v>
+        <v>565667.5383006399</v>
       </c>
       <c r="P83" t="n">
         <v>251900</v>
       </c>
       <c r="Q83" t="n">
-        <v>1259500</v>
+        <v>1007600</v>
       </c>
     </row>
     <row r="84">
@@ -4280,10 +4280,10 @@
         <v>12</v>
       </c>
       <c r="N92" t="n">
-        <v>61666.874092141</v>
+        <v>61666.874114441</v>
       </c>
       <c r="O92" t="n">
-        <v>740002.489105692</v>
+        <v>740002.4893732921</v>
       </c>
       <c r="P92" t="n">
         <v>98900</v>
@@ -6430,10 +6430,10 @@
         <v>1</v>
       </c>
       <c r="N141" t="n">
-        <v>4937.3101635688</v>
+        <v>4937.3101636905</v>
       </c>
       <c r="O141" t="n">
-        <v>4937.3101635688</v>
+        <v>4937.3101636905</v>
       </c>
       <c r="P141" t="n">
         <v>7500</v>
@@ -7221,22 +7221,22 @@
         <v>0</v>
       </c>
       <c r="L159" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M159" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N159" t="n">
-        <v>2582.2557353886</v>
+        <v>2582.2557142857</v>
       </c>
       <c r="O159" t="n">
-        <v>30987.0688246632</v>
+        <v>25822.557142857</v>
       </c>
       <c r="P159" t="n">
         <v>4500</v>
       </c>
       <c r="Q159" t="n">
-        <v>54000</v>
+        <v>45000</v>
       </c>
     </row>
     <row r="160">
@@ -7313,22 +7313,22 @@
         <v>0</v>
       </c>
       <c r="L161" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M161" t="n">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="N161" t="n">
-        <v>5216.8961202577</v>
+        <v>5216.8961124659</v>
       </c>
       <c r="O161" t="n">
-        <v>485171.3391839661</v>
+        <v>464303.7540094651</v>
       </c>
       <c r="P161" t="n">
         <v>8500</v>
       </c>
       <c r="Q161" t="n">
-        <v>790500</v>
+        <v>756500</v>
       </c>
     </row>
     <row r="162">
@@ -7359,22 +7359,22 @@
         <v>0</v>
       </c>
       <c r="L162" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M162" t="n">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="N162" t="n">
-        <v>3158.8608260699</v>
+        <v>3158.8608262318</v>
       </c>
       <c r="O162" t="n">
-        <v>2268062.073118188</v>
+        <v>2255426.629929505</v>
       </c>
       <c r="P162" t="n">
         <v>5600</v>
       </c>
       <c r="Q162" t="n">
-        <v>4020800</v>
+        <v>3998400</v>
       </c>
     </row>
     <row r="163">
@@ -7543,22 +7543,22 @@
         <v>0</v>
       </c>
       <c r="L166" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M166" t="n">
-        <v>1475</v>
+        <v>1445</v>
       </c>
       <c r="N166" t="n">
         <v>156.25</v>
       </c>
       <c r="O166" t="n">
-        <v>230468.75</v>
+        <v>225781.25</v>
       </c>
       <c r="P166" t="n">
         <v>250</v>
       </c>
       <c r="Q166" t="n">
-        <v>368750</v>
+        <v>361250</v>
       </c>
     </row>
     <row r="167">
@@ -7998,22 +7998,22 @@
         <v>0</v>
       </c>
       <c r="L176" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M176" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="N176" t="n">
-        <v>4890.9300487805</v>
+        <v>4890.93004884</v>
       </c>
       <c r="O176" t="n">
-        <v>322801.383219513</v>
+        <v>313019.52312576</v>
       </c>
       <c r="P176" t="n">
         <v>8200</v>
       </c>
       <c r="Q176" t="n">
-        <v>541200</v>
+        <v>524800</v>
       </c>
     </row>
     <row r="177">
@@ -8183,22 +8183,22 @@
         <v>0</v>
       </c>
       <c r="L180" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M180" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="N180" t="n">
         <v>1203.38</v>
       </c>
       <c r="O180" t="n">
-        <v>26474.36</v>
+        <v>7220.280000000001</v>
       </c>
       <c r="P180" t="n">
         <v>1900</v>
       </c>
       <c r="Q180" t="n">
-        <v>41800</v>
+        <v>11400</v>
       </c>
     </row>
     <row r="181">
@@ -8454,22 +8454,22 @@
         <v>0</v>
       </c>
       <c r="L186" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M186" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="N186" t="n">
         <v>5667.94</v>
       </c>
       <c r="O186" t="n">
-        <v>328740.52</v>
+        <v>317404.64</v>
       </c>
       <c r="P186" t="n">
         <v>9500</v>
       </c>
       <c r="Q186" t="n">
-        <v>551000</v>
+        <v>532000</v>
       </c>
     </row>
     <row r="187">
@@ -8729,10 +8729,10 @@
         <v>5</v>
       </c>
       <c r="N192" t="n">
-        <v>3594.2540186916</v>
+        <v>3594.254</v>
       </c>
       <c r="O192" t="n">
-        <v>17971.270093458</v>
+        <v>17971.27</v>
       </c>
       <c r="P192" t="n">
         <v>6500</v>
@@ -8864,22 +8864,22 @@
         <v>0</v>
       </c>
       <c r="L195" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M195" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N195" t="n">
         <v>4891</v>
       </c>
       <c r="O195" t="n">
-        <v>102711</v>
+        <v>92929</v>
       </c>
       <c r="P195" t="n">
         <v>8200</v>
       </c>
       <c r="Q195" t="n">
-        <v>172200</v>
+        <v>155800</v>
       </c>
     </row>
     <row r="196">
@@ -9685,10 +9685,10 @@
         <v>122</v>
       </c>
       <c r="N213" t="n">
-        <v>3041.660013245</v>
+        <v>3041.6600132802</v>
       </c>
       <c r="O213" t="n">
-        <v>371082.52161589</v>
+        <v>371082.5216201844</v>
       </c>
       <c r="P213" t="n">
         <v>5500</v>
@@ -9771,22 +9771,22 @@
         <v>0</v>
       </c>
       <c r="L215" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M215" t="n">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="N215" t="n">
-        <v>1592.566762142</v>
+        <v>1592.5667254408</v>
       </c>
       <c r="O215" t="n">
-        <v>508028.797123298</v>
+        <v>501658.518513852</v>
       </c>
       <c r="P215" t="n">
         <v>3900</v>
       </c>
       <c r="Q215" t="n">
-        <v>1244100</v>
+        <v>1228500</v>
       </c>
     </row>
     <row r="216">
@@ -10130,22 +10130,22 @@
         <v>0</v>
       </c>
       <c r="L223" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M223" t="n">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="N223" t="n">
         <v>1770.37</v>
       </c>
       <c r="O223" t="n">
-        <v>354074</v>
+        <v>341681.41</v>
       </c>
       <c r="P223" t="n">
         <v>3900</v>
       </c>
       <c r="Q223" t="n">
-        <v>780000</v>
+        <v>752700</v>
       </c>
     </row>
     <row r="224">
@@ -10352,22 +10352,22 @@
         <v>0</v>
       </c>
       <c r="L228" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M228" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="N228" t="n">
         <v>9414.309999999999</v>
       </c>
       <c r="O228" t="n">
-        <v>771973.4199999999</v>
+        <v>762559.11</v>
       </c>
       <c r="P228" t="n">
         <v>16900</v>
       </c>
       <c r="Q228" t="n">
-        <v>1385800</v>
+        <v>1368900</v>
       </c>
     </row>
     <row r="229">
@@ -10991,22 +10991,22 @@
         <v>0</v>
       </c>
       <c r="L242" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M242" t="n">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="N242" t="n">
         <v>3751</v>
       </c>
       <c r="O242" t="n">
-        <v>2685716</v>
+        <v>2681965</v>
       </c>
       <c r="P242" t="n">
         <v>6400</v>
       </c>
       <c r="Q242" t="n">
-        <v>4582400</v>
+        <v>4576000</v>
       </c>
     </row>
     <row r="243">
@@ -11092,10 +11092,10 @@
         <v>44</v>
       </c>
       <c r="N244" t="n">
-        <v>1550.1936753491</v>
+        <v>1550.1936973199</v>
       </c>
       <c r="O244" t="n">
-        <v>68208.5217153604</v>
+        <v>68208.52268207559</v>
       </c>
       <c r="P244" t="n">
         <v>2500</v>
@@ -11138,10 +11138,10 @@
         <v>511</v>
       </c>
       <c r="N245" t="n">
-        <v>2403.5119996136</v>
+        <v>2403.5120742613</v>
       </c>
       <c r="O245" t="n">
-        <v>1228194.63180255</v>
+        <v>1228194.669947524</v>
       </c>
       <c r="P245" t="n">
         <v>3500</v>
@@ -11940,10 +11940,10 @@
         <v>26</v>
       </c>
       <c r="N263" t="n">
-        <v>4196.8725291181</v>
+        <v>4196.8725298197</v>
       </c>
       <c r="O263" t="n">
-        <v>109118.6857570706</v>
+        <v>109118.6857753122</v>
       </c>
       <c r="P263" t="n">
         <v>5900</v>
@@ -12068,10 +12068,10 @@
         <v>1</v>
       </c>
       <c r="N266" t="n">
-        <v>7537.4721969697</v>
+        <v>7537.4722307692</v>
       </c>
       <c r="O266" t="n">
-        <v>7537.4721969697</v>
+        <v>7537.4722307692</v>
       </c>
       <c r="P266" t="n">
         <v>8900</v>
@@ -12278,10 +12278,10 @@
         <v>201</v>
       </c>
       <c r="N271" t="n">
-        <v>2029.8738129131</v>
+        <v>2029.8738600103</v>
       </c>
       <c r="O271" t="n">
-        <v>408004.6363955331</v>
+        <v>408004.6458620703</v>
       </c>
       <c r="P271" t="n">
         <v>3600</v>
@@ -12919,7 +12919,7 @@
         </is>
       </c>
       <c r="J286" t="n">
-        <v>106</v>
+        <v>478</v>
       </c>
       <c r="K286" t="n">
         <v>0</v>
@@ -12928,19 +12928,19 @@
         <v>0</v>
       </c>
       <c r="M286" t="n">
-        <v>106</v>
+        <v>478</v>
       </c>
       <c r="N286" t="n">
         <v>3877.89</v>
       </c>
       <c r="O286" t="n">
-        <v>411056.34</v>
+        <v>1853631.42</v>
       </c>
       <c r="P286" t="n">
         <v>6500</v>
       </c>
       <c r="Q286" t="n">
-        <v>689000</v>
+        <v>3107000</v>
       </c>
     </row>
     <row r="287">
@@ -12980,10 +12980,10 @@
         <v>91</v>
       </c>
       <c r="N287" t="n">
-        <v>4285.1955097614</v>
+        <v>4285.1955337691</v>
       </c>
       <c r="O287" t="n">
-        <v>389952.7913882874</v>
+        <v>389952.7935729881</v>
       </c>
       <c r="P287" t="n">
         <v>6900</v>
@@ -13279,22 +13279,22 @@
         <v>0</v>
       </c>
       <c r="L294" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M294" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="N294" t="n">
-        <v>4605.2147318909</v>
+        <v>4605.2147408106</v>
       </c>
       <c r="O294" t="n">
-        <v>271707.6691815631</v>
+        <v>262497.2402262042</v>
       </c>
       <c r="P294" t="n">
         <v>7600</v>
       </c>
       <c r="Q294" t="n">
-        <v>448400</v>
+        <v>433200</v>
       </c>
     </row>
     <row r="295">
@@ -13913,22 +13913,22 @@
         <v>0</v>
       </c>
       <c r="L308" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M308" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N308" t="n">
         <v>29631.46</v>
       </c>
       <c r="O308" t="n">
-        <v>207420.22</v>
+        <v>177788.76</v>
       </c>
       <c r="P308" t="n">
         <v>65500</v>
       </c>
       <c r="Q308" t="n">
-        <v>458500</v>
+        <v>393000</v>
       </c>
     </row>
     <row r="309">
@@ -14307,22 +14307,22 @@
         <v>0</v>
       </c>
       <c r="L317" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M317" t="n">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="N317" t="n">
-        <v>1561.0003205128</v>
+        <v>1561.0009152542</v>
       </c>
       <c r="O317" t="n">
-        <v>92099.0189102552</v>
+        <v>70245.041186439</v>
       </c>
       <c r="P317" t="n">
         <v>2900</v>
       </c>
       <c r="Q317" t="n">
-        <v>171100</v>
+        <v>130500</v>
       </c>
     </row>
     <row r="318">
@@ -14887,10 +14887,10 @@
         <v>22</v>
       </c>
       <c r="N330" t="n">
-        <v>548.14720461095</v>
+        <v>548.1471884058</v>
       </c>
       <c r="O330" t="n">
-        <v>12059.2385014409</v>
+        <v>12059.2381449276</v>
       </c>
       <c r="P330" t="n">
         <v>2000</v>
@@ -15529,22 +15529,22 @@
         <v>0</v>
       </c>
       <c r="L344" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M344" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="N344" t="n">
         <v>5410.72</v>
       </c>
       <c r="O344" t="n">
-        <v>465321.92</v>
+        <v>443679.04</v>
       </c>
       <c r="P344" t="n">
         <v>8700</v>
       </c>
       <c r="Q344" t="n">
-        <v>748200</v>
+        <v>713400</v>
       </c>
     </row>
     <row r="345">
@@ -16458,10 +16458,10 @@
         <v>91</v>
       </c>
       <c r="N364" t="n">
-        <v>1778.4726299141</v>
+        <v>1778.4726458554</v>
       </c>
       <c r="O364" t="n">
-        <v>161841.0093221831</v>
+        <v>161841.0107728414</v>
       </c>
       <c r="P364" t="n">
         <v>4900</v>
@@ -17978,7 +17978,7 @@
         </is>
       </c>
       <c r="J397" t="n">
-        <v>720</v>
+        <v>670</v>
       </c>
       <c r="K397" t="n">
         <v>0</v>
@@ -17987,19 +17987,19 @@
         <v>0</v>
       </c>
       <c r="M397" t="n">
-        <v>720</v>
+        <v>670</v>
       </c>
       <c r="N397" t="n">
         <v>239.91</v>
       </c>
       <c r="O397" t="n">
-        <v>172735.2</v>
+        <v>160739.7</v>
       </c>
       <c r="P397" t="n">
         <v>300</v>
       </c>
       <c r="Q397" t="n">
-        <v>216000</v>
+        <v>201000</v>
       </c>
     </row>
     <row r="398">
@@ -19054,10 +19054,10 @@
         <v>217</v>
       </c>
       <c r="N420" t="n">
-        <v>2328.1187114504</v>
+        <v>2328.1187098747</v>
       </c>
       <c r="O420" t="n">
-        <v>505201.7603847368</v>
+        <v>505201.7600428099</v>
       </c>
       <c r="P420" t="n">
         <v>4500</v>
@@ -21387,22 +21387,22 @@
         <v>0</v>
       </c>
       <c r="L471" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M471" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N471" t="n">
         <v>753</v>
       </c>
       <c r="O471" t="n">
-        <v>1506</v>
+        <v>0</v>
       </c>
       <c r="P471" t="n">
         <v>1600</v>
       </c>
       <c r="Q471" t="n">
-        <v>3200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="472">
@@ -21669,10 +21669,10 @@
         <v>147</v>
       </c>
       <c r="N477" t="n">
-        <v>17075.989523151</v>
+        <v>17075.989522822</v>
       </c>
       <c r="O477" t="n">
-        <v>2510170.459903197</v>
+        <v>2510170.459854834</v>
       </c>
       <c r="P477" t="n">
         <v>27500</v>
@@ -22719,22 +22719,22 @@
         <v>0</v>
       </c>
       <c r="L500" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M500" t="n">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="N500" t="n">
         <v>1326</v>
       </c>
       <c r="O500" t="n">
-        <v>478686</v>
+        <v>474708</v>
       </c>
       <c r="P500" t="n">
         <v>2500</v>
       </c>
       <c r="Q500" t="n">
-        <v>902500</v>
+        <v>895000</v>
       </c>
     </row>
     <row r="501">
@@ -23464,10 +23464,10 @@
         <v>180</v>
       </c>
       <c r="N516" t="n">
-        <v>1516.0387982037</v>
+        <v>1516.0387951453</v>
       </c>
       <c r="O516" t="n">
-        <v>272886.983676666</v>
+        <v>272886.983126154</v>
       </c>
       <c r="P516" t="n">
         <v>2300</v>
@@ -23556,10 +23556,10 @@
         <v>407</v>
       </c>
       <c r="N518" t="n">
-        <v>2458.5131328074</v>
+        <v>2458.5130759032</v>
       </c>
       <c r="O518" t="n">
-        <v>1000614.845052612</v>
+        <v>1000614.821892602</v>
       </c>
       <c r="P518" t="n">
         <v>3500</v>
@@ -23694,10 +23694,10 @@
         <v>441</v>
       </c>
       <c r="N521" t="n">
-        <v>2079.3840254521</v>
+        <v>2079.3839709361</v>
       </c>
       <c r="O521" t="n">
-        <v>917008.3552243762</v>
+        <v>917008.3311828201</v>
       </c>
       <c r="P521" t="n">
         <v>2900</v>
@@ -23740,10 +23740,10 @@
         <v>283</v>
       </c>
       <c r="N522" t="n">
-        <v>1803.0156051587</v>
+        <v>1803.0156237558</v>
       </c>
       <c r="O522" t="n">
-        <v>510253.4162599121</v>
+        <v>510253.4215228914</v>
       </c>
       <c r="P522" t="n">
         <v>2500</v>
@@ -23786,10 +23786,10 @@
         <v>96</v>
       </c>
       <c r="N523" t="n">
-        <v>3306.5951153324</v>
+        <v>3306.5946745562</v>
       </c>
       <c r="O523" t="n">
-        <v>317433.1310719104</v>
+        <v>317433.0887573952</v>
       </c>
       <c r="P523" t="n">
         <v>4900</v>
@@ -23832,10 +23832,10 @@
         <v>535</v>
       </c>
       <c r="N524" t="n">
-        <v>2122.1638529227</v>
+        <v>2122.1638509903</v>
       </c>
       <c r="O524" t="n">
-        <v>1135357.661313644</v>
+        <v>1135357.66027981</v>
       </c>
       <c r="P524" t="n">
         <v>2900</v>
@@ -23878,10 +23878,10 @@
         <v>243</v>
       </c>
       <c r="N525" t="n">
-        <v>2108.7920330806</v>
+        <v>2108.792083045</v>
       </c>
       <c r="O525" t="n">
-        <v>512436.4640385858</v>
+        <v>512436.476179935</v>
       </c>
       <c r="P525" t="n">
         <v>2900</v>
@@ -23924,10 +23924,10 @@
         <v>293</v>
       </c>
       <c r="N526" t="n">
-        <v>2056.0831723454</v>
+        <v>2056.0829891304</v>
       </c>
       <c r="O526" t="n">
-        <v>602432.3694972021</v>
+        <v>602432.3158152072</v>
       </c>
       <c r="P526" t="n">
         <v>2900</v>
@@ -23970,10 +23970,10 @@
         <v>329</v>
       </c>
       <c r="N527" t="n">
-        <v>3224.5688003933</v>
+        <v>3224.5688090551</v>
       </c>
       <c r="O527" t="n">
-        <v>1060883.135329396</v>
+        <v>1060883.138179128</v>
       </c>
       <c r="P527" t="n">
         <v>4500</v>
@@ -24016,10 +24016,10 @@
         <v>261</v>
       </c>
       <c r="N528" t="n">
-        <v>1655.9308592201</v>
+        <v>1655.9308045213</v>
       </c>
       <c r="O528" t="n">
-        <v>432197.9542564461</v>
+        <v>432197.9399800593</v>
       </c>
       <c r="P528" t="n">
         <v>2500</v>
@@ -24200,10 +24200,10 @@
         <v>139</v>
       </c>
       <c r="N532" t="n">
-        <v>1592.2786119257</v>
+        <v>1592.2787749004</v>
       </c>
       <c r="O532" t="n">
-        <v>221326.7270576723</v>
+        <v>221326.7497111556</v>
       </c>
       <c r="P532" t="n">
         <v>2500</v>
@@ -24290,10 +24290,10 @@
         <v>15</v>
       </c>
       <c r="N534" t="n">
-        <v>2546.9839186296</v>
+        <v>2546.9838660907</v>
       </c>
       <c r="O534" t="n">
-        <v>38204.758779444</v>
+        <v>38204.7579913605</v>
       </c>
       <c r="P534" t="n">
         <v>3900</v>
@@ -24336,10 +24336,10 @@
         <v>945</v>
       </c>
       <c r="N535" t="n">
-        <v>1259.2745472973</v>
+        <v>1259.274561681</v>
       </c>
       <c r="O535" t="n">
-        <v>1190014.447195948</v>
+        <v>1190014.460788545</v>
       </c>
       <c r="P535" t="n">
         <v>1900</v>
@@ -24509,22 +24509,22 @@
         <v>0</v>
       </c>
       <c r="L539" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M539" t="n">
-        <v>411</v>
+        <v>402</v>
       </c>
       <c r="N539" t="n">
         <v>1801</v>
       </c>
       <c r="O539" t="n">
-        <v>740211</v>
+        <v>724002</v>
       </c>
       <c r="P539" t="n">
         <v>2900</v>
       </c>
       <c r="Q539" t="n">
-        <v>1191900</v>
+        <v>1165800</v>
       </c>
     </row>
     <row r="540">
@@ -26419,22 +26419,22 @@
         <v>0</v>
       </c>
       <c r="L580" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M580" t="n">
-        <v>1511</v>
+        <v>1487</v>
       </c>
       <c r="N580" t="n">
-        <v>517.2898138359</v>
+        <v>517.28990087531</v>
       </c>
       <c r="O580" t="n">
-        <v>781624.9087060449</v>
+        <v>769210.0826015859</v>
       </c>
       <c r="P580" t="n">
         <v>900</v>
       </c>
       <c r="Q580" t="n">
-        <v>1359900</v>
+        <v>1338300</v>
       </c>
     </row>
     <row r="581">
@@ -26650,22 +26650,22 @@
         <v>0</v>
       </c>
       <c r="L585" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M585" t="n">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="N585" t="n">
-        <v>3110.8415227818</v>
+        <v>3110.8414032101</v>
       </c>
       <c r="O585" t="n">
-        <v>749712.8069904138</v>
+        <v>746601.936770424</v>
       </c>
       <c r="P585" t="n">
         <v>4500</v>
       </c>
       <c r="Q585" t="n">
-        <v>1084500</v>
+        <v>1080000</v>
       </c>
     </row>
     <row r="586">
@@ -26694,22 +26694,22 @@
         <v>0</v>
       </c>
       <c r="L586" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M586" t="n">
-        <v>1495</v>
+        <v>1471</v>
       </c>
       <c r="N586" t="n">
-        <v>703.795175</v>
+        <v>703.79516919374</v>
       </c>
       <c r="O586" t="n">
-        <v>1052173.786625</v>
+        <v>1035282.693883992</v>
       </c>
       <c r="P586" t="n">
         <v>900</v>
       </c>
       <c r="Q586" t="n">
-        <v>1345500</v>
+        <v>1323900</v>
       </c>
     </row>
     <row r="587">
@@ -26988,10 +26988,10 @@
         <v>235</v>
       </c>
       <c r="N592" t="n">
-        <v>1595.5123423818</v>
+        <v>1595.5119633274</v>
       </c>
       <c r="O592" t="n">
-        <v>374945.400459723</v>
+        <v>374945.311381939</v>
       </c>
       <c r="P592" t="n">
         <v>2500</v>
@@ -30866,22 +30866,22 @@
         <v>0</v>
       </c>
       <c r="L673" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M673" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N673" t="n">
         <v>1024.29</v>
       </c>
       <c r="O673" t="n">
-        <v>7170.03</v>
+        <v>5121.45</v>
       </c>
       <c r="P673" t="n">
         <v>2900</v>
       </c>
       <c r="Q673" t="n">
-        <v>20300</v>
+        <v>14500</v>
       </c>
     </row>
     <row r="674">
@@ -30915,22 +30915,22 @@
         <v>0</v>
       </c>
       <c r="L674" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M674" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="N674" t="n">
         <v>711.48</v>
       </c>
       <c r="O674" t="n">
-        <v>65456.16</v>
+        <v>64033.2</v>
       </c>
       <c r="P674" t="n">
         <v>2500</v>
       </c>
       <c r="Q674" t="n">
-        <v>230000</v>
+        <v>225000</v>
       </c>
     </row>
     <row r="675">
@@ -31057,22 +31057,22 @@
         <v>0</v>
       </c>
       <c r="L677" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M677" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N677" t="n">
         <v>7465.9</v>
       </c>
       <c r="O677" t="n">
-        <v>134386.2</v>
+        <v>119454.4</v>
       </c>
       <c r="P677" t="n">
         <v>11900</v>
       </c>
       <c r="Q677" t="n">
-        <v>214200</v>
+        <v>190400</v>
       </c>
     </row>
     <row r="678">
@@ -31193,28 +31193,28 @@
         </is>
       </c>
       <c r="J680" t="n">
-        <v>126</v>
+        <v>326</v>
       </c>
       <c r="K680" t="n">
         <v>0</v>
       </c>
       <c r="L680" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M680" t="n">
-        <v>126</v>
+        <v>320</v>
       </c>
       <c r="N680" t="n">
-        <v>7046.9398281418</v>
+        <v>7046.93982792</v>
       </c>
       <c r="O680" t="n">
-        <v>887914.4183458667</v>
+        <v>2255020.7449344</v>
       </c>
       <c r="P680" t="n">
         <v>9900</v>
       </c>
       <c r="Q680" t="n">
-        <v>1247400</v>
+        <v>3168000</v>
       </c>
     </row>
     <row r="681">
@@ -31863,22 +31863,22 @@
         <v>0</v>
       </c>
       <c r="L694" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M694" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="N694" t="n">
         <v>2000</v>
       </c>
       <c r="O694" t="n">
-        <v>174000</v>
+        <v>168000</v>
       </c>
       <c r="P694" t="n">
         <v>4100</v>
       </c>
       <c r="Q694" t="n">
-        <v>356700</v>
+        <v>344400</v>
       </c>
     </row>
     <row r="695">
@@ -32373,22 +32373,22 @@
         <v>0</v>
       </c>
       <c r="L705" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M705" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N705" t="n">
         <v>3181.9</v>
       </c>
       <c r="O705" t="n">
-        <v>197277.8</v>
+        <v>194095.9</v>
       </c>
       <c r="P705" t="n">
         <v>5100</v>
       </c>
       <c r="Q705" t="n">
-        <v>316200</v>
+        <v>311100</v>
       </c>
     </row>
     <row r="706">
@@ -32463,22 +32463,22 @@
         <v>0</v>
       </c>
       <c r="L707" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M707" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="N707" t="n">
         <v>5077</v>
       </c>
       <c r="O707" t="n">
-        <v>548316</v>
+        <v>533085</v>
       </c>
       <c r="P707" t="n">
         <v>8500</v>
       </c>
       <c r="Q707" t="n">
-        <v>918000</v>
+        <v>892500</v>
       </c>
     </row>
     <row r="708">
@@ -32509,22 +32509,22 @@
         <v>0</v>
       </c>
       <c r="L708" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M708" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="N708" t="n">
         <v>1600</v>
       </c>
       <c r="O708" t="n">
-        <v>115200</v>
+        <v>110400</v>
       </c>
       <c r="P708" t="n">
         <v>3500</v>
       </c>
       <c r="Q708" t="n">
-        <v>252000</v>
+        <v>241500</v>
       </c>
     </row>
     <row r="709">
@@ -33291,22 +33291,22 @@
         <v>0</v>
       </c>
       <c r="L725" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M725" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="N725" t="n">
         <v>9000</v>
       </c>
       <c r="O725" t="n">
-        <v>117000</v>
+        <v>81000</v>
       </c>
       <c r="P725" t="n">
         <v>11500</v>
       </c>
       <c r="Q725" t="n">
-        <v>149500</v>
+        <v>103500</v>
       </c>
     </row>
     <row r="726">
@@ -34211,22 +34211,22 @@
         <v>0</v>
       </c>
       <c r="L745" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M745" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N745" t="n">
         <v>9708.190000000001</v>
       </c>
       <c r="O745" t="n">
-        <v>19416.38</v>
+        <v>0</v>
       </c>
       <c r="P745" t="n">
         <v>10200</v>
       </c>
       <c r="Q745" t="n">
-        <v>20400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="746">
@@ -34441,22 +34441,22 @@
         <v>0</v>
       </c>
       <c r="L750" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M750" t="n">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="N750" t="n">
         <v>7480</v>
       </c>
       <c r="O750" t="n">
-        <v>1914880</v>
+        <v>1892440</v>
       </c>
       <c r="P750" t="n">
         <v>9500</v>
       </c>
       <c r="Q750" t="n">
-        <v>2432000</v>
+        <v>2403500</v>
       </c>
     </row>
     <row r="751">
@@ -34625,22 +34625,22 @@
         <v>0</v>
       </c>
       <c r="L754" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M754" t="n">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="N754" t="n">
         <v>6336</v>
       </c>
       <c r="O754" t="n">
-        <v>677952</v>
+        <v>633600</v>
       </c>
       <c r="P754" t="n">
         <v>7500</v>
       </c>
       <c r="Q754" t="n">
-        <v>802500</v>
+        <v>750000</v>
       </c>
     </row>
     <row r="755">
@@ -34671,22 +34671,22 @@
         <v>0</v>
       </c>
       <c r="L755" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M755" t="n">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="N755" t="n">
         <v>5280</v>
       </c>
       <c r="O755" t="n">
-        <v>675840</v>
+        <v>654720</v>
       </c>
       <c r="P755" t="n">
         <v>6900</v>
       </c>
       <c r="Q755" t="n">
-        <v>883200</v>
+        <v>855600</v>
       </c>
     </row>
     <row r="756">
@@ -34763,22 +34763,22 @@
         <v>0</v>
       </c>
       <c r="L757" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M757" t="n">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="N757" t="n">
         <v>1584</v>
       </c>
       <c r="O757" t="n">
-        <v>313632</v>
+        <v>308880</v>
       </c>
       <c r="P757" t="n">
         <v>2000</v>
       </c>
       <c r="Q757" t="n">
-        <v>396000</v>
+        <v>390000</v>
       </c>
     </row>
     <row r="758">
@@ -34809,22 +34809,22 @@
         <v>0</v>
       </c>
       <c r="L758" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M758" t="n">
-        <v>621</v>
+        <v>615</v>
       </c>
       <c r="N758" t="n">
         <v>1584</v>
       </c>
       <c r="O758" t="n">
-        <v>983664</v>
+        <v>974160</v>
       </c>
       <c r="P758" t="n">
         <v>2000</v>
       </c>
       <c r="Q758" t="n">
-        <v>1242000</v>
+        <v>1230000</v>
       </c>
     </row>
     <row r="759">
@@ -34947,22 +34947,22 @@
         <v>0</v>
       </c>
       <c r="L761" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M761" t="n">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="N761" t="n">
         <v>3872</v>
       </c>
       <c r="O761" t="n">
-        <v>1068672</v>
+        <v>1057056</v>
       </c>
       <c r="P761" t="n">
         <v>4900</v>
       </c>
       <c r="Q761" t="n">
-        <v>1352400</v>
+        <v>1337700</v>
       </c>
     </row>
     <row r="762">
@@ -35177,22 +35177,22 @@
         <v>0</v>
       </c>
       <c r="L766" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M766" t="n">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="N766" t="n">
         <v>3344</v>
       </c>
       <c r="O766" t="n">
-        <v>1210528</v>
+        <v>1207184</v>
       </c>
       <c r="P766" t="n">
         <v>4500</v>
       </c>
       <c r="Q766" t="n">
-        <v>1629000</v>
+        <v>1624500</v>
       </c>
     </row>
     <row r="767">
@@ -35223,22 +35223,22 @@
         <v>0</v>
       </c>
       <c r="L767" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M767" t="n">
-        <v>336</v>
+        <v>320</v>
       </c>
       <c r="N767" t="n">
         <v>3344</v>
       </c>
       <c r="O767" t="n">
-        <v>1123584</v>
+        <v>1070080</v>
       </c>
       <c r="P767" t="n">
         <v>4500</v>
       </c>
       <c r="Q767" t="n">
-        <v>1512000</v>
+        <v>1440000</v>
       </c>
     </row>
     <row r="768">
@@ -35269,22 +35269,22 @@
         <v>0</v>
       </c>
       <c r="L768" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M768" t="n">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="N768" t="n">
         <v>4400</v>
       </c>
       <c r="O768" t="n">
-        <v>682000</v>
+        <v>668800</v>
       </c>
       <c r="P768" t="n">
         <v>5900</v>
       </c>
       <c r="Q768" t="n">
-        <v>914500</v>
+        <v>896800</v>
       </c>
     </row>
     <row r="769">
@@ -35315,22 +35315,22 @@
         <v>0</v>
       </c>
       <c r="L769" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M769" t="n">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="N769" t="n">
         <v>3520</v>
       </c>
       <c r="O769" t="n">
-        <v>587840</v>
+        <v>566720</v>
       </c>
       <c r="P769" t="n">
         <v>4500</v>
       </c>
       <c r="Q769" t="n">
-        <v>751500</v>
+        <v>724500</v>
       </c>
     </row>
     <row r="770">
@@ -35407,22 +35407,22 @@
         <v>0</v>
       </c>
       <c r="L771" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M771" t="n">
-        <v>686</v>
+        <v>680</v>
       </c>
       <c r="N771" t="n">
         <v>9240</v>
       </c>
       <c r="O771" t="n">
-        <v>6338640</v>
+        <v>6283200</v>
       </c>
       <c r="P771" t="n">
         <v>11500</v>
       </c>
       <c r="Q771" t="n">
-        <v>7889000</v>
+        <v>7820000</v>
       </c>
     </row>
     <row r="772">
@@ -35453,22 +35453,22 @@
         <v>0</v>
       </c>
       <c r="L772" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M772" t="n">
-        <v>277</v>
+        <v>253</v>
       </c>
       <c r="N772" t="n">
         <v>2288</v>
       </c>
       <c r="O772" t="n">
-        <v>633776</v>
+        <v>578864</v>
       </c>
       <c r="P772" t="n">
         <v>2900</v>
       </c>
       <c r="Q772" t="n">
-        <v>803300</v>
+        <v>733700</v>
       </c>
     </row>
     <row r="773">
@@ -35545,22 +35545,22 @@
         <v>0</v>
       </c>
       <c r="L774" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M774" t="n">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="N774" t="n">
         <v>4576</v>
       </c>
       <c r="O774" t="n">
-        <v>535392</v>
+        <v>507936</v>
       </c>
       <c r="P774" t="n">
         <v>5900</v>
       </c>
       <c r="Q774" t="n">
-        <v>690300</v>
+        <v>654900</v>
       </c>
     </row>
     <row r="775">
@@ -35591,22 +35591,22 @@
         <v>0</v>
       </c>
       <c r="L775" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M775" t="n">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="N775" t="n">
         <v>5280</v>
       </c>
       <c r="O775" t="n">
-        <v>1404480</v>
+        <v>1393920</v>
       </c>
       <c r="P775" t="n">
         <v>6900</v>
       </c>
       <c r="Q775" t="n">
-        <v>1835400</v>
+        <v>1821600</v>
       </c>
     </row>
     <row r="776">
@@ -36889,22 +36889,22 @@
         <v>0</v>
       </c>
       <c r="L803" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M803" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="N803" t="n">
         <v>1236.3</v>
       </c>
       <c r="O803" t="n">
-        <v>45743.1</v>
+        <v>43270.5</v>
       </c>
       <c r="P803" t="n">
         <v>2300</v>
       </c>
       <c r="Q803" t="n">
-        <v>85100</v>
+        <v>80500</v>
       </c>
     </row>
     <row r="804">
@@ -37078,22 +37078,22 @@
         <v>0</v>
       </c>
       <c r="L807" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M807" t="n">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="N807" t="n">
         <v>571.87</v>
       </c>
       <c r="O807" t="n">
-        <v>112658.39</v>
+        <v>111514.65</v>
       </c>
       <c r="P807" t="n">
         <v>2500</v>
       </c>
       <c r="Q807" t="n">
-        <v>492500</v>
+        <v>487500</v>
       </c>
     </row>
     <row r="808">
@@ -37727,22 +37727,22 @@
         <v>0</v>
       </c>
       <c r="L821" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M821" t="n">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="N821" t="n">
         <v>4550</v>
       </c>
       <c r="O821" t="n">
-        <v>1260350</v>
+        <v>1251250</v>
       </c>
       <c r="P821" t="n">
         <v>5500</v>
       </c>
       <c r="Q821" t="n">
-        <v>1523500</v>
+        <v>1512500</v>
       </c>
     </row>
     <row r="822">

--- a/bodegas/LJ-05.xlsx
+++ b/bodegas/LJ-05.xlsx
@@ -950,10 +950,10 @@
         <v>214</v>
       </c>
       <c r="N13" t="n">
-        <v>1811.307345576</v>
+        <v>1811.3074074074</v>
       </c>
       <c r="O13" t="n">
-        <v>387619.771953264</v>
+        <v>387619.7851851836</v>
       </c>
       <c r="P13" t="n">
         <v>2600</v>
@@ -1663,10 +1663,10 @@
         <v>15</v>
       </c>
       <c r="N31" t="n">
-        <v>3926.8370969414</v>
+        <v>3926.8370954357</v>
       </c>
       <c r="O31" t="n">
-        <v>58902.556454121</v>
+        <v>58902.5564315355</v>
       </c>
       <c r="P31" t="n">
         <v>4800</v>
@@ -3141,10 +3141,10 @@
         <v>41</v>
       </c>
       <c r="N65" t="n">
-        <v>15711.965922747</v>
+        <v>15711.965905172</v>
       </c>
       <c r="O65" t="n">
-        <v>644190.602832627</v>
+        <v>644190.6021120519</v>
       </c>
       <c r="P65" t="n">
         <v>28500</v>
@@ -7365,10 +7365,10 @@
         <v>714</v>
       </c>
       <c r="N162" t="n">
-        <v>3158.8608262318</v>
+        <v>3160.2538267431</v>
       </c>
       <c r="O162" t="n">
-        <v>2255426.629929505</v>
+        <v>2256421.232294573</v>
       </c>
       <c r="P162" t="n">
         <v>5600</v>
@@ -8183,22 +8183,22 @@
         <v>0</v>
       </c>
       <c r="L180" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M180" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N180" t="n">
         <v>1203.38</v>
       </c>
       <c r="O180" t="n">
-        <v>7220.280000000001</v>
+        <v>1203.38</v>
       </c>
       <c r="P180" t="n">
         <v>1900</v>
       </c>
       <c r="Q180" t="n">
-        <v>11400</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="181">
@@ -8408,22 +8408,22 @@
         <v>0</v>
       </c>
       <c r="L185" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M185" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="N185" t="n">
         <v>7041</v>
       </c>
       <c r="O185" t="n">
-        <v>584403</v>
+        <v>563280</v>
       </c>
       <c r="P185" t="n">
         <v>11500</v>
       </c>
       <c r="Q185" t="n">
-        <v>954500</v>
+        <v>920000</v>
       </c>
     </row>
     <row r="186">
@@ -8454,22 +8454,22 @@
         <v>0</v>
       </c>
       <c r="L186" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M186" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N186" t="n">
         <v>5667.94</v>
       </c>
       <c r="O186" t="n">
-        <v>317404.64</v>
+        <v>311736.7</v>
       </c>
       <c r="P186" t="n">
         <v>9500</v>
       </c>
       <c r="Q186" t="n">
-        <v>532000</v>
+        <v>522500</v>
       </c>
     </row>
     <row r="187">
@@ -8723,22 +8723,22 @@
         <v>0</v>
       </c>
       <c r="L192" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M192" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N192" t="n">
-        <v>3594.254</v>
+        <v>3594.2539962477</v>
       </c>
       <c r="O192" t="n">
-        <v>17971.27</v>
+        <v>14377.0159849908</v>
       </c>
       <c r="P192" t="n">
         <v>6500</v>
       </c>
       <c r="Q192" t="n">
-        <v>32500</v>
+        <v>26000</v>
       </c>
     </row>
     <row r="193">
@@ -9050,10 +9050,10 @@
         <v>33</v>
       </c>
       <c r="N199" t="n">
-        <v>2090.85</v>
+        <v>2091.1308394896</v>
       </c>
       <c r="O199" t="n">
-        <v>68998.05</v>
+        <v>69007.3177031568</v>
       </c>
       <c r="P199" t="n">
         <v>2900</v>
@@ -9731,10 +9731,10 @@
         <v>93</v>
       </c>
       <c r="N214" t="n">
-        <v>4372.2107903559</v>
+        <v>4372.2107904123</v>
       </c>
       <c r="O214" t="n">
-        <v>406615.6035030987</v>
+        <v>406615.6035083439</v>
       </c>
       <c r="P214" t="n">
         <v>7500</v>
@@ -9777,10 +9777,10 @@
         <v>315</v>
       </c>
       <c r="N215" t="n">
-        <v>1592.5667254408</v>
+        <v>1600.6713740458</v>
       </c>
       <c r="O215" t="n">
-        <v>501658.518513852</v>
+        <v>504211.482824427</v>
       </c>
       <c r="P215" t="n">
         <v>3900</v>
@@ -10820,10 +10820,10 @@
         <v>9</v>
       </c>
       <c r="N238" t="n">
-        <v>3761.6</v>
+        <v>3775.3787545788</v>
       </c>
       <c r="O238" t="n">
-        <v>33854.4</v>
+        <v>33978.4087912092</v>
       </c>
       <c r="P238" t="n">
         <v>6900</v>
@@ -11092,10 +11092,10 @@
         <v>44</v>
       </c>
       <c r="N244" t="n">
-        <v>1550.1936995315</v>
+        <v>1550.1937050719</v>
       </c>
       <c r="O244" t="n">
-        <v>68208.522779386</v>
+        <v>68208.52302316359</v>
       </c>
       <c r="P244" t="n">
         <v>2500</v>
@@ -11132,22 +11132,22 @@
         <v>0</v>
       </c>
       <c r="L245" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M245" t="n">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="N245" t="n">
-        <v>2403.5121001364</v>
+        <v>2403.5121166602</v>
       </c>
       <c r="O245" t="n">
-        <v>1228194.6831697</v>
+        <v>1220984.155263382</v>
       </c>
       <c r="P245" t="n">
         <v>3500</v>
       </c>
       <c r="Q245" t="n">
-        <v>1788500</v>
+        <v>1778000</v>
       </c>
     </row>
     <row r="246">
@@ -12573,10 +12573,10 @@
         <v>64</v>
       </c>
       <c r="N278" t="n">
-        <v>2680.739695084</v>
+        <v>2680.7396948941</v>
       </c>
       <c r="O278" t="n">
-        <v>171567.340485376</v>
+        <v>171567.3404732224</v>
       </c>
       <c r="P278" t="n">
         <v>4900</v>
@@ -14047,10 +14047,10 @@
         <v>137</v>
       </c>
       <c r="N311" t="n">
-        <v>1466.8807185629</v>
+        <v>1484.6610909091</v>
       </c>
       <c r="O311" t="n">
-        <v>200962.6584431173</v>
+        <v>203398.5694545467</v>
       </c>
       <c r="P311" t="n">
         <v>3400</v>
@@ -14313,10 +14313,10 @@
         <v>45</v>
       </c>
       <c r="N317" t="n">
-        <v>1561.0009337861</v>
+        <v>1561.000952381</v>
       </c>
       <c r="O317" t="n">
-        <v>70245.0420203745</v>
+        <v>70245.042857145</v>
       </c>
       <c r="P317" t="n">
         <v>2900</v>
@@ -15397,10 +15397,10 @@
         <v>65</v>
       </c>
       <c r="N341" t="n">
-        <v>3113.8900274725</v>
+        <v>3113.8900276243</v>
       </c>
       <c r="O341" t="n">
-        <v>202402.8517857125</v>
+        <v>202402.8517955795</v>
       </c>
       <c r="P341" t="n">
         <v>5000</v>
@@ -19606,10 +19606,10 @@
         <v>38</v>
       </c>
       <c r="N432" t="n">
-        <v>4907.822092257</v>
+        <v>4956.8186522463</v>
       </c>
       <c r="O432" t="n">
-        <v>186497.239505766</v>
+        <v>188359.1087853594</v>
       </c>
       <c r="P432" t="n">
         <v>8200</v>
@@ -23691,10 +23691,10 @@
         <v>283</v>
       </c>
       <c r="N521" t="n">
-        <v>1803.0156237558</v>
+        <v>1803.0156368474</v>
       </c>
       <c r="O521" t="n">
-        <v>510253.4215228914</v>
+        <v>510253.4252278142</v>
       </c>
       <c r="P521" t="n">
         <v>2500</v>
@@ -23737,10 +23737,10 @@
         <v>96</v>
       </c>
       <c r="N522" t="n">
-        <v>3306.5946745562</v>
+        <v>3306.5946666667</v>
       </c>
       <c r="O522" t="n">
-        <v>317433.0887573952</v>
+        <v>317433.0880000032</v>
       </c>
       <c r="P522" t="n">
         <v>4900</v>
@@ -23875,10 +23875,10 @@
         <v>293</v>
       </c>
       <c r="N525" t="n">
-        <v>2056.0829843644</v>
+        <v>2056.0829819789</v>
       </c>
       <c r="O525" t="n">
-        <v>602432.3144187692</v>
+        <v>602432.3137198177</v>
       </c>
       <c r="P525" t="n">
         <v>2900</v>
@@ -23967,10 +23967,10 @@
         <v>261</v>
       </c>
       <c r="N527" t="n">
-        <v>1655.9308045213</v>
+        <v>1655.9307861426</v>
       </c>
       <c r="O527" t="n">
-        <v>432197.9399800593</v>
+        <v>432197.9351832186</v>
       </c>
       <c r="P527" t="n">
         <v>2500</v>
@@ -24099,22 +24099,22 @@
         <v>0</v>
       </c>
       <c r="L530" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M530" t="n">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="N530" t="n">
         <v>2454</v>
       </c>
       <c r="O530" t="n">
-        <v>601230</v>
+        <v>581598</v>
       </c>
       <c r="P530" t="n">
         <v>4200</v>
       </c>
       <c r="Q530" t="n">
-        <v>1029000</v>
+        <v>995400</v>
       </c>
     </row>
     <row r="531">
@@ -24151,10 +24151,10 @@
         <v>139</v>
       </c>
       <c r="N531" t="n">
-        <v>1592.27881</v>
+        <v>1592.2788188188</v>
       </c>
       <c r="O531" t="n">
-        <v>221326.75459</v>
+        <v>221326.7558158132</v>
       </c>
       <c r="P531" t="n">
         <v>2500</v>
@@ -26376,10 +26376,10 @@
         <v>1487</v>
       </c>
       <c r="N579" t="n">
-        <v>517.2899423715</v>
+        <v>517.28997081144</v>
       </c>
       <c r="O579" t="n">
-        <v>769210.1443064206</v>
+        <v>769210.1865966112</v>
       </c>
       <c r="P579" t="n">
         <v>900</v>
@@ -26607,10 +26607,10 @@
         <v>240</v>
       </c>
       <c r="N584" t="n">
-        <v>3110.8413822526</v>
+        <v>3110.8413717354</v>
       </c>
       <c r="O584" t="n">
-        <v>746601.931740624</v>
+        <v>746601.9292164961</v>
       </c>
       <c r="P584" t="n">
         <v>4500</v>
@@ -26651,10 +26651,10 @@
         <v>1471</v>
       </c>
       <c r="N585" t="n">
-        <v>703.79516599434</v>
+        <v>703.79516401441</v>
       </c>
       <c r="O585" t="n">
-        <v>1035282.689177674</v>
+        <v>1035282.686265197</v>
       </c>
       <c r="P585" t="n">
         <v>900</v>
@@ -29007,10 +29007,10 @@
         <v>61</v>
       </c>
       <c r="N634" t="n">
-        <v>875.69016806723</v>
+        <v>883.11127118644</v>
       </c>
       <c r="O634" t="n">
-        <v>53417.10025210103</v>
+        <v>53869.78754237284</v>
       </c>
       <c r="P634" t="n">
         <v>4500</v>
@@ -33518,22 +33518,22 @@
         <v>0</v>
       </c>
       <c r="L730" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M730" t="n">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="N730" t="n">
         <v>7200</v>
       </c>
       <c r="O730" t="n">
-        <v>864000</v>
+        <v>842400</v>
       </c>
       <c r="P730" t="n">
         <v>8900</v>
       </c>
       <c r="Q730" t="n">
-        <v>1068000</v>
+        <v>1041300</v>
       </c>
     </row>
     <row r="731">
@@ -33610,22 +33610,22 @@
         <v>0</v>
       </c>
       <c r="L732" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M732" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="N732" t="n">
         <v>10800</v>
       </c>
       <c r="O732" t="n">
-        <v>561600</v>
+        <v>550800</v>
       </c>
       <c r="P732" t="n">
         <v>13500</v>
       </c>
       <c r="Q732" t="n">
-        <v>702000</v>
+        <v>688500</v>
       </c>
     </row>
     <row r="733">
@@ -34346,22 +34346,22 @@
         <v>0</v>
       </c>
       <c r="L748" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M748" t="n">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="N748" t="n">
         <v>7480</v>
       </c>
       <c r="O748" t="n">
-        <v>1892440</v>
+        <v>1870000</v>
       </c>
       <c r="P748" t="n">
         <v>9500</v>
       </c>
       <c r="Q748" t="n">
-        <v>2403500</v>
+        <v>2375000</v>
       </c>
     </row>
     <row r="749">
@@ -34530,22 +34530,22 @@
         <v>0</v>
       </c>
       <c r="L752" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M752" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="N752" t="n">
         <v>6336</v>
       </c>
       <c r="O752" t="n">
-        <v>633600</v>
+        <v>620928</v>
       </c>
       <c r="P752" t="n">
         <v>7500</v>
       </c>
       <c r="Q752" t="n">
-        <v>750000</v>
+        <v>735000</v>
       </c>
     </row>
     <row r="753">
@@ -34582,10 +34582,10 @@
         <v>124</v>
       </c>
       <c r="N753" t="n">
-        <v>5280</v>
+        <v>5305.2631578947</v>
       </c>
       <c r="O753" t="n">
-        <v>654720</v>
+        <v>657852.6315789429</v>
       </c>
       <c r="P753" t="n">
         <v>6900</v>
@@ -34852,22 +34852,22 @@
         <v>0</v>
       </c>
       <c r="L759" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M759" t="n">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="N759" t="n">
         <v>3872</v>
       </c>
       <c r="O759" t="n">
-        <v>1057056</v>
+        <v>1045440</v>
       </c>
       <c r="P759" t="n">
         <v>4900</v>
       </c>
       <c r="Q759" t="n">
-        <v>1337700</v>
+        <v>1323000</v>
       </c>
     </row>
     <row r="760">
@@ -35128,22 +35128,22 @@
         <v>0</v>
       </c>
       <c r="L765" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M765" t="n">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="N765" t="n">
         <v>3344</v>
       </c>
       <c r="O765" t="n">
-        <v>1070080</v>
+        <v>1056704</v>
       </c>
       <c r="P765" t="n">
         <v>4500</v>
       </c>
       <c r="Q765" t="n">
-        <v>1440000</v>
+        <v>1422000</v>
       </c>
     </row>
     <row r="766">
@@ -35174,22 +35174,22 @@
         <v>0</v>
       </c>
       <c r="L766" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M766" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="N766" t="n">
         <v>4400</v>
       </c>
       <c r="O766" t="n">
-        <v>563200</v>
+        <v>550000</v>
       </c>
       <c r="P766" t="n">
         <v>5900</v>
       </c>
       <c r="Q766" t="n">
-        <v>755200</v>
+        <v>737500</v>
       </c>
     </row>
     <row r="767">
@@ -35312,22 +35312,22 @@
         <v>0</v>
       </c>
       <c r="L769" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M769" t="n">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="N769" t="n">
         <v>9240</v>
       </c>
       <c r="O769" t="n">
-        <v>6246240</v>
+        <v>6227760</v>
       </c>
       <c r="P769" t="n">
         <v>11500</v>
       </c>
       <c r="Q769" t="n">
-        <v>7774000</v>
+        <v>7751000</v>
       </c>
     </row>
     <row r="770">
@@ -35358,22 +35358,22 @@
         <v>0</v>
       </c>
       <c r="L770" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M770" t="n">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="N770" t="n">
         <v>2288</v>
       </c>
       <c r="O770" t="n">
-        <v>578864</v>
+        <v>567424</v>
       </c>
       <c r="P770" t="n">
         <v>2900</v>
       </c>
       <c r="Q770" t="n">
-        <v>733700</v>
+        <v>719200</v>
       </c>
     </row>
     <row r="771">
@@ -35450,22 +35450,22 @@
         <v>0</v>
       </c>
       <c r="L772" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M772" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="N772" t="n">
         <v>4576</v>
       </c>
       <c r="O772" t="n">
-        <v>507936</v>
+        <v>498784</v>
       </c>
       <c r="P772" t="n">
         <v>5900</v>
       </c>
       <c r="Q772" t="n">
-        <v>654900</v>
+        <v>643100</v>
       </c>
     </row>
     <row r="773">
@@ -36937,22 +36937,22 @@
         <v>0</v>
       </c>
       <c r="L804" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M804" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="N804" t="n">
         <v>751.45</v>
       </c>
       <c r="O804" t="n">
-        <v>32312.35</v>
+        <v>28555.1</v>
       </c>
       <c r="P804" t="n">
         <v>2500</v>
       </c>
       <c r="Q804" t="n">
-        <v>107500</v>
+        <v>95000</v>
       </c>
     </row>
     <row r="805">

--- a/bodegas/LJ-05.xlsx
+++ b/bodegas/LJ-05.xlsx
@@ -13998,10 +13998,10 @@
         <v>137</v>
       </c>
       <c r="N310" t="n">
-        <v>1484.6610909091</v>
+        <v>1466.8807272727</v>
       </c>
       <c r="O310" t="n">
-        <v>203398.5694545467</v>
+        <v>200962.6596363599</v>
       </c>
       <c r="P310" t="n">
         <v>3400</v>
@@ -19557,10 +19557,10 @@
         <v>38</v>
       </c>
       <c r="N431" t="n">
-        <v>4956.8186522463</v>
+        <v>4907.8221131448</v>
       </c>
       <c r="O431" t="n">
-        <v>188359.1087853594</v>
+        <v>186497.2402995024</v>
       </c>
       <c r="P431" t="n">
         <v>8200</v>
@@ -28958,10 +28958,10 @@
         <v>61</v>
       </c>
       <c r="N633" t="n">
-        <v>883.11127118644</v>
+        <v>875.69016949153</v>
       </c>
       <c r="O633" t="n">
-        <v>53869.78754237284</v>
+        <v>53417.10033898333</v>
       </c>
       <c r="P633" t="n">
         <v>4500</v>

--- a/bodegas/LJ-05.xlsx
+++ b/bodegas/LJ-05.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-30</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-31</t>
         </is>
       </c>
     </row>

--- a/bodegas/LJ-05.xlsx
+++ b/bodegas/LJ-05.xlsx
@@ -2014,22 +2014,22 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M40" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N40" t="n">
         <v>21333.69</v>
       </c>
       <c r="O40" t="n">
-        <v>298671.66</v>
+        <v>277337.97</v>
       </c>
       <c r="P40" t="n">
         <v>30000</v>
       </c>
       <c r="Q40" t="n">
-        <v>420000</v>
+        <v>390000</v>
       </c>
     </row>
     <row r="41">
@@ -3141,10 +3141,10 @@
         <v>41</v>
       </c>
       <c r="N65" t="n">
-        <v>15711.965869565</v>
+        <v>15711.965851528</v>
       </c>
       <c r="O65" t="n">
-        <v>644190.600652165</v>
+        <v>644190.599912648</v>
       </c>
       <c r="P65" t="n">
         <v>28500</v>
@@ -7365,10 +7365,10 @@
         <v>709</v>
       </c>
       <c r="N162" t="n">
-        <v>3158.8608271635</v>
+        <v>3158.8608272041</v>
       </c>
       <c r="O162" t="n">
-        <v>2239632.326458921</v>
+        <v>2239632.326487707</v>
       </c>
       <c r="P162" t="n">
         <v>5600</v>
@@ -8680,10 +8680,10 @@
         <v>2</v>
       </c>
       <c r="N191" t="n">
-        <v>3594.2539622642</v>
+        <v>3594.2539546599</v>
       </c>
       <c r="O191" t="n">
-        <v>7188.5079245284</v>
+        <v>7188.5079093198</v>
       </c>
       <c r="P191" t="n">
         <v>6500</v>
@@ -13236,10 +13236,10 @@
         <v>61</v>
       </c>
       <c r="N293" t="n">
-        <v>30244.600034762</v>
+        <v>30244.600034742</v>
       </c>
       <c r="O293" t="n">
-        <v>1844920.602120482</v>
+        <v>1844920.602119262</v>
       </c>
       <c r="P293" t="n">
         <v>48900</v>
@@ -13685,22 +13685,22 @@
         <v>0</v>
       </c>
       <c r="L303" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M303" t="n">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="N303" t="n">
         <v>4793.53</v>
       </c>
       <c r="O303" t="n">
-        <v>738203.62</v>
+        <v>723823.0299999999</v>
       </c>
       <c r="P303" t="n">
         <v>7900</v>
       </c>
       <c r="Q303" t="n">
-        <v>1216600</v>
+        <v>1192900</v>
       </c>
     </row>
     <row r="304">
@@ -15848,22 +15848,22 @@
         <v>0</v>
       </c>
       <c r="L351" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M351" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="N351" t="n">
         <v>5194</v>
       </c>
       <c r="O351" t="n">
-        <v>451878</v>
+        <v>441490</v>
       </c>
       <c r="P351" t="n">
         <v>9000</v>
       </c>
       <c r="Q351" t="n">
-        <v>783000</v>
+        <v>765000</v>
       </c>
     </row>
     <row r="352">
@@ -23636,22 +23636,22 @@
         <v>0</v>
       </c>
       <c r="L520" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M520" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N520" t="n">
-        <v>1907.3929677419</v>
+        <v>1907.3929220779</v>
       </c>
       <c r="O520" t="n">
-        <v>11444.3578064514</v>
+        <v>0</v>
       </c>
       <c r="P520" t="n">
         <v>2500</v>
       </c>
       <c r="Q520" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="521">
@@ -23774,22 +23774,22 @@
         <v>0</v>
       </c>
       <c r="L523" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M523" t="n">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="N523" t="n">
-        <v>1803.0157013118</v>
+        <v>1803.0157128413</v>
       </c>
       <c r="O523" t="n">
-        <v>465178.0509384444</v>
+        <v>454359.9596360076</v>
       </c>
       <c r="P523" t="n">
         <v>2500</v>
       </c>
       <c r="Q523" t="n">
-        <v>645000</v>
+        <v>630000</v>
       </c>
     </row>
     <row r="524">
@@ -23912,22 +23912,22 @@
         <v>0</v>
       </c>
       <c r="L526" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M526" t="n">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="N526" t="n">
-        <v>2108.7924270463</v>
+        <v>2108.7924803431</v>
       </c>
       <c r="O526" t="n">
-        <v>461825.5415231397</v>
+        <v>449172.7983130803</v>
       </c>
       <c r="P526" t="n">
         <v>2900</v>
       </c>
       <c r="Q526" t="n">
-        <v>635100</v>
+        <v>617700</v>
       </c>
     </row>
     <row r="527">
@@ -23958,22 +23958,22 @@
         <v>0</v>
       </c>
       <c r="L527" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M527" t="n">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="N527" t="n">
-        <v>2056.0829120879</v>
+        <v>2056.0828974535</v>
       </c>
       <c r="O527" t="n">
-        <v>602432.2932417546</v>
+        <v>590095.7915691546</v>
       </c>
       <c r="P527" t="n">
         <v>2900</v>
       </c>
       <c r="Q527" t="n">
-        <v>849700</v>
+        <v>832300</v>
       </c>
     </row>
     <row r="528">
@@ -24240,10 +24240,10 @@
         <v>97</v>
       </c>
       <c r="N533" t="n">
-        <v>1592.2799548023</v>
+        <v>1592.2799660633</v>
       </c>
       <c r="O533" t="n">
-        <v>154451.1556158231</v>
+        <v>154451.1567081401</v>
       </c>
       <c r="P533" t="n">
         <v>2500</v>
@@ -26740,10 +26740,10 @@
         <v>1330</v>
       </c>
       <c r="N587" t="n">
-        <v>703.79511760843</v>
+        <v>703.79511689575</v>
       </c>
       <c r="O587" t="n">
-        <v>936047.506419212</v>
+        <v>936047.5054713475</v>
       </c>
       <c r="P587" t="n">
         <v>900</v>

--- a/bodegas/LJ-05.xlsx
+++ b/bodegas/LJ-05.xlsx
@@ -3099,10 +3099,10 @@
         <v>14</v>
       </c>
       <c r="N64" t="n">
-        <v>16486.408661417</v>
+        <v>16486.408571429</v>
       </c>
       <c r="O64" t="n">
-        <v>230809.721259838</v>
+        <v>230809.720000006</v>
       </c>
       <c r="P64" t="n">
         <v>30500</v>
@@ -3141,10 +3141,10 @@
         <v>41</v>
       </c>
       <c r="N65" t="n">
-        <v>15711.965814978</v>
+        <v>15711.96579646</v>
       </c>
       <c r="O65" t="n">
-        <v>644190.598414098</v>
+        <v>644190.59765486</v>
       </c>
       <c r="P65" t="n">
         <v>28500</v>
@@ -3188,10 +3188,10 @@
         <v>24</v>
       </c>
       <c r="N66" t="n">
-        <v>9392.075000000001</v>
+        <v>9392.0750746269</v>
       </c>
       <c r="O66" t="n">
-        <v>225409.8</v>
+        <v>225409.8017910456</v>
       </c>
       <c r="P66" t="n">
         <v>18500</v>
@@ -7227,10 +7227,10 @@
         <v>242</v>
       </c>
       <c r="N159" t="n">
-        <v>2582.2555555556</v>
+        <v>2582.2555535714</v>
       </c>
       <c r="O159" t="n">
-        <v>624905.8444444552</v>
+        <v>624905.8439642788</v>
       </c>
       <c r="P159" t="n">
         <v>4500</v>
@@ -10032,22 +10032,22 @@
         <v>0</v>
       </c>
       <c r="L221" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M221" t="n">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="N221" t="n">
         <v>4648.6</v>
       </c>
       <c r="O221" t="n">
-        <v>1441066</v>
+        <v>1399228.6</v>
       </c>
       <c r="P221" t="n">
         <v>8900</v>
       </c>
       <c r="Q221" t="n">
-        <v>2759000</v>
+        <v>2678900</v>
       </c>
     </row>
     <row r="222">
@@ -23918,10 +23918,10 @@
         <v>261</v>
       </c>
       <c r="N526" t="n">
-        <v>1655.9307118872</v>
+        <v>1655.9306993948</v>
       </c>
       <c r="O526" t="n">
-        <v>432197.9158025592</v>
+        <v>432197.9125420428</v>
       </c>
       <c r="P526" t="n">
         <v>2500</v>
@@ -24096,22 +24096,22 @@
         <v>0</v>
       </c>
       <c r="L530" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M530" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="N530" t="n">
-        <v>1592.2805889423</v>
+        <v>1592.2806787879</v>
       </c>
       <c r="O530" t="n">
-        <v>97129.11592548031</v>
+        <v>85983.15665454659</v>
       </c>
       <c r="P530" t="n">
         <v>2500</v>
       </c>
       <c r="Q530" t="n">
-        <v>152500</v>
+        <v>135000</v>
       </c>
     </row>
     <row r="531">
@@ -24232,22 +24232,22 @@
         <v>0</v>
       </c>
       <c r="L533" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M533" t="n">
-        <v>909</v>
+        <v>904</v>
       </c>
       <c r="N533" t="n">
-        <v>1259.2746360505</v>
+        <v>1259.2746413793</v>
       </c>
       <c r="O533" t="n">
-        <v>1144680.644169905</v>
+        <v>1138384.275806887</v>
       </c>
       <c r="P533" t="n">
         <v>1900</v>
       </c>
       <c r="Q533" t="n">
-        <v>1727100</v>
+        <v>1717600</v>
       </c>
     </row>
     <row r="534">
@@ -26558,10 +26558,10 @@
         <v>25</v>
       </c>
       <c r="N583" t="n">
-        <v>3110.8404252438</v>
+        <v>3110.840414859</v>
       </c>
       <c r="O583" t="n">
-        <v>77771.01063109499</v>
+        <v>77771.010371475</v>
       </c>
       <c r="P583" t="n">
         <v>4500</v>
@@ -26838,22 +26838,22 @@
         <v>0</v>
       </c>
       <c r="L589" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M589" t="n">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="N589" t="n">
-        <v>1595.5116515014</v>
+        <v>1595.5116012774</v>
       </c>
       <c r="O589" t="n">
-        <v>314315.7953457758</v>
+        <v>304742.7158439834</v>
       </c>
       <c r="P589" t="n">
         <v>2500</v>
       </c>
       <c r="Q589" t="n">
-        <v>492500</v>
+        <v>477500</v>
       </c>
     </row>
     <row r="590">
@@ -34018,22 +34018,22 @@
         <v>0</v>
       </c>
       <c r="L741" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M741" t="n">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="N741" t="n">
         <v>7480</v>
       </c>
       <c r="O741" t="n">
-        <v>1473560</v>
+        <v>1443640</v>
       </c>
       <c r="P741" t="n">
         <v>9500</v>
       </c>
       <c r="Q741" t="n">
-        <v>1871500</v>
+        <v>1833500</v>
       </c>
     </row>
     <row r="742">
@@ -34340,22 +34340,22 @@
         <v>0</v>
       </c>
       <c r="L748" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M748" t="n">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="N748" t="n">
         <v>1584</v>
       </c>
       <c r="O748" t="n">
-        <v>161568</v>
+        <v>153648</v>
       </c>
       <c r="P748" t="n">
         <v>2000</v>
       </c>
       <c r="Q748" t="n">
-        <v>204000</v>
+        <v>194000</v>
       </c>
     </row>
     <row r="749">
@@ -36655,22 +36655,22 @@
         <v>0</v>
       </c>
       <c r="L798" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M798" t="n">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="N798" t="n">
         <v>571.87</v>
       </c>
       <c r="O798" t="n">
-        <v>110942.78</v>
+        <v>108083.43</v>
       </c>
       <c r="P798" t="n">
         <v>2500</v>
       </c>
       <c r="Q798" t="n">
-        <v>485000</v>
+        <v>472500</v>
       </c>
     </row>
     <row r="799">

--- a/bodegas/LJ-05.xlsx
+++ b/bodegas/LJ-05.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-02</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-03</t>
         </is>
       </c>
     </row>
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -947,19 +947,19 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="N13" t="n">
-        <v>1811.3078361532</v>
+        <v>1811.3078994614</v>
       </c>
       <c r="O13" t="n">
-        <v>327846.7183437292</v>
+        <v>311544.9587073608</v>
       </c>
       <c r="P13" t="n">
         <v>2600</v>
       </c>
       <c r="Q13" t="n">
-        <v>470600</v>
+        <v>447200</v>
       </c>
     </row>
     <row r="14">
@@ -1028,10 +1028,10 @@
         <v>206</v>
       </c>
       <c r="N15" t="n">
-        <v>3376.7464583333</v>
+        <v>3376.7464524986</v>
       </c>
       <c r="O15" t="n">
-        <v>695609.7704166598</v>
+        <v>695609.7692147116</v>
       </c>
       <c r="P15" t="n">
         <v>4500</v>
@@ -3141,10 +3141,10 @@
         <v>41</v>
       </c>
       <c r="N65" t="n">
-        <v>15711.96579646</v>
+        <v>15711.965777778</v>
       </c>
       <c r="O65" t="n">
-        <v>644190.59765486</v>
+        <v>644190.5968888979</v>
       </c>
       <c r="P65" t="n">
         <v>28500</v>
@@ -4850,7 +4850,7 @@
         </is>
       </c>
       <c r="J105" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K105" t="n">
         <v>0</v>
@@ -4859,19 +4859,19 @@
         <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N105" t="n">
-        <v>580.36598382749</v>
+        <v>580.36597297297</v>
       </c>
       <c r="O105" t="n">
-        <v>23214.6393530996</v>
+        <v>22634.27294594583</v>
       </c>
       <c r="P105" t="n">
         <v>6800</v>
       </c>
       <c r="Q105" t="n">
-        <v>272000</v>
+        <v>265200</v>
       </c>
     </row>
     <row r="106">
@@ -4935,7 +4935,7 @@
         </is>
       </c>
       <c r="J107" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K107" t="n">
         <v>0</v>
@@ -4944,19 +4944,19 @@
         <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N107" t="n">
         <v>3732.66</v>
       </c>
       <c r="O107" t="n">
-        <v>175435.02</v>
+        <v>171702.36</v>
       </c>
       <c r="P107" t="n">
         <v>7300</v>
       </c>
       <c r="Q107" t="n">
-        <v>343100</v>
+        <v>335800</v>
       </c>
     </row>
     <row r="108">
@@ -5013,7 +5013,7 @@
         </is>
       </c>
       <c r="J109" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K109" t="n">
         <v>0</v>
@@ -5022,19 +5022,19 @@
         <v>0</v>
       </c>
       <c r="M109" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N109" t="n">
         <v>3865.67</v>
       </c>
       <c r="O109" t="n">
-        <v>11597.01</v>
+        <v>7731.34</v>
       </c>
       <c r="P109" t="n">
         <v>5500</v>
       </c>
       <c r="Q109" t="n">
-        <v>16500</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="110">
@@ -5447,7 +5447,7 @@
         </is>
       </c>
       <c r="J119" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K119" t="n">
         <v>0</v>
@@ -5456,19 +5456,19 @@
         <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N119" t="n">
         <v>3564.14</v>
       </c>
       <c r="O119" t="n">
-        <v>74846.94</v>
+        <v>71282.8</v>
       </c>
       <c r="P119" t="n">
         <v>5500</v>
       </c>
       <c r="Q119" t="n">
-        <v>115500</v>
+        <v>110000</v>
       </c>
     </row>
     <row r="120">
@@ -6372,7 +6372,7 @@
         </is>
       </c>
       <c r="J140" t="n">
-        <v>1580</v>
+        <v>1559</v>
       </c>
       <c r="K140" t="n">
         <v>0</v>
@@ -6381,19 +6381,19 @@
         <v>0</v>
       </c>
       <c r="M140" t="n">
-        <v>1580</v>
+        <v>1559</v>
       </c>
       <c r="N140" t="n">
         <v>1726.32</v>
       </c>
       <c r="O140" t="n">
-        <v>2727585.6</v>
+        <v>2691332.88</v>
       </c>
       <c r="P140" t="n">
         <v>1500</v>
       </c>
       <c r="Q140" t="n">
-        <v>2370000</v>
+        <v>2338500</v>
       </c>
     </row>
     <row r="141">
@@ -7215,7 +7215,7 @@
         </is>
       </c>
       <c r="J159" t="n">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="K159" t="n">
         <v>0</v>
@@ -7224,19 +7224,19 @@
         <v>0</v>
       </c>
       <c r="M159" t="n">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="N159" t="n">
-        <v>2582.2555535714</v>
+        <v>2582.255546613</v>
       </c>
       <c r="O159" t="n">
-        <v>624905.8439642788</v>
+        <v>619741.3311871201</v>
       </c>
       <c r="P159" t="n">
         <v>4500</v>
       </c>
       <c r="Q159" t="n">
-        <v>1089000</v>
+        <v>1080000</v>
       </c>
     </row>
     <row r="160">
@@ -7261,7 +7261,7 @@
         </is>
       </c>
       <c r="J160" t="n">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="K160" t="n">
         <v>0</v>
@@ -7270,19 +7270,19 @@
         <v>0</v>
       </c>
       <c r="M160" t="n">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="N160" t="n">
         <v>10600</v>
       </c>
       <c r="O160" t="n">
-        <v>1515800</v>
+        <v>1388600</v>
       </c>
       <c r="P160" t="n">
         <v>17200</v>
       </c>
       <c r="Q160" t="n">
-        <v>2459600</v>
+        <v>2253200</v>
       </c>
     </row>
     <row r="161">
@@ -7307,7 +7307,7 @@
         </is>
       </c>
       <c r="J161" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="K161" t="n">
         <v>0</v>
@@ -7316,19 +7316,19 @@
         <v>0</v>
       </c>
       <c r="M161" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="N161" t="n">
-        <v>5216.89608155</v>
+        <v>5216.8960627633</v>
       </c>
       <c r="O161" t="n">
-        <v>302579.9727299</v>
+        <v>234760.3228243485</v>
       </c>
       <c r="P161" t="n">
         <v>8500</v>
       </c>
       <c r="Q161" t="n">
-        <v>493000</v>
+        <v>382500</v>
       </c>
     </row>
     <row r="162">
@@ -7353,7 +7353,7 @@
         </is>
       </c>
       <c r="J162" t="n">
-        <v>709</v>
+        <v>696</v>
       </c>
       <c r="K162" t="n">
         <v>0</v>
@@ -7362,19 +7362,19 @@
         <v>0</v>
       </c>
       <c r="M162" t="n">
-        <v>709</v>
+        <v>696</v>
       </c>
       <c r="N162" t="n">
-        <v>3158.8608285041</v>
+        <v>3158.8608303391</v>
       </c>
       <c r="O162" t="n">
-        <v>2239632.327409407</v>
+        <v>2198567.137916014</v>
       </c>
       <c r="P162" t="n">
         <v>5600</v>
       </c>
       <c r="Q162" t="n">
-        <v>3970400</v>
+        <v>3897600</v>
       </c>
     </row>
     <row r="163">
@@ -7537,7 +7537,7 @@
         </is>
       </c>
       <c r="J166" t="n">
-        <v>1275</v>
+        <v>1255</v>
       </c>
       <c r="K166" t="n">
         <v>0</v>
@@ -7546,19 +7546,19 @@
         <v>0</v>
       </c>
       <c r="M166" t="n">
-        <v>1275</v>
+        <v>1255</v>
       </c>
       <c r="N166" t="n">
         <v>156.25</v>
       </c>
       <c r="O166" t="n">
-        <v>199218.75</v>
+        <v>196093.75</v>
       </c>
       <c r="P166" t="n">
         <v>250</v>
       </c>
       <c r="Q166" t="n">
-        <v>318750</v>
+        <v>313750</v>
       </c>
     </row>
     <row r="167">
@@ -7583,7 +7583,7 @@
         </is>
       </c>
       <c r="J167" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K167" t="n">
         <v>0</v>
@@ -7592,19 +7592,19 @@
         <v>0</v>
       </c>
       <c r="M167" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="N167" t="n">
         <v>7507.39</v>
       </c>
       <c r="O167" t="n">
-        <v>780768.5600000001</v>
+        <v>773261.17</v>
       </c>
       <c r="P167" t="n">
         <v>13500</v>
       </c>
       <c r="Q167" t="n">
-        <v>1404000</v>
+        <v>1390500</v>
       </c>
     </row>
     <row r="168">
@@ -7629,7 +7629,7 @@
         </is>
       </c>
       <c r="J168" t="n">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="K168" t="n">
         <v>0</v>
@@ -7638,19 +7638,19 @@
         <v>0</v>
       </c>
       <c r="M168" t="n">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="N168" t="n">
         <v>5002</v>
       </c>
       <c r="O168" t="n">
-        <v>595238</v>
+        <v>575230</v>
       </c>
       <c r="P168" t="n">
         <v>8400</v>
       </c>
       <c r="Q168" t="n">
-        <v>999600</v>
+        <v>966000</v>
       </c>
     </row>
     <row r="169">
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="J171" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K171" t="n">
         <v>0</v>
@@ -7776,19 +7776,19 @@
         <v>0</v>
       </c>
       <c r="M171" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="N171" t="n">
-        <v>3795.7100075672</v>
+        <v>3795.7100075815</v>
       </c>
       <c r="O171" t="n">
-        <v>30365.6800605376</v>
+        <v>15182.840030326</v>
       </c>
       <c r="P171" t="n">
         <v>6200</v>
       </c>
       <c r="Q171" t="n">
-        <v>49600</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="172">
@@ -7854,7 +7854,7 @@
         </is>
       </c>
       <c r="J173" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="K173" t="n">
         <v>0</v>
@@ -7863,19 +7863,19 @@
         <v>0</v>
       </c>
       <c r="M173" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="N173" t="n">
         <v>2612.77</v>
       </c>
       <c r="O173" t="n">
-        <v>54868.17</v>
+        <v>44417.09</v>
       </c>
       <c r="P173" t="n">
         <v>4900</v>
       </c>
       <c r="Q173" t="n">
-        <v>102900</v>
+        <v>83300</v>
       </c>
     </row>
     <row r="174">
@@ -8087,7 +8087,7 @@
         </is>
       </c>
       <c r="J178" t="n">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="K178" t="n">
         <v>0</v>
@@ -8096,19 +8096,19 @@
         <v>0</v>
       </c>
       <c r="M178" t="n">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="N178" t="n">
-        <v>4967.846</v>
+        <v>4967.8552054795</v>
       </c>
       <c r="O178" t="n">
-        <v>293102.914</v>
+        <v>258328.470684934</v>
       </c>
       <c r="P178" t="n">
         <v>7500</v>
       </c>
       <c r="Q178" t="n">
-        <v>442500</v>
+        <v>390000</v>
       </c>
     </row>
     <row r="179">
@@ -8174,7 +8174,7 @@
         </is>
       </c>
       <c r="J180" t="n">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="K180" t="n">
         <v>0</v>
@@ -8183,19 +8183,19 @@
         <v>0</v>
       </c>
       <c r="M180" t="n">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="N180" t="n">
         <v>3472</v>
       </c>
       <c r="O180" t="n">
-        <v>381920</v>
+        <v>354144</v>
       </c>
       <c r="P180" t="n">
         <v>4800</v>
       </c>
       <c r="Q180" t="n">
-        <v>528000</v>
+        <v>489600</v>
       </c>
     </row>
     <row r="181">
@@ -8266,7 +8266,7 @@
         </is>
       </c>
       <c r="J182" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K182" t="n">
         <v>0</v>
@@ -8275,19 +8275,19 @@
         <v>0</v>
       </c>
       <c r="M182" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N182" t="n">
         <v>46958</v>
       </c>
       <c r="O182" t="n">
-        <v>234790</v>
+        <v>187832</v>
       </c>
       <c r="P182" t="n">
         <v>76900</v>
       </c>
       <c r="Q182" t="n">
-        <v>384500</v>
+        <v>307600</v>
       </c>
     </row>
     <row r="183">
@@ -8319,10 +8319,10 @@
         <v>82</v>
       </c>
       <c r="N183" t="n">
-        <v>2267.0481436371</v>
+        <v>2267.0481247348</v>
       </c>
       <c r="O183" t="n">
-        <v>185897.9477782422</v>
+        <v>185897.9462282536</v>
       </c>
       <c r="P183" t="n">
         <v>3900</v>
@@ -8353,7 +8353,7 @@
         </is>
       </c>
       <c r="J184" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K184" t="n">
         <v>0</v>
@@ -8362,19 +8362,19 @@
         <v>0</v>
       </c>
       <c r="M184" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="N184" t="n">
         <v>7041</v>
       </c>
       <c r="O184" t="n">
-        <v>563280</v>
+        <v>556239</v>
       </c>
       <c r="P184" t="n">
         <v>11500</v>
       </c>
       <c r="Q184" t="n">
-        <v>920000</v>
+        <v>908500</v>
       </c>
     </row>
     <row r="185">
@@ -8399,7 +8399,7 @@
         </is>
       </c>
       <c r="J185" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K185" t="n">
         <v>0</v>
@@ -8408,19 +8408,19 @@
         <v>0</v>
       </c>
       <c r="M185" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N185" t="n">
         <v>5667.94</v>
       </c>
       <c r="O185" t="n">
-        <v>277729.06</v>
+        <v>272061.12</v>
       </c>
       <c r="P185" t="n">
         <v>9500</v>
       </c>
       <c r="Q185" t="n">
-        <v>465500</v>
+        <v>456000</v>
       </c>
     </row>
     <row r="186">
@@ -8680,10 +8680,10 @@
         <v>48</v>
       </c>
       <c r="N191" t="n">
-        <v>3594.2538892425</v>
+        <v>3594.2538618926</v>
       </c>
       <c r="O191" t="n">
-        <v>172524.18668364</v>
+        <v>172524.1853708448</v>
       </c>
       <c r="P191" t="n">
         <v>6500</v>
@@ -8809,7 +8809,7 @@
         </is>
       </c>
       <c r="J194" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K194" t="n">
         <v>0</v>
@@ -8818,19 +8818,19 @@
         <v>0</v>
       </c>
       <c r="M194" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N194" t="n">
         <v>4891</v>
       </c>
       <c r="O194" t="n">
-        <v>92929</v>
+        <v>83147</v>
       </c>
       <c r="P194" t="n">
         <v>8200</v>
       </c>
       <c r="Q194" t="n">
-        <v>155800</v>
+        <v>139400</v>
       </c>
     </row>
     <row r="195">
@@ -8855,7 +8855,7 @@
         </is>
       </c>
       <c r="J195" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="K195" t="n">
         <v>0</v>
@@ -8864,19 +8864,19 @@
         <v>0</v>
       </c>
       <c r="M195" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="N195" t="n">
         <v>8154</v>
       </c>
       <c r="O195" t="n">
-        <v>587088</v>
+        <v>562626</v>
       </c>
       <c r="P195" t="n">
         <v>13500</v>
       </c>
       <c r="Q195" t="n">
-        <v>972000</v>
+        <v>931500</v>
       </c>
     </row>
     <row r="196">
@@ -9266,7 +9266,7 @@
         </is>
       </c>
       <c r="J204" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K204" t="n">
         <v>0</v>
@@ -9275,19 +9275,19 @@
         <v>0</v>
       </c>
       <c r="M204" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N204" t="n">
-        <v>12267.648552632</v>
+        <v>12267.6484</v>
       </c>
       <c r="O204" t="n">
-        <v>196282.376842112</v>
+        <v>184014.726</v>
       </c>
       <c r="P204" t="n">
         <v>19900</v>
       </c>
       <c r="Q204" t="n">
-        <v>318400</v>
+        <v>298500</v>
       </c>
     </row>
     <row r="205">
@@ -9636,10 +9636,10 @@
         <v>116</v>
       </c>
       <c r="N212" t="n">
-        <v>3041.6600135135</v>
+        <v>3041.660013541</v>
       </c>
       <c r="O212" t="n">
-        <v>352832.561567566</v>
+        <v>352832.561570756</v>
       </c>
       <c r="P212" t="n">
         <v>5500</v>
@@ -9670,7 +9670,7 @@
         </is>
       </c>
       <c r="J213" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="K213" t="n">
         <v>0</v>
@@ -9679,19 +9679,19 @@
         <v>0</v>
       </c>
       <c r="M213" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="N213" t="n">
-        <v>4372.2107914851</v>
+        <v>4372.2107916548</v>
       </c>
       <c r="O213" t="n">
-        <v>349776.863318808</v>
+        <v>336660.2309574196</v>
       </c>
       <c r="P213" t="n">
         <v>7500</v>
       </c>
       <c r="Q213" t="n">
-        <v>600000</v>
+        <v>577500</v>
       </c>
     </row>
     <row r="214">
@@ -9716,7 +9716,7 @@
         </is>
       </c>
       <c r="J214" t="n">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="K214" t="n">
         <v>0</v>
@@ -9725,19 +9725,19 @@
         <v>0</v>
       </c>
       <c r="M214" t="n">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="N214" t="n">
-        <v>1592.5663938974</v>
+        <v>1592.5662962963</v>
       </c>
       <c r="O214" t="n">
-        <v>409289.5632316318</v>
+        <v>399734.1403703713</v>
       </c>
       <c r="P214" t="n">
         <v>3900</v>
       </c>
       <c r="Q214" t="n">
-        <v>1002300</v>
+        <v>978900</v>
       </c>
     </row>
     <row r="215">
@@ -9757,7 +9757,7 @@
         </is>
       </c>
       <c r="J215" t="n">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="K215" t="n">
         <v>0</v>
@@ -9766,19 +9766,19 @@
         <v>0</v>
       </c>
       <c r="M215" t="n">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="N215" t="n">
         <v>4513.76</v>
       </c>
       <c r="O215" t="n">
-        <v>541651.2000000001</v>
+        <v>523596.16</v>
       </c>
       <c r="P215" t="n">
         <v>8900</v>
       </c>
       <c r="Q215" t="n">
-        <v>1068000</v>
+        <v>1032400</v>
       </c>
     </row>
     <row r="216">
@@ -9798,7 +9798,7 @@
         </is>
       </c>
       <c r="J216" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K216" t="n">
         <v>0</v>
@@ -9807,19 +9807,19 @@
         <v>0</v>
       </c>
       <c r="M216" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N216" t="n">
         <v>2224.56</v>
       </c>
       <c r="O216" t="n">
-        <v>104554.32</v>
+        <v>102329.76</v>
       </c>
       <c r="P216" t="n">
         <v>3900</v>
       </c>
       <c r="Q216" t="n">
-        <v>183300</v>
+        <v>179400</v>
       </c>
     </row>
     <row r="217">
@@ -9885,7 +9885,7 @@
         </is>
       </c>
       <c r="J218" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="K218" t="n">
         <v>0</v>
@@ -9894,19 +9894,19 @@
         <v>0</v>
       </c>
       <c r="M218" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="N218" t="n">
         <v>2695.04</v>
       </c>
       <c r="O218" t="n">
-        <v>91631.36</v>
+        <v>78156.16</v>
       </c>
       <c r="P218" t="n">
         <v>7300</v>
       </c>
       <c r="Q218" t="n">
-        <v>248200</v>
+        <v>211700</v>
       </c>
     </row>
     <row r="219">
@@ -9977,7 +9977,7 @@
         </is>
       </c>
       <c r="J220" t="n">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="K220" t="n">
         <v>0</v>
@@ -9986,19 +9986,19 @@
         <v>0</v>
       </c>
       <c r="M220" t="n">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="N220" t="n">
         <v>6242.93</v>
       </c>
       <c r="O220" t="n">
-        <v>368332.87</v>
+        <v>330875.29</v>
       </c>
       <c r="P220" t="n">
         <v>10400</v>
       </c>
       <c r="Q220" t="n">
-        <v>613600</v>
+        <v>551200</v>
       </c>
     </row>
     <row r="221">
@@ -10026,13 +10026,13 @@
         </is>
       </c>
       <c r="J221" t="n">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="K221" t="n">
         <v>0</v>
       </c>
       <c r="L221" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M221" t="n">
         <v>301</v>
@@ -10075,7 +10075,7 @@
         </is>
       </c>
       <c r="J222" t="n">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="K222" t="n">
         <v>0</v>
@@ -10084,19 +10084,19 @@
         <v>0</v>
       </c>
       <c r="M222" t="n">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="N222" t="n">
         <v>1770.37</v>
       </c>
       <c r="O222" t="n">
-        <v>327518.45</v>
+        <v>308044.38</v>
       </c>
       <c r="P222" t="n">
         <v>3900</v>
       </c>
       <c r="Q222" t="n">
-        <v>721500</v>
+        <v>678600</v>
       </c>
     </row>
     <row r="223">
@@ -10341,7 +10341,7 @@
         </is>
       </c>
       <c r="J228" t="n">
-        <v>2230</v>
+        <v>2227</v>
       </c>
       <c r="K228" t="n">
         <v>0</v>
@@ -10350,19 +10350,19 @@
         <v>0</v>
       </c>
       <c r="M228" t="n">
-        <v>2230</v>
+        <v>2227</v>
       </c>
       <c r="N228" t="n">
         <v>1387.55</v>
       </c>
       <c r="O228" t="n">
-        <v>3094236.5</v>
+        <v>3090073.85</v>
       </c>
       <c r="P228" t="n">
         <v>2300</v>
       </c>
       <c r="Q228" t="n">
-        <v>5129000</v>
+        <v>5122100</v>
       </c>
     </row>
     <row r="229">
@@ -10485,7 +10485,7 @@
         </is>
       </c>
       <c r="J231" t="n">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="K231" t="n">
         <v>0</v>
@@ -10494,19 +10494,19 @@
         <v>0</v>
       </c>
       <c r="M231" t="n">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="N231" t="n">
         <v>4635.49</v>
       </c>
       <c r="O231" t="n">
-        <v>959546.4299999999</v>
+        <v>945639.96</v>
       </c>
       <c r="P231" t="n">
         <v>7500</v>
       </c>
       <c r="Q231" t="n">
-        <v>1552500</v>
+        <v>1530000</v>
       </c>
     </row>
     <row r="232">
@@ -10851,7 +10851,7 @@
         </is>
       </c>
       <c r="J239" t="n">
-        <v>17</v>
+        <v>77</v>
       </c>
       <c r="K239" t="n">
         <v>0</v>
@@ -10860,19 +10860,19 @@
         <v>0</v>
       </c>
       <c r="M239" t="n">
-        <v>17</v>
+        <v>77</v>
       </c>
       <c r="N239" t="n">
         <v>11921.4</v>
       </c>
       <c r="O239" t="n">
-        <v>202663.8</v>
+        <v>917947.7999999999</v>
       </c>
       <c r="P239" t="n">
         <v>19900</v>
       </c>
       <c r="Q239" t="n">
-        <v>338300</v>
+        <v>1532300</v>
       </c>
     </row>
     <row r="240">
@@ -11031,7 +11031,7 @@
         </is>
       </c>
       <c r="J243" t="n">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="K243" t="n">
         <v>0</v>
@@ -11040,19 +11040,19 @@
         <v>0</v>
       </c>
       <c r="M243" t="n">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="N243" t="n">
-        <v>2403.5129584811</v>
+        <v>2403.5131199831</v>
       </c>
       <c r="O243" t="n">
-        <v>870071.6909701583</v>
+        <v>848440.1313540343</v>
       </c>
       <c r="P243" t="n">
         <v>3500</v>
       </c>
       <c r="Q243" t="n">
-        <v>1267000</v>
+        <v>1235500</v>
       </c>
     </row>
     <row r="244">
@@ -11845,10 +11845,10 @@
         <v>26</v>
       </c>
       <c r="N261" t="n">
-        <v>4196.8725305216</v>
+        <v>4196.872531224</v>
       </c>
       <c r="O261" t="n">
-        <v>109118.6857935616</v>
+        <v>109118.685811824</v>
       </c>
       <c r="P261" t="n">
         <v>5900</v>
@@ -12048,7 +12048,7 @@
         </is>
       </c>
       <c r="J266" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="K266" t="n">
         <v>0</v>
@@ -12057,19 +12057,19 @@
         <v>0</v>
       </c>
       <c r="M266" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="N266" t="n">
         <v>2567</v>
       </c>
       <c r="O266" t="n">
-        <v>102680</v>
+        <v>97546</v>
       </c>
       <c r="P266" t="n">
         <v>4500</v>
       </c>
       <c r="Q266" t="n">
-        <v>180000</v>
+        <v>171000</v>
       </c>
     </row>
     <row r="267">
@@ -12885,10 +12885,10 @@
         <v>83</v>
       </c>
       <c r="N285" t="n">
-        <v>4285.195740113</v>
+        <v>4285.1957531144</v>
       </c>
       <c r="O285" t="n">
-        <v>355671.246429379</v>
+        <v>355671.2475084952</v>
       </c>
       <c r="P285" t="n">
         <v>6900</v>
@@ -13178,7 +13178,7 @@
         </is>
       </c>
       <c r="J292" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K292" t="n">
         <v>0</v>
@@ -13187,19 +13187,19 @@
         <v>0</v>
       </c>
       <c r="M292" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N292" t="n">
-        <v>4605.2147497639</v>
+        <v>4605.2147542533</v>
       </c>
       <c r="O292" t="n">
-        <v>262497.2407365423</v>
+        <v>257892.0262381848</v>
       </c>
       <c r="P292" t="n">
         <v>7600</v>
       </c>
       <c r="Q292" t="n">
-        <v>433200</v>
+        <v>425600</v>
       </c>
     </row>
     <row r="293">
@@ -13219,7 +13219,7 @@
         </is>
       </c>
       <c r="J293" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K293" t="n">
         <v>0</v>
@@ -13228,19 +13228,19 @@
         <v>0</v>
       </c>
       <c r="M293" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="N293" t="n">
         <v>3591.13</v>
       </c>
       <c r="O293" t="n">
-        <v>305246.05</v>
+        <v>290881.53</v>
       </c>
       <c r="P293" t="n">
         <v>6300</v>
       </c>
       <c r="Q293" t="n">
-        <v>535500</v>
+        <v>510300</v>
       </c>
     </row>
     <row r="294">
@@ -13858,7 +13858,7 @@
         </is>
       </c>
       <c r="J307" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K307" t="n">
         <v>0</v>
@@ -13867,19 +13867,19 @@
         <v>0</v>
       </c>
       <c r="M307" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N307" t="n">
-        <v>27123.765196998</v>
+        <v>27123.76518797</v>
       </c>
       <c r="O307" t="n">
-        <v>705217.895121948</v>
+        <v>678094.12969925</v>
       </c>
       <c r="P307" t="n">
         <v>44500</v>
       </c>
       <c r="Q307" t="n">
-        <v>1157000</v>
+        <v>1112500</v>
       </c>
     </row>
     <row r="308">
@@ -14206,7 +14206,7 @@
         </is>
       </c>
       <c r="J315" t="n">
-        <v>709</v>
+        <v>691</v>
       </c>
       <c r="K315" t="n">
         <v>0</v>
@@ -14215,19 +14215,19 @@
         <v>0</v>
       </c>
       <c r="M315" t="n">
-        <v>709</v>
+        <v>691</v>
       </c>
       <c r="N315" t="n">
-        <v>1561.0019185688</v>
+        <v>1561.0022278481</v>
       </c>
       <c r="O315" t="n">
-        <v>1106750.360265279</v>
+        <v>1078652.539443037</v>
       </c>
       <c r="P315" t="n">
         <v>2900</v>
       </c>
       <c r="Q315" t="n">
-        <v>2056100</v>
+        <v>2003900</v>
       </c>
     </row>
     <row r="316">
@@ -14470,7 +14470,7 @@
         </is>
       </c>
       <c r="J321" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="K321" t="n">
         <v>0</v>
@@ -14479,19 +14479,19 @@
         <v>0</v>
       </c>
       <c r="M321" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="N321" t="n">
         <v>5847.99</v>
       </c>
       <c r="O321" t="n">
-        <v>292399.5</v>
+        <v>269007.54</v>
       </c>
       <c r="P321" t="n">
         <v>7500</v>
       </c>
       <c r="Q321" t="n">
-        <v>375000</v>
+        <v>345000</v>
       </c>
     </row>
     <row r="322">
@@ -15670,10 +15670,10 @@
         <v>88</v>
       </c>
       <c r="N347" t="n">
-        <v>5218.1705677419</v>
+        <v>5218.1705692109</v>
       </c>
       <c r="O347" t="n">
-        <v>459199.0099612873</v>
+        <v>459199.0100905592</v>
       </c>
       <c r="P347" t="n">
         <v>8500</v>
@@ -15716,10 +15716,10 @@
         <v>105</v>
       </c>
       <c r="N348" t="n">
-        <v>1595.0093238434</v>
+        <v>1595.0093202147</v>
       </c>
       <c r="O348" t="n">
-        <v>167475.979003557</v>
+        <v>167475.9786225435</v>
       </c>
       <c r="P348" t="n">
         <v>2600</v>
@@ -15750,7 +15750,7 @@
         </is>
       </c>
       <c r="J349" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K349" t="n">
         <v>0</v>
@@ -15759,19 +15759,19 @@
         <v>0</v>
       </c>
       <c r="M349" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N349" t="n">
         <v>5194</v>
       </c>
       <c r="O349" t="n">
-        <v>441490</v>
+        <v>436296</v>
       </c>
       <c r="P349" t="n">
         <v>9000</v>
       </c>
       <c r="Q349" t="n">
-        <v>765000</v>
+        <v>756000</v>
       </c>
     </row>
     <row r="350">
@@ -16029,7 +16029,7 @@
         </is>
       </c>
       <c r="J355" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="K355" t="n">
         <v>0</v>
@@ -16038,19 +16038,19 @@
         <v>0</v>
       </c>
       <c r="M355" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="N355" t="n">
         <v>18536</v>
       </c>
       <c r="O355" t="n">
-        <v>203896</v>
+        <v>129752</v>
       </c>
       <c r="P355" t="n">
         <v>30900</v>
       </c>
       <c r="Q355" t="n">
-        <v>339900</v>
+        <v>216300</v>
       </c>
     </row>
     <row r="356">
@@ -16305,7 +16305,7 @@
         </is>
       </c>
       <c r="J361" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K361" t="n">
         <v>0</v>
@@ -16314,19 +16314,19 @@
         <v>0</v>
       </c>
       <c r="M361" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N361" t="n">
         <v>34546</v>
       </c>
       <c r="O361" t="n">
-        <v>172730</v>
+        <v>138184</v>
       </c>
       <c r="P361" t="n">
         <v>57900</v>
       </c>
       <c r="Q361" t="n">
-        <v>289500</v>
+        <v>231600</v>
       </c>
     </row>
     <row r="362">
@@ -16351,7 +16351,7 @@
         </is>
       </c>
       <c r="J362" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K362" t="n">
         <v>0</v>
@@ -16360,19 +16360,19 @@
         <v>0</v>
       </c>
       <c r="M362" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N362" t="n">
-        <v>23521.624067797</v>
+        <v>23521.623965517</v>
       </c>
       <c r="O362" t="n">
-        <v>94086.49627118801</v>
+        <v>70564.87189655099</v>
       </c>
       <c r="P362" t="n">
         <v>39000</v>
       </c>
       <c r="Q362" t="n">
-        <v>156000</v>
+        <v>117000</v>
       </c>
     </row>
     <row r="363">
@@ -16397,7 +16397,7 @@
         </is>
       </c>
       <c r="J363" t="n">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="K363" t="n">
         <v>0</v>
@@ -16406,19 +16406,19 @@
         <v>0</v>
       </c>
       <c r="M363" t="n">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="N363" t="n">
-        <v>1778.4726494689</v>
+        <v>1778.4726526892</v>
       </c>
       <c r="O363" t="n">
-        <v>147613.2299059187</v>
+        <v>133385.44895169</v>
       </c>
       <c r="P363" t="n">
         <v>4900</v>
       </c>
       <c r="Q363" t="n">
-        <v>406700</v>
+        <v>367500</v>
       </c>
     </row>
     <row r="364">
@@ -18818,10 +18818,10 @@
         <v>23</v>
       </c>
       <c r="N415" t="n">
-        <v>2252.2973618785</v>
+        <v>2252.2974859551</v>
       </c>
       <c r="O415" t="n">
-        <v>51802.8393232055</v>
+        <v>51802.8421769673</v>
       </c>
       <c r="P415" t="n">
         <v>3900</v>
@@ -19005,10 +19005,10 @@
         <v>193</v>
       </c>
       <c r="N419" t="n">
-        <v>2328.1186979327</v>
+        <v>2328.1186975309</v>
       </c>
       <c r="O419" t="n">
-        <v>449326.9087010111</v>
+        <v>449326.9086234637</v>
       </c>
       <c r="P419" t="n">
         <v>4500</v>
@@ -19361,7 +19361,7 @@
         </is>
       </c>
       <c r="J427" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K427" t="n">
         <v>0</v>
@@ -19370,19 +19370,19 @@
         <v>0</v>
       </c>
       <c r="M427" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N427" t="n">
         <v>4544</v>
       </c>
       <c r="O427" t="n">
-        <v>395328</v>
+        <v>390784</v>
       </c>
       <c r="P427" t="n">
         <v>7900</v>
       </c>
       <c r="Q427" t="n">
-        <v>687300</v>
+        <v>679400</v>
       </c>
     </row>
     <row r="428">
@@ -19545,7 +19545,7 @@
         </is>
       </c>
       <c r="J431" t="n">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="K431" t="n">
         <v>0</v>
@@ -19554,19 +19554,19 @@
         <v>0</v>
       </c>
       <c r="M431" t="n">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="N431" t="n">
-        <v>4907.8221561969</v>
+        <v>4907.8221972318</v>
       </c>
       <c r="O431" t="n">
-        <v>922670.5653650173</v>
+        <v>868684.5289100285</v>
       </c>
       <c r="P431" t="n">
         <v>8200</v>
       </c>
       <c r="Q431" t="n">
-        <v>1541600</v>
+        <v>1451400</v>
       </c>
     </row>
     <row r="432">
@@ -19925,10 +19925,10 @@
         <v>96</v>
       </c>
       <c r="N439" t="n">
-        <v>3903.736877898</v>
+        <v>3903.7369302326</v>
       </c>
       <c r="O439" t="n">
-        <v>374758.740278208</v>
+        <v>374758.7453023296</v>
       </c>
       <c r="P439" t="n">
         <v>7500</v>
@@ -20593,7 +20593,7 @@
         </is>
       </c>
       <c r="J454" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="K454" t="n">
         <v>0</v>
@@ -20602,19 +20602,19 @@
         <v>0</v>
       </c>
       <c r="M454" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="N454" t="n">
         <v>6849.2</v>
       </c>
       <c r="O454" t="n">
-        <v>280817.2</v>
+        <v>260269.6</v>
       </c>
       <c r="P454" t="n">
         <v>11500</v>
       </c>
       <c r="Q454" t="n">
-        <v>471500</v>
+        <v>437000</v>
       </c>
     </row>
     <row r="455">
@@ -21237,7 +21237,7 @@
         </is>
       </c>
       <c r="J468" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K468" t="n">
         <v>0</v>
@@ -21246,19 +21246,19 @@
         <v>0</v>
       </c>
       <c r="M468" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N468" t="n">
         <v>8806</v>
       </c>
       <c r="O468" t="n">
-        <v>255374</v>
+        <v>246568</v>
       </c>
       <c r="P468" t="n">
         <v>14900</v>
       </c>
       <c r="Q468" t="n">
-        <v>432100</v>
+        <v>417200</v>
       </c>
     </row>
     <row r="469">
@@ -21651,7 +21651,7 @@
         </is>
       </c>
       <c r="J477" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="K477" t="n">
         <v>0</v>
@@ -21660,19 +21660,19 @@
         <v>0</v>
       </c>
       <c r="M477" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="N477" t="n">
         <v>10398</v>
       </c>
       <c r="O477" t="n">
-        <v>415920</v>
+        <v>374328</v>
       </c>
       <c r="P477" t="n">
         <v>16900</v>
       </c>
       <c r="Q477" t="n">
-        <v>676000</v>
+        <v>608400</v>
       </c>
     </row>
     <row r="478">
@@ -21697,7 +21697,7 @@
         </is>
       </c>
       <c r="J478" t="n">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="K478" t="n">
         <v>0</v>
@@ -21706,19 +21706,19 @@
         <v>0</v>
       </c>
       <c r="M478" t="n">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="N478" t="n">
         <v>5922</v>
       </c>
       <c r="O478" t="n">
-        <v>911988</v>
+        <v>900144</v>
       </c>
       <c r="P478" t="n">
         <v>9900</v>
       </c>
       <c r="Q478" t="n">
-        <v>1524600</v>
+        <v>1504800</v>
       </c>
     </row>
     <row r="479">
@@ -22523,7 +22523,7 @@
         </is>
       </c>
       <c r="J496" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K496" t="n">
         <v>0</v>
@@ -22532,19 +22532,19 @@
         <v>0</v>
       </c>
       <c r="M496" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N496" t="n">
         <v>14050</v>
       </c>
       <c r="O496" t="n">
-        <v>252900</v>
+        <v>238850</v>
       </c>
       <c r="P496" t="n">
         <v>23900</v>
       </c>
       <c r="Q496" t="n">
-        <v>430200</v>
+        <v>406300</v>
       </c>
     </row>
     <row r="497">
@@ -22615,7 +22615,7 @@
         </is>
       </c>
       <c r="J498" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K498" t="n">
         <v>0</v>
@@ -22624,19 +22624,19 @@
         <v>0</v>
       </c>
       <c r="M498" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N498" t="n">
         <v>3639.35</v>
       </c>
       <c r="O498" t="n">
-        <v>207442.95</v>
+        <v>203803.6</v>
       </c>
       <c r="P498" t="n">
         <v>7500</v>
       </c>
       <c r="Q498" t="n">
-        <v>427500</v>
+        <v>420000</v>
       </c>
     </row>
     <row r="499">
@@ -22707,7 +22707,7 @@
         </is>
       </c>
       <c r="J500" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K500" t="n">
         <v>0</v>
@@ -22716,19 +22716,19 @@
         <v>0</v>
       </c>
       <c r="M500" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N500" t="n">
         <v>5640</v>
       </c>
       <c r="O500" t="n">
-        <v>169200</v>
+        <v>163560</v>
       </c>
       <c r="P500" t="n">
         <v>9900</v>
       </c>
       <c r="Q500" t="n">
-        <v>297000</v>
+        <v>287100</v>
       </c>
     </row>
     <row r="501">
@@ -23400,7 +23400,7 @@
         </is>
       </c>
       <c r="J515" t="n">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="K515" t="n">
         <v>0</v>
@@ -23409,19 +23409,19 @@
         <v>0</v>
       </c>
       <c r="M515" t="n">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="N515" t="n">
-        <v>1516.0387919529</v>
+        <v>1516.0387905286</v>
       </c>
       <c r="O515" t="n">
-        <v>265306.7885917575</v>
+        <v>247114.3228561618</v>
       </c>
       <c r="P515" t="n">
         <v>2300</v>
       </c>
       <c r="Q515" t="n">
-        <v>402500</v>
+        <v>374900</v>
       </c>
     </row>
     <row r="516">
@@ -23504,10 +23504,10 @@
         <v>407</v>
       </c>
       <c r="N517" t="n">
-        <v>2458.5129828687</v>
+        <v>2458.5129162428</v>
       </c>
       <c r="O517" t="n">
-        <v>1000614.784027561</v>
+        <v>1000614.75691082</v>
       </c>
       <c r="P517" t="n">
         <v>3500</v>
@@ -23550,10 +23550,10 @@
         <v>153</v>
       </c>
       <c r="N518" t="n">
-        <v>1771.0903406814</v>
+        <v>1771.0902822581</v>
       </c>
       <c r="O518" t="n">
-        <v>270976.8221242542</v>
+        <v>270976.8131854893</v>
       </c>
       <c r="P518" t="n">
         <v>2500</v>
@@ -23642,10 +23642,10 @@
         <v>250</v>
       </c>
       <c r="N520" t="n">
-        <v>1803.0157988368</v>
+        <v>1803.015867082</v>
       </c>
       <c r="O520" t="n">
-        <v>450753.9497092</v>
+        <v>450753.9667705</v>
       </c>
       <c r="P520" t="n">
         <v>2500</v>
@@ -23734,10 +23734,10 @@
         <v>511</v>
       </c>
       <c r="N522" t="n">
-        <v>2122.1637428023</v>
+        <v>2122.163732778</v>
       </c>
       <c r="O522" t="n">
-        <v>1084425.672571975</v>
+        <v>1084425.667449558</v>
       </c>
       <c r="P522" t="n">
         <v>2900</v>
@@ -23826,10 +23826,10 @@
         <v>287</v>
       </c>
       <c r="N524" t="n">
-        <v>2056.0828901137</v>
+        <v>2056.0828704663</v>
       </c>
       <c r="O524" t="n">
-        <v>590095.7894626319</v>
+        <v>590095.7838238281</v>
       </c>
       <c r="P524" t="n">
         <v>2900</v>
@@ -23872,10 +23872,10 @@
         <v>329</v>
       </c>
       <c r="N525" t="n">
-        <v>3224.5688657751</v>
+        <v>3224.5689232303</v>
       </c>
       <c r="O525" t="n">
-        <v>1060883.156840008</v>
+        <v>1060883.175742769</v>
       </c>
       <c r="P525" t="n">
         <v>4500</v>
@@ -23918,10 +23918,10 @@
         <v>261</v>
       </c>
       <c r="N526" t="n">
-        <v>1655.9306993948</v>
+        <v>1655.9305693829</v>
       </c>
       <c r="O526" t="n">
-        <v>432197.9125420428</v>
+        <v>432197.8786089369</v>
       </c>
       <c r="P526" t="n">
         <v>2500</v>
@@ -24090,28 +24090,28 @@
         </is>
       </c>
       <c r="J530" t="n">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="K530" t="n">
         <v>0</v>
       </c>
       <c r="L530" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M530" t="n">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="N530" t="n">
-        <v>1592.2806787879</v>
+        <v>1592.2810401003</v>
       </c>
       <c r="O530" t="n">
-        <v>85983.15665454659</v>
+        <v>60506.6795238114</v>
       </c>
       <c r="P530" t="n">
         <v>2500</v>
       </c>
       <c r="Q530" t="n">
-        <v>135000</v>
+        <v>95000</v>
       </c>
     </row>
     <row r="531">
@@ -24192,10 +24192,10 @@
         <v>12</v>
       </c>
       <c r="N532" t="n">
-        <v>2546.9831400966</v>
+        <v>2546.9829528536</v>
       </c>
       <c r="O532" t="n">
-        <v>30563.7976811592</v>
+        <v>30563.7954342432</v>
       </c>
       <c r="P532" t="n">
         <v>3900</v>
@@ -24226,28 +24226,28 @@
         </is>
       </c>
       <c r="J533" t="n">
-        <v>909</v>
+        <v>899</v>
       </c>
       <c r="K533" t="n">
         <v>0</v>
       </c>
       <c r="L533" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M533" t="n">
-        <v>904</v>
+        <v>899</v>
       </c>
       <c r="N533" t="n">
-        <v>1259.2746413793</v>
+        <v>1259.2746531459</v>
       </c>
       <c r="O533" t="n">
-        <v>1138384.275806887</v>
+        <v>1132087.913178164</v>
       </c>
       <c r="P533" t="n">
         <v>1900</v>
       </c>
       <c r="Q533" t="n">
-        <v>1717600</v>
+        <v>1708100</v>
       </c>
     </row>
     <row r="534">
@@ -24405,7 +24405,7 @@
         </is>
       </c>
       <c r="J537" t="n">
-        <v>325</v>
+        <v>265</v>
       </c>
       <c r="K537" t="n">
         <v>0</v>
@@ -24414,19 +24414,19 @@
         <v>0</v>
       </c>
       <c r="M537" t="n">
-        <v>325</v>
+        <v>265</v>
       </c>
       <c r="N537" t="n">
         <v>1801</v>
       </c>
       <c r="O537" t="n">
-        <v>585325</v>
+        <v>477265</v>
       </c>
       <c r="P537" t="n">
         <v>2900</v>
       </c>
       <c r="Q537" t="n">
-        <v>942500</v>
+        <v>768500</v>
       </c>
     </row>
     <row r="538">
@@ -25114,7 +25114,7 @@
         </is>
       </c>
       <c r="J552" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="K552" t="n">
         <v>0</v>
@@ -25123,19 +25123,19 @@
         <v>0</v>
       </c>
       <c r="M552" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="N552" t="n">
         <v>1245.62</v>
       </c>
       <c r="O552" t="n">
-        <v>132035.72</v>
+        <v>129544.48</v>
       </c>
       <c r="P552" t="n">
         <v>4000</v>
       </c>
       <c r="Q552" t="n">
-        <v>424000</v>
+        <v>416000</v>
       </c>
     </row>
     <row r="553">
@@ -25544,10 +25544,10 @@
         <v>179</v>
       </c>
       <c r="N561" t="n">
-        <v>1690.8700091743</v>
+        <v>1690.8700092251</v>
       </c>
       <c r="O561" t="n">
-        <v>302665.7316421997</v>
+        <v>302665.7316512929</v>
       </c>
       <c r="P561" t="n">
         <v>3000</v>
@@ -26173,7 +26173,7 @@
         </is>
       </c>
       <c r="J575" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="K575" t="n">
         <v>0</v>
@@ -26182,19 +26182,19 @@
         <v>0</v>
       </c>
       <c r="M575" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="N575" t="n">
         <v>4243.87</v>
       </c>
       <c r="O575" t="n">
-        <v>97609.00999999999</v>
+        <v>80633.53</v>
       </c>
       <c r="P575" t="n">
         <v>5900</v>
       </c>
       <c r="Q575" t="n">
-        <v>135700</v>
+        <v>112100</v>
       </c>
     </row>
     <row r="576">
@@ -26315,7 +26315,7 @@
         </is>
       </c>
       <c r="J578" t="n">
-        <v>1300</v>
+        <v>1228</v>
       </c>
       <c r="K578" t="n">
         <v>0</v>
@@ -26324,19 +26324,19 @@
         <v>0</v>
       </c>
       <c r="M578" t="n">
-        <v>1300</v>
+        <v>1228</v>
       </c>
       <c r="N578" t="n">
-        <v>517.29069907291</v>
+        <v>517.29096206919</v>
       </c>
       <c r="O578" t="n">
-        <v>672477.9087947831</v>
+        <v>635233.3014209652</v>
       </c>
       <c r="P578" t="n">
         <v>900</v>
       </c>
       <c r="Q578" t="n">
-        <v>1170000</v>
+        <v>1105200</v>
       </c>
     </row>
     <row r="579">
@@ -26558,10 +26558,10 @@
         <v>25</v>
       </c>
       <c r="N583" t="n">
-        <v>3110.840414859</v>
+        <v>3110.8403177212</v>
       </c>
       <c r="O583" t="n">
-        <v>77771.010371475</v>
+        <v>77771.00794303</v>
       </c>
       <c r="P583" t="n">
         <v>4500</v>
@@ -26590,7 +26590,7 @@
         </is>
       </c>
       <c r="J584" t="n">
-        <v>1284</v>
+        <v>1220</v>
       </c>
       <c r="K584" t="n">
         <v>0</v>
@@ -26599,19 +26599,19 @@
         <v>0</v>
       </c>
       <c r="M584" t="n">
-        <v>1284</v>
+        <v>1220</v>
       </c>
       <c r="N584" t="n">
-        <v>703.79510612101</v>
+        <v>703.79509062003</v>
       </c>
       <c r="O584" t="n">
-        <v>903672.9162593768</v>
+        <v>858630.0105564366</v>
       </c>
       <c r="P584" t="n">
         <v>900</v>
       </c>
       <c r="Q584" t="n">
-        <v>1155600</v>
+        <v>1098000</v>
       </c>
     </row>
     <row r="585">
@@ -26832,13 +26832,13 @@
         </is>
       </c>
       <c r="J589" t="n">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="K589" t="n">
         <v>0</v>
       </c>
       <c r="L589" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M589" t="n">
         <v>191</v>
@@ -27901,10 +27901,10 @@
         <v>35</v>
       </c>
       <c r="N611" t="n">
-        <v>3505.3804081633</v>
+        <v>3505.3804255319</v>
       </c>
       <c r="O611" t="n">
-        <v>122688.3142857155</v>
+        <v>122688.3148936165</v>
       </c>
       <c r="P611" t="n">
         <v>12900</v>
@@ -31334,7 +31334,7 @@
         </is>
       </c>
       <c r="J683" t="n">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="K683" t="n">
         <v>0</v>
@@ -31343,19 +31343,19 @@
         <v>0</v>
       </c>
       <c r="M683" t="n">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="N683" t="n">
         <v>1080.18</v>
       </c>
       <c r="O683" t="n">
-        <v>365100.84</v>
+        <v>360780.12</v>
       </c>
       <c r="P683" t="n">
         <v>4900</v>
       </c>
       <c r="Q683" t="n">
-        <v>1656200</v>
+        <v>1636600</v>
       </c>
     </row>
     <row r="684">
@@ -31754,7 +31754,7 @@
         </is>
       </c>
       <c r="J692" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K692" t="n">
         <v>0</v>
@@ -31763,19 +31763,19 @@
         <v>0</v>
       </c>
       <c r="M692" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N692" t="n">
         <v>110520.77</v>
       </c>
       <c r="O692" t="n">
-        <v>994686.9300000001</v>
+        <v>773645.39</v>
       </c>
       <c r="P692" t="n">
         <v>176900</v>
       </c>
       <c r="Q692" t="n">
-        <v>1592100</v>
+        <v>1238300</v>
       </c>
     </row>
     <row r="693">
@@ -31798,7 +31798,7 @@
         </is>
       </c>
       <c r="J693" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K693" t="n">
         <v>0</v>
@@ -31807,19 +31807,19 @@
         <v>0</v>
       </c>
       <c r="M693" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="N693" t="n">
         <v>6761.25</v>
       </c>
       <c r="O693" t="n">
-        <v>1176457.5</v>
+        <v>1169696.25</v>
       </c>
       <c r="P693" t="n">
         <v>5200</v>
       </c>
       <c r="Q693" t="n">
-        <v>904800</v>
+        <v>899600</v>
       </c>
     </row>
     <row r="694">
@@ -32174,7 +32174,7 @@
         </is>
       </c>
       <c r="J701" t="n">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="K701" t="n">
         <v>0</v>
@@ -32183,19 +32183,19 @@
         <v>0</v>
       </c>
       <c r="M701" t="n">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="N701" t="n">
         <v>3181.9</v>
       </c>
       <c r="O701" t="n">
-        <v>162276.9</v>
+        <v>124094.1</v>
       </c>
       <c r="P701" t="n">
         <v>5100</v>
       </c>
       <c r="Q701" t="n">
-        <v>260100</v>
+        <v>198900</v>
       </c>
     </row>
     <row r="702">
@@ -32264,7 +32264,7 @@
         </is>
       </c>
       <c r="J703" t="n">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="K703" t="n">
         <v>0</v>
@@ -32273,19 +32273,19 @@
         <v>0</v>
       </c>
       <c r="M703" t="n">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="N703" t="n">
         <v>5077</v>
       </c>
       <c r="O703" t="n">
-        <v>533085</v>
+        <v>512777</v>
       </c>
       <c r="P703" t="n">
         <v>8500</v>
       </c>
       <c r="Q703" t="n">
-        <v>892500</v>
+        <v>858500</v>
       </c>
     </row>
     <row r="704">
@@ -32540,7 +32540,7 @@
         </is>
       </c>
       <c r="J709" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K709" t="n">
         <v>0</v>
@@ -32549,19 +32549,19 @@
         <v>0</v>
       </c>
       <c r="M709" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="N709" t="n">
         <v>20700</v>
       </c>
       <c r="O709" t="n">
-        <v>289800</v>
+        <v>227700</v>
       </c>
       <c r="P709" t="n">
         <v>25900</v>
       </c>
       <c r="Q709" t="n">
-        <v>362600</v>
+        <v>284900</v>
       </c>
     </row>
     <row r="710">
@@ -32632,7 +32632,7 @@
         </is>
       </c>
       <c r="J711" t="n">
-        <v>402</v>
+        <v>392</v>
       </c>
       <c r="K711" t="n">
         <v>0</v>
@@ -32641,19 +32641,19 @@
         <v>0</v>
       </c>
       <c r="M711" t="n">
-        <v>402</v>
+        <v>392</v>
       </c>
       <c r="N711" t="n">
-        <v>5218.9108910891</v>
+        <v>5218.9109137056</v>
       </c>
       <c r="O711" t="n">
-        <v>2098002.178217818</v>
+        <v>2045813.078172595</v>
       </c>
       <c r="P711" t="n">
         <v>6500</v>
       </c>
       <c r="Q711" t="n">
-        <v>2613000</v>
+        <v>2548000</v>
       </c>
     </row>
     <row r="712">
@@ -32770,7 +32770,7 @@
         </is>
       </c>
       <c r="J714" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K714" t="n">
         <v>0</v>
@@ -32779,19 +32779,19 @@
         <v>0</v>
       </c>
       <c r="M714" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="N714" t="n">
         <v>7650</v>
       </c>
       <c r="O714" t="n">
-        <v>160650</v>
+        <v>137700</v>
       </c>
       <c r="P714" t="n">
         <v>9900</v>
       </c>
       <c r="Q714" t="n">
-        <v>207900</v>
+        <v>178200</v>
       </c>
     </row>
     <row r="715">
@@ -32816,7 +32816,7 @@
         </is>
       </c>
       <c r="J715" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K715" t="n">
         <v>0</v>
@@ -32825,19 +32825,19 @@
         <v>0</v>
       </c>
       <c r="M715" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N715" t="n">
         <v>19800</v>
       </c>
       <c r="O715" t="n">
-        <v>99000</v>
+        <v>39600</v>
       </c>
       <c r="P715" t="n">
         <v>24900</v>
       </c>
       <c r="Q715" t="n">
-        <v>124500</v>
+        <v>49800</v>
       </c>
     </row>
     <row r="716">
@@ -32908,7 +32908,7 @@
         </is>
       </c>
       <c r="J717" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K717" t="n">
         <v>0</v>
@@ -32917,19 +32917,19 @@
         <v>0</v>
       </c>
       <c r="M717" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N717" t="n">
         <v>18000</v>
       </c>
       <c r="O717" t="n">
-        <v>108000</v>
+        <v>72000</v>
       </c>
       <c r="P717" t="n">
         <v>23900</v>
       </c>
       <c r="Q717" t="n">
-        <v>143400</v>
+        <v>95600</v>
       </c>
     </row>
     <row r="718">
@@ -33000,7 +33000,7 @@
         </is>
       </c>
       <c r="J719" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K719" t="n">
         <v>0</v>
@@ -33009,19 +33009,19 @@
         <v>0</v>
       </c>
       <c r="M719" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="N719" t="n">
         <v>18900</v>
       </c>
       <c r="O719" t="n">
-        <v>170100</v>
+        <v>113400</v>
       </c>
       <c r="P719" t="n">
         <v>24900</v>
       </c>
       <c r="Q719" t="n">
-        <v>224100</v>
+        <v>149400</v>
       </c>
     </row>
     <row r="720">
@@ -33046,7 +33046,7 @@
         </is>
       </c>
       <c r="J720" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K720" t="n">
         <v>0</v>
@@ -33055,19 +33055,19 @@
         <v>0</v>
       </c>
       <c r="M720" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="N720" t="n">
         <v>18000</v>
       </c>
       <c r="O720" t="n">
-        <v>270000</v>
+        <v>216000</v>
       </c>
       <c r="P720" t="n">
         <v>22500</v>
       </c>
       <c r="Q720" t="n">
-        <v>337500</v>
+        <v>270000</v>
       </c>
     </row>
     <row r="721">
@@ -33138,7 +33138,7 @@
         </is>
       </c>
       <c r="J722" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K722" t="n">
         <v>0</v>
@@ -33147,19 +33147,19 @@
         <v>0</v>
       </c>
       <c r="M722" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N722" t="n">
         <v>27900</v>
       </c>
       <c r="O722" t="n">
-        <v>139500</v>
+        <v>111600</v>
       </c>
       <c r="P722" t="n">
         <v>34900</v>
       </c>
       <c r="Q722" t="n">
-        <v>174500</v>
+        <v>139600</v>
       </c>
     </row>
     <row r="723">
@@ -33184,7 +33184,7 @@
         </is>
       </c>
       <c r="J723" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K723" t="n">
         <v>0</v>
@@ -33193,19 +33193,19 @@
         <v>0</v>
       </c>
       <c r="M723" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N723" t="n">
         <v>25200</v>
       </c>
       <c r="O723" t="n">
-        <v>100800</v>
+        <v>50400</v>
       </c>
       <c r="P723" t="n">
         <v>31900</v>
       </c>
       <c r="Q723" t="n">
-        <v>127600</v>
+        <v>63800</v>
       </c>
     </row>
     <row r="724">
@@ -33368,7 +33368,7 @@
         </is>
       </c>
       <c r="J727" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K727" t="n">
         <v>0</v>
@@ -33377,19 +33377,19 @@
         <v>0</v>
       </c>
       <c r="M727" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N727" t="n">
         <v>29700</v>
       </c>
       <c r="O727" t="n">
-        <v>356400</v>
+        <v>326700</v>
       </c>
       <c r="P727" t="n">
         <v>39900</v>
       </c>
       <c r="Q727" t="n">
-        <v>478800</v>
+        <v>438900</v>
       </c>
     </row>
     <row r="728">
@@ -33414,7 +33414,7 @@
         </is>
       </c>
       <c r="J728" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K728" t="n">
         <v>0</v>
@@ -33423,19 +33423,19 @@
         <v>0</v>
       </c>
       <c r="M728" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="N728" t="n">
         <v>31500</v>
       </c>
       <c r="O728" t="n">
-        <v>567000</v>
+        <v>472500</v>
       </c>
       <c r="P728" t="n">
         <v>39900</v>
       </c>
       <c r="Q728" t="n">
-        <v>718200</v>
+        <v>598500</v>
       </c>
     </row>
     <row r="729">
@@ -33506,7 +33506,7 @@
         </is>
       </c>
       <c r="J730" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="K730" t="n">
         <v>0</v>
@@ -33515,19 +33515,19 @@
         <v>0</v>
       </c>
       <c r="M730" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="N730" t="n">
         <v>36000</v>
       </c>
       <c r="O730" t="n">
-        <v>1800000</v>
+        <v>1728000</v>
       </c>
       <c r="P730" t="n">
         <v>45000</v>
       </c>
       <c r="Q730" t="n">
-        <v>2250000</v>
+        <v>2160000</v>
       </c>
     </row>
     <row r="731">
@@ -33690,7 +33690,7 @@
         </is>
       </c>
       <c r="J734" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K734" t="n">
         <v>0</v>
@@ -33699,19 +33699,19 @@
         <v>0</v>
       </c>
       <c r="M734" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N734" t="n">
         <v>28800</v>
       </c>
       <c r="O734" t="n">
-        <v>518400</v>
+        <v>489600</v>
       </c>
       <c r="P734" t="n">
         <v>36000</v>
       </c>
       <c r="Q734" t="n">
-        <v>648000</v>
+        <v>612000</v>
       </c>
     </row>
     <row r="735">
@@ -34012,28 +34012,28 @@
         </is>
       </c>
       <c r="J741" t="n">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="K741" t="n">
         <v>0</v>
       </c>
       <c r="L741" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M741" t="n">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="N741" t="n">
         <v>7480</v>
       </c>
       <c r="O741" t="n">
-        <v>1443640</v>
+        <v>1376320</v>
       </c>
       <c r="P741" t="n">
         <v>9500</v>
       </c>
       <c r="Q741" t="n">
-        <v>1833500</v>
+        <v>1748000</v>
       </c>
     </row>
     <row r="742">
@@ -34242,7 +34242,7 @@
         </is>
       </c>
       <c r="J746" t="n">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="K746" t="n">
         <v>0</v>
@@ -34251,19 +34251,19 @@
         <v>0</v>
       </c>
       <c r="M746" t="n">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="N746" t="n">
         <v>5280</v>
       </c>
       <c r="O746" t="n">
-        <v>612480</v>
+        <v>591360</v>
       </c>
       <c r="P746" t="n">
         <v>6900</v>
       </c>
       <c r="Q746" t="n">
-        <v>800400</v>
+        <v>772800</v>
       </c>
     </row>
     <row r="747">
@@ -34334,13 +34334,13 @@
         </is>
       </c>
       <c r="J748" t="n">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="K748" t="n">
         <v>0</v>
       </c>
       <c r="L748" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M748" t="n">
         <v>97</v>
@@ -34380,7 +34380,7 @@
         </is>
       </c>
       <c r="J749" t="n">
-        <v>567</v>
+        <v>558</v>
       </c>
       <c r="K749" t="n">
         <v>0</v>
@@ -34389,19 +34389,19 @@
         <v>0</v>
       </c>
       <c r="M749" t="n">
-        <v>567</v>
+        <v>558</v>
       </c>
       <c r="N749" t="n">
         <v>1584</v>
       </c>
       <c r="O749" t="n">
-        <v>898128</v>
+        <v>883872</v>
       </c>
       <c r="P749" t="n">
         <v>2000</v>
       </c>
       <c r="Q749" t="n">
-        <v>1134000</v>
+        <v>1116000</v>
       </c>
     </row>
     <row r="750">
@@ -34472,7 +34472,7 @@
         </is>
       </c>
       <c r="J751" t="n">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="K751" t="n">
         <v>0</v>
@@ -34481,19 +34481,19 @@
         <v>0</v>
       </c>
       <c r="M751" t="n">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="N751" t="n">
         <v>3872</v>
       </c>
       <c r="O751" t="n">
-        <v>638880</v>
+        <v>584672</v>
       </c>
       <c r="P751" t="n">
         <v>4900</v>
       </c>
       <c r="Q751" t="n">
-        <v>808500</v>
+        <v>739900</v>
       </c>
     </row>
     <row r="752">
@@ -34564,7 +34564,7 @@
         </is>
       </c>
       <c r="J753" t="n">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="K753" t="n">
         <v>0</v>
@@ -34573,19 +34573,19 @@
         <v>0</v>
       </c>
       <c r="M753" t="n">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="N753" t="n">
         <v>6160</v>
       </c>
       <c r="O753" t="n">
-        <v>1293600</v>
+        <v>1287440</v>
       </c>
       <c r="P753" t="n">
         <v>7900</v>
       </c>
       <c r="Q753" t="n">
-        <v>1659000</v>
+        <v>1651100</v>
       </c>
     </row>
     <row r="754">
@@ -34748,7 +34748,7 @@
         </is>
       </c>
       <c r="J757" t="n">
-        <v>345</v>
+        <v>331</v>
       </c>
       <c r="K757" t="n">
         <v>0</v>
@@ -34757,19 +34757,19 @@
         <v>0</v>
       </c>
       <c r="M757" t="n">
-        <v>345</v>
+        <v>331</v>
       </c>
       <c r="N757" t="n">
         <v>3344</v>
       </c>
       <c r="O757" t="n">
-        <v>1153680</v>
+        <v>1106864</v>
       </c>
       <c r="P757" t="n">
         <v>4500</v>
       </c>
       <c r="Q757" t="n">
-        <v>1552500</v>
+        <v>1489500</v>
       </c>
     </row>
     <row r="758">
@@ -34886,7 +34886,7 @@
         </is>
       </c>
       <c r="J760" t="n">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="K760" t="n">
         <v>0</v>
@@ -34895,19 +34895,19 @@
         <v>0</v>
       </c>
       <c r="M760" t="n">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="N760" t="n">
         <v>3520</v>
       </c>
       <c r="O760" t="n">
-        <v>538560</v>
+        <v>531520</v>
       </c>
       <c r="P760" t="n">
         <v>4500</v>
       </c>
       <c r="Q760" t="n">
-        <v>688500</v>
+        <v>679500</v>
       </c>
     </row>
     <row r="761">
@@ -34978,7 +34978,7 @@
         </is>
       </c>
       <c r="J762" t="n">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="K762" t="n">
         <v>0</v>
@@ -34987,19 +34987,19 @@
         <v>0</v>
       </c>
       <c r="M762" t="n">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="N762" t="n">
         <v>9240</v>
       </c>
       <c r="O762" t="n">
-        <v>5996760</v>
+        <v>5987520</v>
       </c>
       <c r="P762" t="n">
         <v>11500</v>
       </c>
       <c r="Q762" t="n">
-        <v>7463500</v>
+        <v>7452000</v>
       </c>
     </row>
     <row r="763">
@@ -35024,7 +35024,7 @@
         </is>
       </c>
       <c r="J763" t="n">
-        <v>208</v>
+        <v>177</v>
       </c>
       <c r="K763" t="n">
         <v>0</v>
@@ -35033,19 +35033,19 @@
         <v>0</v>
       </c>
       <c r="M763" t="n">
-        <v>208</v>
+        <v>177</v>
       </c>
       <c r="N763" t="n">
         <v>2288</v>
       </c>
       <c r="O763" t="n">
-        <v>475904</v>
+        <v>404976</v>
       </c>
       <c r="P763" t="n">
         <v>2900</v>
       </c>
       <c r="Q763" t="n">
-        <v>603200</v>
+        <v>513300</v>
       </c>
     </row>
     <row r="764">
@@ -35070,7 +35070,7 @@
         </is>
       </c>
       <c r="J764" t="n">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="K764" t="n">
         <v>0</v>
@@ -35079,19 +35079,19 @@
         <v>0</v>
       </c>
       <c r="M764" t="n">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="N764" t="n">
         <v>7216</v>
       </c>
       <c r="O764" t="n">
-        <v>1912240</v>
+        <v>1825648</v>
       </c>
       <c r="P764" t="n">
         <v>9000</v>
       </c>
       <c r="Q764" t="n">
-        <v>2385000</v>
+        <v>2277000</v>
       </c>
     </row>
     <row r="765">
@@ -35116,7 +35116,7 @@
         </is>
       </c>
       <c r="J765" t="n">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="K765" t="n">
         <v>0</v>
@@ -35125,19 +35125,19 @@
         <v>0</v>
       </c>
       <c r="M765" t="n">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="N765" t="n">
         <v>4576</v>
       </c>
       <c r="O765" t="n">
-        <v>462176</v>
+        <v>407264</v>
       </c>
       <c r="P765" t="n">
         <v>5900</v>
       </c>
       <c r="Q765" t="n">
-        <v>595900</v>
+        <v>525100</v>
       </c>
     </row>
     <row r="766">
@@ -35346,7 +35346,7 @@
         </is>
       </c>
       <c r="J770" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K770" t="n">
         <v>0</v>
@@ -35355,19 +35355,19 @@
         <v>0</v>
       </c>
       <c r="M770" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N770" t="n">
         <v>9500</v>
       </c>
       <c r="O770" t="n">
-        <v>161500</v>
+        <v>152000</v>
       </c>
       <c r="P770" t="n">
         <v>11400</v>
       </c>
       <c r="Q770" t="n">
-        <v>193800</v>
+        <v>182400</v>
       </c>
     </row>
     <row r="771">
@@ -36460,7 +36460,7 @@
         </is>
       </c>
       <c r="J794" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K794" t="n">
         <v>0</v>
@@ -36469,19 +36469,19 @@
         <v>0</v>
       </c>
       <c r="M794" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N794" t="n">
         <v>1236.3</v>
       </c>
       <c r="O794" t="n">
-        <v>42034.2</v>
+        <v>40797.9</v>
       </c>
       <c r="P794" t="n">
         <v>2300</v>
       </c>
       <c r="Q794" t="n">
-        <v>78200</v>
+        <v>75900</v>
       </c>
     </row>
     <row r="795">
@@ -36603,7 +36603,7 @@
         </is>
       </c>
       <c r="J797" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K797" t="n">
         <v>0</v>
@@ -36612,19 +36612,19 @@
         <v>0</v>
       </c>
       <c r="M797" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="N797" t="n">
         <v>751.45</v>
       </c>
       <c r="O797" t="n">
-        <v>26300.75</v>
+        <v>24797.85</v>
       </c>
       <c r="P797" t="n">
         <v>2500</v>
       </c>
       <c r="Q797" t="n">
-        <v>87500</v>
+        <v>82500</v>
       </c>
     </row>
     <row r="798">
@@ -36649,13 +36649,13 @@
         </is>
       </c>
       <c r="J798" t="n">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="K798" t="n">
         <v>0</v>
       </c>
       <c r="L798" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M798" t="n">
         <v>189</v>

--- a/bodegas/LJ-05.xlsx
+++ b/bodegas/LJ-05.xlsx
@@ -7227,10 +7227,10 @@
         <v>240</v>
       </c>
       <c r="N159" t="n">
-        <v>2582.255546613</v>
+        <v>2582.2555436242</v>
       </c>
       <c r="O159" t="n">
-        <v>619741.3311871201</v>
+        <v>619741.3304698081</v>
       </c>
       <c r="P159" t="n">
         <v>4500</v>
@@ -14085,10 +14085,10 @@
         <v>14</v>
       </c>
       <c r="N312" t="n">
-        <v>8332.779621212099</v>
+        <v>8332.779620253201</v>
       </c>
       <c r="O312" t="n">
-        <v>116658.9146969694</v>
+        <v>116658.9146835448</v>
       </c>
       <c r="P312" t="n">
         <v>14900</v>
@@ -21617,10 +21617,10 @@
         <v>147</v>
       </c>
       <c r="N476" t="n">
-        <v>17075.989522491</v>
+        <v>17075.989522161</v>
       </c>
       <c r="O476" t="n">
-        <v>2510170.459806177</v>
+        <v>2510170.459757667</v>
       </c>
       <c r="P476" t="n">
         <v>27500</v>
@@ -24102,10 +24102,10 @@
         <v>38</v>
       </c>
       <c r="N530" t="n">
-        <v>1592.2810401003</v>
+        <v>1592.2811378003</v>
       </c>
       <c r="O530" t="n">
-        <v>60506.6795238114</v>
+        <v>60506.6832364114</v>
       </c>
       <c r="P530" t="n">
         <v>2500</v>
@@ -26321,22 +26321,22 @@
         <v>0</v>
       </c>
       <c r="L578" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M578" t="n">
-        <v>1228</v>
+        <v>1223</v>
       </c>
       <c r="N578" t="n">
-        <v>517.29096206919</v>
+        <v>517.29097263266</v>
       </c>
       <c r="O578" t="n">
-        <v>635233.3014209652</v>
+        <v>632646.8595297432</v>
       </c>
       <c r="P578" t="n">
         <v>900</v>
       </c>
       <c r="Q578" t="n">
-        <v>1105200</v>
+        <v>1100700</v>
       </c>
     </row>
     <row r="579">

--- a/bodegas/LJ-05.xlsx
+++ b/bodegas/LJ-05.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-03</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-04</t>
         </is>
       </c>
     </row>
@@ -1028,10 +1028,10 @@
         <v>206</v>
       </c>
       <c r="N15" t="n">
-        <v>3376.7464524986</v>
+        <v>3376.7464515243</v>
       </c>
       <c r="O15" t="n">
-        <v>695609.7692147116</v>
+        <v>695609.7690140058</v>
       </c>
       <c r="P15" t="n">
         <v>4500</v>
@@ -1663,10 +1663,10 @@
         <v>15</v>
       </c>
       <c r="N31" t="n">
-        <v>3926.8370954357</v>
+        <v>3926.8370909091</v>
       </c>
       <c r="O31" t="n">
-        <v>58902.5564315355</v>
+        <v>58902.5563636365</v>
       </c>
       <c r="P31" t="n">
         <v>4800</v>
@@ -1705,10 +1705,10 @@
         <v>4</v>
       </c>
       <c r="N32" t="n">
-        <v>11324.694146341</v>
+        <v>11324.693846154</v>
       </c>
       <c r="O32" t="n">
-        <v>45298.776585364</v>
+        <v>45298.775384616</v>
       </c>
       <c r="P32" t="n">
         <v>19900</v>
@@ -2101,10 +2101,10 @@
         <v>63</v>
       </c>
       <c r="N42" t="n">
-        <v>15403.520977011</v>
+        <v>15403.521040462</v>
       </c>
       <c r="O42" t="n">
-        <v>970421.821551693</v>
+        <v>970421.825549106</v>
       </c>
       <c r="P42" t="n">
         <v>33500</v>
@@ -3099,10 +3099,10 @@
         <v>14</v>
       </c>
       <c r="N64" t="n">
-        <v>16486.408571429</v>
+        <v>16486.40848</v>
       </c>
       <c r="O64" t="n">
-        <v>230809.720000006</v>
+        <v>230809.71872</v>
       </c>
       <c r="P64" t="n">
         <v>30500</v>
@@ -3141,10 +3141,10 @@
         <v>41</v>
       </c>
       <c r="N65" t="n">
-        <v>15711.965777778</v>
+        <v>15711.96573991</v>
       </c>
       <c r="O65" t="n">
-        <v>644190.5968888979</v>
+        <v>644190.59533631</v>
       </c>
       <c r="P65" t="n">
         <v>28500</v>
@@ -3952,10 +3952,10 @@
         <v>5</v>
       </c>
       <c r="N84" t="n">
-        <v>200072.20075</v>
+        <v>200072.20121739</v>
       </c>
       <c r="O84" t="n">
-        <v>1000361.00375</v>
+        <v>1000361.00608695</v>
       </c>
       <c r="P84" t="n">
         <v>312000</v>
@@ -5321,7 +5321,7 @@
         </is>
       </c>
       <c r="J116" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K116" t="n">
         <v>0</v>
@@ -5330,19 +5330,19 @@
         <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="N116" t="n">
         <v>2570.16</v>
       </c>
       <c r="O116" t="n">
-        <v>46262.88</v>
+        <v>38552.39999999999</v>
       </c>
       <c r="P116" t="n">
         <v>4700</v>
       </c>
       <c r="Q116" t="n">
-        <v>84600</v>
+        <v>70500</v>
       </c>
     </row>
     <row r="117">
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="J126" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K126" t="n">
         <v>0</v>
@@ -5756,19 +5756,19 @@
         <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N126" t="n">
         <v>2563.34</v>
       </c>
       <c r="O126" t="n">
-        <v>10253.36</v>
+        <v>7690.02</v>
       </c>
       <c r="P126" t="n">
         <v>4700</v>
       </c>
       <c r="Q126" t="n">
-        <v>18800</v>
+        <v>14100</v>
       </c>
     </row>
     <row r="127">
@@ -6120,10 +6120,10 @@
         <v>64</v>
       </c>
       <c r="N134" t="n">
-        <v>732.63416666667</v>
+        <v>732.63425531915</v>
       </c>
       <c r="O134" t="n">
-        <v>46888.58666666688</v>
+        <v>46888.5923404256</v>
       </c>
       <c r="P134" t="n">
         <v>6200</v>
@@ -6331,7 +6331,7 @@
         </is>
       </c>
       <c r="J139" t="n">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="K139" t="n">
         <v>0</v>
@@ -6340,19 +6340,19 @@
         <v>0</v>
       </c>
       <c r="M139" t="n">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="N139" t="n">
         <v>2833</v>
       </c>
       <c r="O139" t="n">
-        <v>1988766</v>
+        <v>1983100</v>
       </c>
       <c r="P139" t="n">
         <v>3500</v>
       </c>
       <c r="Q139" t="n">
-        <v>2457000</v>
+        <v>2450000</v>
       </c>
     </row>
     <row r="140">
@@ -6372,7 +6372,7 @@
         </is>
       </c>
       <c r="J140" t="n">
-        <v>1559</v>
+        <v>1538</v>
       </c>
       <c r="K140" t="n">
         <v>0</v>
@@ -6381,19 +6381,19 @@
         <v>0</v>
       </c>
       <c r="M140" t="n">
-        <v>1559</v>
+        <v>1538</v>
       </c>
       <c r="N140" t="n">
         <v>1726.32</v>
       </c>
       <c r="O140" t="n">
-        <v>2691332.88</v>
+        <v>2655080.16</v>
       </c>
       <c r="P140" t="n">
         <v>1500</v>
       </c>
       <c r="Q140" t="n">
-        <v>2338500</v>
+        <v>2307000</v>
       </c>
     </row>
     <row r="141">
@@ -6595,7 +6595,7 @@
         </is>
       </c>
       <c r="J145" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K145" t="n">
         <v>0</v>
@@ -6604,19 +6604,19 @@
         <v>0</v>
       </c>
       <c r="M145" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N145" t="n">
         <v>3775.99</v>
       </c>
       <c r="O145" t="n">
-        <v>162367.57</v>
+        <v>158591.58</v>
       </c>
       <c r="P145" t="n">
         <v>7300</v>
       </c>
       <c r="Q145" t="n">
-        <v>313900</v>
+        <v>306600</v>
       </c>
     </row>
     <row r="146">
@@ -7128,7 +7128,7 @@
         </is>
       </c>
       <c r="J157" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="K157" t="n">
         <v>0</v>
@@ -7137,19 +7137,19 @@
         <v>0</v>
       </c>
       <c r="M157" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="N157" t="n">
         <v>2804.33</v>
       </c>
       <c r="O157" t="n">
-        <v>238368.05</v>
+        <v>232759.39</v>
       </c>
       <c r="P157" t="n">
         <v>4900</v>
       </c>
       <c r="Q157" t="n">
-        <v>416500</v>
+        <v>406700</v>
       </c>
     </row>
     <row r="158">
@@ -7215,7 +7215,7 @@
         </is>
       </c>
       <c r="J159" t="n">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="K159" t="n">
         <v>0</v>
@@ -7224,19 +7224,19 @@
         <v>0</v>
       </c>
       <c r="M159" t="n">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="N159" t="n">
-        <v>2582.2555436242</v>
+        <v>2582.2555195682</v>
       </c>
       <c r="O159" t="n">
-        <v>619741.3304698081</v>
+        <v>604247.7915789587</v>
       </c>
       <c r="P159" t="n">
         <v>4500</v>
       </c>
       <c r="Q159" t="n">
-        <v>1080000</v>
+        <v>1053000</v>
       </c>
     </row>
     <row r="160">
@@ -7307,7 +7307,7 @@
         </is>
       </c>
       <c r="J161" t="n">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="K161" t="n">
         <v>0</v>
@@ -7316,19 +7316,19 @@
         <v>0</v>
       </c>
       <c r="M161" t="n">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="N161" t="n">
-        <v>5216.8960627633</v>
+        <v>5216.8960541642</v>
       </c>
       <c r="O161" t="n">
-        <v>234760.3228243485</v>
+        <v>172157.5697874186</v>
       </c>
       <c r="P161" t="n">
         <v>8500</v>
       </c>
       <c r="Q161" t="n">
-        <v>382500</v>
+        <v>280500</v>
       </c>
     </row>
     <row r="162">
@@ -7503,10 +7503,10 @@
         <v>678</v>
       </c>
       <c r="N165" t="n">
-        <v>2694.8231670588</v>
+        <v>2694.8231638418</v>
       </c>
       <c r="O165" t="n">
-        <v>1827090.107265867</v>
+        <v>1827090.105084741</v>
       </c>
       <c r="P165" t="n">
         <v>4900</v>
@@ -7537,7 +7537,7 @@
         </is>
       </c>
       <c r="J166" t="n">
-        <v>1255</v>
+        <v>1235</v>
       </c>
       <c r="K166" t="n">
         <v>0</v>
@@ -7546,19 +7546,19 @@
         <v>0</v>
       </c>
       <c r="M166" t="n">
-        <v>1255</v>
+        <v>1235</v>
       </c>
       <c r="N166" t="n">
         <v>156.25</v>
       </c>
       <c r="O166" t="n">
-        <v>196093.75</v>
+        <v>192968.75</v>
       </c>
       <c r="P166" t="n">
         <v>250</v>
       </c>
       <c r="Q166" t="n">
-        <v>313750</v>
+        <v>308750</v>
       </c>
     </row>
     <row r="167">
@@ -7779,10 +7779,10 @@
         <v>4</v>
       </c>
       <c r="N171" t="n">
-        <v>3795.7100075815</v>
+        <v>3795.7100075887</v>
       </c>
       <c r="O171" t="n">
-        <v>15182.840030326</v>
+        <v>15182.8400303548</v>
       </c>
       <c r="P171" t="n">
         <v>6200</v>
@@ -7854,7 +7854,7 @@
         </is>
       </c>
       <c r="J173" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K173" t="n">
         <v>0</v>
@@ -7863,19 +7863,19 @@
         <v>0</v>
       </c>
       <c r="M173" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N173" t="n">
         <v>2612.77</v>
       </c>
       <c r="O173" t="n">
-        <v>44417.09</v>
+        <v>39191.55</v>
       </c>
       <c r="P173" t="n">
         <v>4900</v>
       </c>
       <c r="Q173" t="n">
-        <v>83300</v>
+        <v>73500</v>
       </c>
     </row>
     <row r="174">
@@ -8004,10 +8004,10 @@
         <v>64</v>
       </c>
       <c r="N176" t="n">
-        <v>4890.9300489596</v>
+        <v>4890.9300493218</v>
       </c>
       <c r="O176" t="n">
-        <v>313019.5231334144</v>
+        <v>313019.5231565952</v>
       </c>
       <c r="P176" t="n">
         <v>8200</v>
@@ -8087,7 +8087,7 @@
         </is>
       </c>
       <c r="J178" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="K178" t="n">
         <v>0</v>
@@ -8096,19 +8096,19 @@
         <v>0</v>
       </c>
       <c r="M178" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="N178" t="n">
-        <v>4967.8552054795</v>
+        <v>4967.8663636364</v>
       </c>
       <c r="O178" t="n">
-        <v>258328.470684934</v>
+        <v>223553.986363638</v>
       </c>
       <c r="P178" t="n">
         <v>7500</v>
       </c>
       <c r="Q178" t="n">
-        <v>390000</v>
+        <v>337500</v>
       </c>
     </row>
     <row r="179">
@@ -8128,7 +8128,7 @@
         </is>
       </c>
       <c r="J179" t="n">
-        <v>1664</v>
+        <v>1164</v>
       </c>
       <c r="K179" t="n">
         <v>0</v>
@@ -8137,19 +8137,19 @@
         <v>0</v>
       </c>
       <c r="M179" t="n">
-        <v>1664</v>
+        <v>1164</v>
       </c>
       <c r="N179" t="n">
         <v>180</v>
       </c>
       <c r="O179" t="n">
-        <v>299520</v>
+        <v>209520</v>
       </c>
       <c r="P179" t="n">
         <v>220</v>
       </c>
       <c r="Q179" t="n">
-        <v>366080</v>
+        <v>256080</v>
       </c>
     </row>
     <row r="180">
@@ -8174,7 +8174,7 @@
         </is>
       </c>
       <c r="J180" t="n">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="K180" t="n">
         <v>0</v>
@@ -8183,19 +8183,19 @@
         <v>0</v>
       </c>
       <c r="M180" t="n">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="N180" t="n">
         <v>3472</v>
       </c>
       <c r="O180" t="n">
-        <v>354144</v>
+        <v>336784</v>
       </c>
       <c r="P180" t="n">
         <v>4800</v>
       </c>
       <c r="Q180" t="n">
-        <v>489600</v>
+        <v>465600</v>
       </c>
     </row>
     <row r="181">
@@ -8353,7 +8353,7 @@
         </is>
       </c>
       <c r="J184" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="K184" t="n">
         <v>0</v>
@@ -8362,19 +8362,19 @@
         <v>0</v>
       </c>
       <c r="M184" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="N184" t="n">
         <v>7041</v>
       </c>
       <c r="O184" t="n">
-        <v>556239</v>
+        <v>542157</v>
       </c>
       <c r="P184" t="n">
         <v>11500</v>
       </c>
       <c r="Q184" t="n">
-        <v>908500</v>
+        <v>885500</v>
       </c>
     </row>
     <row r="185">
@@ -8445,7 +8445,7 @@
         </is>
       </c>
       <c r="J186" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="K186" t="n">
         <v>0</v>
@@ -8454,19 +8454,19 @@
         <v>0</v>
       </c>
       <c r="M186" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="N186" t="n">
         <v>8012</v>
       </c>
       <c r="O186" t="n">
-        <v>544816</v>
+        <v>512768</v>
       </c>
       <c r="P186" t="n">
         <v>13200</v>
       </c>
       <c r="Q186" t="n">
-        <v>897600</v>
+        <v>844800</v>
       </c>
     </row>
     <row r="187">
@@ -8668,7 +8668,7 @@
         </is>
       </c>
       <c r="J191" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="K191" t="n">
         <v>0</v>
@@ -8677,19 +8677,19 @@
         <v>0</v>
       </c>
       <c r="M191" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N191" t="n">
-        <v>3594.2538618926</v>
+        <v>3594.2537131631</v>
       </c>
       <c r="O191" t="n">
-        <v>172524.1853708448</v>
+        <v>165335.6708055026</v>
       </c>
       <c r="P191" t="n">
         <v>6500</v>
       </c>
       <c r="Q191" t="n">
-        <v>312000</v>
+        <v>299000</v>
       </c>
     </row>
     <row r="192">
@@ -8763,7 +8763,7 @@
         </is>
       </c>
       <c r="J193" t="n">
-        <v>1713</v>
+        <v>1707</v>
       </c>
       <c r="K193" t="n">
         <v>0</v>
@@ -8772,19 +8772,19 @@
         <v>0</v>
       </c>
       <c r="M193" t="n">
-        <v>1713</v>
+        <v>1707</v>
       </c>
       <c r="N193" t="n">
         <v>489.88</v>
       </c>
       <c r="O193" t="n">
-        <v>839164.4399999999</v>
+        <v>836225.16</v>
       </c>
       <c r="P193" t="n">
         <v>700</v>
       </c>
       <c r="Q193" t="n">
-        <v>1199100</v>
+        <v>1194900</v>
       </c>
     </row>
     <row r="194">
@@ -8855,7 +8855,7 @@
         </is>
       </c>
       <c r="J195" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K195" t="n">
         <v>0</v>
@@ -8864,19 +8864,19 @@
         <v>0</v>
       </c>
       <c r="M195" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="N195" t="n">
         <v>8154</v>
       </c>
       <c r="O195" t="n">
-        <v>562626</v>
+        <v>546318</v>
       </c>
       <c r="P195" t="n">
         <v>13500</v>
       </c>
       <c r="Q195" t="n">
-        <v>931500</v>
+        <v>904500</v>
       </c>
     </row>
     <row r="196">
@@ -8957,10 +8957,10 @@
         <v>166</v>
       </c>
       <c r="N197" t="n">
-        <v>616.01871837471</v>
+        <v>616.01871807046</v>
       </c>
       <c r="O197" t="n">
-        <v>102259.1072502019</v>
+        <v>102259.1071996964</v>
       </c>
       <c r="P197" t="n">
         <v>800</v>
@@ -9446,7 +9446,7 @@
         </is>
       </c>
       <c r="J208" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K208" t="n">
         <v>0</v>
@@ -9455,19 +9455,19 @@
         <v>0</v>
       </c>
       <c r="M208" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N208" t="n">
         <v>15851.61</v>
       </c>
       <c r="O208" t="n">
-        <v>79258.05</v>
+        <v>15851.61</v>
       </c>
       <c r="P208" t="n">
         <v>23900</v>
       </c>
       <c r="Q208" t="n">
-        <v>119500</v>
+        <v>23900</v>
       </c>
     </row>
     <row r="209">
@@ -9490,7 +9490,7 @@
         </is>
       </c>
       <c r="J209" t="n">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="K209" t="n">
         <v>0</v>
@@ -9499,19 +9499,19 @@
         <v>0</v>
       </c>
       <c r="M209" t="n">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="N209" t="n">
         <v>1441.01</v>
       </c>
       <c r="O209" t="n">
-        <v>720505</v>
+        <v>714740.96</v>
       </c>
       <c r="P209" t="n">
         <v>2100</v>
       </c>
       <c r="Q209" t="n">
-        <v>1050000</v>
+        <v>1041600</v>
       </c>
     </row>
     <row r="210">
@@ -9575,7 +9575,7 @@
         </is>
       </c>
       <c r="J211" t="n">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="K211" t="n">
         <v>0</v>
@@ -9584,19 +9584,19 @@
         <v>0</v>
       </c>
       <c r="M211" t="n">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="N211" t="n">
         <v>4193.85</v>
       </c>
       <c r="O211" t="n">
-        <v>218080.2</v>
+        <v>167754</v>
       </c>
       <c r="P211" t="n">
         <v>7500</v>
       </c>
       <c r="Q211" t="n">
-        <v>390000</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="212">
@@ -9682,10 +9682,10 @@
         <v>77</v>
       </c>
       <c r="N213" t="n">
-        <v>4372.2107916548</v>
+        <v>4372.2107917679</v>
       </c>
       <c r="O213" t="n">
-        <v>336660.2309574196</v>
+        <v>336660.2309661284</v>
       </c>
       <c r="P213" t="n">
         <v>7500</v>
@@ -9716,7 +9716,7 @@
         </is>
       </c>
       <c r="J214" t="n">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="K214" t="n">
         <v>0</v>
@@ -9725,19 +9725,19 @@
         <v>0</v>
       </c>
       <c r="M214" t="n">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="N214" t="n">
-        <v>1592.5662962963</v>
+        <v>1592.5662209302</v>
       </c>
       <c r="O214" t="n">
-        <v>399734.1403703713</v>
+        <v>382215.893023248</v>
       </c>
       <c r="P214" t="n">
         <v>3900</v>
       </c>
       <c r="Q214" t="n">
-        <v>978900</v>
+        <v>936000</v>
       </c>
     </row>
     <row r="215">
@@ -9757,7 +9757,7 @@
         </is>
       </c>
       <c r="J215" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K215" t="n">
         <v>0</v>
@@ -9766,19 +9766,19 @@
         <v>0</v>
       </c>
       <c r="M215" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N215" t="n">
         <v>4513.76</v>
       </c>
       <c r="O215" t="n">
-        <v>523596.16</v>
+        <v>519082.4</v>
       </c>
       <c r="P215" t="n">
         <v>8900</v>
       </c>
       <c r="Q215" t="n">
-        <v>1032400</v>
+        <v>1023500</v>
       </c>
     </row>
     <row r="216">
@@ -9798,7 +9798,7 @@
         </is>
       </c>
       <c r="J216" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K216" t="n">
         <v>0</v>
@@ -9807,19 +9807,19 @@
         <v>0</v>
       </c>
       <c r="M216" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N216" t="n">
         <v>2224.56</v>
       </c>
       <c r="O216" t="n">
-        <v>102329.76</v>
+        <v>100105.2</v>
       </c>
       <c r="P216" t="n">
         <v>3900</v>
       </c>
       <c r="Q216" t="n">
-        <v>179400</v>
+        <v>175500</v>
       </c>
     </row>
     <row r="217">
@@ -9885,7 +9885,7 @@
         </is>
       </c>
       <c r="J218" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K218" t="n">
         <v>0</v>
@@ -9894,19 +9894,19 @@
         <v>0</v>
       </c>
       <c r="M218" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N218" t="n">
         <v>2695.04</v>
       </c>
       <c r="O218" t="n">
-        <v>78156.16</v>
+        <v>75461.12</v>
       </c>
       <c r="P218" t="n">
         <v>7300</v>
       </c>
       <c r="Q218" t="n">
-        <v>211700</v>
+        <v>204400</v>
       </c>
     </row>
     <row r="219">
@@ -10075,7 +10075,7 @@
         </is>
       </c>
       <c r="J222" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K222" t="n">
         <v>0</v>
@@ -10084,19 +10084,19 @@
         <v>0</v>
       </c>
       <c r="M222" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="N222" t="n">
         <v>1770.37</v>
       </c>
       <c r="O222" t="n">
-        <v>308044.38</v>
+        <v>306274.01</v>
       </c>
       <c r="P222" t="n">
         <v>3900</v>
       </c>
       <c r="Q222" t="n">
-        <v>678600</v>
+        <v>674700</v>
       </c>
     </row>
     <row r="223">
@@ -10851,7 +10851,7 @@
         </is>
       </c>
       <c r="J239" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="K239" t="n">
         <v>0</v>
@@ -10860,19 +10860,19 @@
         <v>0</v>
       </c>
       <c r="M239" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="N239" t="n">
         <v>11921.4</v>
       </c>
       <c r="O239" t="n">
-        <v>917947.7999999999</v>
+        <v>894105</v>
       </c>
       <c r="P239" t="n">
         <v>19900</v>
       </c>
       <c r="Q239" t="n">
-        <v>1532300</v>
+        <v>1492500</v>
       </c>
     </row>
     <row r="240">
@@ -10936,7 +10936,7 @@
         </is>
       </c>
       <c r="J241" t="n">
-        <v>709</v>
+        <v>702</v>
       </c>
       <c r="K241" t="n">
         <v>0</v>
@@ -10945,19 +10945,19 @@
         <v>0</v>
       </c>
       <c r="M241" t="n">
-        <v>709</v>
+        <v>702</v>
       </c>
       <c r="N241" t="n">
         <v>3751</v>
       </c>
       <c r="O241" t="n">
-        <v>2659459</v>
+        <v>2633202</v>
       </c>
       <c r="P241" t="n">
         <v>6400</v>
       </c>
       <c r="Q241" t="n">
-        <v>4537600</v>
+        <v>4492800</v>
       </c>
     </row>
     <row r="242">
@@ -11031,7 +11031,7 @@
         </is>
       </c>
       <c r="J243" t="n">
-        <v>353</v>
+        <v>313</v>
       </c>
       <c r="K243" t="n">
         <v>0</v>
@@ -11040,19 +11040,19 @@
         <v>0</v>
       </c>
       <c r="M243" t="n">
-        <v>353</v>
+        <v>313</v>
       </c>
       <c r="N243" t="n">
-        <v>2403.5131199831</v>
+        <v>2403.5134379057</v>
       </c>
       <c r="O243" t="n">
-        <v>848440.1313540343</v>
+        <v>752299.7060644841</v>
       </c>
       <c r="P243" t="n">
         <v>3500</v>
       </c>
       <c r="Q243" t="n">
-        <v>1235500</v>
+        <v>1095500</v>
       </c>
     </row>
     <row r="244">
@@ -11077,7 +11077,7 @@
         </is>
       </c>
       <c r="J244" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K244" t="n">
         <v>0</v>
@@ -11086,19 +11086,19 @@
         <v>0</v>
       </c>
       <c r="M244" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N244" t="n">
         <v>14778</v>
       </c>
       <c r="O244" t="n">
-        <v>325116</v>
+        <v>310338</v>
       </c>
       <c r="P244" t="n">
         <v>24900</v>
       </c>
       <c r="Q244" t="n">
-        <v>547800</v>
+        <v>522900</v>
       </c>
     </row>
     <row r="245">
@@ -11845,10 +11845,10 @@
         <v>26</v>
       </c>
       <c r="N261" t="n">
-        <v>4196.872531224</v>
+        <v>4196.8725319267</v>
       </c>
       <c r="O261" t="n">
-        <v>109118.685811824</v>
+        <v>109118.6858300942</v>
       </c>
       <c r="P261" t="n">
         <v>5900</v>
@@ -12002,7 +12002,7 @@
         </is>
       </c>
       <c r="J265" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K265" t="n">
         <v>0</v>
@@ -12011,19 +12011,19 @@
         <v>0</v>
       </c>
       <c r="M265" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N265" t="n">
         <v>8794.48</v>
       </c>
       <c r="O265" t="n">
-        <v>404546.08</v>
+        <v>395751.6</v>
       </c>
       <c r="P265" t="n">
         <v>14500</v>
       </c>
       <c r="Q265" t="n">
-        <v>667000</v>
+        <v>652500</v>
       </c>
     </row>
     <row r="266">
@@ -12130,7 +12130,7 @@
         </is>
       </c>
       <c r="J268" t="n">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="K268" t="n">
         <v>0</v>
@@ -12139,19 +12139,19 @@
         <v>0</v>
       </c>
       <c r="M268" t="n">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="N268" t="n">
         <v>2517.22</v>
       </c>
       <c r="O268" t="n">
-        <v>493375.1199999999</v>
+        <v>463168.48</v>
       </c>
       <c r="P268" t="n">
         <v>4200</v>
       </c>
       <c r="Q268" t="n">
-        <v>823200</v>
+        <v>772800</v>
       </c>
     </row>
     <row r="269">
@@ -12224,10 +12224,10 @@
         <v>19</v>
       </c>
       <c r="N270" t="n">
-        <v>22485.695561036</v>
+        <v>22485.695555556</v>
       </c>
       <c r="O270" t="n">
-        <v>427228.215659684</v>
+        <v>427228.215555564</v>
       </c>
       <c r="P270" t="n">
         <v>36500</v>
@@ -12376,7 +12376,7 @@
         </is>
       </c>
       <c r="J274" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K274" t="n">
         <v>0</v>
@@ -12385,19 +12385,19 @@
         <v>0</v>
       </c>
       <c r="M274" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N274" t="n">
         <v>7103</v>
       </c>
       <c r="O274" t="n">
-        <v>177575</v>
+        <v>170472</v>
       </c>
       <c r="P274" t="n">
         <v>10700</v>
       </c>
       <c r="Q274" t="n">
-        <v>267500</v>
+        <v>256800</v>
       </c>
     </row>
     <row r="275">
@@ -12425,7 +12425,7 @@
         </is>
       </c>
       <c r="J275" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K275" t="n">
         <v>0</v>
@@ -12434,19 +12434,19 @@
         <v>0</v>
       </c>
       <c r="M275" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N275" t="n">
         <v>24538.02</v>
       </c>
       <c r="O275" t="n">
-        <v>171766.14</v>
+        <v>122690.1</v>
       </c>
       <c r="P275" t="n">
         <v>52900</v>
       </c>
       <c r="Q275" t="n">
-        <v>370300</v>
+        <v>264500</v>
       </c>
     </row>
     <row r="276">
@@ -12478,10 +12478,10 @@
         <v>64</v>
       </c>
       <c r="N276" t="n">
-        <v>2680.7396948941</v>
+        <v>2680.739694704</v>
       </c>
       <c r="O276" t="n">
-        <v>171567.3404732224</v>
+        <v>171567.340461056</v>
       </c>
       <c r="P276" t="n">
         <v>4900</v>
@@ -12553,7 +12553,7 @@
         </is>
       </c>
       <c r="J278" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K278" t="n">
         <v>0</v>
@@ -12562,19 +12562,19 @@
         <v>0</v>
       </c>
       <c r="M278" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N278" t="n">
         <v>14060.64</v>
       </c>
       <c r="O278" t="n">
-        <v>407758.56</v>
+        <v>393697.92</v>
       </c>
       <c r="P278" t="n">
         <v>22900</v>
       </c>
       <c r="Q278" t="n">
-        <v>664100</v>
+        <v>641200</v>
       </c>
     </row>
     <row r="279">
@@ -12824,7 +12824,7 @@
         </is>
       </c>
       <c r="J284" t="n">
-        <v>451</v>
+        <v>421</v>
       </c>
       <c r="K284" t="n">
         <v>0</v>
@@ -12833,19 +12833,19 @@
         <v>0</v>
       </c>
       <c r="M284" t="n">
-        <v>451</v>
+        <v>421</v>
       </c>
       <c r="N284" t="n">
         <v>3877.89</v>
       </c>
       <c r="O284" t="n">
-        <v>1748928.39</v>
+        <v>1632591.69</v>
       </c>
       <c r="P284" t="n">
         <v>6500</v>
       </c>
       <c r="Q284" t="n">
-        <v>2931500</v>
+        <v>2736500</v>
       </c>
     </row>
     <row r="285">
@@ -13311,7 +13311,7 @@
         </is>
       </c>
       <c r="J295" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K295" t="n">
         <v>0</v>
@@ -13320,19 +13320,19 @@
         <v>0</v>
       </c>
       <c r="M295" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="N295" t="n">
-        <v>11562.038465753</v>
+        <v>11562.038444444</v>
       </c>
       <c r="O295" t="n">
-        <v>323737.077041084</v>
+        <v>300612.999555544</v>
       </c>
       <c r="P295" t="n">
         <v>18500</v>
       </c>
       <c r="Q295" t="n">
-        <v>518000</v>
+        <v>481000</v>
       </c>
     </row>
     <row r="296">
@@ -13357,7 +13357,7 @@
         </is>
       </c>
       <c r="J296" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K296" t="n">
         <v>0</v>
@@ -13366,19 +13366,19 @@
         <v>0</v>
       </c>
       <c r="M296" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="N296" t="n">
-        <v>13513.643106061</v>
+        <v>13513.643153846</v>
       </c>
       <c r="O296" t="n">
-        <v>594600.296666684</v>
+        <v>567573.012461532</v>
       </c>
       <c r="P296" t="n">
         <v>21900</v>
       </c>
       <c r="Q296" t="n">
-        <v>963600</v>
+        <v>919800</v>
       </c>
     </row>
     <row r="297">
@@ -13633,7 +13633,7 @@
         </is>
       </c>
       <c r="J302" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K302" t="n">
         <v>0</v>
@@ -13642,19 +13642,19 @@
         <v>0</v>
       </c>
       <c r="M302" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N302" t="n">
         <v>22730.48</v>
       </c>
       <c r="O302" t="n">
-        <v>340957.2</v>
+        <v>318226.72</v>
       </c>
       <c r="P302" t="n">
         <v>36900</v>
       </c>
       <c r="Q302" t="n">
-        <v>553500</v>
+        <v>516600</v>
       </c>
     </row>
     <row r="303">
@@ -13720,7 +13720,7 @@
         </is>
       </c>
       <c r="J304" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K304" t="n">
         <v>0</v>
@@ -13729,19 +13729,19 @@
         <v>0</v>
       </c>
       <c r="M304" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N304" t="n">
         <v>20727.89</v>
       </c>
       <c r="O304" t="n">
-        <v>165823.12</v>
+        <v>103639.45</v>
       </c>
       <c r="P304" t="n">
         <v>33500</v>
       </c>
       <c r="Q304" t="n">
-        <v>268000</v>
+        <v>167500</v>
       </c>
     </row>
     <row r="305">
@@ -13870,10 +13870,10 @@
         <v>25</v>
       </c>
       <c r="N307" t="n">
-        <v>27123.76518797</v>
+        <v>27123.765160681</v>
       </c>
       <c r="O307" t="n">
-        <v>678094.12969925</v>
+        <v>678094.129017025</v>
       </c>
       <c r="P307" t="n">
         <v>44500</v>
@@ -14206,7 +14206,7 @@
         </is>
       </c>
       <c r="J315" t="n">
-        <v>691</v>
+        <v>662</v>
       </c>
       <c r="K315" t="n">
         <v>0</v>
@@ -14215,19 +14215,19 @@
         <v>0</v>
       </c>
       <c r="M315" t="n">
-        <v>691</v>
+        <v>662</v>
       </c>
       <c r="N315" t="n">
-        <v>1561.0022278481</v>
+        <v>1561.0026027397</v>
       </c>
       <c r="O315" t="n">
-        <v>1078652.539443037</v>
+        <v>1033383.723013681</v>
       </c>
       <c r="P315" t="n">
         <v>2900</v>
       </c>
       <c r="Q315" t="n">
-        <v>2003900</v>
+        <v>1919800</v>
       </c>
     </row>
     <row r="316">
@@ -14792,10 +14792,10 @@
         <v>22</v>
       </c>
       <c r="N328" t="n">
-        <v>548.1471609756099</v>
+        <v>548.14714985309</v>
       </c>
       <c r="O328" t="n">
-        <v>12059.23754146342</v>
+        <v>12059.23729676798</v>
       </c>
       <c r="P328" t="n">
         <v>2000</v>
@@ -16121,7 +16121,7 @@
         </is>
       </c>
       <c r="J357" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K357" t="n">
         <v>0</v>
@@ -16130,19 +16130,19 @@
         <v>0</v>
       </c>
       <c r="M357" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N357" t="n">
         <v>15824</v>
       </c>
       <c r="O357" t="n">
-        <v>110768</v>
+        <v>63296</v>
       </c>
       <c r="P357" t="n">
         <v>26900</v>
       </c>
       <c r="Q357" t="n">
-        <v>188300</v>
+        <v>107600</v>
       </c>
     </row>
     <row r="358">
@@ -16409,10 +16409,10 @@
         <v>75</v>
       </c>
       <c r="N363" t="n">
-        <v>1778.4726526892</v>
+        <v>1778.4726559172</v>
       </c>
       <c r="O363" t="n">
-        <v>133385.44895169</v>
+        <v>133385.44919379</v>
       </c>
       <c r="P363" t="n">
         <v>4900</v>
@@ -16581,7 +16581,7 @@
         </is>
       </c>
       <c r="J367" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="K367" t="n">
         <v>0</v>
@@ -16590,19 +16590,19 @@
         <v>0</v>
       </c>
       <c r="M367" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="N367" t="n">
         <v>25534</v>
       </c>
       <c r="O367" t="n">
-        <v>1021360</v>
+        <v>868156</v>
       </c>
       <c r="P367" t="n">
         <v>40900</v>
       </c>
       <c r="Q367" t="n">
-        <v>1636000</v>
+        <v>1390600</v>
       </c>
     </row>
     <row r="368">
@@ -18576,7 +18576,7 @@
         </is>
       </c>
       <c r="J410" t="n">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="K410" t="n">
         <v>0</v>
@@ -18585,19 +18585,19 @@
         <v>0</v>
       </c>
       <c r="M410" t="n">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="N410" t="n">
         <v>8858.16</v>
       </c>
       <c r="O410" t="n">
-        <v>823808.88</v>
+        <v>779518.08</v>
       </c>
       <c r="P410" t="n">
         <v>15500</v>
       </c>
       <c r="Q410" t="n">
-        <v>1441500</v>
+        <v>1364000</v>
       </c>
     </row>
     <row r="411">
@@ -18622,7 +18622,7 @@
         </is>
       </c>
       <c r="J411" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K411" t="n">
         <v>0</v>
@@ -18631,19 +18631,19 @@
         <v>0</v>
       </c>
       <c r="M411" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N411" t="n">
         <v>10411</v>
       </c>
       <c r="O411" t="n">
-        <v>312330</v>
+        <v>301919</v>
       </c>
       <c r="P411" t="n">
         <v>16900</v>
       </c>
       <c r="Q411" t="n">
-        <v>507000</v>
+        <v>490100</v>
       </c>
     </row>
     <row r="412">
@@ -19223,7 +19223,7 @@
         </is>
       </c>
       <c r="J424" t="n">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="K424" t="n">
         <v>0</v>
@@ -19232,19 +19232,19 @@
         <v>0</v>
       </c>
       <c r="M424" t="n">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="N424" t="n">
         <v>3519</v>
       </c>
       <c r="O424" t="n">
-        <v>362457</v>
+        <v>341343</v>
       </c>
       <c r="P424" t="n">
         <v>5900</v>
       </c>
       <c r="Q424" t="n">
-        <v>607700</v>
+        <v>572300</v>
       </c>
     </row>
     <row r="425">
@@ -19361,7 +19361,7 @@
         </is>
       </c>
       <c r="J427" t="n">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="K427" t="n">
         <v>0</v>
@@ -19370,19 +19370,19 @@
         <v>0</v>
       </c>
       <c r="M427" t="n">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="N427" t="n">
         <v>4544</v>
       </c>
       <c r="O427" t="n">
-        <v>390784</v>
+        <v>281728</v>
       </c>
       <c r="P427" t="n">
         <v>7900</v>
       </c>
       <c r="Q427" t="n">
-        <v>679400</v>
+        <v>489800</v>
       </c>
     </row>
     <row r="428">
@@ -19557,10 +19557,10 @@
         <v>177</v>
       </c>
       <c r="N431" t="n">
-        <v>4907.8221972318</v>
+        <v>4907.8222048611</v>
       </c>
       <c r="O431" t="n">
-        <v>868684.5289100285</v>
+        <v>868684.5302604146</v>
       </c>
       <c r="P431" t="n">
         <v>8200</v>
@@ -19925,10 +19925,10 @@
         <v>96</v>
       </c>
       <c r="N439" t="n">
-        <v>3903.7369302326</v>
+        <v>3903.736969697</v>
       </c>
       <c r="O439" t="n">
-        <v>374758.7453023296</v>
+        <v>374758.749090912</v>
       </c>
       <c r="P439" t="n">
         <v>7500</v>
@@ -20559,10 +20559,10 @@
         <v>203</v>
       </c>
       <c r="N453" t="n">
-        <v>5869.1726051282</v>
+        <v>5869.1725975359</v>
       </c>
       <c r="O453" t="n">
-        <v>1191442.038841025</v>
+        <v>1191442.037299788</v>
       </c>
       <c r="P453" t="n">
         <v>9500</v>
@@ -20593,7 +20593,7 @@
         </is>
       </c>
       <c r="J454" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="K454" t="n">
         <v>0</v>
@@ -20602,19 +20602,19 @@
         <v>0</v>
       </c>
       <c r="M454" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="N454" t="n">
         <v>6849.2</v>
       </c>
       <c r="O454" t="n">
-        <v>260269.6</v>
+        <v>226023.6</v>
       </c>
       <c r="P454" t="n">
         <v>11500</v>
       </c>
       <c r="Q454" t="n">
-        <v>437000</v>
+        <v>379500</v>
       </c>
     </row>
     <row r="455">
@@ -20685,7 +20685,7 @@
         </is>
       </c>
       <c r="J456" t="n">
-        <v>140</v>
+        <v>230</v>
       </c>
       <c r="K456" t="n">
         <v>0</v>
@@ -20694,19 +20694,19 @@
         <v>0</v>
       </c>
       <c r="M456" t="n">
-        <v>140</v>
+        <v>230</v>
       </c>
       <c r="N456" t="n">
         <v>5772</v>
       </c>
       <c r="O456" t="n">
-        <v>808080</v>
+        <v>1327560</v>
       </c>
       <c r="P456" t="n">
         <v>9900</v>
       </c>
       <c r="Q456" t="n">
-        <v>1386000</v>
+        <v>2277000</v>
       </c>
     </row>
     <row r="457">
@@ -20823,7 +20823,7 @@
         </is>
       </c>
       <c r="J459" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="K459" t="n">
         <v>0</v>
@@ -20832,19 +20832,19 @@
         <v>0</v>
       </c>
       <c r="M459" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="N459" t="n">
         <v>13098</v>
       </c>
       <c r="O459" t="n">
-        <v>379842</v>
+        <v>327450</v>
       </c>
       <c r="P459" t="n">
         <v>21200</v>
       </c>
       <c r="Q459" t="n">
-        <v>614800</v>
+        <v>530000</v>
       </c>
     </row>
     <row r="460">
@@ -21007,7 +21007,7 @@
         </is>
       </c>
       <c r="J463" t="n">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="K463" t="n">
         <v>0</v>
@@ -21016,19 +21016,19 @@
         <v>0</v>
       </c>
       <c r="M463" t="n">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="N463" t="n">
         <v>3898</v>
       </c>
       <c r="O463" t="n">
-        <v>561312</v>
+        <v>549618</v>
       </c>
       <c r="P463" t="n">
         <v>6900</v>
       </c>
       <c r="Q463" t="n">
-        <v>993600</v>
+        <v>972900</v>
       </c>
     </row>
     <row r="464">
@@ -21191,7 +21191,7 @@
         </is>
       </c>
       <c r="J467" t="n">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="K467" t="n">
         <v>0</v>
@@ -21200,19 +21200,19 @@
         <v>0</v>
       </c>
       <c r="M467" t="n">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="N467" t="n">
         <v>5682</v>
       </c>
       <c r="O467" t="n">
-        <v>1210266</v>
+        <v>1204584</v>
       </c>
       <c r="P467" t="n">
         <v>9900</v>
       </c>
       <c r="Q467" t="n">
-        <v>2108700</v>
+        <v>2098800</v>
       </c>
     </row>
     <row r="468">
@@ -22017,7 +22017,7 @@
         </is>
       </c>
       <c r="J485" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="K485" t="n">
         <v>0</v>
@@ -22026,19 +22026,19 @@
         <v>0</v>
       </c>
       <c r="M485" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="N485" t="n">
         <v>10755</v>
       </c>
       <c r="O485" t="n">
-        <v>397935</v>
+        <v>333405</v>
       </c>
       <c r="P485" t="n">
         <v>17900</v>
       </c>
       <c r="Q485" t="n">
-        <v>662300</v>
+        <v>554900</v>
       </c>
     </row>
     <row r="486">
@@ -22569,7 +22569,7 @@
         </is>
       </c>
       <c r="J497" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="K497" t="n">
         <v>0</v>
@@ -22578,19 +22578,19 @@
         <v>0</v>
       </c>
       <c r="M497" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="N497" t="n">
         <v>8700</v>
       </c>
       <c r="O497" t="n">
-        <v>339300</v>
+        <v>321900</v>
       </c>
       <c r="P497" t="n">
         <v>14900</v>
       </c>
       <c r="Q497" t="n">
-        <v>581100</v>
+        <v>551300</v>
       </c>
     </row>
     <row r="498">
@@ -22661,7 +22661,7 @@
         </is>
       </c>
       <c r="J499" t="n">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="K499" t="n">
         <v>0</v>
@@ -22670,19 +22670,19 @@
         <v>0</v>
       </c>
       <c r="M499" t="n">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="N499" t="n">
         <v>1326</v>
       </c>
       <c r="O499" t="n">
-        <v>474708</v>
+        <v>472056</v>
       </c>
       <c r="P499" t="n">
         <v>2500</v>
       </c>
       <c r="Q499" t="n">
-        <v>895000</v>
+        <v>890000</v>
       </c>
     </row>
     <row r="500">
@@ -23400,7 +23400,7 @@
         </is>
       </c>
       <c r="J515" t="n">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="K515" t="n">
         <v>0</v>
@@ -23409,19 +23409,19 @@
         <v>0</v>
       </c>
       <c r="M515" t="n">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="N515" t="n">
-        <v>1516.0387905286</v>
+        <v>1516.0387891009</v>
       </c>
       <c r="O515" t="n">
-        <v>247114.3228561618</v>
+        <v>228921.8571542359</v>
       </c>
       <c r="P515" t="n">
         <v>2300</v>
       </c>
       <c r="Q515" t="n">
-        <v>374900</v>
+        <v>347300</v>
       </c>
     </row>
     <row r="516">
@@ -23504,10 +23504,10 @@
         <v>407</v>
       </c>
       <c r="N517" t="n">
-        <v>2458.5129162428</v>
+        <v>2458.5128483396</v>
       </c>
       <c r="O517" t="n">
-        <v>1000614.75691082</v>
+        <v>1000614.729274217</v>
       </c>
       <c r="P517" t="n">
         <v>3500</v>
@@ -23550,10 +23550,10 @@
         <v>153</v>
       </c>
       <c r="N518" t="n">
-        <v>1771.0902822581</v>
+        <v>1771.0902626263</v>
       </c>
       <c r="O518" t="n">
-        <v>270976.8131854893</v>
+        <v>270976.8101818239</v>
       </c>
       <c r="P518" t="n">
         <v>2500</v>
@@ -23596,10 +23596,10 @@
         <v>440</v>
       </c>
       <c r="N519" t="n">
-        <v>2079.383962775</v>
+        <v>2079.3839381583</v>
       </c>
       <c r="O519" t="n">
-        <v>914928.9436209999</v>
+        <v>914928.9327896521</v>
       </c>
       <c r="P519" t="n">
         <v>2900</v>
@@ -23630,7 +23630,7 @@
         </is>
       </c>
       <c r="J520" t="n">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="K520" t="n">
         <v>0</v>
@@ -23639,19 +23639,19 @@
         <v>0</v>
       </c>
       <c r="M520" t="n">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="N520" t="n">
-        <v>1803.015867082</v>
+        <v>1803.0158874609</v>
       </c>
       <c r="O520" t="n">
-        <v>450753.9667705</v>
+        <v>447147.9400903033</v>
       </c>
       <c r="P520" t="n">
         <v>2500</v>
       </c>
       <c r="Q520" t="n">
-        <v>625000</v>
+        <v>620000</v>
       </c>
     </row>
     <row r="521">
@@ -23676,7 +23676,7 @@
         </is>
       </c>
       <c r="J521" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K521" t="n">
         <v>0</v>
@@ -23685,19 +23685,19 @@
         <v>0</v>
       </c>
       <c r="M521" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N521" t="n">
-        <v>3306.5946107784</v>
+        <v>3306.5945945946</v>
       </c>
       <c r="O521" t="n">
-        <v>317433.0826347264</v>
+        <v>310819.8918918924</v>
       </c>
       <c r="P521" t="n">
         <v>4900</v>
       </c>
       <c r="Q521" t="n">
-        <v>470400</v>
+        <v>460600</v>
       </c>
     </row>
     <row r="522">
@@ -23734,10 +23734,10 @@
         <v>511</v>
       </c>
       <c r="N522" t="n">
-        <v>2122.163732778</v>
+        <v>2122.1637267479</v>
       </c>
       <c r="O522" t="n">
-        <v>1084425.667449558</v>
+        <v>1084425.664368177</v>
       </c>
       <c r="P522" t="n">
         <v>2900</v>
@@ -23768,7 +23768,7 @@
         </is>
       </c>
       <c r="J523" t="n">
-        <v>213</v>
+        <v>193</v>
       </c>
       <c r="K523" t="n">
         <v>0</v>
@@ -23777,19 +23777,19 @@
         <v>0</v>
       </c>
       <c r="M523" t="n">
-        <v>213</v>
+        <v>193</v>
       </c>
       <c r="N523" t="n">
-        <v>2108.7926981818</v>
+        <v>2108.7933180778</v>
       </c>
       <c r="O523" t="n">
-        <v>449172.8447127234</v>
+        <v>406997.1103890154</v>
       </c>
       <c r="P523" t="n">
         <v>2900</v>
       </c>
       <c r="Q523" t="n">
-        <v>617700</v>
+        <v>559700</v>
       </c>
     </row>
     <row r="524">
@@ -23814,7 +23814,7 @@
         </is>
       </c>
       <c r="J524" t="n">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="K524" t="n">
         <v>0</v>
@@ -23823,19 +23823,19 @@
         <v>0</v>
       </c>
       <c r="M524" t="n">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="N524" t="n">
-        <v>2056.0828704663</v>
+        <v>2056.0827781666</v>
       </c>
       <c r="O524" t="n">
-        <v>590095.7838238281</v>
+        <v>585983.5917774809</v>
       </c>
       <c r="P524" t="n">
         <v>2900</v>
       </c>
       <c r="Q524" t="n">
-        <v>832300</v>
+        <v>826500</v>
       </c>
     </row>
     <row r="525">
@@ -23872,10 +23872,10 @@
         <v>329</v>
       </c>
       <c r="N525" t="n">
-        <v>3224.5689232303</v>
+        <v>3224.5689410589</v>
       </c>
       <c r="O525" t="n">
-        <v>1060883.175742769</v>
+        <v>1060883.181608378</v>
       </c>
       <c r="P525" t="n">
         <v>4500</v>
@@ -23918,10 +23918,10 @@
         <v>261</v>
       </c>
       <c r="N526" t="n">
-        <v>1655.9305693829</v>
+        <v>1655.9305111492</v>
       </c>
       <c r="O526" t="n">
-        <v>432197.8786089369</v>
+        <v>432197.8634099412</v>
       </c>
       <c r="P526" t="n">
         <v>2500</v>
@@ -24090,7 +24090,7 @@
         </is>
       </c>
       <c r="J530" t="n">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="K530" t="n">
         <v>0</v>
@@ -24099,19 +24099,19 @@
         <v>0</v>
       </c>
       <c r="M530" t="n">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="N530" t="n">
-        <v>1592.2811378003</v>
+        <v>1592.2815314136</v>
       </c>
       <c r="O530" t="n">
-        <v>60506.6832364114</v>
+        <v>23884.222971204</v>
       </c>
       <c r="P530" t="n">
         <v>2500</v>
       </c>
       <c r="Q530" t="n">
-        <v>95000</v>
+        <v>37500</v>
       </c>
     </row>
     <row r="531">
@@ -24134,7 +24134,7 @@
         </is>
       </c>
       <c r="J531" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K531" t="n">
         <v>0</v>
@@ -24143,19 +24143,19 @@
         <v>0</v>
       </c>
       <c r="M531" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="N531" t="n">
         <v>5347.73</v>
       </c>
       <c r="O531" t="n">
-        <v>197866.01</v>
+        <v>192518.28</v>
       </c>
       <c r="P531" t="n">
         <v>9500</v>
       </c>
       <c r="Q531" t="n">
-        <v>351500</v>
+        <v>342000</v>
       </c>
     </row>
     <row r="532">
@@ -24192,10 +24192,10 @@
         <v>12</v>
       </c>
       <c r="N532" t="n">
-        <v>2546.9829528536</v>
+        <v>2546.9828463476</v>
       </c>
       <c r="O532" t="n">
-        <v>30563.7954342432</v>
+        <v>30563.7941561712</v>
       </c>
       <c r="P532" t="n">
         <v>3900</v>
@@ -24238,10 +24238,10 @@
         <v>899</v>
       </c>
       <c r="N533" t="n">
-        <v>1259.2746531459</v>
+        <v>1259.2746638947</v>
       </c>
       <c r="O533" t="n">
-        <v>1132087.913178164</v>
+        <v>1132087.922841335</v>
       </c>
       <c r="P533" t="n">
         <v>1900</v>
@@ -24405,7 +24405,7 @@
         </is>
       </c>
       <c r="J537" t="n">
-        <v>265</v>
+        <v>697</v>
       </c>
       <c r="K537" t="n">
         <v>0</v>
@@ -24414,19 +24414,19 @@
         <v>0</v>
       </c>
       <c r="M537" t="n">
-        <v>265</v>
+        <v>697</v>
       </c>
       <c r="N537" t="n">
         <v>1801</v>
       </c>
       <c r="O537" t="n">
-        <v>477265</v>
+        <v>1255297</v>
       </c>
       <c r="P537" t="n">
         <v>2900</v>
       </c>
       <c r="Q537" t="n">
-        <v>768500</v>
+        <v>2021300</v>
       </c>
     </row>
     <row r="538">
@@ -24783,7 +24783,7 @@
         </is>
       </c>
       <c r="J545" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="K545" t="n">
         <v>0</v>
@@ -24792,19 +24792,19 @@
         <v>0</v>
       </c>
       <c r="M545" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="N545" t="n">
         <v>8945.379999999999</v>
       </c>
       <c r="O545" t="n">
-        <v>1431260.8</v>
+        <v>1413370.04</v>
       </c>
       <c r="P545" t="n">
         <v>14900</v>
       </c>
       <c r="Q545" t="n">
-        <v>2384000</v>
+        <v>2354200</v>
       </c>
     </row>
     <row r="546">
@@ -24829,7 +24829,7 @@
         </is>
       </c>
       <c r="J546" t="n">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="K546" t="n">
         <v>0</v>
@@ -24838,19 +24838,19 @@
         <v>0</v>
       </c>
       <c r="M546" t="n">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="N546" t="n">
-        <v>3026.5153672316</v>
+        <v>3026.5155882353</v>
       </c>
       <c r="O546" t="n">
-        <v>175537.8912994328</v>
+        <v>154352.2950000003</v>
       </c>
       <c r="P546" t="n">
         <v>7000</v>
       </c>
       <c r="Q546" t="n">
-        <v>406000</v>
+        <v>357000</v>
       </c>
     </row>
     <row r="547">
@@ -25114,7 +25114,7 @@
         </is>
       </c>
       <c r="J552" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="K552" t="n">
         <v>0</v>
@@ -25123,19 +25123,19 @@
         <v>0</v>
       </c>
       <c r="M552" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="N552" t="n">
         <v>1245.62</v>
       </c>
       <c r="O552" t="n">
-        <v>129544.48</v>
+        <v>127053.24</v>
       </c>
       <c r="P552" t="n">
         <v>4000</v>
       </c>
       <c r="Q552" t="n">
-        <v>416000</v>
+        <v>408000</v>
       </c>
     </row>
     <row r="553">
@@ -25532,7 +25532,7 @@
         </is>
       </c>
       <c r="J561" t="n">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="K561" t="n">
         <v>0</v>
@@ -25541,19 +25541,19 @@
         <v>0</v>
       </c>
       <c r="M561" t="n">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="N561" t="n">
-        <v>1690.8700092251</v>
+        <v>1690.8700092336</v>
       </c>
       <c r="O561" t="n">
-        <v>302665.7316512929</v>
+        <v>299283.9916343472</v>
       </c>
       <c r="P561" t="n">
         <v>3000</v>
       </c>
       <c r="Q561" t="n">
-        <v>537000</v>
+        <v>531000</v>
       </c>
     </row>
     <row r="562">
@@ -26266,7 +26266,7 @@
         </is>
       </c>
       <c r="J577" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K577" t="n">
         <v>0</v>
@@ -26275,19 +26275,19 @@
         <v>0</v>
       </c>
       <c r="M577" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="N577" t="n">
         <v>1044.54</v>
       </c>
       <c r="O577" t="n">
-        <v>15668.1</v>
+        <v>12534.48</v>
       </c>
       <c r="P577" t="n">
         <v>1200</v>
       </c>
       <c r="Q577" t="n">
-        <v>18000</v>
+        <v>14400</v>
       </c>
     </row>
     <row r="578">
@@ -26315,28 +26315,28 @@
         </is>
       </c>
       <c r="J578" t="n">
-        <v>1228</v>
+        <v>1006</v>
       </c>
       <c r="K578" t="n">
         <v>0</v>
       </c>
       <c r="L578" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M578" t="n">
-        <v>1223</v>
+        <v>1006</v>
       </c>
       <c r="N578" t="n">
-        <v>517.29097263266</v>
+        <v>517.29128286432</v>
       </c>
       <c r="O578" t="n">
-        <v>632646.8595297432</v>
+        <v>520395.0305615059</v>
       </c>
       <c r="P578" t="n">
         <v>900</v>
       </c>
       <c r="Q578" t="n">
-        <v>1100700</v>
+        <v>905400</v>
       </c>
     </row>
     <row r="579">
@@ -26558,10 +26558,10 @@
         <v>25</v>
       </c>
       <c r="N583" t="n">
-        <v>3110.8403177212</v>
+        <v>3110.8402590245</v>
       </c>
       <c r="O583" t="n">
-        <v>77771.00794303</v>
+        <v>77771.00647561251</v>
       </c>
       <c r="P583" t="n">
         <v>4500</v>
@@ -26590,7 +26590,7 @@
         </is>
       </c>
       <c r="J584" t="n">
-        <v>1220</v>
+        <v>1172</v>
       </c>
       <c r="K584" t="n">
         <v>0</v>
@@ -26599,19 +26599,19 @@
         <v>0</v>
       </c>
       <c r="M584" t="n">
-        <v>1220</v>
+        <v>1172</v>
       </c>
       <c r="N584" t="n">
-        <v>703.79509062003</v>
+        <v>703.79502188713</v>
       </c>
       <c r="O584" t="n">
-        <v>858630.0105564366</v>
+        <v>824847.7656517164</v>
       </c>
       <c r="P584" t="n">
         <v>900</v>
       </c>
       <c r="Q584" t="n">
-        <v>1098000</v>
+        <v>1054800</v>
       </c>
     </row>
     <row r="585">
@@ -26832,7 +26832,7 @@
         </is>
       </c>
       <c r="J589" t="n">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="K589" t="n">
         <v>0</v>
@@ -26841,19 +26841,19 @@
         <v>0</v>
       </c>
       <c r="M589" t="n">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="N589" t="n">
-        <v>1595.5116012774</v>
+        <v>1595.5115507777</v>
       </c>
       <c r="O589" t="n">
-        <v>304742.7158439834</v>
+        <v>295169.6368938745</v>
       </c>
       <c r="P589" t="n">
         <v>2500</v>
       </c>
       <c r="Q589" t="n">
-        <v>477500</v>
+        <v>462500</v>
       </c>
     </row>
     <row r="590">
@@ -27653,7 +27653,7 @@
         </is>
       </c>
       <c r="J606" t="n">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="K606" t="n">
         <v>0</v>
@@ -27662,19 +27662,19 @@
         <v>0</v>
       </c>
       <c r="M606" t="n">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="N606" t="n">
         <v>1669.6</v>
       </c>
       <c r="O606" t="n">
-        <v>924958.3999999999</v>
+        <v>923288.7999999999</v>
       </c>
       <c r="P606" t="n">
         <v>2900</v>
       </c>
       <c r="Q606" t="n">
-        <v>1606600</v>
+        <v>1603700</v>
       </c>
     </row>
     <row r="607">
@@ -28912,10 +28912,10 @@
         <v>61</v>
       </c>
       <c r="N632" t="n">
-        <v>875.69016949153</v>
+        <v>875.69017316017</v>
       </c>
       <c r="O632" t="n">
-        <v>53417.10033898333</v>
+        <v>53417.10056277037</v>
       </c>
       <c r="P632" t="n">
         <v>4500</v>
@@ -28949,7 +28949,7 @@
         </is>
       </c>
       <c r="J633" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K633" t="n">
         <v>0</v>
@@ -28958,19 +28958,19 @@
         <v>0</v>
       </c>
       <c r="M633" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="N633" t="n">
         <v>30228.24</v>
       </c>
       <c r="O633" t="n">
-        <v>423195.36</v>
+        <v>332510.64</v>
       </c>
       <c r="P633" t="n">
         <v>40500</v>
       </c>
       <c r="Q633" t="n">
-        <v>567000</v>
+        <v>445500</v>
       </c>
     </row>
     <row r="634">
@@ -29188,7 +29188,7 @@
         </is>
       </c>
       <c r="J638" t="n">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="K638" t="n">
         <v>0</v>
@@ -29197,19 +29197,19 @@
         <v>0</v>
       </c>
       <c r="M638" t="n">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="N638" t="n">
         <v>3000.33</v>
       </c>
       <c r="O638" t="n">
-        <v>762083.8199999999</v>
+        <v>756083.16</v>
       </c>
       <c r="P638" t="n">
         <v>2900</v>
       </c>
       <c r="Q638" t="n">
-        <v>736600</v>
+        <v>730800</v>
       </c>
     </row>
     <row r="639">
@@ -29947,7 +29947,7 @@
         </is>
       </c>
       <c r="J654" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K654" t="n">
         <v>0</v>
@@ -29956,19 +29956,19 @@
         <v>0</v>
       </c>
       <c r="M654" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N654" t="n">
-        <v>34880.156666667</v>
+        <v>34880.158</v>
       </c>
       <c r="O654" t="n">
-        <v>139520.626666668</v>
+        <v>104640.474</v>
       </c>
       <c r="P654" t="n">
         <v>65900</v>
       </c>
       <c r="Q654" t="n">
-        <v>263600</v>
+        <v>197700</v>
       </c>
     </row>
     <row r="655">
@@ -31285,7 +31285,7 @@
         </is>
       </c>
       <c r="J682" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K682" t="n">
         <v>0</v>
@@ -31294,19 +31294,19 @@
         <v>0</v>
       </c>
       <c r="M682" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="N682" t="n">
-        <v>44113.603841808</v>
+        <v>44113.603953488</v>
       </c>
       <c r="O682" t="n">
-        <v>573476.849943504</v>
+        <v>352908.831627904</v>
       </c>
       <c r="P682" t="n">
         <v>71900</v>
       </c>
       <c r="Q682" t="n">
-        <v>934700</v>
+        <v>575200</v>
       </c>
     </row>
     <row r="683">
@@ -31334,7 +31334,7 @@
         </is>
       </c>
       <c r="J683" t="n">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="K683" t="n">
         <v>0</v>
@@ -31343,19 +31343,19 @@
         <v>0</v>
       </c>
       <c r="M683" t="n">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="N683" t="n">
         <v>1080.18</v>
       </c>
       <c r="O683" t="n">
-        <v>360780.12</v>
+        <v>358619.76</v>
       </c>
       <c r="P683" t="n">
         <v>4900</v>
       </c>
       <c r="Q683" t="n">
-        <v>1636600</v>
+        <v>1626800</v>
       </c>
     </row>
     <row r="684">
@@ -31576,7 +31576,7 @@
         </is>
       </c>
       <c r="J688" t="n">
-        <v>72</v>
+        <v>150</v>
       </c>
       <c r="K688" t="n">
         <v>0</v>
@@ -31585,19 +31585,19 @@
         <v>0</v>
       </c>
       <c r="M688" t="n">
-        <v>72</v>
+        <v>150</v>
       </c>
       <c r="N688" t="n">
         <v>3155</v>
       </c>
       <c r="O688" t="n">
-        <v>227160</v>
+        <v>473250</v>
       </c>
       <c r="P688" t="n">
         <v>5900</v>
       </c>
       <c r="Q688" t="n">
-        <v>424800</v>
+        <v>885000</v>
       </c>
     </row>
     <row r="689">
@@ -32264,7 +32264,7 @@
         </is>
       </c>
       <c r="J703" t="n">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="K703" t="n">
         <v>0</v>
@@ -32273,19 +32273,19 @@
         <v>0</v>
       </c>
       <c r="M703" t="n">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="N703" t="n">
         <v>5077</v>
       </c>
       <c r="O703" t="n">
-        <v>512777</v>
+        <v>467084</v>
       </c>
       <c r="P703" t="n">
         <v>8500</v>
       </c>
       <c r="Q703" t="n">
-        <v>858500</v>
+        <v>782000</v>
       </c>
     </row>
     <row r="704">
@@ -32310,7 +32310,7 @@
         </is>
       </c>
       <c r="J704" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="K704" t="n">
         <v>0</v>
@@ -32319,19 +32319,19 @@
         <v>0</v>
       </c>
       <c r="M704" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N704" t="n">
         <v>1600</v>
       </c>
       <c r="O704" t="n">
-        <v>100800</v>
+        <v>97600</v>
       </c>
       <c r="P704" t="n">
         <v>3500</v>
       </c>
       <c r="Q704" t="n">
-        <v>220500</v>
+        <v>213500</v>
       </c>
     </row>
     <row r="705">
@@ -32586,7 +32586,7 @@
         </is>
       </c>
       <c r="J710" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K710" t="n">
         <v>0</v>
@@ -32595,19 +32595,19 @@
         <v>0</v>
       </c>
       <c r="M710" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N710" t="n">
         <v>15300</v>
       </c>
       <c r="O710" t="n">
-        <v>45900</v>
+        <v>30600</v>
       </c>
       <c r="P710" t="n">
         <v>19500</v>
       </c>
       <c r="Q710" t="n">
-        <v>58500</v>
+        <v>39000</v>
       </c>
     </row>
     <row r="711">
@@ -32632,7 +32632,7 @@
         </is>
       </c>
       <c r="J711" t="n">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="K711" t="n">
         <v>0</v>
@@ -32641,19 +32641,19 @@
         <v>0</v>
       </c>
       <c r="M711" t="n">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="N711" t="n">
-        <v>5218.9109137056</v>
+        <v>5218.9109207161</v>
       </c>
       <c r="O711" t="n">
-        <v>2045813.078172595</v>
+        <v>2030156.348158563</v>
       </c>
       <c r="P711" t="n">
         <v>6500</v>
       </c>
       <c r="Q711" t="n">
-        <v>2548000</v>
+        <v>2528500</v>
       </c>
     </row>
     <row r="712">
@@ -32678,7 +32678,7 @@
         </is>
       </c>
       <c r="J712" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K712" t="n">
         <v>0</v>
@@ -32687,19 +32687,19 @@
         <v>0</v>
       </c>
       <c r="M712" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="N712" t="n">
         <v>5850</v>
       </c>
       <c r="O712" t="n">
-        <v>122850</v>
+        <v>105300</v>
       </c>
       <c r="P712" t="n">
         <v>7900</v>
       </c>
       <c r="Q712" t="n">
-        <v>165900</v>
+        <v>142200</v>
       </c>
     </row>
     <row r="713">
@@ -32908,7 +32908,7 @@
         </is>
       </c>
       <c r="J717" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K717" t="n">
         <v>0</v>
@@ -32917,19 +32917,19 @@
         <v>0</v>
       </c>
       <c r="M717" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N717" t="n">
         <v>18000</v>
       </c>
       <c r="O717" t="n">
-        <v>72000</v>
+        <v>54000</v>
       </c>
       <c r="P717" t="n">
         <v>23900</v>
       </c>
       <c r="Q717" t="n">
-        <v>95600</v>
+        <v>71700</v>
       </c>
     </row>
     <row r="718">
@@ -33460,7 +33460,7 @@
         </is>
       </c>
       <c r="J729" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K729" t="n">
         <v>0</v>
@@ -33469,19 +33469,19 @@
         <v>0</v>
       </c>
       <c r="M729" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="N729" t="n">
         <v>9450</v>
       </c>
       <c r="O729" t="n">
-        <v>113400</v>
+        <v>56700</v>
       </c>
       <c r="P729" t="n">
         <v>11900</v>
       </c>
       <c r="Q729" t="n">
-        <v>142800</v>
+        <v>71400</v>
       </c>
     </row>
     <row r="730">
@@ -33690,7 +33690,7 @@
         </is>
       </c>
       <c r="J734" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K734" t="n">
         <v>0</v>
@@ -33699,19 +33699,19 @@
         <v>0</v>
       </c>
       <c r="M734" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N734" t="n">
         <v>28800</v>
       </c>
       <c r="O734" t="n">
-        <v>489600</v>
+        <v>432000</v>
       </c>
       <c r="P734" t="n">
         <v>36000</v>
       </c>
       <c r="Q734" t="n">
-        <v>612000</v>
+        <v>540000</v>
       </c>
     </row>
     <row r="735">
@@ -34012,7 +34012,7 @@
         </is>
       </c>
       <c r="J741" t="n">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="K741" t="n">
         <v>0</v>
@@ -34021,19 +34021,19 @@
         <v>0</v>
       </c>
       <c r="M741" t="n">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="N741" t="n">
         <v>7480</v>
       </c>
       <c r="O741" t="n">
-        <v>1376320</v>
+        <v>1309000</v>
       </c>
       <c r="P741" t="n">
         <v>9500</v>
       </c>
       <c r="Q741" t="n">
-        <v>1748000</v>
+        <v>1662500</v>
       </c>
     </row>
     <row r="742">
@@ -34058,7 +34058,7 @@
         </is>
       </c>
       <c r="J742" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="K742" t="n">
         <v>0</v>
@@ -34067,19 +34067,19 @@
         <v>0</v>
       </c>
       <c r="M742" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="N742" t="n">
         <v>15224</v>
       </c>
       <c r="O742" t="n">
-        <v>1461504</v>
+        <v>1415832</v>
       </c>
       <c r="P742" t="n">
         <v>19000</v>
       </c>
       <c r="Q742" t="n">
-        <v>1824000</v>
+        <v>1767000</v>
       </c>
     </row>
     <row r="743">
@@ -34104,7 +34104,7 @@
         </is>
       </c>
       <c r="J743" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="K743" t="n">
         <v>0</v>
@@ -34113,19 +34113,19 @@
         <v>0</v>
       </c>
       <c r="M743" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="N743" t="n">
         <v>15224</v>
       </c>
       <c r="O743" t="n">
-        <v>1446280</v>
+        <v>1400608</v>
       </c>
       <c r="P743" t="n">
         <v>19000</v>
       </c>
       <c r="Q743" t="n">
-        <v>1805000</v>
+        <v>1748000</v>
       </c>
     </row>
     <row r="744">
@@ -34196,7 +34196,7 @@
         </is>
       </c>
       <c r="J745" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="K745" t="n">
         <v>0</v>
@@ -34205,19 +34205,19 @@
         <v>0</v>
       </c>
       <c r="M745" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="N745" t="n">
         <v>6336</v>
       </c>
       <c r="O745" t="n">
-        <v>177408</v>
+        <v>152064</v>
       </c>
       <c r="P745" t="n">
         <v>7500</v>
       </c>
       <c r="Q745" t="n">
-        <v>210000</v>
+        <v>180000</v>
       </c>
     </row>
     <row r="746">
@@ -34242,7 +34242,7 @@
         </is>
       </c>
       <c r="J746" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K746" t="n">
         <v>0</v>
@@ -34251,19 +34251,19 @@
         <v>0</v>
       </c>
       <c r="M746" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N746" t="n">
         <v>5280</v>
       </c>
       <c r="O746" t="n">
-        <v>591360</v>
+        <v>586080</v>
       </c>
       <c r="P746" t="n">
         <v>6900</v>
       </c>
       <c r="Q746" t="n">
-        <v>772800</v>
+        <v>765900</v>
       </c>
     </row>
     <row r="747">
@@ -34288,7 +34288,7 @@
         </is>
       </c>
       <c r="J747" t="n">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="K747" t="n">
         <v>0</v>
@@ -34297,19 +34297,19 @@
         <v>0</v>
       </c>
       <c r="M747" t="n">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="N747" t="n">
         <v>2376</v>
       </c>
       <c r="O747" t="n">
-        <v>1366200</v>
+        <v>1359072</v>
       </c>
       <c r="P747" t="n">
         <v>3000</v>
       </c>
       <c r="Q747" t="n">
-        <v>1725000</v>
+        <v>1716000</v>
       </c>
     </row>
     <row r="748">
@@ -34564,7 +34564,7 @@
         </is>
       </c>
       <c r="J753" t="n">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="K753" t="n">
         <v>0</v>
@@ -34573,19 +34573,19 @@
         <v>0</v>
       </c>
       <c r="M753" t="n">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="N753" t="n">
         <v>6160</v>
       </c>
       <c r="O753" t="n">
-        <v>1287440</v>
+        <v>1225840</v>
       </c>
       <c r="P753" t="n">
         <v>7900</v>
       </c>
       <c r="Q753" t="n">
-        <v>1651100</v>
+        <v>1572100</v>
       </c>
     </row>
     <row r="754">
@@ -34610,7 +34610,7 @@
         </is>
       </c>
       <c r="J754" t="n">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="K754" t="n">
         <v>0</v>
@@ -34619,19 +34619,19 @@
         <v>0</v>
       </c>
       <c r="M754" t="n">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="N754" t="n">
         <v>6160</v>
       </c>
       <c r="O754" t="n">
-        <v>1318240</v>
+        <v>1293600</v>
       </c>
       <c r="P754" t="n">
         <v>7900</v>
       </c>
       <c r="Q754" t="n">
-        <v>1690600</v>
+        <v>1659000</v>
       </c>
     </row>
     <row r="755">
@@ -34656,7 +34656,7 @@
         </is>
       </c>
       <c r="J755" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="K755" t="n">
         <v>0</v>
@@ -34665,19 +34665,19 @@
         <v>0</v>
       </c>
       <c r="M755" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="N755" t="n">
         <v>6160</v>
       </c>
       <c r="O755" t="n">
-        <v>1244320</v>
+        <v>1232000</v>
       </c>
       <c r="P755" t="n">
         <v>7900</v>
       </c>
       <c r="Q755" t="n">
-        <v>1595800</v>
+        <v>1580000</v>
       </c>
     </row>
     <row r="756">
@@ -34702,7 +34702,7 @@
         </is>
       </c>
       <c r="J756" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="K756" t="n">
         <v>0</v>
@@ -34711,19 +34711,19 @@
         <v>0</v>
       </c>
       <c r="M756" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="N756" t="n">
         <v>6160</v>
       </c>
       <c r="O756" t="n">
-        <v>344960</v>
+        <v>301840</v>
       </c>
       <c r="P756" t="n">
         <v>7900</v>
       </c>
       <c r="Q756" t="n">
-        <v>442400</v>
+        <v>387100</v>
       </c>
     </row>
     <row r="757">
@@ -34978,7 +34978,7 @@
         </is>
       </c>
       <c r="J762" t="n">
-        <v>648</v>
+        <v>626</v>
       </c>
       <c r="K762" t="n">
         <v>0</v>
@@ -34987,19 +34987,19 @@
         <v>0</v>
       </c>
       <c r="M762" t="n">
-        <v>648</v>
+        <v>626</v>
       </c>
       <c r="N762" t="n">
         <v>9240</v>
       </c>
       <c r="O762" t="n">
-        <v>5987520</v>
+        <v>5784240</v>
       </c>
       <c r="P762" t="n">
         <v>11500</v>
       </c>
       <c r="Q762" t="n">
-        <v>7452000</v>
+        <v>7199000</v>
       </c>
     </row>
     <row r="763">
@@ -35024,7 +35024,7 @@
         </is>
       </c>
       <c r="J763" t="n">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="K763" t="n">
         <v>0</v>
@@ -35033,19 +35033,19 @@
         <v>0</v>
       </c>
       <c r="M763" t="n">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="N763" t="n">
         <v>2288</v>
       </c>
       <c r="O763" t="n">
-        <v>404976</v>
+        <v>379808</v>
       </c>
       <c r="P763" t="n">
         <v>2900</v>
       </c>
       <c r="Q763" t="n">
-        <v>513300</v>
+        <v>481400</v>
       </c>
     </row>
     <row r="764">
@@ -35070,7 +35070,7 @@
         </is>
       </c>
       <c r="J764" t="n">
-        <v>253</v>
+        <v>153</v>
       </c>
       <c r="K764" t="n">
         <v>0</v>
@@ -35079,19 +35079,19 @@
         <v>0</v>
       </c>
       <c r="M764" t="n">
-        <v>253</v>
+        <v>153</v>
       </c>
       <c r="N764" t="n">
         <v>7216</v>
       </c>
       <c r="O764" t="n">
-        <v>1825648</v>
+        <v>1104048</v>
       </c>
       <c r="P764" t="n">
         <v>9000</v>
       </c>
       <c r="Q764" t="n">
-        <v>2277000</v>
+        <v>1377000</v>
       </c>
     </row>
     <row r="765">
@@ -35116,7 +35116,7 @@
         </is>
       </c>
       <c r="J765" t="n">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="K765" t="n">
         <v>0</v>
@@ -35125,19 +35125,19 @@
         <v>0</v>
       </c>
       <c r="M765" t="n">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="N765" t="n">
         <v>4576</v>
       </c>
       <c r="O765" t="n">
-        <v>407264</v>
+        <v>338624</v>
       </c>
       <c r="P765" t="n">
         <v>5900</v>
       </c>
       <c r="Q765" t="n">
-        <v>525100</v>
+        <v>436600</v>
       </c>
     </row>
     <row r="766">
@@ -37298,7 +37298,7 @@
         </is>
       </c>
       <c r="J812" t="n">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="K812" t="n">
         <v>0</v>
@@ -37307,19 +37307,19 @@
         <v>0</v>
       </c>
       <c r="M812" t="n">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="N812" t="n">
         <v>4550</v>
       </c>
       <c r="O812" t="n">
-        <v>1223950</v>
+        <v>1183000</v>
       </c>
       <c r="P812" t="n">
         <v>5500</v>
       </c>
       <c r="Q812" t="n">
-        <v>1479500</v>
+        <v>1430000</v>
       </c>
     </row>
     <row r="813">

--- a/bodegas/LJ-05.xlsx
+++ b/bodegas/LJ-05.xlsx
@@ -7641,10 +7641,10 @@
         <v>115</v>
       </c>
       <c r="N168" t="n">
-        <v>5002</v>
+        <v>5013.3940774487</v>
       </c>
       <c r="O168" t="n">
-        <v>575230</v>
+        <v>576540.3189066005</v>
       </c>
       <c r="P168" t="n">
         <v>8400</v>
@@ -8004,10 +8004,10 @@
         <v>64</v>
       </c>
       <c r="N176" t="n">
-        <v>4890.9300493218</v>
+        <v>4890.9300493827</v>
       </c>
       <c r="O176" t="n">
-        <v>313019.5231565952</v>
+        <v>313019.5231604928</v>
       </c>
       <c r="P176" t="n">
         <v>8200</v>
@@ -9001,10 +9001,10 @@
         <v>33</v>
       </c>
       <c r="N198" t="n">
-        <v>2090.85</v>
+        <v>2092.643951094</v>
       </c>
       <c r="O198" t="n">
-        <v>68998.05</v>
+        <v>69057.25038610199</v>
       </c>
       <c r="P198" t="n">
         <v>2900</v>
@@ -9682,10 +9682,10 @@
         <v>77</v>
       </c>
       <c r="N213" t="n">
-        <v>4372.2107917679</v>
+        <v>4372.2107918811</v>
       </c>
       <c r="O213" t="n">
-        <v>336660.2309661284</v>
+        <v>336660.2309748447</v>
       </c>
       <c r="P213" t="n">
         <v>7500</v>
@@ -9728,10 +9728,10 @@
         <v>240</v>
       </c>
       <c r="N214" t="n">
-        <v>1592.5662209302</v>
+        <v>1617.3578206079</v>
       </c>
       <c r="O214" t="n">
-        <v>382215.893023248</v>
+        <v>388165.876945896</v>
       </c>
       <c r="P214" t="n">
         <v>3900</v>
@@ -11043,10 +11043,10 @@
         <v>313</v>
       </c>
       <c r="N243" t="n">
-        <v>2403.5134379057</v>
+        <v>2403.513461205</v>
       </c>
       <c r="O243" t="n">
-        <v>752299.7060644841</v>
+        <v>752299.713357165</v>
       </c>
       <c r="P243" t="n">
         <v>3500</v>
@@ -12142,10 +12142,10 @@
         <v>184</v>
       </c>
       <c r="N268" t="n">
-        <v>2517.22</v>
+        <v>2541.6788178138</v>
       </c>
       <c r="O268" t="n">
-        <v>463168.48</v>
+        <v>467668.9024777392</v>
       </c>
       <c r="P268" t="n">
         <v>4200</v>
@@ -15670,10 +15670,10 @@
         <v>88</v>
       </c>
       <c r="N347" t="n">
-        <v>5218.1705692109</v>
+        <v>5218.1705706874</v>
       </c>
       <c r="O347" t="n">
-        <v>459199.0100905592</v>
+        <v>459199.0102204912</v>
       </c>
       <c r="P347" t="n">
         <v>8500</v>
@@ -15716,10 +15716,10 @@
         <v>105</v>
       </c>
       <c r="N348" t="n">
-        <v>1595.0093202147</v>
+        <v>1595.0093078324</v>
       </c>
       <c r="O348" t="n">
-        <v>167475.9786225435</v>
+        <v>167475.977322402</v>
       </c>
       <c r="P348" t="n">
         <v>2600</v>
@@ -23412,10 +23412,10 @@
         <v>151</v>
       </c>
       <c r="N515" t="n">
-        <v>1516.0387891009</v>
+        <v>1517.8304441599</v>
       </c>
       <c r="O515" t="n">
-        <v>228921.8571542359</v>
+        <v>229192.3970681449</v>
       </c>
       <c r="P515" t="n">
         <v>2300</v>
@@ -23642,10 +23642,10 @@
         <v>248</v>
       </c>
       <c r="N520" t="n">
-        <v>1803.0158874609</v>
+        <v>1803.0158936022</v>
       </c>
       <c r="O520" t="n">
-        <v>447147.9400903033</v>
+        <v>447147.9416133456</v>
       </c>
       <c r="P520" t="n">
         <v>2500</v>
@@ -24102,10 +24102,10 @@
         <v>15</v>
       </c>
       <c r="N530" t="n">
-        <v>1592.2815314136</v>
+        <v>1592.2816534392</v>
       </c>
       <c r="O530" t="n">
-        <v>23884.222971204</v>
+        <v>23884.224801588</v>
       </c>
       <c r="P530" t="n">
         <v>2500</v>
@@ -26327,10 +26327,10 @@
         <v>1006</v>
       </c>
       <c r="N578" t="n">
-        <v>517.29128286432</v>
+        <v>518.11303680169</v>
       </c>
       <c r="O578" t="n">
-        <v>520395.0305615059</v>
+        <v>521221.7150225001</v>
       </c>
       <c r="P578" t="n">
         <v>900</v>
@@ -26602,10 +26602,10 @@
         <v>1172</v>
       </c>
       <c r="N584" t="n">
-        <v>703.79502188713</v>
+        <v>703.79501848956</v>
       </c>
       <c r="O584" t="n">
-        <v>824847.7656517164</v>
+        <v>824847.7616697643</v>
       </c>
       <c r="P584" t="n">
         <v>900</v>
@@ -34898,10 +34898,10 @@
         <v>151</v>
       </c>
       <c r="N760" t="n">
-        <v>3520</v>
+        <v>3571.512195122</v>
       </c>
       <c r="O760" t="n">
-        <v>531520</v>
+        <v>539298.3414634219</v>
       </c>
       <c r="P760" t="n">
         <v>4500</v>

--- a/bodegas/LJ-05.xlsx
+++ b/bodegas/LJ-05.xlsx
@@ -7180,10 +7180,10 @@
         <v>230</v>
       </c>
       <c r="N158" t="n">
-        <v>2582.2555145238</v>
+        <v>2582.2555084555</v>
       </c>
       <c r="O158" t="n">
-        <v>593918.768340474</v>
+        <v>593918.766944765</v>
       </c>
       <c r="P158" t="n">
         <v>4500</v>
@@ -10996,10 +10996,10 @@
         <v>307</v>
       </c>
       <c r="N242" t="n">
-        <v>2403.5136926808</v>
+        <v>2403.513738111</v>
       </c>
       <c r="O242" t="n">
-        <v>737878.7036530057</v>
+        <v>737878.7176000769</v>
       </c>
       <c r="P242" t="n">
         <v>3500</v>
@@ -23963,10 +23963,10 @@
         <v>15</v>
       </c>
       <c r="N527" t="n">
-        <v>1592.2817466667</v>
+        <v>1592.281793842</v>
       </c>
       <c r="O527" t="n">
-        <v>23884.2262000005</v>
+        <v>23884.22690763</v>
       </c>
       <c r="P527" t="n">
         <v>2500</v>
@@ -26463,10 +26463,10 @@
         <v>1160</v>
       </c>
       <c r="N581" t="n">
-        <v>703.79500857932</v>
+        <v>703.79500789654</v>
       </c>
       <c r="O581" t="n">
-        <v>816402.2099520112</v>
+        <v>816402.2091599865</v>
       </c>
       <c r="P581" t="n">
         <v>900</v>

--- a/bodegas/LJ-05.xlsx
+++ b/bodegas/LJ-05.xlsx
@@ -865,10 +865,10 @@
         <v>10</v>
       </c>
       <c r="N11" t="n">
-        <v>27035.809018568</v>
+        <v>27000</v>
       </c>
       <c r="O11" t="n">
-        <v>270358.09018568</v>
+        <v>270000</v>
       </c>
       <c r="P11" t="n">
         <v>20000</v>
@@ -2551,10 +2551,10 @@
         <v>5</v>
       </c>
       <c r="N52" t="n">
-        <v>30074.074074074</v>
+        <v>29000</v>
       </c>
       <c r="O52" t="n">
-        <v>150370.37037037</v>
+        <v>145000</v>
       </c>
       <c r="P52" t="n">
         <v>34800</v>
@@ -9090,10 +9090,10 @@
         <v>4</v>
       </c>
       <c r="N200" t="n">
-        <v>2667.0463248919</v>
+        <v>2665.4</v>
       </c>
       <c r="O200" t="n">
-        <v>10668.1852995676</v>
+        <v>10661.6</v>
       </c>
       <c r="P200" t="n">
         <v>20900</v>
@@ -9635,10 +9635,10 @@
         <v>77</v>
       </c>
       <c r="N212" t="n">
-        <v>4372.5234503719</v>
+        <v>4372.2107923341</v>
       </c>
       <c r="O212" t="n">
-        <v>336684.3056786363</v>
+        <v>336660.2310097257</v>
       </c>
       <c r="P212" t="n">
         <v>7500</v>
@@ -10130,10 +10130,10 @@
         <v>64</v>
       </c>
       <c r="N223" t="n">
-        <v>17473.953844316</v>
+        <v>17472.91</v>
       </c>
       <c r="O223" t="n">
-        <v>1118333.046036224</v>
+        <v>1118266.24</v>
       </c>
       <c r="P223" t="n">
         <v>2900</v>
@@ -10218,10 +10218,10 @@
         <v>89</v>
       </c>
       <c r="N225" t="n">
-        <v>1530.7162764218</v>
+        <v>1530.63</v>
       </c>
       <c r="O225" t="n">
-        <v>136233.7486015402</v>
+        <v>136226.07</v>
       </c>
       <c r="P225" t="n">
         <v>2900</v>
@@ -12013,10 +12013,10 @@
         <v>38</v>
       </c>
       <c r="N265" t="n">
-        <v>2569.7269830028</v>
+        <v>2567</v>
       </c>
       <c r="O265" t="n">
-        <v>97649.62535410639</v>
+        <v>97546</v>
       </c>
       <c r="P265" t="n">
         <v>4500</v>
@@ -14440,10 +14440,10 @@
         <v>151</v>
       </c>
       <c r="N320" t="n">
-        <v>7982.1180305344</v>
+        <v>7969.9501679389</v>
       </c>
       <c r="O320" t="n">
-        <v>1205299.822610694</v>
+        <v>1203462.475358774</v>
       </c>
       <c r="P320" t="n">
         <v>12900</v>
@@ -20333,10 +20333,10 @@
         <v>10</v>
       </c>
       <c r="N448" t="n">
-        <v>9952.091954023001</v>
+        <v>9839</v>
       </c>
       <c r="O448" t="n">
-        <v>99520.91954023001</v>
+        <v>98390</v>
       </c>
       <c r="P448" t="n">
         <v>16900</v>
@@ -21662,10 +21662,10 @@
         <v>33</v>
       </c>
       <c r="N477" t="n">
-        <v>59958.524453694</v>
+        <v>59834</v>
       </c>
       <c r="O477" t="n">
-        <v>1978631.306971902</v>
+        <v>1974522</v>
       </c>
       <c r="P477" t="n">
         <v>7900</v>
@@ -21800,10 +21800,10 @@
         <v>25</v>
       </c>
       <c r="N480" t="n">
-        <v>10270.481108312</v>
+        <v>10219</v>
       </c>
       <c r="O480" t="n">
-        <v>256762.0277078</v>
+        <v>255475</v>
       </c>
       <c r="P480" t="n">
         <v>16900</v>
@@ -22769,10 +22769,10 @@
         <v>227</v>
       </c>
       <c r="N501" t="n">
-        <v>3821.6520477816</v>
+        <v>3821</v>
       </c>
       <c r="O501" t="n">
-        <v>867515.0148464232</v>
+        <v>867367</v>
       </c>
       <c r="P501" t="n">
         <v>5900</v>
@@ -22815,10 +22815,10 @@
         <v>21</v>
       </c>
       <c r="N502" t="n">
-        <v>15512.291666667</v>
+        <v>15472</v>
       </c>
       <c r="O502" t="n">
-        <v>325758.125000007</v>
+        <v>324912</v>
       </c>
       <c r="P502" t="n">
         <v>25900</v>
@@ -23045,10 +23045,10 @@
         <v>147</v>
       </c>
       <c r="N507" t="n">
-        <v>5486.9301397206</v>
+        <v>5476</v>
       </c>
       <c r="O507" t="n">
-        <v>806578.7305389282</v>
+        <v>804972</v>
       </c>
       <c r="P507" t="n">
         <v>8900</v>
@@ -23920,10 +23920,10 @@
         <v>36</v>
       </c>
       <c r="N526" t="n">
-        <v>5372.836713615</v>
+        <v>5347.73</v>
       </c>
       <c r="O526" t="n">
-        <v>193422.12169014</v>
+        <v>192518.28</v>
       </c>
       <c r="P526" t="n">
         <v>9500</v>
@@ -30306,10 +30306,10 @@
         <v>22</v>
       </c>
       <c r="N661" t="n">
-        <v>5235.0773519164</v>
+        <v>5216.9</v>
       </c>
       <c r="O661" t="n">
-        <v>115171.7017421608</v>
+        <v>114771.8</v>
       </c>
       <c r="P661" t="n">
         <v>20500</v>
@@ -30786,10 +30786,10 @@
         <v>320</v>
       </c>
       <c r="N671" t="n">
-        <v>7049.9805782093</v>
+        <v>7046.9398274002</v>
       </c>
       <c r="O671" t="n">
-        <v>2255993.785026976</v>
+        <v>2255020.744768064</v>
       </c>
       <c r="P671" t="n">
         <v>9900</v>

--- a/bodegas/LJ-05.xlsx
+++ b/bodegas/LJ-05.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-06</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-07</t>
         </is>
       </c>
     </row>

--- a/bodegas/LJ-05.xlsx
+++ b/bodegas/LJ-05.xlsx
@@ -1585,10 +1585,10 @@
         <v>18</v>
       </c>
       <c r="N29" t="n">
-        <v>12357.960422535</v>
+        <v>12357.960425532</v>
       </c>
       <c r="O29" t="n">
-        <v>222443.28760563</v>
+        <v>222443.287659576</v>
       </c>
       <c r="P29" t="n">
         <v>15900</v>
@@ -1747,10 +1747,10 @@
         <v>28</v>
       </c>
       <c r="N33" t="n">
-        <v>11491.097222222</v>
+        <v>11491.09755814</v>
       </c>
       <c r="O33" t="n">
-        <v>321750.722222216</v>
+        <v>321750.73162792</v>
       </c>
       <c r="P33" t="n">
         <v>23000</v>
@@ -3141,10 +3141,10 @@
         <v>41</v>
       </c>
       <c r="N65" t="n">
-        <v>15711.96562212</v>
+        <v>15711.965560748</v>
       </c>
       <c r="O65" t="n">
-        <v>644190.59050692</v>
+        <v>644190.587990668</v>
       </c>
       <c r="P65" t="n">
         <v>28500</v>
@@ -3188,10 +3188,10 @@
         <v>24</v>
       </c>
       <c r="N66" t="n">
-        <v>9392.0750746269</v>
+        <v>9392.075312499999</v>
       </c>
       <c r="O66" t="n">
-        <v>225409.8017910456</v>
+        <v>225409.8075</v>
       </c>
       <c r="P66" t="n">
         <v>18500</v>
@@ -3816,10 +3816,10 @@
         <v>1</v>
       </c>
       <c r="N81" t="n">
-        <v>56906.803962264</v>
+        <v>56906.805744681</v>
       </c>
       <c r="O81" t="n">
-        <v>56906.803962264</v>
+        <v>56906.805744681</v>
       </c>
       <c r="P81" t="n">
         <v>95900</v>
@@ -3863,10 +3863,10 @@
         <v>4</v>
       </c>
       <c r="N82" t="n">
-        <v>62349.656875</v>
+        <v>62349.656129032</v>
       </c>
       <c r="O82" t="n">
-        <v>249398.6275</v>
+        <v>249398.624516128</v>
       </c>
       <c r="P82" t="n">
         <v>109900</v>
@@ -3910,10 +3910,10 @@
         <v>3</v>
       </c>
       <c r="N83" t="n">
-        <v>141416.88459016</v>
+        <v>141416.88460526</v>
       </c>
       <c r="O83" t="n">
-        <v>424250.6537704801</v>
+        <v>424250.6538157801</v>
       </c>
       <c r="P83" t="n">
         <v>251900</v>
@@ -3952,10 +3952,10 @@
         <v>4</v>
       </c>
       <c r="N84" t="n">
-        <v>200072.20183486</v>
+        <v>200072.20194444</v>
       </c>
       <c r="O84" t="n">
-        <v>800288.80733944</v>
+        <v>800288.80777776</v>
       </c>
       <c r="P84" t="n">
         <v>312000</v>
@@ -4233,10 +4233,10 @@
         <v>9</v>
       </c>
       <c r="N91" t="n">
-        <v>61666.874148352</v>
+        <v>61666.87415978</v>
       </c>
       <c r="O91" t="n">
-        <v>555001.8673351679</v>
+        <v>555001.8674380201</v>
       </c>
       <c r="P91" t="n">
         <v>98900</v>
@@ -6331,22 +6331,22 @@
         <v>0</v>
       </c>
       <c r="L139" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M139" t="n">
-        <v>1523</v>
+        <v>1521</v>
       </c>
       <c r="N139" t="n">
         <v>1726.32</v>
       </c>
       <c r="O139" t="n">
-        <v>2629185.36</v>
+        <v>2625732.72</v>
       </c>
       <c r="P139" t="n">
         <v>1500</v>
       </c>
       <c r="Q139" t="n">
-        <v>2284500</v>
+        <v>2281500</v>
       </c>
     </row>
     <row r="140">
@@ -7174,22 +7174,22 @@
         <v>0</v>
       </c>
       <c r="L158" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M158" t="n">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="N158" t="n">
-        <v>2582.2554768392</v>
+        <v>2582.2554727273</v>
       </c>
       <c r="O158" t="n">
-        <v>578425.2268119808</v>
+        <v>568096.204000006</v>
       </c>
       <c r="P158" t="n">
         <v>4500</v>
       </c>
       <c r="Q158" t="n">
-        <v>1008000</v>
+        <v>990000</v>
       </c>
     </row>
     <row r="159">
@@ -8633,10 +8633,10 @@
         <v>44</v>
       </c>
       <c r="N190" t="n">
-        <v>3594.253608522</v>
+        <v>3594.2536</v>
       </c>
       <c r="O190" t="n">
-        <v>158147.158774968</v>
+        <v>158147.1584</v>
       </c>
       <c r="P190" t="n">
         <v>6500</v>
@@ -8768,22 +8768,22 @@
         <v>0</v>
       </c>
       <c r="L193" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M193" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N193" t="n">
         <v>4891</v>
       </c>
       <c r="O193" t="n">
-        <v>73365</v>
+        <v>63583</v>
       </c>
       <c r="P193" t="n">
         <v>8200</v>
       </c>
       <c r="Q193" t="n">
-        <v>123000</v>
+        <v>106600</v>
       </c>
     </row>
     <row r="194">
@@ -8814,22 +8814,22 @@
         <v>0</v>
       </c>
       <c r="L194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M194" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N194" t="n">
         <v>8154</v>
       </c>
       <c r="O194" t="n">
-        <v>521856</v>
+        <v>513702</v>
       </c>
       <c r="P194" t="n">
         <v>13500</v>
       </c>
       <c r="Q194" t="n">
-        <v>864000</v>
+        <v>850500</v>
       </c>
     </row>
     <row r="195">
@@ -8860,22 +8860,22 @@
         <v>0</v>
       </c>
       <c r="L195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M195" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N195" t="n">
-        <v>14822.378837068</v>
+        <v>14822.378836364</v>
       </c>
       <c r="O195" t="n">
-        <v>207513.303718952</v>
+        <v>192690.924872732</v>
       </c>
       <c r="P195" t="n">
         <v>24900</v>
       </c>
       <c r="Q195" t="n">
-        <v>348600</v>
+        <v>323700</v>
       </c>
     </row>
     <row r="196">
@@ -9449,22 +9449,22 @@
         <v>0</v>
       </c>
       <c r="L208" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M208" t="n">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="N208" t="n">
         <v>1441.01</v>
       </c>
       <c r="O208" t="n">
-        <v>714740.96</v>
+        <v>711858.9399999999</v>
       </c>
       <c r="P208" t="n">
         <v>2100</v>
       </c>
       <c r="Q208" t="n">
-        <v>1041600</v>
+        <v>1037400</v>
       </c>
     </row>
     <row r="209">
@@ -9681,10 +9681,10 @@
         <v>225</v>
       </c>
       <c r="N213" t="n">
-        <v>1592.5660665658</v>
+        <v>1592.5660516325</v>
       </c>
       <c r="O213" t="n">
-        <v>358327.364977305</v>
+        <v>358327.3616173125</v>
       </c>
       <c r="P213" t="n">
         <v>3900</v>
@@ -10256,22 +10256,22 @@
         <v>0</v>
       </c>
       <c r="L226" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M226" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="N226" t="n">
         <v>9414.309999999999</v>
       </c>
       <c r="O226" t="n">
-        <v>743730.49</v>
+        <v>734316.1799999999</v>
       </c>
       <c r="P226" t="n">
         <v>16900</v>
       </c>
       <c r="Q226" t="n">
-        <v>1335100</v>
+        <v>1318200</v>
       </c>
     </row>
     <row r="227">
@@ -10996,10 +10996,10 @@
         <v>292</v>
       </c>
       <c r="N242" t="n">
-        <v>2403.5140171519</v>
+        <v>2403.5141965714</v>
       </c>
       <c r="O242" t="n">
-        <v>701826.0930083549</v>
+        <v>701826.1453988488</v>
       </c>
       <c r="P242" t="n">
         <v>3500</v>
@@ -11443,22 +11443,22 @@
         <v>0</v>
       </c>
       <c r="L252" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M252" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N252" t="n">
         <v>7028</v>
       </c>
       <c r="O252" t="n">
-        <v>133532</v>
+        <v>126504</v>
       </c>
       <c r="P252" t="n">
         <v>15900</v>
       </c>
       <c r="Q252" t="n">
-        <v>302100</v>
+        <v>286200</v>
       </c>
     </row>
     <row r="253">
@@ -12136,10 +12136,10 @@
         <v>165</v>
       </c>
       <c r="N268" t="n">
-        <v>2029.8739872408</v>
+        <v>2029.8739957379</v>
       </c>
       <c r="O268" t="n">
-        <v>334929.207894732</v>
+        <v>334929.2092967535</v>
       </c>
       <c r="P268" t="n">
         <v>3600</v>
@@ -12512,22 +12512,22 @@
         <v>0</v>
       </c>
       <c r="L277" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M277" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="N277" t="n">
         <v>14060.64</v>
       </c>
       <c r="O277" t="n">
-        <v>393697.92</v>
+        <v>379637.28</v>
       </c>
       <c r="P277" t="n">
         <v>22900</v>
       </c>
       <c r="Q277" t="n">
-        <v>641200</v>
+        <v>618300</v>
       </c>
     </row>
     <row r="278">
@@ -12838,10 +12838,10 @@
         <v>81</v>
       </c>
       <c r="N284" t="n">
-        <v>4285.1958525346</v>
+        <v>4285.1958592849</v>
       </c>
       <c r="O284" t="n">
-        <v>347100.8640553026</v>
+        <v>347100.8646020769</v>
       </c>
       <c r="P284" t="n">
         <v>6900</v>
@@ -13942,25 +13942,25 @@
         <v>6</v>
       </c>
       <c r="K309" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="L309" t="n">
         <v>0</v>
       </c>
       <c r="M309" t="n">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="N309" t="n">
         <v>16974.69</v>
       </c>
       <c r="O309" t="n">
-        <v>101848.14</v>
+        <v>780835.74</v>
       </c>
       <c r="P309" t="n">
         <v>26900</v>
       </c>
       <c r="Q309" t="n">
-        <v>161400</v>
+        <v>1237400</v>
       </c>
     </row>
     <row r="310">
@@ -14339,22 +14339,22 @@
         <v>0</v>
       </c>
       <c r="L318" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M318" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N318" t="n">
         <v>11662.4</v>
       </c>
       <c r="O318" t="n">
-        <v>81636.8</v>
+        <v>69974.39999999999</v>
       </c>
       <c r="P318" t="n">
         <v>19900</v>
       </c>
       <c r="Q318" t="n">
-        <v>139300</v>
+        <v>119400</v>
       </c>
     </row>
     <row r="319">
@@ -15898,25 +15898,25 @@
         <v>5</v>
       </c>
       <c r="K352" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L352" t="n">
         <v>0</v>
       </c>
       <c r="M352" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="N352" t="n">
         <v>38449</v>
       </c>
       <c r="O352" t="n">
-        <v>192245</v>
+        <v>768980</v>
       </c>
       <c r="P352" t="n">
         <v>62900</v>
       </c>
       <c r="Q352" t="n">
-        <v>314500</v>
+        <v>1258000</v>
       </c>
     </row>
     <row r="353">
@@ -16275,10 +16275,10 @@
         <v>75</v>
       </c>
       <c r="N360" t="n">
-        <v>1778.4726973583</v>
+        <v>1778.472697775</v>
       </c>
       <c r="O360" t="n">
-        <v>133385.4523018725</v>
+        <v>133385.452333125</v>
       </c>
       <c r="P360" t="n">
         <v>4900</v>
@@ -16591,25 +16591,25 @@
         <v>1</v>
       </c>
       <c r="K367" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="L367" t="n">
         <v>0</v>
       </c>
       <c r="M367" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="N367" t="n">
         <v>72889</v>
       </c>
       <c r="O367" t="n">
-        <v>72889</v>
+        <v>1239113</v>
       </c>
       <c r="P367" t="n">
         <v>117500</v>
       </c>
       <c r="Q367" t="n">
-        <v>117500</v>
+        <v>1997500</v>
       </c>
     </row>
     <row r="368">
@@ -19417,22 +19417,22 @@
         <v>0</v>
       </c>
       <c r="L428" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M428" t="n">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="N428" t="n">
-        <v>4907.8223782772</v>
+        <v>4907.8223917137</v>
       </c>
       <c r="O428" t="n">
-        <v>829421.9819288468</v>
+        <v>814698.5170244742</v>
       </c>
       <c r="P428" t="n">
         <v>8200</v>
       </c>
       <c r="Q428" t="n">
-        <v>1385800</v>
+        <v>1361200</v>
       </c>
     </row>
     <row r="429">
@@ -21437,10 +21437,10 @@
         <v>146</v>
       </c>
       <c r="N472" t="n">
-        <v>17075.98952183</v>
+        <v>17075.989521166</v>
       </c>
       <c r="O472" t="n">
-        <v>2493094.47018718</v>
+        <v>2493094.470090236</v>
       </c>
       <c r="P472" t="n">
         <v>27500</v>
@@ -22165,22 +22165,22 @@
         <v>0</v>
       </c>
       <c r="L488" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M488" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N488" t="n">
         <v>35909</v>
       </c>
       <c r="O488" t="n">
-        <v>215454</v>
+        <v>179545</v>
       </c>
       <c r="P488" t="n">
         <v>57900</v>
       </c>
       <c r="Q488" t="n">
-        <v>347400</v>
+        <v>289500</v>
       </c>
     </row>
     <row r="489">
@@ -22898,25 +22898,25 @@
         <v>6</v>
       </c>
       <c r="K504" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L504" t="n">
         <v>0</v>
       </c>
       <c r="M504" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="N504" t="n">
         <v>48522</v>
       </c>
       <c r="O504" t="n">
-        <v>291132</v>
+        <v>1261572</v>
       </c>
       <c r="P504" t="n">
         <v>77900</v>
       </c>
       <c r="Q504" t="n">
-        <v>467400</v>
+        <v>2025400</v>
       </c>
     </row>
     <row r="505">
@@ -23646,10 +23646,10 @@
         <v>282</v>
       </c>
       <c r="N520" t="n">
-        <v>2056.082714437</v>
+        <v>2056.08270929</v>
       </c>
       <c r="O520" t="n">
-        <v>579815.325471234</v>
+        <v>579815.3240197799</v>
       </c>
       <c r="P520" t="n">
         <v>2900</v>
@@ -23692,10 +23692,10 @@
         <v>327</v>
       </c>
       <c r="N521" t="n">
-        <v>3224.5689724311</v>
+        <v>3224.568981435</v>
       </c>
       <c r="O521" t="n">
-        <v>1054434.05398497</v>
+        <v>1054434.056929245</v>
       </c>
       <c r="P521" t="n">
         <v>4500</v>
@@ -24465,22 +24465,22 @@
         <v>0</v>
       </c>
       <c r="L538" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M538" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N538" t="n">
         <v>15423.36</v>
       </c>
       <c r="O538" t="n">
-        <v>632357.76</v>
+        <v>616934.4</v>
       </c>
       <c r="P538" t="n">
         <v>24900</v>
       </c>
       <c r="Q538" t="n">
-        <v>1020900</v>
+        <v>996000</v>
       </c>
     </row>
     <row r="539">
@@ -26101,10 +26101,10 @@
         <v>492</v>
       </c>
       <c r="N573" t="n">
-        <v>517.2923857868</v>
+        <v>517.29240467717</v>
       </c>
       <c r="O573" t="n">
-        <v>254507.8538071056</v>
+        <v>254507.8631011676</v>
       </c>
       <c r="P573" t="n">
         <v>900</v>
@@ -26332,10 +26332,10 @@
         <v>16</v>
       </c>
       <c r="N578" t="n">
-        <v>3110.8400113026</v>
+        <v>3110.8399744753</v>
       </c>
       <c r="O578" t="n">
-        <v>49773.4401808416</v>
+        <v>49773.4395916048</v>
       </c>
       <c r="P578" t="n">
         <v>4500</v>
@@ -32501,22 +32501,22 @@
         <v>0</v>
       </c>
       <c r="L708" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M708" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="N708" t="n">
         <v>7650</v>
       </c>
       <c r="O708" t="n">
-        <v>114750</v>
+        <v>91800</v>
       </c>
       <c r="P708" t="n">
         <v>9900</v>
       </c>
       <c r="Q708" t="n">
-        <v>148500</v>
+        <v>118800</v>
       </c>
     </row>
     <row r="709">
@@ -32547,22 +32547,22 @@
         <v>0</v>
       </c>
       <c r="L709" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M709" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N709" t="n">
-        <v>19800</v>
+        <v>0</v>
       </c>
       <c r="O709" t="n">
-        <v>19800</v>
+        <v>0</v>
       </c>
       <c r="P709" t="n">
         <v>24900</v>
       </c>
       <c r="Q709" t="n">
-        <v>24900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="710">
@@ -32915,22 +32915,22 @@
         <v>0</v>
       </c>
       <c r="L717" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M717" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N717" t="n">
         <v>25200</v>
       </c>
       <c r="O717" t="n">
-        <v>50400</v>
+        <v>25200</v>
       </c>
       <c r="P717" t="n">
         <v>31900</v>
       </c>
       <c r="Q717" t="n">
-        <v>63800</v>
+        <v>31900</v>
       </c>
     </row>
     <row r="718">
@@ -33145,22 +33145,22 @@
         <v>0</v>
       </c>
       <c r="L722" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M722" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N722" t="n">
         <v>31500</v>
       </c>
       <c r="O722" t="n">
-        <v>472500</v>
+        <v>441000</v>
       </c>
       <c r="P722" t="n">
         <v>39900</v>
       </c>
       <c r="Q722" t="n">
-        <v>598500</v>
+        <v>558600</v>
       </c>
     </row>
     <row r="723">
@@ -33329,22 +33329,22 @@
         <v>0</v>
       </c>
       <c r="L726" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M726" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N726" t="n">
         <v>36000</v>
       </c>
       <c r="O726" t="n">
-        <v>108000</v>
+        <v>72000</v>
       </c>
       <c r="P726" t="n">
         <v>45000</v>
       </c>
       <c r="Q726" t="n">
-        <v>135000</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="727">
@@ -34433,22 +34433,22 @@
         <v>0</v>
       </c>
       <c r="L750" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M750" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="N750" t="n">
         <v>6160</v>
       </c>
       <c r="O750" t="n">
-        <v>215600</v>
+        <v>190960</v>
       </c>
       <c r="P750" t="n">
         <v>7900</v>
       </c>
       <c r="Q750" t="n">
-        <v>276500</v>
+        <v>244900</v>
       </c>
     </row>
     <row r="751">
@@ -34617,22 +34617,22 @@
         <v>0</v>
       </c>
       <c r="L754" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M754" t="n">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="N754" t="n">
         <v>3520</v>
       </c>
       <c r="O754" t="n">
-        <v>482240</v>
+        <v>475200</v>
       </c>
       <c r="P754" t="n">
         <v>4500</v>
       </c>
       <c r="Q754" t="n">
-        <v>616500</v>
+        <v>607500</v>
       </c>
     </row>
     <row r="755">
@@ -34709,22 +34709,22 @@
         <v>0</v>
       </c>
       <c r="L756" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M756" t="n">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="N756" t="n">
         <v>9240</v>
       </c>
       <c r="O756" t="n">
-        <v>5608680</v>
+        <v>5599440</v>
       </c>
       <c r="P756" t="n">
         <v>11500</v>
       </c>
       <c r="Q756" t="n">
-        <v>6980500</v>
+        <v>6969000</v>
       </c>
     </row>
     <row r="757">

--- a/bodegas/LJ-05.xlsx
+++ b/bodegas/LJ-05.xlsx
@@ -7180,10 +7180,10 @@
         <v>220</v>
       </c>
       <c r="N158" t="n">
-        <v>2582.2554675768</v>
+        <v>2582.2554613807</v>
       </c>
       <c r="O158" t="n">
-        <v>568096.2028668961</v>
+        <v>568096.201503754</v>
       </c>
       <c r="P158" t="n">
         <v>4500</v>
@@ -7548,10 +7548,10 @@
         <v>94</v>
       </c>
       <c r="N166" t="n">
-        <v>7507.39</v>
+        <v>7518.1997768179</v>
       </c>
       <c r="O166" t="n">
-        <v>705694.66</v>
+        <v>706710.7790208826</v>
       </c>
       <c r="P166" t="n">
         <v>13500</v>
@@ -9411,10 +9411,10 @@
         <v>1</v>
       </c>
       <c r="N207" t="n">
-        <v>15851.61</v>
+        <v>15976.425826772</v>
       </c>
       <c r="O207" t="n">
-        <v>15851.61</v>
+        <v>15976.425826772</v>
       </c>
       <c r="P207" t="n">
         <v>23900</v>
@@ -10996,10 +10996,10 @@
         <v>290</v>
       </c>
       <c r="N242" t="n">
-        <v>2403.5142945915</v>
+        <v>2403.514304468</v>
       </c>
       <c r="O242" t="n">
-        <v>697019.145431535</v>
+        <v>697019.14829572</v>
       </c>
       <c r="P242" t="n">
         <v>3500</v>
@@ -16362,10 +16362,10 @@
         <v>75</v>
       </c>
       <c r="N362" t="n">
-        <v>1778.4727006961</v>
+        <v>1778.4727011139</v>
       </c>
       <c r="O362" t="n">
-        <v>133385.4525522075</v>
+        <v>133385.4525835425</v>
       </c>
       <c r="P362" t="n">
         <v>4900</v>
@@ -18400,10 +18400,10 @@
         <v>16</v>
       </c>
       <c r="N406" t="n">
-        <v>28116</v>
+        <v>28613.628318584</v>
       </c>
       <c r="O406" t="n">
-        <v>449856</v>
+        <v>457818.053097344</v>
       </c>
       <c r="P406" t="n">
         <v>45900</v>
@@ -20788,10 +20788,10 @@
         <v>14</v>
       </c>
       <c r="N458" t="n">
-        <v>27186</v>
+        <v>27309.572727273</v>
       </c>
       <c r="O458" t="n">
-        <v>380604</v>
+        <v>382334.018181822</v>
       </c>
       <c r="P458" t="n">
         <v>43900</v>
@@ -21936,10 +21936,10 @@
         <v>27</v>
       </c>
       <c r="N483" t="n">
-        <v>10755</v>
+        <v>10792.803163445</v>
       </c>
       <c r="O483" t="n">
-        <v>290385</v>
+        <v>291405.685413015</v>
       </c>
       <c r="P483" t="n">
         <v>17900</v>
@@ -22672,10 +22672,10 @@
         <v>5</v>
       </c>
       <c r="N499" t="n">
-        <v>10713.21</v>
+        <v>10792.371650246</v>
       </c>
       <c r="O499" t="n">
-        <v>53566.05</v>
+        <v>53961.85825123</v>
       </c>
       <c r="P499" t="n">
         <v>20900</v>
@@ -23549,10 +23549,10 @@
         <v>237</v>
       </c>
       <c r="N518" t="n">
-        <v>1803.0159286464</v>
+        <v>1803.0159327966</v>
       </c>
       <c r="O518" t="n">
-        <v>427314.7750891968</v>
+        <v>427314.7760727942</v>
       </c>
       <c r="P518" t="n">
         <v>2500</v>
@@ -26463,10 +26463,10 @@
         <v>1051</v>
       </c>
       <c r="N581" t="n">
-        <v>703.79497049501</v>
+        <v>703.79496992783</v>
       </c>
       <c r="O581" t="n">
-        <v>739688.5139902555</v>
+        <v>739688.5133941494</v>
       </c>
       <c r="P581" t="n">
         <v>900</v>
@@ -33928,10 +33928,10 @@
         <v>432</v>
       </c>
       <c r="N739" t="n">
-        <v>7480</v>
+        <v>7524.8351648352</v>
       </c>
       <c r="O739" t="n">
-        <v>3231360</v>
+        <v>3250728.791208806</v>
       </c>
       <c r="P739" t="n">
         <v>9500</v>
@@ -34198,22 +34198,22 @@
         <v>0</v>
       </c>
       <c r="L745" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M745" t="n">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="N745" t="n">
         <v>3872</v>
       </c>
       <c r="O745" t="n">
-        <v>987360</v>
+        <v>964128</v>
       </c>
       <c r="P745" t="n">
         <v>4900</v>
       </c>
       <c r="Q745" t="n">
-        <v>1249500</v>
+        <v>1220100</v>
       </c>
     </row>
     <row r="746">
@@ -34290,22 +34290,22 @@
         <v>0</v>
       </c>
       <c r="L747" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M747" t="n">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="N747" t="n">
         <v>3872</v>
       </c>
       <c r="O747" t="n">
-        <v>1022208</v>
+        <v>998976</v>
       </c>
       <c r="P747" t="n">
         <v>4900</v>
       </c>
       <c r="Q747" t="n">
-        <v>1293600</v>
+        <v>1264200</v>
       </c>
     </row>
     <row r="748">
@@ -34336,22 +34336,22 @@
         <v>0</v>
       </c>
       <c r="L748" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M748" t="n">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="N748" t="n">
         <v>6160</v>
       </c>
       <c r="O748" t="n">
-        <v>1207360</v>
+        <v>1182720</v>
       </c>
       <c r="P748" t="n">
         <v>7900</v>
       </c>
       <c r="Q748" t="n">
-        <v>1548400</v>
+        <v>1516800</v>
       </c>
     </row>
     <row r="749">
@@ -34382,22 +34382,22 @@
         <v>0</v>
       </c>
       <c r="L749" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M749" t="n">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="N749" t="n">
         <v>6160</v>
       </c>
       <c r="O749" t="n">
-        <v>1275120</v>
+        <v>1250480</v>
       </c>
       <c r="P749" t="n">
         <v>7900</v>
       </c>
       <c r="Q749" t="n">
-        <v>1635300</v>
+        <v>1603700</v>
       </c>
     </row>
     <row r="750">
@@ -34428,22 +34428,22 @@
         <v>0</v>
       </c>
       <c r="L750" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M750" t="n">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="N750" t="n">
         <v>6160</v>
       </c>
       <c r="O750" t="n">
-        <v>1232000</v>
+        <v>1207360</v>
       </c>
       <c r="P750" t="n">
         <v>7900</v>
       </c>
       <c r="Q750" t="n">
-        <v>1580000</v>
+        <v>1548400</v>
       </c>
     </row>
     <row r="751">
@@ -34474,22 +34474,22 @@
         <v>0</v>
       </c>
       <c r="L751" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M751" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="N751" t="n">
         <v>6160</v>
       </c>
       <c r="O751" t="n">
-        <v>190960</v>
+        <v>166320</v>
       </c>
       <c r="P751" t="n">
         <v>7900</v>
       </c>
       <c r="Q751" t="n">
-        <v>244900</v>
+        <v>213300</v>
       </c>
     </row>
     <row r="752">
@@ -34520,22 +34520,22 @@
         <v>0</v>
       </c>
       <c r="L752" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M752" t="n">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="N752" t="n">
         <v>3344</v>
       </c>
       <c r="O752" t="n">
-        <v>1093488</v>
+        <v>1060048</v>
       </c>
       <c r="P752" t="n">
         <v>4500</v>
       </c>
       <c r="Q752" t="n">
-        <v>1471500</v>
+        <v>1426500</v>
       </c>
     </row>
     <row r="753">
@@ -34566,22 +34566,22 @@
         <v>0</v>
       </c>
       <c r="L753" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M753" t="n">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="N753" t="n">
         <v>3344</v>
       </c>
       <c r="O753" t="n">
-        <v>1043328</v>
+        <v>1029952</v>
       </c>
       <c r="P753" t="n">
         <v>4500</v>
       </c>
       <c r="Q753" t="n">
-        <v>1404000</v>
+        <v>1386000</v>
       </c>
     </row>
     <row r="754">
@@ -34612,22 +34612,22 @@
         <v>0</v>
       </c>
       <c r="L754" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M754" t="n">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="N754" t="n">
         <v>4400</v>
       </c>
       <c r="O754" t="n">
-        <v>497200</v>
+        <v>470800</v>
       </c>
       <c r="P754" t="n">
         <v>5900</v>
       </c>
       <c r="Q754" t="n">
-        <v>666700</v>
+        <v>631300</v>
       </c>
     </row>
     <row r="755">
@@ -34934,22 +34934,22 @@
         <v>0</v>
       </c>
       <c r="L761" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M761" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="N761" t="n">
         <v>4576</v>
       </c>
       <c r="O761" t="n">
-        <v>247104</v>
+        <v>219648</v>
       </c>
       <c r="P761" t="n">
         <v>5900</v>
       </c>
       <c r="Q761" t="n">
-        <v>318600</v>
+        <v>283200</v>
       </c>
     </row>
     <row r="762">

--- a/bodegas/LJ-05.xlsx
+++ b/bodegas/LJ-05.xlsx
@@ -3950,10 +3950,10 @@
         <v>1</v>
       </c>
       <c r="N84" t="n">
-        <v>432516.155</v>
+        <v>288344.22</v>
       </c>
       <c r="O84" t="n">
-        <v>432516.155</v>
+        <v>288344.22</v>
       </c>
       <c r="P84" t="n">
         <v>450000</v>
@@ -6341,10 +6341,10 @@
         <v>696</v>
       </c>
       <c r="N139" t="n">
-        <v>2834.5536057033</v>
+        <v>2833</v>
       </c>
       <c r="O139" t="n">
-        <v>1972849.309569497</v>
+        <v>1971768</v>
       </c>
       <c r="P139" t="n">
         <v>3500</v>
@@ -6961,10 +6961,10 @@
         <v>41</v>
       </c>
       <c r="N153" t="n">
-        <v>13642.54185766</v>
+        <v>13593.35</v>
       </c>
       <c r="O153" t="n">
-        <v>559344.2161640601</v>
+        <v>557327.35</v>
       </c>
       <c r="P153" t="n">
         <v>25500</v>
@@ -7138,10 +7138,10 @@
         <v>80</v>
       </c>
       <c r="N157" t="n">
-        <v>2808.3040151157</v>
+        <v>2804.33</v>
       </c>
       <c r="O157" t="n">
-        <v>224664.321209256</v>
+        <v>224346.4</v>
       </c>
       <c r="P157" t="n">
         <v>4900</v>
@@ -7225,10 +7225,10 @@
         <v>208</v>
       </c>
       <c r="N159" t="n">
-        <v>2584.0407928094</v>
+        <v>2582.2554090804</v>
       </c>
       <c r="O159" t="n">
-        <v>537480.4849043553</v>
+        <v>537109.1250887233</v>
       </c>
       <c r="P159" t="n">
         <v>4500</v>
@@ -7317,10 +7317,10 @@
         <v>83</v>
       </c>
       <c r="N161" t="n">
-        <v>5216.8960111863</v>
+        <v>5216.8960094242</v>
       </c>
       <c r="O161" t="n">
-        <v>433002.3689284629</v>
+        <v>433002.3687822086</v>
       </c>
       <c r="P161" t="n">
         <v>8500</v>
@@ -7363,10 +7363,10 @@
         <v>677</v>
       </c>
       <c r="N162" t="n">
-        <v>3161.3542590035</v>
+        <v>3158.8608322644</v>
       </c>
       <c r="O162" t="n">
-        <v>2140236.833345369</v>
+        <v>2138548.783442999</v>
       </c>
       <c r="P162" t="n">
         <v>5600</v>
@@ -7455,10 +7455,10 @@
         <v>268</v>
       </c>
       <c r="N164" t="n">
-        <v>1482.16796875</v>
+        <v>1480</v>
       </c>
       <c r="O164" t="n">
-        <v>397221.015625</v>
+        <v>396640</v>
       </c>
       <c r="P164" t="n">
         <v>2600</v>
@@ -7864,10 +7864,10 @@
         <v>12</v>
       </c>
       <c r="N173" t="n">
-        <v>2619.5155335628</v>
+        <v>2612.77</v>
       </c>
       <c r="O173" t="n">
-        <v>31434.1864027536</v>
+        <v>31353.24</v>
       </c>
       <c r="P173" t="n">
         <v>4900</v>
@@ -7910,10 +7910,10 @@
         <v>268</v>
       </c>
       <c r="N174" t="n">
-        <v>4362.7231895528</v>
+        <v>4357.55</v>
       </c>
       <c r="O174" t="n">
-        <v>1169209.81480015</v>
+        <v>1167823.4</v>
       </c>
       <c r="P174" t="n">
         <v>7500</v>
@@ -8002,10 +8002,10 @@
         <v>62</v>
       </c>
       <c r="N176" t="n">
-        <v>4890.9300496586</v>
+        <v>4890.9300497203</v>
       </c>
       <c r="O176" t="n">
-        <v>303237.6630788332</v>
+        <v>303237.6630826586</v>
       </c>
       <c r="P176" t="n">
         <v>8200</v>
@@ -8501,10 +8501,10 @@
         <v>87</v>
       </c>
       <c r="N187" t="n">
-        <v>8670.9576008273</v>
+        <v>8662</v>
       </c>
       <c r="O187" t="n">
-        <v>754373.311271975</v>
+        <v>753594</v>
       </c>
       <c r="P187" t="n">
         <v>14200</v>
@@ -8678,10 +8678,10 @@
         <v>44</v>
       </c>
       <c r="N191" t="n">
-        <v>3594.2535785953</v>
+        <v>3594.2535742972</v>
       </c>
       <c r="O191" t="n">
-        <v>158147.1574581932</v>
+        <v>158147.1572690768</v>
       </c>
       <c r="P191" t="n">
         <v>6500</v>
@@ -8773,10 +8773,10 @@
         <v>1439</v>
       </c>
       <c r="N193" t="n">
-        <v>500.91436884092</v>
+        <v>489.88</v>
       </c>
       <c r="O193" t="n">
-        <v>720815.7767620839</v>
+        <v>704937.3199999999</v>
       </c>
       <c r="P193" t="n">
         <v>700</v>
@@ -8911,10 +8911,10 @@
         <v>30</v>
       </c>
       <c r="N196" t="n">
-        <v>14849.377704918</v>
+        <v>14822.378834244</v>
       </c>
       <c r="O196" t="n">
-        <v>445481.33114754</v>
+        <v>444671.36502732</v>
       </c>
       <c r="P196" t="n">
         <v>24900</v>
@@ -9232,10 +9232,10 @@
         <v>13</v>
       </c>
       <c r="N203" t="n">
-        <v>12618.152142857</v>
+        <v>12267.647571429</v>
       </c>
       <c r="O203" t="n">
-        <v>164035.977857141</v>
+        <v>159479.418428577</v>
       </c>
       <c r="P203" t="n">
         <v>19900</v>
@@ -9590,10 +9590,10 @@
         <v>116</v>
       </c>
       <c r="N211" t="n">
-        <v>3041.6600137268</v>
+        <v>3041.6600137646</v>
       </c>
       <c r="O211" t="n">
-        <v>352832.5615923088</v>
+        <v>352832.5615966936</v>
       </c>
       <c r="P211" t="n">
         <v>5500</v>
@@ -9636,10 +9636,10 @@
         <v>73</v>
       </c>
       <c r="N212" t="n">
-        <v>4372.2107926742</v>
+        <v>4374.7145640659</v>
       </c>
       <c r="O212" t="n">
-        <v>319171.3878652166</v>
+        <v>319354.1631768107</v>
       </c>
       <c r="P212" t="n">
         <v>7500</v>
@@ -10263,10 +10263,10 @@
         <v>77</v>
       </c>
       <c r="N226" t="n">
-        <v>9422.619187996501</v>
+        <v>9414.309999999999</v>
       </c>
       <c r="O226" t="n">
-        <v>725541.6774757305</v>
+        <v>724901.87</v>
       </c>
       <c r="P226" t="n">
         <v>16900</v>
@@ -10451,10 +10451,10 @@
         <v>198</v>
       </c>
       <c r="N230" t="n">
-        <v>4673.2793206522</v>
+        <v>4635.49</v>
       </c>
       <c r="O230" t="n">
-        <v>925309.3054891357</v>
+        <v>917827.0199999999</v>
       </c>
       <c r="P230" t="n">
         <v>7500</v>
@@ -10588,10 +10588,10 @@
         <v>87</v>
       </c>
       <c r="N233" t="n">
-        <v>16960.16635514</v>
+        <v>16897</v>
       </c>
       <c r="O233" t="n">
-        <v>1475534.47289718</v>
+        <v>1470039</v>
       </c>
       <c r="P233" t="n">
         <v>27900</v>
@@ -10817,10 +10817,10 @@
         <v>64</v>
       </c>
       <c r="N238" t="n">
-        <v>11939.712442396</v>
+        <v>11921.4</v>
       </c>
       <c r="O238" t="n">
-        <v>764141.596313344</v>
+        <v>762969.6</v>
       </c>
       <c r="P238" t="n">
         <v>19900</v>
@@ -10951,10 +10951,10 @@
         <v>22</v>
       </c>
       <c r="N241" t="n">
-        <v>9926.065993788799</v>
+        <v>9903</v>
       </c>
       <c r="O241" t="n">
-        <v>218373.4518633536</v>
+        <v>217866</v>
       </c>
       <c r="P241" t="n">
         <v>15900</v>
@@ -10997,10 +10997,10 @@
         <v>244</v>
       </c>
       <c r="N242" t="n">
-        <v>2403.5145969448</v>
+        <v>2549.7269035153</v>
       </c>
       <c r="O242" t="n">
-        <v>586457.5616545312</v>
+        <v>622133.3644577332</v>
       </c>
       <c r="P242" t="n">
         <v>3500</v>
@@ -11043,10 +11043,10 @@
         <v>14</v>
       </c>
       <c r="N243" t="n">
-        <v>16994.7</v>
+        <v>14778</v>
       </c>
       <c r="O243" t="n">
-        <v>237925.8</v>
+        <v>206892</v>
       </c>
       <c r="P243" t="n">
         <v>24900</v>
@@ -11968,10 +11968,10 @@
         <v>40</v>
       </c>
       <c r="N264" t="n">
-        <v>8799.4430248307</v>
+        <v>8794.48</v>
       </c>
       <c r="O264" t="n">
-        <v>351977.720993228</v>
+        <v>351779.2</v>
       </c>
       <c r="P264" t="n">
         <v>14500</v>
@@ -12096,10 +12096,10 @@
         <v>156</v>
       </c>
       <c r="N267" t="n">
-        <v>2523.5712699748</v>
+        <v>2517.22</v>
       </c>
       <c r="O267" t="n">
-        <v>393677.1181160688</v>
+        <v>392686.3199999999</v>
       </c>
       <c r="P267" t="n">
         <v>4200</v>
@@ -12519,10 +12519,10 @@
         <v>26</v>
       </c>
       <c r="N277" t="n">
-        <v>14161.073142857</v>
+        <v>14060.64</v>
       </c>
       <c r="O277" t="n">
-        <v>368187.901714282</v>
+        <v>365576.64</v>
       </c>
       <c r="P277" t="n">
         <v>22900</v>
@@ -12839,10 +12839,10 @@
         <v>81</v>
       </c>
       <c r="N284" t="n">
-        <v>4285.1958660508</v>
+        <v>4285.1959694477</v>
       </c>
       <c r="O284" t="n">
-        <v>347100.8651501148</v>
+        <v>347100.8735252637</v>
       </c>
       <c r="P284" t="n">
         <v>6900</v>
@@ -13231,10 +13231,10 @@
         <v>22</v>
       </c>
       <c r="N293" t="n">
-        <v>11594.607549296</v>
+        <v>11562.038422535</v>
       </c>
       <c r="O293" t="n">
-        <v>255081.366084512</v>
+        <v>254364.84529577</v>
       </c>
       <c r="P293" t="n">
         <v>18500</v>
@@ -13277,10 +13277,10 @@
         <v>39</v>
       </c>
       <c r="N294" t="n">
-        <v>13621.7524</v>
+        <v>13513.64328</v>
       </c>
       <c r="O294" t="n">
-        <v>531248.3436</v>
+        <v>527032.08792</v>
       </c>
       <c r="P294" t="n">
         <v>21900</v>
@@ -13778,10 +13778,10 @@
         <v>9</v>
       </c>
       <c r="N305" t="n">
-        <v>27871.270433071</v>
+        <v>27123.76496063</v>
       </c>
       <c r="O305" t="n">
-        <v>250841.433897639</v>
+        <v>244113.88464567</v>
       </c>
       <c r="P305" t="n">
         <v>44500</v>
@@ -13906,10 +13906,10 @@
         <v>28</v>
       </c>
       <c r="N308" t="n">
-        <v>17070.322056338</v>
+        <v>16974.69</v>
       </c>
       <c r="O308" t="n">
-        <v>477969.0175774639</v>
+        <v>475291.3199999999</v>
       </c>
       <c r="P308" t="n">
         <v>26900</v>
@@ -13947,10 +13947,10 @@
         <v>9</v>
       </c>
       <c r="N309" t="n">
-        <v>4110.4025485437</v>
+        <v>4100.45</v>
       </c>
       <c r="O309" t="n">
-        <v>36993.6229368933</v>
+        <v>36904.05</v>
       </c>
       <c r="P309" t="n">
         <v>26900</v>
@@ -14564,10 +14564,10 @@
         <v>57</v>
       </c>
       <c r="N323" t="n">
-        <v>9681.731751412401</v>
+        <v>9627.34</v>
       </c>
       <c r="O323" t="n">
-        <v>551858.7098305068</v>
+        <v>548758.38</v>
       </c>
       <c r="P323" t="n">
         <v>15900</v>
@@ -15995,10 +15995,10 @@
         <v>32</v>
       </c>
       <c r="N354" t="n">
-        <v>15867.472527473</v>
+        <v>15824</v>
       </c>
       <c r="O354" t="n">
-        <v>507759.120879136</v>
+        <v>506368</v>
       </c>
       <c r="P354" t="n">
         <v>26900</v>
@@ -16271,10 +16271,10 @@
         <v>59</v>
       </c>
       <c r="N360" t="n">
-        <v>1778.4727221703</v>
+        <v>1778.4727234441</v>
       </c>
       <c r="O360" t="n">
-        <v>104929.8906080477</v>
+        <v>104929.8906832019</v>
       </c>
       <c r="P360" t="n">
         <v>4900</v>
@@ -17895,10 +17895,10 @@
         <v>14</v>
       </c>
       <c r="N395" t="n">
-        <v>32376.967005076</v>
+        <v>32295</v>
       </c>
       <c r="O395" t="n">
-        <v>453277.538071064</v>
+        <v>452130</v>
       </c>
       <c r="P395" t="n">
         <v>51900</v>
@@ -18450,10 +18450,10 @@
         <v>82</v>
       </c>
       <c r="N407" t="n">
-        <v>8872.340618996799</v>
+        <v>8858.16</v>
       </c>
       <c r="O407" t="n">
-        <v>727531.9307577375</v>
+        <v>726369.12</v>
       </c>
       <c r="P407" t="n">
         <v>15500</v>
@@ -18867,10 +18867,10 @@
         <v>181</v>
       </c>
       <c r="N416" t="n">
-        <v>2336.84913125</v>
+        <v>2328.11868125</v>
       </c>
       <c r="O416" t="n">
-        <v>422969.69275625</v>
+        <v>421389.48130625</v>
       </c>
       <c r="P416" t="n">
         <v>4500</v>
@@ -18959,10 +18959,10 @@
         <v>27</v>
       </c>
       <c r="N418" t="n">
-        <v>9384</v>
+        <v>9686.7096774194</v>
       </c>
       <c r="O418" t="n">
-        <v>253368</v>
+        <v>261541.1612903238</v>
       </c>
       <c r="P418" t="n">
         <v>15900</v>
@@ -19051,10 +19051,10 @@
         <v>4</v>
       </c>
       <c r="N420" t="n">
-        <v>35287.397849462</v>
+        <v>34912</v>
       </c>
       <c r="O420" t="n">
-        <v>141149.591397848</v>
+        <v>139648</v>
       </c>
       <c r="P420" t="n">
         <v>56900</v>
@@ -19787,10 +19787,10 @@
         <v>84</v>
       </c>
       <c r="N436" t="n">
-        <v>3922.9680788177</v>
+        <v>3903.7379310345</v>
       </c>
       <c r="O436" t="n">
-        <v>329529.3186206868</v>
+        <v>327913.986206898</v>
       </c>
       <c r="P436" t="n">
         <v>7500</v>
@@ -20007,10 +20007,10 @@
         <v>25</v>
       </c>
       <c r="N441" t="n">
-        <v>33317.307692308</v>
+        <v>33000</v>
       </c>
       <c r="O441" t="n">
-        <v>832932.6923077001</v>
+        <v>825000</v>
       </c>
       <c r="P441" t="n">
         <v>52900</v>
@@ -20237,10 +20237,10 @@
         <v>37</v>
       </c>
       <c r="N446" t="n">
-        <v>12463.909090909</v>
+        <v>11922</v>
       </c>
       <c r="O446" t="n">
-        <v>461164.636363633</v>
+        <v>441114</v>
       </c>
       <c r="P446" t="n">
         <v>19900</v>
@@ -20789,10 +20789,10 @@
         <v>17</v>
       </c>
       <c r="N458" t="n">
-        <v>7668.5070422535</v>
+        <v>7562</v>
       </c>
       <c r="O458" t="n">
-        <v>130364.6197183095</v>
+        <v>128554</v>
       </c>
       <c r="P458" t="n">
         <v>12900</v>
@@ -20835,10 +20835,10 @@
         <v>140</v>
       </c>
       <c r="N459" t="n">
-        <v>3901.1562753036</v>
+        <v>3898</v>
       </c>
       <c r="O459" t="n">
-        <v>546161.878542504</v>
+        <v>545720</v>
       </c>
       <c r="P459" t="n">
         <v>6900</v>
@@ -20881,10 +20881,10 @@
         <v>21</v>
       </c>
       <c r="N460" t="n">
-        <v>13606.546707504</v>
+        <v>13565</v>
       </c>
       <c r="O460" t="n">
-        <v>285737.480857584</v>
+        <v>284865</v>
       </c>
       <c r="P460" t="n">
         <v>22500</v>
@@ -20927,10 +20927,10 @@
         <v>69</v>
       </c>
       <c r="N461" t="n">
-        <v>7647.7960893855</v>
+        <v>7635</v>
       </c>
       <c r="O461" t="n">
-        <v>527697.9301675995</v>
+        <v>526815</v>
       </c>
       <c r="P461" t="n">
         <v>13900</v>
@@ -21019,10 +21019,10 @@
         <v>211</v>
       </c>
       <c r="N463" t="n">
-        <v>5690.8504672897</v>
+        <v>5682</v>
       </c>
       <c r="O463" t="n">
-        <v>1200769.448598127</v>
+        <v>1198902</v>
       </c>
       <c r="P463" t="n">
         <v>9900</v>
@@ -22351,10 +22351,10 @@
         <v>14</v>
       </c>
       <c r="N492" t="n">
-        <v>14348.936170213</v>
+        <v>14050</v>
       </c>
       <c r="O492" t="n">
-        <v>200885.106382982</v>
+        <v>196700</v>
       </c>
       <c r="P492" t="n">
         <v>23900</v>
@@ -22397,10 +22397,10 @@
         <v>35</v>
       </c>
       <c r="N493" t="n">
-        <v>8721.0653753027</v>
+        <v>8700</v>
       </c>
       <c r="O493" t="n">
-        <v>305237.2881355945</v>
+        <v>304500</v>
       </c>
       <c r="P493" t="n">
         <v>14900</v>
@@ -22719,10 +22719,10 @@
         <v>11</v>
       </c>
       <c r="N500" t="n">
-        <v>21822.282548476</v>
+        <v>21762</v>
       </c>
       <c r="O500" t="n">
-        <v>240045.108033236</v>
+        <v>239382</v>
       </c>
       <c r="P500" t="n">
         <v>35900</v>
@@ -22811,10 +22811,10 @@
         <v>21</v>
       </c>
       <c r="N502" t="n">
-        <v>15512.396866841</v>
+        <v>15472</v>
       </c>
       <c r="O502" t="n">
-        <v>325760.334203661</v>
+        <v>324912</v>
       </c>
       <c r="P502" t="n">
         <v>25900</v>
@@ -23041,10 +23041,10 @@
         <v>147</v>
       </c>
       <c r="N507" t="n">
-        <v>5483.2964690207</v>
+        <v>5476</v>
       </c>
       <c r="O507" t="n">
-        <v>806044.5809460429</v>
+        <v>804972</v>
       </c>
       <c r="P507" t="n">
         <v>8900</v>
@@ -23182,10 +23182,10 @@
         <v>8</v>
       </c>
       <c r="N510" t="n">
-        <v>38558.016</v>
+        <v>38252</v>
       </c>
       <c r="O510" t="n">
-        <v>308464.128</v>
+        <v>306016</v>
       </c>
       <c r="P510" t="n">
         <v>61900</v>
@@ -24467,10 +24467,10 @@
         <v>37</v>
       </c>
       <c r="N538" t="n">
-        <v>15733.897449664</v>
+        <v>15423.36</v>
       </c>
       <c r="O538" t="n">
-        <v>582154.205637568</v>
+        <v>570664.3200000001</v>
       </c>
       <c r="P538" t="n">
         <v>24900</v>
@@ -25129,10 +25129,10 @@
         <v>20</v>
       </c>
       <c r="N552" t="n">
-        <v>10732.242580645</v>
+        <v>10732.242857143</v>
       </c>
       <c r="O552" t="n">
-        <v>214644.8516129</v>
+        <v>214644.85714286</v>
       </c>
       <c r="P552" t="n">
         <v>25900</v>
@@ -26328,10 +26328,10 @@
         <v>9</v>
       </c>
       <c r="N578" t="n">
-        <v>3110.839841954</v>
+        <v>3110.8397979798</v>
       </c>
       <c r="O578" t="n">
-        <v>27997.558577586</v>
+        <v>27997.5581818182</v>
       </c>
       <c r="P578" t="n">
         <v>4500</v>
@@ -27008,10 +27008,10 @@
         <v>7</v>
       </c>
       <c r="N592" t="n">
-        <v>18621.814408602</v>
+        <v>18423.71</v>
       </c>
       <c r="O592" t="n">
-        <v>130352.700860214</v>
+        <v>128965.97</v>
       </c>
       <c r="P592" t="n">
         <v>10000</v>
@@ -29068,10 +29068,10 @@
         <v>19</v>
       </c>
       <c r="N635" t="n">
-        <v>3098.3874489796</v>
+        <v>3067.0906122449</v>
       </c>
       <c r="O635" t="n">
-        <v>58869.3615306124</v>
+        <v>58274.7216326531</v>
       </c>
       <c r="P635" t="n">
         <v>7200</v>
@@ -29778,10 +29778,10 @@
         <v>8</v>
       </c>
       <c r="N650" t="n">
-        <v>10993.181190476</v>
+        <v>10737.525714286</v>
       </c>
       <c r="O650" t="n">
-        <v>87945.449523808</v>
+        <v>85900.20571428799</v>
       </c>
       <c r="P650" t="n">
         <v>18900</v>
@@ -30828,10 +30828,10 @@
         <v>12</v>
       </c>
       <c r="N672" t="n">
-        <v>24490.111557632</v>
+        <v>24338.47</v>
       </c>
       <c r="O672" t="n">
-        <v>293881.338691584</v>
+        <v>292061.64</v>
       </c>
       <c r="P672" t="n">
         <v>27900</v>
@@ -32183,10 +32183,10 @@
         <v>6</v>
       </c>
       <c r="N701" t="n">
-        <v>23100</v>
+        <v>19800</v>
       </c>
       <c r="O701" t="n">
-        <v>138600</v>
+        <v>118800</v>
       </c>
       <c r="P701" t="n">
         <v>24900</v>
@@ -32229,10 +32229,10 @@
         <v>6</v>
       </c>
       <c r="N702" t="n">
-        <v>24150</v>
+        <v>20700</v>
       </c>
       <c r="O702" t="n">
-        <v>144900</v>
+        <v>124200</v>
       </c>
       <c r="P702" t="n">
         <v>25900</v>
@@ -32919,10 +32919,10 @@
         <v>9</v>
       </c>
       <c r="N717" t="n">
-        <v>36300</v>
+        <v>29700</v>
       </c>
       <c r="O717" t="n">
-        <v>326700</v>
+        <v>267300</v>
       </c>
       <c r="P717" t="n">
         <v>39900</v>
@@ -33057,10 +33057,10 @@
         <v>45</v>
       </c>
       <c r="N720" t="n">
-        <v>38400</v>
+        <v>36000</v>
       </c>
       <c r="O720" t="n">
-        <v>1728000</v>
+        <v>1620000</v>
       </c>
       <c r="P720" t="n">
         <v>45000</v>
@@ -34621,10 +34621,10 @@
         <v>38</v>
       </c>
       <c r="N754" t="n">
-        <v>4598.7284768212</v>
+        <v>4576</v>
       </c>
       <c r="O754" t="n">
-        <v>174751.6821192056</v>
+        <v>173888</v>
       </c>
       <c r="P754" t="n">
         <v>5900</v>
@@ -36660,10 +36660,10 @@
         <v>245</v>
       </c>
       <c r="N798" t="n">
-        <v>4566.0211267606</v>
+        <v>4550</v>
       </c>
       <c r="O798" t="n">
-        <v>1118675.176056347</v>
+        <v>1114750</v>
       </c>
       <c r="P798" t="n">
         <v>5500</v>

--- a/bodegas/LJ-05.xlsx
+++ b/bodegas/LJ-05.xlsx
@@ -7181,10 +7181,10 @@
         <v>208</v>
       </c>
       <c r="N158" t="n">
-        <v>2582.2554027233</v>
+        <v>2582.2553995381</v>
       </c>
       <c r="O158" t="n">
-        <v>537109.1237664464</v>
+        <v>537109.1231039248</v>
       </c>
       <c r="P158" t="n">
         <v>4500</v>
@@ -10773,10 +10773,10 @@
         <v>63</v>
       </c>
       <c r="N237" t="n">
-        <v>11921.4</v>
+        <v>11949.297191888</v>
       </c>
       <c r="O237" t="n">
-        <v>751048.2</v>
+        <v>752805.723088944</v>
       </c>
       <c r="P237" t="n">
         <v>19900</v>
@@ -10953,10 +10953,10 @@
         <v>223</v>
       </c>
       <c r="N241" t="n">
-        <v>2403.5147075539</v>
+        <v>2403.51472848</v>
       </c>
       <c r="O241" t="n">
-        <v>535983.7797845197</v>
+        <v>535983.78445104</v>
       </c>
       <c r="P241" t="n">
         <v>3500</v>
@@ -13949,10 +13949,10 @@
         <v>14</v>
       </c>
       <c r="N309" t="n">
-        <v>8332.779613402099</v>
+        <v>8397.710363636401</v>
       </c>
       <c r="O309" t="n">
-        <v>116658.9145876294</v>
+        <v>117567.9450909096</v>
       </c>
       <c r="P309" t="n">
         <v>14900</v>
@@ -16460,10 +16460,10 @@
         <v>10</v>
       </c>
       <c r="N364" t="n">
-        <v>26956</v>
+        <v>28079.166666667</v>
       </c>
       <c r="O364" t="n">
-        <v>269560</v>
+        <v>280791.66666667</v>
       </c>
       <c r="P364" t="n">
         <v>44900</v>
@@ -19743,10 +19743,10 @@
         <v>84</v>
       </c>
       <c r="N435" t="n">
-        <v>3903.7383067896</v>
+        <v>3903.7383529412</v>
       </c>
       <c r="O435" t="n">
-        <v>327914.0177703264</v>
+        <v>327914.0216470608</v>
       </c>
       <c r="P435" t="n">
         <v>7500</v>
@@ -26053,10 +26053,10 @@
         <v>456</v>
       </c>
       <c r="N572" t="n">
-        <v>517.29287307808</v>
+        <v>517.2929433161599</v>
       </c>
       <c r="O572" t="n">
-        <v>235885.5501236045</v>
+        <v>235885.5821521689</v>
       </c>
       <c r="P572" t="n">
         <v>900</v>
@@ -26284,10 +26284,10 @@
         <v>8</v>
       </c>
       <c r="N577" t="n">
-        <v>3110.8397028838</v>
+        <v>3110.8396848556</v>
       </c>
       <c r="O577" t="n">
-        <v>24886.7176230704</v>
+        <v>24886.7174788448</v>
       </c>
       <c r="P577" t="n">
         <v>4500</v>

--- a/bodegas/LJ-05.xlsx
+++ b/bodegas/LJ-05.xlsx
@@ -10947,22 +10947,22 @@
         <v>0</v>
       </c>
       <c r="L241" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M241" t="n">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="N241" t="n">
-        <v>2403.515543043</v>
+        <v>2403.5155820371</v>
       </c>
       <c r="O241" t="n">
-        <v>521562.872840331</v>
+        <v>507141.7878098281</v>
       </c>
       <c r="P241" t="n">
         <v>3500</v>
       </c>
       <c r="Q241" t="n">
-        <v>759500</v>
+        <v>738500</v>
       </c>
     </row>
     <row r="242">
@@ -24137,22 +24137,22 @@
         <v>0</v>
       </c>
       <c r="L531" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M531" t="n">
-        <v>512</v>
+        <v>500</v>
       </c>
       <c r="N531" t="n">
         <v>1801</v>
       </c>
       <c r="O531" t="n">
-        <v>922112</v>
+        <v>900500</v>
       </c>
       <c r="P531" t="n">
         <v>2900</v>
       </c>
       <c r="Q531" t="n">
-        <v>1484800</v>
+        <v>1450000</v>
       </c>
     </row>
     <row r="532">
@@ -26279,10 +26279,10 @@
         <v>991</v>
       </c>
       <c r="N577" t="n">
-        <v>703.79488487659</v>
+        <v>703.79488357273</v>
       </c>
       <c r="O577" t="n">
-        <v>697460.7309127006</v>
+        <v>697460.7296205754</v>
       </c>
       <c r="P577" t="n">
         <v>900</v>
@@ -31854,22 +31854,22 @@
         <v>0</v>
       </c>
       <c r="L694" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M694" t="n">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="N694" t="n">
         <v>5077</v>
       </c>
       <c r="O694" t="n">
-        <v>421391</v>
+        <v>390929</v>
       </c>
       <c r="P694" t="n">
         <v>8500</v>
       </c>
       <c r="Q694" t="n">
-        <v>705500</v>
+        <v>654500</v>
       </c>
     </row>
     <row r="695">

--- a/bodegas/LJ-05.xlsx
+++ b/bodegas/LJ-05.xlsx
@@ -865,10 +865,10 @@
         <v>10</v>
       </c>
       <c r="N11" t="n">
-        <v>27108.144192256</v>
+        <v>27000</v>
       </c>
       <c r="O11" t="n">
-        <v>271081.44192256</v>
+        <v>270000</v>
       </c>
       <c r="P11" t="n">
         <v>20000</v>
@@ -989,10 +989,10 @@
         <v>7</v>
       </c>
       <c r="N14" t="n">
-        <v>27117.391304348</v>
+        <v>27000</v>
       </c>
       <c r="O14" t="n">
-        <v>189821.739130436</v>
+        <v>189000</v>
       </c>
       <c r="P14" t="n">
         <v>30000</v>
@@ -4000,10 +4000,10 @@
         <v>10</v>
       </c>
       <c r="N85" t="n">
-        <v>27229.787234043</v>
+        <v>27000</v>
       </c>
       <c r="O85" t="n">
-        <v>272297.87234043</v>
+        <v>270000</v>
       </c>
       <c r="P85" t="n">
         <v>20000</v>
@@ -7273,10 +7273,10 @@
         <v>79</v>
       </c>
       <c r="N160" t="n">
-        <v>5224.6087374335</v>
+        <v>5216.895993495</v>
       </c>
       <c r="O160" t="n">
-        <v>412744.0902572465</v>
+        <v>412134.783486105</v>
       </c>
       <c r="P160" t="n">
         <v>8500</v>
@@ -7958,10 +7958,10 @@
         <v>62</v>
       </c>
       <c r="N175" t="n">
-        <v>4903.3514603175</v>
+        <v>4890.9300507937</v>
       </c>
       <c r="O175" t="n">
-        <v>304007.790539685</v>
+        <v>303237.6631492094</v>
       </c>
       <c r="P175" t="n">
         <v>8200</v>
@@ -8821,10 +8821,10 @@
         <v>62</v>
       </c>
       <c r="N194" t="n">
-        <v>8184.2747524752</v>
+        <v>8154</v>
       </c>
       <c r="O194" t="n">
-        <v>507425.0346534624</v>
+        <v>505548</v>
       </c>
       <c r="P194" t="n">
         <v>13500</v>
@@ -8867,10 +8867,10 @@
         <v>30</v>
       </c>
       <c r="N195" t="n">
-        <v>14831.411358927</v>
+        <v>14822.378829982</v>
       </c>
       <c r="O195" t="n">
-        <v>444942.34076781</v>
+        <v>444671.36489946</v>
       </c>
       <c r="P195" t="n">
         <v>24900</v>
@@ -10773,10 +10773,10 @@
         <v>63</v>
       </c>
       <c r="N237" t="n">
-        <v>11959.066350711</v>
+        <v>11921.4</v>
       </c>
       <c r="O237" t="n">
-        <v>753421.180094793</v>
+        <v>751048.2</v>
       </c>
       <c r="P237" t="n">
         <v>19900</v>
@@ -11496,10 +11496,10 @@
         <v>6</v>
       </c>
       <c r="N253" t="n">
-        <v>17970.414</v>
+        <v>16336.74</v>
       </c>
       <c r="O253" t="n">
-        <v>107822.484</v>
+        <v>98020.44</v>
       </c>
       <c r="P253" t="n">
         <v>30900</v>
@@ -12134,10 +12134,10 @@
         <v>19</v>
       </c>
       <c r="N268" t="n">
-        <v>22541.90975</v>
+        <v>22485.6955</v>
       </c>
       <c r="O268" t="n">
-        <v>428296.28525</v>
+        <v>427228.2145</v>
       </c>
       <c r="P268" t="n">
         <v>36500</v>
@@ -12257,10 +12257,10 @@
         <v>2</v>
       </c>
       <c r="N271" t="n">
-        <v>39703.055555556</v>
+        <v>38630</v>
       </c>
       <c r="O271" t="n">
-        <v>79406.111111112</v>
+        <v>77260</v>
       </c>
       <c r="P271" t="n">
         <v>46500</v>
@@ -12347,10 +12347,10 @@
         <v>5</v>
       </c>
       <c r="N273" t="n">
-        <v>24573.894298246</v>
+        <v>24538.02</v>
       </c>
       <c r="O273" t="n">
-        <v>122869.47149123</v>
+        <v>122690.1</v>
       </c>
       <c r="P273" t="n">
         <v>52900</v>
@@ -13187,10 +13187,10 @@
         <v>22</v>
       </c>
       <c r="N292" t="n">
-        <v>11594.699548023</v>
+        <v>11562.038418079</v>
       </c>
       <c r="O292" t="n">
-        <v>255083.390056506</v>
+        <v>254364.845197738</v>
       </c>
       <c r="P292" t="n">
         <v>18500</v>
@@ -13371,10 +13371,10 @@
         <v>36</v>
       </c>
       <c r="N296" t="n">
-        <v>22690.398811881</v>
+        <v>21418.04</v>
       </c>
       <c r="O296" t="n">
-        <v>816854.357227716</v>
+        <v>771049.4400000001</v>
       </c>
       <c r="P296" t="n">
         <v>34900</v>
@@ -13734,10 +13734,10 @@
         <v>9</v>
       </c>
       <c r="N304" t="n">
-        <v>27232.25996</v>
+        <v>27123.76488</v>
       </c>
       <c r="O304" t="n">
-        <v>245090.33964</v>
+        <v>244113.88392</v>
       </c>
       <c r="P304" t="n">
         <v>44500</v>
@@ -14174,10 +14174,10 @@
         <v>31</v>
       </c>
       <c r="N314" t="n">
-        <v>27011.040935673</v>
+        <v>26854</v>
       </c>
       <c r="O314" t="n">
-        <v>837342.269005863</v>
+        <v>832474</v>
       </c>
       <c r="P314" t="n">
         <v>43900</v>
@@ -14656,10 +14656,10 @@
         <v>33</v>
       </c>
       <c r="N325" t="n">
-        <v>13079.564264151</v>
+        <v>12981.59</v>
       </c>
       <c r="O325" t="n">
-        <v>431625.620716983</v>
+        <v>428392.47</v>
       </c>
       <c r="P325" t="n">
         <v>21900</v>
@@ -18731,10 +18731,10 @@
         <v>10</v>
       </c>
       <c r="N413" t="n">
-        <v>27408.335664336</v>
+        <v>27218</v>
       </c>
       <c r="O413" t="n">
-        <v>274083.35664336</v>
+        <v>272180</v>
       </c>
       <c r="P413" t="n">
         <v>43900</v>
@@ -19191,10 +19191,10 @@
         <v>53</v>
       </c>
       <c r="N423" t="n">
-        <v>4567.8948290973</v>
+        <v>4544</v>
       </c>
       <c r="O423" t="n">
-        <v>242098.4259421569</v>
+        <v>240832</v>
       </c>
       <c r="P423" t="n">
         <v>7900</v>
@@ -19237,10 +19237,10 @@
         <v>19</v>
       </c>
       <c r="N424" t="n">
-        <v>13948.467680608</v>
+        <v>13922</v>
       </c>
       <c r="O424" t="n">
-        <v>265020.885931552</v>
+        <v>264518</v>
       </c>
       <c r="P424" t="n">
         <v>22900</v>
@@ -19329,10 +19329,10 @@
         <v>10</v>
       </c>
       <c r="N426" t="n">
-        <v>25260.382352941</v>
+        <v>25076</v>
       </c>
       <c r="O426" t="n">
-        <v>252603.82352941</v>
+        <v>250760</v>
       </c>
       <c r="P426" t="n">
         <v>40900</v>
@@ -20285,10 +20285,10 @@
         <v>10</v>
       </c>
       <c r="N447" t="n">
-        <v>10198.963414634</v>
+        <v>9839</v>
       </c>
       <c r="O447" t="n">
-        <v>101989.63414634</v>
+        <v>98390</v>
       </c>
       <c r="P447" t="n">
         <v>16900</v>
@@ -20607,10 +20607,10 @@
         <v>10</v>
       </c>
       <c r="N454" t="n">
-        <v>13121.945155393</v>
+        <v>13098</v>
       </c>
       <c r="O454" t="n">
-        <v>131219.45155393</v>
+        <v>130980</v>
       </c>
       <c r="P454" t="n">
         <v>21200</v>
@@ -21389,10 +21389,10 @@
         <v>143</v>
       </c>
       <c r="N471" t="n">
-        <v>17123.621290098</v>
+        <v>17075.989518828</v>
       </c>
       <c r="O471" t="n">
-        <v>2448677.844484014</v>
+        <v>2441866.501192404</v>
       </c>
       <c r="P471" t="n">
         <v>27500</v>
@@ -21660,10 +21660,10 @@
         <v>22</v>
       </c>
       <c r="N477" t="n">
-        <v>21666.992481203</v>
+        <v>21346</v>
       </c>
       <c r="O477" t="n">
-        <v>476673.834586466</v>
+        <v>469612</v>
       </c>
       <c r="P477" t="n">
         <v>34900</v>
@@ -21847,10 +21847,10 @@
         <v>17</v>
       </c>
       <c r="N481" t="n">
-        <v>17325.987730061</v>
+        <v>17168</v>
       </c>
       <c r="O481" t="n">
-        <v>294541.791411037</v>
+        <v>291856</v>
       </c>
       <c r="P481" t="n">
         <v>27900</v>
@@ -21893,10 +21893,10 @@
         <v>6</v>
       </c>
       <c r="N482" t="n">
-        <v>20944.88372093</v>
+        <v>20014</v>
       </c>
       <c r="O482" t="n">
-        <v>125669.30232558</v>
+        <v>120084</v>
       </c>
       <c r="P482" t="n">
         <v>33900</v>
@@ -21939,10 +21939,10 @@
         <v>16</v>
       </c>
       <c r="N483" t="n">
-        <v>27289.075933076</v>
+        <v>27254</v>
       </c>
       <c r="O483" t="n">
-        <v>436625.214929216</v>
+        <v>436064</v>
       </c>
       <c r="P483" t="n">
         <v>43900</v>
@@ -22169,10 +22169,10 @@
         <v>101</v>
       </c>
       <c r="N488" t="n">
-        <v>40316.604863222</v>
+        <v>40073</v>
       </c>
       <c r="O488" t="n">
-        <v>4071977.091185422</v>
+        <v>4047373</v>
       </c>
       <c r="P488" t="n">
         <v>64900</v>
@@ -22353,10 +22353,10 @@
         <v>35</v>
       </c>
       <c r="N492" t="n">
-        <v>8721.297429620599</v>
+        <v>8700</v>
       </c>
       <c r="O492" t="n">
-        <v>305245.410036721</v>
+        <v>304500</v>
       </c>
       <c r="P492" t="n">
         <v>14900</v>
@@ -29320,10 +29320,10 @@
         <v>76</v>
       </c>
       <c r="N640" t="n">
-        <v>2830.7108053691</v>
+        <v>2356.29</v>
       </c>
       <c r="O640" t="n">
-        <v>215134.0212080516</v>
+        <v>179078.04</v>
       </c>
       <c r="P640" t="n">
         <v>6500</v>
@@ -30694,10 +30694,10 @@
         <v>12</v>
       </c>
       <c r="N669" t="n">
-        <v>24492.510949367</v>
+        <v>24338.47</v>
       </c>
       <c r="O669" t="n">
-        <v>293910.131392404</v>
+        <v>292061.64</v>
       </c>
       <c r="P669" t="n">
         <v>27900</v>
